--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_B8C9EA5BF9E03FB49704B73D6D37A37138B34E99" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AD8D666-4B18-4823-B40A-EEDBBB097EDA}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_B8C9EA5BF9E03FB49704B73D6D37A37138B34E99" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F733B7B-2695-4D68-BC14-9AD1FD38987B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -275,7 +275,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -343,14 +343,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -656,6 +656,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I2141"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -16350,7 +16353,7 @@
       <c r="A542">
         <v>193</v>
       </c>
-      <c r="B542" s="5" t="s">
+      <c r="B542" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C542" t="s">
@@ -16379,7 +16382,7 @@
       <c r="A543">
         <v>193</v>
       </c>
-      <c r="B543" s="5" t="s">
+      <c r="B543" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C543" t="s">
@@ -16408,7 +16411,7 @@
       <c r="A544">
         <v>193</v>
       </c>
-      <c r="B544" s="5" t="s">
+      <c r="B544" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C544" t="s">
@@ -16437,7 +16440,7 @@
       <c r="A545">
         <v>193</v>
       </c>
-      <c r="B545" s="5" t="s">
+      <c r="B545" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C545" t="s">
@@ -16466,7 +16469,7 @@
       <c r="A546">
         <v>193</v>
       </c>
-      <c r="B546" s="5" t="s">
+      <c r="B546" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C546" t="s">
@@ -16495,7 +16498,7 @@
       <c r="A547">
         <v>193</v>
       </c>
-      <c r="B547" s="5" t="s">
+      <c r="B547" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C547" t="s">
@@ -16524,7 +16527,7 @@
       <c r="A548">
         <v>193</v>
       </c>
-      <c r="B548" s="5" t="s">
+      <c r="B548" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C548" t="s">
@@ -16553,7 +16556,7 @@
       <c r="A549">
         <v>193</v>
       </c>
-      <c r="B549" s="5" t="s">
+      <c r="B549" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C549" t="s">
@@ -16582,7 +16585,7 @@
       <c r="A550">
         <v>193</v>
       </c>
-      <c r="B550" s="5" t="s">
+      <c r="B550" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C550" t="s">
@@ -16611,7 +16614,7 @@
       <c r="A551">
         <v>193</v>
       </c>
-      <c r="B551" s="5" t="s">
+      <c r="B551" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C551" t="s">
@@ -16640,7 +16643,7 @@
       <c r="A552">
         <v>193</v>
       </c>
-      <c r="B552" s="5" t="s">
+      <c r="B552" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C552" t="s">
@@ -16669,7 +16672,7 @@
       <c r="A553">
         <v>193</v>
       </c>
-      <c r="B553" s="5" t="s">
+      <c r="B553" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C553" t="s">
@@ -16698,7 +16701,7 @@
       <c r="A554">
         <v>193</v>
       </c>
-      <c r="B554" s="5" t="s">
+      <c r="B554" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C554" t="s">
@@ -16727,7 +16730,7 @@
       <c r="A555">
         <v>193</v>
       </c>
-      <c r="B555" s="5" t="s">
+      <c r="B555" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C555" t="s">
@@ -16756,7 +16759,7 @@
       <c r="A556">
         <v>193</v>
       </c>
-      <c r="B556" s="5" t="s">
+      <c r="B556" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C556" t="s">
@@ -16785,7 +16788,7 @@
       <c r="A557">
         <v>193</v>
       </c>
-      <c r="B557" s="5" t="s">
+      <c r="B557" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C557" t="s">
@@ -16814,7 +16817,7 @@
       <c r="A558">
         <v>193</v>
       </c>
-      <c r="B558" s="5" t="s">
+      <c r="B558" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C558" t="s">
@@ -16843,7 +16846,7 @@
       <c r="A559">
         <v>193</v>
       </c>
-      <c r="B559" s="5" t="s">
+      <c r="B559" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C559" t="s">
@@ -16872,7 +16875,7 @@
       <c r="A560">
         <v>193</v>
       </c>
-      <c r="B560" s="5" t="s">
+      <c r="B560" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C560" t="s">
@@ -16901,7 +16904,7 @@
       <c r="A561">
         <v>193</v>
       </c>
-      <c r="B561" s="5" t="s">
+      <c r="B561" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C561" t="s">
@@ -16930,7 +16933,7 @@
       <c r="A562">
         <v>193</v>
       </c>
-      <c r="B562" s="5" t="s">
+      <c r="B562" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C562" t="s">
@@ -16959,7 +16962,7 @@
       <c r="A563">
         <v>193</v>
       </c>
-      <c r="B563" s="5" t="s">
+      <c r="B563" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C563" t="s">
@@ -16988,7 +16991,7 @@
       <c r="A564">
         <v>193</v>
       </c>
-      <c r="B564" s="5" t="s">
+      <c r="B564" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C564" t="s">
@@ -17017,7 +17020,7 @@
       <c r="A565">
         <v>193</v>
       </c>
-      <c r="B565" s="5" t="s">
+      <c r="B565" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C565" t="s">
@@ -17046,7 +17049,7 @@
       <c r="A566">
         <v>193</v>
       </c>
-      <c r="B566" s="5" t="s">
+      <c r="B566" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C566" t="s">
@@ -17075,7 +17078,7 @@
       <c r="A567">
         <v>193</v>
       </c>
-      <c r="B567" s="5" t="s">
+      <c r="B567" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C567" t="s">
@@ -17104,7 +17107,7 @@
       <c r="A568">
         <v>193</v>
       </c>
-      <c r="B568" s="5" t="s">
+      <c r="B568" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C568" t="s">
@@ -17133,7 +17136,7 @@
       <c r="A569">
         <v>193</v>
       </c>
-      <c r="B569" s="5" t="s">
+      <c r="B569" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C569" t="s">
@@ -17162,7 +17165,7 @@
       <c r="A570">
         <v>193</v>
       </c>
-      <c r="B570" s="5" t="s">
+      <c r="B570" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C570" t="s">
@@ -17191,7 +17194,7 @@
       <c r="A571">
         <v>193</v>
       </c>
-      <c r="B571" s="5" t="s">
+      <c r="B571" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C571" t="s">
@@ -17220,7 +17223,7 @@
       <c r="A572">
         <v>193</v>
       </c>
-      <c r="B572" s="5" t="s">
+      <c r="B572" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C572" t="s">
@@ -17249,7 +17252,7 @@
       <c r="A573">
         <v>193</v>
       </c>
-      <c r="B573" s="5" t="s">
+      <c r="B573" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C573" t="s">
@@ -17278,7 +17281,7 @@
       <c r="A574">
         <v>193</v>
       </c>
-      <c r="B574" s="5" t="s">
+      <c r="B574" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C574" t="s">
@@ -17307,7 +17310,7 @@
       <c r="A575">
         <v>193</v>
       </c>
-      <c r="B575" s="5" t="s">
+      <c r="B575" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C575" t="s">
@@ -17336,7 +17339,7 @@
       <c r="A576">
         <v>193</v>
       </c>
-      <c r="B576" s="5" t="s">
+      <c r="B576" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C576" t="s">
@@ -17365,7 +17368,7 @@
       <c r="A577">
         <v>193</v>
       </c>
-      <c r="B577" s="5" t="s">
+      <c r="B577" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C577" t="s">
@@ -17394,7 +17397,7 @@
       <c r="A578">
         <v>193</v>
       </c>
-      <c r="B578" s="5" t="s">
+      <c r="B578" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C578" t="s">
@@ -17423,7 +17426,7 @@
       <c r="A579">
         <v>193</v>
       </c>
-      <c r="B579" s="5" t="s">
+      <c r="B579" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C579" t="s">
@@ -17452,7 +17455,7 @@
       <c r="A580">
         <v>193</v>
       </c>
-      <c r="B580" s="5" t="s">
+      <c r="B580" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C580" t="s">
@@ -17481,7 +17484,7 @@
       <c r="A581">
         <v>193</v>
       </c>
-      <c r="B581" s="5" t="s">
+      <c r="B581" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C581" t="s">
@@ -17510,7 +17513,7 @@
       <c r="A582">
         <v>193</v>
       </c>
-      <c r="B582" s="5" t="s">
+      <c r="B582" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C582" t="s">
@@ -17539,7 +17542,7 @@
       <c r="A583">
         <v>193</v>
       </c>
-      <c r="B583" s="5" t="s">
+      <c r="B583" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C583" t="s">
@@ -17568,7 +17571,7 @@
       <c r="A584">
         <v>193</v>
       </c>
-      <c r="B584" s="5" t="s">
+      <c r="B584" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C584" t="s">
@@ -17597,7 +17600,7 @@
       <c r="A585">
         <v>193</v>
       </c>
-      <c r="B585" s="5" t="s">
+      <c r="B585" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C585" t="s">
@@ -17626,7 +17629,7 @@
       <c r="A586">
         <v>193</v>
       </c>
-      <c r="B586" s="5" t="s">
+      <c r="B586" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C586" t="s">
@@ -17655,7 +17658,7 @@
       <c r="A587">
         <v>193</v>
       </c>
-      <c r="B587" s="5" t="s">
+      <c r="B587" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C587" t="s">
@@ -17684,7 +17687,7 @@
       <c r="A588">
         <v>193</v>
       </c>
-      <c r="B588" s="5" t="s">
+      <c r="B588" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C588" t="s">
@@ -17713,7 +17716,7 @@
       <c r="A589">
         <v>193</v>
       </c>
-      <c r="B589" s="5" t="s">
+      <c r="B589" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C589" t="s">
@@ -17742,7 +17745,7 @@
       <c r="A590">
         <v>193</v>
       </c>
-      <c r="B590" s="5" t="s">
+      <c r="B590" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C590" t="s">
@@ -17771,7 +17774,7 @@
       <c r="A591">
         <v>193</v>
       </c>
-      <c r="B591" s="5" t="s">
+      <c r="B591" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C591" t="s">
@@ -17800,7 +17803,7 @@
       <c r="A592">
         <v>193</v>
       </c>
-      <c r="B592" s="5" t="s">
+      <c r="B592" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C592" t="s">
@@ -17829,7 +17832,7 @@
       <c r="A593">
         <v>193</v>
       </c>
-      <c r="B593" s="5" t="s">
+      <c r="B593" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C593" t="s">
@@ -17858,7 +17861,7 @@
       <c r="A594">
         <v>193</v>
       </c>
-      <c r="B594" s="5" t="s">
+      <c r="B594" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C594" t="s">
@@ -17887,7 +17890,7 @@
       <c r="A595">
         <v>193</v>
       </c>
-      <c r="B595" s="5" t="s">
+      <c r="B595" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C595" t="s">
@@ -17916,7 +17919,7 @@
       <c r="A596">
         <v>193</v>
       </c>
-      <c r="B596" s="5" t="s">
+      <c r="B596" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C596" t="s">
@@ -17945,7 +17948,7 @@
       <c r="A597">
         <v>193</v>
       </c>
-      <c r="B597" s="5" t="s">
+      <c r="B597" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C597" t="s">
@@ -17974,7 +17977,7 @@
       <c r="A598">
         <v>193</v>
       </c>
-      <c r="B598" s="5" t="s">
+      <c r="B598" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C598" t="s">
@@ -18003,7 +18006,7 @@
       <c r="A599">
         <v>193</v>
       </c>
-      <c r="B599" s="5" t="s">
+      <c r="B599" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C599" t="s">
@@ -18032,7 +18035,7 @@
       <c r="A600">
         <v>193</v>
       </c>
-      <c r="B600" s="5" t="s">
+      <c r="B600" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C600" t="s">
@@ -18061,7 +18064,7 @@
       <c r="A601">
         <v>193</v>
       </c>
-      <c r="B601" s="5" t="s">
+      <c r="B601" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C601" t="s">
@@ -52906,7 +52909,7 @@
         <v>12</v>
       </c>
       <c r="G1802">
-        <v>14629.55</v>
+        <v>14329.55</v>
       </c>
       <c r="H1802">
         <v>14629.55</v>
@@ -52935,7 +52938,7 @@
         <v>12</v>
       </c>
       <c r="G1803">
-        <v>16019.19</v>
+        <v>15319.19</v>
       </c>
       <c r="H1803">
         <v>16019.19</v>
@@ -52964,7 +52967,7 @@
         <v>12</v>
       </c>
       <c r="G1804">
-        <v>17409.03</v>
+        <v>16409.03</v>
       </c>
       <c r="H1804">
         <v>17409.03</v>
@@ -52993,7 +52996,7 @@
         <v>12</v>
       </c>
       <c r="G1805">
-        <v>18794.27</v>
+        <v>17794.27</v>
       </c>
       <c r="H1805">
         <v>18794.27</v>
@@ -53022,7 +53025,7 @@
         <v>12</v>
       </c>
       <c r="G1806">
-        <v>20170.89</v>
+        <v>19170.89</v>
       </c>
       <c r="H1806">
         <v>20170.89</v>
@@ -53051,7 +53054,7 @@
         <v>12</v>
       </c>
       <c r="G1807">
-        <v>21535.59</v>
+        <v>20535.59</v>
       </c>
       <c r="H1807">
         <v>21535.59</v>
@@ -53080,7 +53083,7 @@
         <v>12</v>
       </c>
       <c r="G1808">
-        <v>22885.62</v>
+        <v>20885.62</v>
       </c>
       <c r="H1808">
         <v>21054.77</v>
@@ -53109,7 +53112,7 @@
         <v>12</v>
       </c>
       <c r="G1809">
-        <v>24218.77</v>
+        <v>20218.77</v>
       </c>
       <c r="H1809">
         <v>22281.26</v>
@@ -53138,10 +53141,10 @@
         <v>12</v>
       </c>
       <c r="G1810">
-        <v>25533.25</v>
+        <v>23533.25</v>
       </c>
       <c r="H1810">
-        <v>27093.439999999999</v>
+        <v>25093.439999999999</v>
       </c>
       <c r="I1810">
         <v>27093.439999999999</v>
@@ -53170,7 +53173,7 @@
         <v>26827.67</v>
       </c>
       <c r="H1811">
-        <v>28596.76</v>
+        <v>27596.76</v>
       </c>
       <c r="I1811">
         <v>28596.76</v>
@@ -76113,7 +76116,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>56</v>
       </c>
       <c r="B2" s="3">
@@ -76133,7 +76136,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
+      <c r="A3" s="5"/>
       <c r="B3" s="3">
         <v>46753</v>
       </c>
@@ -76151,7 +76154,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="4"/>
+      <c r="A4" s="5"/>
       <c r="B4" s="3">
         <v>47119</v>
       </c>
@@ -76169,7 +76172,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
+      <c r="A5" s="5"/>
       <c r="B5" s="3">
         <v>47484</v>
       </c>
@@ -76187,7 +76190,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
+      <c r="A6" s="5"/>
       <c r="B6" s="3">
         <v>47849</v>
       </c>
@@ -76205,7 +76208,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
+      <c r="A7" s="5"/>
       <c r="B7" s="3">
         <v>48214</v>
       </c>
@@ -76223,7 +76226,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="4"/>
+      <c r="A8" s="5"/>
       <c r="B8" s="3">
         <v>48580</v>
       </c>
@@ -76241,7 +76244,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
+      <c r="A9" s="5"/>
       <c r="B9" s="3">
         <v>48945</v>
       </c>
@@ -76259,7 +76262,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="4"/>
+      <c r="A10" s="5"/>
       <c r="B10" s="3">
         <v>49310</v>
       </c>
@@ -76277,7 +76280,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
+      <c r="A11" s="5"/>
       <c r="B11" s="3">
         <v>49675</v>
       </c>
@@ -76295,7 +76298,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>50</v>
       </c>
       <c r="B12" s="3">
@@ -76315,7 +76318,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="4"/>
+      <c r="A13" s="5"/>
       <c r="B13" s="3">
         <v>46204</v>
       </c>
@@ -76333,7 +76336,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="4"/>
+      <c r="A14" s="5"/>
       <c r="B14" s="3">
         <v>46388</v>
       </c>
@@ -76351,7 +76354,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
+      <c r="A15" s="5"/>
       <c r="B15" s="3">
         <v>46569</v>
       </c>
@@ -76369,7 +76372,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
+      <c r="A16" s="5"/>
       <c r="B16" s="3">
         <v>46753</v>
       </c>
@@ -76387,7 +76390,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
+      <c r="A17" s="5"/>
       <c r="B17" s="3">
         <v>46935</v>
       </c>
@@ -76405,7 +76408,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="4"/>
+      <c r="A18" s="5"/>
       <c r="B18" s="3">
         <v>47119</v>
       </c>
@@ -76423,7 +76426,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
+      <c r="A19" s="5"/>
       <c r="B19" s="3">
         <v>47300</v>
       </c>
@@ -76441,7 +76444,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
+      <c r="A20" s="5"/>
       <c r="B20" s="3">
         <v>47484</v>
       </c>
@@ -76459,7 +76462,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
+      <c r="A21" s="5"/>
       <c r="B21" s="3">
         <v>47665</v>
       </c>
@@ -76477,7 +76480,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B22" s="3">
@@ -76503,7 +76506,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
+      <c r="A23" s="5"/>
       <c r="B23" s="3">
         <v>46204</v>
       </c>
@@ -76527,7 +76530,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="4"/>
+      <c r="A24" s="5"/>
       <c r="B24" s="3">
         <v>46388</v>
       </c>
@@ -76551,7 +76554,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="4"/>
+      <c r="A25" s="5"/>
       <c r="B25" s="3">
         <v>46569</v>
       </c>
@@ -76575,7 +76578,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="4"/>
+      <c r="A26" s="5"/>
       <c r="B26" s="3">
         <v>46753</v>
       </c>
@@ -76599,7 +76602,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="4"/>
+      <c r="A27" s="5"/>
       <c r="B27" s="3">
         <v>46935</v>
       </c>
@@ -76623,7 +76626,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="4"/>
+      <c r="A28" s="5"/>
       <c r="B28" s="3">
         <v>47119</v>
       </c>
@@ -76647,7 +76650,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="4"/>
+      <c r="A29" s="5"/>
       <c r="B29" s="3">
         <v>47300</v>
       </c>
@@ -76671,7 +76674,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="4"/>
+      <c r="A30" s="5"/>
       <c r="B30" s="3">
         <v>47484</v>
       </c>
@@ -76695,7 +76698,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="4"/>
+      <c r="A31" s="5"/>
       <c r="B31" s="3">
         <v>47665</v>
       </c>
@@ -76719,7 +76722,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="5" t="s">
         <v>57</v>
       </c>
       <c r="B32" s="3">
@@ -76739,7 +76742,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="4"/>
+      <c r="A33" s="5"/>
       <c r="B33" s="3">
         <v>46753</v>
       </c>
@@ -76757,7 +76760,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="4"/>
+      <c r="A34" s="5"/>
       <c r="B34" s="3">
         <v>47119</v>
       </c>
@@ -76775,7 +76778,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="4"/>
+      <c r="A35" s="5"/>
       <c r="B35" s="3">
         <v>47484</v>
       </c>
@@ -76793,7 +76796,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="4"/>
+      <c r="A36" s="5"/>
       <c r="B36" s="3">
         <v>47849</v>
       </c>
@@ -76811,7 +76814,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="4"/>
+      <c r="A37" s="5"/>
       <c r="B37" s="3">
         <v>48214</v>
       </c>
@@ -76829,7 +76832,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="4"/>
+      <c r="A38" s="5"/>
       <c r="B38" s="3">
         <v>48580</v>
       </c>
@@ -76847,7 +76850,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="4"/>
+      <c r="A39" s="5"/>
       <c r="B39" s="3">
         <v>48945</v>
       </c>
@@ -76865,7 +76868,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="4"/>
+      <c r="A40" s="5"/>
       <c r="B40" s="3">
         <v>49310</v>
       </c>
@@ -76883,7 +76886,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="4"/>
+      <c r="A41" s="5"/>
       <c r="B41" s="3">
         <v>49675</v>
       </c>
@@ -76901,7 +76904,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="5" t="s">
         <v>49</v>
       </c>
       <c r="B42" s="3">
@@ -76927,7 +76930,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="4"/>
+      <c r="A43" s="5"/>
       <c r="B43" s="3">
         <v>46204</v>
       </c>
@@ -76951,7 +76954,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="4"/>
+      <c r="A44" s="5"/>
       <c r="B44" s="3">
         <v>46388</v>
       </c>
@@ -76975,7 +76978,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="4"/>
+      <c r="A45" s="5"/>
       <c r="B45" s="3">
         <v>46569</v>
       </c>
@@ -76999,7 +77002,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="4"/>
+      <c r="A46" s="5"/>
       <c r="B46" s="3">
         <v>46753</v>
       </c>
@@ -77023,7 +77026,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="4"/>
+      <c r="A47" s="5"/>
       <c r="B47" s="3">
         <v>46935</v>
       </c>
@@ -77047,7 +77050,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="4"/>
+      <c r="A48" s="5"/>
       <c r="B48" s="3">
         <v>47119</v>
       </c>
@@ -77071,7 +77074,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="4"/>
+      <c r="A49" s="5"/>
       <c r="B49" s="3">
         <v>47300</v>
       </c>
@@ -77095,7 +77098,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="4"/>
+      <c r="A50" s="5"/>
       <c r="B50" s="3">
         <v>47484</v>
       </c>
@@ -77119,7 +77122,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="4"/>
+      <c r="A51" s="5"/>
       <c r="B51" s="3">
         <v>47665</v>
       </c>
@@ -77143,7 +77146,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B52" s="3">
@@ -77169,7 +77172,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="4"/>
+      <c r="A53" s="5"/>
       <c r="B53" s="3">
         <v>46204</v>
       </c>
@@ -77193,7 +77196,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="4"/>
+      <c r="A54" s="5"/>
       <c r="B54" s="3">
         <v>46388</v>
       </c>
@@ -77217,7 +77220,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="4"/>
+      <c r="A55" s="5"/>
       <c r="B55" s="3">
         <v>46569</v>
       </c>
@@ -77241,7 +77244,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="4"/>
+      <c r="A56" s="5"/>
       <c r="B56" s="3">
         <v>46753</v>
       </c>
@@ -77265,7 +77268,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="4"/>
+      <c r="A57" s="5"/>
       <c r="B57" s="3">
         <v>46935</v>
       </c>
@@ -77289,7 +77292,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="4"/>
+      <c r="A58" s="5"/>
       <c r="B58" s="3">
         <v>47119</v>
       </c>
@@ -77313,7 +77316,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="4"/>
+      <c r="A59" s="5"/>
       <c r="B59" s="3">
         <v>47300</v>
       </c>
@@ -77337,7 +77340,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="4"/>
+      <c r="A60" s="5"/>
       <c r="B60" s="3">
         <v>47484</v>
       </c>
@@ -77361,7 +77364,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="4"/>
+      <c r="A61" s="5"/>
       <c r="B61" s="3">
         <v>47665</v>
       </c>
@@ -77385,7 +77388,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B62" s="3">
@@ -77411,7 +77414,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="4"/>
+      <c r="A63" s="5"/>
       <c r="B63" s="3">
         <v>46204</v>
       </c>
@@ -77435,7 +77438,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="4"/>
+      <c r="A64" s="5"/>
       <c r="B64" s="3">
         <v>46388</v>
       </c>
@@ -77459,7 +77462,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="4"/>
+      <c r="A65" s="5"/>
       <c r="B65" s="3">
         <v>46569</v>
       </c>
@@ -77483,7 +77486,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="4"/>
+      <c r="A66" s="5"/>
       <c r="B66" s="3">
         <v>46753</v>
       </c>
@@ -77507,7 +77510,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="4"/>
+      <c r="A67" s="5"/>
       <c r="B67" s="3">
         <v>46935</v>
       </c>
@@ -77531,7 +77534,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="4"/>
+      <c r="A68" s="5"/>
       <c r="B68" s="3">
         <v>47119</v>
       </c>
@@ -77555,7 +77558,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="4"/>
+      <c r="A69" s="5"/>
       <c r="B69" s="3">
         <v>47300</v>
       </c>
@@ -77579,7 +77582,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="4"/>
+      <c r="A70" s="5"/>
       <c r="B70" s="3">
         <v>47484</v>
       </c>
@@ -77603,7 +77606,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="4"/>
+      <c r="A71" s="5"/>
       <c r="B71" s="3">
         <v>47665</v>
       </c>
@@ -77627,7 +77630,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B72" s="3">
@@ -77653,7 +77656,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="4"/>
+      <c r="A73" s="5"/>
       <c r="B73" s="3">
         <v>46753</v>
       </c>
@@ -77677,7 +77680,7 @@
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="4"/>
+      <c r="A74" s="5"/>
       <c r="B74" s="3">
         <v>47119</v>
       </c>
@@ -77701,7 +77704,7 @@
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="4"/>
+      <c r="A75" s="5"/>
       <c r="B75" s="3">
         <v>47484</v>
       </c>
@@ -77725,7 +77728,7 @@
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="4"/>
+      <c r="A76" s="5"/>
       <c r="B76" s="3">
         <v>47849</v>
       </c>
@@ -77749,7 +77752,7 @@
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="4"/>
+      <c r="A77" s="5"/>
       <c r="B77" s="3">
         <v>48214</v>
       </c>
@@ -77773,7 +77776,7 @@
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="4"/>
+      <c r="A78" s="5"/>
       <c r="B78" s="3">
         <v>48580</v>
       </c>
@@ -77797,7 +77800,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="4"/>
+      <c r="A79" s="5"/>
       <c r="B79" s="3">
         <v>48945</v>
       </c>
@@ -77821,7 +77824,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="4"/>
+      <c r="A80" s="5"/>
       <c r="B80" s="3">
         <v>49310</v>
       </c>
@@ -77845,7 +77848,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="4"/>
+      <c r="A81" s="5"/>
       <c r="B81" s="3">
         <v>49675</v>
       </c>
@@ -77869,7 +77872,7 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="4" t="s">
+      <c r="A82" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B82" s="3">
@@ -77895,7 +77898,7 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="4"/>
+      <c r="A83" s="5"/>
       <c r="B83" s="3">
         <v>46204</v>
       </c>
@@ -77919,7 +77922,7 @@
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="4"/>
+      <c r="A84" s="5"/>
       <c r="B84" s="3">
         <v>46388</v>
       </c>
@@ -77943,7 +77946,7 @@
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="4"/>
+      <c r="A85" s="5"/>
       <c r="B85" s="3">
         <v>46569</v>
       </c>
@@ -77967,7 +77970,7 @@
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="4"/>
+      <c r="A86" s="5"/>
       <c r="B86" s="3">
         <v>46753</v>
       </c>
@@ -77991,7 +77994,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="4"/>
+      <c r="A87" s="5"/>
       <c r="B87" s="3">
         <v>46935</v>
       </c>
@@ -78015,7 +78018,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="4"/>
+      <c r="A88" s="5"/>
       <c r="B88" s="3">
         <v>47119</v>
       </c>
@@ -78039,7 +78042,7 @@
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" s="4"/>
+      <c r="A89" s="5"/>
       <c r="B89" s="3">
         <v>47300</v>
       </c>
@@ -78063,7 +78066,7 @@
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="4"/>
+      <c r="A90" s="5"/>
       <c r="B90" s="3">
         <v>47484</v>
       </c>
@@ -78087,7 +78090,7 @@
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="4"/>
+      <c r="A91" s="5"/>
       <c r="B91" s="3">
         <v>47665</v>
       </c>
@@ -78111,7 +78114,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B92" s="3">
@@ -78137,7 +78140,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="4"/>
+      <c r="A93" s="5"/>
       <c r="B93" s="3">
         <v>46204</v>
       </c>
@@ -78161,7 +78164,7 @@
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="4"/>
+      <c r="A94" s="5"/>
       <c r="B94" s="3">
         <v>46388</v>
       </c>
@@ -78185,7 +78188,7 @@
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="4"/>
+      <c r="A95" s="5"/>
       <c r="B95" s="3">
         <v>46569</v>
       </c>
@@ -78209,7 +78212,7 @@
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="4"/>
+      <c r="A96" s="5"/>
       <c r="B96" s="3">
         <v>46753</v>
       </c>
@@ -78233,7 +78236,7 @@
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" s="4"/>
+      <c r="A97" s="5"/>
       <c r="B97" s="3">
         <v>46935</v>
       </c>
@@ -78257,7 +78260,7 @@
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="4"/>
+      <c r="A98" s="5"/>
       <c r="B98" s="3">
         <v>47119</v>
       </c>
@@ -78281,7 +78284,7 @@
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="4"/>
+      <c r="A99" s="5"/>
       <c r="B99" s="3">
         <v>47300</v>
       </c>
@@ -78305,7 +78308,7 @@
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="4"/>
+      <c r="A100" s="5"/>
       <c r="B100" s="3">
         <v>47484</v>
       </c>
@@ -78329,7 +78332,7 @@
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="4"/>
+      <c r="A101" s="5"/>
       <c r="B101" s="3">
         <v>47665</v>
       </c>
@@ -78353,7 +78356,7 @@
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="4" t="s">
+      <c r="A102" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B102" s="3">
@@ -78379,7 +78382,7 @@
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="4"/>
+      <c r="A103" s="5"/>
       <c r="B103" s="3">
         <v>46204</v>
       </c>
@@ -78403,7 +78406,7 @@
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="4"/>
+      <c r="A104" s="5"/>
       <c r="B104" s="3">
         <v>46388</v>
       </c>
@@ -78427,7 +78430,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="4"/>
+      <c r="A105" s="5"/>
       <c r="B105" s="3">
         <v>46569</v>
       </c>
@@ -78451,7 +78454,7 @@
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="4"/>
+      <c r="A106" s="5"/>
       <c r="B106" s="3">
         <v>46753</v>
       </c>
@@ -78475,7 +78478,7 @@
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="4"/>
+      <c r="A107" s="5"/>
       <c r="B107" s="3">
         <v>46935</v>
       </c>
@@ -78499,7 +78502,7 @@
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="4"/>
+      <c r="A108" s="5"/>
       <c r="B108" s="3">
         <v>47119</v>
       </c>
@@ -78523,7 +78526,7 @@
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" s="4"/>
+      <c r="A109" s="5"/>
       <c r="B109" s="3">
         <v>47300</v>
       </c>
@@ -78547,7 +78550,7 @@
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" s="4"/>
+      <c r="A110" s="5"/>
       <c r="B110" s="3">
         <v>47484</v>
       </c>
@@ -78571,7 +78574,7 @@
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="4"/>
+      <c r="A111" s="5"/>
       <c r="B111" s="3">
         <v>47665</v>
       </c>
@@ -78595,7 +78598,7 @@
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" s="4" t="s">
+      <c r="A112" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B112" s="3">
@@ -78621,7 +78624,7 @@
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" s="4"/>
+      <c r="A113" s="5"/>
       <c r="B113" s="3">
         <v>46204</v>
       </c>
@@ -78645,7 +78648,7 @@
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A114" s="4"/>
+      <c r="A114" s="5"/>
       <c r="B114" s="3">
         <v>46388</v>
       </c>
@@ -78669,7 +78672,7 @@
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" s="4"/>
+      <c r="A115" s="5"/>
       <c r="B115" s="3">
         <v>46569</v>
       </c>
@@ -78693,7 +78696,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A116" s="4"/>
+      <c r="A116" s="5"/>
       <c r="B116" s="3">
         <v>46753</v>
       </c>
@@ -78717,7 +78720,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" s="4"/>
+      <c r="A117" s="5"/>
       <c r="B117" s="3">
         <v>46935</v>
       </c>
@@ -78741,7 +78744,7 @@
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A118" s="4"/>
+      <c r="A118" s="5"/>
       <c r="B118" s="3">
         <v>47119</v>
       </c>
@@ -78765,7 +78768,7 @@
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A119" s="4"/>
+      <c r="A119" s="5"/>
       <c r="B119" s="3">
         <v>47300</v>
       </c>
@@ -78789,7 +78792,7 @@
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A120" s="4"/>
+      <c r="A120" s="5"/>
       <c r="B120" s="3">
         <v>47484</v>
       </c>
@@ -78813,7 +78816,7 @@
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A121" s="4"/>
+      <c r="A121" s="5"/>
       <c r="B121" s="3">
         <v>47665</v>
       </c>
@@ -78837,7 +78840,7 @@
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A122" s="4" t="s">
+      <c r="A122" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B122" s="3">
@@ -78857,7 +78860,7 @@
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A123" s="4"/>
+      <c r="A123" s="5"/>
       <c r="B123" s="3">
         <v>46753</v>
       </c>
@@ -78875,7 +78878,7 @@
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A124" s="4"/>
+      <c r="A124" s="5"/>
       <c r="B124" s="3">
         <v>47119</v>
       </c>
@@ -78893,7 +78896,7 @@
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A125" s="4"/>
+      <c r="A125" s="5"/>
       <c r="B125" s="3">
         <v>47484</v>
       </c>
@@ -78911,7 +78914,7 @@
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A126" s="4"/>
+      <c r="A126" s="5"/>
       <c r="B126" s="3">
         <v>47849</v>
       </c>
@@ -78929,7 +78932,7 @@
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A127" s="4"/>
+      <c r="A127" s="5"/>
       <c r="B127" s="3">
         <v>48214</v>
       </c>
@@ -78947,7 +78950,7 @@
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A128" s="4"/>
+      <c r="A128" s="5"/>
       <c r="B128" s="3">
         <v>48580</v>
       </c>
@@ -78965,7 +78968,7 @@
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A129" s="4"/>
+      <c r="A129" s="5"/>
       <c r="B129" s="3">
         <v>48945</v>
       </c>
@@ -78983,7 +78986,7 @@
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A130" s="4"/>
+      <c r="A130" s="5"/>
       <c r="B130" s="3">
         <v>49310</v>
       </c>
@@ -79001,7 +79004,7 @@
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A131" s="4"/>
+      <c r="A131" s="5"/>
       <c r="B131" s="3">
         <v>49675</v>
       </c>
@@ -79019,7 +79022,7 @@
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A132" s="4" t="s">
+      <c r="A132" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B132" s="3">
@@ -79045,7 +79048,7 @@
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A133" s="4"/>
+      <c r="A133" s="5"/>
       <c r="B133" s="3">
         <v>46204</v>
       </c>
@@ -79069,7 +79072,7 @@
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A134" s="4"/>
+      <c r="A134" s="5"/>
       <c r="B134" s="3">
         <v>46388</v>
       </c>
@@ -79093,7 +79096,7 @@
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A135" s="4"/>
+      <c r="A135" s="5"/>
       <c r="B135" s="3">
         <v>46569</v>
       </c>
@@ -79117,7 +79120,7 @@
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A136" s="4"/>
+      <c r="A136" s="5"/>
       <c r="B136" s="3">
         <v>46753</v>
       </c>
@@ -79141,7 +79144,7 @@
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A137" s="4"/>
+      <c r="A137" s="5"/>
       <c r="B137" s="3">
         <v>46935</v>
       </c>
@@ -79165,7 +79168,7 @@
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A138" s="4"/>
+      <c r="A138" s="5"/>
       <c r="B138" s="3">
         <v>47119</v>
       </c>
@@ -79189,7 +79192,7 @@
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A139" s="4"/>
+      <c r="A139" s="5"/>
       <c r="B139" s="3">
         <v>47300</v>
       </c>
@@ -79213,7 +79216,7 @@
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A140" s="4"/>
+      <c r="A140" s="5"/>
       <c r="B140" s="3">
         <v>47484</v>
       </c>
@@ -79237,7 +79240,7 @@
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A141" s="4"/>
+      <c r="A141" s="5"/>
       <c r="B141" s="3">
         <v>47665</v>
       </c>
@@ -79261,7 +79264,7 @@
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A142" s="4" t="s">
+      <c r="A142" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B142" s="3">
@@ -79281,7 +79284,7 @@
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A143" s="4"/>
+      <c r="A143" s="5"/>
       <c r="B143" s="3">
         <v>46753</v>
       </c>
@@ -79299,7 +79302,7 @@
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A144" s="4"/>
+      <c r="A144" s="5"/>
       <c r="B144" s="3">
         <v>47119</v>
       </c>
@@ -79317,7 +79320,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A145" s="4"/>
+      <c r="A145" s="5"/>
       <c r="B145" s="3">
         <v>47484</v>
       </c>
@@ -79335,7 +79338,7 @@
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A146" s="4"/>
+      <c r="A146" s="5"/>
       <c r="B146" s="3">
         <v>47849</v>
       </c>
@@ -79353,7 +79356,7 @@
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A147" s="4"/>
+      <c r="A147" s="5"/>
       <c r="B147" s="3">
         <v>48214</v>
       </c>
@@ -79371,7 +79374,7 @@
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A148" s="4"/>
+      <c r="A148" s="5"/>
       <c r="B148" s="3">
         <v>48580</v>
       </c>
@@ -79389,7 +79392,7 @@
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A149" s="4"/>
+      <c r="A149" s="5"/>
       <c r="B149" s="3">
         <v>48945</v>
       </c>
@@ -79407,7 +79410,7 @@
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A150" s="4"/>
+      <c r="A150" s="5"/>
       <c r="B150" s="3">
         <v>49310</v>
       </c>
@@ -79425,7 +79428,7 @@
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A151" s="4"/>
+      <c r="A151" s="5"/>
       <c r="B151" s="3">
         <v>49675</v>
       </c>
@@ -79443,7 +79446,7 @@
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A152" s="4" t="s">
+      <c r="A152" s="5" t="s">
         <v>46</v>
       </c>
       <c r="B152" s="3">
@@ -79469,7 +79472,7 @@
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A153" s="4"/>
+      <c r="A153" s="5"/>
       <c r="B153" s="3">
         <v>46204</v>
       </c>
@@ -79493,7 +79496,7 @@
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A154" s="4"/>
+      <c r="A154" s="5"/>
       <c r="B154" s="3">
         <v>46388</v>
       </c>
@@ -79517,7 +79520,7 @@
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A155" s="4"/>
+      <c r="A155" s="5"/>
       <c r="B155" s="3">
         <v>46569</v>
       </c>
@@ -79541,7 +79544,7 @@
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A156" s="4"/>
+      <c r="A156" s="5"/>
       <c r="B156" s="3">
         <v>46753</v>
       </c>
@@ -79565,7 +79568,7 @@
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A157" s="4"/>
+      <c r="A157" s="5"/>
       <c r="B157" s="3">
         <v>46935</v>
       </c>
@@ -79589,7 +79592,7 @@
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A158" s="4"/>
+      <c r="A158" s="5"/>
       <c r="B158" s="3">
         <v>47119</v>
       </c>
@@ -79613,7 +79616,7 @@
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A159" s="4"/>
+      <c r="A159" s="5"/>
       <c r="B159" s="3">
         <v>47300</v>
       </c>
@@ -79637,7 +79640,7 @@
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A160" s="4"/>
+      <c r="A160" s="5"/>
       <c r="B160" s="3">
         <v>47484</v>
       </c>
@@ -79661,7 +79664,7 @@
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A161" s="4"/>
+      <c r="A161" s="5"/>
       <c r="B161" s="3">
         <v>47665</v>
       </c>
@@ -79685,7 +79688,7 @@
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A162" s="4" t="s">
+      <c r="A162" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B162" s="3">
@@ -79711,7 +79714,7 @@
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A163" s="4"/>
+      <c r="A163" s="5"/>
       <c r="B163" s="3">
         <v>46023</v>
       </c>
@@ -79735,7 +79738,7 @@
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A164" s="4"/>
+      <c r="A164" s="5"/>
       <c r="B164" s="3">
         <v>46204</v>
       </c>
@@ -79759,7 +79762,7 @@
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A165" s="4"/>
+      <c r="A165" s="5"/>
       <c r="B165" s="3">
         <v>46388</v>
       </c>
@@ -79783,7 +79786,7 @@
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A166" s="4"/>
+      <c r="A166" s="5"/>
       <c r="B166" s="3">
         <v>46569</v>
       </c>
@@ -79807,7 +79810,7 @@
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A167" s="4"/>
+      <c r="A167" s="5"/>
       <c r="B167" s="3">
         <v>46753</v>
       </c>
@@ -79831,7 +79834,7 @@
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A168" s="4"/>
+      <c r="A168" s="5"/>
       <c r="B168" s="3">
         <v>46935</v>
       </c>
@@ -79855,7 +79858,7 @@
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A169" s="4"/>
+      <c r="A169" s="5"/>
       <c r="B169" s="3">
         <v>47119</v>
       </c>
@@ -79879,7 +79882,7 @@
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A170" s="4"/>
+      <c r="A170" s="5"/>
       <c r="B170" s="3">
         <v>47300</v>
       </c>
@@ -79903,7 +79906,7 @@
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A171" s="4"/>
+      <c r="A171" s="5"/>
       <c r="B171" s="3">
         <v>47484</v>
       </c>
@@ -79927,7 +79930,7 @@
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A172" s="4" t="s">
+      <c r="A172" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B172" s="3">
@@ -79953,7 +79956,7 @@
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A173" s="4"/>
+      <c r="A173" s="5"/>
       <c r="B173" s="3">
         <v>46204</v>
       </c>
@@ -79977,7 +79980,7 @@
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A174" s="4"/>
+      <c r="A174" s="5"/>
       <c r="B174" s="3">
         <v>46388</v>
       </c>
@@ -80001,7 +80004,7 @@
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A175" s="4"/>
+      <c r="A175" s="5"/>
       <c r="B175" s="3">
         <v>46569</v>
       </c>
@@ -80025,7 +80028,7 @@
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A176" s="4"/>
+      <c r="A176" s="5"/>
       <c r="B176" s="3">
         <v>46753</v>
       </c>
@@ -80049,7 +80052,7 @@
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A177" s="4"/>
+      <c r="A177" s="5"/>
       <c r="B177" s="3">
         <v>46935</v>
       </c>
@@ -80073,7 +80076,7 @@
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A178" s="4"/>
+      <c r="A178" s="5"/>
       <c r="B178" s="3">
         <v>47119</v>
       </c>
@@ -80097,7 +80100,7 @@
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A179" s="4"/>
+      <c r="A179" s="5"/>
       <c r="B179" s="3">
         <v>47300</v>
       </c>
@@ -80121,7 +80124,7 @@
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A180" s="4"/>
+      <c r="A180" s="5"/>
       <c r="B180" s="3">
         <v>47484</v>
       </c>
@@ -80145,7 +80148,7 @@
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A181" s="4"/>
+      <c r="A181" s="5"/>
       <c r="B181" s="3">
         <v>47665</v>
       </c>
@@ -80169,7 +80172,7 @@
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A182" s="4" t="s">
+      <c r="A182" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B182" s="3">
@@ -80195,7 +80198,7 @@
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A183" s="4"/>
+      <c r="A183" s="5"/>
       <c r="B183" s="3">
         <v>46204</v>
       </c>
@@ -80219,7 +80222,7 @@
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A184" s="4"/>
+      <c r="A184" s="5"/>
       <c r="B184" s="3">
         <v>46388</v>
       </c>
@@ -80243,7 +80246,7 @@
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A185" s="4"/>
+      <c r="A185" s="5"/>
       <c r="B185" s="3">
         <v>46569</v>
       </c>
@@ -80267,7 +80270,7 @@
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A186" s="4"/>
+      <c r="A186" s="5"/>
       <c r="B186" s="3">
         <v>46753</v>
       </c>
@@ -80291,7 +80294,7 @@
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A187" s="4"/>
+      <c r="A187" s="5"/>
       <c r="B187" s="3">
         <v>46935</v>
       </c>
@@ -80315,7 +80318,7 @@
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A188" s="4"/>
+      <c r="A188" s="5"/>
       <c r="B188" s="3">
         <v>47119</v>
       </c>
@@ -80339,7 +80342,7 @@
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A189" s="4"/>
+      <c r="A189" s="5"/>
       <c r="B189" s="3">
         <v>47300</v>
       </c>
@@ -80363,7 +80366,7 @@
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A190" s="4"/>
+      <c r="A190" s="5"/>
       <c r="B190" s="3">
         <v>47484</v>
       </c>
@@ -80387,7 +80390,7 @@
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A191" s="4"/>
+      <c r="A191" s="5"/>
       <c r="B191" s="3">
         <v>47665</v>
       </c>
@@ -80411,7 +80414,7 @@
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A192" s="4" t="s">
+      <c r="A192" s="5" t="s">
         <v>58</v>
       </c>
       <c r="B192" s="3">
@@ -80431,7 +80434,7 @@
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A193" s="4"/>
+      <c r="A193" s="5"/>
       <c r="B193" s="3">
         <v>46204</v>
       </c>
@@ -80449,7 +80452,7 @@
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A194" s="4"/>
+      <c r="A194" s="5"/>
       <c r="B194" s="3">
         <v>46388</v>
       </c>
@@ -80467,7 +80470,7 @@
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A195" s="4"/>
+      <c r="A195" s="5"/>
       <c r="B195" s="3">
         <v>46569</v>
       </c>
@@ -80485,7 +80488,7 @@
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A196" s="4"/>
+      <c r="A196" s="5"/>
       <c r="B196" s="3">
         <v>46753</v>
       </c>
@@ -80503,7 +80506,7 @@
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A197" s="4"/>
+      <c r="A197" s="5"/>
       <c r="B197" s="3">
         <v>46935</v>
       </c>
@@ -80521,7 +80524,7 @@
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A198" s="4"/>
+      <c r="A198" s="5"/>
       <c r="B198" s="3">
         <v>47119</v>
       </c>
@@ -80539,7 +80542,7 @@
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A199" s="4"/>
+      <c r="A199" s="5"/>
       <c r="B199" s="3">
         <v>47300</v>
       </c>
@@ -80557,7 +80560,7 @@
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A200" s="4"/>
+      <c r="A200" s="5"/>
       <c r="B200" s="3">
         <v>47484</v>
       </c>
@@ -80575,7 +80578,7 @@
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A201" s="4"/>
+      <c r="A201" s="5"/>
       <c r="B201" s="3">
         <v>47665</v>
       </c>
@@ -80593,7 +80596,7 @@
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A202" s="4" t="s">
+      <c r="A202" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B202" s="3">
@@ -80619,7 +80622,7 @@
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A203" s="4"/>
+      <c r="A203" s="5"/>
       <c r="B203" s="3">
         <v>46204</v>
       </c>
@@ -80643,7 +80646,7 @@
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A204" s="4"/>
+      <c r="A204" s="5"/>
       <c r="B204" s="3">
         <v>46388</v>
       </c>
@@ -80667,7 +80670,7 @@
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A205" s="4"/>
+      <c r="A205" s="5"/>
       <c r="B205" s="3">
         <v>46569</v>
       </c>
@@ -80691,7 +80694,7 @@
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A206" s="4"/>
+      <c r="A206" s="5"/>
       <c r="B206" s="3">
         <v>46753</v>
       </c>
@@ -80715,7 +80718,7 @@
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A207" s="4"/>
+      <c r="A207" s="5"/>
       <c r="B207" s="3">
         <v>46935</v>
       </c>
@@ -80739,7 +80742,7 @@
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A208" s="4"/>
+      <c r="A208" s="5"/>
       <c r="B208" s="3">
         <v>47119</v>
       </c>
@@ -80763,7 +80766,7 @@
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A209" s="4"/>
+      <c r="A209" s="5"/>
       <c r="B209" s="3">
         <v>47300</v>
       </c>
@@ -80787,7 +80790,7 @@
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A210" s="4"/>
+      <c r="A210" s="5"/>
       <c r="B210" s="3">
         <v>47484</v>
       </c>
@@ -80811,7 +80814,7 @@
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A211" s="4"/>
+      <c r="A211" s="5"/>
       <c r="B211" s="3">
         <v>47665</v>
       </c>
@@ -80835,7 +80838,7 @@
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A212" s="4" t="s">
+      <c r="A212" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B212" s="3">
@@ -80855,7 +80858,7 @@
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A213" s="4"/>
+      <c r="A213" s="5"/>
       <c r="B213" s="3">
         <v>46753</v>
       </c>
@@ -80873,7 +80876,7 @@
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A214" s="4"/>
+      <c r="A214" s="5"/>
       <c r="B214" s="3">
         <v>47119</v>
       </c>
@@ -80891,7 +80894,7 @@
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A215" s="4"/>
+      <c r="A215" s="5"/>
       <c r="B215" s="3">
         <v>47484</v>
       </c>
@@ -80909,7 +80912,7 @@
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A216" s="4"/>
+      <c r="A216" s="5"/>
       <c r="B216" s="3">
         <v>47849</v>
       </c>
@@ -80927,7 +80930,7 @@
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A217" s="4"/>
+      <c r="A217" s="5"/>
       <c r="B217" s="3">
         <v>48214</v>
       </c>
@@ -80945,7 +80948,7 @@
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A218" s="4"/>
+      <c r="A218" s="5"/>
       <c r="B218" s="3">
         <v>48580</v>
       </c>
@@ -80963,7 +80966,7 @@
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A219" s="4"/>
+      <c r="A219" s="5"/>
       <c r="B219" s="3">
         <v>48945</v>
       </c>
@@ -80981,7 +80984,7 @@
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A220" s="4"/>
+      <c r="A220" s="5"/>
       <c r="B220" s="3">
         <v>49310</v>
       </c>
@@ -80999,7 +81002,7 @@
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A221" s="4"/>
+      <c r="A221" s="5"/>
       <c r="B221" s="3">
         <v>49675</v>
       </c>
@@ -81017,7 +81020,7 @@
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A222" s="4" t="s">
+      <c r="A222" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B222" s="3">
@@ -81043,7 +81046,7 @@
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A223" s="4"/>
+      <c r="A223" s="5"/>
       <c r="B223" s="3">
         <v>46204</v>
       </c>
@@ -81067,7 +81070,7 @@
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A224" s="4"/>
+      <c r="A224" s="5"/>
       <c r="B224" s="3">
         <v>46388</v>
       </c>
@@ -81091,7 +81094,7 @@
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A225" s="4"/>
+      <c r="A225" s="5"/>
       <c r="B225" s="3">
         <v>46569</v>
       </c>
@@ -81115,7 +81118,7 @@
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A226" s="4"/>
+      <c r="A226" s="5"/>
       <c r="B226" s="3">
         <v>46753</v>
       </c>
@@ -81139,7 +81142,7 @@
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A227" s="4"/>
+      <c r="A227" s="5"/>
       <c r="B227" s="3">
         <v>46935</v>
       </c>
@@ -81163,7 +81166,7 @@
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A228" s="4"/>
+      <c r="A228" s="5"/>
       <c r="B228" s="3">
         <v>47119</v>
       </c>
@@ -81187,7 +81190,7 @@
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A229" s="4"/>
+      <c r="A229" s="5"/>
       <c r="B229" s="3">
         <v>47300</v>
       </c>
@@ -81211,7 +81214,7 @@
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A230" s="4"/>
+      <c r="A230" s="5"/>
       <c r="B230" s="3">
         <v>47484</v>
       </c>
@@ -81235,7 +81238,7 @@
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A231" s="4"/>
+      <c r="A231" s="5"/>
       <c r="B231" s="3">
         <v>47665</v>
       </c>
@@ -81259,7 +81262,7 @@
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A232" s="4" t="s">
+      <c r="A232" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B232" s="3">
@@ -81285,7 +81288,7 @@
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A233" s="4"/>
+      <c r="A233" s="5"/>
       <c r="B233" s="3">
         <v>46204</v>
       </c>
@@ -81309,7 +81312,7 @@
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A234" s="4"/>
+      <c r="A234" s="5"/>
       <c r="B234" s="3">
         <v>46388</v>
       </c>
@@ -81333,7 +81336,7 @@
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A235" s="4"/>
+      <c r="A235" s="5"/>
       <c r="B235" s="3">
         <v>46569</v>
       </c>
@@ -81357,7 +81360,7 @@
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A236" s="4"/>
+      <c r="A236" s="5"/>
       <c r="B236" s="3">
         <v>46753</v>
       </c>
@@ -81381,7 +81384,7 @@
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A237" s="4"/>
+      <c r="A237" s="5"/>
       <c r="B237" s="3">
         <v>46935</v>
       </c>
@@ -81405,7 +81408,7 @@
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A238" s="4"/>
+      <c r="A238" s="5"/>
       <c r="B238" s="3">
         <v>47119</v>
       </c>
@@ -81429,7 +81432,7 @@
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A239" s="4"/>
+      <c r="A239" s="5"/>
       <c r="B239" s="3">
         <v>47300</v>
       </c>
@@ -81453,7 +81456,7 @@
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A240" s="4"/>
+      <c r="A240" s="5"/>
       <c r="B240" s="3">
         <v>47484</v>
       </c>
@@ -81477,7 +81480,7 @@
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A241" s="4"/>
+      <c r="A241" s="5"/>
       <c r="B241" s="3">
         <v>47665</v>
       </c>
@@ -81501,7 +81504,7 @@
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A242" s="4" t="s">
+      <c r="A242" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B242" s="3">
@@ -81521,7 +81524,7 @@
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A243" s="4"/>
+      <c r="A243" s="5"/>
       <c r="B243" s="3">
         <v>46023</v>
       </c>
@@ -81539,7 +81542,7 @@
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A244" s="4"/>
+      <c r="A244" s="5"/>
       <c r="B244" s="3">
         <v>46204</v>
       </c>
@@ -81557,7 +81560,7 @@
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A245" s="4"/>
+      <c r="A245" s="5"/>
       <c r="B245" s="3">
         <v>46388</v>
       </c>
@@ -81575,7 +81578,7 @@
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A246" s="4"/>
+      <c r="A246" s="5"/>
       <c r="B246" s="3">
         <v>46569</v>
       </c>
@@ -81593,7 +81596,7 @@
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A247" s="4"/>
+      <c r="A247" s="5"/>
       <c r="B247" s="3">
         <v>46753</v>
       </c>
@@ -81611,7 +81614,7 @@
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A248" s="4"/>
+      <c r="A248" s="5"/>
       <c r="B248" s="3">
         <v>46935</v>
       </c>
@@ -81629,7 +81632,7 @@
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A249" s="4"/>
+      <c r="A249" s="5"/>
       <c r="B249" s="3">
         <v>47119</v>
       </c>
@@ -81647,7 +81650,7 @@
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A250" s="4"/>
+      <c r="A250" s="5"/>
       <c r="B250" s="3">
         <v>47300</v>
       </c>
@@ -81665,7 +81668,7 @@
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A251" s="4"/>
+      <c r="A251" s="5"/>
       <c r="B251" s="3">
         <v>47484</v>
       </c>
@@ -81683,7 +81686,7 @@
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A252" s="4" t="s">
+      <c r="A252" s="5" t="s">
         <v>48</v>
       </c>
       <c r="B252" s="3">
@@ -81709,7 +81712,7 @@
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A253" s="4"/>
+      <c r="A253" s="5"/>
       <c r="B253" s="3">
         <v>46204</v>
       </c>
@@ -81733,7 +81736,7 @@
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A254" s="4"/>
+      <c r="A254" s="5"/>
       <c r="B254" s="3">
         <v>46388</v>
       </c>
@@ -81757,7 +81760,7 @@
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A255" s="4"/>
+      <c r="A255" s="5"/>
       <c r="B255" s="3">
         <v>46569</v>
       </c>
@@ -81781,7 +81784,7 @@
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A256" s="4"/>
+      <c r="A256" s="5"/>
       <c r="B256" s="3">
         <v>46753</v>
       </c>
@@ -81805,7 +81808,7 @@
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A257" s="4"/>
+      <c r="A257" s="5"/>
       <c r="B257" s="3">
         <v>46935</v>
       </c>
@@ -81829,7 +81832,7 @@
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A258" s="4"/>
+      <c r="A258" s="5"/>
       <c r="B258" s="3">
         <v>47119</v>
       </c>
@@ -81853,7 +81856,7 @@
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A259" s="4"/>
+      <c r="A259" s="5"/>
       <c r="B259" s="3">
         <v>47300</v>
       </c>
@@ -81877,7 +81880,7 @@
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A260" s="4"/>
+      <c r="A260" s="5"/>
       <c r="B260" s="3">
         <v>47484</v>
       </c>
@@ -81901,7 +81904,7 @@
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A261" s="4"/>
+      <c r="A261" s="5"/>
       <c r="B261" s="3">
         <v>47665</v>
       </c>
@@ -81925,7 +81928,7 @@
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A262" s="4" t="s">
+      <c r="A262" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B262" s="3">
@@ -81951,7 +81954,7 @@
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A263" s="4"/>
+      <c r="A263" s="5"/>
       <c r="B263" s="3">
         <v>46204</v>
       </c>
@@ -81975,7 +81978,7 @@
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A264" s="4"/>
+      <c r="A264" s="5"/>
       <c r="B264" s="3">
         <v>46388</v>
       </c>
@@ -81999,7 +82002,7 @@
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A265" s="4"/>
+      <c r="A265" s="5"/>
       <c r="B265" s="3">
         <v>46569</v>
       </c>
@@ -82023,7 +82026,7 @@
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A266" s="4"/>
+      <c r="A266" s="5"/>
       <c r="B266" s="3">
         <v>46753</v>
       </c>
@@ -82047,7 +82050,7 @@
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A267" s="4"/>
+      <c r="A267" s="5"/>
       <c r="B267" s="3">
         <v>46935</v>
       </c>
@@ -82071,7 +82074,7 @@
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A268" s="4"/>
+      <c r="A268" s="5"/>
       <c r="B268" s="3">
         <v>47119</v>
       </c>
@@ -82095,7 +82098,7 @@
       </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A269" s="4"/>
+      <c r="A269" s="5"/>
       <c r="B269" s="3">
         <v>47300</v>
       </c>
@@ -82119,7 +82122,7 @@
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A270" s="4"/>
+      <c r="A270" s="5"/>
       <c r="B270" s="3">
         <v>47484</v>
       </c>
@@ -82143,7 +82146,7 @@
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A271" s="4"/>
+      <c r="A271" s="5"/>
       <c r="B271" s="3">
         <v>47665</v>
       </c>
@@ -82167,7 +82170,7 @@
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A272" s="4" t="s">
+      <c r="A272" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B272" s="3">
@@ -82193,7 +82196,7 @@
       </c>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A273" s="4"/>
+      <c r="A273" s="5"/>
       <c r="B273" s="3">
         <v>46388</v>
       </c>
@@ -82217,7 +82220,7 @@
       </c>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A274" s="4"/>
+      <c r="A274" s="5"/>
       <c r="B274" s="3">
         <v>46753</v>
       </c>
@@ -82241,7 +82244,7 @@
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A275" s="4"/>
+      <c r="A275" s="5"/>
       <c r="B275" s="3">
         <v>47119</v>
       </c>
@@ -82265,7 +82268,7 @@
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A276" s="4"/>
+      <c r="A276" s="5"/>
       <c r="B276" s="3">
         <v>47484</v>
       </c>
@@ -82289,7 +82292,7 @@
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A277" s="4"/>
+      <c r="A277" s="5"/>
       <c r="B277" s="3">
         <v>47849</v>
       </c>
@@ -82313,7 +82316,7 @@
       </c>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A278" s="4"/>
+      <c r="A278" s="5"/>
       <c r="B278" s="3">
         <v>48214</v>
       </c>
@@ -82337,7 +82340,7 @@
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A279" s="4"/>
+      <c r="A279" s="5"/>
       <c r="B279" s="3">
         <v>48580</v>
       </c>
@@ -82361,7 +82364,7 @@
       </c>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A280" s="4"/>
+      <c r="A280" s="5"/>
       <c r="B280" s="3">
         <v>48945</v>
       </c>
@@ -82385,7 +82388,7 @@
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A281" s="4"/>
+      <c r="A281" s="5"/>
       <c r="B281" s="3">
         <v>49310</v>
       </c>
@@ -82409,7 +82412,7 @@
       </c>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A282" s="4" t="s">
+      <c r="A282" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B282" s="3">
@@ -82429,7 +82432,7 @@
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A283" s="4"/>
+      <c r="A283" s="5"/>
       <c r="B283" s="3">
         <v>46753</v>
       </c>
@@ -82447,7 +82450,7 @@
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A284" s="4"/>
+      <c r="A284" s="5"/>
       <c r="B284" s="3">
         <v>47119</v>
       </c>
@@ -82465,7 +82468,7 @@
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A285" s="4"/>
+      <c r="A285" s="5"/>
       <c r="B285" s="3">
         <v>47484</v>
       </c>
@@ -82483,7 +82486,7 @@
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A286" s="4"/>
+      <c r="A286" s="5"/>
       <c r="B286" s="3">
         <v>47849</v>
       </c>
@@ -82501,7 +82504,7 @@
       </c>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A287" s="4"/>
+      <c r="A287" s="5"/>
       <c r="B287" s="3">
         <v>48214</v>
       </c>
@@ -82519,7 +82522,7 @@
       </c>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A288" s="4"/>
+      <c r="A288" s="5"/>
       <c r="B288" s="3">
         <v>48580</v>
       </c>
@@ -82537,7 +82540,7 @@
       </c>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A289" s="4"/>
+      <c r="A289" s="5"/>
       <c r="B289" s="3">
         <v>48945</v>
       </c>
@@ -82555,7 +82558,7 @@
       </c>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A290" s="4"/>
+      <c r="A290" s="5"/>
       <c r="B290" s="3">
         <v>49310</v>
       </c>
@@ -82573,7 +82576,7 @@
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A291" s="4"/>
+      <c r="A291" s="5"/>
       <c r="B291" s="3">
         <v>49675</v>
       </c>
@@ -82591,7 +82594,7 @@
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A292" s="4" t="s">
+      <c r="A292" s="5" t="s">
         <v>59</v>
       </c>
       <c r="B292" s="3">
@@ -82611,7 +82614,7 @@
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A293" s="4"/>
+      <c r="A293" s="5"/>
       <c r="B293" s="3">
         <v>46204</v>
       </c>
@@ -82629,7 +82632,7 @@
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A294" s="4"/>
+      <c r="A294" s="5"/>
       <c r="B294" s="3">
         <v>46388</v>
       </c>
@@ -82647,7 +82650,7 @@
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A295" s="4"/>
+      <c r="A295" s="5"/>
       <c r="B295" s="3">
         <v>46569</v>
       </c>
@@ -82665,7 +82668,7 @@
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A296" s="4"/>
+      <c r="A296" s="5"/>
       <c r="B296" s="3">
         <v>46753</v>
       </c>
@@ -82683,7 +82686,7 @@
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A297" s="4"/>
+      <c r="A297" s="5"/>
       <c r="B297" s="3">
         <v>46935</v>
       </c>
@@ -82701,7 +82704,7 @@
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A298" s="4"/>
+      <c r="A298" s="5"/>
       <c r="B298" s="3">
         <v>47119</v>
       </c>
@@ -82719,7 +82722,7 @@
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A299" s="4"/>
+      <c r="A299" s="5"/>
       <c r="B299" s="3">
         <v>47300</v>
       </c>
@@ -82737,7 +82740,7 @@
       </c>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A300" s="4"/>
+      <c r="A300" s="5"/>
       <c r="B300" s="3">
         <v>47484</v>
       </c>
@@ -82755,7 +82758,7 @@
       </c>
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A301" s="4"/>
+      <c r="A301" s="5"/>
       <c r="B301" s="3">
         <v>47665</v>
       </c>
@@ -82773,7 +82776,7 @@
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A302" s="4" t="s">
+      <c r="A302" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B302" s="3">
@@ -82799,7 +82802,7 @@
       </c>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A303" s="4"/>
+      <c r="A303" s="5"/>
       <c r="B303" s="3">
         <v>46204</v>
       </c>
@@ -82823,7 +82826,7 @@
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A304" s="4"/>
+      <c r="A304" s="5"/>
       <c r="B304" s="3">
         <v>46388</v>
       </c>
@@ -82847,7 +82850,7 @@
       </c>
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A305" s="4"/>
+      <c r="A305" s="5"/>
       <c r="B305" s="3">
         <v>46569</v>
       </c>
@@ -82871,7 +82874,7 @@
       </c>
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A306" s="4"/>
+      <c r="A306" s="5"/>
       <c r="B306" s="3">
         <v>46753</v>
       </c>
@@ -82895,7 +82898,7 @@
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A307" s="4"/>
+      <c r="A307" s="5"/>
       <c r="B307" s="3">
         <v>46935</v>
       </c>
@@ -82919,7 +82922,7 @@
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A308" s="4"/>
+      <c r="A308" s="5"/>
       <c r="B308" s="3">
         <v>47119</v>
       </c>
@@ -82943,7 +82946,7 @@
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A309" s="4"/>
+      <c r="A309" s="5"/>
       <c r="B309" s="3">
         <v>47300</v>
       </c>
@@ -82967,7 +82970,7 @@
       </c>
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A310" s="4"/>
+      <c r="A310" s="5"/>
       <c r="B310" s="3">
         <v>47484</v>
       </c>
@@ -82991,7 +82994,7 @@
       </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A311" s="4"/>
+      <c r="A311" s="5"/>
       <c r="B311" s="3">
         <v>47665</v>
       </c>
@@ -83015,7 +83018,7 @@
       </c>
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A312" s="4" t="s">
+      <c r="A312" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B312" s="3">
@@ -83041,7 +83044,7 @@
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A313" s="4"/>
+      <c r="A313" s="5"/>
       <c r="B313" s="3">
         <v>46204</v>
       </c>
@@ -83065,7 +83068,7 @@
       </c>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A314" s="4"/>
+      <c r="A314" s="5"/>
       <c r="B314" s="3">
         <v>46388</v>
       </c>
@@ -83089,7 +83092,7 @@
       </c>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A315" s="4"/>
+      <c r="A315" s="5"/>
       <c r="B315" s="3">
         <v>46569</v>
       </c>
@@ -83113,7 +83116,7 @@
       </c>
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A316" s="4"/>
+      <c r="A316" s="5"/>
       <c r="B316" s="3">
         <v>46753</v>
       </c>
@@ -83137,7 +83140,7 @@
       </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A317" s="4"/>
+      <c r="A317" s="5"/>
       <c r="B317" s="3">
         <v>46935</v>
       </c>
@@ -83161,7 +83164,7 @@
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A318" s="4"/>
+      <c r="A318" s="5"/>
       <c r="B318" s="3">
         <v>47119</v>
       </c>
@@ -83185,7 +83188,7 @@
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A319" s="4"/>
+      <c r="A319" s="5"/>
       <c r="B319" s="3">
         <v>47300</v>
       </c>
@@ -83209,7 +83212,7 @@
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A320" s="4"/>
+      <c r="A320" s="5"/>
       <c r="B320" s="3">
         <v>47484</v>
       </c>
@@ -83233,7 +83236,7 @@
       </c>
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A321" s="4"/>
+      <c r="A321" s="5"/>
       <c r="B321" s="3">
         <v>47665</v>
       </c>
@@ -83257,7 +83260,7 @@
       </c>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A322" s="4" t="s">
+      <c r="A322" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B322" s="3">
@@ -83277,7 +83280,7 @@
       </c>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A323" s="4"/>
+      <c r="A323" s="5"/>
       <c r="B323" s="3">
         <v>46753</v>
       </c>
@@ -83295,7 +83298,7 @@
       </c>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A324" s="4"/>
+      <c r="A324" s="5"/>
       <c r="B324" s="3">
         <v>47119</v>
       </c>
@@ -83313,7 +83316,7 @@
       </c>
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A325" s="4"/>
+      <c r="A325" s="5"/>
       <c r="B325" s="3">
         <v>47484</v>
       </c>
@@ -83331,7 +83334,7 @@
       </c>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A326" s="4"/>
+      <c r="A326" s="5"/>
       <c r="B326" s="3">
         <v>47849</v>
       </c>
@@ -83349,7 +83352,7 @@
       </c>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A327" s="4"/>
+      <c r="A327" s="5"/>
       <c r="B327" s="3">
         <v>48214</v>
       </c>
@@ -83367,7 +83370,7 @@
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A328" s="4"/>
+      <c r="A328" s="5"/>
       <c r="B328" s="3">
         <v>48580</v>
       </c>
@@ -83385,7 +83388,7 @@
       </c>
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A329" s="4"/>
+      <c r="A329" s="5"/>
       <c r="B329" s="3">
         <v>48945</v>
       </c>
@@ -83403,7 +83406,7 @@
       </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A330" s="4"/>
+      <c r="A330" s="5"/>
       <c r="B330" s="3">
         <v>49310</v>
       </c>
@@ -83421,7 +83424,7 @@
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A331" s="4"/>
+      <c r="A331" s="5"/>
       <c r="B331" s="3">
         <v>49675</v>
       </c>
@@ -83439,7 +83442,7 @@
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A332" s="4" t="s">
+      <c r="A332" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B332" s="3">
@@ -83459,7 +83462,7 @@
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A333" s="4"/>
+      <c r="A333" s="5"/>
       <c r="B333" s="3">
         <v>46023</v>
       </c>
@@ -83477,7 +83480,7 @@
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A334" s="4"/>
+      <c r="A334" s="5"/>
       <c r="B334" s="3">
         <v>46204</v>
       </c>
@@ -83495,7 +83498,7 @@
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A335" s="4"/>
+      <c r="A335" s="5"/>
       <c r="B335" s="3">
         <v>46388</v>
       </c>
@@ -83513,7 +83516,7 @@
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A336" s="4"/>
+      <c r="A336" s="5"/>
       <c r="B336" s="3">
         <v>46569</v>
       </c>
@@ -83531,7 +83534,7 @@
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A337" s="4"/>
+      <c r="A337" s="5"/>
       <c r="B337" s="3">
         <v>46753</v>
       </c>
@@ -83549,7 +83552,7 @@
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A338" s="4"/>
+      <c r="A338" s="5"/>
       <c r="B338" s="3">
         <v>46935</v>
       </c>
@@ -83567,7 +83570,7 @@
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A339" s="4"/>
+      <c r="A339" s="5"/>
       <c r="B339" s="3">
         <v>47119</v>
       </c>
@@ -83585,7 +83588,7 @@
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A340" s="4"/>
+      <c r="A340" s="5"/>
       <c r="B340" s="3">
         <v>47300</v>
       </c>
@@ -83603,7 +83606,7 @@
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A341" s="4"/>
+      <c r="A341" s="5"/>
       <c r="B341" s="3">
         <v>47484</v>
       </c>
@@ -83621,7 +83624,7 @@
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A342" s="4" t="s">
+      <c r="A342" s="5" t="s">
         <v>54</v>
       </c>
       <c r="B342" s="3">
@@ -83641,7 +83644,7 @@
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A343" s="4"/>
+      <c r="A343" s="5"/>
       <c r="B343" s="3">
         <v>46023</v>
       </c>
@@ -83659,7 +83662,7 @@
       </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A344" s="4"/>
+      <c r="A344" s="5"/>
       <c r="B344" s="3">
         <v>46204</v>
       </c>
@@ -83677,7 +83680,7 @@
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A345" s="4"/>
+      <c r="A345" s="5"/>
       <c r="B345" s="3">
         <v>46388</v>
       </c>
@@ -83695,7 +83698,7 @@
       </c>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A346" s="4"/>
+      <c r="A346" s="5"/>
       <c r="B346" s="3">
         <v>46569</v>
       </c>
@@ -83713,7 +83716,7 @@
       </c>
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A347" s="4"/>
+      <c r="A347" s="5"/>
       <c r="B347" s="3">
         <v>46753</v>
       </c>
@@ -83731,7 +83734,7 @@
       </c>
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A348" s="4"/>
+      <c r="A348" s="5"/>
       <c r="B348" s="3">
         <v>46935</v>
       </c>
@@ -83749,7 +83752,7 @@
       </c>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A349" s="4"/>
+      <c r="A349" s="5"/>
       <c r="B349" s="3">
         <v>47119</v>
       </c>
@@ -83767,7 +83770,7 @@
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A350" s="4"/>
+      <c r="A350" s="5"/>
       <c r="B350" s="3">
         <v>47300</v>
       </c>
@@ -83785,7 +83788,7 @@
       </c>
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A351" s="4"/>
+      <c r="A351" s="5"/>
       <c r="B351" s="3">
         <v>47484</v>
       </c>
@@ -83803,7 +83806,7 @@
       </c>
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A352" s="4" t="s">
+      <c r="A352" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B352" s="3">
@@ -83829,7 +83832,7 @@
       </c>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A353" s="4"/>
+      <c r="A353" s="5"/>
       <c r="B353" s="3">
         <v>46204</v>
       </c>
@@ -83853,7 +83856,7 @@
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A354" s="4"/>
+      <c r="A354" s="5"/>
       <c r="B354" s="3">
         <v>46388</v>
       </c>
@@ -83877,7 +83880,7 @@
       </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A355" s="4"/>
+      <c r="A355" s="5"/>
       <c r="B355" s="3">
         <v>46569</v>
       </c>
@@ -83901,7 +83904,7 @@
       </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A356" s="4"/>
+      <c r="A356" s="5"/>
       <c r="B356" s="3">
         <v>46753</v>
       </c>
@@ -83925,7 +83928,7 @@
       </c>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A357" s="4"/>
+      <c r="A357" s="5"/>
       <c r="B357" s="3">
         <v>46935</v>
       </c>
@@ -83949,7 +83952,7 @@
       </c>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A358" s="4"/>
+      <c r="A358" s="5"/>
       <c r="B358" s="3">
         <v>47119</v>
       </c>
@@ -83973,7 +83976,7 @@
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A359" s="4"/>
+      <c r="A359" s="5"/>
       <c r="B359" s="3">
         <v>47300</v>
       </c>
@@ -83997,7 +84000,7 @@
       </c>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A360" s="4"/>
+      <c r="A360" s="5"/>
       <c r="B360" s="3">
         <v>47484</v>
       </c>
@@ -84021,7 +84024,7 @@
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A361" s="4"/>
+      <c r="A361" s="5"/>
       <c r="B361" s="3">
         <v>47665</v>
       </c>
@@ -84045,7 +84048,7 @@
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A362" s="4" t="s">
+      <c r="A362" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B362" s="3">
@@ -84071,7 +84074,7 @@
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A363" s="4"/>
+      <c r="A363" s="5"/>
       <c r="B363" s="3">
         <v>46204</v>
       </c>
@@ -84095,7 +84098,7 @@
       </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A364" s="4"/>
+      <c r="A364" s="5"/>
       <c r="B364" s="3">
         <v>46388</v>
       </c>
@@ -84119,7 +84122,7 @@
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A365" s="4"/>
+      <c r="A365" s="5"/>
       <c r="B365" s="3">
         <v>46569</v>
       </c>
@@ -84143,7 +84146,7 @@
       </c>
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A366" s="4"/>
+      <c r="A366" s="5"/>
       <c r="B366" s="3">
         <v>46753</v>
       </c>
@@ -84167,7 +84170,7 @@
       </c>
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A367" s="4"/>
+      <c r="A367" s="5"/>
       <c r="B367" s="3">
         <v>46935</v>
       </c>
@@ -84191,7 +84194,7 @@
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A368" s="4"/>
+      <c r="A368" s="5"/>
       <c r="B368" s="3">
         <v>47119</v>
       </c>
@@ -84215,7 +84218,7 @@
       </c>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A369" s="4"/>
+      <c r="A369" s="5"/>
       <c r="B369" s="3">
         <v>47300</v>
       </c>
@@ -84239,7 +84242,7 @@
       </c>
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A370" s="4"/>
+      <c r="A370" s="5"/>
       <c r="B370" s="3">
         <v>47484</v>
       </c>
@@ -84263,7 +84266,7 @@
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A371" s="4"/>
+      <c r="A371" s="5"/>
       <c r="B371" s="3">
         <v>47665</v>
       </c>
@@ -84287,7 +84290,7 @@
       </c>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A372" s="4" t="s">
+      <c r="A372" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B372" s="3">
@@ -84313,7 +84316,7 @@
       </c>
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A373" s="4"/>
+      <c r="A373" s="5"/>
       <c r="B373" s="3">
         <v>46204</v>
       </c>
@@ -84337,7 +84340,7 @@
       </c>
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A374" s="4"/>
+      <c r="A374" s="5"/>
       <c r="B374" s="3">
         <v>46388</v>
       </c>
@@ -84361,7 +84364,7 @@
       </c>
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A375" s="4"/>
+      <c r="A375" s="5"/>
       <c r="B375" s="3">
         <v>46569</v>
       </c>
@@ -84385,7 +84388,7 @@
       </c>
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A376" s="4"/>
+      <c r="A376" s="5"/>
       <c r="B376" s="3">
         <v>46753</v>
       </c>
@@ -84409,7 +84412,7 @@
       </c>
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A377" s="4"/>
+      <c r="A377" s="5"/>
       <c r="B377" s="3">
         <v>46935</v>
       </c>
@@ -84433,7 +84436,7 @@
       </c>
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A378" s="4"/>
+      <c r="A378" s="5"/>
       <c r="B378" s="3">
         <v>47119</v>
       </c>
@@ -84457,7 +84460,7 @@
       </c>
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A379" s="4"/>
+      <c r="A379" s="5"/>
       <c r="B379" s="3">
         <v>47300</v>
       </c>
@@ -84481,7 +84484,7 @@
       </c>
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A380" s="4"/>
+      <c r="A380" s="5"/>
       <c r="B380" s="3">
         <v>47484</v>
       </c>
@@ -84505,7 +84508,7 @@
       </c>
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A381" s="4"/>
+      <c r="A381" s="5"/>
       <c r="B381" s="3">
         <v>47665</v>
       </c>
@@ -84529,7 +84532,7 @@
       </c>
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A382" s="4" t="s">
+      <c r="A382" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B382" s="3">
@@ -84555,7 +84558,7 @@
       </c>
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A383" s="4"/>
+      <c r="A383" s="5"/>
       <c r="B383" s="3">
         <v>46204</v>
       </c>
@@ -84579,7 +84582,7 @@
       </c>
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A384" s="4"/>
+      <c r="A384" s="5"/>
       <c r="B384" s="3">
         <v>46388</v>
       </c>
@@ -84603,7 +84606,7 @@
       </c>
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A385" s="4"/>
+      <c r="A385" s="5"/>
       <c r="B385" s="3">
         <v>46569</v>
       </c>
@@ -84627,7 +84630,7 @@
       </c>
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A386" s="4"/>
+      <c r="A386" s="5"/>
       <c r="B386" s="3">
         <v>46753</v>
       </c>
@@ -84651,7 +84654,7 @@
       </c>
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A387" s="4"/>
+      <c r="A387" s="5"/>
       <c r="B387" s="3">
         <v>46935</v>
       </c>
@@ -84675,7 +84678,7 @@
       </c>
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A388" s="4"/>
+      <c r="A388" s="5"/>
       <c r="B388" s="3">
         <v>47119</v>
       </c>
@@ -84699,7 +84702,7 @@
       </c>
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A389" s="4"/>
+      <c r="A389" s="5"/>
       <c r="B389" s="3">
         <v>47300</v>
       </c>
@@ -84723,7 +84726,7 @@
       </c>
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A390" s="4"/>
+      <c r="A390" s="5"/>
       <c r="B390" s="3">
         <v>47484</v>
       </c>
@@ -84747,7 +84750,7 @@
       </c>
     </row>
     <row r="391" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A391" s="4"/>
+      <c r="A391" s="5"/>
       <c r="B391" s="3">
         <v>47665</v>
       </c>
@@ -84771,7 +84774,7 @@
       </c>
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A392" s="4" t="s">
+      <c r="A392" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B392" s="3">
@@ -84797,7 +84800,7 @@
       </c>
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A393" s="4"/>
+      <c r="A393" s="5"/>
       <c r="B393" s="3">
         <v>46204</v>
       </c>
@@ -84821,7 +84824,7 @@
       </c>
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A394" s="4"/>
+      <c r="A394" s="5"/>
       <c r="B394" s="3">
         <v>46388</v>
       </c>
@@ -84845,7 +84848,7 @@
       </c>
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A395" s="4"/>
+      <c r="A395" s="5"/>
       <c r="B395" s="3">
         <v>46569</v>
       </c>
@@ -84869,7 +84872,7 @@
       </c>
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A396" s="4"/>
+      <c r="A396" s="5"/>
       <c r="B396" s="3">
         <v>46753</v>
       </c>
@@ -84893,7 +84896,7 @@
       </c>
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A397" s="4"/>
+      <c r="A397" s="5"/>
       <c r="B397" s="3">
         <v>46935</v>
       </c>
@@ -84917,7 +84920,7 @@
       </c>
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A398" s="4"/>
+      <c r="A398" s="5"/>
       <c r="B398" s="3">
         <v>47119</v>
       </c>
@@ -84941,7 +84944,7 @@
       </c>
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A399" s="4"/>
+      <c r="A399" s="5"/>
       <c r="B399" s="3">
         <v>47300</v>
       </c>
@@ -84965,7 +84968,7 @@
       </c>
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A400" s="4"/>
+      <c r="A400" s="5"/>
       <c r="B400" s="3">
         <v>47484</v>
       </c>
@@ -84989,7 +84992,7 @@
       </c>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A401" s="4"/>
+      <c r="A401" s="5"/>
       <c r="B401" s="3">
         <v>47665</v>
       </c>
@@ -85014,11 +85017,14 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="A392:A401"/>
-    <mergeCell ref="A22:A31"/>
-    <mergeCell ref="A12:A21"/>
-    <mergeCell ref="A192:A201"/>
-    <mergeCell ref="A272:A281"/>
+    <mergeCell ref="A322:A331"/>
+    <mergeCell ref="A312:A321"/>
+    <mergeCell ref="A152:A161"/>
+    <mergeCell ref="A162:A171"/>
+    <mergeCell ref="A242:A251"/>
+    <mergeCell ref="A252:A261"/>
+    <mergeCell ref="A292:A301"/>
+    <mergeCell ref="A282:A291"/>
     <mergeCell ref="A2:A11"/>
     <mergeCell ref="A302:A311"/>
     <mergeCell ref="A42:A51"/>
@@ -85026,19 +85032,24 @@
     <mergeCell ref="A72:A81"/>
     <mergeCell ref="A32:A41"/>
     <mergeCell ref="A52:A61"/>
-    <mergeCell ref="A332:A341"/>
-    <mergeCell ref="A372:A381"/>
     <mergeCell ref="A102:A111"/>
     <mergeCell ref="A142:A151"/>
-    <mergeCell ref="A362:A371"/>
     <mergeCell ref="A202:A211"/>
     <mergeCell ref="A182:A191"/>
     <mergeCell ref="A92:A101"/>
     <mergeCell ref="A232:A241"/>
-    <mergeCell ref="A352:A361"/>
     <mergeCell ref="A172:A181"/>
     <mergeCell ref="A82:A91"/>
     <mergeCell ref="A222:A231"/>
+    <mergeCell ref="A392:A401"/>
+    <mergeCell ref="A22:A31"/>
+    <mergeCell ref="A12:A21"/>
+    <mergeCell ref="A192:A201"/>
+    <mergeCell ref="A272:A281"/>
+    <mergeCell ref="A332:A341"/>
+    <mergeCell ref="A372:A381"/>
+    <mergeCell ref="A362:A371"/>
+    <mergeCell ref="A352:A361"/>
     <mergeCell ref="A132:A141"/>
     <mergeCell ref="A212:A221"/>
     <mergeCell ref="A112:A121"/>
@@ -85046,14 +85057,6 @@
     <mergeCell ref="A62:A71"/>
     <mergeCell ref="A342:A351"/>
     <mergeCell ref="A382:A391"/>
-    <mergeCell ref="A152:A161"/>
-    <mergeCell ref="A162:A171"/>
-    <mergeCell ref="A242:A251"/>
-    <mergeCell ref="A252:A261"/>
-    <mergeCell ref="A292:A301"/>
-    <mergeCell ref="A282:A291"/>
-    <mergeCell ref="A322:A331"/>
-    <mergeCell ref="A312:A321"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -85066,12 +85069,12 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B1" s="1"/>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
       <c r="G1" s="1" t="s">
         <v>0</v>
       </c>
@@ -85103,7 +85106,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -85126,7 +85129,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
+      <c r="A5" s="5"/>
       <c r="B5" s="1" t="s">
         <v>17</v>
       </c>
@@ -85147,7 +85150,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
+      <c r="A6" s="5"/>
       <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
@@ -85168,7 +85171,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
+      <c r="A7" s="5"/>
       <c r="B7" s="1" t="s">
         <v>15</v>
       </c>
@@ -85189,7 +85192,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="4"/>
+      <c r="A8" s="5"/>
       <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
@@ -85210,7 +85213,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
+      <c r="A9" s="5"/>
       <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
@@ -85231,7 +85234,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -85254,7 +85257,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
+      <c r="A11" s="5"/>
       <c r="B11" s="1" t="s">
         <v>17</v>
       </c>
@@ -85275,7 +85278,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="4"/>
+      <c r="A12" s="5"/>
       <c r="B12" s="1" t="s">
         <v>13</v>
       </c>
@@ -85296,7 +85299,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="4"/>
+      <c r="A13" s="5"/>
       <c r="B13" s="1" t="s">
         <v>15</v>
       </c>
@@ -85317,7 +85320,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="4"/>
+      <c r="A14" s="5"/>
       <c r="B14" s="1" t="s">
         <v>14</v>
       </c>
@@ -85338,7 +85341,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
+      <c r="A15" s="5"/>
       <c r="B15" s="1" t="s">
         <v>16</v>
       </c>

--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_F9CF0E37EBD1EBA544304DA6FBECF471CF04C795" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C432117-798E-4172-9DFB-A5CDA4242ED3}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_F9CF0E37EBD1EBA544304DA6FBECF471CF04C795" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA15DB3E-DFC2-4C22-8470-B0ABF90B34EA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -287,7 +287,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -344,8 +344,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -711,10 +711,10 @@
         <v>56776.89</v>
       </c>
       <c r="H2">
-        <v>55065.07</v>
+        <v>55267.77</v>
       </c>
       <c r="I2">
-        <v>58488.71</v>
+        <v>58286.01</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -740,10 +740,10 @@
         <v>56510.13</v>
       </c>
       <c r="H3">
-        <v>54797.88</v>
+        <v>54364.99</v>
       </c>
       <c r="I3">
-        <v>58222.39</v>
+        <v>58655.28</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -769,10 +769,10 @@
         <v>56771.85</v>
       </c>
       <c r="H4">
-        <v>55043.15</v>
+        <v>54148.88</v>
       </c>
       <c r="I4">
-        <v>58500.55</v>
+        <v>59394.82</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -798,10 +798,10 @@
         <v>56515.08</v>
       </c>
       <c r="H5">
-        <v>54785.71</v>
+        <v>53481.38</v>
       </c>
       <c r="I5">
-        <v>58244.44</v>
+        <v>59548.77</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -827,10 +827,10 @@
         <v>56767</v>
       </c>
       <c r="H6">
-        <v>55021.42</v>
+        <v>53378.42</v>
       </c>
       <c r="I6">
-        <v>58512.59</v>
+        <v>60155.58</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -856,10 +856,10 @@
         <v>56519.83</v>
       </c>
       <c r="H7">
-        <v>54773.37</v>
+        <v>52804.33</v>
       </c>
       <c r="I7">
-        <v>58266.3</v>
+        <v>60235.34</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -885,10 +885,10 @@
         <v>56762.34</v>
       </c>
       <c r="H8">
-        <v>54999.87</v>
+        <v>52751.73</v>
       </c>
       <c r="I8">
-        <v>58524.81</v>
+        <v>60772.94</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -914,10 +914,10 @@
         <v>56524.41</v>
       </c>
       <c r="H9">
-        <v>54760.85</v>
+        <v>52234.11</v>
       </c>
       <c r="I9">
-        <v>58287.97</v>
+        <v>60814.71</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -943,10 +943,10 @@
         <v>56757.84</v>
       </c>
       <c r="H10">
-        <v>54978.48</v>
+        <v>52217.22</v>
       </c>
       <c r="I10">
-        <v>58537.2</v>
+        <v>61298.47</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -972,10 +972,10 @@
         <v>56528.82</v>
       </c>
       <c r="H11">
-        <v>54748.160000000003</v>
+        <v>52006.51</v>
       </c>
       <c r="I11">
-        <v>58309.48</v>
+        <v>61051.13</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -1581,10 +1581,10 @@
         <v>55448.86</v>
       </c>
       <c r="H32">
-        <v>53777.08</v>
+        <v>53803.33</v>
       </c>
       <c r="I32">
-        <v>57120.639999999999</v>
+        <v>57065.18</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
@@ -1610,10 +1610,10 @@
         <v>56283.5</v>
       </c>
       <c r="H33">
-        <v>54578.11</v>
+        <v>54773.88</v>
       </c>
       <c r="I33">
-        <v>57988.89</v>
+        <v>57791.57</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
@@ -1639,10 +1639,10 @@
         <v>57131.97</v>
       </c>
       <c r="H34">
-        <v>55392.3</v>
+        <v>55681.97</v>
       </c>
       <c r="I34">
-        <v>58871.64</v>
+        <v>58702.94</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
@@ -1668,10 +1668,10 @@
         <v>57966.61</v>
       </c>
       <c r="H35">
-        <v>56192.83</v>
+        <v>56535.61</v>
       </c>
       <c r="I35">
-        <v>59740.39</v>
+        <v>59586.69</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
@@ -1697,10 +1697,10 @@
         <v>58815.08</v>
       </c>
       <c r="H36">
-        <v>57006.52</v>
+        <v>57239.56</v>
       </c>
       <c r="I36">
-        <v>60623.64</v>
+        <v>60547.33</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
@@ -1726,10 +1726,10 @@
         <v>59654.33</v>
       </c>
       <c r="H37">
-        <v>57811.01</v>
+        <v>58148.19</v>
       </c>
       <c r="I37">
-        <v>61497.65</v>
+        <v>61136.11</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
@@ -1755,10 +1755,10 @@
         <v>60502.8</v>
       </c>
       <c r="H38">
-        <v>58624.19</v>
+        <v>58927.12</v>
       </c>
       <c r="I38">
-        <v>62381.41</v>
+        <v>62139.93</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
@@ -1784,10 +1784,10 @@
         <v>61337.440000000002</v>
       </c>
       <c r="H39">
-        <v>59423.71</v>
+        <v>59887.54</v>
       </c>
       <c r="I39">
-        <v>63251.17</v>
+        <v>62910.92</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
@@ -1813,10 +1813,10 @@
         <v>62185.91</v>
       </c>
       <c r="H40">
-        <v>60236.38</v>
+        <v>60669.11</v>
       </c>
       <c r="I40">
-        <v>64135.44</v>
+        <v>63732.97</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
@@ -1842,10 +1842,10 @@
         <v>63020.55</v>
       </c>
       <c r="H41">
-        <v>61035.4</v>
+        <v>61397.59</v>
       </c>
       <c r="I41">
-        <v>65005.7</v>
+        <v>64530.31</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
@@ -2538,7 +2538,7 @@
         <v>10211.74</v>
       </c>
       <c r="H65">
-        <v>9394.7999999999993</v>
+        <v>9397.66</v>
       </c>
       <c r="I65">
         <v>11028.68</v>
@@ -2741,10 +2741,10 @@
         <v>9653.06</v>
       </c>
       <c r="H72">
-        <v>8925.01</v>
+        <v>8880.81</v>
       </c>
       <c r="I72">
-        <v>9653.06</v>
+        <v>10425.299999999999</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
@@ -2773,7 +2773,7 @@
         <v>9721.36</v>
       </c>
       <c r="I73">
-        <v>10566.69</v>
+        <v>11412.03</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
@@ -2802,7 +2802,7 @@
         <v>10561.77</v>
       </c>
       <c r="I74">
-        <v>11480.18</v>
+        <v>12398.59</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
@@ -2831,7 +2831,7 @@
         <v>11399.15</v>
       </c>
       <c r="I75">
-        <v>12390.38</v>
+        <v>13381.61</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
@@ -2860,7 +2860,7 @@
         <v>12231.11</v>
       </c>
       <c r="I76">
-        <v>13294.68</v>
+        <v>14358.26</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
@@ -2889,7 +2889,7 @@
         <v>13055.65</v>
       </c>
       <c r="I77">
-        <v>14190.92</v>
+        <v>15326.2</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
@@ -2918,7 +2918,7 @@
         <v>12462.7</v>
       </c>
       <c r="I78">
-        <v>15077.33</v>
+        <v>14630.13</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
@@ -2947,7 +2947,7 @@
         <v>12681.52</v>
       </c>
       <c r="I79">
-        <v>15952.46</v>
+        <v>14887</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
@@ -2976,7 +2976,7 @@
         <v>12898.14</v>
       </c>
       <c r="I80">
-        <v>16815.169999999998</v>
+        <v>15141.3</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
@@ -3005,7 +3005,7 @@
         <v>13112.6</v>
       </c>
       <c r="I81">
-        <v>17664.560000000001</v>
+        <v>15393.05</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
@@ -3031,10 +3031,10 @@
         <v>9653.06</v>
       </c>
       <c r="H82">
-        <v>8925.01</v>
+        <v>8880.81</v>
       </c>
       <c r="I82">
-        <v>9653.06</v>
+        <v>10425.299999999999</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
@@ -3063,7 +3063,7 @@
         <v>9142.27</v>
       </c>
       <c r="I83">
-        <v>10566.69</v>
+        <v>10732.23</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
@@ -3089,7 +3089,7 @@
         <v>9904.36</v>
       </c>
       <c r="H84">
-        <v>9251.09</v>
+        <v>9112.01</v>
       </c>
       <c r="I84">
         <v>10696.7</v>
@@ -3147,7 +3147,7 @@
         <v>9974.16</v>
       </c>
       <c r="H86">
-        <v>9534.66</v>
+        <v>9176.2199999999993</v>
       </c>
       <c r="I86">
         <v>10772.09</v>
@@ -3176,7 +3176,7 @@
         <v>10269.950000000001</v>
       </c>
       <c r="H87">
-        <v>9662.98</v>
+        <v>9448.36</v>
       </c>
       <c r="I87">
         <v>11091.55</v>
@@ -3205,7 +3205,7 @@
         <v>10306.16</v>
       </c>
       <c r="H88">
-        <v>9783.41</v>
+        <v>9481.66</v>
       </c>
       <c r="I88">
         <v>11130.65</v>
@@ -3234,7 +3234,7 @@
         <v>10269.950000000001</v>
       </c>
       <c r="H89">
-        <v>9896.65</v>
+        <v>9448.36</v>
       </c>
       <c r="I89">
         <v>11091.55</v>
@@ -3263,7 +3263,7 @@
         <v>10306.16</v>
       </c>
       <c r="H90">
-        <v>10003.32</v>
+        <v>9481.66</v>
       </c>
       <c r="I90">
         <v>11130.65</v>
@@ -3292,7 +3292,7 @@
         <v>10306.16</v>
       </c>
       <c r="H91">
-        <v>10103.959999999999</v>
+        <v>9481.66</v>
       </c>
       <c r="I91">
         <v>11130.65</v>
@@ -3611,10 +3611,10 @@
         <v>9380.0400000000009</v>
       </c>
       <c r="H102">
-        <v>8925.01</v>
+        <v>8629.64</v>
       </c>
       <c r="I102">
-        <v>9653.06</v>
+        <v>10130.44</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
@@ -3643,7 +3643,7 @@
         <v>9258.42</v>
       </c>
       <c r="I103">
-        <v>10566.69</v>
+        <v>10868.58</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
@@ -3672,7 +3672,7 @@
         <v>9933.01</v>
       </c>
       <c r="I104">
-        <v>11480.18</v>
+        <v>11660.49</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
@@ -3701,7 +3701,7 @@
         <v>10656.76</v>
       </c>
       <c r="I105">
-        <v>12390.38</v>
+        <v>12510.11</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
@@ -3730,7 +3730,7 @@
         <v>11433.24</v>
       </c>
       <c r="I106">
-        <v>13294.68</v>
+        <v>13421.63</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
@@ -3759,7 +3759,7 @@
         <v>13055.65</v>
       </c>
       <c r="I107">
-        <v>14190.92</v>
+        <v>15326.2</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
@@ -3785,10 +3785,10 @@
         <v>15077.33</v>
       </c>
       <c r="H108">
-        <v>15077.33</v>
+        <v>13871.14</v>
       </c>
       <c r="I108">
-        <v>15077.33</v>
+        <v>16283.51</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
@@ -3814,10 +3814,10 @@
         <v>15952.46</v>
       </c>
       <c r="H109">
-        <v>15952.46</v>
+        <v>14676.27</v>
       </c>
       <c r="I109">
-        <v>15952.46</v>
+        <v>17228.66</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
@@ -3843,10 +3843,10 @@
         <v>16815.169999999998</v>
       </c>
       <c r="H110">
-        <v>16815.169999999998</v>
+        <v>15469.96</v>
       </c>
       <c r="I110">
-        <v>16815.169999999998</v>
+        <v>18160.39</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
@@ -3872,10 +3872,10 @@
         <v>17664.560000000001</v>
       </c>
       <c r="H111">
-        <v>17664.560000000001</v>
+        <v>16251.39</v>
       </c>
       <c r="I111">
-        <v>17664.560000000001</v>
+        <v>19077.72</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
@@ -3901,10 +3901,10 @@
         <v>9585.6200000000008</v>
       </c>
       <c r="H112">
-        <v>8925.01</v>
+        <v>8818.77</v>
       </c>
       <c r="I112">
-        <v>9653.06</v>
+        <v>10352.459999999999</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
@@ -3933,7 +3933,7 @@
         <v>9405.4599999999991</v>
       </c>
       <c r="I113">
-        <v>10566.69</v>
+        <v>11041.19</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
@@ -3962,7 +3962,7 @@
         <v>9651.81</v>
       </c>
       <c r="I114">
-        <v>11480.18</v>
+        <v>11330.39</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
@@ -4481,10 +4481,10 @@
         <v>52787.95</v>
       </c>
       <c r="H132">
-        <v>48767.19</v>
+        <v>48564.91</v>
       </c>
       <c r="I132">
-        <v>52787.95</v>
+        <v>57010.98</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
@@ -4513,7 +4513,7 @@
         <v>53211.77</v>
       </c>
       <c r="I133">
-        <v>57838.879999999997</v>
+        <v>62465.99</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
@@ -4542,7 +4542,7 @@
         <v>57862.27</v>
       </c>
       <c r="I134">
-        <v>62893.78</v>
+        <v>67925.279999999999</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
@@ -4571,7 +4571,7 @@
         <v>62500.11</v>
       </c>
       <c r="I135">
-        <v>67934.899999999994</v>
+        <v>73369.7</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
@@ -4600,7 +4600,7 @@
         <v>62152.27</v>
       </c>
       <c r="I136">
-        <v>72947.42</v>
+        <v>72961.36</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
@@ -4629,7 +4629,7 @@
         <v>63050.03</v>
       </c>
       <c r="I137">
-        <v>77918.990000000005</v>
+        <v>74015.25</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
@@ -4771,10 +4771,10 @@
         <v>52787.95</v>
       </c>
       <c r="H142">
-        <v>48767.19</v>
+        <v>48564.91</v>
       </c>
       <c r="I142">
-        <v>52787.95</v>
+        <v>57010.98</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
@@ -4803,7 +4803,7 @@
         <v>50876.37</v>
       </c>
       <c r="I143">
-        <v>57838.879999999997</v>
+        <v>59724.43</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.3">
@@ -4858,7 +4858,7 @@
         <v>55400.56</v>
       </c>
       <c r="H145">
-        <v>51378.54</v>
+        <v>50968.52</v>
       </c>
       <c r="I145">
         <v>59832.61</v>
@@ -4916,7 +4916,7 @@
         <v>55487.67</v>
       </c>
       <c r="H147">
-        <v>52845.07</v>
+        <v>51048.65</v>
       </c>
       <c r="I147">
         <v>59926.68</v>
@@ -4945,7 +4945,7 @@
         <v>56427.32</v>
       </c>
       <c r="H148">
-        <v>53510.9</v>
+        <v>51913.13</v>
       </c>
       <c r="I148">
         <v>60941.5</v>
@@ -4974,7 +4974,7 @@
         <v>56629.77</v>
       </c>
       <c r="H149">
-        <v>54137.06</v>
+        <v>52099.39</v>
       </c>
       <c r="I149">
         <v>61160.15</v>
@@ -5003,7 +5003,7 @@
         <v>55285.22</v>
       </c>
       <c r="H150">
-        <v>54726.95</v>
+        <v>50862.400000000001</v>
       </c>
       <c r="I150">
         <v>59708.03</v>
@@ -5032,7 +5032,7 @@
         <v>56427.32</v>
       </c>
       <c r="H151">
-        <v>55283.6</v>
+        <v>51913.13</v>
       </c>
       <c r="I151">
         <v>60941.5</v>
@@ -5351,10 +5351,10 @@
         <v>51280.160000000003</v>
       </c>
       <c r="H162">
-        <v>48767.19</v>
+        <v>47177.75</v>
       </c>
       <c r="I162">
-        <v>52787.95</v>
+        <v>55382.58</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
@@ -5383,7 +5383,7 @@
         <v>50652.88</v>
       </c>
       <c r="I163">
-        <v>57838.879999999997</v>
+        <v>59462.07</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
@@ -5412,7 +5412,7 @@
         <v>54383.98</v>
       </c>
       <c r="I164">
-        <v>62893.78</v>
+        <v>63842.07</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
@@ -5441,7 +5441,7 @@
         <v>58389.919999999998</v>
       </c>
       <c r="I165">
-        <v>67934.899999999994</v>
+        <v>68544.69</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
@@ -5470,7 +5470,7 @@
         <v>62690.94</v>
       </c>
       <c r="I166">
-        <v>72947.42</v>
+        <v>73593.72</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
@@ -5499,7 +5499,7 @@
         <v>71685.47</v>
       </c>
       <c r="I167">
-        <v>77918.990000000005</v>
+        <v>84152.51</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
@@ -5525,10 +5525,10 @@
         <v>82839.45</v>
       </c>
       <c r="H168">
-        <v>82839.45</v>
+        <v>76212.289999999994</v>
       </c>
       <c r="I168">
-        <v>82839.45</v>
+        <v>89466.6</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
@@ -5554,10 +5554,10 @@
         <v>87700.51</v>
       </c>
       <c r="H169">
-        <v>87700.51</v>
+        <v>80684.47</v>
       </c>
       <c r="I169">
-        <v>87700.51</v>
+        <v>94716.55</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.3">
@@ -5583,10 +5583,10 @@
         <v>92495.48</v>
       </c>
       <c r="H170">
-        <v>92495.48</v>
+        <v>85095.85</v>
       </c>
       <c r="I170">
-        <v>92495.48</v>
+        <v>99895.12</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
@@ -5612,10 +5612,10 @@
         <v>97219.07</v>
       </c>
       <c r="H171">
-        <v>97219.07</v>
+        <v>89441.54</v>
       </c>
       <c r="I171">
-        <v>97219.07</v>
+        <v>104996.6</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
@@ -5641,10 +5641,10 @@
         <v>52414.76</v>
       </c>
       <c r="H172">
-        <v>48767.19</v>
+        <v>48221.58</v>
       </c>
       <c r="I172">
-        <v>52787.95</v>
+        <v>56607.94</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
@@ -5673,7 +5673,7 @@
         <v>51256.86</v>
       </c>
       <c r="I173">
-        <v>57838.879999999997</v>
+        <v>60171.09</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
@@ -5873,7 +5873,7 @@
         <v>58769.19</v>
       </c>
       <c r="H180">
-        <v>54726.95</v>
+        <v>54067.65</v>
       </c>
       <c r="I180">
         <v>63470.720000000001</v>
@@ -5902,7 +5902,7 @@
         <v>59240.11</v>
       </c>
       <c r="H181">
-        <v>55283.6</v>
+        <v>54500.9</v>
       </c>
       <c r="I181">
         <v>63979.32</v>
@@ -6018,7 +6018,7 @@
         <v>60732.99</v>
       </c>
       <c r="H185">
-        <v>55874.35</v>
+        <v>55968.94</v>
       </c>
       <c r="I185">
         <v>65591.63</v>
@@ -6221,10 +6221,10 @@
         <v>57480.89</v>
       </c>
       <c r="H192">
-        <v>53172.98</v>
+        <v>52882.42</v>
       </c>
       <c r="I192">
-        <v>57480.89</v>
+        <v>62079.37</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.3">
@@ -6253,7 +6253,7 @@
         <v>57852.74</v>
       </c>
       <c r="I193">
-        <v>62883.41</v>
+        <v>67914.080000000002</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.3">
@@ -6282,7 +6282,7 @@
         <v>62819.23</v>
       </c>
       <c r="I194">
-        <v>68281.77</v>
+        <v>73744.31</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.3">
@@ -6311,7 +6311,7 @@
         <v>67765.09</v>
       </c>
       <c r="I195">
-        <v>73657.710000000006</v>
+        <v>79550.33</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.3">
@@ -6340,7 +6340,7 @@
         <v>67919.649999999994</v>
       </c>
       <c r="I196">
-        <v>78996.06</v>
+        <v>79731.759999999995</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.3">
@@ -6369,7 +6369,7 @@
         <v>68816.399999999994</v>
       </c>
       <c r="I197">
-        <v>84284.28</v>
+        <v>80784.47</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.3">
@@ -6398,7 +6398,7 @@
         <v>69704.19</v>
       </c>
       <c r="I198">
-        <v>89512.15</v>
+        <v>81826.649999999994</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.3">
@@ -6511,10 +6511,10 @@
         <v>57480.89</v>
       </c>
       <c r="H202">
-        <v>53172.98</v>
+        <v>52882.42</v>
       </c>
       <c r="I202">
-        <v>57480.89</v>
+        <v>62079.37</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.3">
@@ -6543,7 +6543,7 @@
         <v>54853.11</v>
       </c>
       <c r="I203">
-        <v>62883.41</v>
+        <v>64392.78</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.3">
@@ -6569,7 +6569,7 @@
         <v>59386.61</v>
       </c>
       <c r="H204">
-        <v>55102.02</v>
+        <v>54635.68</v>
       </c>
       <c r="I204">
         <v>64137.54</v>
@@ -6598,7 +6598,7 @@
         <v>59600.58</v>
       </c>
       <c r="H205">
-        <v>55968.94</v>
+        <v>54832.54</v>
       </c>
       <c r="I205">
         <v>64368.63</v>
@@ -6627,7 +6627,7 @@
         <v>60065.68</v>
       </c>
       <c r="H206">
-        <v>56779.16</v>
+        <v>55260.42</v>
       </c>
       <c r="I206">
         <v>64870.93</v>
@@ -6656,7 +6656,7 @@
         <v>60065.68</v>
       </c>
       <c r="H207">
-        <v>57537.99</v>
+        <v>55260.42</v>
       </c>
       <c r="I207">
         <v>64870.93</v>
@@ -6685,7 +6685,7 @@
         <v>59835.55</v>
       </c>
       <c r="H208">
-        <v>58250.09</v>
+        <v>55048.71</v>
       </c>
       <c r="I208">
         <v>64622.400000000001</v>
@@ -6714,7 +6714,7 @@
         <v>59835.55</v>
       </c>
       <c r="H209">
-        <v>58919.62</v>
+        <v>55048.71</v>
       </c>
       <c r="I209">
         <v>64622.400000000001</v>
@@ -6743,7 +6743,7 @@
         <v>60065.68</v>
       </c>
       <c r="H210">
-        <v>59550.239999999998</v>
+        <v>55260.42</v>
       </c>
       <c r="I210">
         <v>64870.93</v>
@@ -6772,7 +6772,7 @@
         <v>60065.68</v>
       </c>
       <c r="H211">
-        <v>60145.21</v>
+        <v>55260.42</v>
       </c>
       <c r="I211">
         <v>64870.93</v>
@@ -7091,10 +7091,10 @@
         <v>55865.43</v>
       </c>
       <c r="H222">
-        <v>53172.98</v>
+        <v>51396.19</v>
       </c>
       <c r="I222">
-        <v>57480.89</v>
+        <v>60334.66</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.3">
@@ -7123,7 +7123,7 @@
         <v>55114.98</v>
       </c>
       <c r="I223">
-        <v>62883.41</v>
+        <v>64700.2</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.3">
@@ -7152,7 +7152,7 @@
         <v>59102.85</v>
       </c>
       <c r="I224">
-        <v>68281.77</v>
+        <v>69381.61</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.3">
@@ -7181,7 +7181,7 @@
         <v>63379.26</v>
       </c>
       <c r="I225">
-        <v>73657.710000000006</v>
+        <v>74401.740000000005</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.3">
@@ -7210,7 +7210,7 @@
         <v>67965.09</v>
       </c>
       <c r="I226">
-        <v>78996.06</v>
+        <v>79785.11</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.3">
@@ -7239,7 +7239,7 @@
         <v>77541.539999999994</v>
       </c>
       <c r="I227">
-        <v>84284.28</v>
+        <v>91027.02</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.3">
@@ -7265,10 +7265,10 @@
         <v>89512.15</v>
       </c>
       <c r="H228">
-        <v>89512.15</v>
+        <v>82351.179999999993</v>
       </c>
       <c r="I228">
-        <v>89512.15</v>
+        <v>96673.12</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.3">
@@ -7294,10 +7294,10 @@
         <v>94671.4</v>
       </c>
       <c r="H229">
-        <v>94671.4</v>
+        <v>87097.69</v>
       </c>
       <c r="I229">
-        <v>94671.4</v>
+        <v>102245.11</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.3">
@@ -7323,10 +7323,10 @@
         <v>99755.44</v>
       </c>
       <c r="H230">
-        <v>99755.44</v>
+        <v>91775</v>
       </c>
       <c r="I230">
-        <v>99755.44</v>
+        <v>107735.88</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.3">
@@ -7352,10 +7352,10 @@
         <v>104759.1</v>
       </c>
       <c r="H231">
-        <v>104759.1</v>
+        <v>96378.37</v>
       </c>
       <c r="I231">
-        <v>104759.1</v>
+        <v>113139.83</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.3">
@@ -7381,10 +7381,10 @@
         <v>57082.33</v>
       </c>
       <c r="H232">
-        <v>53172.98</v>
+        <v>52515.74</v>
       </c>
       <c r="I232">
-        <v>57480.89</v>
+        <v>61648.92</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.3">
@@ -7413,7 +7413,7 @@
         <v>55787.96</v>
       </c>
       <c r="I233">
-        <v>62883.41</v>
+        <v>65490.21</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.3">
@@ -7584,7 +7584,7 @@
         <v>63371.839999999997</v>
       </c>
       <c r="H239">
-        <v>58919.62</v>
+        <v>58302.09</v>
       </c>
       <c r="I239">
         <v>68441.59</v>
@@ -7613,7 +7613,7 @@
         <v>63978.49</v>
       </c>
       <c r="H240">
-        <v>59550.239999999998</v>
+        <v>58860.21</v>
       </c>
       <c r="I240">
         <v>69096.759999999995</v>
@@ -7642,7 +7642,7 @@
         <v>64349.68</v>
       </c>
       <c r="H241">
-        <v>60145.21</v>
+        <v>59201.71</v>
       </c>
       <c r="I241">
         <v>69497.66</v>
@@ -7961,10 +7961,10 @@
         <v>4912.8900000000003</v>
       </c>
       <c r="H252">
-        <v>4523.8</v>
+        <v>4519.8500000000004</v>
       </c>
       <c r="I252">
-        <v>4912.8900000000003</v>
+        <v>5305.92</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.3">
@@ -7993,7 +7993,7 @@
         <v>4989.5600000000004</v>
       </c>
       <c r="I253">
-        <v>5423.43</v>
+        <v>5857.31</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.3">
@@ -8022,7 +8022,7 @@
         <v>5463.18</v>
       </c>
       <c r="I254">
-        <v>5938.24</v>
+        <v>6413.3</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.3">
@@ -8051,7 +8051,7 @@
         <v>5938.8</v>
       </c>
       <c r="I255">
-        <v>6455.22</v>
+        <v>6971.63</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.3">
@@ -8080,7 +8080,7 @@
         <v>6414.76</v>
       </c>
       <c r="I256">
-        <v>6972.57</v>
+        <v>7530.38</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.3">
@@ -8109,7 +8109,7 @@
         <v>6254.54</v>
       </c>
       <c r="I257">
-        <v>7488.76</v>
+        <v>7342.28</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.3">
@@ -8138,7 +8138,7 @@
         <v>6464.25</v>
       </c>
       <c r="I258">
-        <v>8002.49</v>
+        <v>7588.47</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.3">
@@ -8167,7 +8167,7 @@
         <v>6671.87</v>
       </c>
       <c r="I259">
-        <v>8512.64</v>
+        <v>7832.19</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.3">
@@ -8196,7 +8196,7 @@
         <v>6877.41</v>
       </c>
       <c r="I260">
-        <v>9018.31</v>
+        <v>8073.48</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.3">
@@ -8225,7 +8225,7 @@
         <v>7080.9</v>
       </c>
       <c r="I261">
-        <v>9518.7000000000007</v>
+        <v>8312.3700000000008</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.3">
@@ -8251,10 +8251,10 @@
         <v>4912.8900000000003</v>
       </c>
       <c r="H262">
-        <v>4523.8</v>
+        <v>4519.8500000000004</v>
       </c>
       <c r="I262">
-        <v>4912.8900000000003</v>
+        <v>5305.92</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.3">
@@ -8283,7 +8283,7 @@
         <v>4747.83</v>
       </c>
       <c r="I263">
-        <v>5423.43</v>
+        <v>5573.54</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.3">
@@ -8338,7 +8338,7 @@
         <v>5199.08</v>
       </c>
       <c r="H265">
-        <v>4824.75</v>
+        <v>4783.16</v>
       </c>
       <c r="I265">
         <v>5615.01</v>
@@ -8367,7 +8367,7 @@
         <v>5191.5</v>
       </c>
       <c r="H266">
-        <v>4912.7299999999996</v>
+        <v>4776.18</v>
       </c>
       <c r="I266">
         <v>5606.82</v>
@@ -8396,7 +8396,7 @@
         <v>5191.5</v>
       </c>
       <c r="H267">
-        <v>4995.4399999999996</v>
+        <v>4776.18</v>
       </c>
       <c r="I267">
         <v>5606.82</v>
@@ -8425,7 +8425,7 @@
         <v>5191.5</v>
       </c>
       <c r="H268">
-        <v>5073.32</v>
+        <v>4776.18</v>
       </c>
       <c r="I268">
         <v>5606.82</v>
@@ -8454,7 +8454,7 @@
         <v>5191.5</v>
       </c>
       <c r="H269">
-        <v>5146.78</v>
+        <v>4776.18</v>
       </c>
       <c r="I269">
         <v>5606.82</v>
@@ -8483,7 +8483,7 @@
         <v>5191.5</v>
       </c>
       <c r="H270">
-        <v>5216.18</v>
+        <v>4776.18</v>
       </c>
       <c r="I270">
         <v>5606.82</v>
@@ -8512,7 +8512,7 @@
         <v>5281.84</v>
       </c>
       <c r="H271">
-        <v>5281.84</v>
+        <v>4859.29</v>
       </c>
       <c r="I271">
         <v>5704.39</v>
@@ -8686,7 +8686,7 @@
         <v>7488.76</v>
       </c>
       <c r="H277">
-        <v>7488.76</v>
+        <v>6889.66</v>
       </c>
       <c r="I277">
         <v>7488.76</v>
@@ -8715,7 +8715,7 @@
         <v>8002.49</v>
       </c>
       <c r="H278">
-        <v>8002.49</v>
+        <v>7362.29</v>
       </c>
       <c r="I278">
         <v>8002.49</v>
@@ -8744,7 +8744,7 @@
         <v>8512.64</v>
       </c>
       <c r="H279">
-        <v>8512.64</v>
+        <v>7831.63</v>
       </c>
       <c r="I279">
         <v>8512.64</v>
@@ -8773,7 +8773,7 @@
         <v>9018.31</v>
       </c>
       <c r="H280">
-        <v>9018.31</v>
+        <v>8296.84</v>
       </c>
       <c r="I280">
         <v>9018.31</v>
@@ -8802,7 +8802,7 @@
         <v>9518.7000000000007</v>
       </c>
       <c r="H281">
-        <v>9518.7000000000007</v>
+        <v>8757.2000000000007</v>
       </c>
       <c r="I281">
         <v>9518.7000000000007</v>
@@ -8831,10 +8831,10 @@
         <v>4810.8100000000004</v>
       </c>
       <c r="H282">
-        <v>4523.8</v>
+        <v>4425.9399999999996</v>
       </c>
       <c r="I282">
-        <v>4912.8900000000003</v>
+        <v>5195.67</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.3">
@@ -8863,7 +8863,7 @@
         <v>4829.3</v>
       </c>
       <c r="I283">
-        <v>5423.43</v>
+        <v>5669.18</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.3">
@@ -8892,7 +8892,7 @@
         <v>5269.41</v>
       </c>
       <c r="I284">
-        <v>5938.24</v>
+        <v>6185.83</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.3">
@@ -8921,7 +8921,7 @@
         <v>5938.8</v>
       </c>
       <c r="I285">
-        <v>6455.22</v>
+        <v>6971.63</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.3">
@@ -8950,7 +8950,7 @@
         <v>6414.76</v>
       </c>
       <c r="I286">
-        <v>6972.57</v>
+        <v>7530.38</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.3">
@@ -8976,10 +8976,10 @@
         <v>7488.76</v>
       </c>
       <c r="H287">
-        <v>7488.76</v>
+        <v>6889.66</v>
       </c>
       <c r="I287">
-        <v>7488.76</v>
+        <v>8087.86</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.3">
@@ -9005,10 +9005,10 @@
         <v>8002.49</v>
       </c>
       <c r="H288">
-        <v>8002.49</v>
+        <v>7362.29</v>
       </c>
       <c r="I288">
-        <v>8002.49</v>
+        <v>8642.69</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.3">
@@ -9034,10 +9034,10 @@
         <v>8512.64</v>
       </c>
       <c r="H289">
-        <v>8512.64</v>
+        <v>7831.63</v>
       </c>
       <c r="I289">
-        <v>8512.64</v>
+        <v>9193.66</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.3">
@@ -9063,10 +9063,10 @@
         <v>9018.31</v>
       </c>
       <c r="H290">
-        <v>9018.31</v>
+        <v>8296.84</v>
       </c>
       <c r="I290">
-        <v>9018.31</v>
+        <v>9739.77</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.3">
@@ -9092,10 +9092,10 @@
         <v>9518.7000000000007</v>
       </c>
       <c r="H291">
-        <v>9518.7000000000007</v>
+        <v>8757.2000000000007</v>
       </c>
       <c r="I291">
-        <v>9518.7000000000007</v>
+        <v>10280.200000000001</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.3">
@@ -9121,10 +9121,10 @@
         <v>4864.4799999999996</v>
       </c>
       <c r="H292">
-        <v>4523.8</v>
+        <v>4475.32</v>
       </c>
       <c r="I292">
-        <v>4912.8900000000003</v>
+        <v>5253.64</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.3">
@@ -9153,7 +9153,7 @@
         <v>4714.1000000000004</v>
       </c>
       <c r="I293">
-        <v>5423.43</v>
+        <v>5533.94</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.3">
@@ -76626,6 +76626,31 @@
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="A382:A391"/>
+    <mergeCell ref="A152:A161"/>
+    <mergeCell ref="A162:A171"/>
+    <mergeCell ref="A242:A251"/>
+    <mergeCell ref="A252:A261"/>
+    <mergeCell ref="A292:A301"/>
+    <mergeCell ref="A282:A291"/>
+    <mergeCell ref="A322:A331"/>
+    <mergeCell ref="A312:A321"/>
+    <mergeCell ref="A332:A341"/>
+    <mergeCell ref="A372:A381"/>
+    <mergeCell ref="A102:A111"/>
+    <mergeCell ref="A142:A151"/>
+    <mergeCell ref="A362:A371"/>
+    <mergeCell ref="A202:A211"/>
+    <mergeCell ref="A182:A191"/>
+    <mergeCell ref="A232:A241"/>
+    <mergeCell ref="A352:A361"/>
+    <mergeCell ref="A172:A181"/>
+    <mergeCell ref="A222:A231"/>
+    <mergeCell ref="A132:A141"/>
+    <mergeCell ref="A212:A221"/>
+    <mergeCell ref="A112:A121"/>
+    <mergeCell ref="A262:A271"/>
+    <mergeCell ref="A342:A351"/>
     <mergeCell ref="A12:A21"/>
     <mergeCell ref="A192:A201"/>
     <mergeCell ref="A272:A281"/>
@@ -76637,34 +76662,9 @@
     <mergeCell ref="A32:A41"/>
     <mergeCell ref="A22:A31"/>
     <mergeCell ref="A52:A61"/>
-    <mergeCell ref="A332:A341"/>
-    <mergeCell ref="A372:A381"/>
-    <mergeCell ref="A102:A111"/>
-    <mergeCell ref="A142:A151"/>
-    <mergeCell ref="A362:A371"/>
-    <mergeCell ref="A202:A211"/>
-    <mergeCell ref="A182:A191"/>
     <mergeCell ref="A92:A101"/>
-    <mergeCell ref="A232:A241"/>
-    <mergeCell ref="A352:A361"/>
-    <mergeCell ref="A172:A181"/>
     <mergeCell ref="A82:A91"/>
-    <mergeCell ref="A222:A231"/>
-    <mergeCell ref="A132:A141"/>
-    <mergeCell ref="A212:A221"/>
-    <mergeCell ref="A112:A121"/>
-    <mergeCell ref="A262:A271"/>
     <mergeCell ref="A62:A71"/>
-    <mergeCell ref="A342:A351"/>
-    <mergeCell ref="A382:A391"/>
-    <mergeCell ref="A152:A161"/>
-    <mergeCell ref="A162:A171"/>
-    <mergeCell ref="A242:A251"/>
-    <mergeCell ref="A252:A261"/>
-    <mergeCell ref="A292:A301"/>
-    <mergeCell ref="A282:A291"/>
-    <mergeCell ref="A322:A331"/>
-    <mergeCell ref="A312:A321"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Documentos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="545" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FCF35C3-ABE5-48A2-88F6-3EEBCB61B905}"/>
+  <xr:revisionPtr revIDLastSave="583" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE08D481-A9EE-4CCA-B5BD-FAFA6290DE59}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Proyecciones" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$I$436</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$I$451</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="89">
   <si>
     <t>Id</t>
   </si>
@@ -370,7 +370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -378,30 +378,11 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -731,7 +712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}">
-  <dimension ref="A1:I436"/>
+  <dimension ref="A1:I451"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
@@ -5267,147 +5248,147 @@
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A157" s="5">
+      <c r="A157">
         <v>325</v>
       </c>
-      <c r="B157" s="5" t="s">
+      <c r="B157" t="s">
         <v>54</v>
       </c>
-      <c r="C157" s="6">
+      <c r="C157" s="2">
         <v>46387</v>
       </c>
-      <c r="D157" s="5">
+      <c r="D157">
         <v>2026</v>
       </c>
-      <c r="E157" s="5" t="s">
+      <c r="E157" t="s">
         <v>12</v>
       </c>
-      <c r="F157" s="5" t="s">
+      <c r="F157" t="s">
         <v>30</v>
       </c>
-      <c r="G157" s="5">
+      <c r="G157">
         <v>6</v>
       </c>
-      <c r="H157" s="5">
+      <c r="H157">
         <v>4</v>
       </c>
-      <c r="I157" s="5">
+      <c r="I157">
         <v>8</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A158" s="5">
+      <c r="A158">
         <v>325</v>
       </c>
-      <c r="B158" s="5" t="s">
+      <c r="B158" t="s">
         <v>54</v>
       </c>
-      <c r="C158" s="6">
+      <c r="C158" s="2">
         <v>46752</v>
       </c>
-      <c r="D158" s="5">
+      <c r="D158">
         <v>2027</v>
       </c>
-      <c r="E158" s="5" t="s">
+      <c r="E158" t="s">
         <v>14</v>
       </c>
-      <c r="F158" s="5" t="s">
+      <c r="F158" t="s">
         <v>30</v>
       </c>
-      <c r="G158" s="5">
+      <c r="G158">
         <v>6</v>
       </c>
-      <c r="H158" s="5">
+      <c r="H158">
         <v>4</v>
       </c>
-      <c r="I158" s="5">
+      <c r="I158">
         <v>8</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A159" s="5">
+      <c r="A159">
         <v>325</v>
       </c>
-      <c r="B159" s="5" t="s">
+      <c r="B159" t="s">
         <v>54</v>
       </c>
-      <c r="C159" s="6">
+      <c r="C159" s="2">
         <v>47118</v>
       </c>
-      <c r="D159" s="5">
+      <c r="D159">
         <v>2028</v>
       </c>
-      <c r="E159" s="5" t="s">
+      <c r="E159" t="s">
         <v>16</v>
       </c>
-      <c r="F159" s="5" t="s">
+      <c r="F159" t="s">
         <v>30</v>
       </c>
-      <c r="G159" s="5">
+      <c r="G159">
         <v>7</v>
       </c>
-      <c r="H159" s="5">
+      <c r="H159">
         <v>5</v>
       </c>
-      <c r="I159" s="5">
+      <c r="I159">
         <v>9</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A160" s="5">
+      <c r="A160">
         <v>325</v>
       </c>
-      <c r="B160" s="5" t="s">
+      <c r="B160" t="s">
         <v>54</v>
       </c>
-      <c r="C160" s="6">
+      <c r="C160" s="2">
         <v>47483</v>
       </c>
-      <c r="D160" s="5">
+      <c r="D160">
         <v>2029</v>
       </c>
-      <c r="E160" s="5" t="s">
+      <c r="E160" t="s">
         <v>18</v>
       </c>
-      <c r="F160" s="5" t="s">
+      <c r="F160" t="s">
         <v>30</v>
       </c>
-      <c r="G160" s="5">
+      <c r="G160">
         <v>7</v>
       </c>
-      <c r="H160" s="5">
+      <c r="H160">
         <v>5</v>
       </c>
-      <c r="I160" s="5">
+      <c r="I160">
         <v>9</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A161" s="5">
+      <c r="A161">
         <v>325</v>
       </c>
-      <c r="B161" s="5" t="s">
+      <c r="B161" t="s">
         <v>54</v>
       </c>
-      <c r="C161" s="6">
+      <c r="C161" s="2">
         <v>47848</v>
       </c>
-      <c r="D161" s="5">
+      <c r="D161">
         <v>2030</v>
       </c>
-      <c r="E161" s="5" t="s">
+      <c r="E161" t="s">
         <v>20</v>
       </c>
-      <c r="F161" s="5" t="s">
+      <c r="F161" t="s">
         <v>30</v>
       </c>
-      <c r="G161" s="5">
+      <c r="G161">
         <v>7</v>
       </c>
-      <c r="H161" s="5">
+      <c r="H161">
         <v>5</v>
       </c>
-      <c r="I161" s="5">
+      <c r="I161">
         <v>9</v>
       </c>
     </row>
@@ -5991,148 +5972,148 @@
         <v>97.333863682011312</v>
       </c>
     </row>
-    <row r="182" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="5">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A182">
         <v>361</v>
       </c>
-      <c r="B182" s="5" t="s">
+      <c r="B182" t="s">
         <v>57</v>
       </c>
-      <c r="C182" s="6">
+      <c r="C182" s="2">
         <v>46387</v>
       </c>
-      <c r="D182" s="5">
+      <c r="D182">
         <v>2026</v>
       </c>
-      <c r="E182" s="5" t="s">
+      <c r="E182" t="s">
         <v>12</v>
       </c>
-      <c r="F182" s="5" t="s">
+      <c r="F182" t="s">
         <v>88</v>
       </c>
-      <c r="G182" s="5">
+      <c r="G182">
         <v>4.82</v>
       </c>
-      <c r="H182" s="5">
+      <c r="H182">
         <v>4.7236000000000002</v>
       </c>
-      <c r="I182" s="5">
+      <c r="I182">
         <v>4.83446</v>
       </c>
     </row>
-    <row r="183" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="5">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A183">
         <v>361</v>
       </c>
-      <c r="B183" s="5" t="s">
+      <c r="B183" t="s">
         <v>57</v>
       </c>
-      <c r="C183" s="6">
+      <c r="C183" s="2">
         <v>46752</v>
       </c>
-      <c r="D183" s="5">
+      <c r="D183">
         <v>2027</v>
       </c>
-      <c r="E183" s="5" t="s">
+      <c r="E183" t="s">
         <v>14</v>
       </c>
-      <c r="F183" s="5" t="s">
+      <c r="F183" t="s">
         <v>88</v>
       </c>
-      <c r="G183" s="5">
+      <c r="G183">
         <v>4.8499999999999996</v>
       </c>
-      <c r="H183" s="5">
+      <c r="H183">
         <v>4.7529999999999992</v>
       </c>
-      <c r="I183" s="5">
+      <c r="I183">
         <v>4.8645499999999995</v>
       </c>
     </row>
-    <row r="184" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="5">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A184">
         <v>361</v>
       </c>
-      <c r="B184" s="5" t="s">
+      <c r="B184" t="s">
         <v>57</v>
       </c>
-      <c r="C184" s="6">
+      <c r="C184" s="2">
         <v>47118</v>
       </c>
-      <c r="D184" s="5">
+      <c r="D184">
         <v>2028</v>
       </c>
-      <c r="E184" s="5" t="s">
+      <c r="E184" t="s">
         <v>16</v>
       </c>
-      <c r="F184" s="5" t="s">
+      <c r="F184" t="s">
         <v>88</v>
       </c>
-      <c r="G184" s="5">
+      <c r="G184">
         <v>4.87</v>
       </c>
-      <c r="H184" s="5">
+      <c r="H184">
         <v>4.7725999999999997</v>
       </c>
-      <c r="I184" s="5">
+      <c r="I184">
         <v>4.8846099999999995</v>
       </c>
     </row>
-    <row r="185" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="5">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A185">
         <v>361</v>
       </c>
-      <c r="B185" s="5" t="s">
+      <c r="B185" t="s">
         <v>57</v>
       </c>
-      <c r="C185" s="6">
+      <c r="C185" s="2">
         <v>47483</v>
       </c>
-      <c r="D185" s="5">
+      <c r="D185">
         <v>2029</v>
       </c>
-      <c r="E185" s="5" t="s">
+      <c r="E185" t="s">
         <v>18</v>
       </c>
-      <c r="F185" s="5" t="s">
+      <c r="F185" t="s">
         <v>88</v>
       </c>
-      <c r="G185" s="5">
+      <c r="G185">
         <v>4.91</v>
       </c>
-      <c r="H185" s="5">
+      <c r="H185">
         <v>4.8117999999999999</v>
       </c>
-      <c r="I185" s="5">
+      <c r="I185">
         <v>4.9247299999999994</v>
       </c>
     </row>
-    <row r="186" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="5">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A186">
         <v>361</v>
       </c>
-      <c r="B186" s="5" t="s">
+      <c r="B186" t="s">
         <v>57</v>
       </c>
-      <c r="C186" s="6">
+      <c r="C186" s="2">
         <v>47848</v>
       </c>
-      <c r="D186" s="5">
+      <c r="D186">
         <v>2030</v>
       </c>
-      <c r="E186" s="5" t="s">
+      <c r="E186" t="s">
         <v>20</v>
       </c>
-      <c r="F186" s="5" t="s">
+      <c r="F186" t="s">
         <v>88</v>
       </c>
-      <c r="G186" s="5">
+      <c r="G186">
         <v>4.96</v>
       </c>
-      <c r="H186" s="5">
+      <c r="H186">
         <v>4.8608000000000002</v>
       </c>
-      <c r="I186" s="5">
+      <c r="I186">
         <v>4.9748799999999997</v>
       </c>
     </row>
@@ -6716,293 +6697,293 @@
         <v>29413.876278137071</v>
       </c>
     </row>
-    <row r="207" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="5">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A207">
         <v>423</v>
       </c>
-      <c r="B207" s="5" t="s">
+      <c r="B207" t="s">
         <v>67</v>
       </c>
-      <c r="C207" s="6">
+      <c r="C207" s="2">
         <v>46387</v>
       </c>
-      <c r="D207" s="5">
+      <c r="D207">
         <v>2026</v>
       </c>
-      <c r="E207" s="5" t="s">
+      <c r="E207" t="s">
         <v>12</v>
       </c>
-      <c r="F207" s="5" t="s">
+      <c r="F207" t="s">
         <v>30</v>
       </c>
-      <c r="G207" s="5">
+      <c r="G207">
         <v>12.6</v>
       </c>
-      <c r="H207" s="5">
+      <c r="H207">
         <v>12</v>
       </c>
-      <c r="I207" s="5">
+      <c r="I207">
         <v>13.2</v>
       </c>
     </row>
-    <row r="208" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="5">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A208">
         <v>423</v>
       </c>
-      <c r="B208" s="5" t="s">
+      <c r="B208" t="s">
         <v>67</v>
       </c>
-      <c r="C208" s="6">
+      <c r="C208" s="2">
         <v>46752</v>
       </c>
-      <c r="D208" s="5">
+      <c r="D208">
         <v>2027</v>
       </c>
-      <c r="E208" s="5" t="s">
+      <c r="E208" t="s">
         <v>14</v>
       </c>
-      <c r="F208" s="5" t="s">
+      <c r="F208" t="s">
         <v>30</v>
       </c>
-      <c r="G208" s="5">
+      <c r="G208">
         <v>13</v>
       </c>
-      <c r="H208" s="5">
+      <c r="H208">
         <v>12.4</v>
       </c>
-      <c r="I208" s="5">
+      <c r="I208">
         <v>13.3</v>
       </c>
     </row>
-    <row r="209" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="5">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A209">
         <v>423</v>
       </c>
-      <c r="B209" s="5" t="s">
+      <c r="B209" t="s">
         <v>67</v>
       </c>
-      <c r="C209" s="6">
+      <c r="C209" s="2">
         <v>47118</v>
       </c>
-      <c r="D209" s="5">
+      <c r="D209">
         <v>2028</v>
       </c>
-      <c r="E209" s="5" t="s">
+      <c r="E209" t="s">
         <v>16</v>
       </c>
-      <c r="F209" s="5" t="s">
+      <c r="F209" t="s">
         <v>30</v>
       </c>
-      <c r="G209" s="5">
+      <c r="G209">
         <v>13.3</v>
       </c>
-      <c r="H209" s="5">
+      <c r="H209">
         <v>12.6</v>
       </c>
-      <c r="I209" s="5">
+      <c r="I209">
         <v>13.5</v>
       </c>
     </row>
-    <row r="210" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="5">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A210">
         <v>423</v>
       </c>
-      <c r="B210" s="5" t="s">
+      <c r="B210" t="s">
         <v>67</v>
       </c>
-      <c r="C210" s="6">
+      <c r="C210" s="2">
         <v>47483</v>
       </c>
-      <c r="D210" s="5">
+      <c r="D210">
         <v>2029</v>
       </c>
-      <c r="E210" s="5" t="s">
+      <c r="E210" t="s">
         <v>18</v>
       </c>
-      <c r="F210" s="5" t="s">
+      <c r="F210" t="s">
         <v>30</v>
       </c>
-      <c r="G210" s="5">
+      <c r="G210">
         <v>13.5</v>
       </c>
-      <c r="H210" s="5">
+      <c r="H210">
         <v>13</v>
       </c>
-      <c r="I210" s="5">
+      <c r="I210">
         <v>13.8</v>
       </c>
     </row>
-    <row r="211" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="5">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A211">
         <v>423</v>
       </c>
-      <c r="B211" s="5" t="s">
+      <c r="B211" t="s">
         <v>67</v>
       </c>
-      <c r="C211" s="6">
+      <c r="C211" s="2">
         <v>47848</v>
       </c>
-      <c r="D211" s="5">
+      <c r="D211">
         <v>2030</v>
       </c>
-      <c r="E211" s="5" t="s">
+      <c r="E211" t="s">
         <v>20</v>
       </c>
-      <c r="F211" s="5" t="s">
+      <c r="F211" t="s">
         <v>30</v>
       </c>
-      <c r="G211" s="5">
+      <c r="G211">
         <v>13.8</v>
       </c>
-      <c r="H211" s="5">
+      <c r="H211">
         <v>13.3</v>
       </c>
-      <c r="I211" s="5">
+      <c r="I211">
         <v>14</v>
       </c>
     </row>
-    <row r="212" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="5">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A212">
         <v>424</v>
       </c>
-      <c r="B212" s="5" t="s">
+      <c r="B212" t="s">
         <v>68</v>
       </c>
-      <c r="C212" s="6">
+      <c r="C212" s="2">
         <v>46387</v>
       </c>
-      <c r="D212" s="5">
+      <c r="D212">
         <v>2026</v>
       </c>
-      <c r="E212" s="5" t="s">
+      <c r="E212" t="s">
         <v>12</v>
       </c>
-      <c r="F212" s="5" t="s">
+      <c r="F212" t="s">
         <v>30</v>
       </c>
-      <c r="G212" s="5">
+      <c r="G212">
         <v>9.6</v>
       </c>
-      <c r="H212" s="5">
+      <c r="H212">
         <v>8.8000000000000007</v>
       </c>
-      <c r="I212" s="5">
+      <c r="I212">
         <v>10.4</v>
       </c>
     </row>
-    <row r="213" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="5">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A213">
         <v>424</v>
       </c>
-      <c r="B213" s="5" t="s">
+      <c r="B213" t="s">
         <v>68</v>
       </c>
-      <c r="C213" s="6">
+      <c r="C213" s="2">
         <v>46752</v>
       </c>
-      <c r="D213" s="5">
+      <c r="D213">
         <v>2027</v>
       </c>
-      <c r="E213" s="5" t="s">
+      <c r="E213" t="s">
         <v>14</v>
       </c>
-      <c r="F213" s="5" t="s">
+      <c r="F213" t="s">
         <v>30</v>
       </c>
-      <c r="G213" s="5">
+      <c r="G213">
         <v>10.199999999999999</v>
       </c>
-      <c r="H213" s="5">
+      <c r="H213">
         <v>9.4</v>
       </c>
-      <c r="I213" s="5">
+      <c r="I213">
         <v>11</v>
       </c>
     </row>
-    <row r="214" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="5">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A214">
         <v>424</v>
       </c>
-      <c r="B214" s="5" t="s">
+      <c r="B214" t="s">
         <v>68</v>
       </c>
-      <c r="C214" s="6">
+      <c r="C214" s="2">
         <v>47118</v>
       </c>
-      <c r="D214" s="5">
+      <c r="D214">
         <v>2028</v>
       </c>
-      <c r="E214" s="5" t="s">
+      <c r="E214" t="s">
         <v>16</v>
       </c>
-      <c r="F214" s="5" t="s">
+      <c r="F214" t="s">
         <v>30</v>
       </c>
-      <c r="G214" s="5">
+      <c r="G214">
         <v>10.8</v>
       </c>
-      <c r="H214" s="5">
+      <c r="H214">
         <v>9.9</v>
       </c>
-      <c r="I214" s="5">
+      <c r="I214">
         <v>11.2</v>
       </c>
     </row>
-    <row r="215" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="5">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A215">
         <v>424</v>
       </c>
-      <c r="B215" s="5" t="s">
+      <c r="B215" t="s">
         <v>68</v>
       </c>
-      <c r="C215" s="6">
+      <c r="C215" s="2">
         <v>47483</v>
       </c>
-      <c r="D215" s="5">
+      <c r="D215">
         <v>2029</v>
       </c>
-      <c r="E215" s="5" t="s">
+      <c r="E215" t="s">
         <v>18</v>
       </c>
-      <c r="F215" s="5" t="s">
+      <c r="F215" t="s">
         <v>30</v>
       </c>
-      <c r="G215" s="5">
+      <c r="G215">
         <v>11.4</v>
       </c>
-      <c r="H215" s="5">
+      <c r="H215">
         <v>10.5</v>
       </c>
-      <c r="I215" s="5">
+      <c r="I215">
         <v>11.6</v>
       </c>
     </row>
-    <row r="216" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="5">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A216">
         <v>424</v>
       </c>
-      <c r="B216" s="5" t="s">
+      <c r="B216" t="s">
         <v>68</v>
       </c>
-      <c r="C216" s="6">
+      <c r="C216" s="2">
         <v>47848</v>
       </c>
-      <c r="D216" s="5">
+      <c r="D216">
         <v>2030</v>
       </c>
-      <c r="E216" s="5" t="s">
+      <c r="E216" t="s">
         <v>20</v>
       </c>
-      <c r="F216" s="5" t="s">
+      <c r="F216" t="s">
         <v>30</v>
       </c>
-      <c r="G216" s="5">
+      <c r="G216">
         <v>11.6</v>
       </c>
-      <c r="H216" s="5">
+      <c r="H216">
         <v>11</v>
       </c>
-      <c r="I216" s="5">
+      <c r="I216">
         <v>11.8</v>
       </c>
     </row>
@@ -7151,293 +7132,293 @@
         <v>98.831307694343209</v>
       </c>
     </row>
-    <row r="222" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="5">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A222">
         <v>77</v>
       </c>
-      <c r="B222" s="5" t="s">
+      <c r="B222" t="s">
         <v>71</v>
       </c>
-      <c r="C222" s="6">
+      <c r="C222" s="2">
         <v>46387</v>
       </c>
-      <c r="D222" s="5">
+      <c r="D222">
         <v>2026</v>
       </c>
-      <c r="E222" s="5" t="s">
+      <c r="E222" t="s">
         <v>12</v>
       </c>
-      <c r="F222" s="5" t="s">
+      <c r="F222" t="s">
         <v>61</v>
       </c>
-      <c r="G222" s="5">
+      <c r="G222">
         <v>95.596500000000006</v>
       </c>
-      <c r="H222" s="5">
+      <c r="H222">
         <v>88.991250000000008</v>
       </c>
-      <c r="I222" s="5">
+      <c r="I222">
         <v>98.67895</v>
       </c>
     </row>
-    <row r="223" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="5">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A223">
         <v>77</v>
       </c>
-      <c r="B223" s="5" t="s">
+      <c r="B223" t="s">
         <v>71</v>
       </c>
-      <c r="C223" s="6">
+      <c r="C223" s="2">
         <v>46752</v>
       </c>
-      <c r="D223" s="5">
+      <c r="D223">
         <v>2027</v>
       </c>
-      <c r="E223" s="5" t="s">
+      <c r="E223" t="s">
         <v>14</v>
       </c>
-      <c r="F223" s="5" t="s">
+      <c r="F223" t="s">
         <v>61</v>
       </c>
-      <c r="G223" s="5">
+      <c r="G223">
         <v>96.552465000000012</v>
       </c>
-      <c r="H223" s="5">
+      <c r="H223">
         <v>91.38116250000003</v>
       </c>
-      <c r="I223" s="5">
+      <c r="I223">
         <v>98.965739499999998</v>
       </c>
     </row>
-    <row r="224" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="5">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A224">
         <v>77</v>
       </c>
-      <c r="B224" s="5" t="s">
+      <c r="B224" t="s">
         <v>71</v>
       </c>
-      <c r="C224" s="6">
+      <c r="C224" s="2">
         <v>47118</v>
       </c>
-      <c r="D224" s="5">
+      <c r="D224">
         <v>2028</v>
       </c>
-      <c r="E224" s="5" t="s">
+      <c r="E224" t="s">
         <v>16</v>
       </c>
-      <c r="F224" s="5" t="s">
+      <c r="F224" t="s">
         <v>61</v>
       </c>
-      <c r="G224" s="5">
+      <c r="G224">
         <v>97.517989650000018</v>
       </c>
-      <c r="H224" s="5">
-        <v>93.794974125000039</v>
-      </c>
-      <c r="I224" s="5">
+      <c r="H224">
+        <v>91.666910271000006</v>
+      </c>
+      <c r="I224">
         <v>99.255396895000004</v>
       </c>
     </row>
-    <row r="225" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="5">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A225">
         <v>77</v>
       </c>
-      <c r="B225" s="5" t="s">
+      <c r="B225" t="s">
         <v>71</v>
       </c>
-      <c r="C225" s="6">
+      <c r="C225" s="2">
         <v>47483</v>
       </c>
-      <c r="D225" s="5">
+      <c r="D225">
         <v>2029</v>
       </c>
-      <c r="E225" s="5" t="s">
+      <c r="E225" t="s">
         <v>18</v>
       </c>
-      <c r="F225" s="5" t="s">
+      <c r="F225" t="s">
         <v>61</v>
       </c>
-      <c r="G225" s="5">
+      <c r="G225">
         <v>98.493169546500013</v>
       </c>
-      <c r="H225" s="5">
-        <v>96.232923866250033</v>
-      </c>
-      <c r="I225" s="5">
+      <c r="H225">
+        <v>92.583579373710009</v>
+      </c>
+      <c r="I225">
         <v>99.547950863950007</v>
       </c>
     </row>
-    <row r="226" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="5">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A226">
         <v>77</v>
       </c>
-      <c r="B226" s="5" t="s">
+      <c r="B226" t="s">
         <v>71</v>
       </c>
-      <c r="C226" s="6">
+      <c r="C226" s="2">
         <v>47848</v>
       </c>
-      <c r="D226" s="5">
+      <c r="D226">
         <v>2030</v>
       </c>
-      <c r="E226" s="5" t="s">
+      <c r="E226" t="s">
         <v>20</v>
       </c>
-      <c r="F226" s="5" t="s">
+      <c r="F226" t="s">
         <v>61</v>
       </c>
-      <c r="G226" s="5">
+      <c r="G226">
         <v>99.478101241965021</v>
       </c>
-      <c r="H226" s="5">
-        <v>98.695253104912553</v>
-      </c>
-      <c r="I226" s="5">
+      <c r="H226">
+        <v>93.509415167447116</v>
+      </c>
+      <c r="I226">
         <v>99.843430372589509</v>
       </c>
     </row>
-    <row r="227" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="5">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A227">
         <v>98</v>
       </c>
-      <c r="B227" s="5" t="s">
+      <c r="B227" t="s">
         <v>74</v>
       </c>
-      <c r="C227" s="6">
+      <c r="C227" s="2">
         <v>46387</v>
       </c>
-      <c r="D227" s="5">
+      <c r="D227">
         <v>2026</v>
       </c>
-      <c r="E227" s="5" t="s">
+      <c r="E227" t="s">
         <v>12</v>
       </c>
-      <c r="F227" s="5" t="s">
+      <c r="F227" t="s">
         <v>35</v>
       </c>
-      <c r="G227" s="5">
+      <c r="G227">
         <v>8</v>
       </c>
-      <c r="H227" s="5">
+      <c r="H227">
         <v>6</v>
       </c>
-      <c r="I227" s="5">
+      <c r="I227">
         <v>10</v>
       </c>
     </row>
-    <row r="228" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="5">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A228">
         <v>98</v>
       </c>
-      <c r="B228" s="5" t="s">
+      <c r="B228" t="s">
         <v>74</v>
       </c>
-      <c r="C228" s="6">
+      <c r="C228" s="2">
         <v>46752</v>
       </c>
-      <c r="D228" s="5">
+      <c r="D228">
         <v>2027</v>
       </c>
-      <c r="E228" s="5" t="s">
+      <c r="E228" t="s">
         <v>14</v>
       </c>
-      <c r="F228" s="5" t="s">
+      <c r="F228" t="s">
         <v>35</v>
       </c>
-      <c r="G228" s="5">
+      <c r="G228">
         <v>7</v>
       </c>
-      <c r="H228" s="5">
+      <c r="H228">
         <v>5</v>
       </c>
-      <c r="I228" s="5">
+      <c r="I228">
         <v>10</v>
       </c>
     </row>
-    <row r="229" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A229" s="5">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A229">
         <v>98</v>
       </c>
-      <c r="B229" s="5" t="s">
+      <c r="B229" t="s">
         <v>74</v>
       </c>
-      <c r="C229" s="6">
+      <c r="C229" s="2">
         <v>47118</v>
       </c>
-      <c r="D229" s="5">
+      <c r="D229">
         <v>2028</v>
       </c>
-      <c r="E229" s="5" t="s">
+      <c r="E229" t="s">
         <v>16</v>
       </c>
-      <c r="F229" s="5" t="s">
+      <c r="F229" t="s">
         <v>35</v>
       </c>
-      <c r="G229" s="5">
+      <c r="G229">
         <v>7</v>
       </c>
-      <c r="H229" s="5">
+      <c r="H229">
         <v>5</v>
       </c>
-      <c r="I229" s="5">
+      <c r="I229">
         <v>10</v>
       </c>
     </row>
-    <row r="230" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="5">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A230">
         <v>98</v>
       </c>
-      <c r="B230" s="5" t="s">
+      <c r="B230" t="s">
         <v>74</v>
       </c>
-      <c r="C230" s="6">
+      <c r="C230" s="2">
         <v>47483</v>
       </c>
-      <c r="D230" s="5">
+      <c r="D230">
         <v>2029</v>
       </c>
-      <c r="E230" s="5" t="s">
+      <c r="E230" t="s">
         <v>18</v>
       </c>
-      <c r="F230" s="5" t="s">
+      <c r="F230" t="s">
         <v>35</v>
       </c>
-      <c r="G230" s="5">
+      <c r="G230">
         <v>9</v>
       </c>
-      <c r="H230" s="5">
+      <c r="H230">
         <v>7</v>
       </c>
-      <c r="I230" s="5">
+      <c r="I230">
         <v>12</v>
       </c>
     </row>
-    <row r="231" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="5">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A231">
         <v>98</v>
       </c>
-      <c r="B231" s="5" t="s">
+      <c r="B231" t="s">
         <v>74</v>
       </c>
-      <c r="C231" s="6">
+      <c r="C231" s="2">
         <v>47848</v>
       </c>
-      <c r="D231" s="5">
+      <c r="D231">
         <v>2030</v>
       </c>
-      <c r="E231" s="5" t="s">
+      <c r="E231" t="s">
         <v>20</v>
       </c>
-      <c r="F231" s="5" t="s">
+      <c r="F231" t="s">
         <v>35</v>
       </c>
-      <c r="G231" s="5">
+      <c r="G231">
         <v>9</v>
       </c>
-      <c r="H231" s="5">
+      <c r="H231">
         <v>7</v>
       </c>
-      <c r="I231" s="5">
+      <c r="I231">
         <v>12</v>
       </c>
     </row>
@@ -7457,17 +7438,17 @@
       <c r="E232" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F232" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G232" s="3">
-        <v>1658.8996505499999</v>
-      </c>
-      <c r="H232" s="3">
-        <v>1327.11972044</v>
-      </c>
-      <c r="I232" s="3">
-        <v>1990.6795806600001</v>
+      <c r="F232" t="s">
+        <v>35</v>
+      </c>
+      <c r="G232">
+        <v>5021.3256906738234</v>
+      </c>
+      <c r="H232">
+        <v>4017.0605525390588</v>
+      </c>
+      <c r="I232">
+        <v>6025.5908288085884</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.3">
@@ -7486,17 +7467,17 @@
       <c r="E233" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F233" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G233" s="3">
-        <v>1708.6666400664999</v>
-      </c>
-      <c r="H233" s="3">
-        <v>1356.681312212801</v>
-      </c>
-      <c r="I233" s="3">
-        <v>2060.6519679201988</v>
+      <c r="F233" t="s">
+        <v>35</v>
+      </c>
+      <c r="G233">
+        <v>5914.5712658767779</v>
+      </c>
+      <c r="H233">
+        <v>4696.1695851061622</v>
+      </c>
+      <c r="I233">
+        <v>7132.9729466473937</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.3">
@@ -7515,17 +7496,17 @@
       <c r="E234" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F234" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G234" s="3">
-        <v>1759.9266392684949</v>
-      </c>
-      <c r="H234" s="3">
-        <v>1386.822191743574</v>
-      </c>
-      <c r="I234" s="3">
-        <v>2133.0310867934159</v>
+      <c r="F234" t="s">
+        <v>35</v>
+      </c>
+      <c r="G234">
+        <v>6920.7335283964458</v>
+      </c>
+      <c r="H234">
+        <v>5453.5380203763998</v>
+      </c>
+      <c r="I234">
+        <v>8387.9290364164917</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.3">
@@ -7544,17 +7525,17 @@
       <c r="E235" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F235" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G235" s="3">
-        <v>1812.72443844655</v>
-      </c>
-      <c r="H235" s="3">
-        <v>1417.5505108652021</v>
-      </c>
-      <c r="I235" s="3">
-        <v>2207.8983660278982</v>
+      <c r="F235" t="s">
+        <v>35</v>
+      </c>
+      <c r="G235">
+        <v>8039.8124782328259</v>
+      </c>
+      <c r="H235">
+        <v>6287.1333579780694</v>
+      </c>
+      <c r="I235">
+        <v>9792.4915984875806</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.3">
@@ -7573,17 +7554,17 @@
       <c r="E236" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F236" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G236" s="3">
-        <v>1867.106171599946</v>
-      </c>
-      <c r="H236" s="3">
-        <v>1448.8743891615591</v>
-      </c>
-      <c r="I236" s="3">
-        <v>2285.3379540383339</v>
+      <c r="F236" t="s">
+        <v>35</v>
+      </c>
+      <c r="G236">
+        <v>9271.8081153859184</v>
+      </c>
+      <c r="H236">
+        <v>7194.923097539473</v>
+      </c>
+      <c r="I236">
+        <v>11348.693133232369</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.3">
@@ -7602,17 +7583,17 @@
       <c r="E237" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F237" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G237" s="3">
-        <v>3459.6733695200001</v>
-      </c>
-      <c r="H237" s="3">
-        <v>2767.7386956159999</v>
-      </c>
-      <c r="I237" s="3">
-        <v>4151.6080434240002</v>
+      <c r="F237" t="s">
+        <v>35</v>
+      </c>
+      <c r="G237">
+        <v>6702.3186977606192</v>
+      </c>
+      <c r="H237">
+        <v>5361.8549582084961</v>
+      </c>
+      <c r="I237">
+        <v>7390.2362842041885</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.3">
@@ -7631,17 +7612,17 @@
       <c r="E238" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F238" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G238" s="3">
-        <v>3563.4635706056001</v>
-      </c>
-      <c r="H238" s="3">
-        <v>2829.3900750608459</v>
-      </c>
-      <c r="I238" s="3">
-        <v>4297.537066150353</v>
+      <c r="F238" t="s">
+        <v>35</v>
+      </c>
+      <c r="G238">
+        <v>6668.9435105391967</v>
+      </c>
+      <c r="H238">
+        <v>5295.1411473681228</v>
+      </c>
+      <c r="I238">
+        <v>7373.9702695911656</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.3">
@@ -7660,17 +7641,17 @@
       <c r="E239" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F239" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G239" s="3">
-        <v>3670.3674777237679</v>
-      </c>
-      <c r="H239" s="3">
-        <v>2892.2495724463288</v>
-      </c>
-      <c r="I239" s="3">
-        <v>4448.4853830012071</v>
+      <c r="F239" t="s">
+        <v>35</v>
+      </c>
+      <c r="G239">
+        <v>6619.4758826049401</v>
+      </c>
+      <c r="H239">
+        <v>5216.1469954926933</v>
+      </c>
+      <c r="I239">
+        <v>7339.6554686125028</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.3">
@@ -7689,17 +7670,17 @@
       <c r="E240" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F240" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G240" s="3">
-        <v>3780.4785020554809</v>
-      </c>
-      <c r="H240" s="3">
-        <v>2956.3341886073872</v>
-      </c>
-      <c r="I240" s="3">
-        <v>4604.6228155035769</v>
+      <c r="F240" t="s">
+        <v>35</v>
+      </c>
+      <c r="G240">
+        <v>6553.9158139578494</v>
+      </c>
+      <c r="H240">
+        <v>5125.1621665150387</v>
+      </c>
+      <c r="I240">
+        <v>7287.1432275540574</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.3">
@@ -7718,17 +7699,17 @@
       <c r="E241" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F241" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G241" s="3">
-        <v>3893.892857117145</v>
-      </c>
-      <c r="H241" s="3">
-        <v>3021.6608571229049</v>
-      </c>
-      <c r="I241" s="3">
-        <v>4766.1248571113856</v>
+      <c r="F241" t="s">
+        <v>35</v>
+      </c>
+      <c r="G241">
+        <v>6472.2633045979237</v>
+      </c>
+      <c r="H241">
+        <v>5022.476324367989</v>
+      </c>
+      <c r="I241">
+        <v>7216.2848927016921</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.3">
@@ -7747,17 +7728,17 @@
       <c r="E242" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F242" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G242" s="3">
-        <v>3936.1035425</v>
-      </c>
-      <c r="H242" s="3">
-        <v>3605.5565998220659</v>
-      </c>
-      <c r="I242" s="3">
-        <v>4266.6504851779337</v>
+      <c r="F242" t="s">
+        <v>35</v>
+      </c>
+      <c r="G242">
+        <v>5646.493414116343</v>
+      </c>
+      <c r="H242">
+        <v>5477.0986116928534</v>
+      </c>
+      <c r="I242">
+        <v>6775.7920969396118</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.3">
@@ -7776,17 +7757,17 @@
       <c r="E243" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F243" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G243" s="3">
-        <v>4054.1866487749999</v>
-      </c>
-      <c r="H243" s="3">
-        <v>3703.509397287979</v>
-      </c>
-      <c r="I243" s="3">
-        <v>4404.8639002620193</v>
+      <c r="F243" t="s">
+        <v>35</v>
+      </c>
+      <c r="G243">
+        <v>6374.4716673772846</v>
+      </c>
+      <c r="H243">
+        <v>6177.5004928553271</v>
+      </c>
+      <c r="I243">
+        <v>7687.612830857006</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.3">
@@ -7805,17 +7786,17 @@
       <c r="E244" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F244" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G244" s="3">
-        <v>4175.8122482382496</v>
-      </c>
-      <c r="H244" s="3">
-        <v>3804.0943616620079</v>
-      </c>
-      <c r="I244" s="3">
-        <v>4547.5301348144903</v>
+      <c r="F244" t="s">
+        <v>35</v>
+      </c>
+      <c r="G244">
+        <v>7227.2111180454294</v>
+      </c>
+      <c r="H244">
+        <v>6997.3858044915851</v>
+      </c>
+      <c r="I244">
+        <v>8759.3798750710612</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.3">
@@ -7834,17 +7815,17 @@
       <c r="E245" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F245" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G245" s="3">
-        <v>4301.0866156853981</v>
-      </c>
-      <c r="H245" s="3">
-        <v>3907.3812654409198</v>
-      </c>
-      <c r="I245" s="3">
-        <v>4694.791965929875</v>
+      <c r="F245" t="s">
+        <v>35</v>
+      </c>
+      <c r="G245">
+        <v>8204.7117661207758</v>
+      </c>
+      <c r="H245">
+        <v>7936.417691368626</v>
+      </c>
+      <c r="I245">
+        <v>9993.3389311351038</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.3">
@@ -7863,17 +7844,17 @@
       <c r="E246" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F246" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G246" s="3">
-        <v>4430.1192141559604</v>
-      </c>
-      <c r="H246" s="3">
-        <v>4013.4416985210701</v>
-      </c>
-      <c r="I246" s="3">
-        <v>4846.7967297908481</v>
+      <c r="F246" t="s">
+        <v>35</v>
+      </c>
+      <c r="G246">
+        <v>9306.9736116033237</v>
+      </c>
+      <c r="H246">
+        <v>8994.2592982534516</v>
+      </c>
+      <c r="I246">
+        <v>11391.73570060247</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.3">
@@ -12227,147 +12208,147 @@
       </c>
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A397" s="5">
+      <c r="A397">
         <v>323</v>
       </c>
-      <c r="B397" s="5" t="s">
+      <c r="B397" t="s">
         <v>53</v>
       </c>
-      <c r="C397" s="6">
+      <c r="C397" s="2">
         <v>46387</v>
       </c>
-      <c r="D397" s="5">
+      <c r="D397">
         <v>2026</v>
       </c>
-      <c r="E397" s="5" t="s">
+      <c r="E397" t="s">
         <v>12</v>
       </c>
-      <c r="F397" s="5" t="s">
+      <c r="F397" t="s">
         <v>41</v>
       </c>
-      <c r="G397" s="5">
+      <c r="G397">
         <v>1</v>
       </c>
-      <c r="H397" s="5">
+      <c r="H397">
         <v>0</v>
       </c>
-      <c r="I397" s="5">
+      <c r="I397">
         <v>2</v>
       </c>
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A398" s="5">
+      <c r="A398">
         <v>323</v>
       </c>
-      <c r="B398" s="5" t="s">
+      <c r="B398" t="s">
         <v>53</v>
       </c>
-      <c r="C398" s="6">
+      <c r="C398" s="2">
         <v>46752</v>
       </c>
-      <c r="D398" s="5">
+      <c r="D398">
         <v>2027</v>
       </c>
-      <c r="E398" s="5" t="s">
+      <c r="E398" t="s">
         <v>14</v>
       </c>
-      <c r="F398" s="5" t="s">
+      <c r="F398" t="s">
         <v>41</v>
       </c>
-      <c r="G398" s="5">
+      <c r="G398">
         <v>1</v>
       </c>
-      <c r="H398" s="5">
+      <c r="H398">
         <v>0</v>
       </c>
-      <c r="I398" s="5">
+      <c r="I398">
         <v>2</v>
       </c>
     </row>
     <row r="399" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A399" s="5">
+      <c r="A399">
         <v>323</v>
       </c>
-      <c r="B399" s="5" t="s">
+      <c r="B399" t="s">
         <v>53</v>
       </c>
-      <c r="C399" s="6">
+      <c r="C399" s="2">
         <v>47118</v>
       </c>
-      <c r="D399" s="5">
+      <c r="D399">
         <v>2028</v>
       </c>
-      <c r="E399" s="5" t="s">
+      <c r="E399" t="s">
         <v>16</v>
       </c>
-      <c r="F399" s="5" t="s">
+      <c r="F399" t="s">
         <v>41</v>
       </c>
-      <c r="G399" s="5">
+      <c r="G399">
         <v>2</v>
       </c>
-      <c r="H399" s="5">
+      <c r="H399">
         <v>1</v>
       </c>
-      <c r="I399" s="5">
+      <c r="I399">
         <v>3</v>
       </c>
     </row>
     <row r="400" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A400" s="5">
+      <c r="A400">
         <v>323</v>
       </c>
-      <c r="B400" s="5" t="s">
+      <c r="B400" t="s">
         <v>53</v>
       </c>
-      <c r="C400" s="6">
+      <c r="C400" s="2">
         <v>47483</v>
       </c>
-      <c r="D400" s="5">
+      <c r="D400">
         <v>2029</v>
       </c>
-      <c r="E400" s="5" t="s">
+      <c r="E400" t="s">
         <v>18</v>
       </c>
-      <c r="F400" s="5" t="s">
+      <c r="F400" t="s">
         <v>41</v>
       </c>
-      <c r="G400" s="5">
+      <c r="G400">
         <v>2</v>
       </c>
-      <c r="H400" s="5">
+      <c r="H400">
         <v>1</v>
       </c>
-      <c r="I400" s="5">
+      <c r="I400">
         <v>3</v>
       </c>
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A401" s="5">
+      <c r="A401">
         <v>323</v>
       </c>
-      <c r="B401" s="5" t="s">
+      <c r="B401" t="s">
         <v>53</v>
       </c>
-      <c r="C401" s="6">
+      <c r="C401" s="2">
         <v>47848</v>
       </c>
-      <c r="D401" s="5">
+      <c r="D401">
         <v>2030</v>
       </c>
-      <c r="E401" s="5" t="s">
+      <c r="E401" t="s">
         <v>20</v>
       </c>
-      <c r="F401" s="5" t="s">
+      <c r="F401" t="s">
         <v>41</v>
       </c>
-      <c r="G401" s="5">
+      <c r="G401">
         <v>2</v>
       </c>
-      <c r="H401" s="5">
+      <c r="H401">
         <v>1</v>
       </c>
-      <c r="I401" s="5">
+      <c r="I401">
         <v>3</v>
       </c>
     </row>
@@ -13386,7 +13367,443 @@
         <v>30662.479119881289</v>
       </c>
     </row>
+    <row r="437" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A437" s="3">
+        <v>386.1</v>
+      </c>
+      <c r="B437" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C437" s="4">
+        <v>46387</v>
+      </c>
+      <c r="D437" s="3">
+        <v>2026</v>
+      </c>
+      <c r="E437" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F437" t="s">
+        <v>30</v>
+      </c>
+      <c r="G437">
+        <v>5053.2904950000002</v>
+      </c>
+      <c r="H437">
+        <v>4042.632396</v>
+      </c>
+      <c r="I437">
+        <v>6063.9485940000004</v>
+      </c>
+    </row>
+    <row r="438" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A438" s="3">
+        <v>386.1</v>
+      </c>
+      <c r="B438" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C438" s="4">
+        <v>46752</v>
+      </c>
+      <c r="D438" s="3">
+        <v>2027</v>
+      </c>
+      <c r="E438" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F438" t="s">
+        <v>30</v>
+      </c>
+      <c r="G438">
+        <v>6316.6131187499996</v>
+      </c>
+      <c r="H438">
+        <v>5015.3908162875014</v>
+      </c>
+      <c r="I438">
+        <v>7617.8354212124996</v>
+      </c>
+    </row>
+    <row r="439" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A439" s="3">
+        <v>386.1</v>
+      </c>
+      <c r="B439" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C439" s="4">
+        <v>47118</v>
+      </c>
+      <c r="D439" s="3">
+        <v>2028</v>
+      </c>
+      <c r="E439" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F439" t="s">
+        <v>30</v>
+      </c>
+      <c r="G439">
+        <v>7895.7663984375004</v>
+      </c>
+      <c r="H439">
+        <v>6221.8639219687502</v>
+      </c>
+      <c r="I439">
+        <v>9569.6688749062487</v>
+      </c>
+    </row>
+    <row r="440" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A440" s="3">
+        <v>386.1</v>
+      </c>
+      <c r="B440" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C440" s="4">
+        <v>47483</v>
+      </c>
+      <c r="D440" s="3">
+        <v>2029</v>
+      </c>
+      <c r="E440" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F440" t="s">
+        <v>30</v>
+      </c>
+      <c r="G440">
+        <v>9050.2238278000004</v>
+      </c>
+      <c r="H440">
+        <v>7077.2750333395998</v>
+      </c>
+      <c r="I440">
+        <v>11023.172622260399</v>
+      </c>
+    </row>
+    <row r="441" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A441" s="3">
+        <v>386.1</v>
+      </c>
+      <c r="B441" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C441" s="4">
+        <v>47848</v>
+      </c>
+      <c r="D441" s="3">
+        <v>2030</v>
+      </c>
+      <c r="E441" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F441" t="s">
+        <v>30</v>
+      </c>
+      <c r="G441">
+        <v>10086.119943899999</v>
+      </c>
+      <c r="H441">
+        <v>7826.8290764664016</v>
+      </c>
+      <c r="I441">
+        <v>12345.410811333601</v>
+      </c>
+    </row>
+    <row r="442" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A442" s="3">
+        <v>386.2</v>
+      </c>
+      <c r="B442" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C442" s="4">
+        <v>46387</v>
+      </c>
+      <c r="D442" s="3">
+        <v>2026</v>
+      </c>
+      <c r="E442" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F442" t="s">
+        <v>30</v>
+      </c>
+      <c r="G442">
+        <v>6864.5522870000004</v>
+      </c>
+      <c r="H442">
+        <v>5491.6418296000011</v>
+      </c>
+      <c r="I442">
+        <v>7569.1213256024957</v>
+      </c>
+    </row>
+    <row r="443" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A443" s="3">
+        <v>386.2</v>
+      </c>
+      <c r="B443" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C443" s="4">
+        <v>46752</v>
+      </c>
+      <c r="D443" s="3">
+        <v>2027</v>
+      </c>
+      <c r="E443" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F443" t="s">
+        <v>30</v>
+      </c>
+      <c r="G443">
+        <v>6928.2554168999995</v>
+      </c>
+      <c r="H443">
+        <v>5501.0348010186008</v>
+      </c>
+      <c r="I443">
+        <v>7660.696088310985</v>
+      </c>
+    </row>
+    <row r="444" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A444" s="3">
+        <v>386.2</v>
+      </c>
+      <c r="B444" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C444" s="4">
+        <v>47118</v>
+      </c>
+      <c r="D444" s="3">
+        <v>2028</v>
+      </c>
+      <c r="E444" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F444" t="s">
+        <v>30</v>
+      </c>
+      <c r="G444">
+        <v>6991.9585467999996</v>
+      </c>
+      <c r="H444">
+        <v>5509.6633348784007</v>
+      </c>
+      <c r="I444">
+        <v>7752.6631555816357</v>
+      </c>
+    </row>
+    <row r="445" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A445" s="3">
+        <v>386.2</v>
+      </c>
+      <c r="B445" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C445" s="4">
+        <v>47483</v>
+      </c>
+      <c r="D445" s="3">
+        <v>2029</v>
+      </c>
+      <c r="E445" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F445" t="s">
+        <v>30</v>
+      </c>
+      <c r="G445">
+        <v>7055.6616766999996</v>
+      </c>
+      <c r="H445">
+        <v>5517.5274311794001</v>
+      </c>
+      <c r="I445">
+        <v>7845.0225274144459</v>
+      </c>
+    </row>
+    <row r="446" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A446" s="3">
+        <v>386.2</v>
+      </c>
+      <c r="B446" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C446" s="4">
+        <v>47848</v>
+      </c>
+      <c r="D446" s="3">
+        <v>2030</v>
+      </c>
+      <c r="E446" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F446" t="s">
+        <v>30</v>
+      </c>
+      <c r="G446">
+        <v>7119.3648065999996</v>
+      </c>
+      <c r="H446">
+        <v>5524.6270899215997</v>
+      </c>
+      <c r="I446">
+        <v>7937.7742038094157</v>
+      </c>
+    </row>
+    <row r="447" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A447" s="3">
+        <v>386.3</v>
+      </c>
+      <c r="B447" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C447" s="4">
+        <v>46387</v>
+      </c>
+      <c r="D447" s="3">
+        <v>2026</v>
+      </c>
+      <c r="E447" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F447" t="s">
+        <v>30</v>
+      </c>
+      <c r="G447">
+        <v>5855.0681234999993</v>
+      </c>
+      <c r="H447">
+        <v>5679.416079794999</v>
+      </c>
+      <c r="I447">
+        <v>7026.0817481999993</v>
+      </c>
+    </row>
+    <row r="448" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A448" s="3">
+        <v>386.3</v>
+      </c>
+      <c r="B448" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C448" s="4">
+        <v>46752</v>
+      </c>
+      <c r="D448" s="3">
+        <v>2027</v>
+      </c>
+      <c r="E448" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F448" t="s">
+        <v>30</v>
+      </c>
+      <c r="G448">
+        <v>6416.9538656999994</v>
+      </c>
+      <c r="H448">
+        <v>6218.6699912498698</v>
+      </c>
+      <c r="I448">
+        <v>7738.846362034199</v>
+      </c>
+    </row>
+    <row r="449" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A449" s="3">
+        <v>386.3</v>
+      </c>
+      <c r="B449" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C449" s="4">
+        <v>47118</v>
+      </c>
+      <c r="D449" s="3">
+        <v>2028</v>
+      </c>
+      <c r="E449" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F449" t="s">
+        <v>30</v>
+      </c>
+      <c r="G449">
+        <v>6978.8396078999986</v>
+      </c>
+      <c r="H449">
+        <v>6756.9125083687786</v>
+      </c>
+      <c r="I449">
+        <v>8458.3536047747984</v>
+      </c>
+    </row>
+    <row r="450" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A450" s="3">
+        <v>386.3</v>
+      </c>
+      <c r="B450" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C450" s="4">
+        <v>47483</v>
+      </c>
+      <c r="D450" s="3">
+        <v>2029</v>
+      </c>
+      <c r="E450" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F450" t="s">
+        <v>30</v>
+      </c>
+      <c r="G450">
+        <v>7540.7253500999996</v>
+      </c>
+      <c r="H450">
+        <v>7294.1436311517291</v>
+      </c>
+      <c r="I450">
+        <v>9184.6034764218002</v>
+      </c>
+    </row>
+    <row r="451" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A451" s="3">
+        <v>386.3</v>
+      </c>
+      <c r="B451" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C451" s="4">
+        <v>47848</v>
+      </c>
+      <c r="D451" s="3">
+        <v>2030</v>
+      </c>
+      <c r="E451" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F451" t="s">
+        <v>30</v>
+      </c>
+      <c r="G451">
+        <v>8102.6110922999997</v>
+      </c>
+      <c r="H451">
+        <v>7830.3633595987194</v>
+      </c>
+      <c r="I451">
+        <v>9917.5959769751989</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:I451" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="583" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE08D481-A9EE-4CCA-B5BD-FAFA6290DE59}"/>
+  <xr:revisionPtr revIDLastSave="585" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89B4A75B-DA6B-4AEC-8F8F-3E22D4C16E34}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="90">
   <si>
     <t>Id</t>
   </si>
@@ -306,6 +306,9 @@
   </si>
   <si>
     <t>Conservador_4.2%↑</t>
+  </si>
+  <si>
+    <t>Proyeccion_CAGR_11.8%↑</t>
   </si>
 </sst>
 </file>
@@ -712,6 +715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I451"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -747,7 +751,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>109</v>
       </c>
@@ -776,7 +780,7 @@
         <v>96.466210501716631</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>109</v>
       </c>
@@ -805,7 +809,7 @@
         <v>98.817673270209056</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>109</v>
       </c>
@@ -834,7 +838,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>109</v>
       </c>
@@ -863,7 +867,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>109</v>
       </c>
@@ -892,7 +896,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>148</v>
       </c>
@@ -921,7 +925,7 @@
         <v>6.4632000000000014</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>148</v>
       </c>
@@ -950,7 +954,7 @@
         <v>6.6767605714285727</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>148</v>
       </c>
@@ -979,7 +983,7 @@
         <v>6.8921245714285728</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>148</v>
       </c>
@@ -1008,7 +1012,7 @@
         <v>7.1092920000000008</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>148</v>
       </c>
@@ -1037,7 +1041,7 @@
         <v>7.3282628571428594</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>148</v>
       </c>
@@ -1066,7 +1070,7 @@
         <v>7.5490371428571432</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>148</v>
       </c>
@@ -1095,7 +1099,7 @@
         <v>7.7716148571428576</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>148</v>
       </c>
@@ -1124,7 +1128,7 @@
         <v>7.9959960000000017</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>148</v>
       </c>
@@ -1153,7 +1157,7 @@
         <v>8.2221805714285736</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>148</v>
       </c>
@@ -1182,7 +1186,7 @@
         <v>8.4501685714285717</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>148</v>
       </c>
@@ -1211,7 +1215,7 @@
         <v>6.1899902761070864</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>148</v>
       </c>
@@ -1240,7 +1244,7 @@
         <v>6.3279819822962171</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>148</v>
       </c>
@@ -1269,7 +1273,7 @@
         <v>6.4686394813710644</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>148</v>
       </c>
@@ -1298,7 +1302,7 @@
         <v>6.6119865461157588</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>148</v>
       </c>
@@ -1327,7 +1331,7 @@
         <v>6.7580469493144291</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>148</v>
       </c>
@@ -1356,7 +1360,7 @@
         <v>6.906844463751205</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>148</v>
       </c>
@@ -1385,7 +1389,7 @@
         <v>7.0584028622102162</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>148</v>
       </c>
@@ -1414,7 +1418,7 @@
         <v>7.2127459174755941</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>148</v>
       </c>
@@ -1443,7 +1447,7 @@
         <v>7.3698974023314676</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>148</v>
       </c>
@@ -1472,7 +1476,7 @@
         <v>7.5298810895619628</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>148</v>
       </c>
@@ -1501,7 +1505,7 @@
         <v>6.4272000000000009</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>148</v>
       </c>
@@ -1530,7 +1534,7 @@
         <v>6.6531160800000002</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>148</v>
       </c>
@@ -1559,7 +1563,7 @@
         <v>6.8868026448000004</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>148</v>
       </c>
@@ -1588,7 +1592,7 @@
         <v>7.1285225990160006</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>148</v>
       </c>
@@ -1617,7 +1621,7 @@
         <v>7.3785476281046396</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>148</v>
       </c>
@@ -1646,7 +1650,7 @@
         <v>7.6371584885994839</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>148</v>
       </c>
@@ -1675,7 +1679,7 @@
         <v>7.9046453078587247</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>148</v>
       </c>
@@ -1704,7 +1708,7 @@
         <v>8.1813078936337824</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>148</v>
       </c>
@@ -1733,7 +1737,7 @@
         <v>8.4674560537782675</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>148</v>
       </c>
@@ -1762,7 +1766,7 @@
         <v>8.7634099264271512</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>202</v>
       </c>
@@ -1792,7 +1796,7 @@
         <v>86.460524321264955</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>202</v>
       </c>
@@ -1822,7 +1826,7 @@
         <v>87.89444169204053</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>202</v>
       </c>
@@ -1852,7 +1856,7 @@
         <v>89.352140077821005</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>202</v>
       </c>
@@ -1882,7 +1886,7 @@
         <v>90.834013878371721</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>202</v>
       </c>
@@ -1912,7 +1916,7 @@
         <v>92.340464034439464</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>193</v>
       </c>
@@ -1941,7 +1945,7 @@
         <v>97.708742857142852</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>193</v>
       </c>
@@ -1970,7 +1974,7 @@
         <v>98.622035714285715</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>193</v>
       </c>
@@ -1999,7 +2003,7 @@
         <v>98.785214285714289</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>193</v>
       </c>
@@ -2028,7 +2032,7 @@
         <v>98.948392857142849</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>193</v>
       </c>
@@ -2057,7 +2061,7 @@
         <v>99.111571428571423</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>193</v>
       </c>
@@ -2086,7 +2090,7 @@
         <v>99.274749999999997</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>193</v>
       </c>
@@ -2115,7 +2119,7 @@
         <v>99.437928571428571</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>193</v>
       </c>
@@ -2144,7 +2148,7 @@
         <v>99.601107142857131</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>193</v>
       </c>
@@ -2173,7 +2177,7 @@
         <v>99.764285714285705</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>193</v>
       </c>
@@ -2202,7 +2206,7 @@
         <v>99.927464285714279</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>200</v>
       </c>
@@ -2231,7 +2235,7 @@
         <v>90.92222000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>200</v>
       </c>
@@ -2260,7 +2264,7 @@
         <v>91.911683266000011</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>200</v>
       </c>
@@ -2289,7 +2293,7 @@
         <v>92.91184357532002</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>200</v>
       </c>
@@ -2318,7 +2322,7 @@
         <v>93.922815922499808</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>200</v>
       </c>
@@ -2347,7 +2351,7 @@
         <v>94.944716532265687</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>203</v>
       </c>
@@ -2376,7 +2380,7 @@
         <v>361906.34571078792</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>203</v>
       </c>
@@ -2405,7 +2409,7 @@
         <v>387019.50024189468</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>203</v>
       </c>
@@ -2434,7 +2438,7 @@
         <v>412231.55552550871</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>203</v>
       </c>
@@ -2463,7 +2467,7 @@
         <v>437542.51156162989</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>203</v>
       </c>
@@ -2492,7 +2496,7 @@
         <v>462952.36835025827</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>203</v>
       </c>
@@ -2521,7 +2525,7 @@
         <v>344656.92064585851</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>203</v>
       </c>
@@ -2550,7 +2554,7 @@
         <v>364402.73401411739</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>203</v>
       </c>
@@ -2579,7 +2583,7 @@
         <v>384225.81483198522</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>203</v>
       </c>
@@ -2608,7 +2612,7 @@
         <v>404126.16309946158</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>203</v>
       </c>
@@ -2637,7 +2641,7 @@
         <v>424103.77881654678</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>204</v>
       </c>
@@ -2666,7 +2670,7 @@
         <v>25370.876424564001</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>204</v>
       </c>
@@ -2695,7 +2699,7 @@
         <v>26262.662730887419</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>204</v>
       </c>
@@ -2724,7 +2728,7 @@
         <v>27185.12242680815</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>204</v>
       </c>
@@ -2753,7 +2757,7 @@
         <v>28139.293308026321</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>204</v>
       </c>
@@ -2782,7 +2786,7 @@
         <v>29126.24783193344</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>205</v>
       </c>
@@ -2811,7 +2815,7 @@
         <v>11094.4845707844</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>205</v>
       </c>
@@ -2840,7 +2844,7 @@
         <v>11484.455703447469</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>205</v>
       </c>
@@ -2869,7 +2873,7 @@
         <v>11887.84006795662</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>205</v>
       </c>
@@ -2898,7 +2902,7 @@
         <v>12305.09148420322</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>205</v>
       </c>
@@ -2927,7 +2931,7 @@
         <v>12736.67892936345</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>207</v>
       </c>
@@ -2956,7 +2960,7 @@
         <v>129998.22584691409</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>207</v>
       </c>
@@ -2985,7 +2989,7 @@
         <v>144049.70191530959</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>207</v>
       </c>
@@ -3014,7 +3018,7 @@
         <v>159610.88372067409</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>207</v>
       </c>
@@ -3043,7 +3047,7 @@
         <v>176842.83189646521</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>207</v>
       </c>
@@ -3072,7 +3076,7 @@
         <v>195923.64518797089</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>228</v>
       </c>
@@ -3101,7 +3105,7 @@
         <v>892.42950861146085</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>228</v>
       </c>
@@ -3130,7 +3134,7 @@
         <v>1019.5881230993029</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>228</v>
       </c>
@@ -3159,7 +3163,7 @@
         <v>1147.967597954756</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>228</v>
       </c>
@@ -3188,7 +3192,7 @@
         <v>1277.5679331778181</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>228</v>
       </c>
@@ -3217,7 +3221,7 @@
         <v>1408.3891287684901</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>228</v>
       </c>
@@ -3246,7 +3250,7 @@
         <v>796.70494376731313</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>228</v>
       </c>
@@ -3275,7 +3279,7 @@
         <v>917.28571818365663</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>228</v>
       </c>
@@ -3304,7 +3308,7 @@
         <v>1055.298221956233</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>228</v>
       </c>
@@ -3333,7 +3337,7 @@
         <v>1210.984111882826</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>228</v>
       </c>
@@ -3362,7 +3366,7 @@
         <v>1384.585044761219</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>244</v>
       </c>
@@ -3391,7 +3395,7 @@
         <v>19.733333333333331</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>244</v>
       </c>
@@ -3420,7 +3424,7 @@
         <v>19.196888888888889</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>244</v>
       </c>
@@ -3449,7 +3453,7 @@
         <v>18.66577777777778</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>244</v>
       </c>
@@ -3478,7 +3482,7 @@
         <v>18.14</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>244</v>
       </c>
@@ -3507,7 +3511,7 @@
         <v>17.61955555555555</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>245</v>
       </c>
@@ -3536,7 +3540,7 @@
         <v>89.198827494123194</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>245</v>
       </c>
@@ -3565,7 +3569,7 @@
         <v>89.380807536188684</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>245</v>
       </c>
@@ -3594,7 +3598,7 @@
         <v>89.563090584620838</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>245</v>
       </c>
@@ -3623,7 +3627,7 @@
         <v>89.745677098501574</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>245</v>
       </c>
@@ -3652,7 +3656,7 @@
         <v>89.928567537571354</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>245</v>
       </c>
@@ -3681,7 +3685,7 @@
         <v>90.11176236223001</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>245</v>
       </c>
@@ -3710,7 +3714,7 @@
         <v>90.295262033537696</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>245</v>
       </c>
@@ -3739,7 +3743,7 @@
         <v>90.479067013215754</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>245</v>
       </c>
@@ -3768,7 +3772,7 @@
         <v>90.663177763647781</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>245</v>
       </c>
@@ -3797,7 +3801,7 @@
         <v>90.847594747880279</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>245</v>
       </c>
@@ -3826,7 +3830,7 @@
         <v>89.125900000000001</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>245</v>
       </c>
@@ -3855,7 +3859,7 @@
         <v>89.909943499999997</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>245</v>
       </c>
@@ -3884,7 +3888,7 @@
         <v>90.695220000000006</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>245</v>
       </c>
@@ -3913,7 +3917,7 @@
         <v>91.481729500000014</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>245</v>
       </c>
@@ -3942,7 +3946,7 @@
         <v>92.269472000000007</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>245</v>
       </c>
@@ -3971,7 +3975,7 @@
         <v>93.058447500000014</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>245</v>
       </c>
@@ -4000,7 +4004,7 @@
         <v>93.84865600000002</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>245</v>
       </c>
@@ -4029,7 +4033,7 @@
         <v>94.640097500000024</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>245</v>
       </c>
@@ -4058,7 +4062,7 @@
         <v>95.432772000000014</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>245</v>
       </c>
@@ -4087,7 +4091,7 @@
         <v>96.226679500000017</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>276</v>
       </c>
@@ -4116,7 +4120,7 @@
         <v>64.626946951668998</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>276</v>
       </c>
@@ -4145,7 +4149,7 @@
         <v>61.797659797529029</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>276</v>
       </c>
@@ -4174,7 +4178,7 @@
         <v>58.996085245839843</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>276</v>
       </c>
@@ -4203,7 +4207,7 @@
         <v>56.222223296601427</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>276</v>
       </c>
@@ -4232,7 +4236,7 @@
         <v>53.476073949813816</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>276</v>
       </c>
@@ -4261,7 +4265,7 @@
         <v>50.757637205477003</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>276</v>
       </c>
@@ -4290,7 +4294,7 @@
         <v>48.06691306359096</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>276</v>
       </c>
@@ -4319,7 +4323,7 @@
         <v>45.403901524155707</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>276</v>
       </c>
@@ -4348,7 +4352,7 @@
         <v>42.768602587171237</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>276</v>
       </c>
@@ -4377,7 +4381,7 @@
         <v>40.16101625263758</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>276</v>
       </c>
@@ -4406,7 +4410,7 @@
         <v>67.115704744213033</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>276</v>
       </c>
@@ -4435,7 +4439,7 @@
         <v>64.444136422217625</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>276</v>
       </c>
@@ -4464,7 +4468,7 @@
         <v>61.650155398709487</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>276</v>
       </c>
@@ -4493,7 +4497,7 @@
         <v>58.736271336376369</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>276</v>
       </c>
@@ -4522,7 +4526,7 @@
         <v>55.704993897906057</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>276</v>
       </c>
@@ -4551,7 +4555,7 @@
         <v>52.558832745986322</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>276</v>
       </c>
@@ -4580,7 +4584,7 @@
         <v>49.300297543304907</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>276</v>
       </c>
@@ -4609,7 +4613,7 @@
         <v>45.931897952549583</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>276</v>
       </c>
@@ -4638,7 +4642,7 @@
         <v>42.456143636408108</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>276</v>
       </c>
@@ -4667,7 +4671,7 @@
         <v>38.875544257568272</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>277</v>
       </c>
@@ -4696,7 +4700,7 @@
         <v>65.423590000000004</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>277</v>
       </c>
@@ -4725,7 +4729,7 @@
         <v>63.790038399999993</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>277</v>
       </c>
@@ -4754,7 +4758,7 @@
         <v>62.159408199999987</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>277</v>
       </c>
@@ -4783,7 +4787,7 @@
         <v>60.531699400000001</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>277</v>
       </c>
@@ -4812,7 +4816,7 @@
         <v>58.906911999999991</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>277</v>
       </c>
@@ -4841,7 +4845,7 @@
         <v>57.285045999999987</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>277</v>
       </c>
@@ -4870,7 +4874,7 @@
         <v>55.666101400000002</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>277</v>
       </c>
@@ -4899,7 +4903,7 @@
         <v>54.050078199999987</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>277</v>
       </c>
@@ -4928,7 +4932,7 @@
         <v>52.436976399999992</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>277</v>
       </c>
@@ -4957,7 +4961,7 @@
         <v>50.826795999999987</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>277</v>
       </c>
@@ -4986,7 +4990,7 @@
         <v>66.485942686567171</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>277</v>
       </c>
@@ -5015,7 +5019,7 @@
         <v>64.739279082089539</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>277</v>
       </c>
@@ -5044,7 +5048,7 @@
         <v>62.796252588059687</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>277</v>
       </c>
@@ -5073,7 +5077,7 @@
         <v>60.657419525373108</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>277</v>
       </c>
@@ -5102,7 +5106,7 @@
         <v>58.323336214925362</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>277</v>
       </c>
@@ -5131,7 +5135,7 @@
         <v>55.794558977611921</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>277</v>
       </c>
@@ -5160,7 +5164,7 @@
         <v>53.071644134328317</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>277</v>
       </c>
@@ -5189,7 +5193,7 @@
         <v>50.155148005970112</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>277</v>
       </c>
@@ -5218,7 +5222,7 @@
         <v>47.045626913432791</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>277</v>
       </c>
@@ -5247,7 +5251,7 @@
         <v>43.743637177611888</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>325</v>
       </c>
@@ -5276,7 +5280,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>325</v>
       </c>
@@ -5305,7 +5309,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>325</v>
       </c>
@@ -5334,7 +5338,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>325</v>
       </c>
@@ -5363,7 +5367,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>325</v>
       </c>
@@ -5392,7 +5396,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>332</v>
       </c>
@@ -5421,7 +5425,7 @@
         <v>0.96258217913204036</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>332</v>
       </c>
@@ -5450,7 +5454,7 @@
         <v>0.76924555493998137</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>332</v>
       </c>
@@ -5479,7 +5483,7 @@
         <v>0.61474029325946433</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>332</v>
       </c>
@@ -5508,7 +5512,7 @@
         <v>0.49126731405355478</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>332</v>
       </c>
@@ -5537,7 +5541,7 @@
         <v>0.39259391479963057</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>332</v>
       </c>
@@ -5566,7 +5570,7 @@
         <v>0.98985714285714266</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>332</v>
       </c>
@@ -5595,7 +5599,7 @@
         <v>0.86821714285714269</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>332</v>
       </c>
@@ -5624,7 +5628,7 @@
         <v>0.74683428571428556</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>332</v>
       </c>
@@ -5653,7 +5657,7 @@
         <v>0.62570857142857128</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>332</v>
       </c>
@@ -5682,7 +5686,7 @@
         <v>0.50483999999999984</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>334</v>
       </c>
@@ -5711,7 +5715,7 @@
         <v>93.538188902985453</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>334</v>
       </c>
@@ -5740,7 +5744,7 @@
         <v>94.56709042548556</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>334</v>
       </c>
@@ -5769,7 +5773,7 @@
         <v>95.597946658009604</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>334</v>
       </c>
@@ -5798,7 +5802,7 @@
         <v>96.630757600557587</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>334</v>
       </c>
@@ -5827,7 +5831,7 @@
         <v>97.665523253129464</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>334</v>
       </c>
@@ -5856,7 +5860,7 @@
         <v>92.782347962234354</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>334</v>
       </c>
@@ -5885,7 +5889,7 @@
         <v>93.741605516469846</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>334</v>
       </c>
@@ -5914,7 +5918,7 @@
         <v>94.819698424443658</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>334</v>
       </c>
@@ -5943,7 +5947,7 @@
         <v>96.016995031257053</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>334</v>
       </c>
@@ -5972,7 +5976,7 @@
         <v>97.333863682011312</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>361</v>
       </c>
@@ -6001,7 +6005,7 @@
         <v>4.83446</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>361</v>
       </c>
@@ -6030,7 +6034,7 @@
         <v>4.8645499999999995</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>361</v>
       </c>
@@ -6059,7 +6063,7 @@
         <v>4.8846099999999995</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>361</v>
       </c>
@@ -6088,7 +6092,7 @@
         <v>4.9247299999999994</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>361</v>
       </c>
@@ -6117,7 +6121,7 @@
         <v>4.9748799999999997</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
         <v>364</v>
       </c>
@@ -6146,7 +6150,7 @@
         <v>115494.72</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>364</v>
       </c>
@@ -6175,7 +6179,7 @@
         <v>126091.36056</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3">
         <v>364</v>
       </c>
@@ -6204,7 +6208,7 @@
         <v>137652.38203200011</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
         <v>364</v>
       </c>
@@ -6233,7 +6237,7 @@
         <v>150264.6941928</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
         <v>364</v>
       </c>
@@ -6262,7 +6266,7 @@
         <v>164022.94496544011</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>367</v>
       </c>
@@ -6291,7 +6295,7 @@
         <v>5.5479450746268659</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
         <v>367</v>
       </c>
@@ -6320,7 +6324,7 @@
         <v>5.6197363811343282</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>367</v>
       </c>
@@ -6349,7 +6353,7 @@
         <v>5.6924087192644777</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
         <v>367</v>
       </c>
@@ -6378,7 +6382,7 @@
         <v>5.7659725305191172</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>367</v>
       </c>
@@ -6407,7 +6411,7 @@
         <v>5.8404383771269233</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
         <v>369</v>
       </c>
@@ -6436,7 +6440,7 @@
         <v>88.128</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
         <v>369</v>
       </c>
@@ -6465,7 +6469,7 @@
         <v>90.340012799999997</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
         <v>369</v>
       </c>
@@ -6494,7 +6498,7 @@
         <v>92.605254912000021</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
         <v>369</v>
       </c>
@@ -6523,7 +6527,7 @@
         <v>94.924970703359989</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3">
         <v>369</v>
       </c>
@@ -6552,7 +6556,7 @@
         <v>97.3004330244096</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
         <v>377</v>
       </c>
@@ -6581,7 +6585,7 @@
         <v>16487.724732840001</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="3">
         <v>377</v>
       </c>
@@ -6610,7 +6614,7 @@
         <v>19055.687859979829</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3">
         <v>377</v>
       </c>
@@ -6639,7 +6643,7 @@
         <v>22023.066118772709</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
         <v>377</v>
       </c>
@@ -6668,7 +6672,7 @@
         <v>25451.9048783539</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3">
         <v>377</v>
       </c>
@@ -6697,7 +6701,7 @@
         <v>29413.876278137071</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>423</v>
       </c>
@@ -6726,7 +6730,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>423</v>
       </c>
@@ -6755,7 +6759,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>423</v>
       </c>
@@ -6784,7 +6788,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>423</v>
       </c>
@@ -6813,7 +6817,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>423</v>
       </c>
@@ -6842,7 +6846,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>424</v>
       </c>
@@ -6871,7 +6875,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>424</v>
       </c>
@@ -6900,7 +6904,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>424</v>
       </c>
@@ -6929,7 +6933,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>424</v>
       </c>
@@ -6958,7 +6962,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>424</v>
       </c>
@@ -6987,7 +6991,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>460</v>
       </c>
@@ -7016,7 +7020,7 @@
         <v>95.125032000000004</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>460</v>
       </c>
@@ -7045,7 +7049,7 @@
         <v>96.160232469600004</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>460</v>
       </c>
@@ -7074,7 +7078,7 @@
         <v>97.206624445392023</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>460</v>
       </c>
@@ -7103,7 +7107,7 @@
         <v>98.545849202319999</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>460</v>
       </c>
@@ -7132,7 +7136,7 @@
         <v>98.831307694343209</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>77</v>
       </c>
@@ -7161,7 +7165,7 @@
         <v>98.67895</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>77</v>
       </c>
@@ -7190,7 +7194,7 @@
         <v>98.965739499999998</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>77</v>
       </c>
@@ -7219,7 +7223,7 @@
         <v>99.255396895000004</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>77</v>
       </c>
@@ -7248,7 +7252,7 @@
         <v>99.547950863950007</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>77</v>
       </c>
@@ -7277,7 +7281,7 @@
         <v>99.843430372589509</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>98</v>
       </c>
@@ -7306,7 +7310,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>98</v>
       </c>
@@ -7335,7 +7339,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>98</v>
       </c>
@@ -7364,7 +7368,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>98</v>
       </c>
@@ -7393,7 +7397,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>98</v>
       </c>
@@ -7422,7 +7426,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="3">
         <v>386.1</v>
       </c>
@@ -7451,7 +7455,7 @@
         <v>6025.5908288085884</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="3">
         <v>386.1</v>
       </c>
@@ -7480,7 +7484,7 @@
         <v>7132.9729466473937</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="3">
         <v>386.1</v>
       </c>
@@ -7509,7 +7513,7 @@
         <v>8387.9290364164917</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="3">
         <v>386.1</v>
       </c>
@@ -7538,7 +7542,7 @@
         <v>9792.4915984875806</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3">
         <v>386.1</v>
       </c>
@@ -7584,16 +7588,16 @@
         <v>12</v>
       </c>
       <c r="F237" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="G237">
-        <v>6702.3186977606192</v>
+        <v>8322.3104068060129</v>
       </c>
       <c r="H237">
-        <v>5361.8549582084961</v>
+        <v>6657.8483254448111</v>
       </c>
       <c r="I237">
-        <v>7390.2362842041885</v>
+        <v>9176.5019107995558</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.3">
@@ -7613,16 +7617,16 @@
         <v>14</v>
       </c>
       <c r="F238" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="G238">
-        <v>6668.9435105391967</v>
+        <v>9300.7150739219178</v>
       </c>
       <c r="H238">
-        <v>5295.1411473681228</v>
+        <v>7384.7677686940033</v>
       </c>
       <c r="I238">
-        <v>7373.9702695911656</v>
+        <v>10283.967217993961</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.3">
@@ -7642,16 +7646,16 @@
         <v>16</v>
       </c>
       <c r="F239" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="G239">
-        <v>6619.4758826049401</v>
+        <v>10394.14497391682</v>
       </c>
       <c r="H239">
-        <v>5216.1469954926933</v>
+        <v>8190.5862394464584</v>
       </c>
       <c r="I239">
-        <v>7339.6554686125028</v>
+        <v>11524.99750015523</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.3">
@@ -7671,16 +7675,16 @@
         <v>18</v>
       </c>
       <c r="F240" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="G240">
-        <v>6553.9158139578494</v>
+        <v>11616.122941098</v>
       </c>
       <c r="H240">
-        <v>5125.1621665150387</v>
+        <v>9083.8081399386374</v>
       </c>
       <c r="I240">
-        <v>7287.1432275540574</v>
+        <v>12915.691019463869</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.3">
@@ -7700,19 +7704,19 @@
         <v>20</v>
       </c>
       <c r="F241" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="G241">
-        <v>6472.2633045979237</v>
+        <v>12981.76160918564</v>
       </c>
       <c r="H241">
-        <v>5022.476324367989</v>
+        <v>10073.847008728049</v>
       </c>
       <c r="I241">
-        <v>7216.2848927016921</v>
-      </c>
-    </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+        <v>14474.085149544269</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="3">
         <v>386.3</v>
       </c>
@@ -7741,7 +7745,7 @@
         <v>6775.7920969396118</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="3">
         <v>386.3</v>
       </c>
@@ -7770,7 +7774,7 @@
         <v>7687.612830857006</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="3">
         <v>386.3</v>
       </c>
@@ -7799,7 +7803,7 @@
         <v>8759.3798750710612</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="3">
         <v>386.3</v>
       </c>
@@ -7828,7 +7832,7 @@
         <v>9993.3389311351038</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="3">
         <v>386.3</v>
       </c>
@@ -7857,7 +7861,7 @@
         <v>11391.73570060247</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>379</v>
       </c>
@@ -7886,7 +7890,7 @@
         <v>13317.175813442071</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>274</v>
       </c>
@@ -7915,7 +7919,7 @@
         <v>46054.901058930787</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>379</v>
       </c>
@@ -7944,7 +7948,7 @@
         <v>13418.021660158851</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>274</v>
       </c>
@@ -7973,7 +7977,7 @@
         <v>46403.657098334967</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>379</v>
       </c>
@@ -8002,7 +8006,7 @@
         <v>13536.316299144</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>274</v>
       </c>
@@ -8031,7 +8035,7 @@
         <v>46812.756442714293</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>379</v>
       </c>
@@ -8060,7 +8064,7 @@
         <v>13665.23975007113</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>274</v>
       </c>
@@ -8089,7 +8093,7 @@
         <v>47258.613496777638</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>379</v>
       </c>
@@ -8118,7 +8122,7 @@
         <v>13801.316029168571</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>274</v>
       </c>
@@ -8147,7 +8151,7 @@
         <v>47729.20723662855</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>379</v>
       </c>
@@ -8176,7 +8180,7 @@
         <v>13942.80055708834</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>274</v>
       </c>
@@ -8205,7 +8209,7 @@
         <v>48218.50436884314</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>379</v>
       </c>
@@ -8234,7 +8238,7 @@
         <v>14088.84540208515</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>274</v>
       </c>
@@ -8263,7 +8267,7 @@
         <v>48723.572483938951</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>379</v>
       </c>
@@ -8292,7 +8296,7 @@
         <v>14239.06717106818</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>274</v>
       </c>
@@ -8321,7 +8325,7 @@
         <v>49243.085690367268</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>379</v>
       </c>
@@ -8350,7 +8354,7 @@
         <v>14393.32333139659</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>274</v>
       </c>
@@ -8379,7 +8383,7 @@
         <v>49776.551066298169</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>379</v>
       </c>
@@ -8408,7 +8412,7 @@
         <v>14551.59642655029</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>274</v>
       </c>
@@ -8437,7 +8441,7 @@
         <v>50323.908241701443</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>14</v>
       </c>
@@ -8466,7 +8470,7 @@
         <v>59371.884262853768</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>14</v>
       </c>
@@ -8495,7 +8499,7 @@
         <v>59821.484690416968</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>14</v>
       </c>
@@ -8524,7 +8528,7 @@
         <v>60348.876962857597</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>14</v>
       </c>
@@ -8553,7 +8557,7 @@
         <v>60923.655603197178</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>14</v>
       </c>
@@ -8582,7 +8586,7 @@
         <v>61530.323654041553</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>14</v>
       </c>
@@ -8611,7 +8615,7 @@
         <v>62161.103267851133</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>14</v>
       </c>
@@ -8640,7 +8644,7 @@
         <v>62812.214115662013</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>14</v>
       </c>
@@ -8669,7 +8673,7 @@
         <v>63481.946918379748</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>14</v>
       </c>
@@ -8698,7 +8702,7 @@
         <v>64169.666223595093</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>14</v>
       </c>
@@ -8727,7 +8731,7 @@
         <v>64875.294205010192</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>14</v>
       </c>
@@ -8756,7 +8760,7 @@
         <v>60802.946712188583</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>14</v>
       </c>
@@ -8785,7 +8789,7 @@
         <v>61412.55539447139</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>14</v>
       </c>
@@ -8814,7 +8818,7 @@
         <v>62023.951131092377</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>14</v>
       </c>
@@ -8843,7 +8847,7 @@
         <v>62637.133922051551</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>14</v>
       </c>
@@ -8872,7 +8876,7 @@
         <v>63252.103767348883</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>14</v>
       </c>
@@ -8901,7 +8905,7 @@
         <v>63868.860666984387</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>14</v>
       </c>
@@ -8930,7 +8934,7 @@
         <v>64487.404620958077</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>14</v>
       </c>
@@ -8959,7 +8963,7 @@
         <v>65107.735629269962</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>14</v>
       </c>
@@ -8988,7 +8992,7 @@
         <v>65729.853691919998</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>14</v>
       </c>
@@ -9017,7 +9021,7 @@
         <v>66353.758808908198</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>379</v>
       </c>
@@ -9046,7 +9050,7 @@
         <v>13638.16461941349</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>274</v>
       </c>
@@ -9075,7 +9079,7 @@
         <v>47164.979344832544</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>379</v>
       </c>
@@ -9104,7 +9108,7 @@
         <v>13774.90048522195</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>274</v>
       </c>
@@ -9133,7 +9137,7 @@
         <v>47637.854138950643</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>379</v>
       </c>
@@ -9162,7 +9166,7 @@
         <v>13912.037189189839</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>274</v>
       </c>
@@ -9191,7 +9195,7 @@
         <v>48112.115155044899</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>379</v>
       </c>
@@ -9220,7 +9224,7 @@
         <v>14049.574731317151</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>274</v>
       </c>
@@ -9249,7 +9253,7 @@
         <v>48587.762393115328</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>379</v>
       </c>
@@ -9278,7 +9282,7 @@
         <v>14187.513111603899</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>274</v>
       </c>
@@ -9307,7 +9311,7 @@
         <v>49064.795853161922</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>379</v>
       </c>
@@ -9336,7 +9340,7 @@
         <v>14325.85233005006</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>274</v>
       </c>
@@ -9365,7 +9369,7 @@
         <v>49543.215535184667</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>379</v>
       </c>
@@ -9394,7 +9398,7 @@
         <v>14464.59238665566</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>274</v>
       </c>
@@ -9423,7 +9427,7 @@
         <v>50023.021439183598</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>379</v>
       </c>
@@ -9452,7 +9456,7 @@
         <v>14603.73328142068</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>274</v>
       </c>
@@ -9481,7 +9485,7 @@
         <v>50504.213565158687</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>379</v>
       </c>
@@ -9510,7 +9514,7 @@
         <v>14743.275014345139</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>274</v>
       </c>
@@ -9539,7 +9543,7 @@
         <v>50986.791913109962</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>379</v>
       </c>
@@ -9568,7 +9572,7 @@
         <v>14883.217585429011</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>274</v>
       </c>
@@ -9597,7 +9601,7 @@
         <v>51470.756483037367</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>14.1</v>
       </c>
@@ -9626,7 +9630,7 @@
         <v>9487.176818882821</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>14.2</v>
       </c>
@@ -9655,7 +9659,7 @@
         <v>51315.769893305762</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>14.1</v>
       </c>
@@ -9684,7 +9688,7 @@
         <v>9582.2949944297943</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>14.2</v>
       </c>
@@ -9713,7 +9717,7 @@
         <v>51830.260400041603</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>14.1</v>
       </c>
@@ -9742,7 +9746,7 @@
         <v>9677.6920067997835</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>14.2</v>
       </c>
@@ -9771,7 +9775,7 @@
         <v>52346.259124292606</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>14.1</v>
       </c>
@@ -9800,7 +9804,7 @@
         <v>9773.3678559927885</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>14.2</v>
       </c>
@@ -9829,7 +9833,7 @@
         <v>52863.766066058772</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>14.1</v>
       </c>
@@ -9858,7 +9862,7 @@
         <v>9869.3225420088074</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>14.2</v>
       </c>
@@ -9887,7 +9891,7 @@
         <v>53382.781225340077</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>14.1</v>
       </c>
@@ -9916,7 +9920,7 @@
         <v>9965.556064847844</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>14.2</v>
       </c>
@@ -9945,7 +9949,7 @@
         <v>53903.304602136559</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>14.1</v>
       </c>
@@ -9974,7 +9978,7 @@
         <v>10062.0684245099</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>14.2</v>
       </c>
@@ -10003,7 +10007,7 @@
         <v>54425.336196448203</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>14.1</v>
       </c>
@@ -10032,7 +10036,7 @@
         <v>10158.859620994959</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>14.2</v>
       </c>
@@ -10061,7 +10065,7 @@
         <v>54948.876008275001</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>14.1</v>
       </c>
@@ -10090,7 +10094,7 @@
         <v>10255.92965430305</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>14.2</v>
       </c>
@@ -10119,7 +10123,7 @@
         <v>55473.924037616962</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>14.1</v>
       </c>
@@ -10148,7 +10152,7 @@
         <v>10353.278524434139</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>14.2</v>
       </c>
@@ -10177,7 +10181,7 @@
         <v>56000.480284474063</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>14.1</v>
       </c>
@@ -10206,7 +10210,7 @@
         <v>9263.8859550375455</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>14.2</v>
       </c>
@@ -10235,7 +10239,7 @@
         <v>50107.998307816233</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>14.1</v>
       </c>
@@ -10264,7 +10268,7 @@
         <v>9334.0377977488515</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>14.2</v>
       </c>
@@ -10293,7 +10297,7 @@
         <v>50487.446892668122</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>14.1</v>
       </c>
@@ -10322,7 +10326,7 @@
         <v>9416.3276210569329</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>14.2</v>
       </c>
@@ -10351,7 +10355,7 @@
         <v>50932.549341800674</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>14.1</v>
       </c>
@@ -10380,7 +10384,7 @@
         <v>9506.0112118610195</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>14.2</v>
       </c>
@@ -10409,7 +10413,7 @@
         <v>51417.644391336173</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>14.1</v>
       </c>
@@ -10438,7 +10442,7 @@
         <v>9600.6705561847666</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>14.2</v>
       </c>
@@ -10467,7 +10471,7 @@
         <v>51929.65309785679</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>14.1</v>
       </c>
@@ -10496,7 +10500,7 @@
         <v>9699.0920645745646</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>14.2</v>
       </c>
@@ -10525,7 +10529,7 @@
         <v>52462.011203276568</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>14.1</v>
       </c>
@@ -10554,7 +10558,7 @@
         <v>9800.6858865173472</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>14.2</v>
       </c>
@@ -10583,7 +10587,7 @@
         <v>53011.528229144671</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>14.1</v>
       </c>
@@ -10612,7 +10616,7 @@
         <v>9905.1853205803909</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>14.2</v>
       </c>
@@ -10641,7 +10645,7 @@
         <v>53576.761597799363</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>14.1</v>
       </c>
@@ -10670,7 +10674,7 @@
         <v>10012.491216151881</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>14.2</v>
       </c>
@@ -10699,7 +10703,7 @@
         <v>54157.175007443213</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>14.1</v>
       </c>
@@ -10728,7 +10732,7 @@
         <v>10122.59142987548</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>14.2</v>
       </c>
@@ -10757,7 +10761,7 @@
         <v>54752.70277513472</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>14.3</v>
       </c>
@@ -10786,7 +10790,7 @@
         <v>56552.414086080753</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>14.4</v>
       </c>
@@ -10815,7 +10819,7 @@
         <v>4250.5326261078344</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>14.3</v>
       </c>
@@ -10844,7 +10848,7 @@
         <v>57119.407044400919</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>14.4</v>
       </c>
@@ -10873,7 +10877,7 @@
         <v>4293.1483500704726</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>14.3</v>
       </c>
@@ -10902,7 +10906,7 @@
         <v>57688.062130009188</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>14.4</v>
       </c>
@@ -10931,7 +10935,7 @@
         <v>4335.8890010831956</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>14.3</v>
       </c>
@@ -10960,7 +10964,7 @@
         <v>58258.379342905551</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>14.4</v>
       </c>
@@ -10989,7 +10993,7 @@
         <v>4378.7545791459988</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>14.3</v>
       </c>
@@ -11018,7 +11022,7 @@
         <v>58830.358683090002</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>14.4</v>
       </c>
@@ -11047,7 +11051,7 @@
         <v>4421.7450842588833</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>14.3</v>
       </c>
@@ -11076,7 +11080,7 @@
         <v>59404.000150562548</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>14.4</v>
       </c>
@@ -11105,7 +11109,7 @@
         <v>4464.8605164218507</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>14.3</v>
       </c>
@@ -11134,7 +11138,7 @@
         <v>59979.303745323188</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>14.4</v>
       </c>
@@ -11163,7 +11167,7 @@
         <v>4508.1008756348992</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>14.3</v>
       </c>
@@ -11192,7 +11196,7 @@
         <v>60556.269467371923</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>14.4</v>
       </c>
@@ -11221,7 +11225,7 @@
         <v>4551.4661618980308</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>14.3</v>
       </c>
@@ -11250,7 +11254,7 @@
         <v>61134.897316708753</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>14.4</v>
       </c>
@@ -11279,7 +11283,7 @@
         <v>4594.9563752112444</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>14.3</v>
       </c>
@@ -11308,7 +11312,7 @@
         <v>61715.187293333664</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>14.4</v>
       </c>
@@ -11337,7 +11341,7 @@
         <v>4638.5715155745374</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>14.3</v>
       </c>
@@ -11366,7 +11370,7 @@
         <v>55221.39247291936</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>14.4</v>
       </c>
@@ -11395,7 +11399,7 @@
         <v>4150.4917899344118</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>14.3</v>
       </c>
@@ -11424,7 +11428,7 @@
         <v>55639.562823662178</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>14.4</v>
       </c>
@@ -11453,7 +11457,7 @@
         <v>4181.9218667547893</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>14.3</v>
       </c>
@@ -11482,7 +11486,7 @@
         <v>56130.086849052597</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>14.4</v>
       </c>
@@ -11511,7 +11515,7 @@
         <v>4218.7901138050047</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>14.3</v>
       </c>
@@ -11540,7 +11544,7 @@
         <v>56664.68461830516</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>14.4</v>
       </c>
@@ -11569,7 +11573,7 @@
         <v>4258.9709848920229</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>14.3</v>
       </c>
@@ -11598,7 +11602,7 @@
         <v>57228.942514991417</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>14.4</v>
       </c>
@@ -11627,7 +11631,7 @@
         <v>4301.3811390501323</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>14.3</v>
       </c>
@@ -11656,7 +11660,7 @@
         <v>57815.626415133163</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>14.4</v>
       </c>
@@ -11685,7 +11689,7 @@
         <v>4345.4768527179676</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>14.3</v>
       </c>
@@ -11714,7 +11718,7 @@
         <v>58421.220260043949</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>14.4</v>
       </c>
@@ -11743,7 +11747,7 @@
         <v>4390.9938556180596</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>14.3</v>
       </c>
@@ -11772,7 +11776,7 @@
         <v>59044.134260669722</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>14.4</v>
       </c>
@@ -11801,7 +11805,7 @@
         <v>4437.8126577100284</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>14.3</v>
       </c>
@@ -11830,7 +11834,7 @@
         <v>59683.777386974543</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>14.4</v>
       </c>
@@ -11859,7 +11863,7 @@
         <v>4485.8888366205483</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>14.3</v>
       </c>
@@ -11888,7 +11892,7 @@
         <v>60340.077253239288</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>14.4</v>
       </c>
@@ -11917,7 +11921,7 @@
         <v>4535.2169517708999</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>194</v>
       </c>
@@ -11946,7 +11950,7 @@
         <v>93.008258302465308</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>194</v>
       </c>
@@ -11975,7 +11979,7 @@
         <v>93.941532956484238</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>194</v>
       </c>
@@ -12004,7 +12008,7 @@
         <v>94.87480761050314</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>194</v>
       </c>
@@ -12033,7 +12037,7 @@
         <v>95.808082264522056</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>194</v>
       </c>
@@ -12062,7 +12066,7 @@
         <v>96.741356918540987</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>194</v>
       </c>
@@ -12091,7 +12095,7 @@
         <v>93.424405824177825</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>194</v>
       </c>
@@ -12120,7 +12124,7 @@
         <v>94.15447253075159</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>194</v>
       </c>
@@ -12149,7 +12153,7 @@
         <v>94.890244356788997</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>194</v>
       </c>
@@ -12178,7 +12182,7 @@
         <v>95.631765885049148</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>194</v>
       </c>
@@ -12207,7 +12211,7 @@
         <v>96.379082046683891</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>323</v>
       </c>
@@ -12236,7 +12240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>323</v>
       </c>
@@ -12265,7 +12269,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>323</v>
       </c>
@@ -12294,7 +12298,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>323</v>
       </c>
@@ -12323,7 +12327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>323</v>
       </c>
@@ -12352,7 +12356,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>376</v>
       </c>
@@ -12381,7 +12385,7 @@
         <v>36033.446856183858</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>376</v>
       </c>
@@ -12410,7 +12414,7 @@
         <v>38872.61512155136</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>376</v>
       </c>
@@ -12439,7 +12443,7 @@
         <v>41717.57657108127</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>376</v>
       </c>
@@ -12468,7 +12472,7 @@
         <v>44568.331204773582</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>376</v>
       </c>
@@ -12497,7 +12501,7 @@
         <v>47424.879022628324</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>376</v>
       </c>
@@ -12526,7 +12530,7 @@
         <v>34556.673694232348</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>376</v>
       </c>
@@ -12555,7 +12559,7 @@
         <v>37856.02412414951</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>376</v>
       </c>
@@ -12584,7 +12588,7 @@
         <v>41689.182193960667</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>376</v>
       </c>
@@ -12613,7 +12617,7 @@
         <v>46057.780844716202</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>376</v>
       </c>
@@ -12642,7 +12646,7 @@
         <v>50963.453017466447</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>466</v>
       </c>
@@ -12671,7 +12675,7 @@
         <v>60.742268041340189</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>466</v>
       </c>
@@ -12700,7 +12704,7 @@
         <v>62.622639562581618</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>466</v>
       </c>
@@ -12729,7 +12733,7 @@
         <v>64.561276595843793</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>466</v>
       </c>
@@ -12758,7 +12762,7 @@
         <v>66.559986395217919</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>466</v>
       </c>
@@ -12787,7 +12791,7 @@
         <v>68.620632331635861</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>466</v>
       </c>
@@ -12816,7 +12820,7 @@
         <v>57.97444574550294</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>466</v>
       </c>
@@ -12845,7 +12849,7 @@
         <v>59.769135016331823</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>466</v>
       </c>
@@ -12874,7 +12878,7 @@
         <v>61.619434834385345</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>466</v>
       </c>
@@ -12903,7 +12907,7 @@
         <v>63.527070103221561</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>466</v>
       </c>
@@ -12932,7 +12936,7 @@
         <v>65.493819286181989</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>96</v>
       </c>
@@ -12961,7 +12965,7 @@
         <v>990.23735660954856</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>96</v>
       </c>
@@ -12990,7 +12994,7 @@
         <v>1074.101030045967</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>96</v>
       </c>
@@ -13019,7 +13023,7 @@
         <v>1165.04537214991</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>96</v>
       </c>
@@ -13048,7 +13052,7 @@
         <v>1263.666562398188</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>96</v>
       </c>
@@ -13077,7 +13081,7 @@
         <v>1370.6108527044289</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>385</v>
       </c>
@@ -13106,7 +13110,7 @@
         <v>22394.58706838209</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>385</v>
       </c>
@@ -13135,7 +13139,7 @@
         <v>24510.31089960839</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>385</v>
       </c>
@@ -13164,7 +13168,7 @@
         <v>26645.972550694249</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>385</v>
       </c>
@@ -13193,7 +13197,7 @@
         <v>28801.572021639651</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>385</v>
       </c>
@@ -13222,7 +13226,7 @@
         <v>30977.109312444602</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>385</v>
       </c>
@@ -13251,7 +13255,7 @@
         <v>20844.165363419648</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>385</v>
       </c>
@@ -13280,7 +13284,7 @@
         <v>22863.33165174054</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>385</v>
       </c>
@@ -13309,7 +13313,7 @@
         <v>25170.11368192935</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>385</v>
       </c>
@@ -13338,7 +13342,7 @@
         <v>27768.499991978719</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>385</v>
       </c>
@@ -13367,7 +13371,7 @@
         <v>30662.479119881289</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="3">
         <v>386.1</v>
       </c>
@@ -13396,7 +13400,7 @@
         <v>6063.9485940000004</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="3">
         <v>386.1</v>
       </c>
@@ -13425,7 +13429,7 @@
         <v>7617.8354212124996</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="3">
         <v>386.1</v>
       </c>
@@ -13454,7 +13458,7 @@
         <v>9569.6688749062487</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="3">
         <v>386.1</v>
       </c>
@@ -13483,7 +13487,7 @@
         <v>11023.172622260399</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="3">
         <v>386.1</v>
       </c>
@@ -13657,7 +13661,7 @@
         <v>7937.7742038094157</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="3">
         <v>386.3</v>
       </c>
@@ -13686,7 +13690,7 @@
         <v>7026.0817481999993</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="3">
         <v>386.3</v>
       </c>
@@ -13715,7 +13719,7 @@
         <v>7738.846362034199</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" s="3">
         <v>386.3</v>
       </c>
@@ -13744,7 +13748,7 @@
         <v>8458.3536047747984</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" s="3">
         <v>386.3</v>
       </c>
@@ -13773,7 +13777,7 @@
         <v>9184.6034764218002</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" s="3">
         <v>386.3</v>
       </c>
@@ -13803,7 +13807,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I451" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}"/>
+  <autoFilter ref="A1:I451" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="386,2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="585" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89B4A75B-DA6B-4AEC-8F8F-3E22D4C16E34}"/>
+  <xr:revisionPtr revIDLastSave="587" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F74FB05-C0CE-405C-BC60-D476B8FA0794}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -715,7 +715,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I451"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -751,7 +750,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>109</v>
       </c>
@@ -780,7 +779,7 @@
         <v>96.466210501716631</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>109</v>
       </c>
@@ -809,7 +808,7 @@
         <v>98.817673270209056</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>109</v>
       </c>
@@ -838,7 +837,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>109</v>
       </c>
@@ -867,7 +866,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>109</v>
       </c>
@@ -896,7 +895,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>148</v>
       </c>
@@ -925,7 +924,7 @@
         <v>6.4632000000000014</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>148</v>
       </c>
@@ -954,7 +953,7 @@
         <v>6.6767605714285727</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>148</v>
       </c>
@@ -983,7 +982,7 @@
         <v>6.8921245714285728</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>148</v>
       </c>
@@ -1012,7 +1011,7 @@
         <v>7.1092920000000008</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>148</v>
       </c>
@@ -1041,7 +1040,7 @@
         <v>7.3282628571428594</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>148</v>
       </c>
@@ -1070,7 +1069,7 @@
         <v>7.5490371428571432</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>148</v>
       </c>
@@ -1099,7 +1098,7 @@
         <v>7.7716148571428576</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>148</v>
       </c>
@@ -1128,7 +1127,7 @@
         <v>7.9959960000000017</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>148</v>
       </c>
@@ -1157,7 +1156,7 @@
         <v>8.2221805714285736</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>148</v>
       </c>
@@ -1186,7 +1185,7 @@
         <v>8.4501685714285717</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>148</v>
       </c>
@@ -1215,7 +1214,7 @@
         <v>6.1899902761070864</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>148</v>
       </c>
@@ -1244,7 +1243,7 @@
         <v>6.3279819822962171</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>148</v>
       </c>
@@ -1273,7 +1272,7 @@
         <v>6.4686394813710644</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>148</v>
       </c>
@@ -1302,7 +1301,7 @@
         <v>6.6119865461157588</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>148</v>
       </c>
@@ -1331,7 +1330,7 @@
         <v>6.7580469493144291</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>148</v>
       </c>
@@ -1360,7 +1359,7 @@
         <v>6.906844463751205</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>148</v>
       </c>
@@ -1389,7 +1388,7 @@
         <v>7.0584028622102162</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>148</v>
       </c>
@@ -1418,7 +1417,7 @@
         <v>7.2127459174755941</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>148</v>
       </c>
@@ -1447,7 +1446,7 @@
         <v>7.3698974023314676</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>148</v>
       </c>
@@ -1476,7 +1475,7 @@
         <v>7.5298810895619628</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>148</v>
       </c>
@@ -1505,7 +1504,7 @@
         <v>6.4272000000000009</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>148</v>
       </c>
@@ -1534,7 +1533,7 @@
         <v>6.6531160800000002</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>148</v>
       </c>
@@ -1563,7 +1562,7 @@
         <v>6.8868026448000004</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>148</v>
       </c>
@@ -1592,7 +1591,7 @@
         <v>7.1285225990160006</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>148</v>
       </c>
@@ -1621,7 +1620,7 @@
         <v>7.3785476281046396</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>148</v>
       </c>
@@ -1650,7 +1649,7 @@
         <v>7.6371584885994839</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>148</v>
       </c>
@@ -1679,7 +1678,7 @@
         <v>7.9046453078587247</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>148</v>
       </c>
@@ -1708,7 +1707,7 @@
         <v>8.1813078936337824</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>148</v>
       </c>
@@ -1737,7 +1736,7 @@
         <v>8.4674560537782675</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>148</v>
       </c>
@@ -1766,7 +1765,7 @@
         <v>8.7634099264271512</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>202</v>
       </c>
@@ -1796,7 +1795,7 @@
         <v>86.460524321264955</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>202</v>
       </c>
@@ -1826,7 +1825,7 @@
         <v>87.89444169204053</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>202</v>
       </c>
@@ -1856,7 +1855,7 @@
         <v>89.352140077821005</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>202</v>
       </c>
@@ -1886,7 +1885,7 @@
         <v>90.834013878371721</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>202</v>
       </c>
@@ -1916,7 +1915,7 @@
         <v>92.340464034439464</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>193</v>
       </c>
@@ -1945,7 +1944,7 @@
         <v>97.708742857142852</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>193</v>
       </c>
@@ -1974,7 +1973,7 @@
         <v>98.622035714285715</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>193</v>
       </c>
@@ -2003,7 +2002,7 @@
         <v>98.785214285714289</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>193</v>
       </c>
@@ -2032,7 +2031,7 @@
         <v>98.948392857142849</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>193</v>
       </c>
@@ -2061,7 +2060,7 @@
         <v>99.111571428571423</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>193</v>
       </c>
@@ -2090,7 +2089,7 @@
         <v>99.274749999999997</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>193</v>
       </c>
@@ -2119,7 +2118,7 @@
         <v>99.437928571428571</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>193</v>
       </c>
@@ -2148,7 +2147,7 @@
         <v>99.601107142857131</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>193</v>
       </c>
@@ -2177,7 +2176,7 @@
         <v>99.764285714285705</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>193</v>
       </c>
@@ -2206,7 +2205,7 @@
         <v>99.927464285714279</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>200</v>
       </c>
@@ -2235,7 +2234,7 @@
         <v>90.92222000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>200</v>
       </c>
@@ -2264,7 +2263,7 @@
         <v>91.911683266000011</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>200</v>
       </c>
@@ -2293,7 +2292,7 @@
         <v>92.91184357532002</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>200</v>
       </c>
@@ -2322,7 +2321,7 @@
         <v>93.922815922499808</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>200</v>
       </c>
@@ -2351,7 +2350,7 @@
         <v>94.944716532265687</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>203</v>
       </c>
@@ -2380,7 +2379,7 @@
         <v>361906.34571078792</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>203</v>
       </c>
@@ -2409,7 +2408,7 @@
         <v>387019.50024189468</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>203</v>
       </c>
@@ -2438,7 +2437,7 @@
         <v>412231.55552550871</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>203</v>
       </c>
@@ -2467,7 +2466,7 @@
         <v>437542.51156162989</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>203</v>
       </c>
@@ -2496,7 +2495,7 @@
         <v>462952.36835025827</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>203</v>
       </c>
@@ -2525,7 +2524,7 @@
         <v>344656.92064585851</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>203</v>
       </c>
@@ -2554,7 +2553,7 @@
         <v>364402.73401411739</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>203</v>
       </c>
@@ -2583,7 +2582,7 @@
         <v>384225.81483198522</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>203</v>
       </c>
@@ -2612,7 +2611,7 @@
         <v>404126.16309946158</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>203</v>
       </c>
@@ -2641,7 +2640,7 @@
         <v>424103.77881654678</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>204</v>
       </c>
@@ -2670,7 +2669,7 @@
         <v>25370.876424564001</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>204</v>
       </c>
@@ -2699,7 +2698,7 @@
         <v>26262.662730887419</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>204</v>
       </c>
@@ -2728,7 +2727,7 @@
         <v>27185.12242680815</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>204</v>
       </c>
@@ -2757,7 +2756,7 @@
         <v>28139.293308026321</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>204</v>
       </c>
@@ -2786,7 +2785,7 @@
         <v>29126.24783193344</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>205</v>
       </c>
@@ -2815,7 +2814,7 @@
         <v>11094.4845707844</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>205</v>
       </c>
@@ -2844,7 +2843,7 @@
         <v>11484.455703447469</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>205</v>
       </c>
@@ -2873,7 +2872,7 @@
         <v>11887.84006795662</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>205</v>
       </c>
@@ -2902,7 +2901,7 @@
         <v>12305.09148420322</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>205</v>
       </c>
@@ -2931,7 +2930,7 @@
         <v>12736.67892936345</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>207</v>
       </c>
@@ -2960,7 +2959,7 @@
         <v>129998.22584691409</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>207</v>
       </c>
@@ -2989,7 +2988,7 @@
         <v>144049.70191530959</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>207</v>
       </c>
@@ -3018,7 +3017,7 @@
         <v>159610.88372067409</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>207</v>
       </c>
@@ -3047,7 +3046,7 @@
         <v>176842.83189646521</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>207</v>
       </c>
@@ -3076,7 +3075,7 @@
         <v>195923.64518797089</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>228</v>
       </c>
@@ -3105,7 +3104,7 @@
         <v>892.42950861146085</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>228</v>
       </c>
@@ -3134,7 +3133,7 @@
         <v>1019.5881230993029</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>228</v>
       </c>
@@ -3163,7 +3162,7 @@
         <v>1147.967597954756</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>228</v>
       </c>
@@ -3192,7 +3191,7 @@
         <v>1277.5679331778181</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>228</v>
       </c>
@@ -3221,7 +3220,7 @@
         <v>1408.3891287684901</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>228</v>
       </c>
@@ -3250,7 +3249,7 @@
         <v>796.70494376731313</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>228</v>
       </c>
@@ -3279,7 +3278,7 @@
         <v>917.28571818365663</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>228</v>
       </c>
@@ -3308,7 +3307,7 @@
         <v>1055.298221956233</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>228</v>
       </c>
@@ -3337,7 +3336,7 @@
         <v>1210.984111882826</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>228</v>
       </c>
@@ -3366,7 +3365,7 @@
         <v>1384.585044761219</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>244</v>
       </c>
@@ -3395,7 +3394,7 @@
         <v>19.733333333333331</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>244</v>
       </c>
@@ -3424,7 +3423,7 @@
         <v>19.196888888888889</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>244</v>
       </c>
@@ -3453,7 +3452,7 @@
         <v>18.66577777777778</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>244</v>
       </c>
@@ -3482,7 +3481,7 @@
         <v>18.14</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>244</v>
       </c>
@@ -3511,7 +3510,7 @@
         <v>17.61955555555555</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>245</v>
       </c>
@@ -3540,7 +3539,7 @@
         <v>89.198827494123194</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>245</v>
       </c>
@@ -3569,7 +3568,7 @@
         <v>89.380807536188684</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>245</v>
       </c>
@@ -3598,7 +3597,7 @@
         <v>89.563090584620838</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>245</v>
       </c>
@@ -3627,7 +3626,7 @@
         <v>89.745677098501574</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>245</v>
       </c>
@@ -3656,7 +3655,7 @@
         <v>89.928567537571354</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>245</v>
       </c>
@@ -3685,7 +3684,7 @@
         <v>90.11176236223001</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>245</v>
       </c>
@@ -3714,7 +3713,7 @@
         <v>90.295262033537696</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>245</v>
       </c>
@@ -3743,7 +3742,7 @@
         <v>90.479067013215754</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>245</v>
       </c>
@@ -3772,7 +3771,7 @@
         <v>90.663177763647781</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>245</v>
       </c>
@@ -3801,7 +3800,7 @@
         <v>90.847594747880279</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>245</v>
       </c>
@@ -3830,7 +3829,7 @@
         <v>89.125900000000001</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>245</v>
       </c>
@@ -3859,7 +3858,7 @@
         <v>89.909943499999997</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>245</v>
       </c>
@@ -3888,7 +3887,7 @@
         <v>90.695220000000006</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>245</v>
       </c>
@@ -3917,7 +3916,7 @@
         <v>91.481729500000014</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>245</v>
       </c>
@@ -3946,7 +3945,7 @@
         <v>92.269472000000007</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>245</v>
       </c>
@@ -3975,7 +3974,7 @@
         <v>93.058447500000014</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>245</v>
       </c>
@@ -4004,7 +4003,7 @@
         <v>93.84865600000002</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>245</v>
       </c>
@@ -4033,7 +4032,7 @@
         <v>94.640097500000024</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>245</v>
       </c>
@@ -4062,7 +4061,7 @@
         <v>95.432772000000014</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>245</v>
       </c>
@@ -4091,7 +4090,7 @@
         <v>96.226679500000017</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>276</v>
       </c>
@@ -4120,7 +4119,7 @@
         <v>64.626946951668998</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>276</v>
       </c>
@@ -4149,7 +4148,7 @@
         <v>61.797659797529029</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>276</v>
       </c>
@@ -4178,7 +4177,7 @@
         <v>58.996085245839843</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>276</v>
       </c>
@@ -4207,7 +4206,7 @@
         <v>56.222223296601427</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>276</v>
       </c>
@@ -4236,7 +4235,7 @@
         <v>53.476073949813816</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>276</v>
       </c>
@@ -4265,7 +4264,7 @@
         <v>50.757637205477003</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>276</v>
       </c>
@@ -4294,7 +4293,7 @@
         <v>48.06691306359096</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>276</v>
       </c>
@@ -4323,7 +4322,7 @@
         <v>45.403901524155707</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>276</v>
       </c>
@@ -4352,7 +4351,7 @@
         <v>42.768602587171237</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>276</v>
       </c>
@@ -4381,7 +4380,7 @@
         <v>40.16101625263758</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>276</v>
       </c>
@@ -4410,7 +4409,7 @@
         <v>67.115704744213033</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>276</v>
       </c>
@@ -4439,7 +4438,7 @@
         <v>64.444136422217625</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>276</v>
       </c>
@@ -4468,7 +4467,7 @@
         <v>61.650155398709487</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>276</v>
       </c>
@@ -4497,7 +4496,7 @@
         <v>58.736271336376369</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>276</v>
       </c>
@@ -4526,7 +4525,7 @@
         <v>55.704993897906057</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>276</v>
       </c>
@@ -4555,7 +4554,7 @@
         <v>52.558832745986322</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>276</v>
       </c>
@@ -4584,7 +4583,7 @@
         <v>49.300297543304907</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>276</v>
       </c>
@@ -4613,7 +4612,7 @@
         <v>45.931897952549583</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>276</v>
       </c>
@@ -4642,7 +4641,7 @@
         <v>42.456143636408108</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>276</v>
       </c>
@@ -4671,7 +4670,7 @@
         <v>38.875544257568272</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>277</v>
       </c>
@@ -4700,7 +4699,7 @@
         <v>65.423590000000004</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>277</v>
       </c>
@@ -4729,7 +4728,7 @@
         <v>63.790038399999993</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>277</v>
       </c>
@@ -4758,7 +4757,7 @@
         <v>62.159408199999987</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>277</v>
       </c>
@@ -4787,7 +4786,7 @@
         <v>60.531699400000001</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>277</v>
       </c>
@@ -4816,7 +4815,7 @@
         <v>58.906911999999991</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>277</v>
       </c>
@@ -4845,7 +4844,7 @@
         <v>57.285045999999987</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>277</v>
       </c>
@@ -4874,7 +4873,7 @@
         <v>55.666101400000002</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>277</v>
       </c>
@@ -4903,7 +4902,7 @@
         <v>54.050078199999987</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>277</v>
       </c>
@@ -4932,7 +4931,7 @@
         <v>52.436976399999992</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>277</v>
       </c>
@@ -4961,7 +4960,7 @@
         <v>50.826795999999987</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>277</v>
       </c>
@@ -4990,7 +4989,7 @@
         <v>66.485942686567171</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>277</v>
       </c>
@@ -5019,7 +5018,7 @@
         <v>64.739279082089539</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>277</v>
       </c>
@@ -5048,7 +5047,7 @@
         <v>62.796252588059687</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>277</v>
       </c>
@@ -5077,7 +5076,7 @@
         <v>60.657419525373108</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>277</v>
       </c>
@@ -5106,7 +5105,7 @@
         <v>58.323336214925362</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>277</v>
       </c>
@@ -5135,7 +5134,7 @@
         <v>55.794558977611921</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>277</v>
       </c>
@@ -5164,7 +5163,7 @@
         <v>53.071644134328317</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>277</v>
       </c>
@@ -5193,7 +5192,7 @@
         <v>50.155148005970112</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>277</v>
       </c>
@@ -5222,7 +5221,7 @@
         <v>47.045626913432791</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>277</v>
       </c>
@@ -5251,7 +5250,7 @@
         <v>43.743637177611888</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>325</v>
       </c>
@@ -5280,7 +5279,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>325</v>
       </c>
@@ -5309,7 +5308,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>325</v>
       </c>
@@ -5338,7 +5337,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>325</v>
       </c>
@@ -5367,7 +5366,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>325</v>
       </c>
@@ -5396,7 +5395,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>332</v>
       </c>
@@ -5425,7 +5424,7 @@
         <v>0.96258217913204036</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>332</v>
       </c>
@@ -5454,7 +5453,7 @@
         <v>0.76924555493998137</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>332</v>
       </c>
@@ -5483,7 +5482,7 @@
         <v>0.61474029325946433</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>332</v>
       </c>
@@ -5512,7 +5511,7 @@
         <v>0.49126731405355478</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>332</v>
       </c>
@@ -5541,7 +5540,7 @@
         <v>0.39259391479963057</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>332</v>
       </c>
@@ -5570,7 +5569,7 @@
         <v>0.98985714285714266</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>332</v>
       </c>
@@ -5599,7 +5598,7 @@
         <v>0.86821714285714269</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>332</v>
       </c>
@@ -5628,7 +5627,7 @@
         <v>0.74683428571428556</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>332</v>
       </c>
@@ -5657,7 +5656,7 @@
         <v>0.62570857142857128</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>332</v>
       </c>
@@ -5686,7 +5685,7 @@
         <v>0.50483999999999984</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>334</v>
       </c>
@@ -5715,7 +5714,7 @@
         <v>93.538188902985453</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>334</v>
       </c>
@@ -5744,7 +5743,7 @@
         <v>94.56709042548556</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>334</v>
       </c>
@@ -5773,7 +5772,7 @@
         <v>95.597946658009604</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>334</v>
       </c>
@@ -5802,7 +5801,7 @@
         <v>96.630757600557587</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>334</v>
       </c>
@@ -5831,7 +5830,7 @@
         <v>97.665523253129464</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>334</v>
       </c>
@@ -5860,7 +5859,7 @@
         <v>92.782347962234354</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>334</v>
       </c>
@@ -5889,7 +5888,7 @@
         <v>93.741605516469846</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>334</v>
       </c>
@@ -5918,7 +5917,7 @@
         <v>94.819698424443658</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>334</v>
       </c>
@@ -5947,7 +5946,7 @@
         <v>96.016995031257053</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>334</v>
       </c>
@@ -5976,7 +5975,7 @@
         <v>97.333863682011312</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>361</v>
       </c>
@@ -6005,7 +6004,7 @@
         <v>4.83446</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>361</v>
       </c>
@@ -6034,7 +6033,7 @@
         <v>4.8645499999999995</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>361</v>
       </c>
@@ -6063,7 +6062,7 @@
         <v>4.8846099999999995</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>361</v>
       </c>
@@ -6092,7 +6091,7 @@
         <v>4.9247299999999994</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>361</v>
       </c>
@@ -6121,7 +6120,7 @@
         <v>4.9748799999999997</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
         <v>364</v>
       </c>
@@ -6150,7 +6149,7 @@
         <v>115494.72</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>364</v>
       </c>
@@ -6179,7 +6178,7 @@
         <v>126091.36056</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="3">
         <v>364</v>
       </c>
@@ -6208,7 +6207,7 @@
         <v>137652.38203200011</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
         <v>364</v>
       </c>
@@ -6237,7 +6236,7 @@
         <v>150264.6941928</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
         <v>364</v>
       </c>
@@ -6266,7 +6265,7 @@
         <v>164022.94496544011</v>
       </c>
     </row>
-    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>367</v>
       </c>
@@ -6295,7 +6294,7 @@
         <v>5.5479450746268659</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
         <v>367</v>
       </c>
@@ -6324,7 +6323,7 @@
         <v>5.6197363811343282</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>367</v>
       </c>
@@ -6353,7 +6352,7 @@
         <v>5.6924087192644777</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
         <v>367</v>
       </c>
@@ -6382,7 +6381,7 @@
         <v>5.7659725305191172</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>367</v>
       </c>
@@ -6411,7 +6410,7 @@
         <v>5.8404383771269233</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
         <v>369</v>
       </c>
@@ -6440,7 +6439,7 @@
         <v>88.128</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
         <v>369</v>
       </c>
@@ -6469,7 +6468,7 @@
         <v>90.340012799999997</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
         <v>369</v>
       </c>
@@ -6498,7 +6497,7 @@
         <v>92.605254912000021</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
         <v>369</v>
       </c>
@@ -6527,7 +6526,7 @@
         <v>94.924970703359989</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="3">
         <v>369</v>
       </c>
@@ -6556,7 +6555,7 @@
         <v>97.3004330244096</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
         <v>377</v>
       </c>
@@ -6585,7 +6584,7 @@
         <v>16487.724732840001</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="3">
         <v>377</v>
       </c>
@@ -6614,7 +6613,7 @@
         <v>19055.687859979829</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="3">
         <v>377</v>
       </c>
@@ -6643,7 +6642,7 @@
         <v>22023.066118772709</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
         <v>377</v>
       </c>
@@ -6672,7 +6671,7 @@
         <v>25451.9048783539</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="3">
         <v>377</v>
       </c>
@@ -6701,7 +6700,7 @@
         <v>29413.876278137071</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>423</v>
       </c>
@@ -6730,7 +6729,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>423</v>
       </c>
@@ -6759,7 +6758,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>423</v>
       </c>
@@ -6788,7 +6787,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>423</v>
       </c>
@@ -6817,7 +6816,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>423</v>
       </c>
@@ -6846,7 +6845,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>424</v>
       </c>
@@ -6875,7 +6874,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>424</v>
       </c>
@@ -6904,7 +6903,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>424</v>
       </c>
@@ -6933,7 +6932,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>424</v>
       </c>
@@ -6962,7 +6961,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>424</v>
       </c>
@@ -6991,7 +6990,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>460</v>
       </c>
@@ -7020,7 +7019,7 @@
         <v>95.125032000000004</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>460</v>
       </c>
@@ -7049,7 +7048,7 @@
         <v>96.160232469600004</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>460</v>
       </c>
@@ -7078,7 +7077,7 @@
         <v>97.206624445392023</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>460</v>
       </c>
@@ -7107,7 +7106,7 @@
         <v>98.545849202319999</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>460</v>
       </c>
@@ -7136,7 +7135,7 @@
         <v>98.831307694343209</v>
       </c>
     </row>
-    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>77</v>
       </c>
@@ -7165,7 +7164,7 @@
         <v>98.67895</v>
       </c>
     </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>77</v>
       </c>
@@ -7194,7 +7193,7 @@
         <v>98.965739499999998</v>
       </c>
     </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>77</v>
       </c>
@@ -7223,7 +7222,7 @@
         <v>99.255396895000004</v>
       </c>
     </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>77</v>
       </c>
@@ -7252,7 +7251,7 @@
         <v>99.547950863950007</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>77</v>
       </c>
@@ -7281,7 +7280,7 @@
         <v>99.843430372589509</v>
       </c>
     </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>98</v>
       </c>
@@ -7310,7 +7309,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>98</v>
       </c>
@@ -7339,7 +7338,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>98</v>
       </c>
@@ -7368,7 +7367,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>98</v>
       </c>
@@ -7397,7 +7396,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>98</v>
       </c>
@@ -7426,7 +7425,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" s="3">
         <v>386.1</v>
       </c>
@@ -7455,7 +7454,7 @@
         <v>6025.5908288085884</v>
       </c>
     </row>
-    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="3">
         <v>386.1</v>
       </c>
@@ -7484,7 +7483,7 @@
         <v>7132.9729466473937</v>
       </c>
     </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" s="3">
         <v>386.1</v>
       </c>
@@ -7513,7 +7512,7 @@
         <v>8387.9290364164917</v>
       </c>
     </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" s="3">
         <v>386.1</v>
       </c>
@@ -7542,7 +7541,7 @@
         <v>9792.4915984875806</v>
       </c>
     </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" s="3">
         <v>386.1</v>
       </c>
@@ -7716,7 +7715,7 @@
         <v>14474.085149544269</v>
       </c>
     </row>
-    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" s="3">
         <v>386.3</v>
       </c>
@@ -7745,7 +7744,7 @@
         <v>6775.7920969396118</v>
       </c>
     </row>
-    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" s="3">
         <v>386.3</v>
       </c>
@@ -7774,7 +7773,7 @@
         <v>7687.612830857006</v>
       </c>
     </row>
-    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" s="3">
         <v>386.3</v>
       </c>
@@ -7803,7 +7802,7 @@
         <v>8759.3798750710612</v>
       </c>
     </row>
-    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" s="3">
         <v>386.3</v>
       </c>
@@ -7832,7 +7831,7 @@
         <v>9993.3389311351038</v>
       </c>
     </row>
-    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" s="3">
         <v>386.3</v>
       </c>
@@ -7861,7 +7860,7 @@
         <v>11391.73570060247</v>
       </c>
     </row>
-    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>379</v>
       </c>
@@ -7890,7 +7889,7 @@
         <v>13317.175813442071</v>
       </c>
     </row>
-    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>274</v>
       </c>
@@ -7919,7 +7918,7 @@
         <v>46054.901058930787</v>
       </c>
     </row>
-    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>379</v>
       </c>
@@ -7948,7 +7947,7 @@
         <v>13418.021660158851</v>
       </c>
     </row>
-    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>274</v>
       </c>
@@ -7977,7 +7976,7 @@
         <v>46403.657098334967</v>
       </c>
     </row>
-    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>379</v>
       </c>
@@ -8006,7 +8005,7 @@
         <v>13536.316299144</v>
       </c>
     </row>
-    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>274</v>
       </c>
@@ -8035,7 +8034,7 @@
         <v>46812.756442714293</v>
       </c>
     </row>
-    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>379</v>
       </c>
@@ -8064,7 +8063,7 @@
         <v>13665.23975007113</v>
       </c>
     </row>
-    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>274</v>
       </c>
@@ -8093,7 +8092,7 @@
         <v>47258.613496777638</v>
       </c>
     </row>
-    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>379</v>
       </c>
@@ -8122,7 +8121,7 @@
         <v>13801.316029168571</v>
       </c>
     </row>
-    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>274</v>
       </c>
@@ -8151,7 +8150,7 @@
         <v>47729.20723662855</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>379</v>
       </c>
@@ -8180,7 +8179,7 @@
         <v>13942.80055708834</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>274</v>
       </c>
@@ -8209,7 +8208,7 @@
         <v>48218.50436884314</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>379</v>
       </c>
@@ -8238,7 +8237,7 @@
         <v>14088.84540208515</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>274</v>
       </c>
@@ -8267,7 +8266,7 @@
         <v>48723.572483938951</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>379</v>
       </c>
@@ -8296,7 +8295,7 @@
         <v>14239.06717106818</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>274</v>
       </c>
@@ -8325,7 +8324,7 @@
         <v>49243.085690367268</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>379</v>
       </c>
@@ -8354,7 +8353,7 @@
         <v>14393.32333139659</v>
       </c>
     </row>
-    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>274</v>
       </c>
@@ -8383,7 +8382,7 @@
         <v>49776.551066298169</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>379</v>
       </c>
@@ -8412,7 +8411,7 @@
         <v>14551.59642655029</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>274</v>
       </c>
@@ -8441,7 +8440,7 @@
         <v>50323.908241701443</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>14</v>
       </c>
@@ -8470,7 +8469,7 @@
         <v>59371.884262853768</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>14</v>
       </c>
@@ -8499,7 +8498,7 @@
         <v>59821.484690416968</v>
       </c>
     </row>
-    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>14</v>
       </c>
@@ -8528,7 +8527,7 @@
         <v>60348.876962857597</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>14</v>
       </c>
@@ -8557,7 +8556,7 @@
         <v>60923.655603197178</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>14</v>
       </c>
@@ -8586,7 +8585,7 @@
         <v>61530.323654041553</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>14</v>
       </c>
@@ -8615,7 +8614,7 @@
         <v>62161.103267851133</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>14</v>
       </c>
@@ -8644,7 +8643,7 @@
         <v>62812.214115662013</v>
       </c>
     </row>
-    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>14</v>
       </c>
@@ -8673,7 +8672,7 @@
         <v>63481.946918379748</v>
       </c>
     </row>
-    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>14</v>
       </c>
@@ -8702,7 +8701,7 @@
         <v>64169.666223595093</v>
       </c>
     </row>
-    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>14</v>
       </c>
@@ -8731,7 +8730,7 @@
         <v>64875.294205010192</v>
       </c>
     </row>
-    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>14</v>
       </c>
@@ -8760,7 +8759,7 @@
         <v>60802.946712188583</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>14</v>
       </c>
@@ -8789,7 +8788,7 @@
         <v>61412.55539447139</v>
       </c>
     </row>
-    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>14</v>
       </c>
@@ -8818,7 +8817,7 @@
         <v>62023.951131092377</v>
       </c>
     </row>
-    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>14</v>
       </c>
@@ -8847,7 +8846,7 @@
         <v>62637.133922051551</v>
       </c>
     </row>
-    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>14</v>
       </c>
@@ -8876,7 +8875,7 @@
         <v>63252.103767348883</v>
       </c>
     </row>
-    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>14</v>
       </c>
@@ -8905,7 +8904,7 @@
         <v>63868.860666984387</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>14</v>
       </c>
@@ -8934,7 +8933,7 @@
         <v>64487.404620958077</v>
       </c>
     </row>
-    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>14</v>
       </c>
@@ -8963,7 +8962,7 @@
         <v>65107.735629269962</v>
       </c>
     </row>
-    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>14</v>
       </c>
@@ -8992,7 +8991,7 @@
         <v>65729.853691919998</v>
       </c>
     </row>
-    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>14</v>
       </c>
@@ -9021,7 +9020,7 @@
         <v>66353.758808908198</v>
       </c>
     </row>
-    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>379</v>
       </c>
@@ -9050,7 +9049,7 @@
         <v>13638.16461941349</v>
       </c>
     </row>
-    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>274</v>
       </c>
@@ -9079,7 +9078,7 @@
         <v>47164.979344832544</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>379</v>
       </c>
@@ -9108,7 +9107,7 @@
         <v>13774.90048522195</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>274</v>
       </c>
@@ -9137,7 +9136,7 @@
         <v>47637.854138950643</v>
       </c>
     </row>
-    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>379</v>
       </c>
@@ -9166,7 +9165,7 @@
         <v>13912.037189189839</v>
       </c>
     </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>274</v>
       </c>
@@ -9195,7 +9194,7 @@
         <v>48112.115155044899</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>379</v>
       </c>
@@ -9224,7 +9223,7 @@
         <v>14049.574731317151</v>
       </c>
     </row>
-    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>274</v>
       </c>
@@ -9253,7 +9252,7 @@
         <v>48587.762393115328</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>379</v>
       </c>
@@ -9282,7 +9281,7 @@
         <v>14187.513111603899</v>
       </c>
     </row>
-    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>274</v>
       </c>
@@ -9311,7 +9310,7 @@
         <v>49064.795853161922</v>
       </c>
     </row>
-    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>379</v>
       </c>
@@ -9340,7 +9339,7 @@
         <v>14325.85233005006</v>
       </c>
     </row>
-    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>274</v>
       </c>
@@ -9369,7 +9368,7 @@
         <v>49543.215535184667</v>
       </c>
     </row>
-    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>379</v>
       </c>
@@ -9398,7 +9397,7 @@
         <v>14464.59238665566</v>
       </c>
     </row>
-    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>274</v>
       </c>
@@ -9427,7 +9426,7 @@
         <v>50023.021439183598</v>
       </c>
     </row>
-    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>379</v>
       </c>
@@ -9456,7 +9455,7 @@
         <v>14603.73328142068</v>
       </c>
     </row>
-    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>274</v>
       </c>
@@ -9485,7 +9484,7 @@
         <v>50504.213565158687</v>
       </c>
     </row>
-    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>379</v>
       </c>
@@ -9514,7 +9513,7 @@
         <v>14743.275014345139</v>
       </c>
     </row>
-    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>274</v>
       </c>
@@ -9543,7 +9542,7 @@
         <v>50986.791913109962</v>
       </c>
     </row>
-    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>379</v>
       </c>
@@ -9572,7 +9571,7 @@
         <v>14883.217585429011</v>
       </c>
     </row>
-    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>274</v>
       </c>
@@ -9601,7 +9600,7 @@
         <v>51470.756483037367</v>
       </c>
     </row>
-    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>14.1</v>
       </c>
@@ -9630,7 +9629,7 @@
         <v>9487.176818882821</v>
       </c>
     </row>
-    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>14.2</v>
       </c>
@@ -9659,7 +9658,7 @@
         <v>51315.769893305762</v>
       </c>
     </row>
-    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>14.1</v>
       </c>
@@ -9688,7 +9687,7 @@
         <v>9582.2949944297943</v>
       </c>
     </row>
-    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>14.2</v>
       </c>
@@ -9717,7 +9716,7 @@
         <v>51830.260400041603</v>
       </c>
     </row>
-    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>14.1</v>
       </c>
@@ -9746,7 +9745,7 @@
         <v>9677.6920067997835</v>
       </c>
     </row>
-    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>14.2</v>
       </c>
@@ -9775,7 +9774,7 @@
         <v>52346.259124292606</v>
       </c>
     </row>
-    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>14.1</v>
       </c>
@@ -9804,7 +9803,7 @@
         <v>9773.3678559927885</v>
       </c>
     </row>
-    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>14.2</v>
       </c>
@@ -9833,7 +9832,7 @@
         <v>52863.766066058772</v>
       </c>
     </row>
-    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>14.1</v>
       </c>
@@ -9862,7 +9861,7 @@
         <v>9869.3225420088074</v>
       </c>
     </row>
-    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>14.2</v>
       </c>
@@ -9891,7 +9890,7 @@
         <v>53382.781225340077</v>
       </c>
     </row>
-    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>14.1</v>
       </c>
@@ -9920,7 +9919,7 @@
         <v>9965.556064847844</v>
       </c>
     </row>
-    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>14.2</v>
       </c>
@@ -9949,7 +9948,7 @@
         <v>53903.304602136559</v>
       </c>
     </row>
-    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>14.1</v>
       </c>
@@ -9978,7 +9977,7 @@
         <v>10062.0684245099</v>
       </c>
     </row>
-    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>14.2</v>
       </c>
@@ -10007,7 +10006,7 @@
         <v>54425.336196448203</v>
       </c>
     </row>
-    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>14.1</v>
       </c>
@@ -10036,7 +10035,7 @@
         <v>10158.859620994959</v>
       </c>
     </row>
-    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>14.2</v>
       </c>
@@ -10065,7 +10064,7 @@
         <v>54948.876008275001</v>
       </c>
     </row>
-    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>14.1</v>
       </c>
@@ -10094,7 +10093,7 @@
         <v>10255.92965430305</v>
       </c>
     </row>
-    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>14.2</v>
       </c>
@@ -10123,7 +10122,7 @@
         <v>55473.924037616962</v>
       </c>
     </row>
-    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>14.1</v>
       </c>
@@ -10152,7 +10151,7 @@
         <v>10353.278524434139</v>
       </c>
     </row>
-    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>14.2</v>
       </c>
@@ -10181,7 +10180,7 @@
         <v>56000.480284474063</v>
       </c>
     </row>
-    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>14.1</v>
       </c>
@@ -10210,7 +10209,7 @@
         <v>9263.8859550375455</v>
       </c>
     </row>
-    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>14.2</v>
       </c>
@@ -10239,7 +10238,7 @@
         <v>50107.998307816233</v>
       </c>
     </row>
-    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>14.1</v>
       </c>
@@ -10268,7 +10267,7 @@
         <v>9334.0377977488515</v>
       </c>
     </row>
-    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>14.2</v>
       </c>
@@ -10297,7 +10296,7 @@
         <v>50487.446892668122</v>
       </c>
     </row>
-    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>14.1</v>
       </c>
@@ -10326,7 +10325,7 @@
         <v>9416.3276210569329</v>
       </c>
     </row>
-    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>14.2</v>
       </c>
@@ -10355,7 +10354,7 @@
         <v>50932.549341800674</v>
       </c>
     </row>
-    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>14.1</v>
       </c>
@@ -10384,7 +10383,7 @@
         <v>9506.0112118610195</v>
       </c>
     </row>
-    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>14.2</v>
       </c>
@@ -10413,7 +10412,7 @@
         <v>51417.644391336173</v>
       </c>
     </row>
-    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>14.1</v>
       </c>
@@ -10442,7 +10441,7 @@
         <v>9600.6705561847666</v>
       </c>
     </row>
-    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>14.2</v>
       </c>
@@ -10471,7 +10470,7 @@
         <v>51929.65309785679</v>
       </c>
     </row>
-    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>14.1</v>
       </c>
@@ -10500,7 +10499,7 @@
         <v>9699.0920645745646</v>
       </c>
     </row>
-    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>14.2</v>
       </c>
@@ -10529,7 +10528,7 @@
         <v>52462.011203276568</v>
       </c>
     </row>
-    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>14.1</v>
       </c>
@@ -10558,7 +10557,7 @@
         <v>9800.6858865173472</v>
       </c>
     </row>
-    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>14.2</v>
       </c>
@@ -10587,7 +10586,7 @@
         <v>53011.528229144671</v>
       </c>
     </row>
-    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>14.1</v>
       </c>
@@ -10616,7 +10615,7 @@
         <v>9905.1853205803909</v>
       </c>
     </row>
-    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>14.2</v>
       </c>
@@ -10645,7 +10644,7 @@
         <v>53576.761597799363</v>
       </c>
     </row>
-    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>14.1</v>
       </c>
@@ -10674,7 +10673,7 @@
         <v>10012.491216151881</v>
       </c>
     </row>
-    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>14.2</v>
       </c>
@@ -10703,7 +10702,7 @@
         <v>54157.175007443213</v>
       </c>
     </row>
-    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>14.1</v>
       </c>
@@ -10732,7 +10731,7 @@
         <v>10122.59142987548</v>
       </c>
     </row>
-    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>14.2</v>
       </c>
@@ -10761,7 +10760,7 @@
         <v>54752.70277513472</v>
       </c>
     </row>
-    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>14.3</v>
       </c>
@@ -10790,7 +10789,7 @@
         <v>56552.414086080753</v>
       </c>
     </row>
-    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>14.4</v>
       </c>
@@ -10819,7 +10818,7 @@
         <v>4250.5326261078344</v>
       </c>
     </row>
-    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>14.3</v>
       </c>
@@ -10848,7 +10847,7 @@
         <v>57119.407044400919</v>
       </c>
     </row>
-    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>14.4</v>
       </c>
@@ -10877,7 +10876,7 @@
         <v>4293.1483500704726</v>
       </c>
     </row>
-    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>14.3</v>
       </c>
@@ -10906,7 +10905,7 @@
         <v>57688.062130009188</v>
       </c>
     </row>
-    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>14.4</v>
       </c>
@@ -10935,7 +10934,7 @@
         <v>4335.8890010831956</v>
       </c>
     </row>
-    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>14.3</v>
       </c>
@@ -10964,7 +10963,7 @@
         <v>58258.379342905551</v>
       </c>
     </row>
-    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>14.4</v>
       </c>
@@ -10993,7 +10992,7 @@
         <v>4378.7545791459988</v>
       </c>
     </row>
-    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>14.3</v>
       </c>
@@ -11022,7 +11021,7 @@
         <v>58830.358683090002</v>
       </c>
     </row>
-    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>14.4</v>
       </c>
@@ -11051,7 +11050,7 @@
         <v>4421.7450842588833</v>
       </c>
     </row>
-    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>14.3</v>
       </c>
@@ -11080,7 +11079,7 @@
         <v>59404.000150562548</v>
       </c>
     </row>
-    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>14.4</v>
       </c>
@@ -11109,7 +11108,7 @@
         <v>4464.8605164218507</v>
       </c>
     </row>
-    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>14.3</v>
       </c>
@@ -11138,7 +11137,7 @@
         <v>59979.303745323188</v>
       </c>
     </row>
-    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>14.4</v>
       </c>
@@ -11167,7 +11166,7 @@
         <v>4508.1008756348992</v>
       </c>
     </row>
-    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>14.3</v>
       </c>
@@ -11196,7 +11195,7 @@
         <v>60556.269467371923</v>
       </c>
     </row>
-    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>14.4</v>
       </c>
@@ -11225,7 +11224,7 @@
         <v>4551.4661618980308</v>
       </c>
     </row>
-    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>14.3</v>
       </c>
@@ -11254,7 +11253,7 @@
         <v>61134.897316708753</v>
       </c>
     </row>
-    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>14.4</v>
       </c>
@@ -11283,7 +11282,7 @@
         <v>4594.9563752112444</v>
       </c>
     </row>
-    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>14.3</v>
       </c>
@@ -11312,7 +11311,7 @@
         <v>61715.187293333664</v>
       </c>
     </row>
-    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>14.4</v>
       </c>
@@ -11341,7 +11340,7 @@
         <v>4638.5715155745374</v>
       </c>
     </row>
-    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>14.3</v>
       </c>
@@ -11370,7 +11369,7 @@
         <v>55221.39247291936</v>
       </c>
     </row>
-    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>14.4</v>
       </c>
@@ -11399,7 +11398,7 @@
         <v>4150.4917899344118</v>
       </c>
     </row>
-    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>14.3</v>
       </c>
@@ -11428,7 +11427,7 @@
         <v>55639.562823662178</v>
       </c>
     </row>
-    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>14.4</v>
       </c>
@@ -11457,7 +11456,7 @@
         <v>4181.9218667547893</v>
       </c>
     </row>
-    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>14.3</v>
       </c>
@@ -11486,7 +11485,7 @@
         <v>56130.086849052597</v>
       </c>
     </row>
-    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>14.4</v>
       </c>
@@ -11515,7 +11514,7 @@
         <v>4218.7901138050047</v>
       </c>
     </row>
-    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>14.3</v>
       </c>
@@ -11544,7 +11543,7 @@
         <v>56664.68461830516</v>
       </c>
     </row>
-    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>14.4</v>
       </c>
@@ -11573,7 +11572,7 @@
         <v>4258.9709848920229</v>
       </c>
     </row>
-    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>14.3</v>
       </c>
@@ -11602,7 +11601,7 @@
         <v>57228.942514991417</v>
       </c>
     </row>
-    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>14.4</v>
       </c>
@@ -11631,7 +11630,7 @@
         <v>4301.3811390501323</v>
       </c>
     </row>
-    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>14.3</v>
       </c>
@@ -11660,7 +11659,7 @@
         <v>57815.626415133163</v>
       </c>
     </row>
-    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>14.4</v>
       </c>
@@ -11689,7 +11688,7 @@
         <v>4345.4768527179676</v>
       </c>
     </row>
-    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>14.3</v>
       </c>
@@ -11718,7 +11717,7 @@
         <v>58421.220260043949</v>
       </c>
     </row>
-    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>14.4</v>
       </c>
@@ -11747,7 +11746,7 @@
         <v>4390.9938556180596</v>
       </c>
     </row>
-    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>14.3</v>
       </c>
@@ -11776,7 +11775,7 @@
         <v>59044.134260669722</v>
       </c>
     </row>
-    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>14.4</v>
       </c>
@@ -11805,7 +11804,7 @@
         <v>4437.8126577100284</v>
       </c>
     </row>
-    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>14.3</v>
       </c>
@@ -11834,7 +11833,7 @@
         <v>59683.777386974543</v>
       </c>
     </row>
-    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>14.4</v>
       </c>
@@ -11863,7 +11862,7 @@
         <v>4485.8888366205483</v>
       </c>
     </row>
-    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>14.3</v>
       </c>
@@ -11892,7 +11891,7 @@
         <v>60340.077253239288</v>
       </c>
     </row>
-    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>14.4</v>
       </c>
@@ -11921,7 +11920,7 @@
         <v>4535.2169517708999</v>
       </c>
     </row>
-    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>194</v>
       </c>
@@ -11950,7 +11949,7 @@
         <v>93.008258302465308</v>
       </c>
     </row>
-    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>194</v>
       </c>
@@ -11979,7 +11978,7 @@
         <v>93.941532956484238</v>
       </c>
     </row>
-    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>194</v>
       </c>
@@ -12008,7 +12007,7 @@
         <v>94.87480761050314</v>
       </c>
     </row>
-    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>194</v>
       </c>
@@ -12037,7 +12036,7 @@
         <v>95.808082264522056</v>
       </c>
     </row>
-    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>194</v>
       </c>
@@ -12066,7 +12065,7 @@
         <v>96.741356918540987</v>
       </c>
     </row>
-    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>194</v>
       </c>
@@ -12095,7 +12094,7 @@
         <v>93.424405824177825</v>
       </c>
     </row>
-    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>194</v>
       </c>
@@ -12124,7 +12123,7 @@
         <v>94.15447253075159</v>
       </c>
     </row>
-    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>194</v>
       </c>
@@ -12153,7 +12152,7 @@
         <v>94.890244356788997</v>
       </c>
     </row>
-    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>194</v>
       </c>
@@ -12182,7 +12181,7 @@
         <v>95.631765885049148</v>
       </c>
     </row>
-    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>194</v>
       </c>
@@ -12211,7 +12210,7 @@
         <v>96.379082046683891</v>
       </c>
     </row>
-    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>323</v>
       </c>
@@ -12240,7 +12239,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>323</v>
       </c>
@@ -12269,7 +12268,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>323</v>
       </c>
@@ -12298,7 +12297,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>323</v>
       </c>
@@ -12327,7 +12326,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>323</v>
       </c>
@@ -12356,7 +12355,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>376</v>
       </c>
@@ -12385,7 +12384,7 @@
         <v>36033.446856183858</v>
       </c>
     </row>
-    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>376</v>
       </c>
@@ -12414,7 +12413,7 @@
         <v>38872.61512155136</v>
       </c>
     </row>
-    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>376</v>
       </c>
@@ -12443,7 +12442,7 @@
         <v>41717.57657108127</v>
       </c>
     </row>
-    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>376</v>
       </c>
@@ -12472,7 +12471,7 @@
         <v>44568.331204773582</v>
       </c>
     </row>
-    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>376</v>
       </c>
@@ -12501,7 +12500,7 @@
         <v>47424.879022628324</v>
       </c>
     </row>
-    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>376</v>
       </c>
@@ -12530,7 +12529,7 @@
         <v>34556.673694232348</v>
       </c>
     </row>
-    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>376</v>
       </c>
@@ -12559,7 +12558,7 @@
         <v>37856.02412414951</v>
       </c>
     </row>
-    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>376</v>
       </c>
@@ -12588,7 +12587,7 @@
         <v>41689.182193960667</v>
       </c>
     </row>
-    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>376</v>
       </c>
@@ -12617,7 +12616,7 @@
         <v>46057.780844716202</v>
       </c>
     </row>
-    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>376</v>
       </c>
@@ -12646,7 +12645,7 @@
         <v>50963.453017466447</v>
       </c>
     </row>
-    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>466</v>
       </c>
@@ -12675,7 +12674,7 @@
         <v>60.742268041340189</v>
       </c>
     </row>
-    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>466</v>
       </c>
@@ -12704,7 +12703,7 @@
         <v>62.622639562581618</v>
       </c>
     </row>
-    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>466</v>
       </c>
@@ -12733,7 +12732,7 @@
         <v>64.561276595843793</v>
       </c>
     </row>
-    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>466</v>
       </c>
@@ -12762,7 +12761,7 @@
         <v>66.559986395217919</v>
       </c>
     </row>
-    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>466</v>
       </c>
@@ -12791,7 +12790,7 @@
         <v>68.620632331635861</v>
       </c>
     </row>
-    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>466</v>
       </c>
@@ -12820,7 +12819,7 @@
         <v>57.97444574550294</v>
       </c>
     </row>
-    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>466</v>
       </c>
@@ -12849,7 +12848,7 @@
         <v>59.769135016331823</v>
       </c>
     </row>
-    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>466</v>
       </c>
@@ -12878,7 +12877,7 @@
         <v>61.619434834385345</v>
       </c>
     </row>
-    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>466</v>
       </c>
@@ -12907,7 +12906,7 @@
         <v>63.527070103221561</v>
       </c>
     </row>
-    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>466</v>
       </c>
@@ -12936,7 +12935,7 @@
         <v>65.493819286181989</v>
       </c>
     </row>
-    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>96</v>
       </c>
@@ -12965,7 +12964,7 @@
         <v>990.23735660954856</v>
       </c>
     </row>
-    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>96</v>
       </c>
@@ -12994,7 +12993,7 @@
         <v>1074.101030045967</v>
       </c>
     </row>
-    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>96</v>
       </c>
@@ -13023,7 +13022,7 @@
         <v>1165.04537214991</v>
       </c>
     </row>
-    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>96</v>
       </c>
@@ -13052,7 +13051,7 @@
         <v>1263.666562398188</v>
       </c>
     </row>
-    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>96</v>
       </c>
@@ -13081,7 +13080,7 @@
         <v>1370.6108527044289</v>
       </c>
     </row>
-    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>385</v>
       </c>
@@ -13110,7 +13109,7 @@
         <v>22394.58706838209</v>
       </c>
     </row>
-    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>385</v>
       </c>
@@ -13139,7 +13138,7 @@
         <v>24510.31089960839</v>
       </c>
     </row>
-    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>385</v>
       </c>
@@ -13168,7 +13167,7 @@
         <v>26645.972550694249</v>
       </c>
     </row>
-    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>385</v>
       </c>
@@ -13197,7 +13196,7 @@
         <v>28801.572021639651</v>
       </c>
     </row>
-    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>385</v>
       </c>
@@ -13226,7 +13225,7 @@
         <v>30977.109312444602</v>
       </c>
     </row>
-    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>385</v>
       </c>
@@ -13255,7 +13254,7 @@
         <v>20844.165363419648</v>
       </c>
     </row>
-    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>385</v>
       </c>
@@ -13284,7 +13283,7 @@
         <v>22863.33165174054</v>
       </c>
     </row>
-    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>385</v>
       </c>
@@ -13313,7 +13312,7 @@
         <v>25170.11368192935</v>
       </c>
     </row>
-    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>385</v>
       </c>
@@ -13342,7 +13341,7 @@
         <v>27768.499991978719</v>
       </c>
     </row>
-    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>385</v>
       </c>
@@ -13371,7 +13370,7 @@
         <v>30662.479119881289</v>
       </c>
     </row>
-    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A437" s="3">
         <v>386.1</v>
       </c>
@@ -13400,7 +13399,7 @@
         <v>6063.9485940000004</v>
       </c>
     </row>
-    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A438" s="3">
         <v>386.1</v>
       </c>
@@ -13429,7 +13428,7 @@
         <v>7617.8354212124996</v>
       </c>
     </row>
-    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A439" s="3">
         <v>386.1</v>
       </c>
@@ -13458,7 +13457,7 @@
         <v>9569.6688749062487</v>
       </c>
     </row>
-    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A440" s="3">
         <v>386.1</v>
       </c>
@@ -13487,7 +13486,7 @@
         <v>11023.172622260399</v>
       </c>
     </row>
-    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A441" s="3">
         <v>386.1</v>
       </c>
@@ -13661,7 +13660,7 @@
         <v>7937.7742038094157</v>
       </c>
     </row>
-    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A447" s="3">
         <v>386.3</v>
       </c>
@@ -13690,7 +13689,7 @@
         <v>7026.0817481999993</v>
       </c>
     </row>
-    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A448" s="3">
         <v>386.3</v>
       </c>
@@ -13719,7 +13718,7 @@
         <v>7738.846362034199</v>
       </c>
     </row>
-    <row r="449" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A449" s="3">
         <v>386.3</v>
       </c>
@@ -13748,7 +13747,7 @@
         <v>8458.3536047747984</v>
       </c>
     </row>
-    <row r="450" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A450" s="3">
         <v>386.3</v>
       </c>
@@ -13777,7 +13776,7 @@
         <v>9184.6034764218002</v>
       </c>
     </row>
-    <row r="451" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A451" s="3">
         <v>386.3</v>
       </c>
@@ -13807,13 +13806,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I451" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="386,2"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I451" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="587" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F74FB05-C0CE-405C-BC60-D476B8FA0794}"/>
+  <xr:revisionPtr revIDLastSave="609" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41B49B1E-B5A8-4175-9174-50DB2DF49CB5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Proyecciones" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$I$451</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$I$456</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="92">
   <si>
     <t>Id</t>
   </si>
@@ -310,6 +310,12 @@
   <si>
     <t>Proyeccion_CAGR_11.8%↑</t>
   </si>
+  <si>
+    <t>423</t>
+  </si>
+  <si>
+    <t>Proyeccion_CAGR_24.6%↑</t>
+  </si>
 </sst>
 </file>
 
@@ -330,6 +336,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -715,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}">
-  <dimension ref="A1:I451"/>
+  <dimension ref="A1:I456"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
@@ -6702,10 +6709,10 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B207" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C207" s="2">
         <v>46387</v>
@@ -6720,21 +6727,21 @@
         <v>30</v>
       </c>
       <c r="G207">
-        <v>12.6</v>
+        <v>11.6</v>
       </c>
       <c r="H207">
-        <v>12</v>
+        <v>10.7</v>
       </c>
       <c r="I207">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B208" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C208" s="2">
         <v>46752</v>
@@ -6749,21 +6756,21 @@
         <v>30</v>
       </c>
       <c r="G208">
-        <v>13</v>
+        <v>12.2</v>
       </c>
       <c r="H208">
-        <v>12.4</v>
+        <v>11.2</v>
       </c>
       <c r="I208">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B209" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C209" s="2">
         <v>47118</v>
@@ -6778,21 +6785,21 @@
         <v>30</v>
       </c>
       <c r="G209">
-        <v>13.3</v>
+        <v>12.8</v>
       </c>
       <c r="H209">
-        <v>12.6</v>
+        <v>11.8</v>
       </c>
       <c r="I209">
-        <v>13.5</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B210" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C210" s="2">
         <v>47483</v>
@@ -6807,21 +6814,21 @@
         <v>30</v>
       </c>
       <c r="G210">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="H210">
-        <v>13</v>
+        <v>12.3</v>
       </c>
       <c r="I210">
-        <v>13.8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B211" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C211" s="2">
         <v>47848</v>
@@ -6836,21 +6843,21 @@
         <v>30</v>
       </c>
       <c r="G211">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="H211">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
       <c r="I211">
-        <v>14</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212">
-        <v>424</v>
+        <v>460</v>
       </c>
       <c r="B212" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C212" s="2">
         <v>46387</v>
@@ -6862,24 +6869,24 @@
         <v>12</v>
       </c>
       <c r="F212" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G212">
-        <v>9.6</v>
+        <v>92.354399999999998</v>
       </c>
       <c r="H212">
-        <v>8.8000000000000007</v>
+        <v>89.583767999999992</v>
       </c>
       <c r="I212">
-        <v>10.4</v>
+        <v>95.125032000000004</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213">
-        <v>424</v>
+        <v>460</v>
       </c>
       <c r="B213" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C213" s="2">
         <v>46752</v>
@@ -6891,24 +6898,24 @@
         <v>14</v>
       </c>
       <c r="F213" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G213">
-        <v>10.199999999999999</v>
+        <v>93.277944000000005</v>
       </c>
       <c r="H213">
-        <v>9.4</v>
+        <v>90.395655530400006</v>
       </c>
       <c r="I213">
-        <v>11</v>
+        <v>96.160232469600004</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214">
-        <v>424</v>
+        <v>460</v>
       </c>
       <c r="B214" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C214" s="2">
         <v>47118</v>
@@ -6920,24 +6927,24 @@
         <v>16</v>
       </c>
       <c r="F214" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G214">
-        <v>10.8</v>
+        <v>94.21072344000001</v>
       </c>
       <c r="H214">
-        <v>9.9</v>
+        <v>91.214822434607996</v>
       </c>
       <c r="I214">
-        <v>11.2</v>
+        <v>97.206624445392023</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215">
-        <v>424</v>
+        <v>460</v>
       </c>
       <c r="B215" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C215" s="2">
         <v>47483</v>
@@ -6949,24 +6956,24 @@
         <v>18</v>
       </c>
       <c r="F215" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G215">
-        <v>11.4</v>
+        <v>95.152830674399993</v>
       </c>
       <c r="H215">
-        <v>10.5</v>
+        <v>87.882076685999976</v>
       </c>
       <c r="I215">
-        <v>11.6</v>
+        <v>98.545849202319999</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216">
-        <v>424</v>
+        <v>460</v>
       </c>
       <c r="B216" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C216" s="2">
         <v>47848</v>
@@ -6978,24 +6985,24 @@
         <v>20</v>
       </c>
       <c r="F216" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G216">
-        <v>11.6</v>
+        <v>96.104358981144017</v>
       </c>
       <c r="H216">
-        <v>11</v>
+        <v>90.260897452860036</v>
       </c>
       <c r="I216">
-        <v>11.8</v>
+        <v>98.831307694343209</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217">
-        <v>460</v>
+        <v>77</v>
       </c>
       <c r="B217" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C217" s="2">
         <v>46387</v>
@@ -7007,24 +7014,24 @@
         <v>12</v>
       </c>
       <c r="F217" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="G217">
-        <v>92.354399999999998</v>
+        <v>95.596500000000006</v>
       </c>
       <c r="H217">
-        <v>89.583767999999992</v>
+        <v>88.991250000000008</v>
       </c>
       <c r="I217">
-        <v>95.125032000000004</v>
+        <v>98.67895</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218">
-        <v>460</v>
+        <v>77</v>
       </c>
       <c r="B218" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C218" s="2">
         <v>46752</v>
@@ -7036,24 +7043,24 @@
         <v>14</v>
       </c>
       <c r="F218" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="G218">
-        <v>93.277944000000005</v>
+        <v>96.552465000000012</v>
       </c>
       <c r="H218">
-        <v>90.395655530400006</v>
+        <v>91.38116250000003</v>
       </c>
       <c r="I218">
-        <v>96.160232469600004</v>
+        <v>98.965739499999998</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219">
-        <v>460</v>
+        <v>77</v>
       </c>
       <c r="B219" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C219" s="2">
         <v>47118</v>
@@ -7065,24 +7072,24 @@
         <v>16</v>
       </c>
       <c r="F219" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="G219">
-        <v>94.21072344000001</v>
+        <v>97.517989650000018</v>
       </c>
       <c r="H219">
-        <v>91.214822434607996</v>
+        <v>91.666910271000006</v>
       </c>
       <c r="I219">
-        <v>97.206624445392023</v>
+        <v>99.255396895000004</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220">
-        <v>460</v>
+        <v>77</v>
       </c>
       <c r="B220" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C220" s="2">
         <v>47483</v>
@@ -7094,24 +7101,24 @@
         <v>18</v>
       </c>
       <c r="F220" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="G220">
-        <v>95.152830674399993</v>
+        <v>98.493169546500013</v>
       </c>
       <c r="H220">
-        <v>87.882076685999976</v>
+        <v>92.583579373710009</v>
       </c>
       <c r="I220">
-        <v>98.545849202319999</v>
+        <v>99.547950863950007</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221">
-        <v>460</v>
+        <v>77</v>
       </c>
       <c r="B221" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C221" s="2">
         <v>47848</v>
@@ -7123,24 +7130,24 @@
         <v>20</v>
       </c>
       <c r="F221" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="G221">
-        <v>96.104358981144017</v>
+        <v>99.478101241965021</v>
       </c>
       <c r="H221">
-        <v>90.260897452860036</v>
+        <v>93.509415167447116</v>
       </c>
       <c r="I221">
-        <v>98.831307694343209</v>
+        <v>99.843430372589509</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="B222" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C222" s="2">
         <v>46387</v>
@@ -7152,24 +7159,24 @@
         <v>12</v>
       </c>
       <c r="F222" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="G222">
-        <v>95.596500000000006</v>
+        <v>8</v>
       </c>
       <c r="H222">
-        <v>88.991250000000008</v>
+        <v>6</v>
       </c>
       <c r="I222">
-        <v>98.67895</v>
+        <v>10</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="B223" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C223" s="2">
         <v>46752</v>
@@ -7181,24 +7188,24 @@
         <v>14</v>
       </c>
       <c r="F223" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="G223">
-        <v>96.552465000000012</v>
+        <v>7</v>
       </c>
       <c r="H223">
-        <v>91.38116250000003</v>
+        <v>5</v>
       </c>
       <c r="I223">
-        <v>98.965739499999998</v>
+        <v>10</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="B224" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C224" s="2">
         <v>47118</v>
@@ -7210,24 +7217,24 @@
         <v>16</v>
       </c>
       <c r="F224" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="G224">
-        <v>97.517989650000018</v>
+        <v>7</v>
       </c>
       <c r="H224">
-        <v>91.666910271000006</v>
+        <v>5</v>
       </c>
       <c r="I224">
-        <v>99.255396895000004</v>
+        <v>10</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="B225" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C225" s="2">
         <v>47483</v>
@@ -7239,24 +7246,24 @@
         <v>18</v>
       </c>
       <c r="F225" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="G225">
-        <v>98.493169546500013</v>
+        <v>9</v>
       </c>
       <c r="H225">
-        <v>92.583579373710009</v>
+        <v>7</v>
       </c>
       <c r="I225">
-        <v>99.547950863950007</v>
+        <v>12</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="B226" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C226" s="2">
         <v>47848</v>
@@ -7268,169 +7275,169 @@
         <v>20</v>
       </c>
       <c r="F226" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="G226">
-        <v>99.478101241965021</v>
+        <v>9</v>
       </c>
       <c r="H226">
-        <v>93.509415167447116</v>
+        <v>7</v>
       </c>
       <c r="I226">
-        <v>99.843430372589509</v>
+        <v>12</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A227">
-        <v>98</v>
-      </c>
-      <c r="B227" t="s">
-        <v>74</v>
-      </c>
-      <c r="C227" s="2">
+      <c r="A227" s="3">
+        <v>386.1</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C227" s="4">
         <v>46387</v>
       </c>
-      <c r="D227">
+      <c r="D227" s="3">
         <v>2026</v>
       </c>
-      <c r="E227" t="s">
+      <c r="E227" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F227" t="s">
         <v>35</v>
       </c>
       <c r="G227">
-        <v>8</v>
+        <v>5021.3256906738234</v>
       </c>
       <c r="H227">
-        <v>6</v>
+        <v>4017.0605525390588</v>
       </c>
       <c r="I227">
-        <v>10</v>
+        <v>6025.5908288085884</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A228">
-        <v>98</v>
-      </c>
-      <c r="B228" t="s">
-        <v>74</v>
-      </c>
-      <c r="C228" s="2">
+      <c r="A228" s="3">
+        <v>386.1</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C228" s="4">
         <v>46752</v>
       </c>
-      <c r="D228">
+      <c r="D228" s="3">
         <v>2027</v>
       </c>
-      <c r="E228" t="s">
+      <c r="E228" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F228" t="s">
         <v>35</v>
       </c>
       <c r="G228">
-        <v>7</v>
+        <v>5914.5712658767779</v>
       </c>
       <c r="H228">
-        <v>5</v>
+        <v>4696.1695851061622</v>
       </c>
       <c r="I228">
-        <v>10</v>
+        <v>7132.9729466473937</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A229">
-        <v>98</v>
-      </c>
-      <c r="B229" t="s">
-        <v>74</v>
-      </c>
-      <c r="C229" s="2">
+      <c r="A229" s="3">
+        <v>386.1</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C229" s="4">
         <v>47118</v>
       </c>
-      <c r="D229">
+      <c r="D229" s="3">
         <v>2028</v>
       </c>
-      <c r="E229" t="s">
+      <c r="E229" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F229" t="s">
         <v>35</v>
       </c>
       <c r="G229">
-        <v>7</v>
+        <v>6920.7335283964458</v>
       </c>
       <c r="H229">
-        <v>5</v>
+        <v>5453.5380203763998</v>
       </c>
       <c r="I229">
-        <v>10</v>
+        <v>8387.9290364164917</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A230">
-        <v>98</v>
-      </c>
-      <c r="B230" t="s">
-        <v>74</v>
-      </c>
-      <c r="C230" s="2">
+      <c r="A230" s="3">
+        <v>386.1</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C230" s="4">
         <v>47483</v>
       </c>
-      <c r="D230">
+      <c r="D230" s="3">
         <v>2029</v>
       </c>
-      <c r="E230" t="s">
+      <c r="E230" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F230" t="s">
         <v>35</v>
       </c>
       <c r="G230">
-        <v>9</v>
+        <v>8039.8124782328259</v>
       </c>
       <c r="H230">
-        <v>7</v>
+        <v>6287.1333579780694</v>
       </c>
       <c r="I230">
-        <v>12</v>
+        <v>9792.4915984875806</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A231">
-        <v>98</v>
-      </c>
-      <c r="B231" t="s">
-        <v>74</v>
-      </c>
-      <c r="C231" s="2">
+      <c r="A231" s="3">
+        <v>386.1</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C231" s="4">
         <v>47848</v>
       </c>
-      <c r="D231">
+      <c r="D231" s="3">
         <v>2030</v>
       </c>
-      <c r="E231" t="s">
+      <c r="E231" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F231" t="s">
         <v>35</v>
       </c>
       <c r="G231">
-        <v>9</v>
+        <v>9271.8081153859184</v>
       </c>
       <c r="H231">
-        <v>7</v>
+        <v>7194.923097539473</v>
       </c>
       <c r="I231">
-        <v>12</v>
+        <v>11348.693133232369</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" s="3">
-        <v>386.1</v>
+        <v>386.2</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C232" s="4">
         <v>46387</v>
@@ -7442,24 +7449,24 @@
         <v>12</v>
       </c>
       <c r="F232" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="G232">
-        <v>5021.3256906738234</v>
+        <v>8322.3104068060129</v>
       </c>
       <c r="H232">
-        <v>4017.0605525390588</v>
+        <v>6657.8483254448111</v>
       </c>
       <c r="I232">
-        <v>6025.5908288085884</v>
+        <v>9176.5019107995558</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="3">
-        <v>386.1</v>
+        <v>386.2</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C233" s="4">
         <v>46752</v>
@@ -7471,24 +7478,24 @@
         <v>14</v>
       </c>
       <c r="F233" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="G233">
-        <v>5914.5712658767779</v>
+        <v>9300.7150739219178</v>
       </c>
       <c r="H233">
-        <v>4696.1695851061622</v>
+        <v>7384.7677686940033</v>
       </c>
       <c r="I233">
-        <v>7132.9729466473937</v>
+        <v>10283.967217993961</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" s="3">
-        <v>386.1</v>
+        <v>386.2</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C234" s="4">
         <v>47118</v>
@@ -7500,24 +7507,24 @@
         <v>16</v>
       </c>
       <c r="F234" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="G234">
-        <v>6920.7335283964458</v>
+        <v>10394.14497391682</v>
       </c>
       <c r="H234">
-        <v>5453.5380203763998</v>
+        <v>8190.5862394464584</v>
       </c>
       <c r="I234">
-        <v>8387.9290364164917</v>
+        <v>11524.99750015523</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" s="3">
-        <v>386.1</v>
+        <v>386.2</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C235" s="4">
         <v>47483</v>
@@ -7529,24 +7536,24 @@
         <v>18</v>
       </c>
       <c r="F235" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="G235">
-        <v>8039.8124782328259</v>
+        <v>11616.122941098</v>
       </c>
       <c r="H235">
-        <v>6287.1333579780694</v>
+        <v>9083.8081399386374</v>
       </c>
       <c r="I235">
-        <v>9792.4915984875806</v>
+        <v>12915.691019463869</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" s="3">
-        <v>386.1</v>
+        <v>386.2</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C236" s="4">
         <v>47848</v>
@@ -7558,24 +7565,24 @@
         <v>20</v>
       </c>
       <c r="F236" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="G236">
-        <v>9271.8081153859184</v>
+        <v>12981.76160918564</v>
       </c>
       <c r="H236">
-        <v>7194.923097539473</v>
+        <v>10073.847008728049</v>
       </c>
       <c r="I236">
-        <v>11348.693133232369</v>
+        <v>14474.085149544269</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" s="3">
-        <v>386.2</v>
+        <v>386.3</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C237" s="4">
         <v>46387</v>
@@ -7587,24 +7594,24 @@
         <v>12</v>
       </c>
       <c r="F237" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="G237">
-        <v>8322.3104068060129</v>
+        <v>5646.493414116343</v>
       </c>
       <c r="H237">
-        <v>6657.8483254448111</v>
+        <v>5477.0986116928534</v>
       </c>
       <c r="I237">
-        <v>9176.5019107995558</v>
+        <v>6775.7920969396118</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" s="3">
-        <v>386.2</v>
+        <v>386.3</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C238" s="4">
         <v>46752</v>
@@ -7616,24 +7623,24 @@
         <v>14</v>
       </c>
       <c r="F238" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="G238">
-        <v>9300.7150739219178</v>
+        <v>6374.4716673772846</v>
       </c>
       <c r="H238">
-        <v>7384.7677686940033</v>
+        <v>6177.5004928553271</v>
       </c>
       <c r="I238">
-        <v>10283.967217993961</v>
+        <v>7687.612830857006</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" s="3">
-        <v>386.2</v>
+        <v>386.3</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C239" s="4">
         <v>47118</v>
@@ -7645,24 +7652,24 @@
         <v>16</v>
       </c>
       <c r="F239" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="G239">
-        <v>10394.14497391682</v>
+        <v>7227.2111180454294</v>
       </c>
       <c r="H239">
-        <v>8190.5862394464584</v>
+        <v>6997.3858044915851</v>
       </c>
       <c r="I239">
-        <v>11524.99750015523</v>
+        <v>8759.3798750710612</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" s="3">
-        <v>386.2</v>
+        <v>386.3</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C240" s="4">
         <v>47483</v>
@@ -7674,24 +7681,24 @@
         <v>18</v>
       </c>
       <c r="F240" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="G240">
-        <v>11616.122941098</v>
+        <v>8204.7117661207758</v>
       </c>
       <c r="H240">
-        <v>9083.8081399386374</v>
+        <v>7936.417691368626</v>
       </c>
       <c r="I240">
-        <v>12915.691019463869</v>
+        <v>9993.3389311351038</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" s="3">
-        <v>386.2</v>
+        <v>386.3</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C241" s="4">
         <v>47848</v>
@@ -7703,741 +7710,741 @@
         <v>20</v>
       </c>
       <c r="F241" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="G241">
-        <v>12981.76160918564</v>
+        <v>9306.9736116033237</v>
       </c>
       <c r="H241">
-        <v>10073.847008728049</v>
+        <v>8994.2592982534516</v>
       </c>
       <c r="I241">
-        <v>14474.085149544269</v>
+        <v>11391.73570060247</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A242" s="3">
-        <v>386.3</v>
-      </c>
-      <c r="B242" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C242" s="4">
+      <c r="A242">
+        <v>379</v>
+      </c>
+      <c r="B242" t="s">
+        <v>78</v>
+      </c>
+      <c r="C242" s="2">
+        <v>46203</v>
+      </c>
+      <c r="D242">
+        <v>2026</v>
+      </c>
+      <c r="E242" t="s">
+        <v>10</v>
+      </c>
+      <c r="F242" t="s">
+        <v>79</v>
+      </c>
+      <c r="G242">
+        <v>12524.007412694569</v>
+      </c>
+      <c r="H242">
+        <v>11793.36050119014</v>
+      </c>
+      <c r="I242">
+        <v>13317.175813442071</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A243">
+        <v>274</v>
+      </c>
+      <c r="B243" t="s">
+        <v>80</v>
+      </c>
+      <c r="C243" s="2">
+        <v>46203</v>
+      </c>
+      <c r="D243">
+        <v>2026</v>
+      </c>
+      <c r="E243" t="s">
+        <v>10</v>
+      </c>
+      <c r="F243" t="s">
+        <v>79</v>
+      </c>
+      <c r="G243">
+        <v>43311.880111304308</v>
+      </c>
+      <c r="H243">
+        <v>40785.077755478633</v>
+      </c>
+      <c r="I243">
+        <v>46054.901058930787</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A244">
+        <v>379</v>
+      </c>
+      <c r="B244" t="s">
+        <v>78</v>
+      </c>
+      <c r="C244" s="2">
         <v>46387</v>
       </c>
-      <c r="D242" s="3">
+      <c r="D244">
         <v>2026</v>
       </c>
-      <c r="E242" s="3" t="s">
+      <c r="E244" t="s">
         <v>12</v>
       </c>
-      <c r="F242" t="s">
-        <v>35</v>
-      </c>
-      <c r="G242">
-        <v>5646.493414116343</v>
-      </c>
-      <c r="H242">
-        <v>5477.0986116928534</v>
-      </c>
-      <c r="I242">
-        <v>6775.7920969396118</v>
-      </c>
-    </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A243" s="3">
-        <v>386.3</v>
-      </c>
-      <c r="B243" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C243" s="4">
-        <v>46752</v>
-      </c>
-      <c r="D243" s="3">
+      <c r="F244" t="s">
+        <v>79</v>
+      </c>
+      <c r="G244">
+        <v>12596.339833898201</v>
+      </c>
+      <c r="H244">
+        <v>11839.42706728914</v>
+      </c>
+      <c r="I244">
+        <v>13418.021660158851</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A245">
+        <v>274</v>
+      </c>
+      <c r="B245" t="s">
+        <v>80</v>
+      </c>
+      <c r="C245" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D245">
+        <v>2026</v>
+      </c>
+      <c r="E245" t="s">
+        <v>12</v>
+      </c>
+      <c r="F245" t="s">
+        <v>79</v>
+      </c>
+      <c r="G245">
+        <v>43562.027931574383</v>
+      </c>
+      <c r="H245">
+        <v>40944.390148251347</v>
+      </c>
+      <c r="I245">
+        <v>46403.657098334967</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A246">
+        <v>379</v>
+      </c>
+      <c r="B246" t="s">
+        <v>78</v>
+      </c>
+      <c r="C246" s="2">
+        <v>46568</v>
+      </c>
+      <c r="D246">
         <v>2027</v>
       </c>
-      <c r="E243" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F243" t="s">
-        <v>35</v>
-      </c>
-      <c r="G243">
-        <v>6374.4716673772846</v>
-      </c>
-      <c r="H243">
-        <v>6177.5004928553271</v>
-      </c>
-      <c r="I243">
-        <v>7687.612830857006</v>
-      </c>
-    </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A244" s="3">
-        <v>386.3</v>
-      </c>
-      <c r="B244" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C244" s="4">
-        <v>47118</v>
-      </c>
-      <c r="D244" s="3">
-        <v>2028</v>
-      </c>
-      <c r="E244" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F244" t="s">
-        <v>35</v>
-      </c>
-      <c r="G244">
-        <v>7227.2111180454294</v>
-      </c>
-      <c r="H244">
-        <v>6997.3858044915851</v>
-      </c>
-      <c r="I244">
-        <v>8759.3798750710612</v>
-      </c>
-    </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A245" s="3">
-        <v>386.3</v>
-      </c>
-      <c r="B245" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C245" s="4">
-        <v>47483</v>
-      </c>
-      <c r="D245" s="3">
-        <v>2029</v>
-      </c>
-      <c r="E245" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F245" t="s">
-        <v>35</v>
-      </c>
-      <c r="G245">
-        <v>8204.7117661207758</v>
-      </c>
-      <c r="H245">
-        <v>7936.417691368626</v>
-      </c>
-      <c r="I245">
-        <v>9993.3389311351038</v>
-      </c>
-    </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A246" s="3">
-        <v>386.3</v>
-      </c>
-      <c r="B246" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C246" s="4">
-        <v>47848</v>
-      </c>
-      <c r="D246" s="3">
-        <v>2030</v>
-      </c>
-      <c r="E246" s="3" t="s">
-        <v>20</v>
+      <c r="E246" t="s">
+        <v>13</v>
       </c>
       <c r="F246" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="G246">
-        <v>9306.9736116033237</v>
+        <v>12684.76580268722</v>
       </c>
       <c r="H246">
-        <v>8994.2592982534516</v>
+        <v>11900.33876343572</v>
       </c>
       <c r="I246">
-        <v>11391.73570060247</v>
+        <v>13536.316299144</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247">
-        <v>379</v>
+        <v>274</v>
       </c>
       <c r="B247" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C247" s="2">
-        <v>46203</v>
+        <v>46568</v>
       </c>
       <c r="D247">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E247" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F247" t="s">
         <v>79</v>
       </c>
       <c r="G247">
-        <v>12524.007412694569</v>
+        <v>43867.832202740341</v>
       </c>
       <c r="H247">
-        <v>11793.36050119014</v>
+        <v>41155.041579054749</v>
       </c>
       <c r="I247">
-        <v>13317.175813442071</v>
+        <v>46812.756442714293</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248">
-        <v>274</v>
+        <v>379</v>
       </c>
       <c r="B248" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C248" s="2">
-        <v>46203</v>
+        <v>46752</v>
       </c>
       <c r="D248">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E248" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F248" t="s">
         <v>79</v>
       </c>
       <c r="G248">
-        <v>43311.880111304308</v>
+        <v>12782.81992485196</v>
       </c>
       <c r="H248">
-        <v>40785.077755478633</v>
+        <v>11969.956831290679</v>
       </c>
       <c r="I248">
-        <v>46054.901058930787</v>
+        <v>13665.23975007113</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249">
-        <v>379</v>
+        <v>274</v>
       </c>
       <c r="B249" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C249" s="2">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="D249">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E249" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F249" t="s">
         <v>79</v>
       </c>
       <c r="G249">
-        <v>12596.339833898201</v>
+        <v>44206.933597659161</v>
       </c>
       <c r="H249">
-        <v>11839.42706728914</v>
+        <v>41395.802328322461</v>
       </c>
       <c r="I249">
-        <v>13418.021660158851</v>
+        <v>47258.613496777638</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250">
-        <v>274</v>
+        <v>379</v>
       </c>
       <c r="B250" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C250" s="2">
-        <v>46387</v>
+        <v>46934</v>
       </c>
       <c r="D250">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="E250" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F250" t="s">
         <v>79</v>
       </c>
       <c r="G250">
-        <v>43562.027931574383</v>
+        <v>12887.205199203119</v>
       </c>
       <c r="H250">
-        <v>40944.390148251347</v>
+        <v>12045.149143947299</v>
       </c>
       <c r="I250">
-        <v>46403.657098334967</v>
+        <v>13801.316029168571</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251">
-        <v>379</v>
+        <v>274</v>
       </c>
       <c r="B251" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C251" s="2">
-        <v>46568</v>
+        <v>46934</v>
       </c>
       <c r="D251">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E251" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F251" t="s">
         <v>79</v>
       </c>
       <c r="G251">
-        <v>12684.76580268722</v>
+        <v>44567.930069403526</v>
       </c>
       <c r="H251">
-        <v>11900.33876343572</v>
+        <v>41655.840535244497</v>
       </c>
       <c r="I251">
-        <v>13536.316299144</v>
+        <v>47729.20723662855</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252">
-        <v>274</v>
+        <v>379</v>
       </c>
       <c r="B252" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C252" s="2">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="D252">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E252" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F252" t="s">
         <v>79</v>
       </c>
       <c r="G252">
-        <v>43867.832202740341</v>
+        <v>12996.26184424147</v>
       </c>
       <c r="H252">
-        <v>41155.041579054749</v>
+        <v>12124.33403356571</v>
       </c>
       <c r="I252">
-        <v>46812.756442714293</v>
+        <v>13942.80055708834</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253">
-        <v>379</v>
+        <v>274</v>
       </c>
       <c r="B253" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C253" s="2">
-        <v>46752</v>
+        <v>47118</v>
       </c>
       <c r="D253">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E253" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F253" t="s">
         <v>79</v>
       </c>
       <c r="G253">
-        <v>12782.81992485196</v>
+        <v>44945.081581662613</v>
       </c>
       <c r="H253">
-        <v>11969.956831290679</v>
+        <v>41929.68630463483</v>
       </c>
       <c r="I253">
-        <v>13665.23975007113</v>
+        <v>48218.50436884314</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254">
-        <v>274</v>
+        <v>379</v>
       </c>
       <c r="B254" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C254" s="2">
-        <v>46752</v>
+        <v>47299</v>
       </c>
       <c r="D254">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="E254" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F254" t="s">
         <v>79</v>
       </c>
       <c r="G254">
-        <v>44206.933597659161</v>
+        <v>13109.17611451162</v>
       </c>
       <c r="H254">
-        <v>41395.802328322461</v>
+        <v>12206.729246246599</v>
       </c>
       <c r="I254">
-        <v>47258.613496777638</v>
+        <v>14088.84540208515</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255">
-        <v>379</v>
+        <v>274</v>
       </c>
       <c r="B255" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C255" s="2">
-        <v>46934</v>
+        <v>47299</v>
       </c>
       <c r="D255">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E255" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F255" t="s">
         <v>79</v>
       </c>
       <c r="G255">
-        <v>12887.205199203119</v>
+        <v>45335.573951687817</v>
       </c>
       <c r="H255">
-        <v>12045.149143947299</v>
+        <v>42214.634361257893</v>
       </c>
       <c r="I255">
-        <v>13801.316029168571</v>
+        <v>48723.572483938951</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256">
-        <v>274</v>
+        <v>379</v>
       </c>
       <c r="B256" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C256" s="2">
-        <v>46934</v>
+        <v>47483</v>
       </c>
       <c r="D256">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E256" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F256" t="s">
         <v>79</v>
       </c>
       <c r="G256">
-        <v>44567.930069403526</v>
+        <v>13225.571482829941</v>
       </c>
       <c r="H256">
-        <v>41655.840535244497</v>
+        <v>12291.96457950846</v>
       </c>
       <c r="I256">
-        <v>47729.20723662855</v>
+        <v>14239.06717106818</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257">
-        <v>379</v>
+        <v>274</v>
       </c>
       <c r="B257" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C257" s="2">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="D257">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E257" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F257" t="s">
         <v>79</v>
       </c>
       <c r="G257">
-        <v>12996.26184424147</v>
+        <v>45738.105032354877</v>
       </c>
       <c r="H257">
-        <v>12124.33403356571</v>
+        <v>42509.404430759962</v>
       </c>
       <c r="I257">
-        <v>13942.80055708834</v>
+        <v>49243.085690367268</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258">
-        <v>274</v>
+        <v>379</v>
       </c>
       <c r="B258" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C258" s="2">
-        <v>47118</v>
+        <v>47664</v>
       </c>
       <c r="D258">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="E258" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F258" t="s">
         <v>79</v>
       </c>
       <c r="G258">
-        <v>44945.081581662613</v>
+        <v>13345.297397789929</v>
       </c>
       <c r="H258">
-        <v>41929.68630463483</v>
+        <v>12379.882095258199</v>
       </c>
       <c r="I258">
-        <v>48218.50436884314</v>
+        <v>14393.32333139659</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259">
-        <v>379</v>
+        <v>274</v>
       </c>
       <c r="B259" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C259" s="2">
-        <v>47299</v>
+        <v>47664</v>
       </c>
       <c r="D259">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E259" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F259" t="s">
         <v>79</v>
       </c>
       <c r="G259">
-        <v>13109.17611451162</v>
+        <v>46152.154170469177</v>
       </c>
       <c r="H259">
-        <v>12206.729246246599</v>
+        <v>42813.450314506154</v>
       </c>
       <c r="I259">
-        <v>14088.84540208515</v>
+        <v>49776.551066298169</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260">
-        <v>274</v>
+        <v>379</v>
       </c>
       <c r="B260" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C260" s="2">
-        <v>47299</v>
+        <v>47848</v>
       </c>
       <c r="D260">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E260" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F260" t="s">
         <v>79</v>
       </c>
       <c r="G260">
-        <v>45335.573951687817</v>
+        <v>13468.320131950481</v>
       </c>
       <c r="H260">
-        <v>42214.634361257893</v>
+        <v>12470.433077688849</v>
       </c>
       <c r="I260">
-        <v>48723.572483938951</v>
+        <v>14551.59642655029</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261">
-        <v>379</v>
+        <v>274</v>
       </c>
       <c r="B261" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C261" s="2">
-        <v>47483</v>
+        <v>47848</v>
       </c>
       <c r="D261">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E261" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F261" t="s">
         <v>79</v>
       </c>
       <c r="G261">
-        <v>13225.571482829941</v>
+        <v>46577.604726137601</v>
       </c>
       <c r="H261">
-        <v>12291.96457950846</v>
+        <v>43126.603538211682</v>
       </c>
       <c r="I261">
-        <v>14239.06717106818</v>
+        <v>50323.908241701443</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262">
-        <v>274</v>
+        <v>14</v>
       </c>
       <c r="B262" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="C262" s="2">
-        <v>47483</v>
+        <v>46203</v>
       </c>
       <c r="D262">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="E262" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F262" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G262">
-        <v>45738.105032354877</v>
+        <v>55835.706386265258</v>
       </c>
       <c r="H262">
-        <v>42509.404430759962</v>
+        <v>52578.2676864573</v>
       </c>
       <c r="I262">
-        <v>49243.085690367268</v>
+        <v>59371.884262853768</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263">
-        <v>379</v>
+        <v>14</v>
       </c>
       <c r="B263" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="C263" s="2">
-        <v>47664</v>
+        <v>46387</v>
       </c>
       <c r="D263">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="E263" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F263" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G263">
-        <v>13345.297397789929</v>
+        <v>56158.185581577738</v>
       </c>
       <c r="H263">
-        <v>12379.882095258199</v>
+        <v>52783.645979057183</v>
       </c>
       <c r="I263">
-        <v>14393.32333139659</v>
+        <v>59821.484690416968</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264">
-        <v>274</v>
+        <v>14</v>
       </c>
       <c r="B264" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="C264" s="2">
-        <v>47664</v>
+        <v>46568</v>
       </c>
       <c r="D264">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="E264" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F264" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G264">
-        <v>46152.154170469177</v>
+        <v>56552.414542606661</v>
       </c>
       <c r="H264">
-        <v>42813.450314506154</v>
+        <v>53055.208225026639</v>
       </c>
       <c r="I264">
-        <v>49776.551066298169</v>
+        <v>60348.876962857597</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265">
-        <v>379</v>
+        <v>14</v>
       </c>
       <c r="B265" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="C265" s="2">
-        <v>47848</v>
+        <v>46752</v>
       </c>
       <c r="D265">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="E265" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F265" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G265">
-        <v>13468.320131950481</v>
+        <v>56989.568641509853</v>
       </c>
       <c r="H265">
-        <v>12470.433077688849</v>
+        <v>53365.586035246437</v>
       </c>
       <c r="I265">
-        <v>14551.59642655029</v>
+        <v>60923.655603197178</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266">
-        <v>274</v>
+        <v>14</v>
       </c>
       <c r="B266" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="C266" s="2">
-        <v>47848</v>
+        <v>46934</v>
       </c>
       <c r="D266">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="E266" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F266" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G266">
-        <v>46577.604726137601</v>
+        <v>57454.948877856034</v>
       </c>
       <c r="H266">
-        <v>43126.603538211682</v>
+        <v>53700.815467300577</v>
       </c>
       <c r="I266">
-        <v>50323.908241701443</v>
+        <v>61530.323654041553</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.3">
@@ -8448,25 +8455,25 @@
         <v>9</v>
       </c>
       <c r="C267" s="2">
-        <v>46203</v>
+        <v>47118</v>
       </c>
       <c r="D267">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="E267" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F267" t="s">
         <v>11</v>
       </c>
       <c r="G267">
-        <v>55835.706386265258</v>
+        <v>57941.155457840963</v>
       </c>
       <c r="H267">
-        <v>52578.2676864573</v>
+        <v>54053.844981039212</v>
       </c>
       <c r="I267">
-        <v>59371.884262853768</v>
+        <v>62161.103267851133</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.3">
@@ -8477,25 +8484,25 @@
         <v>9</v>
       </c>
       <c r="C268" s="2">
-        <v>46387</v>
+        <v>47299</v>
       </c>
       <c r="D268">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="E268" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F268" t="s">
         <v>11</v>
       </c>
       <c r="G268">
-        <v>56158.185581577738</v>
+        <v>58444.560465030037</v>
       </c>
       <c r="H268">
-        <v>52783.645979057183</v>
+        <v>54421.187058641372</v>
       </c>
       <c r="I268">
-        <v>59821.484690416968</v>
+        <v>62812.214115662013</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.3">
@@ -8506,25 +8513,25 @@
         <v>9</v>
       </c>
       <c r="C269" s="2">
-        <v>46568</v>
+        <v>47483</v>
       </c>
       <c r="D269">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="E269" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F269" t="s">
         <v>11</v>
       </c>
       <c r="G269">
-        <v>56552.414542606661</v>
+        <v>58963.4852305612</v>
       </c>
       <c r="H269">
-        <v>53055.208225026639</v>
+        <v>54801.19122862615</v>
       </c>
       <c r="I269">
-        <v>60348.876962857597</v>
+        <v>63481.946918379748</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.3">
@@ -8535,25 +8542,25 @@
         <v>9</v>
       </c>
       <c r="C270" s="2">
-        <v>46752</v>
+        <v>47664</v>
       </c>
       <c r="D270">
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="E270" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F270" t="s">
         <v>11</v>
       </c>
       <c r="G270">
-        <v>56989.568641509853</v>
+        <v>59497.258552010768</v>
       </c>
       <c r="H270">
-        <v>53365.586035246437</v>
+        <v>55193.15335654989</v>
       </c>
       <c r="I270">
-        <v>60923.655603197178</v>
+        <v>64169.666223595093</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.3">
@@ -8564,25 +8571,25 @@
         <v>9</v>
       </c>
       <c r="C271" s="2">
-        <v>46934</v>
+        <v>47848</v>
       </c>
       <c r="D271">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="E271" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F271" t="s">
         <v>11</v>
       </c>
       <c r="G271">
-        <v>57454.948877856034</v>
+        <v>60045.730062532319</v>
       </c>
       <c r="H271">
-        <v>53700.815467300577</v>
+        <v>55596.85625302542</v>
       </c>
       <c r="I271">
-        <v>61530.323654041553</v>
+        <v>64875.294205010192</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.3">
@@ -8593,25 +8600,25 @@
         <v>9</v>
       </c>
       <c r="C272" s="2">
-        <v>47118</v>
+        <v>46203</v>
       </c>
       <c r="D272">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="E272" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F272" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G272">
-        <v>57941.155457840963</v>
+        <v>57181.535034514192</v>
       </c>
       <c r="H272">
-        <v>54053.844981039212</v>
+        <v>53845.581086922153</v>
       </c>
       <c r="I272">
-        <v>62161.103267851133</v>
+        <v>60802.946712188583</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.3">
@@ -8622,25 +8629,25 @@
         <v>9</v>
       </c>
       <c r="C273" s="2">
-        <v>47299</v>
+        <v>46387</v>
       </c>
       <c r="D273">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="E273" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F273" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G273">
-        <v>58444.560465030037</v>
+        <v>57651.823600328113</v>
       </c>
       <c r="H273">
-        <v>54421.187058641372</v>
+        <v>54187.531442700827</v>
       </c>
       <c r="I273">
-        <v>62812.214115662013</v>
+        <v>61412.55539447139</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.3">
@@ -8651,25 +8658,25 @@
         <v>9</v>
       </c>
       <c r="C274" s="2">
-        <v>47483</v>
+        <v>46568</v>
       </c>
       <c r="D274">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="E274" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F274" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G274">
-        <v>58963.4852305612</v>
+        <v>58122.112166142033</v>
       </c>
       <c r="H274">
-        <v>54801.19122862615</v>
+        <v>54527.835608677153</v>
       </c>
       <c r="I274">
-        <v>63481.946918379748</v>
+        <v>62023.951131092377</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.3">
@@ -8680,25 +8687,25 @@
         <v>9</v>
       </c>
       <c r="C275" s="2">
-        <v>47664</v>
+        <v>46752</v>
       </c>
       <c r="D275">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="E275" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F275" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G275">
-        <v>59497.258552010768</v>
+        <v>58592.400731955953</v>
       </c>
       <c r="H275">
-        <v>55193.15335654989</v>
+        <v>54866.493584851087</v>
       </c>
       <c r="I275">
-        <v>64169.666223595093</v>
+        <v>62637.133922051551</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.3">
@@ -8709,25 +8716,25 @@
         <v>9</v>
       </c>
       <c r="C276" s="2">
-        <v>47848</v>
+        <v>46934</v>
       </c>
       <c r="D276">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="E276" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F276" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G276">
-        <v>60045.730062532319</v>
+        <v>59062.689297769859</v>
       </c>
       <c r="H276">
-        <v>55596.85625302542</v>
+        <v>55203.505371222651</v>
       </c>
       <c r="I276">
-        <v>64875.294205010192</v>
+        <v>63252.103767348883</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.3">
@@ -8738,25 +8745,25 @@
         <v>9</v>
       </c>
       <c r="C277" s="2">
-        <v>46203</v>
+        <v>47118</v>
       </c>
       <c r="D277">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="E277" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F277" t="s">
         <v>37</v>
       </c>
       <c r="G277">
-        <v>57181.535034514192</v>
+        <v>59532.977863583779</v>
       </c>
       <c r="H277">
-        <v>53845.581086922153</v>
+        <v>55538.870967791838</v>
       </c>
       <c r="I277">
-        <v>60802.946712188583</v>
+        <v>63868.860666984387</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.3">
@@ -8767,25 +8774,25 @@
         <v>9</v>
       </c>
       <c r="C278" s="2">
-        <v>46387</v>
+        <v>47299</v>
       </c>
       <c r="D278">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="E278" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F278" t="s">
         <v>37</v>
       </c>
       <c r="G278">
-        <v>57651.823600328113</v>
+        <v>60003.2664293977</v>
       </c>
       <c r="H278">
-        <v>54187.531442700827</v>
+        <v>55872.590374558647</v>
       </c>
       <c r="I278">
-        <v>61412.55539447139</v>
+        <v>64487.404620958077</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.3">
@@ -8796,25 +8803,25 @@
         <v>9</v>
       </c>
       <c r="C279" s="2">
-        <v>46568</v>
+        <v>47483</v>
       </c>
       <c r="D279">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="E279" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F279" t="s">
         <v>37</v>
       </c>
       <c r="G279">
-        <v>58122.112166142033</v>
+        <v>60473.55499521162</v>
       </c>
       <c r="H279">
-        <v>54527.835608677153</v>
+        <v>56204.663591523087</v>
       </c>
       <c r="I279">
-        <v>62023.951131092377</v>
+        <v>65107.735629269962</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.3">
@@ -8825,25 +8832,25 @@
         <v>9</v>
       </c>
       <c r="C280" s="2">
-        <v>46752</v>
+        <v>47664</v>
       </c>
       <c r="D280">
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="E280" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F280" t="s">
         <v>37</v>
       </c>
       <c r="G280">
-        <v>58592.400731955953</v>
+        <v>60943.84356102554</v>
       </c>
       <c r="H280">
-        <v>54866.493584851087</v>
+        <v>56535.090618685143</v>
       </c>
       <c r="I280">
-        <v>62637.133922051551</v>
+        <v>65729.853691919998</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.3">
@@ -8854,3049 +8861,3049 @@
         <v>9</v>
       </c>
       <c r="C281" s="2">
-        <v>46934</v>
+        <v>47848</v>
       </c>
       <c r="D281">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="E281" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F281" t="s">
         <v>37</v>
       </c>
       <c r="G281">
-        <v>59062.689297769859</v>
+        <v>61414.13212683946</v>
       </c>
       <c r="H281">
-        <v>55203.505371222651</v>
+        <v>56863.871456044813</v>
       </c>
       <c r="I281">
-        <v>63252.103767348883</v>
+        <v>66353.758808908198</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282">
-        <v>14</v>
+        <v>379</v>
       </c>
       <c r="B282" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="C282" s="2">
-        <v>47118</v>
+        <v>46203</v>
       </c>
       <c r="D282">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="E282" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F282" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="G282">
-        <v>59532.977863583779</v>
+        <v>12825.87818782696</v>
       </c>
       <c r="H282">
-        <v>55538.870967791838</v>
+        <v>12077.620224024649</v>
       </c>
       <c r="I282">
-        <v>63868.860666984387</v>
+        <v>13638.16461941349</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283">
-        <v>14</v>
+        <v>274</v>
       </c>
       <c r="B283" t="s">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="C283" s="2">
-        <v>47299</v>
+        <v>46203</v>
       </c>
       <c r="D283">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="E283" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F283" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="G283">
-        <v>60003.2664293977</v>
+        <v>44355.842350450519</v>
       </c>
       <c r="H283">
-        <v>55872.590374558647</v>
+        <v>41768.135544425757</v>
       </c>
       <c r="I283">
-        <v>64487.404620958077</v>
+        <v>47164.979344832544</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284">
-        <v>14</v>
+        <v>379</v>
       </c>
       <c r="B284" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="C284" s="2">
-        <v>47483</v>
+        <v>46387</v>
       </c>
       <c r="D284">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="E284" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F284" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="G284">
-        <v>60473.55499521162</v>
+        <v>12931.36440561766</v>
       </c>
       <c r="H284">
-        <v>56204.663591523087</v>
+        <v>12154.320046910731</v>
       </c>
       <c r="I284">
-        <v>65107.735629269962</v>
+        <v>13774.90048522195</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285">
-        <v>14</v>
+        <v>274</v>
       </c>
       <c r="B285" t="s">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="C285" s="2">
-        <v>47664</v>
+        <v>46387</v>
       </c>
       <c r="D285">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="E285" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F285" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="G285">
-        <v>60943.84356102554</v>
+        <v>44720.646224146301</v>
       </c>
       <c r="H285">
-        <v>56535.090618685143</v>
+        <v>42033.387186646367</v>
       </c>
       <c r="I285">
-        <v>65729.853691919998</v>
+        <v>47637.854138950643</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286">
-        <v>14</v>
+        <v>379</v>
       </c>
       <c r="B286" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="C286" s="2">
-        <v>47848</v>
+        <v>46568</v>
       </c>
       <c r="D286">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="E286" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F286" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="G286">
-        <v>61414.13212683946</v>
+        <v>13036.850623408351</v>
       </c>
       <c r="H286">
-        <v>56863.871456044813</v>
+        <v>12230.650627700281</v>
       </c>
       <c r="I286">
-        <v>66353.758808908198</v>
+        <v>13912.037189189839</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287">
-        <v>379</v>
+        <v>274</v>
       </c>
       <c r="B287" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C287" s="2">
-        <v>46203</v>
+        <v>46568</v>
       </c>
       <c r="D287">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E287" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F287" t="s">
         <v>81</v>
       </c>
       <c r="G287">
-        <v>12825.87818782696</v>
+        <v>45085.450097842077</v>
       </c>
       <c r="H287">
-        <v>12077.620224024649</v>
+        <v>42297.361875820701</v>
       </c>
       <c r="I287">
-        <v>13638.16461941349</v>
+        <v>48112.115155044899</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288">
-        <v>274</v>
+        <v>379</v>
       </c>
       <c r="B288" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C288" s="2">
-        <v>46203</v>
+        <v>46752</v>
       </c>
       <c r="D288">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E288" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F288" t="s">
         <v>81</v>
       </c>
       <c r="G288">
-        <v>44355.842350450519</v>
+        <v>13142.33684119905</v>
       </c>
       <c r="H288">
-        <v>41768.135544425757</v>
+        <v>12306.61196639329</v>
       </c>
       <c r="I288">
-        <v>47164.979344832544</v>
+        <v>14049.574731317151</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289">
-        <v>379</v>
+        <v>274</v>
       </c>
       <c r="B289" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C289" s="2">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="D289">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E289" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F289" t="s">
         <v>81</v>
       </c>
       <c r="G289">
-        <v>12931.36440561766</v>
+        <v>45450.253971537859</v>
       </c>
       <c r="H289">
-        <v>12154.320046910731</v>
+        <v>42560.059611948753</v>
       </c>
       <c r="I289">
-        <v>13774.90048522195</v>
+        <v>48587.762393115328</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290">
-        <v>274</v>
+        <v>379</v>
       </c>
       <c r="B290" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C290" s="2">
-        <v>46387</v>
+        <v>46934</v>
       </c>
       <c r="D290">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="E290" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F290" t="s">
         <v>81</v>
       </c>
       <c r="G290">
-        <v>44720.646224146301</v>
+        <v>13247.82305898975</v>
       </c>
       <c r="H290">
-        <v>42033.387186646367</v>
+        <v>12382.20406298976</v>
       </c>
       <c r="I290">
-        <v>47637.854138950643</v>
+        <v>14187.513111603899</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291">
-        <v>379</v>
+        <v>274</v>
       </c>
       <c r="B291" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C291" s="2">
-        <v>46568</v>
+        <v>46934</v>
       </c>
       <c r="D291">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E291" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F291" t="s">
         <v>81</v>
       </c>
       <c r="G291">
-        <v>13036.850623408351</v>
+        <v>45815.057845233627</v>
       </c>
       <c r="H291">
-        <v>12230.650627700281</v>
+        <v>42821.480395030529</v>
       </c>
       <c r="I291">
-        <v>13912.037189189839</v>
+        <v>49064.795853161922</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292">
-        <v>274</v>
+        <v>379</v>
       </c>
       <c r="B292" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C292" s="2">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="D292">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E292" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F292" t="s">
         <v>81</v>
       </c>
       <c r="G292">
-        <v>45085.450097842077</v>
+        <v>13353.30927678045</v>
       </c>
       <c r="H292">
-        <v>42297.361875820701</v>
+        <v>12457.4269174897</v>
       </c>
       <c r="I292">
-        <v>48112.115155044899</v>
+        <v>14325.85233005006</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293">
-        <v>379</v>
+        <v>274</v>
       </c>
       <c r="B293" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C293" s="2">
-        <v>46752</v>
+        <v>47118</v>
       </c>
       <c r="D293">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E293" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F293" t="s">
         <v>81</v>
       </c>
       <c r="G293">
-        <v>13142.33684119905</v>
+        <v>46179.861718929409</v>
       </c>
       <c r="H293">
-        <v>12306.61196639329</v>
+        <v>43081.624225066029</v>
       </c>
       <c r="I293">
-        <v>14049.574731317151</v>
+        <v>49543.215535184667</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294">
-        <v>274</v>
+        <v>379</v>
       </c>
       <c r="B294" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C294" s="2">
-        <v>46752</v>
+        <v>47299</v>
       </c>
       <c r="D294">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="E294" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F294" t="s">
         <v>81</v>
       </c>
       <c r="G294">
-        <v>45450.253971537859</v>
+        <v>13458.795494571141</v>
       </c>
       <c r="H294">
-        <v>42560.059611948753</v>
+        <v>12532.2805298931</v>
       </c>
       <c r="I294">
-        <v>48587.762393115328</v>
+        <v>14464.59238665566</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295">
-        <v>379</v>
+        <v>274</v>
       </c>
       <c r="B295" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C295" s="2">
-        <v>46934</v>
+        <v>47299</v>
       </c>
       <c r="D295">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E295" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F295" t="s">
         <v>81</v>
       </c>
       <c r="G295">
-        <v>13247.82305898975</v>
+        <v>46544.665592625191</v>
       </c>
       <c r="H295">
-        <v>12382.20406298976</v>
+        <v>43340.491102055254</v>
       </c>
       <c r="I295">
-        <v>14187.513111603899</v>
+        <v>50023.021439183598</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296">
-        <v>274</v>
+        <v>379</v>
       </c>
       <c r="B296" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C296" s="2">
-        <v>46934</v>
+        <v>47483</v>
       </c>
       <c r="D296">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E296" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F296" t="s">
         <v>81</v>
       </c>
       <c r="G296">
-        <v>45815.057845233627</v>
+        <v>13564.281712361841</v>
       </c>
       <c r="H296">
-        <v>42821.480395030529</v>
+        <v>12606.764900199971</v>
       </c>
       <c r="I296">
-        <v>49064.795853161922</v>
+        <v>14603.73328142068</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297">
-        <v>379</v>
+        <v>274</v>
       </c>
       <c r="B297" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C297" s="2">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="D297">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E297" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F297" t="s">
         <v>81</v>
       </c>
       <c r="G297">
-        <v>13353.30927678045</v>
+        <v>46909.469466320967</v>
       </c>
       <c r="H297">
-        <v>12457.4269174897</v>
+        <v>43598.081025998203</v>
       </c>
       <c r="I297">
-        <v>14325.85233005006</v>
+        <v>50504.213565158687</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298">
-        <v>274</v>
+        <v>379</v>
       </c>
       <c r="B298" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C298" s="2">
-        <v>47118</v>
+        <v>47664</v>
       </c>
       <c r="D298">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="E298" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F298" t="s">
         <v>81</v>
       </c>
       <c r="G298">
-        <v>46179.861718929409</v>
+        <v>13669.76793015254</v>
       </c>
       <c r="H298">
-        <v>43081.624225066029</v>
+        <v>12680.880028410291</v>
       </c>
       <c r="I298">
-        <v>49543.215535184667</v>
+        <v>14743.275014345139</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299">
-        <v>379</v>
+        <v>274</v>
       </c>
       <c r="B299" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C299" s="2">
-        <v>47299</v>
+        <v>47664</v>
       </c>
       <c r="D299">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E299" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F299" t="s">
         <v>81</v>
       </c>
       <c r="G299">
-        <v>13458.795494571141</v>
+        <v>47274.273340016749</v>
       </c>
       <c r="H299">
-        <v>12532.2805298931</v>
+        <v>43854.393996894862</v>
       </c>
       <c r="I299">
-        <v>14464.59238665566</v>
+        <v>50986.791913109962</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300">
-        <v>274</v>
+        <v>379</v>
       </c>
       <c r="B300" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C300" s="2">
-        <v>47299</v>
+        <v>47848</v>
       </c>
       <c r="D300">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E300" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F300" t="s">
         <v>81</v>
       </c>
       <c r="G300">
-        <v>46544.665592625191</v>
+        <v>13775.25414794324</v>
       </c>
       <c r="H300">
-        <v>43340.491102055254</v>
+        <v>12754.62591452408</v>
       </c>
       <c r="I300">
-        <v>50023.021439183598</v>
+        <v>14883.217585429011</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301">
-        <v>379</v>
+        <v>274</v>
       </c>
       <c r="B301" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C301" s="2">
-        <v>47483</v>
+        <v>47848</v>
       </c>
       <c r="D301">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E301" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F301" t="s">
         <v>81</v>
       </c>
       <c r="G301">
-        <v>13564.281712361841</v>
+        <v>47639.077213712531</v>
       </c>
       <c r="H301">
-        <v>12606.764900199971</v>
+        <v>44109.430014745238</v>
       </c>
       <c r="I301">
-        <v>14603.73328142068</v>
+        <v>51470.756483037367</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302">
-        <v>274</v>
+        <v>14.1</v>
       </c>
       <c r="B302" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C302" s="2">
-        <v>47483</v>
+        <v>46203</v>
       </c>
       <c r="D302">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="E302" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F302" t="s">
         <v>81</v>
       </c>
       <c r="G302">
-        <v>46909.469466320967</v>
+        <v>8922.1224131696708</v>
       </c>
       <c r="H302">
-        <v>43598.081025998203</v>
+        <v>8401.6084139014165</v>
       </c>
       <c r="I302">
-        <v>50504.213565158687</v>
+        <v>9487.176818882821</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303">
-        <v>379</v>
+        <v>14.2</v>
       </c>
       <c r="B303" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C303" s="2">
-        <v>47664</v>
+        <v>46203</v>
       </c>
       <c r="D303">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="E303" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F303" t="s">
         <v>81</v>
       </c>
       <c r="G303">
-        <v>13669.76793015254</v>
+        <v>48259.41262134452</v>
       </c>
       <c r="H303">
-        <v>12680.880028410291</v>
+        <v>45443.972673020733</v>
       </c>
       <c r="I303">
-        <v>14743.275014345139</v>
+        <v>51315.769893305762</v>
       </c>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304">
-        <v>274</v>
+        <v>14.1</v>
       </c>
       <c r="B304" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C304" s="2">
-        <v>47664</v>
+        <v>46387</v>
       </c>
       <c r="D304">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="E304" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F304" t="s">
         <v>81</v>
       </c>
       <c r="G304">
-        <v>47274.273340016749</v>
+        <v>8995.5022577501495</v>
       </c>
       <c r="H304">
-        <v>43854.393996894862</v>
+        <v>8454.9634511812455</v>
       </c>
       <c r="I304">
-        <v>50986.791913109962</v>
+        <v>9582.2949944297943</v>
       </c>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305">
-        <v>379</v>
+        <v>14.2</v>
       </c>
       <c r="B305" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C305" s="2">
-        <v>47848</v>
+        <v>46387</v>
       </c>
       <c r="D305">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="E305" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F305" t="s">
         <v>81</v>
       </c>
       <c r="G305">
-        <v>13775.25414794324</v>
+        <v>48656.321342577961</v>
       </c>
       <c r="H305">
-        <v>12754.62591452408</v>
+        <v>45732.567991519587</v>
       </c>
       <c r="I305">
-        <v>14883.217585429011</v>
+        <v>51830.260400041603</v>
       </c>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306">
-        <v>274</v>
+        <v>14.1</v>
       </c>
       <c r="B306" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C306" s="2">
-        <v>47848</v>
+        <v>46568</v>
       </c>
       <c r="D306">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="E306" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F306" t="s">
         <v>81</v>
       </c>
       <c r="G306">
-        <v>47639.077213712531</v>
+        <v>9068.8821023306264</v>
       </c>
       <c r="H306">
-        <v>44109.430014745238</v>
+        <v>8508.0616309471388</v>
       </c>
       <c r="I306">
-        <v>51470.756483037367</v>
+        <v>9677.6920067997835</v>
       </c>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="B307" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C307" s="2">
-        <v>46203</v>
+        <v>46568</v>
       </c>
       <c r="D307">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E307" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F307" t="s">
         <v>81</v>
       </c>
       <c r="G307">
-        <v>8922.1224131696708</v>
+        <v>49053.23006381141</v>
       </c>
       <c r="H307">
-        <v>8401.6084139014165</v>
+        <v>46019.773977730023</v>
       </c>
       <c r="I307">
-        <v>9487.176818882821</v>
+        <v>52346.259124292606</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A308">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="B308" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C308" s="2">
-        <v>46203</v>
+        <v>46752</v>
       </c>
       <c r="D308">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E308" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F308" t="s">
         <v>81</v>
       </c>
       <c r="G308">
-        <v>48259.41262134452</v>
+        <v>9142.261946911105</v>
       </c>
       <c r="H308">
-        <v>45443.972673020733</v>
+        <v>8560.9029531990927</v>
       </c>
       <c r="I308">
-        <v>51315.769893305762</v>
+        <v>9773.3678559927885</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="B309" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C309" s="2">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="D309">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E309" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F309" t="s">
         <v>81</v>
       </c>
       <c r="G309">
-        <v>8995.5022577501495</v>
+        <v>49450.138785044852</v>
       </c>
       <c r="H309">
-        <v>8454.9634511812455</v>
+        <v>46305.590631651998</v>
       </c>
       <c r="I309">
-        <v>9582.2949944297943</v>
+        <v>52863.766066058772</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="B310" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C310" s="2">
-        <v>46387</v>
+        <v>46934</v>
       </c>
       <c r="D310">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="E310" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F310" t="s">
         <v>81</v>
       </c>
       <c r="G310">
-        <v>48656.321342577961</v>
+        <v>9215.6417914915819</v>
       </c>
       <c r="H310">
-        <v>45732.567991519587</v>
+        <v>8613.4874179371091</v>
       </c>
       <c r="I310">
-        <v>51830.260400041603</v>
+        <v>9869.3225420088074</v>
       </c>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="B311" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C311" s="2">
-        <v>46568</v>
+        <v>46934</v>
       </c>
       <c r="D311">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E311" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F311" t="s">
         <v>81</v>
       </c>
       <c r="G311">
-        <v>9068.8821023306264</v>
+        <v>49847.047506278293</v>
       </c>
       <c r="H311">
-        <v>8508.0616309471388</v>
+        <v>46590.017953285547</v>
       </c>
       <c r="I311">
-        <v>9677.6920067997835</v>
+        <v>53382.781225340077</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="B312" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C312" s="2">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="D312">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E312" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F312" t="s">
         <v>81</v>
       </c>
       <c r="G312">
-        <v>49053.23006381141</v>
+        <v>9289.0216360720588</v>
       </c>
       <c r="H312">
-        <v>46019.773977730023</v>
+        <v>8665.8150251611878</v>
       </c>
       <c r="I312">
-        <v>52346.259124292606</v>
+        <v>9965.556064847844</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A313">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="B313" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C313" s="2">
-        <v>46752</v>
+        <v>47118</v>
       </c>
       <c r="D313">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E313" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F313" t="s">
         <v>81</v>
       </c>
       <c r="G313">
-        <v>9142.261946911105</v>
+        <v>50243.956227511728</v>
       </c>
       <c r="H313">
-        <v>8560.9029531990927</v>
+        <v>46873.055942630657</v>
       </c>
       <c r="I313">
-        <v>9773.3678559927885</v>
+        <v>53903.304602136559</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A314">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="B314" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C314" s="2">
-        <v>46752</v>
+        <v>47299</v>
       </c>
       <c r="D314">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="E314" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F314" t="s">
         <v>81</v>
       </c>
       <c r="G314">
-        <v>49450.138785044852</v>
+        <v>9362.4014806525374</v>
       </c>
       <c r="H314">
-        <v>46305.590631651998</v>
+        <v>8717.885774871329</v>
       </c>
       <c r="I314">
-        <v>52863.766066058772</v>
+        <v>10062.0684245099</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A315">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="B315" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C315" s="2">
-        <v>46934</v>
+        <v>47299</v>
       </c>
       <c r="D315">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E315" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F315" t="s">
         <v>81</v>
       </c>
       <c r="G315">
-        <v>9215.6417914915819</v>
+        <v>50640.864948745169</v>
       </c>
       <c r="H315">
-        <v>8613.4874179371091</v>
+        <v>47154.704599687328</v>
       </c>
       <c r="I315">
-        <v>9869.3225420088074</v>
+        <v>54425.336196448203</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A316">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="B316" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C316" s="2">
-        <v>46934</v>
+        <v>47483</v>
       </c>
       <c r="D316">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E316" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F316" t="s">
         <v>81</v>
       </c>
       <c r="G316">
-        <v>49847.047506278293</v>
+        <v>9435.7813252330143</v>
       </c>
       <c r="H316">
-        <v>46590.017953285547</v>
+        <v>8769.6996670675326</v>
       </c>
       <c r="I316">
-        <v>53382.781225340077</v>
+        <v>10158.859620994959</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A317">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="B317" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C317" s="2">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="D317">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E317" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F317" t="s">
         <v>81</v>
       </c>
       <c r="G317">
-        <v>9289.0216360720588</v>
+        <v>51037.773669978611</v>
       </c>
       <c r="H317">
-        <v>8665.8150251611878</v>
+        <v>47434.963924455573</v>
       </c>
       <c r="I317">
-        <v>9965.556064847844</v>
+        <v>54948.876008275001</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A318">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="B318" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C318" s="2">
-        <v>47118</v>
+        <v>47664</v>
       </c>
       <c r="D318">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="E318" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F318" t="s">
         <v>81</v>
       </c>
       <c r="G318">
-        <v>50243.956227511728</v>
+        <v>9509.161169813493</v>
       </c>
       <c r="H318">
-        <v>46873.055942630657</v>
+        <v>8821.2567017497968</v>
       </c>
       <c r="I318">
-        <v>53903.304602136559</v>
+        <v>10255.92965430305</v>
       </c>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A319">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="B319" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C319" s="2">
-        <v>47299</v>
+        <v>47664</v>
       </c>
       <c r="D319">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E319" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F319" t="s">
         <v>81</v>
       </c>
       <c r="G319">
-        <v>9362.4014806525374</v>
+        <v>51434.682391212053</v>
       </c>
       <c r="H319">
-        <v>8717.885774871329</v>
+        <v>47713.833916935349</v>
       </c>
       <c r="I319">
-        <v>10062.0684245099</v>
+        <v>55473.924037616962</v>
       </c>
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A320">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="B320" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C320" s="2">
-        <v>47299</v>
+        <v>47848</v>
       </c>
       <c r="D320">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E320" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F320" t="s">
         <v>81</v>
       </c>
       <c r="G320">
-        <v>50640.864948745169</v>
+        <v>9582.5410143939698</v>
       </c>
       <c r="H320">
-        <v>47154.704599687328</v>
+        <v>8872.5568789181234</v>
       </c>
       <c r="I320">
-        <v>54425.336196448203</v>
+        <v>10353.278524434139</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A321">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="B321" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C321" s="2">
-        <v>47483</v>
+        <v>47848</v>
       </c>
       <c r="D321">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E321" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F321" t="s">
         <v>81</v>
       </c>
       <c r="G321">
-        <v>9435.7813252330143</v>
+        <v>51831.591112445501</v>
       </c>
       <c r="H321">
-        <v>8769.6996670675326</v>
+        <v>47991.314577126701</v>
       </c>
       <c r="I321">
-        <v>10158.859620994959</v>
+        <v>56000.480284474063</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A322">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="B322" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C322" s="2">
-        <v>47483</v>
+        <v>46203</v>
       </c>
       <c r="D322">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="E322" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F322" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G322">
-        <v>51037.773669978611</v>
+        <v>8712.1307097363897</v>
       </c>
       <c r="H322">
-        <v>47434.963924455573</v>
+        <v>8203.8675647274158</v>
       </c>
       <c r="I322">
-        <v>54948.876008275001</v>
+        <v>9263.8859550375455</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A323">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="B323" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C323" s="2">
-        <v>47664</v>
+        <v>46203</v>
       </c>
       <c r="D323">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="E323" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F323" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G323">
-        <v>9509.161169813493</v>
+        <v>47123.575676528882</v>
       </c>
       <c r="H323">
-        <v>8821.2567017497968</v>
+        <v>44374.400121729886</v>
       </c>
       <c r="I323">
-        <v>10255.92965430305</v>
+        <v>50107.998307816233</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A324">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="B324" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C324" s="2">
-        <v>47664</v>
+        <v>46387</v>
       </c>
       <c r="D324">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="E324" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F324" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G324">
-        <v>51434.682391212053</v>
+        <v>8762.4476320530375</v>
       </c>
       <c r="H324">
-        <v>47713.833916935349</v>
+        <v>8235.9130540007973</v>
       </c>
       <c r="I324">
-        <v>55473.924037616962</v>
+        <v>9334.0377977488515</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A325">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="B325" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C325" s="2">
-        <v>47848</v>
+        <v>46387</v>
       </c>
       <c r="D325">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="E325" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F325" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G325">
-        <v>9582.5410143939698</v>
+        <v>47395.737949524708</v>
       </c>
       <c r="H325">
-        <v>8872.5568789181234</v>
+        <v>44547.732925056393</v>
       </c>
       <c r="I325">
-        <v>10353.278524434139</v>
+        <v>50487.446892668122</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A326">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="B326" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C326" s="2">
-        <v>47848</v>
+        <v>46568</v>
       </c>
       <c r="D326">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="E326" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F326" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G326">
-        <v>51831.591112445501</v>
+        <v>8823.9597801091131</v>
       </c>
       <c r="H326">
-        <v>47991.314577126701</v>
+        <v>8278.2853267960672</v>
       </c>
       <c r="I326">
-        <v>56000.480284474063</v>
+        <v>9416.3276210569329</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A327">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="B327" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C327" s="2">
-        <v>46203</v>
+        <v>46568</v>
       </c>
       <c r="D327">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E327" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F327" t="s">
         <v>79</v>
       </c>
       <c r="G327">
-        <v>8712.1307097363897</v>
+        <v>47728.454762497553</v>
       </c>
       <c r="H327">
-        <v>8203.8675647274158</v>
+        <v>44776.922898230579</v>
       </c>
       <c r="I327">
-        <v>9263.8859550375455</v>
+        <v>50932.549341800674</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A328">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="B328" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C328" s="2">
-        <v>46203</v>
+        <v>46752</v>
       </c>
       <c r="D328">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E328" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F328" t="s">
         <v>79</v>
       </c>
       <c r="G328">
-        <v>47123.575676528882</v>
+        <v>8892.1696031136707</v>
       </c>
       <c r="H328">
-        <v>44374.400121729886</v>
+        <v>8326.7140514786261</v>
       </c>
       <c r="I328">
-        <v>50107.998307816233</v>
+        <v>9506.0112118610195</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A329">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="B329" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C329" s="2">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="D329">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E329" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F329" t="s">
         <v>79</v>
       </c>
       <c r="G329">
-        <v>8762.4476320530375</v>
+        <v>48097.399038396186</v>
       </c>
       <c r="H329">
-        <v>8235.9130540007973</v>
+        <v>45038.871983767807</v>
       </c>
       <c r="I329">
-        <v>9334.0377977488515</v>
+        <v>51417.644391336173</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A330">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="B330" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C330" s="2">
-        <v>46387</v>
+        <v>46934</v>
       </c>
       <c r="D330">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="E330" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F330" t="s">
         <v>79</v>
       </c>
       <c r="G330">
-        <v>47395.737949524708</v>
+        <v>8964.7835935363528</v>
       </c>
       <c r="H330">
-        <v>44547.732925056393</v>
+        <v>8379.0204127450579</v>
       </c>
       <c r="I330">
-        <v>50487.446892668122</v>
+        <v>9600.6705561847666</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A331">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="B331" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C331" s="2">
-        <v>46568</v>
+        <v>46934</v>
       </c>
       <c r="D331">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E331" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F331" t="s">
         <v>79</v>
       </c>
       <c r="G331">
-        <v>8823.9597801091131</v>
+        <v>48490.165284319693</v>
       </c>
       <c r="H331">
-        <v>8278.2853267960672</v>
+        <v>45321.795054555543</v>
       </c>
       <c r="I331">
-        <v>9416.3276210569329</v>
+        <v>51929.65309785679</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A332">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="B332" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C332" s="2">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="D332">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E332" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F332" t="s">
         <v>79</v>
       </c>
       <c r="G332">
-        <v>47728.454762497553</v>
+        <v>9040.6471502263867</v>
       </c>
       <c r="H332">
-        <v>44776.922898230579</v>
+        <v>8434.1041479951982</v>
       </c>
       <c r="I332">
-        <v>50932.549341800674</v>
+        <v>9699.0920645745646</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A333">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="B333" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C333" s="2">
-        <v>46752</v>
+        <v>47118</v>
       </c>
       <c r="D333">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E333" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F333" t="s">
         <v>79</v>
       </c>
       <c r="G333">
-        <v>8892.1696031136707</v>
+        <v>48900.508307614567</v>
       </c>
       <c r="H333">
-        <v>8326.7140514786261</v>
+        <v>45619.740833044023</v>
       </c>
       <c r="I333">
-        <v>9506.0112118610195</v>
+        <v>52462.011203276568</v>
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A334">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="B334" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C334" s="2">
-        <v>46752</v>
+        <v>47299</v>
       </c>
       <c r="D334">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="E334" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F334" t="s">
         <v>79</v>
       </c>
       <c r="G334">
-        <v>48097.399038396186</v>
+        <v>9119.1942038308862</v>
       </c>
       <c r="H334">
-        <v>45038.871983767807</v>
+        <v>8491.42109448669</v>
       </c>
       <c r="I334">
-        <v>51417.644391336173</v>
+        <v>9800.6858865173472</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A335">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="B335" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C335" s="2">
-        <v>46934</v>
+        <v>47299</v>
       </c>
       <c r="D335">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E335" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F335" t="s">
         <v>79</v>
       </c>
       <c r="G335">
-        <v>8964.7835935363528</v>
+        <v>49325.36626119916</v>
       </c>
       <c r="H335">
-        <v>8379.0204127450579</v>
+        <v>45929.765964154692</v>
       </c>
       <c r="I335">
-        <v>9600.6705561847666</v>
+        <v>53011.528229144671</v>
       </c>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A336">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="B336" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C336" s="2">
-        <v>46934</v>
+        <v>47483</v>
       </c>
       <c r="D336">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E336" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F336" t="s">
         <v>79</v>
       </c>
       <c r="G336">
-        <v>48490.165284319693</v>
+        <v>9200.1628290785266</v>
       </c>
       <c r="H336">
-        <v>45321.795054555543</v>
+        <v>8550.7137266287391</v>
       </c>
       <c r="I336">
-        <v>51929.65309785679</v>
+        <v>9905.1853205803909</v>
       </c>
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A337">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="B337" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C337" s="2">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="D337">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E337" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F337" t="s">
         <v>79</v>
       </c>
       <c r="G337">
-        <v>9040.6471502263867</v>
+        <v>49763.322401482677</v>
       </c>
       <c r="H337">
-        <v>8434.1041479951982</v>
+        <v>46250.477501997419</v>
       </c>
       <c r="I337">
-        <v>9699.0920645745646</v>
+        <v>53576.761597799363</v>
       </c>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A338">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="B338" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C338" s="2">
-        <v>47118</v>
+        <v>47664</v>
       </c>
       <c r="D338">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="E338" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F338" t="s">
         <v>79</v>
       </c>
       <c r="G338">
-        <v>48900.508307614567</v>
+        <v>9283.4482972280384</v>
       </c>
       <c r="H338">
-        <v>45619.740833044023</v>
+        <v>8611.8721772466033</v>
       </c>
       <c r="I338">
-        <v>52462.011203276568</v>
+        <v>10012.491216151881</v>
       </c>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A339">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="B339" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C339" s="2">
-        <v>47299</v>
+        <v>47664</v>
       </c>
       <c r="D339">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E339" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F339" t="s">
         <v>79</v>
       </c>
       <c r="G339">
-        <v>9119.1942038308862</v>
+        <v>50213.810254782737</v>
       </c>
       <c r="H339">
-        <v>8491.42109448669</v>
+        <v>46581.281179303303</v>
       </c>
       <c r="I339">
-        <v>9800.6858865173472</v>
+        <v>54157.175007443213</v>
       </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A340">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="B340" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C340" s="2">
-        <v>47299</v>
+        <v>47848</v>
       </c>
       <c r="D340">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E340" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F340" t="s">
         <v>79</v>
       </c>
       <c r="G340">
-        <v>49325.36626119916</v>
+        <v>9369.0271463102763</v>
       </c>
       <c r="H340">
-        <v>45929.765964154692</v>
+        <v>8674.8625579478521</v>
       </c>
       <c r="I340">
-        <v>53011.528229144671</v>
+        <v>10122.59142987548</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A341">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="B341" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C341" s="2">
-        <v>47483</v>
+        <v>47848</v>
       </c>
       <c r="D341">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E341" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F341" t="s">
         <v>79</v>
       </c>
       <c r="G341">
-        <v>9200.1628290785266</v>
+        <v>50676.70291622205</v>
       </c>
       <c r="H341">
-        <v>8550.7137266287391</v>
+        <v>46921.993695077566</v>
       </c>
       <c r="I341">
-        <v>9905.1853205803909</v>
+        <v>54752.70277513472</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A342">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="B342" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C342" s="2">
-        <v>47483</v>
+        <v>46203</v>
       </c>
       <c r="D342">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="E342" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F342" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G342">
-        <v>49763.322401482677</v>
+        <v>53184.163304725829</v>
       </c>
       <c r="H342">
-        <v>46250.477501997419</v>
+        <v>50081.414848975357</v>
       </c>
       <c r="I342">
-        <v>53576.761597799363</v>
+        <v>56552.414086080753</v>
       </c>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A343">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="B343" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C343" s="2">
-        <v>47664</v>
+        <v>46203</v>
       </c>
       <c r="D343">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="E343" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F343" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G343">
-        <v>9283.4482972280384</v>
+        <v>3997.37172978836</v>
       </c>
       <c r="H343">
-        <v>8611.8721772466033</v>
+        <v>3764.1662379467821</v>
       </c>
       <c r="I343">
-        <v>10012.491216151881</v>
+        <v>4250.5326261078344</v>
       </c>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A344">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="B344" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C344" s="2">
-        <v>47664</v>
+        <v>46387</v>
       </c>
       <c r="D344">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="E344" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F344" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G344">
-        <v>50213.810254782737</v>
+        <v>53621.575554493087</v>
       </c>
       <c r="H344">
-        <v>46581.281179303303</v>
+        <v>50399.460587916547</v>
       </c>
       <c r="I344">
-        <v>54157.175007443213</v>
+        <v>57119.407044400919</v>
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A345">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="B345" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C345" s="2">
-        <v>47848</v>
+        <v>46387</v>
       </c>
       <c r="D345">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="E345" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F345" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G345">
-        <v>9369.0271463102763</v>
+        <v>4030.2480458350101</v>
       </c>
       <c r="H345">
-        <v>8674.8625579478521</v>
+        <v>3788.0708547842928</v>
       </c>
       <c r="I345">
-        <v>10122.59142987548</v>
+        <v>4293.1483500704726</v>
       </c>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A346">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="B346" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C346" s="2">
-        <v>47848</v>
+        <v>46568</v>
       </c>
       <c r="D346">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="E346" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F346" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G346">
-        <v>50676.70291622205</v>
+        <v>54058.987804260367</v>
       </c>
       <c r="H346">
-        <v>46921.993695077566</v>
+        <v>50715.975216732273</v>
       </c>
       <c r="I346">
-        <v>54752.70277513472</v>
+        <v>57688.062130009188</v>
       </c>
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A347">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="B347" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C347" s="2">
-        <v>46203</v>
+        <v>46568</v>
       </c>
       <c r="D347">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E347" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F347" t="s">
         <v>81</v>
       </c>
       <c r="G347">
-        <v>53184.163304725829</v>
+        <v>4063.1243618816602</v>
       </c>
       <c r="H347">
-        <v>50081.414848975357</v>
+        <v>3811.8603919448801</v>
       </c>
       <c r="I347">
-        <v>56552.414086080753</v>
+        <v>4335.8890010831956</v>
       </c>
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A348">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="B348" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C348" s="2">
-        <v>46203</v>
+        <v>46752</v>
       </c>
       <c r="D348">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E348" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F348" t="s">
         <v>81</v>
       </c>
       <c r="G348">
-        <v>3997.37172978836</v>
+        <v>54496.400054027639</v>
       </c>
       <c r="H348">
-        <v>3764.1662379467821</v>
+        <v>51030.958735422559</v>
       </c>
       <c r="I348">
-        <v>4250.5326261078344</v>
+        <v>58258.379342905551</v>
       </c>
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A349">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="B349" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C349" s="2">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="D349">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E349" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F349" t="s">
         <v>81</v>
       </c>
       <c r="G349">
-        <v>53621.575554493087</v>
+        <v>4096.0006779283094</v>
       </c>
       <c r="H349">
-        <v>50399.460587916547</v>
+        <v>3835.5348494285399</v>
       </c>
       <c r="I349">
-        <v>57119.407044400919</v>
+        <v>4378.7545791459988</v>
       </c>
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A350">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="B350" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C350" s="2">
-        <v>46387</v>
+        <v>46934</v>
       </c>
       <c r="D350">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="E350" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F350" t="s">
         <v>81</v>
       </c>
       <c r="G350">
-        <v>4030.2480458350101</v>
+        <v>54933.812303794897</v>
       </c>
       <c r="H350">
-        <v>3788.0708547842928</v>
+        <v>51344.411143987381</v>
       </c>
       <c r="I350">
-        <v>4293.1483500704726</v>
+        <v>58830.358683090002</v>
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A351">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="B351" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C351" s="2">
-        <v>46568</v>
+        <v>46934</v>
       </c>
       <c r="D351">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E351" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F351" t="s">
         <v>81</v>
       </c>
       <c r="G351">
-        <v>54058.987804260367</v>
+        <v>4128.8769939749591</v>
       </c>
       <c r="H351">
-        <v>50715.975216732273</v>
+        <v>3859.094227235275</v>
       </c>
       <c r="I351">
-        <v>57688.062130009188</v>
+        <v>4421.7450842588833</v>
       </c>
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A352">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="B352" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C352" s="2">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="D352">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E352" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F352" t="s">
         <v>81</v>
       </c>
       <c r="G352">
-        <v>4063.1243618816602</v>
+        <v>55371.22455356217</v>
       </c>
       <c r="H352">
-        <v>3811.8603919448801</v>
+        <v>51656.332442426763</v>
       </c>
       <c r="I352">
-        <v>4335.8890010831956</v>
+        <v>59404.000150562548</v>
       </c>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A353">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="B353" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C353" s="2">
-        <v>46752</v>
+        <v>47118</v>
       </c>
       <c r="D353">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E353" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F353" t="s">
         <v>81</v>
       </c>
       <c r="G353">
-        <v>54496.400054027639</v>
+        <v>4161.7533100216096</v>
       </c>
       <c r="H353">
-        <v>51030.958735422559</v>
+        <v>3882.5385253650838</v>
       </c>
       <c r="I353">
-        <v>58258.379342905551</v>
+        <v>4464.8605164218507</v>
       </c>
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A354">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="B354" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C354" s="2">
-        <v>46752</v>
+        <v>47299</v>
       </c>
       <c r="D354">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="E354" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F354" t="s">
         <v>81</v>
       </c>
       <c r="G354">
-        <v>4096.0006779283094</v>
+        <v>55808.636803329442</v>
       </c>
       <c r="H354">
-        <v>3835.5348494285399</v>
+        <v>51966.722630740682</v>
       </c>
       <c r="I354">
-        <v>4378.7545791459988</v>
+        <v>59979.303745323188</v>
       </c>
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A355">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="B355" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C355" s="2">
-        <v>46934</v>
+        <v>47299</v>
       </c>
       <c r="D355">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E355" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F355" t="s">
         <v>81</v>
       </c>
       <c r="G355">
-        <v>54933.812303794897</v>
+        <v>4194.6296260682593</v>
       </c>
       <c r="H355">
-        <v>51344.411143987381</v>
+        <v>3905.867743817967</v>
       </c>
       <c r="I355">
-        <v>58830.358683090002</v>
+        <v>4508.1008756348992</v>
       </c>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A356">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="B356" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C356" s="2">
-        <v>46934</v>
+        <v>47483</v>
       </c>
       <c r="D356">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E356" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F356" t="s">
         <v>81</v>
       </c>
       <c r="G356">
-        <v>4128.8769939749591</v>
+        <v>56246.049053096707</v>
       </c>
       <c r="H356">
-        <v>3859.094227235275</v>
+        <v>52275.581708929167</v>
       </c>
       <c r="I356">
-        <v>4421.7450842588833</v>
+        <v>60556.269467371923</v>
       </c>
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A357">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="B357" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C357" s="2">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="D357">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E357" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F357" t="s">
         <v>81</v>
       </c>
       <c r="G357">
-        <v>55371.22455356217</v>
+        <v>4227.505942114909</v>
       </c>
       <c r="H357">
-        <v>51656.332442426763</v>
+        <v>3929.081882593925</v>
       </c>
       <c r="I357">
-        <v>59404.000150562548</v>
+        <v>4551.4661618980308</v>
       </c>
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A358">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="B358" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C358" s="2">
-        <v>47118</v>
+        <v>47664</v>
       </c>
       <c r="D358">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="E358" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F358" t="s">
         <v>81</v>
       </c>
       <c r="G358">
-        <v>4161.7533100216096</v>
+        <v>56683.461302863987</v>
       </c>
       <c r="H358">
-        <v>3882.5385253650838</v>
+        <v>52582.909676992182</v>
       </c>
       <c r="I358">
-        <v>4464.8605164218507</v>
+        <v>61134.897316708753</v>
       </c>
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A359">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="B359" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C359" s="2">
-        <v>47299</v>
+        <v>47664</v>
       </c>
       <c r="D359">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E359" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F359" t="s">
         <v>81</v>
       </c>
       <c r="G359">
-        <v>55808.636803329442</v>
+        <v>4260.3822581615595</v>
       </c>
       <c r="H359">
-        <v>51966.722630740682</v>
+        <v>3952.1809416929568</v>
       </c>
       <c r="I359">
-        <v>59979.303745323188</v>
+        <v>4594.9563752112444</v>
       </c>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A360">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="B360" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C360" s="2">
-        <v>47299</v>
+        <v>47848</v>
       </c>
       <c r="D360">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E360" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F360" t="s">
         <v>81</v>
       </c>
       <c r="G360">
-        <v>4194.6296260682593</v>
+        <v>57120.873552631252</v>
       </c>
       <c r="H360">
-        <v>3905.867743817967</v>
+        <v>52888.706534929763</v>
       </c>
       <c r="I360">
-        <v>4508.1008756348992</v>
+        <v>61715.187293333664</v>
       </c>
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A361">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="B361" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C361" s="2">
-        <v>47483</v>
+        <v>47848</v>
       </c>
       <c r="D361">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E361" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F361" t="s">
         <v>81</v>
       </c>
       <c r="G361">
-        <v>56246.049053096707</v>
+        <v>4293.2585742082092</v>
       </c>
       <c r="H361">
-        <v>52275.581708929167</v>
+        <v>3975.164921115063</v>
       </c>
       <c r="I361">
-        <v>60556.269467371923</v>
+        <v>4638.5715155745374</v>
       </c>
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A362">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="B362" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C362" s="2">
-        <v>47483</v>
+        <v>46203</v>
       </c>
       <c r="D362">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="E362" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F362" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G362">
-        <v>4227.505942114909</v>
+        <v>51932.417079909617</v>
       </c>
       <c r="H362">
-        <v>3929.081882593925</v>
+        <v>48902.695131012093</v>
       </c>
       <c r="I362">
-        <v>4551.4661618980308</v>
+        <v>55221.39247291936</v>
       </c>
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A363">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="B363" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C363" s="2">
-        <v>47664</v>
+        <v>46203</v>
       </c>
       <c r="D363">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="E363" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F363" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G363">
-        <v>56683.461302863987</v>
+        <v>3903.2893063556498</v>
       </c>
       <c r="H363">
-        <v>52582.909676992182</v>
+        <v>3675.5725554452119</v>
       </c>
       <c r="I363">
-        <v>61134.897316708753</v>
+        <v>4150.4917899344118</v>
       </c>
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A364">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="B364" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C364" s="2">
-        <v>47664</v>
+        <v>46387</v>
       </c>
       <c r="D364">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="E364" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F364" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G364">
-        <v>4260.3822581615595</v>
+        <v>52232.352822724548</v>
       </c>
       <c r="H364">
-        <v>3952.1809416929568</v>
+        <v>49093.716107386463</v>
       </c>
       <c r="I364">
-        <v>4594.9563752112444</v>
+        <v>55639.562823662178</v>
       </c>
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A365">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="B365" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C365" s="2">
-        <v>47848</v>
+        <v>46387</v>
       </c>
       <c r="D365">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="E365" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F365" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G365">
-        <v>57120.873552631252</v>
+        <v>3925.8327588531888</v>
       </c>
       <c r="H365">
-        <v>52888.706534929763</v>
+        <v>3689.929871670729</v>
       </c>
       <c r="I365">
-        <v>61715.187293333664</v>
+        <v>4181.9218667547893</v>
       </c>
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A366">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="B366" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C366" s="2">
-        <v>47848</v>
+        <v>46568</v>
       </c>
       <c r="D366">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="E366" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F366" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G366">
-        <v>4293.2585742082092</v>
+        <v>52599.022542768958</v>
       </c>
       <c r="H366">
-        <v>3975.164921115063</v>
+        <v>49346.294336150691</v>
       </c>
       <c r="I366">
-        <v>4638.5715155745374</v>
+        <v>56130.086849052597</v>
       </c>
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A367">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="B367" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C367" s="2">
-        <v>46203</v>
+        <v>46568</v>
       </c>
       <c r="D367">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E367" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F367" t="s">
         <v>79</v>
       </c>
       <c r="G367">
-        <v>51932.417079909617</v>
+        <v>3953.3919998377082</v>
       </c>
       <c r="H367">
-        <v>48902.695131012093</v>
+        <v>3708.9138888759489</v>
       </c>
       <c r="I367">
-        <v>55221.39247291936</v>
+        <v>4218.7901138050047</v>
       </c>
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A368">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="B368" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C368" s="2">
-        <v>46203</v>
+        <v>46752</v>
       </c>
       <c r="D368">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E368" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F368" t="s">
         <v>79</v>
       </c>
       <c r="G368">
-        <v>3903.2893063556498</v>
+        <v>53005.616646466318</v>
       </c>
       <c r="H368">
-        <v>3675.5725554452119</v>
+        <v>49634.974661625158</v>
       </c>
       <c r="I368">
-        <v>4150.4917899344118</v>
+        <v>56664.68461830516</v>
       </c>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A369">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="B369" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C369" s="2">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="D369">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E369" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F369" t="s">
         <v>79</v>
       </c>
       <c r="G369">
-        <v>52232.352822724548</v>
+        <v>3983.951995043537</v>
       </c>
       <c r="H369">
-        <v>49093.716107386463</v>
+        <v>3730.6113736212851</v>
       </c>
       <c r="I369">
-        <v>55639.562823662178</v>
+        <v>4258.9709848920229</v>
       </c>
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A370">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="B370" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C370" s="2">
-        <v>46387</v>
+        <v>46934</v>
       </c>
       <c r="D370">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="E370" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F370" t="s">
         <v>79</v>
       </c>
       <c r="G370">
-        <v>3925.8327588531888</v>
+        <v>53438.463691822617</v>
       </c>
       <c r="H370">
-        <v>3689.929871670729</v>
+        <v>49946.769314359757</v>
       </c>
       <c r="I370">
-        <v>4181.9218667547893</v>
+        <v>57228.942514991417</v>
       </c>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A371">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="B371" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C371" s="2">
-        <v>46568</v>
+        <v>46934</v>
       </c>
       <c r="D371">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E371" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F371" t="s">
         <v>79</v>
       </c>
       <c r="G371">
-        <v>52599.022542768958</v>
+        <v>4016.4851860334188</v>
       </c>
       <c r="H371">
-        <v>49346.294336150691</v>
+        <v>3754.046152940823</v>
       </c>
       <c r="I371">
-        <v>56130.086849052597</v>
+        <v>4301.3811390501323</v>
       </c>
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A372">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="B372" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C372" s="2">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="D372">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E372" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F372" t="s">
         <v>79</v>
       </c>
       <c r="G372">
-        <v>3953.3919998377082</v>
+        <v>53890.681180110441</v>
       </c>
       <c r="H372">
-        <v>3708.9138888759489</v>
+        <v>50275.119704021919</v>
       </c>
       <c r="I372">
-        <v>4218.7901138050047</v>
+        <v>57815.626415133163</v>
       </c>
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A373">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="B373" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C373" s="2">
-        <v>46752</v>
+        <v>47118</v>
       </c>
       <c r="D373">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E373" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F373" t="s">
         <v>79</v>
       </c>
       <c r="G373">
-        <v>53005.616646466318</v>
+        <v>4050.474277730515</v>
       </c>
       <c r="H373">
-        <v>49634.974661625158</v>
+        <v>3778.7252770172909</v>
       </c>
       <c r="I373">
-        <v>56664.68461830516</v>
+        <v>4345.4768527179676</v>
       </c>
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A374">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="B374" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C374" s="2">
-        <v>46752</v>
+        <v>47299</v>
       </c>
       <c r="D374">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="E374" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F374" t="s">
         <v>79</v>
       </c>
       <c r="G374">
-        <v>3983.951995043537</v>
+        <v>54358.894810517537</v>
       </c>
       <c r="H374">
-        <v>3730.6113736212851</v>
+        <v>50616.782113610927</v>
       </c>
       <c r="I374">
-        <v>4258.9709848920229</v>
+        <v>58421.220260043949</v>
       </c>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A375">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="B375" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C375" s="2">
-        <v>46934</v>
+        <v>47299</v>
       </c>
       <c r="D375">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E375" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F375" t="s">
         <v>79</v>
       </c>
       <c r="G375">
-        <v>53438.463691822617</v>
+        <v>4085.6656545124938</v>
       </c>
       <c r="H375">
-        <v>49946.769314359757</v>
+        <v>3804.404945030441</v>
       </c>
       <c r="I375">
-        <v>57228.942514991417</v>
+        <v>4390.9938556180596</v>
       </c>
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A376">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="B376" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C376" s="2">
-        <v>46934</v>
+        <v>47483</v>
       </c>
       <c r="D376">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E376" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F376" t="s">
         <v>79</v>
       </c>
       <c r="G376">
-        <v>4016.4851860334188</v>
+        <v>54841.543264362263</v>
       </c>
       <c r="H376">
-        <v>3754.046152940823</v>
+        <v>50970.221450640784</v>
       </c>
       <c r="I376">
-        <v>4301.3811390501323</v>
+        <v>59044.134260669722</v>
       </c>
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A377">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="B377" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C377" s="2">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="D377">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E377" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F377" t="s">
         <v>79</v>
       </c>
       <c r="G377">
-        <v>53890.681180110441</v>
+        <v>4121.9419661989377</v>
       </c>
       <c r="H377">
-        <v>50275.119704021919</v>
+        <v>3830.96977798538</v>
       </c>
       <c r="I377">
-        <v>57815.626415133163</v>
+        <v>4437.8126577100284</v>
       </c>
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A378">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="B378" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C378" s="2">
-        <v>47118</v>
+        <v>47664</v>
       </c>
       <c r="D378">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="E378" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F378" t="s">
         <v>79</v>
       </c>
       <c r="G378">
-        <v>4050.474277730515</v>
+        <v>55338.002260759349</v>
       </c>
       <c r="H378">
-        <v>3778.7252770172909</v>
+        <v>51334.782804374663</v>
       </c>
       <c r="I378">
-        <v>4345.4768527179676</v>
+        <v>59683.777386974543</v>
       </c>
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A379">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="B379" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C379" s="2">
-        <v>47299</v>
+        <v>47664</v>
       </c>
       <c r="D379">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E379" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F379" t="s">
         <v>79</v>
       </c>
       <c r="G379">
-        <v>54358.894810517537</v>
+        <v>4159.2562912514186</v>
       </c>
       <c r="H379">
-        <v>50616.782113610927</v>
+        <v>3858.3705521752349</v>
       </c>
       <c r="I379">
-        <v>58421.220260043949</v>
+        <v>4485.8888366205483</v>
       </c>
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A380">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="B380" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C380" s="2">
-        <v>47299</v>
+        <v>47848</v>
       </c>
       <c r="D380">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E380" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F380" t="s">
         <v>79</v>
       </c>
       <c r="G380">
-        <v>4085.6656545124938</v>
+        <v>55848.131944510613</v>
       </c>
       <c r="H380">
-        <v>3804.404945030441</v>
+        <v>51710.264168416143</v>
       </c>
       <c r="I380">
-        <v>4390.9938556180596</v>
+        <v>60340.077253239288</v>
       </c>
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A381">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="B381" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C381" s="2">
-        <v>47483</v>
+        <v>47848</v>
       </c>
       <c r="D381">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E381" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F381" t="s">
         <v>79</v>
       </c>
       <c r="G381">
-        <v>54841.543264362263</v>
+        <v>4197.5981180217186</v>
       </c>
       <c r="H381">
-        <v>50970.221450640784</v>
+        <v>3886.592084609279</v>
       </c>
       <c r="I381">
-        <v>59044.134260669722</v>
+        <v>4535.2169517708999</v>
       </c>
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A382">
-        <v>14.4</v>
+        <v>194</v>
       </c>
       <c r="B382" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="C382" s="2">
-        <v>47483</v>
+        <v>46387</v>
       </c>
       <c r="D382">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="E382" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F382" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="G382">
-        <v>4121.9419661989377</v>
+        <v>90.299279905306122</v>
       </c>
       <c r="H382">
-        <v>3830.96977798538</v>
+        <v>87.590301508146936</v>
       </c>
       <c r="I382">
-        <v>4437.8126577100284</v>
+        <v>93.008258302465308</v>
       </c>
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A383">
-        <v>14.3</v>
+        <v>194</v>
       </c>
       <c r="B383" t="s">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="C383" s="2">
-        <v>47664</v>
+        <v>46752</v>
       </c>
       <c r="D383">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="E383" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F383" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="G383">
-        <v>55338.002260759349</v>
+        <v>91.205371802411875</v>
       </c>
       <c r="H383">
-        <v>51334.782804374663</v>
+        <v>88.469210648339512</v>
       </c>
       <c r="I383">
-        <v>59683.777386974543</v>
+        <v>93.941532956484238</v>
       </c>
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A384">
-        <v>14.4</v>
+        <v>194</v>
       </c>
       <c r="B384" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="C384" s="2">
-        <v>47664</v>
+        <v>47118</v>
       </c>
       <c r="D384">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="E384" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F384" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="G384">
-        <v>4159.2562912514186</v>
+        <v>92.111463699517614</v>
       </c>
       <c r="H384">
-        <v>3858.3705521752349</v>
+        <v>89.348119788532088</v>
       </c>
       <c r="I384">
-        <v>4485.8888366205483</v>
+        <v>94.87480761050314</v>
       </c>
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A385">
-        <v>14.3</v>
+        <v>194</v>
       </c>
       <c r="B385" t="s">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="C385" s="2">
-        <v>47848</v>
+        <v>47483</v>
       </c>
       <c r="D385">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="E385" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F385" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="G385">
-        <v>55848.131944510613</v>
+        <v>93.017555596623353</v>
       </c>
       <c r="H385">
-        <v>51710.264168416143</v>
+        <v>90.22702892872465</v>
       </c>
       <c r="I385">
-        <v>60340.077253239288</v>
+        <v>95.808082264522056</v>
       </c>
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A386">
-        <v>14.4</v>
+        <v>194</v>
       </c>
       <c r="B386" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="C386" s="2">
         <v>47848</v>
@@ -11908,16 +11915,16 @@
         <v>20</v>
       </c>
       <c r="F386" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="G386">
-        <v>4197.5981180217186</v>
+        <v>93.923647493729106</v>
       </c>
       <c r="H386">
-        <v>3886.592084609279</v>
+        <v>91.105938068917226</v>
       </c>
       <c r="I386">
-        <v>4535.2169517708999</v>
+        <v>96.741356918540987</v>
       </c>
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.3">
@@ -11937,16 +11944,16 @@
         <v>12</v>
       </c>
       <c r="F387" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G387">
-        <v>90.299279905306122</v>
+        <v>90.703306625415365</v>
       </c>
       <c r="H387">
-        <v>87.590301508146936</v>
+        <v>87.982207426652906</v>
       </c>
       <c r="I387">
-        <v>93.008258302465308</v>
+        <v>93.424405824177825</v>
       </c>
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.3">
@@ -11966,16 +11973,16 @@
         <v>14</v>
       </c>
       <c r="F388" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G388">
-        <v>91.205371802411875</v>
+        <v>91.412109253156885</v>
       </c>
       <c r="H388">
-        <v>88.469210648339512</v>
+        <v>88.669745975562179</v>
       </c>
       <c r="I388">
-        <v>93.941532956484238</v>
+        <v>94.15447253075159</v>
       </c>
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.3">
@@ -11995,16 +12002,16 @@
         <v>16</v>
       </c>
       <c r="F389" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G389">
-        <v>92.111463699517614</v>
+        <v>92.126450831833978</v>
       </c>
       <c r="H389">
-        <v>89.348119788532088</v>
+        <v>89.362657306878958</v>
       </c>
       <c r="I389">
-        <v>94.87480761050314</v>
+        <v>94.890244356788997</v>
       </c>
     </row>
     <row r="390" spans="1:9" x14ac:dyDescent="0.3">
@@ -12024,16 +12031,16 @@
         <v>18</v>
       </c>
       <c r="F390" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G390">
-        <v>93.017555596623353</v>
+        <v>92.846374645678779</v>
       </c>
       <c r="H390">
-        <v>90.22702892872465</v>
+        <v>90.060983406308409</v>
       </c>
       <c r="I390">
-        <v>95.808082264522056</v>
+        <v>95.631765885049148</v>
       </c>
     </row>
     <row r="391" spans="1:9" x14ac:dyDescent="0.3">
@@ -12053,24 +12060,24 @@
         <v>20</v>
       </c>
       <c r="F391" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G391">
-        <v>93.923647493729106</v>
+        <v>93.571924317168822</v>
       </c>
       <c r="H391">
-        <v>91.105938068917226</v>
+        <v>90.764766587653753</v>
       </c>
       <c r="I391">
-        <v>96.741356918540987</v>
+        <v>96.379082046683891</v>
       </c>
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A392">
-        <v>194</v>
+        <v>323</v>
       </c>
       <c r="B392" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C392" s="2">
         <v>46387</v>
@@ -12082,24 +12089,24 @@
         <v>12</v>
       </c>
       <c r="F392" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G392">
-        <v>90.703306625415365</v>
+        <v>1</v>
       </c>
       <c r="H392">
-        <v>87.982207426652906</v>
+        <v>0</v>
       </c>
       <c r="I392">
-        <v>93.424405824177825</v>
+        <v>2</v>
       </c>
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A393">
-        <v>194</v>
+        <v>323</v>
       </c>
       <c r="B393" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C393" s="2">
         <v>46752</v>
@@ -12111,24 +12118,24 @@
         <v>14</v>
       </c>
       <c r="F393" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G393">
-        <v>91.412109253156885</v>
+        <v>1</v>
       </c>
       <c r="H393">
-        <v>88.669745975562179</v>
+        <v>0</v>
       </c>
       <c r="I393">
-        <v>94.15447253075159</v>
+        <v>2</v>
       </c>
     </row>
     <row r="394" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A394">
-        <v>194</v>
+        <v>323</v>
       </c>
       <c r="B394" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C394" s="2">
         <v>47118</v>
@@ -12140,24 +12147,24 @@
         <v>16</v>
       </c>
       <c r="F394" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G394">
-        <v>92.126450831833978</v>
+        <v>2</v>
       </c>
       <c r="H394">
-        <v>89.362657306878958</v>
+        <v>1</v>
       </c>
       <c r="I394">
-        <v>94.890244356788997</v>
+        <v>3</v>
       </c>
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A395">
-        <v>194</v>
+        <v>323</v>
       </c>
       <c r="B395" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C395" s="2">
         <v>47483</v>
@@ -12169,24 +12176,24 @@
         <v>18</v>
       </c>
       <c r="F395" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G395">
-        <v>92.846374645678779</v>
+        <v>2</v>
       </c>
       <c r="H395">
-        <v>90.060983406308409</v>
+        <v>1</v>
       </c>
       <c r="I395">
-        <v>95.631765885049148</v>
+        <v>3</v>
       </c>
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A396">
-        <v>194</v>
+        <v>323</v>
       </c>
       <c r="B396" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C396" s="2">
         <v>47848</v>
@@ -12198,24 +12205,24 @@
         <v>20</v>
       </c>
       <c r="F396" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G396">
-        <v>93.571924317168822</v>
+        <v>2</v>
       </c>
       <c r="H396">
-        <v>90.764766587653753</v>
+        <v>1</v>
       </c>
       <c r="I396">
-        <v>96.379082046683891</v>
+        <v>3</v>
       </c>
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A397">
-        <v>323</v>
+        <v>376</v>
       </c>
       <c r="B397" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C397" s="2">
         <v>46387</v>
@@ -12227,24 +12234,24 @@
         <v>12</v>
       </c>
       <c r="F397" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G397">
-        <v>1</v>
+        <v>34790.444801582693</v>
       </c>
       <c r="H397">
-        <v>0</v>
+        <v>33746.731457535207</v>
       </c>
       <c r="I397">
-        <v>2</v>
+        <v>36033.446856183858</v>
       </c>
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A398">
-        <v>323</v>
+        <v>376</v>
       </c>
       <c r="B398" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C398" s="2">
         <v>46752</v>
@@ -12256,24 +12263,24 @@
         <v>14</v>
       </c>
       <c r="F398" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G398">
-        <v>1</v>
+        <v>37492.873343857507</v>
       </c>
       <c r="H398">
-        <v>0</v>
+        <v>36334.343557532309</v>
       </c>
       <c r="I398">
-        <v>2</v>
+        <v>38872.61512155136</v>
       </c>
     </row>
     <row r="399" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A399">
-        <v>323</v>
+        <v>376</v>
       </c>
       <c r="B399" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C399" s="2">
         <v>47118</v>
@@ -12285,24 +12292,24 @@
         <v>16</v>
       </c>
       <c r="F399" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G399">
-        <v>2</v>
+        <v>40195.301886132322</v>
       </c>
       <c r="H399">
-        <v>1</v>
+        <v>38917.091286153307</v>
       </c>
       <c r="I399">
-        <v>3</v>
+        <v>41717.57657108127</v>
       </c>
     </row>
     <row r="400" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A400">
-        <v>323</v>
+        <v>376</v>
       </c>
       <c r="B400" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C400" s="2">
         <v>47483</v>
@@ -12314,24 +12321,24 @@
         <v>18</v>
       </c>
       <c r="F400" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G400">
-        <v>2</v>
+        <v>42897.730428407129</v>
       </c>
       <c r="H400">
-        <v>1</v>
+        <v>41494.974643398207</v>
       </c>
       <c r="I400">
-        <v>3</v>
+        <v>44568.331204773582</v>
       </c>
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A401">
-        <v>323</v>
+        <v>376</v>
       </c>
       <c r="B401" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C401" s="2">
         <v>47848</v>
@@ -12343,16 +12350,16 @@
         <v>20</v>
       </c>
       <c r="F401" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G401">
-        <v>2</v>
+        <v>45600.15897068195</v>
       </c>
       <c r="H401">
-        <v>1</v>
+        <v>44067.993629267032</v>
       </c>
       <c r="I401">
-        <v>3</v>
+        <v>47424.879022628324</v>
       </c>
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.3">
@@ -12372,16 +12379,16 @@
         <v>12</v>
       </c>
       <c r="F402" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G402">
-        <v>34790.444801582693</v>
+        <v>33364.614089900009</v>
       </c>
       <c r="H402">
-        <v>33746.731457535207</v>
+        <v>32363.67566720301</v>
       </c>
       <c r="I402">
-        <v>36033.446856183858</v>
+        <v>34556.673694232348</v>
       </c>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.3">
@@ -12401,16 +12408,16 @@
         <v>14</v>
       </c>
       <c r="F403" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G403">
-        <v>37492.873343857507</v>
+        <v>36512.365153479492</v>
       </c>
       <c r="H403">
-        <v>36334.343557532309</v>
+        <v>35384.133070236967</v>
       </c>
       <c r="I403">
-        <v>38872.61512155136</v>
+        <v>37856.02412414951</v>
       </c>
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.3">
@@ -12430,16 +12437,16 @@
         <v>16</v>
       </c>
       <c r="F404" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G404">
-        <v>40195.301886132322</v>
+        <v>40167.943620047838</v>
       </c>
       <c r="H404">
-        <v>38917.091286153307</v>
+        <v>38890.603012930333</v>
       </c>
       <c r="I404">
-        <v>41717.57657108127</v>
+        <v>41689.182193960667</v>
       </c>
     </row>
     <row r="405" spans="1:9" x14ac:dyDescent="0.3">
@@ -12459,16 +12466,16 @@
         <v>18</v>
       </c>
       <c r="F405" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G405">
-        <v>42897.730428407129</v>
+        <v>44331.349489605069</v>
       </c>
       <c r="H405">
-        <v>41494.974643398207</v>
+        <v>42881.71436129498</v>
       </c>
       <c r="I405">
-        <v>44568.331204773582</v>
+        <v>46057.780844716202</v>
       </c>
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.3">
@@ -12488,24 +12495,24 @@
         <v>20</v>
       </c>
       <c r="F406" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G406">
-        <v>45600.15897068195</v>
+        <v>49002.582762151171</v>
       </c>
       <c r="H406">
-        <v>44067.993629267032</v>
+        <v>47356.095981342893</v>
       </c>
       <c r="I406">
-        <v>47424.879022628324</v>
+        <v>50963.453017466447</v>
       </c>
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A407">
-        <v>376</v>
+        <v>466</v>
       </c>
       <c r="B407" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C407" s="2">
         <v>46387</v>
@@ -12514,27 +12521,27 @@
         <v>2026</v>
       </c>
       <c r="E407" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F407" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G407">
-        <v>33364.614089900009</v>
+        <v>58.919999999999987</v>
       </c>
       <c r="H407">
-        <v>32363.67566720301</v>
+        <v>57.152399999902997</v>
       </c>
       <c r="I407">
-        <v>34556.673694232348</v>
+        <v>60.742268041340189</v>
       </c>
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A408">
-        <v>376</v>
+        <v>466</v>
       </c>
       <c r="B408" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C408" s="2">
         <v>46752</v>
@@ -12543,27 +12550,27 @@
         <v>2027</v>
       </c>
       <c r="E408" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F408" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G408">
-        <v>36512.365153479492</v>
+        <v>60.687600000000003</v>
       </c>
       <c r="H408">
-        <v>35384.133070236967</v>
+        <v>58.812353159905193</v>
       </c>
       <c r="I408">
-        <v>37856.02412414951</v>
+        <v>62.622639562581618</v>
       </c>
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A409">
-        <v>376</v>
+        <v>466</v>
       </c>
       <c r="B409" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C409" s="2">
         <v>47118</v>
@@ -12572,27 +12579,27 @@
         <v>2028</v>
       </c>
       <c r="E409" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F409" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G409">
-        <v>40167.943620047838</v>
+        <v>62.508228000000003</v>
       </c>
       <c r="H409">
-        <v>38890.603012930333</v>
+        <v>60.520466349507103</v>
       </c>
       <c r="I409">
-        <v>41689.182193960667</v>
+        <v>64.561276595843793</v>
       </c>
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A410">
-        <v>376</v>
+        <v>466</v>
       </c>
       <c r="B410" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C410" s="2">
         <v>47483</v>
@@ -12601,27 +12608,27 @@
         <v>2029</v>
       </c>
       <c r="E410" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F410" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G410">
-        <v>44331.349489605069</v>
+        <v>64.383474839999991</v>
       </c>
       <c r="H410">
-        <v>42881.71436129498</v>
+        <v>62.27813521264077</v>
       </c>
       <c r="I410">
-        <v>46057.780844716202</v>
+        <v>66.559986395217919</v>
       </c>
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A411">
-        <v>376</v>
+        <v>466</v>
       </c>
       <c r="B411" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C411" s="2">
         <v>47848</v>
@@ -12630,19 +12637,19 @@
         <v>2030</v>
       </c>
       <c r="E411" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F411" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G411">
-        <v>49002.582762151171</v>
+        <v>66.314979085199994</v>
       </c>
       <c r="H411">
-        <v>47356.095981342893</v>
+        <v>64.086795787847493</v>
       </c>
       <c r="I411">
-        <v>50963.453017466447</v>
+        <v>68.620632331635861</v>
       </c>
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.3">
@@ -12662,16 +12669,16 @@
         <v>22</v>
       </c>
       <c r="F412" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G412">
-        <v>58.919999999999987</v>
+        <v>56.235212373037847</v>
       </c>
       <c r="H412">
-        <v>57.152399999902997</v>
+        <v>54.54815600174971</v>
       </c>
       <c r="I412">
-        <v>60.742268041340189</v>
+        <v>57.97444574550294</v>
       </c>
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.3">
@@ -12691,16 +12698,16 @@
         <v>24</v>
       </c>
       <c r="F413" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G413">
-        <v>60.687600000000003</v>
+        <v>57.922268744228987</v>
       </c>
       <c r="H413">
-        <v>58.812353159905193</v>
+        <v>56.132470639937168</v>
       </c>
       <c r="I413">
-        <v>62.622639562581618</v>
+        <v>59.769135016331823</v>
       </c>
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.3">
@@ -12720,16 +12727,16 @@
         <v>25</v>
       </c>
       <c r="F414" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G414">
-        <v>62.508228000000003</v>
+        <v>59.659936806555862</v>
       </c>
       <c r="H414">
-        <v>60.520466349507103</v>
+        <v>57.762750816014403</v>
       </c>
       <c r="I414">
-        <v>64.561276595843793</v>
+        <v>61.619434834385345</v>
       </c>
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.3">
@@ -12749,16 +12756,16 @@
         <v>26</v>
       </c>
       <c r="F415" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G415">
-        <v>64.383474839999991</v>
+        <v>61.449734910752539</v>
       </c>
       <c r="H415">
-        <v>62.27813521264077</v>
+        <v>59.440328579080322</v>
       </c>
       <c r="I415">
-        <v>66.559986395217919</v>
+        <v>63.527070103221561</v>
       </c>
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.3">
@@ -12778,306 +12785,306 @@
         <v>27</v>
       </c>
       <c r="F416" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G416">
-        <v>66.314979085199994</v>
+        <v>63.293226958075117</v>
       </c>
       <c r="H416">
-        <v>64.086795787847493</v>
+        <v>61.166574532195703</v>
       </c>
       <c r="I416">
-        <v>68.620632331635861</v>
+        <v>65.493819286181989</v>
       </c>
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A417">
-        <v>466</v>
+        <v>96</v>
       </c>
       <c r="B417" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C417" s="2">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="D417">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E417" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="F417" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="G417">
-        <v>56.235212373037847</v>
+        <v>846.88288415165562</v>
       </c>
       <c r="H417">
-        <v>54.54815600174971</v>
+        <v>703.52841169356259</v>
       </c>
       <c r="I417">
-        <v>57.97444574550294</v>
+        <v>990.23735660954856</v>
       </c>
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A418">
-        <v>466</v>
+        <v>96</v>
       </c>
       <c r="B418" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C418" s="2">
-        <v>46752</v>
+        <v>46387</v>
       </c>
       <c r="D418">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E418" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F418" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="G418">
-        <v>57.922268744228987</v>
+        <v>914.63351488378817</v>
       </c>
       <c r="H418">
-        <v>56.132470639937168</v>
+        <v>755.16599972142001</v>
       </c>
       <c r="I418">
-        <v>59.769135016331823</v>
+        <v>1074.101030045967</v>
       </c>
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A419">
-        <v>466</v>
+        <v>96</v>
       </c>
       <c r="B419" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C419" s="2">
-        <v>47118</v>
+        <v>46752</v>
       </c>
       <c r="D419">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E419" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F419" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="G419">
-        <v>59.659936806555862</v>
+        <v>987.8041960744913</v>
       </c>
       <c r="H419">
-        <v>57.762750816014403</v>
+        <v>810.56301999889411</v>
       </c>
       <c r="I419">
-        <v>61.619434834385345</v>
+        <v>1165.04537214991</v>
       </c>
     </row>
     <row r="420" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A420">
-        <v>466</v>
+        <v>96</v>
       </c>
       <c r="B420" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C420" s="2">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="D420">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="E420" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F420" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="G420">
-        <v>61.449734910752539</v>
+        <v>1066.8285317604509</v>
       </c>
       <c r="H420">
-        <v>59.440328579080322</v>
+        <v>869.9905011225452</v>
       </c>
       <c r="I420">
-        <v>63.527070103221561</v>
+        <v>1263.666562398188</v>
       </c>
     </row>
     <row r="421" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A421">
-        <v>466</v>
+        <v>96</v>
       </c>
       <c r="B421" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C421" s="2">
-        <v>47848</v>
+        <v>47483</v>
       </c>
       <c r="D421">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="E421" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F421" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="G421">
-        <v>63.293226958075117</v>
+        <v>1152.1748143012869</v>
       </c>
       <c r="H421">
-        <v>61.166574532195703</v>
+        <v>933.73877589798656</v>
       </c>
       <c r="I421">
-        <v>65.493819286181989</v>
+        <v>1370.6108527044289</v>
       </c>
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A422">
-        <v>96</v>
+        <v>385</v>
       </c>
       <c r="B422" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C422" s="2">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="D422">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E422" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="F422" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="G422">
-        <v>846.88288415165562</v>
+        <v>18662.155890318401</v>
       </c>
       <c r="H422">
-        <v>703.52841169356259</v>
+        <v>14929.724712254731</v>
       </c>
       <c r="I422">
-        <v>990.23735660954856</v>
+        <v>22394.58706838209</v>
       </c>
     </row>
     <row r="423" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A423">
-        <v>96</v>
+        <v>385</v>
       </c>
       <c r="B423" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C423" s="2">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="D423">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E423" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F423" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="G423">
-        <v>914.63351488378817</v>
+        <v>20323.640878613929</v>
       </c>
       <c r="H423">
-        <v>755.16599972142001</v>
+        <v>16136.970857619461</v>
       </c>
       <c r="I423">
-        <v>1074.101030045967</v>
+        <v>24510.31089960839</v>
       </c>
     </row>
     <row r="424" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A424">
-        <v>96</v>
+        <v>385</v>
       </c>
       <c r="B424" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C424" s="2">
-        <v>46752</v>
+        <v>47118</v>
       </c>
       <c r="D424">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E424" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F424" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="G424">
-        <v>987.8041960744913</v>
+        <v>21985.12586690945</v>
       </c>
       <c r="H424">
-        <v>810.56301999889411</v>
+        <v>17324.27918312464</v>
       </c>
       <c r="I424">
-        <v>1165.04537214991</v>
+        <v>26645.972550694249</v>
       </c>
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A425">
-        <v>96</v>
+        <v>385</v>
       </c>
       <c r="B425" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C425" s="2">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="D425">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E425" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F425" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="G425">
-        <v>1066.8285317604509</v>
+        <v>23646.61085520497</v>
       </c>
       <c r="H425">
-        <v>869.9905011225452</v>
+        <v>18491.649688770289</v>
       </c>
       <c r="I425">
-        <v>1263.666562398188</v>
+        <v>28801.572021639651</v>
       </c>
     </row>
     <row r="426" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A426">
-        <v>96</v>
+        <v>385</v>
       </c>
       <c r="B426" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C426" s="2">
-        <v>47483</v>
+        <v>47848</v>
       </c>
       <c r="D426">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E426" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F426" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="G426">
-        <v>1152.1748143012869</v>
+        <v>25308.09584350049</v>
       </c>
       <c r="H426">
-        <v>933.73877589798656</v>
+        <v>19639.082374556379</v>
       </c>
       <c r="I426">
-        <v>1370.6108527044289</v>
+        <v>30977.109312444602</v>
       </c>
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.3">
@@ -13097,16 +13104,16 @@
         <v>22</v>
       </c>
       <c r="F427" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G427">
-        <v>18662.155890318401</v>
+        <v>17370.137802849709</v>
       </c>
       <c r="H427">
-        <v>14929.724712254731</v>
+        <v>13896.11024227977</v>
       </c>
       <c r="I427">
-        <v>22394.58706838209</v>
+        <v>20844.165363419648</v>
       </c>
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.3">
@@ -13126,16 +13133,16 @@
         <v>24</v>
       </c>
       <c r="F428" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G428">
-        <v>20323.640878613929</v>
+        <v>18957.986444229311</v>
       </c>
       <c r="H428">
-        <v>16136.970857619461</v>
+        <v>15052.641236718069</v>
       </c>
       <c r="I428">
-        <v>24510.31089960839</v>
+        <v>22863.33165174054</v>
       </c>
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.3">
@@ -13155,16 +13162,16 @@
         <v>25</v>
       </c>
       <c r="F429" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G429">
-        <v>21985.12586690945</v>
+        <v>20767.420529644682</v>
       </c>
       <c r="H429">
-        <v>17324.27918312464</v>
+        <v>16364.72737736001</v>
       </c>
       <c r="I429">
-        <v>26645.972550694249</v>
+        <v>25170.11368192935</v>
       </c>
     </row>
     <row r="430" spans="1:9" x14ac:dyDescent="0.3">
@@ -13184,16 +13191,16 @@
         <v>26</v>
       </c>
       <c r="F430" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G430">
-        <v>23646.61085520497</v>
+        <v>22798.440059095828</v>
       </c>
       <c r="H430">
-        <v>18491.649688770289</v>
+        <v>17828.380126212938</v>
       </c>
       <c r="I430">
-        <v>28801.572021639651</v>
+        <v>27768.499991978719</v>
       </c>
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.3">
@@ -13213,169 +13220,169 @@
         <v>27</v>
       </c>
       <c r="F431" t="s">
+        <v>35</v>
+      </c>
+      <c r="G431">
+        <v>25051.045032582759</v>
+      </c>
+      <c r="H431">
+        <v>19439.610945284221</v>
+      </c>
+      <c r="I431">
+        <v>30662.479119881289</v>
+      </c>
+    </row>
+    <row r="432" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A432" s="3">
+        <v>386.1</v>
+      </c>
+      <c r="B432" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C432" s="4">
+        <v>46387</v>
+      </c>
+      <c r="D432" s="3">
+        <v>2026</v>
+      </c>
+      <c r="E432" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F432" t="s">
         <v>30</v>
       </c>
-      <c r="G431">
-        <v>25308.09584350049</v>
-      </c>
-      <c r="H431">
-        <v>19639.082374556379</v>
-      </c>
-      <c r="I431">
-        <v>30977.109312444602</v>
-      </c>
-    </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A432">
-        <v>385</v>
-      </c>
-      <c r="B432" t="s">
-        <v>87</v>
-      </c>
-      <c r="C432" s="2">
-        <v>46387</v>
-      </c>
-      <c r="D432">
-        <v>2026</v>
-      </c>
-      <c r="E432" t="s">
-        <v>22</v>
-      </c>
-      <c r="F432" t="s">
-        <v>35</v>
-      </c>
       <c r="G432">
-        <v>17370.137802849709</v>
+        <v>5053.2904950000002</v>
       </c>
       <c r="H432">
-        <v>13896.11024227977</v>
+        <v>4042.632396</v>
       </c>
       <c r="I432">
-        <v>20844.165363419648</v>
+        <v>6063.9485940000004</v>
       </c>
     </row>
     <row r="433" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A433">
-        <v>385</v>
-      </c>
-      <c r="B433" t="s">
-        <v>87</v>
-      </c>
-      <c r="C433" s="2">
+      <c r="A433" s="3">
+        <v>386.1</v>
+      </c>
+      <c r="B433" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C433" s="4">
         <v>46752</v>
       </c>
-      <c r="D433">
+      <c r="D433" s="3">
         <v>2027</v>
       </c>
-      <c r="E433" t="s">
-        <v>24</v>
+      <c r="E433" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="F433" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G433">
-        <v>18957.986444229311</v>
+        <v>6316.6131187499996</v>
       </c>
       <c r="H433">
-        <v>15052.641236718069</v>
+        <v>5015.3908162875014</v>
       </c>
       <c r="I433">
-        <v>22863.33165174054</v>
+        <v>7617.8354212124996</v>
       </c>
     </row>
     <row r="434" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A434">
-        <v>385</v>
-      </c>
-      <c r="B434" t="s">
-        <v>87</v>
-      </c>
-      <c r="C434" s="2">
+      <c r="A434" s="3">
+        <v>386.1</v>
+      </c>
+      <c r="B434" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C434" s="4">
         <v>47118</v>
       </c>
-      <c r="D434">
+      <c r="D434" s="3">
         <v>2028</v>
       </c>
-      <c r="E434" t="s">
-        <v>25</v>
+      <c r="E434" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="F434" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G434">
-        <v>20767.420529644682</v>
+        <v>7895.7663984375004</v>
       </c>
       <c r="H434">
-        <v>16364.72737736001</v>
+        <v>6221.8639219687502</v>
       </c>
       <c r="I434">
-        <v>25170.11368192935</v>
+        <v>9569.6688749062487</v>
       </c>
     </row>
     <row r="435" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A435">
-        <v>385</v>
-      </c>
-      <c r="B435" t="s">
-        <v>87</v>
-      </c>
-      <c r="C435" s="2">
+      <c r="A435" s="3">
+        <v>386.1</v>
+      </c>
+      <c r="B435" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C435" s="4">
         <v>47483</v>
       </c>
-      <c r="D435">
+      <c r="D435" s="3">
         <v>2029</v>
       </c>
-      <c r="E435" t="s">
-        <v>26</v>
+      <c r="E435" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="F435" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G435">
-        <v>22798.440059095828</v>
+        <v>9050.2238278000004</v>
       </c>
       <c r="H435">
-        <v>17828.380126212938</v>
+        <v>7077.2750333395998</v>
       </c>
       <c r="I435">
-        <v>27768.499991978719</v>
+        <v>11023.172622260399</v>
       </c>
     </row>
     <row r="436" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A436">
-        <v>385</v>
-      </c>
-      <c r="B436" t="s">
-        <v>87</v>
-      </c>
-      <c r="C436" s="2">
+      <c r="A436" s="3">
+        <v>386.1</v>
+      </c>
+      <c r="B436" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C436" s="4">
         <v>47848</v>
       </c>
-      <c r="D436">
+      <c r="D436" s="3">
         <v>2030</v>
       </c>
-      <c r="E436" t="s">
-        <v>27</v>
+      <c r="E436" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="F436" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G436">
-        <v>25051.045032582759</v>
+        <v>10086.119943899999</v>
       </c>
       <c r="H436">
-        <v>19439.610945284221</v>
+        <v>7826.8290764664016</v>
       </c>
       <c r="I436">
-        <v>30662.479119881289</v>
+        <v>12345.410811333601</v>
       </c>
     </row>
     <row r="437" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A437" s="3">
-        <v>386.1</v>
+        <v>386.2</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C437" s="4">
         <v>46387</v>
@@ -13390,21 +13397,21 @@
         <v>30</v>
       </c>
       <c r="G437">
-        <v>5053.2904950000002</v>
+        <v>6864.5522870000004</v>
       </c>
       <c r="H437">
-        <v>4042.632396</v>
+        <v>5491.6418296000011</v>
       </c>
       <c r="I437">
-        <v>6063.9485940000004</v>
+        <v>7569.1213256024957</v>
       </c>
     </row>
     <row r="438" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A438" s="3">
-        <v>386.1</v>
+        <v>386.2</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C438" s="4">
         <v>46752</v>
@@ -13419,21 +13426,21 @@
         <v>30</v>
       </c>
       <c r="G438">
-        <v>6316.6131187499996</v>
+        <v>6928.2554168999995</v>
       </c>
       <c r="H438">
-        <v>5015.3908162875014</v>
+        <v>5501.0348010186008</v>
       </c>
       <c r="I438">
-        <v>7617.8354212124996</v>
+        <v>7660.696088310985</v>
       </c>
     </row>
     <row r="439" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A439" s="3">
-        <v>386.1</v>
+        <v>386.2</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C439" s="4">
         <v>47118</v>
@@ -13448,21 +13455,21 @@
         <v>30</v>
       </c>
       <c r="G439">
-        <v>7895.7663984375004</v>
+        <v>6991.9585467999996</v>
       </c>
       <c r="H439">
-        <v>6221.8639219687502</v>
+        <v>5509.6633348784007</v>
       </c>
       <c r="I439">
-        <v>9569.6688749062487</v>
+        <v>7752.6631555816357</v>
       </c>
     </row>
     <row r="440" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A440" s="3">
-        <v>386.1</v>
+        <v>386.2</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C440" s="4">
         <v>47483</v>
@@ -13477,21 +13484,21 @@
         <v>30</v>
       </c>
       <c r="G440">
-        <v>9050.2238278000004</v>
+        <v>7055.6616766999996</v>
       </c>
       <c r="H440">
-        <v>7077.2750333395998</v>
+        <v>5517.5274311794001</v>
       </c>
       <c r="I440">
-        <v>11023.172622260399</v>
+        <v>7845.0225274144459</v>
       </c>
     </row>
     <row r="441" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A441" s="3">
-        <v>386.1</v>
+        <v>386.2</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C441" s="4">
         <v>47848</v>
@@ -13506,21 +13513,21 @@
         <v>30</v>
       </c>
       <c r="G441">
-        <v>10086.119943899999</v>
+        <v>7119.3648065999996</v>
       </c>
       <c r="H441">
-        <v>7826.8290764664016</v>
+        <v>5524.6270899215997</v>
       </c>
       <c r="I441">
-        <v>12345.410811333601</v>
+        <v>7937.7742038094157</v>
       </c>
     </row>
     <row r="442" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A442" s="3">
-        <v>386.2</v>
+        <v>386.3</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C442" s="4">
         <v>46387</v>
@@ -13535,21 +13542,21 @@
         <v>30</v>
       </c>
       <c r="G442">
-        <v>6864.5522870000004</v>
+        <v>5855.0681234999993</v>
       </c>
       <c r="H442">
-        <v>5491.6418296000011</v>
+        <v>5679.416079794999</v>
       </c>
       <c r="I442">
-        <v>7569.1213256024957</v>
+        <v>7026.0817481999993</v>
       </c>
     </row>
     <row r="443" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A443" s="3">
-        <v>386.2</v>
+        <v>386.3</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C443" s="4">
         <v>46752</v>
@@ -13564,21 +13571,21 @@
         <v>30</v>
       </c>
       <c r="G443">
-        <v>6928.2554168999995</v>
+        <v>6416.9538656999994</v>
       </c>
       <c r="H443">
-        <v>5501.0348010186008</v>
+        <v>6218.6699912498698</v>
       </c>
       <c r="I443">
-        <v>7660.696088310985</v>
+        <v>7738.846362034199</v>
       </c>
     </row>
     <row r="444" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A444" s="3">
-        <v>386.2</v>
+        <v>386.3</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C444" s="4">
         <v>47118</v>
@@ -13593,21 +13600,21 @@
         <v>30</v>
       </c>
       <c r="G444">
-        <v>6991.9585467999996</v>
+        <v>6978.8396078999986</v>
       </c>
       <c r="H444">
-        <v>5509.6633348784007</v>
+        <v>6756.9125083687786</v>
       </c>
       <c r="I444">
-        <v>7752.6631555816357</v>
+        <v>8458.3536047747984</v>
       </c>
     </row>
     <row r="445" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A445" s="3">
-        <v>386.2</v>
+        <v>386.3</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C445" s="4">
         <v>47483</v>
@@ -13622,21 +13629,21 @@
         <v>30</v>
       </c>
       <c r="G445">
-        <v>7055.6616766999996</v>
+        <v>7540.7253500999996</v>
       </c>
       <c r="H445">
-        <v>5517.5274311794001</v>
+        <v>7294.1436311517291</v>
       </c>
       <c r="I445">
-        <v>7845.0225274144459</v>
+        <v>9184.6034764218002</v>
       </c>
     </row>
     <row r="446" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A446" s="3">
-        <v>386.2</v>
+        <v>386.3</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C446" s="4">
         <v>47848</v>
@@ -13651,162 +13658,306 @@
         <v>30</v>
       </c>
       <c r="G446">
-        <v>7119.3648065999996</v>
+        <v>8102.6110922999997</v>
       </c>
       <c r="H446">
-        <v>5524.6270899215997</v>
+        <v>7830.3633595987194</v>
       </c>
       <c r="I446">
-        <v>7937.7742038094157</v>
+        <v>9917.5959769751989</v>
       </c>
     </row>
     <row r="447" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A447" s="3">
-        <v>386.3</v>
-      </c>
-      <c r="B447" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C447" s="4">
+      <c r="A447" t="s">
+        <v>90</v>
+      </c>
+      <c r="B447" t="s">
+        <v>67</v>
+      </c>
+      <c r="C447" s="2">
         <v>46387</v>
       </c>
-      <c r="D447" s="3">
+      <c r="D447">
         <v>2026</v>
       </c>
-      <c r="E447" s="3" t="s">
+      <c r="E447" t="s">
         <v>12</v>
       </c>
       <c r="F447" t="s">
+        <v>91</v>
+      </c>
+      <c r="G447">
+        <v>15.7</v>
+      </c>
+      <c r="H447">
+        <v>14.9</v>
+      </c>
+      <c r="I447">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="448" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A448" t="s">
+        <v>90</v>
+      </c>
+      <c r="B448" t="s">
+        <v>67</v>
+      </c>
+      <c r="C448" s="2">
+        <v>46752</v>
+      </c>
+      <c r="D448">
+        <v>2027</v>
+      </c>
+      <c r="E448" t="s">
+        <v>14</v>
+      </c>
+      <c r="F448" t="s">
+        <v>91</v>
+      </c>
+      <c r="G448">
+        <v>16.3</v>
+      </c>
+      <c r="H448">
+        <v>15.5</v>
+      </c>
+      <c r="I448">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="449" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A449" t="s">
+        <v>90</v>
+      </c>
+      <c r="B449" t="s">
+        <v>67</v>
+      </c>
+      <c r="C449" s="2">
+        <v>47118</v>
+      </c>
+      <c r="D449">
+        <v>2028</v>
+      </c>
+      <c r="E449" t="s">
+        <v>16</v>
+      </c>
+      <c r="F449" t="s">
+        <v>91</v>
+      </c>
+      <c r="G449">
+        <v>16.8</v>
+      </c>
+      <c r="H449">
+        <v>16</v>
+      </c>
+      <c r="I449">
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+    <row r="450" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A450" t="s">
+        <v>90</v>
+      </c>
+      <c r="B450" t="s">
+        <v>67</v>
+      </c>
+      <c r="C450" s="2">
+        <v>47483</v>
+      </c>
+      <c r="D450">
+        <v>2029</v>
+      </c>
+      <c r="E450" t="s">
+        <v>18</v>
+      </c>
+      <c r="F450" t="s">
+        <v>91</v>
+      </c>
+      <c r="G450">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="H450">
+        <v>16.5</v>
+      </c>
+      <c r="I450">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="451" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A451" t="s">
+        <v>90</v>
+      </c>
+      <c r="B451" t="s">
+        <v>67</v>
+      </c>
+      <c r="C451" s="2">
+        <v>47848</v>
+      </c>
+      <c r="D451">
+        <v>2030</v>
+      </c>
+      <c r="E451" t="s">
+        <v>20</v>
+      </c>
+      <c r="F451" t="s">
+        <v>91</v>
+      </c>
+      <c r="G451">
+        <v>18</v>
+      </c>
+      <c r="H451">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="I451">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="452" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A452" t="s">
+        <v>90</v>
+      </c>
+      <c r="B452" t="s">
+        <v>67</v>
+      </c>
+      <c r="C452" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D452">
+        <v>2026</v>
+      </c>
+      <c r="E452" t="s">
+        <v>12</v>
+      </c>
+      <c r="F452" t="s">
         <v>30</v>
       </c>
-      <c r="G447">
-        <v>5855.0681234999993</v>
-      </c>
-      <c r="H447">
-        <v>5679.416079794999</v>
-      </c>
-      <c r="I447">
-        <v>7026.0817481999993</v>
-      </c>
-    </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A448" s="3">
-        <v>386.3</v>
-      </c>
-      <c r="B448" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C448" s="4">
+      <c r="G452">
+        <v>15.7</v>
+      </c>
+      <c r="H452">
+        <v>14.9</v>
+      </c>
+      <c r="I452">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="453" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A453" t="s">
+        <v>90</v>
+      </c>
+      <c r="B453" t="s">
+        <v>67</v>
+      </c>
+      <c r="C453" s="2">
         <v>46752</v>
       </c>
-      <c r="D448" s="3">
+      <c r="D453">
         <v>2027</v>
       </c>
-      <c r="E448" s="3" t="s">
+      <c r="E453" t="s">
         <v>14</v>
       </c>
-      <c r="F448" t="s">
+      <c r="F453" t="s">
         <v>30</v>
       </c>
-      <c r="G448">
-        <v>6416.9538656999994</v>
-      </c>
-      <c r="H448">
-        <v>6218.6699912498698</v>
-      </c>
-      <c r="I448">
-        <v>7738.846362034199</v>
-      </c>
-    </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A449" s="3">
-        <v>386.3</v>
-      </c>
-      <c r="B449" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C449" s="4">
+      <c r="G453">
+        <v>16.3</v>
+      </c>
+      <c r="H453">
+        <v>15.5</v>
+      </c>
+      <c r="I453">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="454" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A454" t="s">
+        <v>90</v>
+      </c>
+      <c r="B454" t="s">
+        <v>67</v>
+      </c>
+      <c r="C454" s="2">
         <v>47118</v>
       </c>
-      <c r="D449" s="3">
+      <c r="D454">
         <v>2028</v>
       </c>
-      <c r="E449" s="3" t="s">
+      <c r="E454" t="s">
         <v>16</v>
       </c>
-      <c r="F449" t="s">
+      <c r="F454" t="s">
         <v>30</v>
       </c>
-      <c r="G449">
-        <v>6978.8396078999986</v>
-      </c>
-      <c r="H449">
-        <v>6756.9125083687786</v>
-      </c>
-      <c r="I449">
-        <v>8458.3536047747984</v>
-      </c>
-    </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A450" s="3">
-        <v>386.3</v>
-      </c>
-      <c r="B450" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C450" s="4">
+      <c r="G454">
+        <v>16.8</v>
+      </c>
+      <c r="H454">
+        <v>16</v>
+      </c>
+      <c r="I454">
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+    <row r="455" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A455" t="s">
+        <v>90</v>
+      </c>
+      <c r="B455" t="s">
+        <v>67</v>
+      </c>
+      <c r="C455" s="2">
         <v>47483</v>
       </c>
-      <c r="D450" s="3">
+      <c r="D455">
         <v>2029</v>
       </c>
-      <c r="E450" s="3" t="s">
+      <c r="E455" t="s">
         <v>18</v>
       </c>
-      <c r="F450" t="s">
+      <c r="F455" t="s">
         <v>30</v>
       </c>
-      <c r="G450">
-        <v>7540.7253500999996</v>
-      </c>
-      <c r="H450">
-        <v>7294.1436311517291</v>
-      </c>
-      <c r="I450">
-        <v>9184.6034764218002</v>
-      </c>
-    </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A451" s="3">
-        <v>386.3</v>
-      </c>
-      <c r="B451" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C451" s="4">
+      <c r="G455">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="H455">
+        <v>16.5</v>
+      </c>
+      <c r="I455">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="456" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A456" t="s">
+        <v>90</v>
+      </c>
+      <c r="B456" t="s">
+        <v>67</v>
+      </c>
+      <c r="C456" s="2">
         <v>47848</v>
       </c>
-      <c r="D451" s="3">
+      <c r="D456">
         <v>2030</v>
       </c>
-      <c r="E451" s="3" t="s">
+      <c r="E456" t="s">
         <v>20</v>
       </c>
-      <c r="F451" t="s">
+      <c r="F456" t="s">
         <v>30</v>
       </c>
-      <c r="G451">
-        <v>8102.6110922999997</v>
-      </c>
-      <c r="H451">
-        <v>7830.3633595987194</v>
-      </c>
-      <c r="I451">
-        <v>9917.5959769751989</v>
+      <c r="G456">
+        <v>18</v>
+      </c>
+      <c r="H456">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="I456">
+        <v>18.3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I451" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="609" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41B49B1E-B5A8-4175-9174-50DB2DF49CB5}"/>
+  <xr:revisionPtr revIDLastSave="615" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B92FEEEF-6523-45D6-A1D1-8A6D1796EDC4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="91">
   <si>
     <t>Id</t>
   </si>
@@ -312,9 +312,6 @@
   </si>
   <si>
     <t>423</t>
-  </si>
-  <si>
-    <t>Proyeccion_CAGR_24.6%↑</t>
   </si>
 </sst>
 </file>
@@ -13684,16 +13681,16 @@
         <v>12</v>
       </c>
       <c r="F447" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="G447">
         <v>15.7</v>
       </c>
       <c r="H447">
-        <v>14.9</v>
+        <v>15.2</v>
       </c>
       <c r="I447">
-        <v>16.5</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="448" spans="1:9" x14ac:dyDescent="0.3">
@@ -13713,16 +13710,16 @@
         <v>14</v>
       </c>
       <c r="F448" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="G448">
         <v>16.3</v>
       </c>
       <c r="H448">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="I448">
-        <v>17.100000000000001</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="449" spans="1:9" x14ac:dyDescent="0.3">
@@ -13742,16 +13739,16 @@
         <v>16</v>
       </c>
       <c r="F449" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="G449">
         <v>16.8</v>
       </c>
       <c r="H449">
-        <v>16</v>
+        <v>16.3</v>
       </c>
       <c r="I449">
-        <v>17.600000000000001</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="450" spans="1:9" x14ac:dyDescent="0.3">
@@ -13771,16 +13768,16 @@
         <v>18</v>
       </c>
       <c r="F450" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="G450">
         <v>17.399999999999999</v>
       </c>
       <c r="H450">
-        <v>16.5</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="I450">
-        <v>18</v>
+        <v>17.899999999999999</v>
       </c>
     </row>
     <row r="451" spans="1:9" x14ac:dyDescent="0.3">
@@ -13800,16 +13797,16 @@
         <v>20</v>
       </c>
       <c r="F451" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="G451">
         <v>18</v>
       </c>
       <c r="H451">
-        <v>17.100000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="I451">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="452" spans="1:9" x14ac:dyDescent="0.3">
@@ -13835,10 +13832,10 @@
         <v>15.7</v>
       </c>
       <c r="H452">
-        <v>14.9</v>
+        <v>15.2</v>
       </c>
       <c r="I452">
-        <v>16.5</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="453" spans="1:9" x14ac:dyDescent="0.3">
@@ -13864,10 +13861,10 @@
         <v>16.3</v>
       </c>
       <c r="H453">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="I453">
-        <v>17.100000000000001</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="454" spans="1:9" x14ac:dyDescent="0.3">
@@ -13893,10 +13890,10 @@
         <v>16.8</v>
       </c>
       <c r="H454">
-        <v>16</v>
+        <v>16.3</v>
       </c>
       <c r="I454">
-        <v>17.600000000000001</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="455" spans="1:9" x14ac:dyDescent="0.3">
@@ -13922,10 +13919,10 @@
         <v>17.399999999999999</v>
       </c>
       <c r="H455">
-        <v>16.5</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="I455">
-        <v>18</v>
+        <v>17.899999999999999</v>
       </c>
     </row>
     <row r="456" spans="1:9" x14ac:dyDescent="0.3">
@@ -13951,13 +13948,14 @@
         <v>18</v>
       </c>
       <c r="H456">
-        <v>17.100000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="I456">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I456" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="615" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B92FEEEF-6523-45D6-A1D1-8A6D1796EDC4}"/>
+  <xr:revisionPtr revIDLastSave="619" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{049F4923-022F-47F5-9F0E-AA696328E1F1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="93">
   <si>
     <t>Id</t>
   </si>
@@ -312,6 +312,12 @@
   </si>
   <si>
     <t>423</t>
+  </si>
+  <si>
+    <t>339</t>
+  </si>
+  <si>
+    <t>Programas acreditables acreditados Sede Bogotá</t>
   </si>
 </sst>
 </file>
@@ -719,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}">
-  <dimension ref="A1:I456"/>
+  <dimension ref="A1:I461"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
@@ -13954,6 +13960,151 @@
         <v>18.2</v>
       </c>
     </row>
+    <row r="457" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A457" t="s">
+        <v>91</v>
+      </c>
+      <c r="B457" t="s">
+        <v>92</v>
+      </c>
+      <c r="C457" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D457">
+        <v>2026</v>
+      </c>
+      <c r="E457" t="s">
+        <v>12</v>
+      </c>
+      <c r="F457" t="s">
+        <v>43</v>
+      </c>
+      <c r="G457">
+        <v>34.298999999999999</v>
+      </c>
+      <c r="H457">
+        <v>31.026750885006429</v>
+      </c>
+      <c r="I457">
+        <v>37.57124911499357</v>
+      </c>
+    </row>
+    <row r="458" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A458" t="s">
+        <v>91</v>
+      </c>
+      <c r="B458" t="s">
+        <v>92</v>
+      </c>
+      <c r="C458" s="2">
+        <v>46752</v>
+      </c>
+      <c r="D458">
+        <v>2027</v>
+      </c>
+      <c r="E458" t="s">
+        <v>14</v>
+      </c>
+      <c r="F458" t="s">
+        <v>43</v>
+      </c>
+      <c r="G458">
+        <v>35.327969999999993</v>
+      </c>
+      <c r="H458">
+        <v>31.85644091390332</v>
+      </c>
+      <c r="I458">
+        <v>38.799499086096667</v>
+      </c>
+    </row>
+    <row r="459" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A459" t="s">
+        <v>91</v>
+      </c>
+      <c r="B459" t="s">
+        <v>92</v>
+      </c>
+      <c r="C459" s="2">
+        <v>47118</v>
+      </c>
+      <c r="D459">
+        <v>2028</v>
+      </c>
+      <c r="E459" t="s">
+        <v>16</v>
+      </c>
+      <c r="F459" t="s">
+        <v>43</v>
+      </c>
+      <c r="G459">
+        <v>36.387809099999998</v>
+      </c>
+      <c r="H459">
+        <v>32.707988268737523</v>
+      </c>
+      <c r="I459">
+        <v>40.067629931262481</v>
+      </c>
+    </row>
+    <row r="460" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A460" t="s">
+        <v>91</v>
+      </c>
+      <c r="B460" t="s">
+        <v>92</v>
+      </c>
+      <c r="C460" s="2">
+        <v>47483</v>
+      </c>
+      <c r="D460">
+        <v>2029</v>
+      </c>
+      <c r="E460" t="s">
+        <v>18</v>
+      </c>
+      <c r="F460" t="s">
+        <v>43</v>
+      </c>
+      <c r="G460">
+        <v>37.479443373000002</v>
+      </c>
+      <c r="H460">
+        <v>33.581957668039273</v>
+      </c>
+      <c r="I460">
+        <v>41.376929077960739</v>
+      </c>
+    </row>
+    <row r="461" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A461" t="s">
+        <v>91</v>
+      </c>
+      <c r="B461" t="s">
+        <v>92</v>
+      </c>
+      <c r="C461" s="2">
+        <v>47848</v>
+      </c>
+      <c r="D461">
+        <v>2030</v>
+      </c>
+      <c r="E461" t="s">
+        <v>20</v>
+      </c>
+      <c r="F461" t="s">
+        <v>43</v>
+      </c>
+      <c r="G461">
+        <v>38.603826674190003</v>
+      </c>
+      <c r="H461">
+        <v>34.478928041857237</v>
+      </c>
+      <c r="I461">
+        <v>42.728725306522747</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I456" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="619" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{049F4923-022F-47F5-9F0E-AA696328E1F1}"/>
+  <xr:revisionPtr revIDLastSave="653" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFDE6934-BAD5-4EBC-97E9-9E53F496A23A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Proyecciones" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$I$456</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$I$461</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="80">
   <si>
     <t>Id</t>
   </si>
@@ -149,16 +149,10 @@
     <t>Polinomial_Grado_2</t>
   </si>
   <si>
-    <t>Proyeccion_CAGR_3.0%↑_Suavizado</t>
-  </si>
-  <si>
     <t>Suavizado_Exponencial</t>
   </si>
   <si>
     <t>Nivel de efectividad de las capacitaciones</t>
-  </si>
-  <si>
-    <t>Conservador_1.0%↑</t>
   </si>
   <si>
     <t>Cumplimiento de Ingresos</t>
@@ -170,16 +164,10 @@
     <t>Caja</t>
   </si>
   <si>
-    <t>Conservador_3.0%↑</t>
-  </si>
-  <si>
     <t>Utilidad Neta</t>
   </si>
   <si>
     <t>Nivel de Cumplimiento Opex</t>
-  </si>
-  <si>
-    <t>Conservador_11.6%↑</t>
   </si>
   <si>
     <t>Compensación de Gases de Efecto Invernadero</t>
@@ -189,9 +177,6 @@
   </si>
   <si>
     <t>Permanencia Intersemestral</t>
-  </si>
-  <si>
-    <t>Proyeccion_CAGR_0.1%↑_Suavizado</t>
   </si>
   <si>
     <t>Relación Estudiante-Docente Tiempo completo</t>
@@ -218,28 +203,16 @@
     <t>Impacto de actividades de Responsabilidad y proyección</t>
   </si>
   <si>
-    <t>Conservador_10.0%↑</t>
-  </si>
-  <si>
     <t>Estudiantes con Becas</t>
   </si>
   <si>
-    <t>Proyeccion_CAGR_1.0%↑_Suavizado</t>
-  </si>
-  <si>
     <t>Participación de POLI- voluntariados (Estudiantes- Colaboradores)</t>
-  </si>
-  <si>
-    <t>Conservador_2.0%↑</t>
   </si>
   <si>
     <t>Cumplimiento EBIDTA</t>
   </si>
   <si>
     <t>CAPEX</t>
-  </si>
-  <si>
-    <t>Conservador_15.0%↑</t>
   </si>
   <si>
     <t>Brand equity</t>
@@ -260,9 +233,6 @@
     <t>Productos de investigación, innovación y creación</t>
   </si>
   <si>
-    <t>Conservador_14.4%↑</t>
-  </si>
-  <si>
     <t>Lanzamiento de nuevos programas virtual</t>
   </si>
   <si>
@@ -278,13 +248,7 @@
     <t>Total estudiantes nuevos</t>
   </si>
   <si>
-    <t>TopDown_Ensemble_Promedio</t>
-  </si>
-  <si>
     <t>Total Matriculados antiguos</t>
-  </si>
-  <si>
-    <t>TopDown_Suavizado_Exponencial</t>
   </si>
   <si>
     <t>Estudiantes Presencial</t>
@@ -305,12 +269,6 @@
     <t>Ingresos totales de educación para la vida</t>
   </si>
   <si>
-    <t>Conservador_4.2%↑</t>
-  </si>
-  <si>
-    <t>Proyeccion_CAGR_11.8%↑</t>
-  </si>
-  <si>
     <t>423</t>
   </si>
   <si>
@@ -318,6 +276,9 @@
   </si>
   <si>
     <t>Programas acreditables acreditados Sede Bogotá</t>
+  </si>
+  <si>
+    <t>Modelo_Conservador</t>
   </si>
 </sst>
 </file>
@@ -1502,7 +1463,7 @@
         <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G27">
         <v>5.3560000000000008</v>
@@ -1531,7 +1492,7 @@
         <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G28">
         <v>5.51668</v>
@@ -1560,7 +1521,7 @@
         <v>13</v>
       </c>
       <c r="F29" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G29">
         <v>5.6821804</v>
@@ -1589,7 +1550,7 @@
         <v>14</v>
       </c>
       <c r="F30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G30">
         <v>5.8526458120000013</v>
@@ -1618,7 +1579,7 @@
         <v>15</v>
       </c>
       <c r="F31" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G31">
         <v>6.0282251863600003</v>
@@ -1647,7 +1608,7 @@
         <v>16</v>
       </c>
       <c r="F32" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G32">
         <v>6.2090719419508007</v>
@@ -1676,7 +1637,7 @@
         <v>17</v>
       </c>
       <c r="F33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G33">
         <v>6.395344100209325</v>
@@ -1705,7 +1666,7 @@
         <v>18</v>
       </c>
       <c r="F34" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G34">
         <v>6.5872044232156064</v>
@@ -1734,7 +1695,7 @@
         <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G35">
         <v>6.7848205559120736</v>
@@ -1763,7 +1724,7 @@
         <v>20</v>
       </c>
       <c r="F36" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G36">
         <v>6.988365172589436</v>
@@ -2220,7 +2181,7 @@
         <v>200</v>
       </c>
       <c r="B52" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C52" s="2">
         <v>46387</v>
@@ -2232,7 +2193,7 @@
         <v>12</v>
       </c>
       <c r="F52" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="G52">
         <v>88.274000000000001</v>
@@ -2249,7 +2210,7 @@
         <v>200</v>
       </c>
       <c r="B53" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C53" s="2">
         <v>46752</v>
@@ -2261,7 +2222,7 @@
         <v>14</v>
       </c>
       <c r="F53" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="G53">
         <v>89.156740000000013</v>
@@ -2278,7 +2239,7 @@
         <v>200</v>
       </c>
       <c r="B54" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C54" s="2">
         <v>47118</v>
@@ -2290,7 +2251,7 @@
         <v>16</v>
       </c>
       <c r="F54" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="G54">
         <v>90.048307400000013</v>
@@ -2307,7 +2268,7 @@
         <v>200</v>
       </c>
       <c r="B55" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C55" s="2">
         <v>47483</v>
@@ -2319,7 +2280,7 @@
         <v>18</v>
       </c>
       <c r="F55" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="G55">
         <v>90.948790474000006</v>
@@ -2336,7 +2297,7 @@
         <v>200</v>
       </c>
       <c r="B56" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C56" s="2">
         <v>47848</v>
@@ -2348,7 +2309,7 @@
         <v>20</v>
       </c>
       <c r="F56" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="G56">
         <v>91.858278378740025</v>
@@ -2365,7 +2326,7 @@
         <v>203</v>
       </c>
       <c r="B57" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C57" s="2">
         <v>46387</v>
@@ -2377,7 +2338,7 @@
         <v>12</v>
       </c>
       <c r="F57" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G57">
         <v>337385.42515227583</v>
@@ -2394,7 +2355,7 @@
         <v>203</v>
       </c>
       <c r="B58" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C58" s="2">
         <v>46752</v>
@@ -2406,7 +2367,7 @@
         <v>14</v>
       </c>
       <c r="F58" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G58">
         <v>360065.15581525367</v>
@@ -2423,7 +2384,7 @@
         <v>203</v>
       </c>
       <c r="B59" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C59" s="2">
         <v>47118</v>
@@ -2435,7 +2396,7 @@
         <v>16</v>
       </c>
       <c r="F59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G59">
         <v>382744.8864782317</v>
@@ -2452,7 +2413,7 @@
         <v>203</v>
       </c>
       <c r="B60" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C60" s="2">
         <v>47483</v>
@@ -2464,7 +2425,7 @@
         <v>18</v>
       </c>
       <c r="F60" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G60">
         <v>405424.61714120972</v>
@@ -2481,7 +2442,7 @@
         <v>203</v>
       </c>
       <c r="B61" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C61" s="2">
         <v>47848</v>
@@ -2493,7 +2454,7 @@
         <v>20</v>
       </c>
       <c r="F61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G61">
         <v>428104.34780418762</v>
@@ -2510,7 +2471,7 @@
         <v>203</v>
       </c>
       <c r="B62" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C62" s="2">
         <v>46387</v>
@@ -2522,7 +2483,7 @@
         <v>12</v>
       </c>
       <c r="F62" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G62">
         <v>321304.73279046162</v>
@@ -2539,7 +2500,7 @@
         <v>203</v>
       </c>
       <c r="B63" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C63" s="2">
         <v>46752</v>
@@ -2551,7 +2512,7 @@
         <v>14</v>
       </c>
       <c r="F63" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G63">
         <v>339023.55597144237</v>
@@ -2568,7 +2529,7 @@
         <v>203</v>
       </c>
       <c r="B64" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C64" s="2">
         <v>47118</v>
@@ -2580,7 +2541,7 @@
         <v>16</v>
       </c>
       <c r="F64" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G64">
         <v>356742.37915242318</v>
@@ -2597,7 +2558,7 @@
         <v>203</v>
       </c>
       <c r="B65" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C65" s="2">
         <v>47483</v>
@@ -2609,7 +2570,7 @@
         <v>18</v>
       </c>
       <c r="F65" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G65">
         <v>374461.20233340398</v>
@@ -2626,7 +2587,7 @@
         <v>203</v>
       </c>
       <c r="B66" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C66" s="2">
         <v>47848</v>
@@ -2638,7 +2599,7 @@
         <v>20</v>
       </c>
       <c r="F66" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G66">
         <v>392180.02551438479</v>
@@ -2655,7 +2616,7 @@
         <v>204</v>
       </c>
       <c r="B67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C67" s="2">
         <v>46387</v>
@@ -2667,7 +2628,7 @@
         <v>12</v>
       </c>
       <c r="F67" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="G67">
         <v>21142.397020470002</v>
@@ -2684,7 +2645,7 @@
         <v>204</v>
       </c>
       <c r="B68" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C68" s="2">
         <v>46752</v>
@@ -2696,7 +2657,7 @@
         <v>14</v>
       </c>
       <c r="F68" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="G68">
         <v>21776.668931084099</v>
@@ -2713,7 +2674,7 @@
         <v>204</v>
       </c>
       <c r="B69" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C69" s="2">
         <v>47118</v>
@@ -2725,7 +2686,7 @@
         <v>16</v>
       </c>
       <c r="F69" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="G69">
         <v>22429.968999016619</v>
@@ -2742,7 +2703,7 @@
         <v>204</v>
       </c>
       <c r="B70" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C70" s="2">
         <v>47483</v>
@@ -2754,7 +2715,7 @@
         <v>18</v>
       </c>
       <c r="F70" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="G70">
         <v>23102.868068987129</v>
@@ -2771,7 +2732,7 @@
         <v>204</v>
       </c>
       <c r="B71" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C71" s="2">
         <v>47848</v>
@@ -2783,7 +2744,7 @@
         <v>20</v>
       </c>
       <c r="F71" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="G71">
         <v>23795.954111056741</v>
@@ -2800,7 +2761,7 @@
         <v>205</v>
       </c>
       <c r="B72" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C72" s="2">
         <v>46387</v>
@@ -2812,7 +2773,7 @@
         <v>12</v>
       </c>
       <c r="F72" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="G72">
         <v>9245.4038089869991</v>
@@ -2829,7 +2790,7 @@
         <v>205</v>
       </c>
       <c r="B73" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C73" s="2">
         <v>46752</v>
@@ -2841,7 +2802,7 @@
         <v>14</v>
       </c>
       <c r="F73" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="G73">
         <v>9522.7659232566093</v>
@@ -2858,7 +2819,7 @@
         <v>205</v>
       </c>
       <c r="B74" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C74" s="2">
         <v>47118</v>
@@ -2870,7 +2831,7 @@
         <v>16</v>
       </c>
       <c r="F74" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="G74">
         <v>9808.4489009543086</v>
@@ -2887,7 +2848,7 @@
         <v>205</v>
       </c>
       <c r="B75" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C75" s="2">
         <v>47483</v>
@@ -2899,7 +2860,7 @@
         <v>18</v>
       </c>
       <c r="F75" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="G75">
         <v>10102.70236798294</v>
@@ -2916,7 +2877,7 @@
         <v>205</v>
       </c>
       <c r="B76" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C76" s="2">
         <v>47848</v>
@@ -2928,7 +2889,7 @@
         <v>20</v>
       </c>
       <c r="F76" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="G76">
         <v>10405.783439022431</v>
@@ -2945,7 +2906,7 @@
         <v>207</v>
       </c>
       <c r="B77" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C77" s="2">
         <v>46387</v>
@@ -2957,7 +2918,7 @@
         <v>12</v>
       </c>
       <c r="F77" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="G77">
         <v>162497.78230864269</v>
@@ -2974,7 +2935,7 @@
         <v>207</v>
       </c>
       <c r="B78" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C78" s="2">
         <v>46752</v>
@@ -2986,7 +2947,7 @@
         <v>14</v>
       </c>
       <c r="F78" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="G78">
         <v>181422.79838200199</v>
@@ -3003,7 +2964,7 @@
         <v>207</v>
       </c>
       <c r="B79" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C79" s="2">
         <v>47118</v>
@@ -3015,7 +2976,7 @@
         <v>16</v>
       </c>
       <c r="F79" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="G79">
         <v>202551.88289425641</v>
@@ -3032,7 +2993,7 @@
         <v>207</v>
       </c>
       <c r="B80" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C80" s="2">
         <v>47483</v>
@@ -3044,7 +3005,7 @@
         <v>18</v>
       </c>
       <c r="F80" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="G80">
         <v>226141.72876785841</v>
@@ -3061,7 +3022,7 @@
         <v>207</v>
       </c>
       <c r="B81" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C81" s="2">
         <v>47848</v>
@@ -3073,7 +3034,7 @@
         <v>20</v>
       </c>
       <c r="F81" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="G81">
         <v>252478.92421130271</v>
@@ -3090,7 +3051,7 @@
         <v>228</v>
       </c>
       <c r="B82" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C82" s="2">
         <v>46387</v>
@@ -3102,7 +3063,7 @@
         <v>12</v>
       </c>
       <c r="F82" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G82">
         <v>743.69125717621739</v>
@@ -3119,7 +3080,7 @@
         <v>228</v>
       </c>
       <c r="B83" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C83" s="2">
         <v>46752</v>
@@ -3131,7 +3092,7 @@
         <v>14</v>
       </c>
       <c r="F83" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G83">
         <v>845.42962114370084</v>
@@ -3148,7 +3109,7 @@
         <v>228</v>
       </c>
       <c r="B84" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C84" s="2">
         <v>47118</v>
@@ -3160,7 +3121,7 @@
         <v>16</v>
       </c>
       <c r="F84" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G84">
         <v>947.16798511118441</v>
@@ -3177,7 +3138,7 @@
         <v>228</v>
       </c>
       <c r="B85" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C85" s="2">
         <v>47483</v>
@@ -3189,7 +3150,7 @@
         <v>18</v>
       </c>
       <c r="F85" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G85">
         <v>1048.906349078668</v>
@@ -3206,7 +3167,7 @@
         <v>228</v>
       </c>
       <c r="B86" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C86" s="2">
         <v>47848</v>
@@ -3218,7 +3179,7 @@
         <v>20</v>
       </c>
       <c r="F86" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G86">
         <v>1150.644713046152</v>
@@ -3235,7 +3196,7 @@
         <v>228</v>
       </c>
       <c r="B87" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C87" s="2">
         <v>46387</v>
@@ -3264,7 +3225,7 @@
         <v>228</v>
       </c>
       <c r="B88" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C88" s="2">
         <v>46752</v>
@@ -3293,7 +3254,7 @@
         <v>228</v>
       </c>
       <c r="B89" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C89" s="2">
         <v>47118</v>
@@ -3322,7 +3283,7 @@
         <v>228</v>
       </c>
       <c r="B90" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C90" s="2">
         <v>47483</v>
@@ -3351,7 +3312,7 @@
         <v>228</v>
       </c>
       <c r="B91" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C91" s="2">
         <v>47848</v>
@@ -3380,7 +3341,7 @@
         <v>244</v>
       </c>
       <c r="B92" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C92" s="2">
         <v>46387</v>
@@ -3409,7 +3370,7 @@
         <v>244</v>
       </c>
       <c r="B93" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C93" s="2">
         <v>46752</v>
@@ -3438,7 +3399,7 @@
         <v>244</v>
       </c>
       <c r="B94" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C94" s="2">
         <v>47118</v>
@@ -3467,7 +3428,7 @@
         <v>244</v>
       </c>
       <c r="B95" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C95" s="2">
         <v>47483</v>
@@ -3496,7 +3457,7 @@
         <v>244</v>
       </c>
       <c r="B96" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C96" s="2">
         <v>47848</v>
@@ -3525,7 +3486,7 @@
         <v>245</v>
       </c>
       <c r="B97" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C97" s="2">
         <v>46203</v>
@@ -3537,7 +3498,7 @@
         <v>10</v>
       </c>
       <c r="F97" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G97">
         <v>86.600803392352617</v>
@@ -3554,7 +3515,7 @@
         <v>245</v>
       </c>
       <c r="B98" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C98" s="2">
         <v>46387</v>
@@ -3566,7 +3527,7 @@
         <v>12</v>
       </c>
       <c r="F98" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G98">
         <v>86.701724256657954</v>
@@ -3583,7 +3544,7 @@
         <v>245</v>
       </c>
       <c r="B99" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C99" s="2">
         <v>46568</v>
@@ -3595,7 +3556,7 @@
         <v>13</v>
       </c>
       <c r="F99" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G99">
         <v>86.802762729812784</v>
@@ -3612,7 +3573,7 @@
         <v>245</v>
       </c>
       <c r="B100" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C100" s="2">
         <v>46752</v>
@@ -3624,7 +3585,7 @@
         <v>14</v>
       </c>
       <c r="F100" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G100">
         <v>86.903918948873411</v>
@@ -3641,7 +3602,7 @@
         <v>245</v>
       </c>
       <c r="B101" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C101" s="2">
         <v>46934</v>
@@ -3653,7 +3614,7 @@
         <v>15</v>
       </c>
       <c r="F101" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G101">
         <v>87.005193051055869</v>
@@ -3670,7 +3631,7 @@
         <v>245</v>
       </c>
       <c r="B102" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C102" s="2">
         <v>47118</v>
@@ -3682,7 +3643,7 @@
         <v>16</v>
       </c>
       <c r="F102" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G102">
         <v>87.106585173736121</v>
@@ -3699,7 +3660,7 @@
         <v>245</v>
       </c>
       <c r="B103" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C103" s="2">
         <v>47299</v>
@@ -3711,7 +3672,7 @@
         <v>17</v>
       </c>
       <c r="F103" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G103">
         <v>87.208095454450159</v>
@@ -3728,7 +3689,7 @@
         <v>245</v>
       </c>
       <c r="B104" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C104" s="2">
         <v>47483</v>
@@ -3740,7 +3701,7 @@
         <v>18</v>
       </c>
       <c r="F104" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G104">
         <v>87.309724030894301</v>
@@ -3757,7 +3718,7 @@
         <v>245</v>
       </c>
       <c r="B105" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C105" s="2">
         <v>47664</v>
@@ -3769,7 +3730,7 @@
         <v>19</v>
       </c>
       <c r="F105" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G105">
         <v>87.411471040925349</v>
@@ -3786,7 +3747,7 @@
         <v>245</v>
       </c>
       <c r="B106" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C106" s="2">
         <v>47848</v>
@@ -3798,7 +3759,7 @@
         <v>20</v>
       </c>
       <c r="F106" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G106">
         <v>87.513336622560715</v>
@@ -3815,7 +3776,7 @@
         <v>245</v>
       </c>
       <c r="B107" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C107" s="2">
         <v>46203</v>
@@ -3827,7 +3788,7 @@
         <v>10</v>
       </c>
       <c r="F107" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G107">
         <v>86.53</v>
@@ -3844,7 +3805,7 @@
         <v>245</v>
       </c>
       <c r="B108" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C108" s="2">
         <v>46387</v>
@@ -3856,7 +3817,7 @@
         <v>12</v>
       </c>
       <c r="F108" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G108">
         <v>87.215000000000003</v>
@@ -3873,7 +3834,7 @@
         <v>245</v>
       </c>
       <c r="B109" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C109" s="2">
         <v>46568</v>
@@ -3885,7 +3846,7 @@
         <v>13</v>
       </c>
       <c r="F109" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G109">
         <v>87.9</v>
@@ -3902,7 +3863,7 @@
         <v>245</v>
       </c>
       <c r="B110" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C110" s="2">
         <v>46752</v>
@@ -3914,7 +3875,7 @@
         <v>14</v>
       </c>
       <c r="F110" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G110">
         <v>88.585000000000008</v>
@@ -3931,7 +3892,7 @@
         <v>245</v>
       </c>
       <c r="B111" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C111" s="2">
         <v>46934</v>
@@ -3943,7 +3904,7 @@
         <v>15</v>
       </c>
       <c r="F111" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G111">
         <v>89.27000000000001</v>
@@ -3960,7 +3921,7 @@
         <v>245</v>
       </c>
       <c r="B112" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C112" s="2">
         <v>47118</v>
@@ -3972,7 +3933,7 @@
         <v>16</v>
       </c>
       <c r="F112" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G112">
         <v>89.955000000000013</v>
@@ -3989,7 +3950,7 @@
         <v>245</v>
       </c>
       <c r="B113" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C113" s="2">
         <v>47299</v>
@@ -4001,7 +3962,7 @@
         <v>17</v>
       </c>
       <c r="F113" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G113">
         <v>90.640000000000015</v>
@@ -4018,7 +3979,7 @@
         <v>245</v>
       </c>
       <c r="B114" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C114" s="2">
         <v>47483</v>
@@ -4030,7 +3991,7 @@
         <v>18</v>
       </c>
       <c r="F114" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G114">
         <v>91.325000000000017</v>
@@ -4047,7 +4008,7 @@
         <v>245</v>
       </c>
       <c r="B115" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C115" s="2">
         <v>47664</v>
@@ -4059,7 +4020,7 @@
         <v>19</v>
       </c>
       <c r="F115" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G115">
         <v>92.010000000000019</v>
@@ -4076,7 +4037,7 @@
         <v>245</v>
       </c>
       <c r="B116" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C116" s="2">
         <v>47848</v>
@@ -4088,7 +4049,7 @@
         <v>20</v>
       </c>
       <c r="F116" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G116">
         <v>92.695000000000022</v>
@@ -4105,7 +4066,7 @@
         <v>276</v>
       </c>
       <c r="B117" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C117" s="2">
         <v>46203</v>
@@ -4134,7 +4095,7 @@
         <v>276</v>
       </c>
       <c r="B118" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C118" s="2">
         <v>46387</v>
@@ -4163,7 +4124,7 @@
         <v>276</v>
       </c>
       <c r="B119" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C119" s="2">
         <v>46568</v>
@@ -4192,7 +4153,7 @@
         <v>276</v>
       </c>
       <c r="B120" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C120" s="2">
         <v>46752</v>
@@ -4221,7 +4182,7 @@
         <v>276</v>
       </c>
       <c r="B121" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C121" s="2">
         <v>46934</v>
@@ -4250,7 +4211,7 @@
         <v>276</v>
       </c>
       <c r="B122" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C122" s="2">
         <v>47118</v>
@@ -4279,7 +4240,7 @@
         <v>276</v>
       </c>
       <c r="B123" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C123" s="2">
         <v>47299</v>
@@ -4308,7 +4269,7 @@
         <v>276</v>
       </c>
       <c r="B124" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C124" s="2">
         <v>47483</v>
@@ -4337,7 +4298,7 @@
         <v>276</v>
       </c>
       <c r="B125" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C125" s="2">
         <v>47664</v>
@@ -4366,7 +4327,7 @@
         <v>276</v>
       </c>
       <c r="B126" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C126" s="2">
         <v>47848</v>
@@ -4395,7 +4356,7 @@
         <v>276</v>
       </c>
       <c r="B127" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C127" s="2">
         <v>46203</v>
@@ -4407,16 +4368,16 @@
         <v>10</v>
       </c>
       <c r="F127" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G127">
-        <v>79.60324432576769</v>
+        <v>82.234038282271925</v>
       </c>
       <c r="H127">
-        <v>83.329331605164725</v>
+        <v>86.083268380521034</v>
       </c>
       <c r="I127">
-        <v>67.115704744213033</v>
+        <v>69.3338001487799</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
@@ -4424,7 +4385,7 @@
         <v>276</v>
       </c>
       <c r="B128" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C128" s="2">
         <v>46387</v>
@@ -4436,16 +4397,16 @@
         <v>12</v>
       </c>
       <c r="F128" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G128">
-        <v>76.863641522029383</v>
+        <v>80.333060729510137</v>
       </c>
       <c r="H128">
-        <v>80.569428371920111</v>
+        <v>84.206116886725511</v>
       </c>
       <c r="I128">
-        <v>64.444136422217625</v>
+        <v>67.352972385300021</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
@@ -4453,7 +4414,7 @@
         <v>276</v>
       </c>
       <c r="B129" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C129" s="2">
         <v>46568</v>
@@ -4465,16 +4426,16 @@
         <v>13</v>
       </c>
       <c r="F129" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G129">
-        <v>73.946281708945278</v>
+        <v>78.476027457384305</v>
       </c>
       <c r="H129">
-        <v>77.615254250029693</v>
+        <v>82.369751160866997</v>
       </c>
       <c r="I129">
-        <v>61.650155398709487</v>
+        <v>65.426674283148913</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
@@ -4482,7 +4443,7 @@
         <v>276</v>
       </c>
       <c r="B130" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C130" s="2">
         <v>46752</v>
@@ -4494,16 +4455,16 @@
         <v>14</v>
       </c>
       <c r="F130" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G130">
-        <v>70.851164886515363</v>
+        <v>76.661922620232403</v>
       </c>
       <c r="H130">
-        <v>74.466060395243119</v>
+        <v>80.573288653722372</v>
       </c>
       <c r="I130">
-        <v>58.736271336376369</v>
+        <v>63.553443269459287</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
@@ -4511,7 +4472,7 @@
         <v>276</v>
       </c>
       <c r="B131" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C131" s="2">
         <v>46934</v>
@@ -4523,16 +4484,16 @@
         <v>15</v>
       </c>
       <c r="F131" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G131">
-        <v>67.578291054739665</v>
+        <v>74.889753855366578</v>
       </c>
       <c r="H131">
-        <v>71.121097963310092</v>
+        <v>78.815865824149853</v>
       </c>
       <c r="I131">
-        <v>55.704993897906057</v>
+        <v>61.731855251410558</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
@@ -4540,7 +4501,7 @@
         <v>276</v>
       </c>
       <c r="B132" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C132" s="2">
         <v>47118</v>
@@ -4552,16 +4513,16 @@
         <v>16</v>
       </c>
       <c r="F132" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G132">
-        <v>64.127660213618185</v>
+        <v>73.158551740224951</v>
       </c>
       <c r="H132">
-        <v>67.579618109980302</v>
+        <v>77.096637731899037</v>
       </c>
       <c r="I132">
-        <v>52.558832745986322</v>
+        <v>59.960523618738179</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
@@ -4569,7 +4530,7 @@
         <v>276</v>
       </c>
       <c r="B133" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C133" s="2">
         <v>47299</v>
@@ -4581,16 +4542,16 @@
         <v>17</v>
       </c>
       <c r="F133" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G133">
-        <v>60.499272363150887</v>
+        <v>71.467369262072097</v>
       </c>
       <c r="H133">
-        <v>63.840871991003347</v>
+        <v>75.414777639089081</v>
       </c>
       <c r="I133">
-        <v>49.300297543304907</v>
+        <v>58.238098271797057</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
@@ -4598,7 +4559,7 @@
         <v>276</v>
       </c>
       <c r="B134" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C134" s="2">
         <v>47483</v>
@@ -4610,16 +4571,16 @@
         <v>18</v>
       </c>
       <c r="F134" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G134">
-        <v>56.693127503337813</v>
+        <v>69.815281299958414</v>
       </c>
       <c r="H134">
-        <v>59.90411076212893</v>
+        <v>73.769476620171801</v>
       </c>
       <c r="I134">
-        <v>45.931897952549583</v>
+        <v>56.563264674531062</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
@@ -4627,7 +4588,7 @@
         <v>276</v>
       </c>
       <c r="B135" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C135" s="2">
         <v>47664</v>
@@ -4639,16 +4600,16 @@
         <v>19</v>
       </c>
       <c r="F135" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G135">
-        <v>52.709225634178942</v>
+        <v>68.201384118654829</v>
       </c>
       <c r="H135">
-        <v>55.76858557910672</v>
+        <v>72.159943180200727</v>
       </c>
       <c r="I135">
-        <v>42.456143636408108</v>
+        <v>54.934742931716322</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
@@ -4656,7 +4617,7 @@
         <v>276</v>
       </c>
       <c r="B136" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C136" s="2">
         <v>47848</v>
@@ -4668,16 +4629,16 @@
         <v>20</v>
       </c>
       <c r="F136" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G136">
-        <v>48.547566755674268</v>
+        <v>66.624794874285968</v>
       </c>
       <c r="H136">
-        <v>51.433547597686378</v>
+        <v>70.585402881230067</v>
       </c>
       <c r="I136">
-        <v>38.875544257568272</v>
+        <v>53.351286889862124</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
@@ -4685,7 +4646,7 @@
         <v>277</v>
       </c>
       <c r="B137" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C137" s="2">
         <v>46203</v>
@@ -4714,7 +4675,7 @@
         <v>277</v>
       </c>
       <c r="B138" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C138" s="2">
         <v>46387</v>
@@ -4743,7 +4704,7 @@
         <v>277</v>
       </c>
       <c r="B139" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C139" s="2">
         <v>46568</v>
@@ -4772,7 +4733,7 @@
         <v>277</v>
       </c>
       <c r="B140" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C140" s="2">
         <v>46752</v>
@@ -4801,7 +4762,7 @@
         <v>277</v>
       </c>
       <c r="B141" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C141" s="2">
         <v>46934</v>
@@ -4830,7 +4791,7 @@
         <v>277</v>
       </c>
       <c r="B142" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C142" s="2">
         <v>47118</v>
@@ -4859,7 +4820,7 @@
         <v>277</v>
       </c>
       <c r="B143" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C143" s="2">
         <v>47299</v>
@@ -4888,7 +4849,7 @@
         <v>277</v>
       </c>
       <c r="B144" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C144" s="2">
         <v>47483</v>
@@ -4917,7 +4878,7 @@
         <v>277</v>
       </c>
       <c r="B145" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C145" s="2">
         <v>47664</v>
@@ -4946,7 +4907,7 @@
         <v>277</v>
       </c>
       <c r="B146" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C146" s="2">
         <v>47848</v>
@@ -4975,7 +4936,7 @@
         <v>277</v>
       </c>
       <c r="B147" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C147" s="2">
         <v>46203</v>
@@ -4987,16 +4948,16 @@
         <v>10</v>
       </c>
       <c r="F147" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G147">
-        <v>68.542208955223884</v>
+        <v>67.888278699901591</v>
       </c>
       <c r="H147">
-        <v>71.308385317087897</v>
+        <v>70.628064222570998</v>
       </c>
       <c r="I147">
-        <v>66.485942686567171</v>
+        <v>65.851630338904542</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
@@ -5004,7 +4965,7 @@
         <v>277</v>
       </c>
       <c r="B148" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C148" s="2">
         <v>46387</v>
@@ -5016,16 +4977,16 @@
         <v>12</v>
       </c>
       <c r="F148" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G148">
-        <v>66.803507462686554</v>
+        <v>66.419057282540876</v>
       </c>
       <c r="H148">
-        <v>69.580394794319162</v>
+        <v>69.179963794072279</v>
       </c>
       <c r="I148">
-        <v>64.739279082089539</v>
+        <v>64.366708412510363</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
@@ -5033,7 +4994,7 @@
         <v>277</v>
       </c>
       <c r="B149" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C149" s="2">
         <v>46568</v>
@@ -5045,16 +5006,16 @@
         <v>13</v>
       </c>
       <c r="F149" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G149">
-        <v>64.858761194029839</v>
+        <v>64.9816323934553</v>
       </c>
       <c r="H149">
-        <v>67.633335012090257</v>
+        <v>67.761462482320823</v>
       </c>
       <c r="I149">
-        <v>62.796252588059687</v>
+        <v>62.915216483343421</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.3">
@@ -5062,7 +5023,7 @@
         <v>277</v>
       </c>
       <c r="B150" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C150" s="2">
         <v>46752</v>
@@ -5074,16 +5035,16 @@
         <v>14</v>
       </c>
       <c r="F150" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G150">
-        <v>62.707970149253718</v>
+        <v>63.57531590000643</v>
       </c>
       <c r="H150">
-        <v>65.466457584000892</v>
+        <v>66.371957374014286</v>
       </c>
       <c r="I150">
-        <v>60.657419525373108</v>
+        <v>61.496403070076219</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
@@ -5091,7 +5052,7 @@
         <v>277</v>
       </c>
       <c r="B151" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C151" s="2">
         <v>46934</v>
@@ -5103,16 +5064,16 @@
         <v>15</v>
       </c>
       <c r="F151" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G151">
-        <v>60.351134328358192</v>
+        <v>62.199434561953034</v>
       </c>
       <c r="H151">
-        <v>63.079014123650779</v>
+        <v>65.010857788847503</v>
       </c>
       <c r="I151">
-        <v>58.323336214925362</v>
+        <v>60.109533560671402</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
@@ -5120,7 +5081,7 @@
         <v>277</v>
       </c>
       <c r="B152" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C152" s="2">
         <v>47118</v>
@@ -5132,16 +5093,16 @@
         <v>16</v>
       </c>
       <c r="F152" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G152">
-        <v>57.788253731343261</v>
+        <v>60.853329709153464</v>
       </c>
       <c r="H152">
-        <v>60.470256244639657</v>
+        <v>63.677585032409269</v>
       </c>
       <c r="I152">
-        <v>55.794558977611921</v>
+        <v>58.75388983418766</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
@@ -5149,7 +5110,7 @@
         <v>277</v>
       </c>
       <c r="B153" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C153" s="2">
         <v>47299</v>
@@ -5161,16 +5122,16 @@
         <v>17</v>
       </c>
       <c r="F153" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G153">
-        <v>55.019328358208917</v>
+        <v>59.536356926243137</v>
       </c>
       <c r="H153">
-        <v>57.63943556056725</v>
+        <v>62.371572154045019</v>
       </c>
       <c r="I153">
-        <v>53.071644134328317</v>
+        <v>57.428769891054131</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.3">
@@ -5178,7 +5139,7 @@
         <v>277</v>
       </c>
       <c r="B154" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C154" s="2">
         <v>47483</v>
@@ -5190,16 +5151,16 @@
         <v>18</v>
       </c>
       <c r="F154" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G154">
-        <v>52.044358208955188</v>
+        <v>58.247885744136177</v>
       </c>
       <c r="H154">
-        <v>54.585803685033291</v>
+        <v>61.092263709586383</v>
       </c>
       <c r="I154">
-        <v>50.155148005970112</v>
+        <v>56.133487491624052</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.3">
@@ -5207,7 +5168,7 @@
         <v>277</v>
       </c>
       <c r="B155" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C155" s="2">
         <v>47664</v>
@@ -5219,16 +5180,16 @@
         <v>19</v>
       </c>
       <c r="F155" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G155">
-        <v>48.863343283582047</v>
+        <v>56.987299338203513</v>
       </c>
       <c r="H155">
-        <v>51.308612231637497</v>
+        <v>59.839115528850272</v>
       </c>
       <c r="I155">
-        <v>47.045626913432791</v>
+        <v>54.867371802822348</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
@@ -5236,7 +5197,7 @@
         <v>277</v>
       </c>
       <c r="B156" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C156" s="2">
         <v>47848</v>
@@ -5248,16 +5209,16 @@
         <v>20</v>
       </c>
       <c r="F156" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G156">
-        <v>45.476283582089508</v>
+        <v>55.753994232982812</v>
       </c>
       <c r="H156">
-        <v>47.8071128139796</v>
+        <v>58.611594487812098</v>
       </c>
       <c r="I156">
-        <v>43.743637177611888</v>
+        <v>53.629767052706171</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
@@ -5265,7 +5226,7 @@
         <v>325</v>
       </c>
       <c r="B157" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C157" s="2">
         <v>46387</v>
@@ -5294,7 +5255,7 @@
         <v>325</v>
       </c>
       <c r="B158" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C158" s="2">
         <v>46752</v>
@@ -5323,7 +5284,7 @@
         <v>325</v>
       </c>
       <c r="B159" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C159" s="2">
         <v>47118</v>
@@ -5352,7 +5313,7 @@
         <v>325</v>
       </c>
       <c r="B160" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C160" s="2">
         <v>47483</v>
@@ -5381,7 +5342,7 @@
         <v>325</v>
       </c>
       <c r="B161" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C161" s="2">
         <v>47848</v>
@@ -5410,7 +5371,7 @@
         <v>332</v>
       </c>
       <c r="B162" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C162" s="2">
         <v>46387</v>
@@ -5439,7 +5400,7 @@
         <v>332</v>
       </c>
       <c r="B163" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C163" s="2">
         <v>46752</v>
@@ -5468,7 +5429,7 @@
         <v>332</v>
       </c>
       <c r="B164" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C164" s="2">
         <v>47118</v>
@@ -5497,7 +5458,7 @@
         <v>332</v>
       </c>
       <c r="B165" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C165" s="2">
         <v>47483</v>
@@ -5526,7 +5487,7 @@
         <v>332</v>
       </c>
       <c r="B166" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C166" s="2">
         <v>47848</v>
@@ -5555,7 +5516,7 @@
         <v>332</v>
       </c>
       <c r="B167" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C167" s="2">
         <v>46387</v>
@@ -5567,7 +5528,7 @@
         <v>12</v>
       </c>
       <c r="F167" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G167">
         <v>1.0249999999999999</v>
@@ -5584,7 +5545,7 @@
         <v>332</v>
       </c>
       <c r="B168" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C168" s="2">
         <v>46752</v>
@@ -5596,7 +5557,7 @@
         <v>14</v>
       </c>
       <c r="F168" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G168">
         <v>0.89999999999999991</v>
@@ -5613,7 +5574,7 @@
         <v>332</v>
       </c>
       <c r="B169" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C169" s="2">
         <v>47118</v>
@@ -5625,7 +5586,7 @@
         <v>16</v>
       </c>
       <c r="F169" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G169">
         <v>0.77499999999999991</v>
@@ -5642,7 +5603,7 @@
         <v>332</v>
       </c>
       <c r="B170" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C170" s="2">
         <v>47483</v>
@@ -5654,7 +5615,7 @@
         <v>18</v>
       </c>
       <c r="F170" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G170">
         <v>0.64999999999999991</v>
@@ -5671,7 +5632,7 @@
         <v>332</v>
       </c>
       <c r="B171" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C171" s="2">
         <v>47848</v>
@@ -5683,7 +5644,7 @@
         <v>20</v>
       </c>
       <c r="F171" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G171">
         <v>0.52499999999999991</v>
@@ -5700,7 +5661,7 @@
         <v>334</v>
       </c>
       <c r="B172" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C172" s="2">
         <v>46387</v>
@@ -5729,7 +5690,7 @@
         <v>334</v>
       </c>
       <c r="B173" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C173" s="2">
         <v>46752</v>
@@ -5758,7 +5719,7 @@
         <v>334</v>
       </c>
       <c r="B174" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C174" s="2">
         <v>47118</v>
@@ -5787,7 +5748,7 @@
         <v>334</v>
       </c>
       <c r="B175" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C175" s="2">
         <v>47483</v>
@@ -5816,7 +5777,7 @@
         <v>334</v>
       </c>
       <c r="B176" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C176" s="2">
         <v>47848</v>
@@ -5845,7 +5806,7 @@
         <v>334</v>
       </c>
       <c r="B177" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C177" s="2">
         <v>46387</v>
@@ -5874,7 +5835,7 @@
         <v>334</v>
       </c>
       <c r="B178" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C178" s="2">
         <v>46752</v>
@@ -5903,7 +5864,7 @@
         <v>334</v>
       </c>
       <c r="B179" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C179" s="2">
         <v>47118</v>
@@ -5932,7 +5893,7 @@
         <v>334</v>
       </c>
       <c r="B180" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C180" s="2">
         <v>47483</v>
@@ -5961,7 +5922,7 @@
         <v>334</v>
       </c>
       <c r="B181" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C181" s="2">
         <v>47848</v>
@@ -5990,7 +5951,7 @@
         <v>361</v>
       </c>
       <c r="B182" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C182" s="2">
         <v>46387</v>
@@ -6002,7 +5963,7 @@
         <v>12</v>
       </c>
       <c r="F182" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G182">
         <v>4.82</v>
@@ -6019,7 +5980,7 @@
         <v>361</v>
       </c>
       <c r="B183" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C183" s="2">
         <v>46752</v>
@@ -6031,7 +5992,7 @@
         <v>14</v>
       </c>
       <c r="F183" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G183">
         <v>4.8499999999999996</v>
@@ -6048,7 +6009,7 @@
         <v>361</v>
       </c>
       <c r="B184" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C184" s="2">
         <v>47118</v>
@@ -6060,7 +6021,7 @@
         <v>16</v>
       </c>
       <c r="F184" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G184">
         <v>4.87</v>
@@ -6077,7 +6038,7 @@
         <v>361</v>
       </c>
       <c r="B185" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C185" s="2">
         <v>47483</v>
@@ -6089,7 +6050,7 @@
         <v>18</v>
       </c>
       <c r="F185" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G185">
         <v>4.91</v>
@@ -6106,7 +6067,7 @@
         <v>361</v>
       </c>
       <c r="B186" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C186" s="2">
         <v>47848</v>
@@ -6118,7 +6079,7 @@
         <v>20</v>
       </c>
       <c r="F186" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G186">
         <v>4.96</v>
@@ -6135,7 +6096,7 @@
         <v>364</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C187" s="4">
         <v>46387</v>
@@ -6146,8 +6107,8 @@
       <c r="E187" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F187" s="3" t="s">
-        <v>59</v>
+      <c r="F187" t="s">
+        <v>79</v>
       </c>
       <c r="G187" s="3">
         <v>144368.4</v>
@@ -6164,7 +6125,7 @@
         <v>364</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C188" s="4">
         <v>46752</v>
@@ -6175,8 +6136,8 @@
       <c r="E188" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F188" s="3" t="s">
-        <v>59</v>
+      <c r="F188" t="s">
+        <v>79</v>
       </c>
       <c r="G188" s="3">
         <v>158805.24</v>
@@ -6193,7 +6154,7 @@
         <v>364</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C189" s="4">
         <v>47118</v>
@@ -6204,8 +6165,8 @@
       <c r="E189" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F189" s="3" t="s">
-        <v>59</v>
+      <c r="F189" t="s">
+        <v>79</v>
       </c>
       <c r="G189" s="3">
         <v>174685.76400000011</v>
@@ -6222,7 +6183,7 @@
         <v>364</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C190" s="4">
         <v>47483</v>
@@ -6233,8 +6194,8 @@
       <c r="E190" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F190" s="3" t="s">
-        <v>59</v>
+      <c r="F190" t="s">
+        <v>79</v>
       </c>
       <c r="G190" s="3">
         <v>192154.34039999999</v>
@@ -6251,7 +6212,7 @@
         <v>364</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C191" s="4">
         <v>47848</v>
@@ -6262,8 +6223,8 @@
       <c r="E191" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F191" s="3" t="s">
-        <v>59</v>
+      <c r="F191" t="s">
+        <v>79</v>
       </c>
       <c r="G191" s="3">
         <v>211369.7744400001</v>
@@ -6280,7 +6241,7 @@
         <v>367</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C192" s="4">
         <v>46387</v>
@@ -6291,8 +6252,8 @@
       <c r="E192" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F192" s="3" t="s">
-        <v>61</v>
+      <c r="F192" t="s">
+        <v>34</v>
       </c>
       <c r="G192" s="3">
         <v>5.0095999999999998</v>
@@ -6309,7 +6270,7 @@
         <v>367</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C193" s="4">
         <v>46752</v>
@@ -6320,8 +6281,8 @@
       <c r="E193" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F193" s="3" t="s">
-        <v>61</v>
+      <c r="F193" t="s">
+        <v>34</v>
       </c>
       <c r="G193" s="3">
         <v>5.0596959999999997</v>
@@ -6338,7 +6299,7 @@
         <v>367</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C194" s="4">
         <v>47118</v>
@@ -6349,8 +6310,8 @@
       <c r="E194" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F194" s="3" t="s">
-        <v>61</v>
+      <c r="F194" t="s">
+        <v>34</v>
       </c>
       <c r="G194" s="3">
         <v>5.1102929600000007</v>
@@ -6367,7 +6328,7 @@
         <v>367</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C195" s="4">
         <v>47483</v>
@@ -6378,8 +6339,8 @@
       <c r="E195" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F195" s="3" t="s">
-        <v>61</v>
+      <c r="F195" t="s">
+        <v>34</v>
       </c>
       <c r="G195" s="3">
         <v>5.1613958896000014</v>
@@ -6396,7 +6357,7 @@
         <v>367</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C196" s="4">
         <v>47848</v>
@@ -6407,8 +6368,8 @@
       <c r="E196" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F196" s="3" t="s">
-        <v>61</v>
+      <c r="F196" t="s">
+        <v>34</v>
       </c>
       <c r="G196" s="3">
         <v>5.213009848496001</v>
@@ -6425,7 +6386,7 @@
         <v>369</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C197" s="4">
         <v>46387</v>
@@ -6436,8 +6397,8 @@
       <c r="E197" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F197" s="3" t="s">
-        <v>63</v>
+      <c r="F197" t="s">
+        <v>79</v>
       </c>
       <c r="G197" s="3">
         <v>73.44</v>
@@ -6454,7 +6415,7 @@
         <v>369</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C198" s="4">
         <v>46752</v>
@@ -6465,8 +6426,8 @@
       <c r="E198" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F198" s="3" t="s">
-        <v>63</v>
+      <c r="F198" t="s">
+        <v>79</v>
       </c>
       <c r="G198" s="3">
         <v>74.908799999999999</v>
@@ -6483,7 +6444,7 @@
         <v>369</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C199" s="4">
         <v>47118</v>
@@ -6494,8 +6455,8 @@
       <c r="E199" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F199" s="3" t="s">
-        <v>63</v>
+      <c r="F199" t="s">
+        <v>79</v>
       </c>
       <c r="G199" s="3">
         <v>76.406976000000014</v>
@@ -6512,7 +6473,7 @@
         <v>369</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C200" s="4">
         <v>47483</v>
@@ -6523,8 +6484,8 @@
       <c r="E200" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F200" s="3" t="s">
-        <v>63</v>
+      <c r="F200" t="s">
+        <v>79</v>
       </c>
       <c r="G200" s="3">
         <v>77.935115519999997</v>
@@ -6541,7 +6502,7 @@
         <v>369</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C201" s="4">
         <v>47848</v>
@@ -6552,8 +6513,8 @@
       <c r="E201" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F201" s="3" t="s">
-        <v>63</v>
+      <c r="F201" t="s">
+        <v>79</v>
       </c>
       <c r="G201" s="3">
         <v>79.493817830400005</v>
@@ -6570,7 +6531,7 @@
         <v>377</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C202" s="4">
         <v>46387</v>
@@ -6581,8 +6542,8 @@
       <c r="E202" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F202" s="3" t="s">
-        <v>66</v>
+      <c r="F202" t="s">
+        <v>79</v>
       </c>
       <c r="G202" s="3">
         <v>13739.770610699999</v>
@@ -6599,7 +6560,7 @@
         <v>377</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C203" s="4">
         <v>46752</v>
@@ -6610,8 +6571,8 @@
       <c r="E203" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F203" s="3" t="s">
-        <v>66</v>
+      <c r="F203" t="s">
+        <v>79</v>
       </c>
       <c r="G203" s="3">
         <v>15800.736202304999</v>
@@ -6628,7 +6589,7 @@
         <v>377</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C204" s="4">
         <v>47118</v>
@@ -6639,8 +6600,8 @@
       <c r="E204" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F204" s="3" t="s">
-        <v>66</v>
+      <c r="F204" t="s">
+        <v>79</v>
       </c>
       <c r="G204" s="3">
         <v>18170.846632650751</v>
@@ -6657,7 +6618,7 @@
         <v>377</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C205" s="4">
         <v>47483</v>
@@ -6668,8 +6629,8 @@
       <c r="E205" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F205" s="3" t="s">
-        <v>66</v>
+      <c r="F205" t="s">
+        <v>79</v>
       </c>
       <c r="G205" s="3">
         <v>20896.473627548359</v>
@@ -6686,7 +6647,7 @@
         <v>377</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C206" s="4">
         <v>47848</v>
@@ -6697,8 +6658,8 @@
       <c r="E206" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F206" s="3" t="s">
-        <v>66</v>
+      <c r="F206" t="s">
+        <v>79</v>
       </c>
       <c r="G206" s="3">
         <v>24030.944671680609</v>
@@ -6715,7 +6676,7 @@
         <v>424</v>
       </c>
       <c r="B207" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C207" s="2">
         <v>46387</v>
@@ -6744,7 +6705,7 @@
         <v>424</v>
       </c>
       <c r="B208" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C208" s="2">
         <v>46752</v>
@@ -6773,7 +6734,7 @@
         <v>424</v>
       </c>
       <c r="B209" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C209" s="2">
         <v>47118</v>
@@ -6802,7 +6763,7 @@
         <v>424</v>
       </c>
       <c r="B210" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C210" s="2">
         <v>47483</v>
@@ -6831,7 +6792,7 @@
         <v>424</v>
       </c>
       <c r="B211" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C211" s="2">
         <v>47848</v>
@@ -6860,7 +6821,7 @@
         <v>460</v>
       </c>
       <c r="B212" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C212" s="2">
         <v>46387</v>
@@ -6872,7 +6833,7 @@
         <v>12</v>
       </c>
       <c r="F212" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="G212">
         <v>92.354399999999998</v>
@@ -6889,7 +6850,7 @@
         <v>460</v>
       </c>
       <c r="B213" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C213" s="2">
         <v>46752</v>
@@ -6901,7 +6862,7 @@
         <v>14</v>
       </c>
       <c r="F213" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="G213">
         <v>93.277944000000005</v>
@@ -6918,7 +6879,7 @@
         <v>460</v>
       </c>
       <c r="B214" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C214" s="2">
         <v>47118</v>
@@ -6930,7 +6891,7 @@
         <v>16</v>
       </c>
       <c r="F214" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="G214">
         <v>94.21072344000001</v>
@@ -6947,7 +6908,7 @@
         <v>460</v>
       </c>
       <c r="B215" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C215" s="2">
         <v>47483</v>
@@ -6959,7 +6920,7 @@
         <v>18</v>
       </c>
       <c r="F215" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="G215">
         <v>95.152830674399993</v>
@@ -6976,7 +6937,7 @@
         <v>460</v>
       </c>
       <c r="B216" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C216" s="2">
         <v>47848</v>
@@ -6988,7 +6949,7 @@
         <v>20</v>
       </c>
       <c r="F216" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="G216">
         <v>96.104358981144017</v>
@@ -7005,7 +6966,7 @@
         <v>77</v>
       </c>
       <c r="B217" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C217" s="2">
         <v>46387</v>
@@ -7017,7 +6978,7 @@
         <v>12</v>
       </c>
       <c r="F217" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="G217">
         <v>95.596500000000006</v>
@@ -7034,7 +6995,7 @@
         <v>77</v>
       </c>
       <c r="B218" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C218" s="2">
         <v>46752</v>
@@ -7046,7 +7007,7 @@
         <v>14</v>
       </c>
       <c r="F218" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="G218">
         <v>96.552465000000012</v>
@@ -7063,7 +7024,7 @@
         <v>77</v>
       </c>
       <c r="B219" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C219" s="2">
         <v>47118</v>
@@ -7075,7 +7036,7 @@
         <v>16</v>
       </c>
       <c r="F219" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="G219">
         <v>97.517989650000018</v>
@@ -7092,7 +7053,7 @@
         <v>77</v>
       </c>
       <c r="B220" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C220" s="2">
         <v>47483</v>
@@ -7104,7 +7065,7 @@
         <v>18</v>
       </c>
       <c r="F220" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="G220">
         <v>98.493169546500013</v>
@@ -7121,7 +7082,7 @@
         <v>77</v>
       </c>
       <c r="B221" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C221" s="2">
         <v>47848</v>
@@ -7133,7 +7094,7 @@
         <v>20</v>
       </c>
       <c r="F221" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="G221">
         <v>99.478101241965021</v>
@@ -7150,7 +7111,7 @@
         <v>98</v>
       </c>
       <c r="B222" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C222" s="2">
         <v>46387</v>
@@ -7179,7 +7140,7 @@
         <v>98</v>
       </c>
       <c r="B223" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C223" s="2">
         <v>46752</v>
@@ -7208,7 +7169,7 @@
         <v>98</v>
       </c>
       <c r="B224" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C224" s="2">
         <v>47118</v>
@@ -7237,7 +7198,7 @@
         <v>98</v>
       </c>
       <c r="B225" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C225" s="2">
         <v>47483</v>
@@ -7266,7 +7227,7 @@
         <v>98</v>
       </c>
       <c r="B226" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C226" s="2">
         <v>47848</v>
@@ -7295,7 +7256,7 @@
         <v>386.1</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C227" s="4">
         <v>46387</v>
@@ -7324,7 +7285,7 @@
         <v>386.1</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C228" s="4">
         <v>46752</v>
@@ -7353,7 +7314,7 @@
         <v>386.1</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C229" s="4">
         <v>47118</v>
@@ -7382,7 +7343,7 @@
         <v>386.1</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C230" s="4">
         <v>47483</v>
@@ -7411,7 +7372,7 @@
         <v>386.1</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C231" s="4">
         <v>47848</v>
@@ -7440,7 +7401,7 @@
         <v>386.2</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C232" s="4">
         <v>46387</v>
@@ -7452,7 +7413,7 @@
         <v>12</v>
       </c>
       <c r="F232" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="G232">
         <v>8322.3104068060129</v>
@@ -7469,7 +7430,7 @@
         <v>386.2</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C233" s="4">
         <v>46752</v>
@@ -7481,7 +7442,7 @@
         <v>14</v>
       </c>
       <c r="F233" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="G233">
         <v>9300.7150739219178</v>
@@ -7498,7 +7459,7 @@
         <v>386.2</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C234" s="4">
         <v>47118</v>
@@ -7510,7 +7471,7 @@
         <v>16</v>
       </c>
       <c r="F234" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="G234">
         <v>10394.14497391682</v>
@@ -7527,7 +7488,7 @@
         <v>386.2</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C235" s="4">
         <v>47483</v>
@@ -7539,7 +7500,7 @@
         <v>18</v>
       </c>
       <c r="F235" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="G235">
         <v>11616.122941098</v>
@@ -7556,7 +7517,7 @@
         <v>386.2</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C236" s="4">
         <v>47848</v>
@@ -7568,7 +7529,7 @@
         <v>20</v>
       </c>
       <c r="F236" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="G236">
         <v>12981.76160918564</v>
@@ -7585,7 +7546,7 @@
         <v>386.3</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C237" s="4">
         <v>46387</v>
@@ -7614,7 +7575,7 @@
         <v>386.3</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C238" s="4">
         <v>46752</v>
@@ -7643,7 +7604,7 @@
         <v>386.3</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C239" s="4">
         <v>47118</v>
@@ -7672,7 +7633,7 @@
         <v>386.3</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C240" s="4">
         <v>47483</v>
@@ -7701,7 +7662,7 @@
         <v>386.3</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C241" s="4">
         <v>47848</v>
@@ -7730,7 +7691,7 @@
         <v>379</v>
       </c>
       <c r="B242" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C242" s="2">
         <v>46203</v>
@@ -7742,7 +7703,7 @@
         <v>10</v>
       </c>
       <c r="F242" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G242">
         <v>12524.007412694569</v>
@@ -7759,7 +7720,7 @@
         <v>274</v>
       </c>
       <c r="B243" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C243" s="2">
         <v>46203</v>
@@ -7771,7 +7732,7 @@
         <v>10</v>
       </c>
       <c r="F243" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G243">
         <v>43311.880111304308</v>
@@ -7788,7 +7749,7 @@
         <v>379</v>
       </c>
       <c r="B244" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C244" s="2">
         <v>46387</v>
@@ -7800,7 +7761,7 @@
         <v>12</v>
       </c>
       <c r="F244" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G244">
         <v>12596.339833898201</v>
@@ -7817,7 +7778,7 @@
         <v>274</v>
       </c>
       <c r="B245" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C245" s="2">
         <v>46387</v>
@@ -7829,7 +7790,7 @@
         <v>12</v>
       </c>
       <c r="F245" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G245">
         <v>43562.027931574383</v>
@@ -7846,7 +7807,7 @@
         <v>379</v>
       </c>
       <c r="B246" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C246" s="2">
         <v>46568</v>
@@ -7858,7 +7819,7 @@
         <v>13</v>
       </c>
       <c r="F246" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G246">
         <v>12684.76580268722</v>
@@ -7875,7 +7836,7 @@
         <v>274</v>
       </c>
       <c r="B247" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C247" s="2">
         <v>46568</v>
@@ -7887,7 +7848,7 @@
         <v>13</v>
       </c>
       <c r="F247" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G247">
         <v>43867.832202740341</v>
@@ -7904,7 +7865,7 @@
         <v>379</v>
       </c>
       <c r="B248" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C248" s="2">
         <v>46752</v>
@@ -7916,7 +7877,7 @@
         <v>14</v>
       </c>
       <c r="F248" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G248">
         <v>12782.81992485196</v>
@@ -7933,7 +7894,7 @@
         <v>274</v>
       </c>
       <c r="B249" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C249" s="2">
         <v>46752</v>
@@ -7945,7 +7906,7 @@
         <v>14</v>
       </c>
       <c r="F249" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G249">
         <v>44206.933597659161</v>
@@ -7962,7 +7923,7 @@
         <v>379</v>
       </c>
       <c r="B250" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C250" s="2">
         <v>46934</v>
@@ -7974,7 +7935,7 @@
         <v>15</v>
       </c>
       <c r="F250" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G250">
         <v>12887.205199203119</v>
@@ -7991,7 +7952,7 @@
         <v>274</v>
       </c>
       <c r="B251" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C251" s="2">
         <v>46934</v>
@@ -8003,7 +7964,7 @@
         <v>15</v>
       </c>
       <c r="F251" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G251">
         <v>44567.930069403526</v>
@@ -8020,7 +7981,7 @@
         <v>379</v>
       </c>
       <c r="B252" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C252" s="2">
         <v>47118</v>
@@ -8032,7 +7993,7 @@
         <v>16</v>
       </c>
       <c r="F252" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G252">
         <v>12996.26184424147</v>
@@ -8049,7 +8010,7 @@
         <v>274</v>
       </c>
       <c r="B253" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C253" s="2">
         <v>47118</v>
@@ -8061,7 +8022,7 @@
         <v>16</v>
       </c>
       <c r="F253" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G253">
         <v>44945.081581662613</v>
@@ -8078,7 +8039,7 @@
         <v>379</v>
       </c>
       <c r="B254" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C254" s="2">
         <v>47299</v>
@@ -8090,7 +8051,7 @@
         <v>17</v>
       </c>
       <c r="F254" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G254">
         <v>13109.17611451162</v>
@@ -8107,7 +8068,7 @@
         <v>274</v>
       </c>
       <c r="B255" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C255" s="2">
         <v>47299</v>
@@ -8119,7 +8080,7 @@
         <v>17</v>
       </c>
       <c r="F255" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G255">
         <v>45335.573951687817</v>
@@ -8136,7 +8097,7 @@
         <v>379</v>
       </c>
       <c r="B256" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C256" s="2">
         <v>47483</v>
@@ -8148,7 +8109,7 @@
         <v>18</v>
       </c>
       <c r="F256" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G256">
         <v>13225.571482829941</v>
@@ -8165,7 +8126,7 @@
         <v>274</v>
       </c>
       <c r="B257" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C257" s="2">
         <v>47483</v>
@@ -8177,7 +8138,7 @@
         <v>18</v>
       </c>
       <c r="F257" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G257">
         <v>45738.105032354877</v>
@@ -8194,7 +8155,7 @@
         <v>379</v>
       </c>
       <c r="B258" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C258" s="2">
         <v>47664</v>
@@ -8206,7 +8167,7 @@
         <v>19</v>
       </c>
       <c r="F258" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G258">
         <v>13345.297397789929</v>
@@ -8223,7 +8184,7 @@
         <v>274</v>
       </c>
       <c r="B259" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C259" s="2">
         <v>47664</v>
@@ -8235,7 +8196,7 @@
         <v>19</v>
       </c>
       <c r="F259" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G259">
         <v>46152.154170469177</v>
@@ -8252,7 +8213,7 @@
         <v>379</v>
       </c>
       <c r="B260" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C260" s="2">
         <v>47848</v>
@@ -8264,7 +8225,7 @@
         <v>20</v>
       </c>
       <c r="F260" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G260">
         <v>13468.320131950481</v>
@@ -8281,7 +8242,7 @@
         <v>274</v>
       </c>
       <c r="B261" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C261" s="2">
         <v>47848</v>
@@ -8293,7 +8254,7 @@
         <v>20</v>
       </c>
       <c r="F261" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G261">
         <v>46577.604726137601</v>
@@ -8612,7 +8573,7 @@
         <v>10</v>
       </c>
       <c r="F272" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G272">
         <v>57181.535034514192</v>
@@ -8641,7 +8602,7 @@
         <v>12</v>
       </c>
       <c r="F273" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G273">
         <v>57651.823600328113</v>
@@ -8670,7 +8631,7 @@
         <v>13</v>
       </c>
       <c r="F274" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G274">
         <v>58122.112166142033</v>
@@ -8699,7 +8660,7 @@
         <v>14</v>
       </c>
       <c r="F275" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G275">
         <v>58592.400731955953</v>
@@ -8728,7 +8689,7 @@
         <v>15</v>
       </c>
       <c r="F276" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G276">
         <v>59062.689297769859</v>
@@ -8757,7 +8718,7 @@
         <v>16</v>
       </c>
       <c r="F277" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G277">
         <v>59532.977863583779</v>
@@ -8786,7 +8747,7 @@
         <v>17</v>
       </c>
       <c r="F278" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G278">
         <v>60003.2664293977</v>
@@ -8815,7 +8776,7 @@
         <v>18</v>
       </c>
       <c r="F279" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G279">
         <v>60473.55499521162</v>
@@ -8844,7 +8805,7 @@
         <v>19</v>
       </c>
       <c r="F280" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G280">
         <v>60943.84356102554</v>
@@ -8873,7 +8834,7 @@
         <v>20</v>
       </c>
       <c r="F281" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G281">
         <v>61414.13212683946</v>
@@ -8890,7 +8851,7 @@
         <v>379</v>
       </c>
       <c r="B282" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C282" s="2">
         <v>46203</v>
@@ -8902,7 +8863,7 @@
         <v>10</v>
       </c>
       <c r="F282" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G282">
         <v>12825.87818782696</v>
@@ -8919,7 +8880,7 @@
         <v>274</v>
       </c>
       <c r="B283" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C283" s="2">
         <v>46203</v>
@@ -8931,7 +8892,7 @@
         <v>10</v>
       </c>
       <c r="F283" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G283">
         <v>44355.842350450519</v>
@@ -8948,7 +8909,7 @@
         <v>379</v>
       </c>
       <c r="B284" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C284" s="2">
         <v>46387</v>
@@ -8960,7 +8921,7 @@
         <v>12</v>
       </c>
       <c r="F284" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G284">
         <v>12931.36440561766</v>
@@ -8977,7 +8938,7 @@
         <v>274</v>
       </c>
       <c r="B285" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C285" s="2">
         <v>46387</v>
@@ -8989,7 +8950,7 @@
         <v>12</v>
       </c>
       <c r="F285" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G285">
         <v>44720.646224146301</v>
@@ -9006,7 +8967,7 @@
         <v>379</v>
       </c>
       <c r="B286" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C286" s="2">
         <v>46568</v>
@@ -9018,7 +8979,7 @@
         <v>13</v>
       </c>
       <c r="F286" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G286">
         <v>13036.850623408351</v>
@@ -9035,7 +8996,7 @@
         <v>274</v>
       </c>
       <c r="B287" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C287" s="2">
         <v>46568</v>
@@ -9047,7 +9008,7 @@
         <v>13</v>
       </c>
       <c r="F287" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G287">
         <v>45085.450097842077</v>
@@ -9064,7 +9025,7 @@
         <v>379</v>
       </c>
       <c r="B288" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C288" s="2">
         <v>46752</v>
@@ -9076,7 +9037,7 @@
         <v>14</v>
       </c>
       <c r="F288" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G288">
         <v>13142.33684119905</v>
@@ -9093,7 +9054,7 @@
         <v>274</v>
       </c>
       <c r="B289" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C289" s="2">
         <v>46752</v>
@@ -9105,7 +9066,7 @@
         <v>14</v>
       </c>
       <c r="F289" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G289">
         <v>45450.253971537859</v>
@@ -9122,7 +9083,7 @@
         <v>379</v>
       </c>
       <c r="B290" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C290" s="2">
         <v>46934</v>
@@ -9134,7 +9095,7 @@
         <v>15</v>
       </c>
       <c r="F290" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G290">
         <v>13247.82305898975</v>
@@ -9151,7 +9112,7 @@
         <v>274</v>
       </c>
       <c r="B291" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C291" s="2">
         <v>46934</v>
@@ -9163,7 +9124,7 @@
         <v>15</v>
       </c>
       <c r="F291" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G291">
         <v>45815.057845233627</v>
@@ -9180,7 +9141,7 @@
         <v>379</v>
       </c>
       <c r="B292" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C292" s="2">
         <v>47118</v>
@@ -9192,7 +9153,7 @@
         <v>16</v>
       </c>
       <c r="F292" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G292">
         <v>13353.30927678045</v>
@@ -9209,7 +9170,7 @@
         <v>274</v>
       </c>
       <c r="B293" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C293" s="2">
         <v>47118</v>
@@ -9221,7 +9182,7 @@
         <v>16</v>
       </c>
       <c r="F293" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G293">
         <v>46179.861718929409</v>
@@ -9238,7 +9199,7 @@
         <v>379</v>
       </c>
       <c r="B294" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C294" s="2">
         <v>47299</v>
@@ -9250,7 +9211,7 @@
         <v>17</v>
       </c>
       <c r="F294" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G294">
         <v>13458.795494571141</v>
@@ -9267,7 +9228,7 @@
         <v>274</v>
       </c>
       <c r="B295" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C295" s="2">
         <v>47299</v>
@@ -9279,7 +9240,7 @@
         <v>17</v>
       </c>
       <c r="F295" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G295">
         <v>46544.665592625191</v>
@@ -9296,7 +9257,7 @@
         <v>379</v>
       </c>
       <c r="B296" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C296" s="2">
         <v>47483</v>
@@ -9308,7 +9269,7 @@
         <v>18</v>
       </c>
       <c r="F296" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G296">
         <v>13564.281712361841</v>
@@ -9325,7 +9286,7 @@
         <v>274</v>
       </c>
       <c r="B297" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C297" s="2">
         <v>47483</v>
@@ -9337,7 +9298,7 @@
         <v>18</v>
       </c>
       <c r="F297" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G297">
         <v>46909.469466320967</v>
@@ -9354,7 +9315,7 @@
         <v>379</v>
       </c>
       <c r="B298" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C298" s="2">
         <v>47664</v>
@@ -9366,7 +9327,7 @@
         <v>19</v>
       </c>
       <c r="F298" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G298">
         <v>13669.76793015254</v>
@@ -9383,7 +9344,7 @@
         <v>274</v>
       </c>
       <c r="B299" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C299" s="2">
         <v>47664</v>
@@ -9395,7 +9356,7 @@
         <v>19</v>
       </c>
       <c r="F299" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G299">
         <v>47274.273340016749</v>
@@ -9412,7 +9373,7 @@
         <v>379</v>
       </c>
       <c r="B300" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C300" s="2">
         <v>47848</v>
@@ -9424,7 +9385,7 @@
         <v>20</v>
       </c>
       <c r="F300" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G300">
         <v>13775.25414794324</v>
@@ -9441,7 +9402,7 @@
         <v>274</v>
       </c>
       <c r="B301" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C301" s="2">
         <v>47848</v>
@@ -9453,7 +9414,7 @@
         <v>20</v>
       </c>
       <c r="F301" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G301">
         <v>47639.077213712531</v>
@@ -9470,7 +9431,7 @@
         <v>14.1</v>
       </c>
       <c r="B302" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C302" s="2">
         <v>46203</v>
@@ -9482,7 +9443,7 @@
         <v>10</v>
       </c>
       <c r="F302" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G302">
         <v>8922.1224131696708</v>
@@ -9499,7 +9460,7 @@
         <v>14.2</v>
       </c>
       <c r="B303" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C303" s="2">
         <v>46203</v>
@@ -9511,7 +9472,7 @@
         <v>10</v>
       </c>
       <c r="F303" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G303">
         <v>48259.41262134452</v>
@@ -9528,7 +9489,7 @@
         <v>14.1</v>
       </c>
       <c r="B304" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C304" s="2">
         <v>46387</v>
@@ -9540,7 +9501,7 @@
         <v>12</v>
       </c>
       <c r="F304" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G304">
         <v>8995.5022577501495</v>
@@ -9557,7 +9518,7 @@
         <v>14.2</v>
       </c>
       <c r="B305" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C305" s="2">
         <v>46387</v>
@@ -9569,7 +9530,7 @@
         <v>12</v>
       </c>
       <c r="F305" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G305">
         <v>48656.321342577961</v>
@@ -9586,7 +9547,7 @@
         <v>14.1</v>
       </c>
       <c r="B306" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C306" s="2">
         <v>46568</v>
@@ -9598,7 +9559,7 @@
         <v>13</v>
       </c>
       <c r="F306" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G306">
         <v>9068.8821023306264</v>
@@ -9615,7 +9576,7 @@
         <v>14.2</v>
       </c>
       <c r="B307" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C307" s="2">
         <v>46568</v>
@@ -9627,7 +9588,7 @@
         <v>13</v>
       </c>
       <c r="F307" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G307">
         <v>49053.23006381141</v>
@@ -9644,7 +9605,7 @@
         <v>14.1</v>
       </c>
       <c r="B308" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C308" s="2">
         <v>46752</v>
@@ -9656,7 +9617,7 @@
         <v>14</v>
       </c>
       <c r="F308" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G308">
         <v>9142.261946911105</v>
@@ -9673,7 +9634,7 @@
         <v>14.2</v>
       </c>
       <c r="B309" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C309" s="2">
         <v>46752</v>
@@ -9685,7 +9646,7 @@
         <v>14</v>
       </c>
       <c r="F309" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G309">
         <v>49450.138785044852</v>
@@ -9702,7 +9663,7 @@
         <v>14.1</v>
       </c>
       <c r="B310" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C310" s="2">
         <v>46934</v>
@@ -9714,7 +9675,7 @@
         <v>15</v>
       </c>
       <c r="F310" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G310">
         <v>9215.6417914915819</v>
@@ -9731,7 +9692,7 @@
         <v>14.2</v>
       </c>
       <c r="B311" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C311" s="2">
         <v>46934</v>
@@ -9743,7 +9704,7 @@
         <v>15</v>
       </c>
       <c r="F311" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G311">
         <v>49847.047506278293</v>
@@ -9760,7 +9721,7 @@
         <v>14.1</v>
       </c>
       <c r="B312" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C312" s="2">
         <v>47118</v>
@@ -9772,7 +9733,7 @@
         <v>16</v>
       </c>
       <c r="F312" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G312">
         <v>9289.0216360720588</v>
@@ -9789,7 +9750,7 @@
         <v>14.2</v>
       </c>
       <c r="B313" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C313" s="2">
         <v>47118</v>
@@ -9801,7 +9762,7 @@
         <v>16</v>
       </c>
       <c r="F313" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G313">
         <v>50243.956227511728</v>
@@ -9818,7 +9779,7 @@
         <v>14.1</v>
       </c>
       <c r="B314" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C314" s="2">
         <v>47299</v>
@@ -9830,7 +9791,7 @@
         <v>17</v>
       </c>
       <c r="F314" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G314">
         <v>9362.4014806525374</v>
@@ -9847,7 +9808,7 @@
         <v>14.2</v>
       </c>
       <c r="B315" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C315" s="2">
         <v>47299</v>
@@ -9859,7 +9820,7 @@
         <v>17</v>
       </c>
       <c r="F315" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G315">
         <v>50640.864948745169</v>
@@ -9876,7 +9837,7 @@
         <v>14.1</v>
       </c>
       <c r="B316" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C316" s="2">
         <v>47483</v>
@@ -9888,7 +9849,7 @@
         <v>18</v>
       </c>
       <c r="F316" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G316">
         <v>9435.7813252330143</v>
@@ -9905,7 +9866,7 @@
         <v>14.2</v>
       </c>
       <c r="B317" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C317" s="2">
         <v>47483</v>
@@ -9917,7 +9878,7 @@
         <v>18</v>
       </c>
       <c r="F317" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G317">
         <v>51037.773669978611</v>
@@ -9934,7 +9895,7 @@
         <v>14.1</v>
       </c>
       <c r="B318" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C318" s="2">
         <v>47664</v>
@@ -9946,7 +9907,7 @@
         <v>19</v>
       </c>
       <c r="F318" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G318">
         <v>9509.161169813493</v>
@@ -9963,7 +9924,7 @@
         <v>14.2</v>
       </c>
       <c r="B319" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C319" s="2">
         <v>47664</v>
@@ -9975,7 +9936,7 @@
         <v>19</v>
       </c>
       <c r="F319" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G319">
         <v>51434.682391212053</v>
@@ -9992,7 +9953,7 @@
         <v>14.1</v>
       </c>
       <c r="B320" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C320" s="2">
         <v>47848</v>
@@ -10004,7 +9965,7 @@
         <v>20</v>
       </c>
       <c r="F320" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G320">
         <v>9582.5410143939698</v>
@@ -10021,7 +9982,7 @@
         <v>14.2</v>
       </c>
       <c r="B321" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C321" s="2">
         <v>47848</v>
@@ -10033,7 +9994,7 @@
         <v>20</v>
       </c>
       <c r="F321" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G321">
         <v>51831.591112445501</v>
@@ -10050,7 +10011,7 @@
         <v>14.1</v>
       </c>
       <c r="B322" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C322" s="2">
         <v>46203</v>
@@ -10062,7 +10023,7 @@
         <v>10</v>
       </c>
       <c r="F322" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G322">
         <v>8712.1307097363897</v>
@@ -10079,7 +10040,7 @@
         <v>14.2</v>
       </c>
       <c r="B323" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C323" s="2">
         <v>46203</v>
@@ -10091,7 +10052,7 @@
         <v>10</v>
       </c>
       <c r="F323" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G323">
         <v>47123.575676528882</v>
@@ -10108,7 +10069,7 @@
         <v>14.1</v>
       </c>
       <c r="B324" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C324" s="2">
         <v>46387</v>
@@ -10120,7 +10081,7 @@
         <v>12</v>
       </c>
       <c r="F324" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G324">
         <v>8762.4476320530375</v>
@@ -10137,7 +10098,7 @@
         <v>14.2</v>
       </c>
       <c r="B325" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C325" s="2">
         <v>46387</v>
@@ -10149,7 +10110,7 @@
         <v>12</v>
       </c>
       <c r="F325" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G325">
         <v>47395.737949524708</v>
@@ -10166,7 +10127,7 @@
         <v>14.1</v>
       </c>
       <c r="B326" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C326" s="2">
         <v>46568</v>
@@ -10178,7 +10139,7 @@
         <v>13</v>
       </c>
       <c r="F326" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G326">
         <v>8823.9597801091131</v>
@@ -10195,7 +10156,7 @@
         <v>14.2</v>
       </c>
       <c r="B327" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C327" s="2">
         <v>46568</v>
@@ -10207,7 +10168,7 @@
         <v>13</v>
       </c>
       <c r="F327" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G327">
         <v>47728.454762497553</v>
@@ -10224,7 +10185,7 @@
         <v>14.1</v>
       </c>
       <c r="B328" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C328" s="2">
         <v>46752</v>
@@ -10236,7 +10197,7 @@
         <v>14</v>
       </c>
       <c r="F328" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G328">
         <v>8892.1696031136707</v>
@@ -10253,7 +10214,7 @@
         <v>14.2</v>
       </c>
       <c r="B329" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C329" s="2">
         <v>46752</v>
@@ -10265,7 +10226,7 @@
         <v>14</v>
       </c>
       <c r="F329" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G329">
         <v>48097.399038396186</v>
@@ -10282,7 +10243,7 @@
         <v>14.1</v>
       </c>
       <c r="B330" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C330" s="2">
         <v>46934</v>
@@ -10294,7 +10255,7 @@
         <v>15</v>
       </c>
       <c r="F330" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G330">
         <v>8964.7835935363528</v>
@@ -10311,7 +10272,7 @@
         <v>14.2</v>
       </c>
       <c r="B331" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C331" s="2">
         <v>46934</v>
@@ -10323,7 +10284,7 @@
         <v>15</v>
       </c>
       <c r="F331" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G331">
         <v>48490.165284319693</v>
@@ -10340,7 +10301,7 @@
         <v>14.1</v>
       </c>
       <c r="B332" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C332" s="2">
         <v>47118</v>
@@ -10352,7 +10313,7 @@
         <v>16</v>
       </c>
       <c r="F332" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G332">
         <v>9040.6471502263867</v>
@@ -10369,7 +10330,7 @@
         <v>14.2</v>
       </c>
       <c r="B333" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C333" s="2">
         <v>47118</v>
@@ -10381,7 +10342,7 @@
         <v>16</v>
       </c>
       <c r="F333" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G333">
         <v>48900.508307614567</v>
@@ -10398,7 +10359,7 @@
         <v>14.1</v>
       </c>
       <c r="B334" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C334" s="2">
         <v>47299</v>
@@ -10410,7 +10371,7 @@
         <v>17</v>
       </c>
       <c r="F334" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G334">
         <v>9119.1942038308862</v>
@@ -10427,7 +10388,7 @@
         <v>14.2</v>
       </c>
       <c r="B335" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C335" s="2">
         <v>47299</v>
@@ -10439,7 +10400,7 @@
         <v>17</v>
       </c>
       <c r="F335" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G335">
         <v>49325.36626119916</v>
@@ -10456,7 +10417,7 @@
         <v>14.1</v>
       </c>
       <c r="B336" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C336" s="2">
         <v>47483</v>
@@ -10468,7 +10429,7 @@
         <v>18</v>
       </c>
       <c r="F336" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G336">
         <v>9200.1628290785266</v>
@@ -10485,7 +10446,7 @@
         <v>14.2</v>
       </c>
       <c r="B337" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C337" s="2">
         <v>47483</v>
@@ -10497,7 +10458,7 @@
         <v>18</v>
       </c>
       <c r="F337" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G337">
         <v>49763.322401482677</v>
@@ -10514,7 +10475,7 @@
         <v>14.1</v>
       </c>
       <c r="B338" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C338" s="2">
         <v>47664</v>
@@ -10526,7 +10487,7 @@
         <v>19</v>
       </c>
       <c r="F338" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G338">
         <v>9283.4482972280384</v>
@@ -10543,7 +10504,7 @@
         <v>14.2</v>
       </c>
       <c r="B339" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C339" s="2">
         <v>47664</v>
@@ -10555,7 +10516,7 @@
         <v>19</v>
       </c>
       <c r="F339" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G339">
         <v>50213.810254782737</v>
@@ -10572,7 +10533,7 @@
         <v>14.1</v>
       </c>
       <c r="B340" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C340" s="2">
         <v>47848</v>
@@ -10584,7 +10545,7 @@
         <v>20</v>
       </c>
       <c r="F340" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G340">
         <v>9369.0271463102763</v>
@@ -10601,7 +10562,7 @@
         <v>14.2</v>
       </c>
       <c r="B341" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C341" s="2">
         <v>47848</v>
@@ -10613,7 +10574,7 @@
         <v>20</v>
       </c>
       <c r="F341" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G341">
         <v>50676.70291622205</v>
@@ -10630,7 +10591,7 @@
         <v>14.3</v>
       </c>
       <c r="B342" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C342" s="2">
         <v>46203</v>
@@ -10642,7 +10603,7 @@
         <v>10</v>
       </c>
       <c r="F342" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G342">
         <v>53184.163304725829</v>
@@ -10659,7 +10620,7 @@
         <v>14.4</v>
       </c>
       <c r="B343" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C343" s="2">
         <v>46203</v>
@@ -10671,7 +10632,7 @@
         <v>10</v>
       </c>
       <c r="F343" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G343">
         <v>3997.37172978836</v>
@@ -10688,7 +10649,7 @@
         <v>14.3</v>
       </c>
       <c r="B344" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C344" s="2">
         <v>46387</v>
@@ -10700,7 +10661,7 @@
         <v>12</v>
       </c>
       <c r="F344" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G344">
         <v>53621.575554493087</v>
@@ -10717,7 +10678,7 @@
         <v>14.4</v>
       </c>
       <c r="B345" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C345" s="2">
         <v>46387</v>
@@ -10729,7 +10690,7 @@
         <v>12</v>
       </c>
       <c r="F345" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G345">
         <v>4030.2480458350101</v>
@@ -10746,7 +10707,7 @@
         <v>14.3</v>
       </c>
       <c r="B346" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C346" s="2">
         <v>46568</v>
@@ -10758,7 +10719,7 @@
         <v>13</v>
       </c>
       <c r="F346" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G346">
         <v>54058.987804260367</v>
@@ -10775,7 +10736,7 @@
         <v>14.4</v>
       </c>
       <c r="B347" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C347" s="2">
         <v>46568</v>
@@ -10787,7 +10748,7 @@
         <v>13</v>
       </c>
       <c r="F347" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G347">
         <v>4063.1243618816602</v>
@@ -10804,7 +10765,7 @@
         <v>14.3</v>
       </c>
       <c r="B348" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C348" s="2">
         <v>46752</v>
@@ -10816,7 +10777,7 @@
         <v>14</v>
       </c>
       <c r="F348" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G348">
         <v>54496.400054027639</v>
@@ -10833,7 +10794,7 @@
         <v>14.4</v>
       </c>
       <c r="B349" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C349" s="2">
         <v>46752</v>
@@ -10845,7 +10806,7 @@
         <v>14</v>
       </c>
       <c r="F349" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G349">
         <v>4096.0006779283094</v>
@@ -10862,7 +10823,7 @@
         <v>14.3</v>
       </c>
       <c r="B350" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C350" s="2">
         <v>46934</v>
@@ -10874,7 +10835,7 @@
         <v>15</v>
       </c>
       <c r="F350" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G350">
         <v>54933.812303794897</v>
@@ -10891,7 +10852,7 @@
         <v>14.4</v>
       </c>
       <c r="B351" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C351" s="2">
         <v>46934</v>
@@ -10903,7 +10864,7 @@
         <v>15</v>
       </c>
       <c r="F351" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G351">
         <v>4128.8769939749591</v>
@@ -10920,7 +10881,7 @@
         <v>14.3</v>
       </c>
       <c r="B352" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C352" s="2">
         <v>47118</v>
@@ -10932,7 +10893,7 @@
         <v>16</v>
       </c>
       <c r="F352" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G352">
         <v>55371.22455356217</v>
@@ -10949,7 +10910,7 @@
         <v>14.4</v>
       </c>
       <c r="B353" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C353" s="2">
         <v>47118</v>
@@ -10961,7 +10922,7 @@
         <v>16</v>
       </c>
       <c r="F353" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G353">
         <v>4161.7533100216096</v>
@@ -10978,7 +10939,7 @@
         <v>14.3</v>
       </c>
       <c r="B354" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C354" s="2">
         <v>47299</v>
@@ -10990,7 +10951,7 @@
         <v>17</v>
       </c>
       <c r="F354" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G354">
         <v>55808.636803329442</v>
@@ -11007,7 +10968,7 @@
         <v>14.4</v>
       </c>
       <c r="B355" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C355" s="2">
         <v>47299</v>
@@ -11019,7 +10980,7 @@
         <v>17</v>
       </c>
       <c r="F355" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G355">
         <v>4194.6296260682593</v>
@@ -11036,7 +10997,7 @@
         <v>14.3</v>
       </c>
       <c r="B356" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C356" s="2">
         <v>47483</v>
@@ -11048,7 +11009,7 @@
         <v>18</v>
       </c>
       <c r="F356" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G356">
         <v>56246.049053096707</v>
@@ -11065,7 +11026,7 @@
         <v>14.4</v>
       </c>
       <c r="B357" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C357" s="2">
         <v>47483</v>
@@ -11077,7 +11038,7 @@
         <v>18</v>
       </c>
       <c r="F357" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G357">
         <v>4227.505942114909</v>
@@ -11094,7 +11055,7 @@
         <v>14.3</v>
       </c>
       <c r="B358" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C358" s="2">
         <v>47664</v>
@@ -11106,7 +11067,7 @@
         <v>19</v>
       </c>
       <c r="F358" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G358">
         <v>56683.461302863987</v>
@@ -11123,7 +11084,7 @@
         <v>14.4</v>
       </c>
       <c r="B359" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C359" s="2">
         <v>47664</v>
@@ -11135,7 +11096,7 @@
         <v>19</v>
       </c>
       <c r="F359" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G359">
         <v>4260.3822581615595</v>
@@ -11152,7 +11113,7 @@
         <v>14.3</v>
       </c>
       <c r="B360" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C360" s="2">
         <v>47848</v>
@@ -11164,7 +11125,7 @@
         <v>20</v>
       </c>
       <c r="F360" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G360">
         <v>57120.873552631252</v>
@@ -11181,7 +11142,7 @@
         <v>14.4</v>
       </c>
       <c r="B361" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C361" s="2">
         <v>47848</v>
@@ -11193,7 +11154,7 @@
         <v>20</v>
       </c>
       <c r="F361" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="G361">
         <v>4293.2585742082092</v>
@@ -11210,7 +11171,7 @@
         <v>14.3</v>
       </c>
       <c r="B362" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C362" s="2">
         <v>46203</v>
@@ -11222,7 +11183,7 @@
         <v>10</v>
       </c>
       <c r="F362" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G362">
         <v>51932.417079909617</v>
@@ -11239,7 +11200,7 @@
         <v>14.4</v>
       </c>
       <c r="B363" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C363" s="2">
         <v>46203</v>
@@ -11251,7 +11212,7 @@
         <v>10</v>
       </c>
       <c r="F363" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G363">
         <v>3903.2893063556498</v>
@@ -11268,7 +11229,7 @@
         <v>14.3</v>
       </c>
       <c r="B364" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C364" s="2">
         <v>46387</v>
@@ -11280,7 +11241,7 @@
         <v>12</v>
       </c>
       <c r="F364" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G364">
         <v>52232.352822724548</v>
@@ -11297,7 +11258,7 @@
         <v>14.4</v>
       </c>
       <c r="B365" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C365" s="2">
         <v>46387</v>
@@ -11309,7 +11270,7 @@
         <v>12</v>
       </c>
       <c r="F365" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G365">
         <v>3925.8327588531888</v>
@@ -11326,7 +11287,7 @@
         <v>14.3</v>
       </c>
       <c r="B366" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C366" s="2">
         <v>46568</v>
@@ -11338,7 +11299,7 @@
         <v>13</v>
       </c>
       <c r="F366" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G366">
         <v>52599.022542768958</v>
@@ -11355,7 +11316,7 @@
         <v>14.4</v>
       </c>
       <c r="B367" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C367" s="2">
         <v>46568</v>
@@ -11367,7 +11328,7 @@
         <v>13</v>
       </c>
       <c r="F367" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G367">
         <v>3953.3919998377082</v>
@@ -11384,7 +11345,7 @@
         <v>14.3</v>
       </c>
       <c r="B368" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C368" s="2">
         <v>46752</v>
@@ -11396,7 +11357,7 @@
         <v>14</v>
       </c>
       <c r="F368" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G368">
         <v>53005.616646466318</v>
@@ -11413,7 +11374,7 @@
         <v>14.4</v>
       </c>
       <c r="B369" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C369" s="2">
         <v>46752</v>
@@ -11425,7 +11386,7 @@
         <v>14</v>
       </c>
       <c r="F369" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G369">
         <v>3983.951995043537</v>
@@ -11442,7 +11403,7 @@
         <v>14.3</v>
       </c>
       <c r="B370" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C370" s="2">
         <v>46934</v>
@@ -11454,7 +11415,7 @@
         <v>15</v>
       </c>
       <c r="F370" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G370">
         <v>53438.463691822617</v>
@@ -11471,7 +11432,7 @@
         <v>14.4</v>
       </c>
       <c r="B371" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C371" s="2">
         <v>46934</v>
@@ -11483,7 +11444,7 @@
         <v>15</v>
       </c>
       <c r="F371" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G371">
         <v>4016.4851860334188</v>
@@ -11500,7 +11461,7 @@
         <v>14.3</v>
       </c>
       <c r="B372" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C372" s="2">
         <v>47118</v>
@@ -11512,7 +11473,7 @@
         <v>16</v>
       </c>
       <c r="F372" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G372">
         <v>53890.681180110441</v>
@@ -11529,7 +11490,7 @@
         <v>14.4</v>
       </c>
       <c r="B373" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C373" s="2">
         <v>47118</v>
@@ -11541,7 +11502,7 @@
         <v>16</v>
       </c>
       <c r="F373" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G373">
         <v>4050.474277730515</v>
@@ -11558,7 +11519,7 @@
         <v>14.3</v>
       </c>
       <c r="B374" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C374" s="2">
         <v>47299</v>
@@ -11570,7 +11531,7 @@
         <v>17</v>
       </c>
       <c r="F374" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G374">
         <v>54358.894810517537</v>
@@ -11587,7 +11548,7 @@
         <v>14.4</v>
       </c>
       <c r="B375" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C375" s="2">
         <v>47299</v>
@@ -11599,7 +11560,7 @@
         <v>17</v>
       </c>
       <c r="F375" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G375">
         <v>4085.6656545124938</v>
@@ -11616,7 +11577,7 @@
         <v>14.3</v>
       </c>
       <c r="B376" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C376" s="2">
         <v>47483</v>
@@ -11628,7 +11589,7 @@
         <v>18</v>
       </c>
       <c r="F376" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G376">
         <v>54841.543264362263</v>
@@ -11645,7 +11606,7 @@
         <v>14.4</v>
       </c>
       <c r="B377" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C377" s="2">
         <v>47483</v>
@@ -11657,7 +11618,7 @@
         <v>18</v>
       </c>
       <c r="F377" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G377">
         <v>4121.9419661989377</v>
@@ -11674,7 +11635,7 @@
         <v>14.3</v>
       </c>
       <c r="B378" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C378" s="2">
         <v>47664</v>
@@ -11686,7 +11647,7 @@
         <v>19</v>
       </c>
       <c r="F378" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G378">
         <v>55338.002260759349</v>
@@ -11703,7 +11664,7 @@
         <v>14.4</v>
       </c>
       <c r="B379" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C379" s="2">
         <v>47664</v>
@@ -11715,7 +11676,7 @@
         <v>19</v>
       </c>
       <c r="F379" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G379">
         <v>4159.2562912514186</v>
@@ -11732,7 +11693,7 @@
         <v>14.3</v>
       </c>
       <c r="B380" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C380" s="2">
         <v>47848</v>
@@ -11744,7 +11705,7 @@
         <v>20</v>
       </c>
       <c r="F380" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G380">
         <v>55848.131944510613</v>
@@ -11761,7 +11722,7 @@
         <v>14.4</v>
       </c>
       <c r="B381" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C381" s="2">
         <v>47848</v>
@@ -11773,7 +11734,7 @@
         <v>20</v>
       </c>
       <c r="F381" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="G381">
         <v>4197.5981180217186</v>
@@ -12080,7 +12041,7 @@
         <v>323</v>
       </c>
       <c r="B392" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C392" s="2">
         <v>46387</v>
@@ -12092,7 +12053,7 @@
         <v>12</v>
       </c>
       <c r="F392" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G392">
         <v>1</v>
@@ -12109,7 +12070,7 @@
         <v>323</v>
       </c>
       <c r="B393" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C393" s="2">
         <v>46752</v>
@@ -12121,7 +12082,7 @@
         <v>14</v>
       </c>
       <c r="F393" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G393">
         <v>1</v>
@@ -12138,7 +12099,7 @@
         <v>323</v>
       </c>
       <c r="B394" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C394" s="2">
         <v>47118</v>
@@ -12150,7 +12111,7 @@
         <v>16</v>
       </c>
       <c r="F394" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G394">
         <v>2</v>
@@ -12167,7 +12128,7 @@
         <v>323</v>
       </c>
       <c r="B395" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C395" s="2">
         <v>47483</v>
@@ -12179,7 +12140,7 @@
         <v>18</v>
       </c>
       <c r="F395" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G395">
         <v>2</v>
@@ -12196,7 +12157,7 @@
         <v>323</v>
       </c>
       <c r="B396" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C396" s="2">
         <v>47848</v>
@@ -12208,7 +12169,7 @@
         <v>20</v>
       </c>
       <c r="F396" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G396">
         <v>2</v>
@@ -12225,7 +12186,7 @@
         <v>376</v>
       </c>
       <c r="B397" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C397" s="2">
         <v>46387</v>
@@ -12254,7 +12215,7 @@
         <v>376</v>
       </c>
       <c r="B398" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C398" s="2">
         <v>46752</v>
@@ -12283,7 +12244,7 @@
         <v>376</v>
       </c>
       <c r="B399" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C399" s="2">
         <v>47118</v>
@@ -12312,7 +12273,7 @@
         <v>376</v>
       </c>
       <c r="B400" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C400" s="2">
         <v>47483</v>
@@ -12341,7 +12302,7 @@
         <v>376</v>
       </c>
       <c r="B401" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C401" s="2">
         <v>47848</v>
@@ -12370,7 +12331,7 @@
         <v>376</v>
       </c>
       <c r="B402" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C402" s="2">
         <v>46387</v>
@@ -12399,7 +12360,7 @@
         <v>376</v>
       </c>
       <c r="B403" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C403" s="2">
         <v>46752</v>
@@ -12428,7 +12389,7 @@
         <v>376</v>
       </c>
       <c r="B404" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C404" s="2">
         <v>47118</v>
@@ -12457,7 +12418,7 @@
         <v>376</v>
       </c>
       <c r="B405" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C405" s="2">
         <v>47483</v>
@@ -12486,7 +12447,7 @@
         <v>376</v>
       </c>
       <c r="B406" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C406" s="2">
         <v>47848</v>
@@ -12515,7 +12476,7 @@
         <v>466</v>
       </c>
       <c r="B407" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C407" s="2">
         <v>46387</v>
@@ -12544,7 +12505,7 @@
         <v>466</v>
       </c>
       <c r="B408" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C408" s="2">
         <v>46752</v>
@@ -12573,7 +12534,7 @@
         <v>466</v>
       </c>
       <c r="B409" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C409" s="2">
         <v>47118</v>
@@ -12602,7 +12563,7 @@
         <v>466</v>
       </c>
       <c r="B410" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C410" s="2">
         <v>47483</v>
@@ -12631,7 +12592,7 @@
         <v>466</v>
       </c>
       <c r="B411" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C411" s="2">
         <v>47848</v>
@@ -12660,7 +12621,7 @@
         <v>466</v>
       </c>
       <c r="B412" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C412" s="2">
         <v>46387</v>
@@ -12689,7 +12650,7 @@
         <v>466</v>
       </c>
       <c r="B413" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C413" s="2">
         <v>46752</v>
@@ -12718,7 +12679,7 @@
         <v>466</v>
       </c>
       <c r="B414" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C414" s="2">
         <v>47118</v>
@@ -12747,7 +12708,7 @@
         <v>466</v>
       </c>
       <c r="B415" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C415" s="2">
         <v>47483</v>
@@ -12776,7 +12737,7 @@
         <v>466</v>
       </c>
       <c r="B416" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C416" s="2">
         <v>47848</v>
@@ -12805,7 +12766,7 @@
         <v>96</v>
       </c>
       <c r="B417" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C417" s="2">
         <v>46022</v>
@@ -12814,10 +12775,10 @@
         <v>2025</v>
       </c>
       <c r="E417" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F417" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G417">
         <v>846.88288415165562</v>
@@ -12834,7 +12795,7 @@
         <v>96</v>
       </c>
       <c r="B418" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C418" s="2">
         <v>46387</v>
@@ -12846,7 +12807,7 @@
         <v>22</v>
       </c>
       <c r="F418" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G418">
         <v>914.63351488378817</v>
@@ -12863,7 +12824,7 @@
         <v>96</v>
       </c>
       <c r="B419" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C419" s="2">
         <v>46752</v>
@@ -12875,7 +12836,7 @@
         <v>24</v>
       </c>
       <c r="F419" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G419">
         <v>987.8041960744913</v>
@@ -12892,7 +12853,7 @@
         <v>96</v>
       </c>
       <c r="B420" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C420" s="2">
         <v>47118</v>
@@ -12904,7 +12865,7 @@
         <v>25</v>
       </c>
       <c r="F420" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G420">
         <v>1066.8285317604509</v>
@@ -12921,7 +12882,7 @@
         <v>96</v>
       </c>
       <c r="B421" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C421" s="2">
         <v>47483</v>
@@ -12933,7 +12894,7 @@
         <v>26</v>
       </c>
       <c r="F421" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G421">
         <v>1152.1748143012869</v>
@@ -12950,7 +12911,7 @@
         <v>385</v>
       </c>
       <c r="B422" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C422" s="2">
         <v>46387</v>
@@ -12979,7 +12940,7 @@
         <v>385</v>
       </c>
       <c r="B423" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C423" s="2">
         <v>46752</v>
@@ -13008,7 +12969,7 @@
         <v>385</v>
       </c>
       <c r="B424" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C424" s="2">
         <v>47118</v>
@@ -13037,7 +12998,7 @@
         <v>385</v>
       </c>
       <c r="B425" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C425" s="2">
         <v>47483</v>
@@ -13066,7 +13027,7 @@
         <v>385</v>
       </c>
       <c r="B426" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C426" s="2">
         <v>47848</v>
@@ -13095,7 +13056,7 @@
         <v>385</v>
       </c>
       <c r="B427" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C427" s="2">
         <v>46387</v>
@@ -13124,7 +13085,7 @@
         <v>385</v>
       </c>
       <c r="B428" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C428" s="2">
         <v>46752</v>
@@ -13153,7 +13114,7 @@
         <v>385</v>
       </c>
       <c r="B429" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C429" s="2">
         <v>47118</v>
@@ -13182,7 +13143,7 @@
         <v>385</v>
       </c>
       <c r="B430" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C430" s="2">
         <v>47483</v>
@@ -13211,7 +13172,7 @@
         <v>385</v>
       </c>
       <c r="B431" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C431" s="2">
         <v>47848</v>
@@ -13240,7 +13201,7 @@
         <v>386.1</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C432" s="4">
         <v>46387</v>
@@ -13269,7 +13230,7 @@
         <v>386.1</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C433" s="4">
         <v>46752</v>
@@ -13298,7 +13259,7 @@
         <v>386.1</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C434" s="4">
         <v>47118</v>
@@ -13327,7 +13288,7 @@
         <v>386.1</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C435" s="4">
         <v>47483</v>
@@ -13356,7 +13317,7 @@
         <v>386.1</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C436" s="4">
         <v>47848</v>
@@ -13385,7 +13346,7 @@
         <v>386.2</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C437" s="4">
         <v>46387</v>
@@ -13414,7 +13375,7 @@
         <v>386.2</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C438" s="4">
         <v>46752</v>
@@ -13443,7 +13404,7 @@
         <v>386.2</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C439" s="4">
         <v>47118</v>
@@ -13472,7 +13433,7 @@
         <v>386.2</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C440" s="4">
         <v>47483</v>
@@ -13501,7 +13462,7 @@
         <v>386.2</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C441" s="4">
         <v>47848</v>
@@ -13530,7 +13491,7 @@
         <v>386.3</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C442" s="4">
         <v>46387</v>
@@ -13559,7 +13520,7 @@
         <v>386.3</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C443" s="4">
         <v>46752</v>
@@ -13588,7 +13549,7 @@
         <v>386.3</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C444" s="4">
         <v>47118</v>
@@ -13617,7 +13578,7 @@
         <v>386.3</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C445" s="4">
         <v>47483</v>
@@ -13646,7 +13607,7 @@
         <v>386.3</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C446" s="4">
         <v>47848</v>
@@ -13672,10 +13633,10 @@
     </row>
     <row r="447" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B447" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C447" s="2">
         <v>46387</v>
@@ -13687,7 +13648,7 @@
         <v>12</v>
       </c>
       <c r="F447" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G447">
         <v>15.7</v>
@@ -13701,10 +13662,10 @@
     </row>
     <row r="448" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B448" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C448" s="2">
         <v>46752</v>
@@ -13716,7 +13677,7 @@
         <v>14</v>
       </c>
       <c r="F448" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G448">
         <v>16.3</v>
@@ -13730,10 +13691,10 @@
     </row>
     <row r="449" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B449" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C449" s="2">
         <v>47118</v>
@@ -13745,7 +13706,7 @@
         <v>16</v>
       </c>
       <c r="F449" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G449">
         <v>16.8</v>
@@ -13759,10 +13720,10 @@
     </row>
     <row r="450" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B450" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C450" s="2">
         <v>47483</v>
@@ -13774,7 +13735,7 @@
         <v>18</v>
       </c>
       <c r="F450" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G450">
         <v>17.399999999999999</v>
@@ -13788,10 +13749,10 @@
     </row>
     <row r="451" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B451" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C451" s="2">
         <v>47848</v>
@@ -13803,7 +13764,7 @@
         <v>20</v>
       </c>
       <c r="F451" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G451">
         <v>18</v>
@@ -13817,10 +13778,10 @@
     </row>
     <row r="452" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B452" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C452" s="2">
         <v>46387</v>
@@ -13846,10 +13807,10 @@
     </row>
     <row r="453" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B453" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C453" s="2">
         <v>46752</v>
@@ -13875,10 +13836,10 @@
     </row>
     <row r="454" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B454" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C454" s="2">
         <v>47118</v>
@@ -13904,10 +13865,10 @@
     </row>
     <row r="455" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B455" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C455" s="2">
         <v>47483</v>
@@ -13933,10 +13894,10 @@
     </row>
     <row r="456" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B456" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C456" s="2">
         <v>47848</v>
@@ -13962,10 +13923,10 @@
     </row>
     <row r="457" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="B457" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C457" s="2">
         <v>46387</v>
@@ -13977,7 +13938,7 @@
         <v>12</v>
       </c>
       <c r="F457" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="G457">
         <v>34.298999999999999</v>
@@ -13991,10 +13952,10 @@
     </row>
     <row r="458" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="B458" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C458" s="2">
         <v>46752</v>
@@ -14006,7 +13967,7 @@
         <v>14</v>
       </c>
       <c r="F458" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="G458">
         <v>35.327969999999993</v>
@@ -14020,10 +13981,10 @@
     </row>
     <row r="459" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="B459" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C459" s="2">
         <v>47118</v>
@@ -14035,7 +13996,7 @@
         <v>16</v>
       </c>
       <c r="F459" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="G459">
         <v>36.387809099999998</v>
@@ -14049,10 +14010,10 @@
     </row>
     <row r="460" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="B460" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C460" s="2">
         <v>47483</v>
@@ -14064,7 +14025,7 @@
         <v>18</v>
       </c>
       <c r="F460" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="G460">
         <v>37.479443373000002</v>
@@ -14078,10 +14039,10 @@
     </row>
     <row r="461" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="B461" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C461" s="2">
         <v>47848</v>
@@ -14093,7 +14054,7 @@
         <v>20</v>
       </c>
       <c r="F461" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="G461">
         <v>38.603826674190003</v>
@@ -14106,7 +14067,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I456" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}"/>
+  <autoFilter ref="A1:I461" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="653" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFDE6934-BAD5-4EBC-97E9-9E53F496A23A}"/>
+  <xr:revisionPtr revIDLastSave="711" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9874C7DE-2873-402B-A1C7-92BBBC2B0E3D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Proyecciones" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$I$461</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$I$466</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="80">
   <si>
     <t>Id</t>
   </si>
@@ -203,13 +203,7 @@
     <t>Impacto de actividades de Responsabilidad y proyección</t>
   </si>
   <si>
-    <t>Estudiantes con Becas</t>
-  </si>
-  <si>
     <t>Participación de POLI- voluntariados (Estudiantes- Colaboradores)</t>
-  </si>
-  <si>
-    <t>Cumplimiento EBIDTA</t>
   </si>
   <si>
     <t>CAPEX</t>
@@ -275,10 +269,16 @@
     <t>339</t>
   </si>
   <si>
-    <t>Programas acreditables acreditados Sede Bogotá</t>
+    <t>Modelo_Conservador</t>
   </si>
   <si>
-    <t>Modelo_Conservador</t>
+    <t>% Estudiantes con Becas</t>
+  </si>
+  <si>
+    <t>% Programas acreditables acreditados Sede Bogotá</t>
+  </si>
+  <si>
+    <t>Cumplimiento EBITDA</t>
   </si>
 </sst>
 </file>
@@ -686,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}">
-  <dimension ref="A1:I461"/>
+  <dimension ref="A1:I466"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
@@ -2193,7 +2193,7 @@
         <v>12</v>
       </c>
       <c r="F52" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G52">
         <v>88.274000000000001</v>
@@ -2222,7 +2222,7 @@
         <v>14</v>
       </c>
       <c r="F53" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G53">
         <v>89.156740000000013</v>
@@ -2251,7 +2251,7 @@
         <v>16</v>
       </c>
       <c r="F54" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G54">
         <v>90.048307400000013</v>
@@ -2280,7 +2280,7 @@
         <v>18</v>
       </c>
       <c r="F55" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G55">
         <v>90.948790474000006</v>
@@ -2309,7 +2309,7 @@
         <v>20</v>
       </c>
       <c r="F56" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G56">
         <v>91.858278378740025</v>
@@ -2628,16 +2628,16 @@
         <v>12</v>
       </c>
       <c r="F67" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G67">
-        <v>21142.397020470002</v>
+        <v>132301.57511745999</v>
       </c>
       <c r="H67">
-        <v>16913.917616375998</v>
+        <v>105841.260093968</v>
       </c>
       <c r="I67">
-        <v>25370.876424564001</v>
+        <v>158761.89014095199</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
@@ -2657,16 +2657,16 @@
         <v>14</v>
       </c>
       <c r="F68" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G68">
-        <v>21776.668931084099</v>
+        <v>136270.62237098379</v>
       </c>
       <c r="H68">
-        <v>17290.675131280779</v>
+        <v>108198.8741625611</v>
       </c>
       <c r="I68">
-        <v>26262.662730887419</v>
+        <v>164342.37057940639</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
@@ -2686,16 +2686,16 @@
         <v>16</v>
       </c>
       <c r="F69" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G69">
-        <v>22429.968999016619</v>
+        <v>140358.74104211331</v>
       </c>
       <c r="H69">
-        <v>17674.815571225099</v>
+        <v>110602.6879411853</v>
       </c>
       <c r="I69">
-        <v>27185.12242680815</v>
+        <v>170114.7941430413</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
@@ -2715,16 +2715,16 @@
         <v>18</v>
       </c>
       <c r="F70" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G70">
-        <v>23102.868068987129</v>
+        <v>144569.5032733767</v>
       </c>
       <c r="H70">
-        <v>18066.44282994793</v>
+        <v>113053.3515597806</v>
       </c>
       <c r="I70">
-        <v>28139.293308026321</v>
+        <v>176085.65498697289</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
@@ -2744,16 +2744,16 @@
         <v>20</v>
       </c>
       <c r="F71" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G71">
-        <v>23795.954111056741</v>
+        <v>148906.58837157799</v>
       </c>
       <c r="H71">
-        <v>18465.66039018003</v>
+        <v>115551.5125763446</v>
       </c>
       <c r="I71">
-        <v>29126.24783193344</v>
+        <v>182261.6641668115</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
@@ -2773,16 +2773,16 @@
         <v>12</v>
       </c>
       <c r="F72" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="G72">
-        <v>9245.4038089869991</v>
+        <v>5855</v>
       </c>
       <c r="H72">
-        <v>7396.3230471895986</v>
+        <v>4684</v>
       </c>
       <c r="I72">
-        <v>11094.4845707844</v>
+        <v>7026</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
@@ -2802,16 +2802,16 @@
         <v>14</v>
       </c>
       <c r="F73" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="G73">
-        <v>9522.7659232566093</v>
+        <v>6219.0240919999987</v>
       </c>
       <c r="H73">
-        <v>7561.0761430657494</v>
+        <v>4937.9051290480002</v>
       </c>
       <c r="I73">
-        <v>11484.455703447469</v>
+        <v>7500.1430549519973</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
@@ -2831,16 +2831,16 @@
         <v>16</v>
       </c>
       <c r="F74" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="G74">
-        <v>9808.4489009543086</v>
+        <v>6485.9967514999989</v>
       </c>
       <c r="H74">
-        <v>7729.057733951995</v>
+        <v>5110.9654401819989</v>
       </c>
       <c r="I74">
-        <v>11887.84006795662</v>
+        <v>7861.0280628179989</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
@@ -2860,16 +2860,16 @@
         <v>18</v>
       </c>
       <c r="F75" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="G75">
-        <v>10102.70236798294</v>
+        <v>6752.9694109999982</v>
       </c>
       <c r="H75">
-        <v>7900.3132517626573</v>
+        <v>5280.822079401999</v>
       </c>
       <c r="I75">
-        <v>12305.09148420322</v>
+        <v>8225.1167425979966</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
@@ -2889,16 +2889,16 @@
         <v>20</v>
       </c>
       <c r="F76" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="G76">
-        <v>10405.783439022431</v>
+        <v>7019.9420704999966</v>
       </c>
       <c r="H76">
-        <v>8074.8879486814021</v>
+        <v>5447.4750467079984</v>
       </c>
       <c r="I76">
-        <v>12736.67892936345</v>
+        <v>8592.4090942919956</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
@@ -2918,16 +2918,16 @@
         <v>12</v>
       </c>
       <c r="F77" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G77">
-        <v>162497.78230864269</v>
+        <v>293409.4756239889</v>
       </c>
       <c r="H77">
-        <v>194997.33877037119</v>
+        <v>314242.98358171928</v>
       </c>
       <c r="I77">
-        <v>129998.22584691409</v>
+        <v>272575.96766625863</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
@@ -2947,16 +2947,16 @@
         <v>14</v>
       </c>
       <c r="F78" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G78">
-        <v>181422.79838200199</v>
+        <v>310591.22318889661</v>
       </c>
       <c r="H78">
-        <v>218795.89484869441</v>
+        <v>333306.32414918538</v>
       </c>
       <c r="I78">
-        <v>144049.70191530959</v>
+        <v>287876.12222860788</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
@@ -2976,16 +2976,16 @@
         <v>16</v>
       </c>
       <c r="F79" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G79">
-        <v>202551.88289425641</v>
+        <v>328779.11566018942</v>
       </c>
       <c r="H79">
-        <v>245492.88206783871</v>
+        <v>353524.73659266828</v>
       </c>
       <c r="I79">
-        <v>159610.88372067409</v>
+        <v>304033.49472771061</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
@@ -3005,16 +3005,16 @@
         <v>18</v>
       </c>
       <c r="F80" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G80">
-        <v>226141.72876785841</v>
+        <v>348032.07181599637</v>
       </c>
       <c r="H80">
-        <v>275440.62563925138</v>
+        <v>374968.12943755521</v>
       </c>
       <c r="I80">
-        <v>176842.83189646521</v>
+        <v>321096.01419443771</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
@@ -3034,16 +3034,16 @@
         <v>20</v>
       </c>
       <c r="F81" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G81">
-        <v>252478.92421130271</v>
+        <v>368412.46065557672</v>
       </c>
       <c r="H81">
-        <v>309034.20323463448</v>
+        <v>397710.63783342228</v>
       </c>
       <c r="I81">
-        <v>195923.64518797089</v>
+        <v>339114.28347773122</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
@@ -5386,13 +5386,13 @@
         <v>35</v>
       </c>
       <c r="G162">
-        <v>0.99675669436749748</v>
+        <v>0.71510849492151418</v>
       </c>
       <c r="H162">
-        <v>1.196108033240997</v>
+        <v>0.73962650046168033</v>
       </c>
       <c r="I162">
-        <v>0.96258217913204036</v>
+        <v>0.64546314585089737</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
@@ -5415,13 +5415,13 @@
         <v>35</v>
       </c>
       <c r="G163">
-        <v>0.79740535549399805</v>
+        <v>0.57208679593721135</v>
       </c>
       <c r="H163">
-        <v>0.96167085872576163</v>
+        <v>0.59228963250230826</v>
       </c>
       <c r="I163">
-        <v>0.76924555493998137</v>
+        <v>0.51469902830302305</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
@@ -5444,13 +5444,13 @@
         <v>35</v>
       </c>
       <c r="G164">
-        <v>0.63792428439519844</v>
+        <v>0.45766943674976912</v>
       </c>
       <c r="H164">
-        <v>0.77316423268698053</v>
+        <v>0.47430245170821778</v>
       </c>
       <c r="I164">
-        <v>0.61474029325946433</v>
+        <v>0.41042203194026261</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
@@ -5473,13 +5473,13 @@
         <v>35</v>
       </c>
       <c r="G165">
-        <v>0.51033942751615879</v>
+        <v>0.3661355493998153</v>
       </c>
       <c r="H165">
-        <v>0.62159342271468143</v>
+        <v>0.37981855793167119</v>
       </c>
       <c r="I165">
-        <v>0.49126731405355478</v>
+        <v>0.32726787299048538</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
@@ -5502,13 +5502,13 @@
         <v>35</v>
       </c>
       <c r="G166">
-        <v>0.40827154201292698</v>
+        <v>0.29290843951985218</v>
       </c>
       <c r="H166">
-        <v>0.49972436742382259</v>
+        <v>0.30415612359741451</v>
       </c>
       <c r="I166">
-        <v>0.39259391479963057</v>
+        <v>0.26095849634300861</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
@@ -5531,13 +5531,13 @@
         <v>39</v>
       </c>
       <c r="G167">
-        <v>1.0249999999999999</v>
+        <v>0.72500000000000009</v>
       </c>
       <c r="H167">
-        <v>1.23</v>
+        <v>0.74985714285714289</v>
       </c>
       <c r="I167">
-        <v>0.98985714285714266</v>
+        <v>0.65439130434782633</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
@@ -5560,13 +5560,13 @@
         <v>39</v>
       </c>
       <c r="G168">
-        <v>0.89999999999999991</v>
+        <v>0.58000000000000007</v>
       </c>
       <c r="H168">
-        <v>1.0853999999999999</v>
+        <v>0.60048228571428575</v>
       </c>
       <c r="I168">
-        <v>0.86821714285714269</v>
+        <v>0.52181843478260892</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
@@ -5589,13 +5589,13 @@
         <v>39</v>
       </c>
       <c r="G169">
-        <v>0.77499999999999991</v>
+        <v>0.46400000000000008</v>
       </c>
       <c r="H169">
-        <v>0.9392999999999998</v>
+        <v>0.48086308571428582</v>
       </c>
       <c r="I169">
-        <v>0.74683428571428556</v>
+        <v>0.41609906086956538</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.3">
@@ -5618,13 +5618,13 @@
         <v>39</v>
       </c>
       <c r="G170">
-        <v>0.64999999999999991</v>
+        <v>0.37120000000000009</v>
       </c>
       <c r="H170">
-        <v>0.79169999999999996</v>
+        <v>0.38507227428571439</v>
       </c>
       <c r="I170">
-        <v>0.62570857142857128</v>
+        <v>0.33179469913043491</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
@@ -5647,13 +5647,13 @@
         <v>39</v>
       </c>
       <c r="G171">
-        <v>0.52499999999999991</v>
+        <v>0.29696000000000011</v>
       </c>
       <c r="H171">
-        <v>0.64259999999999995</v>
+        <v>0.30836326400000008</v>
       </c>
       <c r="I171">
-        <v>0.50483999999999984</v>
+        <v>0.26456811965217403</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
@@ -5676,13 +5676,13 @@
         <v>30</v>
       </c>
       <c r="G172">
-        <v>90.260000000000019</v>
+        <v>90.42</v>
       </c>
       <c r="H172">
-        <v>87.552200000000013</v>
+        <v>87.707399999999993</v>
       </c>
       <c r="I172">
-        <v>93.538188902985453</v>
+        <v>93.70400000673547</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
@@ -5705,13 +5705,13 @@
         <v>30</v>
       </c>
       <c r="G173">
-        <v>91.157000000000011</v>
+        <v>91.365000000000009</v>
       </c>
       <c r="H173">
-        <v>88.340248700000004</v>
+        <v>88.541821500000012</v>
       </c>
       <c r="I173">
-        <v>94.56709042548556</v>
+        <v>94.782871493406859</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
@@ -5734,13 +5734,13 @@
         <v>30</v>
       </c>
       <c r="G174">
-        <v>92.054000000000016</v>
+        <v>92.31</v>
       </c>
       <c r="H174">
-        <v>89.126682800000012</v>
+        <v>89.374542000000005</v>
       </c>
       <c r="I174">
-        <v>95.597946658009604</v>
+        <v>95.863802289969655</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
@@ -5763,13 +5763,13 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>92.951000000000022</v>
+        <v>93.25500000000001</v>
       </c>
       <c r="H175">
-        <v>89.911502300000009</v>
+        <v>90.205561500000002</v>
       </c>
       <c r="I175">
-        <v>96.630757600557587</v>
+        <v>96.946792396423888</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.3">
@@ -5792,13 +5792,13 @@
         <v>30</v>
       </c>
       <c r="G176">
-        <v>93.848000000000027</v>
+        <v>94.2</v>
       </c>
       <c r="H176">
-        <v>90.694707200000011</v>
+        <v>91.034879999999987</v>
       </c>
       <c r="I176">
-        <v>97.665523253129464</v>
+        <v>98.0318418127695</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.3">
@@ -5821,13 +5821,13 @@
         <v>35</v>
       </c>
       <c r="G177">
-        <v>89.53064866112652</v>
+        <v>89.680861034164366</v>
       </c>
       <c r="H177">
-        <v>86.844729201292722</v>
+        <v>86.990435203139427</v>
       </c>
       <c r="I177">
-        <v>92.782347962234354</v>
+        <v>92.93801595829882</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
@@ -5850,13 +5850,13 @@
         <v>35</v>
       </c>
       <c r="G178">
-        <v>90.361282086795953</v>
+        <v>90.58039935364728</v>
       </c>
       <c r="H178">
-        <v>87.569118470313967</v>
+        <v>87.781465013619567</v>
       </c>
       <c r="I178">
-        <v>93.741605516469846</v>
+        <v>93.968919736860101</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.3">
@@ -5879,13 +5879,13 @@
         <v>35</v>
       </c>
       <c r="G179">
-        <v>91.30460249307481</v>
+        <v>91.605034626038787</v>
       </c>
       <c r="H179">
-        <v>88.401116133795028</v>
+        <v>88.691994524930763</v>
       </c>
       <c r="I179">
-        <v>94.819698424443658</v>
+        <v>95.131696762608669</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
@@ -5908,13 +5908,13 @@
         <v>35</v>
       </c>
       <c r="G180">
-        <v>92.360609879963079</v>
+        <v>92.754766851338871</v>
       </c>
       <c r="H180">
-        <v>89.340417936888272</v>
+        <v>89.72168597530009</v>
       </c>
       <c r="I180">
-        <v>96.016995031257053</v>
+        <v>96.426755945691355</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.3">
@@ -5937,13 +5937,13 @@
         <v>35</v>
       </c>
       <c r="G181">
-        <v>93.529304247460772</v>
+        <v>94.029596029547562</v>
       </c>
       <c r="H181">
-        <v>90.386719624746092</v>
+        <v>90.870201602954765</v>
       </c>
       <c r="I181">
-        <v>97.333863682011312</v>
+        <v>97.854506196255059</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.3">
@@ -5963,7 +5963,7 @@
         <v>12</v>
       </c>
       <c r="F182" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G182">
         <v>4.82</v>
@@ -5992,7 +5992,7 @@
         <v>14</v>
       </c>
       <c r="F183" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G183">
         <v>4.8499999999999996</v>
@@ -6021,7 +6021,7 @@
         <v>16</v>
       </c>
       <c r="F184" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G184">
         <v>4.87</v>
@@ -6050,7 +6050,7 @@
         <v>18</v>
       </c>
       <c r="F185" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G185">
         <v>4.91</v>
@@ -6079,7 +6079,7 @@
         <v>20</v>
       </c>
       <c r="F186" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G186">
         <v>4.96</v>
@@ -6108,7 +6108,7 @@
         <v>12</v>
       </c>
       <c r="F187" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G187" s="3">
         <v>144368.4</v>
@@ -6137,7 +6137,7 @@
         <v>14</v>
       </c>
       <c r="F188" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G188" s="3">
         <v>158805.24</v>
@@ -6166,7 +6166,7 @@
         <v>16</v>
       </c>
       <c r="F189" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G189" s="3">
         <v>174685.76400000011</v>
@@ -6195,7 +6195,7 @@
         <v>18</v>
       </c>
       <c r="F190" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G190" s="3">
         <v>192154.34039999999</v>
@@ -6224,7 +6224,7 @@
         <v>20</v>
       </c>
       <c r="F191" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G191" s="3">
         <v>211369.7744400001</v>
@@ -6240,8 +6240,8 @@
       <c r="A192" s="3">
         <v>367</v>
       </c>
-      <c r="B192" s="3" t="s">
-        <v>54</v>
+      <c r="B192" t="s">
+        <v>77</v>
       </c>
       <c r="C192" s="4">
         <v>46387</v>
@@ -6269,8 +6269,8 @@
       <c r="A193" s="3">
         <v>367</v>
       </c>
-      <c r="B193" s="3" t="s">
-        <v>54</v>
+      <c r="B193" t="s">
+        <v>77</v>
       </c>
       <c r="C193" s="4">
         <v>46752</v>
@@ -6298,8 +6298,8 @@
       <c r="A194" s="3">
         <v>367</v>
       </c>
-      <c r="B194" s="3" t="s">
-        <v>54</v>
+      <c r="B194" t="s">
+        <v>77</v>
       </c>
       <c r="C194" s="4">
         <v>47118</v>
@@ -6327,8 +6327,8 @@
       <c r="A195" s="3">
         <v>367</v>
       </c>
-      <c r="B195" s="3" t="s">
-        <v>54</v>
+      <c r="B195" t="s">
+        <v>77</v>
       </c>
       <c r="C195" s="4">
         <v>47483</v>
@@ -6356,8 +6356,8 @@
       <c r="A196" s="3">
         <v>367</v>
       </c>
-      <c r="B196" s="3" t="s">
-        <v>54</v>
+      <c r="B196" t="s">
+        <v>77</v>
       </c>
       <c r="C196" s="4">
         <v>47848</v>
@@ -6386,7 +6386,7 @@
         <v>369</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C197" s="4">
         <v>46387</v>
@@ -6398,7 +6398,7 @@
         <v>12</v>
       </c>
       <c r="F197" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G197" s="3">
         <v>73.44</v>
@@ -6415,7 +6415,7 @@
         <v>369</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C198" s="4">
         <v>46752</v>
@@ -6427,7 +6427,7 @@
         <v>14</v>
       </c>
       <c r="F198" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G198" s="3">
         <v>74.908799999999999</v>
@@ -6444,7 +6444,7 @@
         <v>369</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C199" s="4">
         <v>47118</v>
@@ -6456,7 +6456,7 @@
         <v>16</v>
       </c>
       <c r="F199" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G199" s="3">
         <v>76.406976000000014</v>
@@ -6473,7 +6473,7 @@
         <v>369</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C200" s="4">
         <v>47483</v>
@@ -6485,7 +6485,7 @@
         <v>18</v>
       </c>
       <c r="F200" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G200" s="3">
         <v>77.935115519999997</v>
@@ -6502,7 +6502,7 @@
         <v>369</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C201" s="4">
         <v>47848</v>
@@ -6514,7 +6514,7 @@
         <v>20</v>
       </c>
       <c r="F201" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G201" s="3">
         <v>79.493817830400005</v>
@@ -6531,7 +6531,7 @@
         <v>377</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C202" s="4">
         <v>46387</v>
@@ -6543,16 +6543,16 @@
         <v>12</v>
       </c>
       <c r="F202" t="s">
-        <v>79</v>
-      </c>
-      <c r="G202" s="3">
-        <v>13739.770610699999</v>
-      </c>
-      <c r="H202" s="3">
-        <v>10991.81648856</v>
-      </c>
-      <c r="I202" s="3">
-        <v>16487.724732840001</v>
+        <v>76</v>
+      </c>
+      <c r="G202">
+        <v>11828.030016950001</v>
+      </c>
+      <c r="H202">
+        <v>9462.4240135599994</v>
+      </c>
+      <c r="I202">
+        <v>14193.63602034</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.3">
@@ -6560,7 +6560,7 @@
         <v>377</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C203" s="4">
         <v>46752</v>
@@ -6572,16 +6572,16 @@
         <v>14</v>
       </c>
       <c r="F203" t="s">
-        <v>79</v>
-      </c>
-      <c r="G203" s="3">
-        <v>15800.736202304999</v>
-      </c>
-      <c r="H203" s="3">
-        <v>12545.784544630171</v>
-      </c>
-      <c r="I203" s="3">
-        <v>19055.687859979829</v>
+        <v>76</v>
+      </c>
+      <c r="G203">
+        <v>13602.2345194925</v>
+      </c>
+      <c r="H203">
+        <v>10800.174208477039</v>
+      </c>
+      <c r="I203">
+        <v>16404.294830507952</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.3">
@@ -6589,7 +6589,7 @@
         <v>377</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C204" s="4">
         <v>47118</v>
@@ -6601,16 +6601,16 @@
         <v>16</v>
       </c>
       <c r="F204" t="s">
-        <v>79</v>
-      </c>
-      <c r="G204" s="3">
-        <v>18170.846632650751</v>
-      </c>
-      <c r="H204" s="3">
-        <v>14318.62714652879</v>
-      </c>
-      <c r="I204" s="3">
-        <v>22023.066118772709</v>
+        <v>76</v>
+      </c>
+      <c r="G204">
+        <v>15642.569697416369</v>
+      </c>
+      <c r="H204">
+        <v>12326.344921564099</v>
+      </c>
+      <c r="I204">
+        <v>18958.794473268641</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.3">
@@ -6618,7 +6618,7 @@
         <v>377</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C205" s="4">
         <v>47483</v>
@@ -6630,16 +6630,16 @@
         <v>18</v>
       </c>
       <c r="F205" t="s">
-        <v>79</v>
-      </c>
-      <c r="G205" s="3">
-        <v>20896.473627548359</v>
-      </c>
-      <c r="H205" s="3">
-        <v>16341.042376742809</v>
-      </c>
-      <c r="I205" s="3">
-        <v>25451.9048783539</v>
+        <v>76</v>
+      </c>
+      <c r="G205">
+        <v>17988.95515202883</v>
+      </c>
+      <c r="H205">
+        <v>14067.36292888654</v>
+      </c>
+      <c r="I205">
+        <v>21910.547375171111</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.3">
@@ -6647,7 +6647,7 @@
         <v>377</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C206" s="4">
         <v>47848</v>
@@ -6659,16 +6659,16 @@
         <v>20</v>
       </c>
       <c r="F206" t="s">
-        <v>79</v>
-      </c>
-      <c r="G206" s="3">
-        <v>24030.944671680609</v>
-      </c>
-      <c r="H206" s="3">
-        <v>18648.01306522415</v>
-      </c>
-      <c r="I206" s="3">
-        <v>29413.876278137071</v>
+        <v>76</v>
+      </c>
+      <c r="G206">
+        <v>20687.298424833149</v>
+      </c>
+      <c r="H206">
+        <v>16053.343577670519</v>
+      </c>
+      <c r="I206">
+        <v>25321.253271995771</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.3">
@@ -6676,7 +6676,7 @@
         <v>424</v>
       </c>
       <c r="B207" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C207" s="2">
         <v>46387</v>
@@ -6705,7 +6705,7 @@
         <v>424</v>
       </c>
       <c r="B208" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C208" s="2">
         <v>46752</v>
@@ -6734,7 +6734,7 @@
         <v>424</v>
       </c>
       <c r="B209" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C209" s="2">
         <v>47118</v>
@@ -6763,7 +6763,7 @@
         <v>424</v>
       </c>
       <c r="B210" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C210" s="2">
         <v>47483</v>
@@ -6792,7 +6792,7 @@
         <v>424</v>
       </c>
       <c r="B211" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C211" s="2">
         <v>47848</v>
@@ -6821,7 +6821,7 @@
         <v>460</v>
       </c>
       <c r="B212" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C212" s="2">
         <v>46387</v>
@@ -6833,7 +6833,7 @@
         <v>12</v>
       </c>
       <c r="F212" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G212">
         <v>92.354399999999998</v>
@@ -6850,7 +6850,7 @@
         <v>460</v>
       </c>
       <c r="B213" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C213" s="2">
         <v>46752</v>
@@ -6862,7 +6862,7 @@
         <v>14</v>
       </c>
       <c r="F213" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G213">
         <v>93.277944000000005</v>
@@ -6879,7 +6879,7 @@
         <v>460</v>
       </c>
       <c r="B214" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C214" s="2">
         <v>47118</v>
@@ -6891,7 +6891,7 @@
         <v>16</v>
       </c>
       <c r="F214" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G214">
         <v>94.21072344000001</v>
@@ -6908,7 +6908,7 @@
         <v>460</v>
       </c>
       <c r="B215" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C215" s="2">
         <v>47483</v>
@@ -6920,7 +6920,7 @@
         <v>18</v>
       </c>
       <c r="F215" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G215">
         <v>95.152830674399993</v>
@@ -6937,7 +6937,7 @@
         <v>460</v>
       </c>
       <c r="B216" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C216" s="2">
         <v>47848</v>
@@ -6949,7 +6949,7 @@
         <v>20</v>
       </c>
       <c r="F216" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G216">
         <v>96.104358981144017</v>
@@ -6966,7 +6966,7 @@
         <v>77</v>
       </c>
       <c r="B217" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C217" s="2">
         <v>46387</v>
@@ -6995,7 +6995,7 @@
         <v>77</v>
       </c>
       <c r="B218" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C218" s="2">
         <v>46752</v>
@@ -7024,7 +7024,7 @@
         <v>77</v>
       </c>
       <c r="B219" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C219" s="2">
         <v>47118</v>
@@ -7053,7 +7053,7 @@
         <v>77</v>
       </c>
       <c r="B220" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C220" s="2">
         <v>47483</v>
@@ -7082,7 +7082,7 @@
         <v>77</v>
       </c>
       <c r="B221" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C221" s="2">
         <v>47848</v>
@@ -7111,7 +7111,7 @@
         <v>98</v>
       </c>
       <c r="B222" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C222" s="2">
         <v>46387</v>
@@ -7140,7 +7140,7 @@
         <v>98</v>
       </c>
       <c r="B223" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C223" s="2">
         <v>46752</v>
@@ -7169,7 +7169,7 @@
         <v>98</v>
       </c>
       <c r="B224" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C224" s="2">
         <v>47118</v>
@@ -7198,7 +7198,7 @@
         <v>98</v>
       </c>
       <c r="B225" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C225" s="2">
         <v>47483</v>
@@ -7227,7 +7227,7 @@
         <v>98</v>
       </c>
       <c r="B226" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C226" s="2">
         <v>47848</v>
@@ -7256,7 +7256,7 @@
         <v>386.1</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C227" s="4">
         <v>46387</v>
@@ -7285,7 +7285,7 @@
         <v>386.1</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C228" s="4">
         <v>46752</v>
@@ -7314,7 +7314,7 @@
         <v>386.1</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C229" s="4">
         <v>47118</v>
@@ -7343,7 +7343,7 @@
         <v>386.1</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C230" s="4">
         <v>47483</v>
@@ -7372,7 +7372,7 @@
         <v>386.1</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C231" s="4">
         <v>47848</v>
@@ -7401,7 +7401,7 @@
         <v>386.2</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C232" s="4">
         <v>46387</v>
@@ -7430,7 +7430,7 @@
         <v>386.2</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C233" s="4">
         <v>46752</v>
@@ -7459,7 +7459,7 @@
         <v>386.2</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C234" s="4">
         <v>47118</v>
@@ -7488,7 +7488,7 @@
         <v>386.2</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C235" s="4">
         <v>47483</v>
@@ -7517,7 +7517,7 @@
         <v>386.2</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C236" s="4">
         <v>47848</v>
@@ -7546,7 +7546,7 @@
         <v>386.3</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C237" s="4">
         <v>46387</v>
@@ -7575,7 +7575,7 @@
         <v>386.3</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C238" s="4">
         <v>46752</v>
@@ -7604,7 +7604,7 @@
         <v>386.3</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C239" s="4">
         <v>47118</v>
@@ -7633,7 +7633,7 @@
         <v>386.3</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C240" s="4">
         <v>47483</v>
@@ -7662,7 +7662,7 @@
         <v>386.3</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C241" s="4">
         <v>47848</v>
@@ -7691,7 +7691,7 @@
         <v>379</v>
       </c>
       <c r="B242" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C242" s="2">
         <v>46203</v>
@@ -7720,7 +7720,7 @@
         <v>274</v>
       </c>
       <c r="B243" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C243" s="2">
         <v>46203</v>
@@ -7749,7 +7749,7 @@
         <v>379</v>
       </c>
       <c r="B244" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C244" s="2">
         <v>46387</v>
@@ -7778,7 +7778,7 @@
         <v>274</v>
       </c>
       <c r="B245" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C245" s="2">
         <v>46387</v>
@@ -7807,7 +7807,7 @@
         <v>379</v>
       </c>
       <c r="B246" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C246" s="2">
         <v>46568</v>
@@ -7836,7 +7836,7 @@
         <v>274</v>
       </c>
       <c r="B247" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C247" s="2">
         <v>46568</v>
@@ -7865,7 +7865,7 @@
         <v>379</v>
       </c>
       <c r="B248" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C248" s="2">
         <v>46752</v>
@@ -7894,7 +7894,7 @@
         <v>274</v>
       </c>
       <c r="B249" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C249" s="2">
         <v>46752</v>
@@ -7923,7 +7923,7 @@
         <v>379</v>
       </c>
       <c r="B250" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C250" s="2">
         <v>46934</v>
@@ -7952,7 +7952,7 @@
         <v>274</v>
       </c>
       <c r="B251" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C251" s="2">
         <v>46934</v>
@@ -7981,7 +7981,7 @@
         <v>379</v>
       </c>
       <c r="B252" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C252" s="2">
         <v>47118</v>
@@ -8010,7 +8010,7 @@
         <v>274</v>
       </c>
       <c r="B253" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C253" s="2">
         <v>47118</v>
@@ -8039,7 +8039,7 @@
         <v>379</v>
       </c>
       <c r="B254" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C254" s="2">
         <v>47299</v>
@@ -8068,7 +8068,7 @@
         <v>274</v>
       </c>
       <c r="B255" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C255" s="2">
         <v>47299</v>
@@ -8097,7 +8097,7 @@
         <v>379</v>
       </c>
       <c r="B256" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C256" s="2">
         <v>47483</v>
@@ -8126,7 +8126,7 @@
         <v>274</v>
       </c>
       <c r="B257" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C257" s="2">
         <v>47483</v>
@@ -8155,7 +8155,7 @@
         <v>379</v>
       </c>
       <c r="B258" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C258" s="2">
         <v>47664</v>
@@ -8184,7 +8184,7 @@
         <v>274</v>
       </c>
       <c r="B259" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C259" s="2">
         <v>47664</v>
@@ -8213,7 +8213,7 @@
         <v>379</v>
       </c>
       <c r="B260" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C260" s="2">
         <v>47848</v>
@@ -8242,7 +8242,7 @@
         <v>274</v>
       </c>
       <c r="B261" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C261" s="2">
         <v>47848</v>
@@ -8851,7 +8851,7 @@
         <v>379</v>
       </c>
       <c r="B282" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C282" s="2">
         <v>46203</v>
@@ -8880,7 +8880,7 @@
         <v>274</v>
       </c>
       <c r="B283" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C283" s="2">
         <v>46203</v>
@@ -8909,7 +8909,7 @@
         <v>379</v>
       </c>
       <c r="B284" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C284" s="2">
         <v>46387</v>
@@ -8938,7 +8938,7 @@
         <v>274</v>
       </c>
       <c r="B285" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C285" s="2">
         <v>46387</v>
@@ -8967,7 +8967,7 @@
         <v>379</v>
       </c>
       <c r="B286" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C286" s="2">
         <v>46568</v>
@@ -8996,7 +8996,7 @@
         <v>274</v>
       </c>
       <c r="B287" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C287" s="2">
         <v>46568</v>
@@ -9025,7 +9025,7 @@
         <v>379</v>
       </c>
       <c r="B288" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C288" s="2">
         <v>46752</v>
@@ -9054,7 +9054,7 @@
         <v>274</v>
       </c>
       <c r="B289" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C289" s="2">
         <v>46752</v>
@@ -9083,7 +9083,7 @@
         <v>379</v>
       </c>
       <c r="B290" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C290" s="2">
         <v>46934</v>
@@ -9112,7 +9112,7 @@
         <v>274</v>
       </c>
       <c r="B291" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C291" s="2">
         <v>46934</v>
@@ -9141,7 +9141,7 @@
         <v>379</v>
       </c>
       <c r="B292" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C292" s="2">
         <v>47118</v>
@@ -9170,7 +9170,7 @@
         <v>274</v>
       </c>
       <c r="B293" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C293" s="2">
         <v>47118</v>
@@ -9199,7 +9199,7 @@
         <v>379</v>
       </c>
       <c r="B294" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C294" s="2">
         <v>47299</v>
@@ -9228,7 +9228,7 @@
         <v>274</v>
       </c>
       <c r="B295" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C295" s="2">
         <v>47299</v>
@@ -9257,7 +9257,7 @@
         <v>379</v>
       </c>
       <c r="B296" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C296" s="2">
         <v>47483</v>
@@ -9286,7 +9286,7 @@
         <v>274</v>
       </c>
       <c r="B297" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C297" s="2">
         <v>47483</v>
@@ -9315,7 +9315,7 @@
         <v>379</v>
       </c>
       <c r="B298" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C298" s="2">
         <v>47664</v>
@@ -9344,7 +9344,7 @@
         <v>274</v>
       </c>
       <c r="B299" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C299" s="2">
         <v>47664</v>
@@ -9373,7 +9373,7 @@
         <v>379</v>
       </c>
       <c r="B300" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C300" s="2">
         <v>47848</v>
@@ -9402,7 +9402,7 @@
         <v>274</v>
       </c>
       <c r="B301" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C301" s="2">
         <v>47848</v>
@@ -9431,7 +9431,7 @@
         <v>14.1</v>
       </c>
       <c r="B302" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C302" s="2">
         <v>46203</v>
@@ -9460,7 +9460,7 @@
         <v>14.2</v>
       </c>
       <c r="B303" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C303" s="2">
         <v>46203</v>
@@ -9489,7 +9489,7 @@
         <v>14.1</v>
       </c>
       <c r="B304" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C304" s="2">
         <v>46387</v>
@@ -9518,7 +9518,7 @@
         <v>14.2</v>
       </c>
       <c r="B305" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C305" s="2">
         <v>46387</v>
@@ -9547,7 +9547,7 @@
         <v>14.1</v>
       </c>
       <c r="B306" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C306" s="2">
         <v>46568</v>
@@ -9576,7 +9576,7 @@
         <v>14.2</v>
       </c>
       <c r="B307" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C307" s="2">
         <v>46568</v>
@@ -9605,7 +9605,7 @@
         <v>14.1</v>
       </c>
       <c r="B308" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C308" s="2">
         <v>46752</v>
@@ -9634,7 +9634,7 @@
         <v>14.2</v>
       </c>
       <c r="B309" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C309" s="2">
         <v>46752</v>
@@ -9663,7 +9663,7 @@
         <v>14.1</v>
       </c>
       <c r="B310" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C310" s="2">
         <v>46934</v>
@@ -9692,7 +9692,7 @@
         <v>14.2</v>
       </c>
       <c r="B311" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C311" s="2">
         <v>46934</v>
@@ -9721,7 +9721,7 @@
         <v>14.1</v>
       </c>
       <c r="B312" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C312" s="2">
         <v>47118</v>
@@ -9750,7 +9750,7 @@
         <v>14.2</v>
       </c>
       <c r="B313" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C313" s="2">
         <v>47118</v>
@@ -9779,7 +9779,7 @@
         <v>14.1</v>
       </c>
       <c r="B314" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C314" s="2">
         <v>47299</v>
@@ -9808,7 +9808,7 @@
         <v>14.2</v>
       </c>
       <c r="B315" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C315" s="2">
         <v>47299</v>
@@ -9837,7 +9837,7 @@
         <v>14.1</v>
       </c>
       <c r="B316" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C316" s="2">
         <v>47483</v>
@@ -9866,7 +9866,7 @@
         <v>14.2</v>
       </c>
       <c r="B317" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C317" s="2">
         <v>47483</v>
@@ -9895,7 +9895,7 @@
         <v>14.1</v>
       </c>
       <c r="B318" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C318" s="2">
         <v>47664</v>
@@ -9924,7 +9924,7 @@
         <v>14.2</v>
       </c>
       <c r="B319" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C319" s="2">
         <v>47664</v>
@@ -9953,7 +9953,7 @@
         <v>14.1</v>
       </c>
       <c r="B320" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C320" s="2">
         <v>47848</v>
@@ -9982,7 +9982,7 @@
         <v>14.2</v>
       </c>
       <c r="B321" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C321" s="2">
         <v>47848</v>
@@ -10011,7 +10011,7 @@
         <v>14.1</v>
       </c>
       <c r="B322" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C322" s="2">
         <v>46203</v>
@@ -10040,7 +10040,7 @@
         <v>14.2</v>
       </c>
       <c r="B323" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C323" s="2">
         <v>46203</v>
@@ -10069,7 +10069,7 @@
         <v>14.1</v>
       </c>
       <c r="B324" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C324" s="2">
         <v>46387</v>
@@ -10098,7 +10098,7 @@
         <v>14.2</v>
       </c>
       <c r="B325" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C325" s="2">
         <v>46387</v>
@@ -10127,7 +10127,7 @@
         <v>14.1</v>
       </c>
       <c r="B326" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C326" s="2">
         <v>46568</v>
@@ -10156,7 +10156,7 @@
         <v>14.2</v>
       </c>
       <c r="B327" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C327" s="2">
         <v>46568</v>
@@ -10185,7 +10185,7 @@
         <v>14.1</v>
       </c>
       <c r="B328" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C328" s="2">
         <v>46752</v>
@@ -10214,7 +10214,7 @@
         <v>14.2</v>
       </c>
       <c r="B329" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C329" s="2">
         <v>46752</v>
@@ -10243,7 +10243,7 @@
         <v>14.1</v>
       </c>
       <c r="B330" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C330" s="2">
         <v>46934</v>
@@ -10272,7 +10272,7 @@
         <v>14.2</v>
       </c>
       <c r="B331" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C331" s="2">
         <v>46934</v>
@@ -10301,7 +10301,7 @@
         <v>14.1</v>
       </c>
       <c r="B332" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C332" s="2">
         <v>47118</v>
@@ -10330,7 +10330,7 @@
         <v>14.2</v>
       </c>
       <c r="B333" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C333" s="2">
         <v>47118</v>
@@ -10359,7 +10359,7 @@
         <v>14.1</v>
       </c>
       <c r="B334" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C334" s="2">
         <v>47299</v>
@@ -10388,7 +10388,7 @@
         <v>14.2</v>
       </c>
       <c r="B335" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C335" s="2">
         <v>47299</v>
@@ -10417,7 +10417,7 @@
         <v>14.1</v>
       </c>
       <c r="B336" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C336" s="2">
         <v>47483</v>
@@ -10446,7 +10446,7 @@
         <v>14.2</v>
       </c>
       <c r="B337" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C337" s="2">
         <v>47483</v>
@@ -10475,7 +10475,7 @@
         <v>14.1</v>
       </c>
       <c r="B338" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C338" s="2">
         <v>47664</v>
@@ -10504,7 +10504,7 @@
         <v>14.2</v>
       </c>
       <c r="B339" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C339" s="2">
         <v>47664</v>
@@ -10533,7 +10533,7 @@
         <v>14.1</v>
       </c>
       <c r="B340" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C340" s="2">
         <v>47848</v>
@@ -10562,7 +10562,7 @@
         <v>14.2</v>
       </c>
       <c r="B341" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C341" s="2">
         <v>47848</v>
@@ -10591,7 +10591,7 @@
         <v>14.3</v>
       </c>
       <c r="B342" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C342" s="2">
         <v>46203</v>
@@ -10620,7 +10620,7 @@
         <v>14.4</v>
       </c>
       <c r="B343" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C343" s="2">
         <v>46203</v>
@@ -10649,7 +10649,7 @@
         <v>14.3</v>
       </c>
       <c r="B344" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C344" s="2">
         <v>46387</v>
@@ -10678,7 +10678,7 @@
         <v>14.4</v>
       </c>
       <c r="B345" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C345" s="2">
         <v>46387</v>
@@ -10707,7 +10707,7 @@
         <v>14.3</v>
       </c>
       <c r="B346" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C346" s="2">
         <v>46568</v>
@@ -10736,7 +10736,7 @@
         <v>14.4</v>
       </c>
       <c r="B347" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C347" s="2">
         <v>46568</v>
@@ -10765,7 +10765,7 @@
         <v>14.3</v>
       </c>
       <c r="B348" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C348" s="2">
         <v>46752</v>
@@ -10794,7 +10794,7 @@
         <v>14.4</v>
       </c>
       <c r="B349" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C349" s="2">
         <v>46752</v>
@@ -10823,7 +10823,7 @@
         <v>14.3</v>
       </c>
       <c r="B350" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C350" s="2">
         <v>46934</v>
@@ -10852,7 +10852,7 @@
         <v>14.4</v>
       </c>
       <c r="B351" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C351" s="2">
         <v>46934</v>
@@ -10881,7 +10881,7 @@
         <v>14.3</v>
       </c>
       <c r="B352" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C352" s="2">
         <v>47118</v>
@@ -10910,7 +10910,7 @@
         <v>14.4</v>
       </c>
       <c r="B353" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C353" s="2">
         <v>47118</v>
@@ -10939,7 +10939,7 @@
         <v>14.3</v>
       </c>
       <c r="B354" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C354" s="2">
         <v>47299</v>
@@ -10968,7 +10968,7 @@
         <v>14.4</v>
       </c>
       <c r="B355" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C355" s="2">
         <v>47299</v>
@@ -10997,7 +10997,7 @@
         <v>14.3</v>
       </c>
       <c r="B356" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C356" s="2">
         <v>47483</v>
@@ -11026,7 +11026,7 @@
         <v>14.4</v>
       </c>
       <c r="B357" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C357" s="2">
         <v>47483</v>
@@ -11055,7 +11055,7 @@
         <v>14.3</v>
       </c>
       <c r="B358" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C358" s="2">
         <v>47664</v>
@@ -11084,7 +11084,7 @@
         <v>14.4</v>
       </c>
       <c r="B359" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C359" s="2">
         <v>47664</v>
@@ -11113,7 +11113,7 @@
         <v>14.3</v>
       </c>
       <c r="B360" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C360" s="2">
         <v>47848</v>
@@ -11142,7 +11142,7 @@
         <v>14.4</v>
       </c>
       <c r="B361" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C361" s="2">
         <v>47848</v>
@@ -11171,7 +11171,7 @@
         <v>14.3</v>
       </c>
       <c r="B362" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C362" s="2">
         <v>46203</v>
@@ -11200,7 +11200,7 @@
         <v>14.4</v>
       </c>
       <c r="B363" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C363" s="2">
         <v>46203</v>
@@ -11229,7 +11229,7 @@
         <v>14.3</v>
       </c>
       <c r="B364" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C364" s="2">
         <v>46387</v>
@@ -11258,7 +11258,7 @@
         <v>14.4</v>
       </c>
       <c r="B365" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C365" s="2">
         <v>46387</v>
@@ -11287,7 +11287,7 @@
         <v>14.3</v>
       </c>
       <c r="B366" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C366" s="2">
         <v>46568</v>
@@ -11316,7 +11316,7 @@
         <v>14.4</v>
       </c>
       <c r="B367" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C367" s="2">
         <v>46568</v>
@@ -11345,7 +11345,7 @@
         <v>14.3</v>
       </c>
       <c r="B368" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C368" s="2">
         <v>46752</v>
@@ -11374,7 +11374,7 @@
         <v>14.4</v>
       </c>
       <c r="B369" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C369" s="2">
         <v>46752</v>
@@ -11403,7 +11403,7 @@
         <v>14.3</v>
       </c>
       <c r="B370" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C370" s="2">
         <v>46934</v>
@@ -11432,7 +11432,7 @@
         <v>14.4</v>
       </c>
       <c r="B371" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C371" s="2">
         <v>46934</v>
@@ -11461,7 +11461,7 @@
         <v>14.3</v>
       </c>
       <c r="B372" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C372" s="2">
         <v>47118</v>
@@ -11490,7 +11490,7 @@
         <v>14.4</v>
       </c>
       <c r="B373" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C373" s="2">
         <v>47118</v>
@@ -11519,7 +11519,7 @@
         <v>14.3</v>
       </c>
       <c r="B374" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C374" s="2">
         <v>47299</v>
@@ -11548,7 +11548,7 @@
         <v>14.4</v>
       </c>
       <c r="B375" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C375" s="2">
         <v>47299</v>
@@ -11577,7 +11577,7 @@
         <v>14.3</v>
       </c>
       <c r="B376" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C376" s="2">
         <v>47483</v>
@@ -11606,7 +11606,7 @@
         <v>14.4</v>
       </c>
       <c r="B377" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C377" s="2">
         <v>47483</v>
@@ -11635,7 +11635,7 @@
         <v>14.3</v>
       </c>
       <c r="B378" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C378" s="2">
         <v>47664</v>
@@ -11664,7 +11664,7 @@
         <v>14.4</v>
       </c>
       <c r="B379" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C379" s="2">
         <v>47664</v>
@@ -11693,7 +11693,7 @@
         <v>14.3</v>
       </c>
       <c r="B380" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C380" s="2">
         <v>47848</v>
@@ -11722,7 +11722,7 @@
         <v>14.4</v>
       </c>
       <c r="B381" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C381" s="2">
         <v>47848</v>
@@ -12186,7 +12186,7 @@
         <v>376</v>
       </c>
       <c r="B397" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C397" s="2">
         <v>46387</v>
@@ -12215,7 +12215,7 @@
         <v>376</v>
       </c>
       <c r="B398" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C398" s="2">
         <v>46752</v>
@@ -12244,7 +12244,7 @@
         <v>376</v>
       </c>
       <c r="B399" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C399" s="2">
         <v>47118</v>
@@ -12273,7 +12273,7 @@
         <v>376</v>
       </c>
       <c r="B400" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C400" s="2">
         <v>47483</v>
@@ -12302,7 +12302,7 @@
         <v>376</v>
       </c>
       <c r="B401" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C401" s="2">
         <v>47848</v>
@@ -12331,7 +12331,7 @@
         <v>376</v>
       </c>
       <c r="B402" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C402" s="2">
         <v>46387</v>
@@ -12360,7 +12360,7 @@
         <v>376</v>
       </c>
       <c r="B403" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C403" s="2">
         <v>46752</v>
@@ -12389,7 +12389,7 @@
         <v>376</v>
       </c>
       <c r="B404" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C404" s="2">
         <v>47118</v>
@@ -12418,7 +12418,7 @@
         <v>376</v>
       </c>
       <c r="B405" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C405" s="2">
         <v>47483</v>
@@ -12447,7 +12447,7 @@
         <v>376</v>
       </c>
       <c r="B406" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C406" s="2">
         <v>47848</v>
@@ -12476,7 +12476,7 @@
         <v>466</v>
       </c>
       <c r="B407" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C407" s="2">
         <v>46387</v>
@@ -12505,7 +12505,7 @@
         <v>466</v>
       </c>
       <c r="B408" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C408" s="2">
         <v>46752</v>
@@ -12534,7 +12534,7 @@
         <v>466</v>
       </c>
       <c r="B409" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C409" s="2">
         <v>47118</v>
@@ -12563,7 +12563,7 @@
         <v>466</v>
       </c>
       <c r="B410" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C410" s="2">
         <v>47483</v>
@@ -12592,7 +12592,7 @@
         <v>466</v>
       </c>
       <c r="B411" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C411" s="2">
         <v>47848</v>
@@ -12621,7 +12621,7 @@
         <v>466</v>
       </c>
       <c r="B412" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C412" s="2">
         <v>46387</v>
@@ -12650,7 +12650,7 @@
         <v>466</v>
       </c>
       <c r="B413" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C413" s="2">
         <v>46752</v>
@@ -12679,7 +12679,7 @@
         <v>466</v>
       </c>
       <c r="B414" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C414" s="2">
         <v>47118</v>
@@ -12708,7 +12708,7 @@
         <v>466</v>
       </c>
       <c r="B415" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C415" s="2">
         <v>47483</v>
@@ -12737,7 +12737,7 @@
         <v>466</v>
       </c>
       <c r="B416" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C416" s="2">
         <v>47848</v>
@@ -12766,7 +12766,7 @@
         <v>96</v>
       </c>
       <c r="B417" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C417" s="2">
         <v>46022</v>
@@ -12775,10 +12775,10 @@
         <v>2025</v>
       </c>
       <c r="E417" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F417" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G417">
         <v>846.88288415165562</v>
@@ -12795,7 +12795,7 @@
         <v>96</v>
       </c>
       <c r="B418" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C418" s="2">
         <v>46387</v>
@@ -12807,7 +12807,7 @@
         <v>22</v>
       </c>
       <c r="F418" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G418">
         <v>914.63351488378817</v>
@@ -12824,7 +12824,7 @@
         <v>96</v>
       </c>
       <c r="B419" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C419" s="2">
         <v>46752</v>
@@ -12836,7 +12836,7 @@
         <v>24</v>
       </c>
       <c r="F419" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G419">
         <v>987.8041960744913</v>
@@ -12853,7 +12853,7 @@
         <v>96</v>
       </c>
       <c r="B420" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C420" s="2">
         <v>47118</v>
@@ -12865,7 +12865,7 @@
         <v>25</v>
       </c>
       <c r="F420" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G420">
         <v>1066.8285317604509</v>
@@ -12882,7 +12882,7 @@
         <v>96</v>
       </c>
       <c r="B421" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C421" s="2">
         <v>47483</v>
@@ -12894,7 +12894,7 @@
         <v>26</v>
       </c>
       <c r="F421" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G421">
         <v>1152.1748143012869</v>
@@ -12911,7 +12911,7 @@
         <v>385</v>
       </c>
       <c r="B422" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C422" s="2">
         <v>46387</v>
@@ -12940,7 +12940,7 @@
         <v>385</v>
       </c>
       <c r="B423" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C423" s="2">
         <v>46752</v>
@@ -12969,7 +12969,7 @@
         <v>385</v>
       </c>
       <c r="B424" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C424" s="2">
         <v>47118</v>
@@ -12998,7 +12998,7 @@
         <v>385</v>
       </c>
       <c r="B425" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C425" s="2">
         <v>47483</v>
@@ -13027,7 +13027,7 @@
         <v>385</v>
       </c>
       <c r="B426" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C426" s="2">
         <v>47848</v>
@@ -13056,7 +13056,7 @@
         <v>385</v>
       </c>
       <c r="B427" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C427" s="2">
         <v>46387</v>
@@ -13085,7 +13085,7 @@
         <v>385</v>
       </c>
       <c r="B428" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C428" s="2">
         <v>46752</v>
@@ -13114,7 +13114,7 @@
         <v>385</v>
       </c>
       <c r="B429" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C429" s="2">
         <v>47118</v>
@@ -13143,7 +13143,7 @@
         <v>385</v>
       </c>
       <c r="B430" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C430" s="2">
         <v>47483</v>
@@ -13172,7 +13172,7 @@
         <v>385</v>
       </c>
       <c r="B431" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C431" s="2">
         <v>47848</v>
@@ -13201,7 +13201,7 @@
         <v>386.1</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C432" s="4">
         <v>46387</v>
@@ -13230,7 +13230,7 @@
         <v>386.1</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C433" s="4">
         <v>46752</v>
@@ -13259,7 +13259,7 @@
         <v>386.1</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C434" s="4">
         <v>47118</v>
@@ -13288,7 +13288,7 @@
         <v>386.1</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C435" s="4">
         <v>47483</v>
@@ -13317,7 +13317,7 @@
         <v>386.1</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C436" s="4">
         <v>47848</v>
@@ -13346,7 +13346,7 @@
         <v>386.2</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C437" s="4">
         <v>46387</v>
@@ -13375,7 +13375,7 @@
         <v>386.2</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C438" s="4">
         <v>46752</v>
@@ -13404,7 +13404,7 @@
         <v>386.2</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C439" s="4">
         <v>47118</v>
@@ -13433,7 +13433,7 @@
         <v>386.2</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C440" s="4">
         <v>47483</v>
@@ -13462,7 +13462,7 @@
         <v>386.2</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C441" s="4">
         <v>47848</v>
@@ -13491,7 +13491,7 @@
         <v>386.3</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C442" s="4">
         <v>46387</v>
@@ -13520,7 +13520,7 @@
         <v>386.3</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C443" s="4">
         <v>46752</v>
@@ -13549,7 +13549,7 @@
         <v>386.3</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C444" s="4">
         <v>47118</v>
@@ -13578,7 +13578,7 @@
         <v>386.3</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C445" s="4">
         <v>47483</v>
@@ -13607,7 +13607,7 @@
         <v>386.3</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C446" s="4">
         <v>47848</v>
@@ -13633,10 +13633,10 @@
     </row>
     <row r="447" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B447" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C447" s="2">
         <v>46387</v>
@@ -13662,10 +13662,10 @@
     </row>
     <row r="448" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B448" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C448" s="2">
         <v>46752</v>
@@ -13691,10 +13691,10 @@
     </row>
     <row r="449" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B449" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C449" s="2">
         <v>47118</v>
@@ -13720,10 +13720,10 @@
     </row>
     <row r="450" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B450" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C450" s="2">
         <v>47483</v>
@@ -13749,10 +13749,10 @@
     </row>
     <row r="451" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B451" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C451" s="2">
         <v>47848</v>
@@ -13778,10 +13778,10 @@
     </row>
     <row r="452" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B452" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C452" s="2">
         <v>46387</v>
@@ -13807,10 +13807,10 @@
     </row>
     <row r="453" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B453" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C453" s="2">
         <v>46752</v>
@@ -13836,10 +13836,10 @@
     </row>
     <row r="454" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B454" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C454" s="2">
         <v>47118</v>
@@ -13865,10 +13865,10 @@
     </row>
     <row r="455" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B455" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C455" s="2">
         <v>47483</v>
@@ -13894,10 +13894,10 @@
     </row>
     <row r="456" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B456" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C456" s="2">
         <v>47848</v>
@@ -13923,7 +13923,7 @@
     </row>
     <row r="457" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B457" t="s">
         <v>78</v>
@@ -13938,21 +13938,21 @@
         <v>12</v>
       </c>
       <c r="F457" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="G457">
-        <v>34.298999999999999</v>
+        <v>34.965000000000003</v>
       </c>
       <c r="H457">
-        <v>31.026750885006429</v>
+        <v>32.813568677938846</v>
       </c>
       <c r="I457">
-        <v>37.57124911499357</v>
+        <v>41.957999999999991</v>
       </c>
     </row>
     <row r="458" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B458" t="s">
         <v>78</v>
@@ -13967,21 +13967,21 @@
         <v>14</v>
       </c>
       <c r="F458" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="G458">
-        <v>35.327969999999993</v>
+        <v>36.713250000000002</v>
       </c>
       <c r="H458">
-        <v>31.85644091390332</v>
+        <v>34.386477025190871</v>
       </c>
       <c r="I458">
-        <v>38.799499086096667</v>
+        <v>44.276179499999998</v>
       </c>
     </row>
     <row r="459" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B459" t="s">
         <v>78</v>
@@ -13996,21 +13996,21 @@
         <v>16</v>
       </c>
       <c r="F459" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="G459">
-        <v>36.387809099999998</v>
+        <v>38.548912499999993</v>
       </c>
       <c r="H459">
-        <v>32.707988268737523</v>
+        <v>36.03464228547324</v>
       </c>
       <c r="I459">
-        <v>40.067629931262481</v>
+        <v>46.721281949999991</v>
       </c>
     </row>
     <row r="460" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B460" t="s">
         <v>78</v>
@@ -14025,21 +14025,21 @@
         <v>18</v>
       </c>
       <c r="F460" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="G460">
-        <v>37.479443373000002</v>
+        <v>40.476358124999997</v>
       </c>
       <c r="H460">
-        <v>33.581957668039273</v>
+        <v>37.76165787922087</v>
       </c>
       <c r="I460">
-        <v>41.376929077960739</v>
+        <v>49.300204196249993</v>
       </c>
     </row>
     <row r="461" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B461" t="s">
         <v>78</v>
@@ -14054,20 +14054,164 @@
         <v>20</v>
       </c>
       <c r="F461" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="G461">
-        <v>38.603826674190003</v>
+        <v>42.50017603125</v>
       </c>
       <c r="H461">
-        <v>34.478928041857237</v>
+        <v>39.571288426629593</v>
       </c>
       <c r="I461">
-        <v>42.728725306522747</v>
+        <v>52.020215462249993</v>
+      </c>
+    </row>
+    <row r="462" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A462">
+        <v>332</v>
+      </c>
+      <c r="B462" t="s">
+        <v>50</v>
+      </c>
+      <c r="C462" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D462">
+        <v>2026</v>
+      </c>
+      <c r="E462" t="s">
+        <v>12</v>
+      </c>
+      <c r="F462" t="s">
+        <v>34</v>
+      </c>
+      <c r="G462">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="H462">
+        <v>0.79122857142857139</v>
+      </c>
+      <c r="I462">
+        <v>0.69049565217391329</v>
+      </c>
+    </row>
+    <row r="463" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A463">
+        <v>332</v>
+      </c>
+      <c r="B463" t="s">
+        <v>50</v>
+      </c>
+      <c r="C463" s="2">
+        <v>46752</v>
+      </c>
+      <c r="D463">
+        <v>2027</v>
+      </c>
+      <c r="E463" t="s">
+        <v>14</v>
+      </c>
+      <c r="F463" t="s">
+        <v>34</v>
+      </c>
+      <c r="G463">
+        <v>0.6885</v>
+      </c>
+      <c r="H463">
+        <v>0.71281388571428561</v>
+      </c>
+      <c r="I463">
+        <v>0.61943446956521764</v>
+      </c>
+    </row>
+    <row r="464" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A464">
+        <v>332</v>
+      </c>
+      <c r="B464" t="s">
+        <v>50</v>
+      </c>
+      <c r="C464" s="2">
+        <v>47118</v>
+      </c>
+      <c r="D464">
+        <v>2028</v>
+      </c>
+      <c r="E464" t="s">
+        <v>16</v>
+      </c>
+      <c r="F464" t="s">
+        <v>34</v>
+      </c>
+      <c r="G464">
+        <v>0.61965000000000003</v>
+      </c>
+      <c r="H464">
+        <v>0.64216985142857141</v>
+      </c>
+      <c r="I464">
+        <v>0.5556805669565219</v>
+      </c>
+    </row>
+    <row r="465" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A465">
+        <v>332</v>
+      </c>
+      <c r="B465" t="s">
+        <v>50</v>
+      </c>
+      <c r="C465" s="2">
+        <v>47483</v>
+      </c>
+      <c r="D465">
+        <v>2029</v>
+      </c>
+      <c r="E465" t="s">
+        <v>18</v>
+      </c>
+      <c r="F465" t="s">
+        <v>34</v>
+      </c>
+      <c r="G465">
+        <v>0.55768499999999999</v>
+      </c>
+      <c r="H465">
+        <v>0.57852648514285721</v>
+      </c>
+      <c r="I465">
+        <v>0.49848310017391317</v>
+      </c>
+    </row>
+    <row r="466" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A466">
+        <v>332</v>
+      </c>
+      <c r="B466" t="s">
+        <v>50</v>
+      </c>
+      <c r="C466" s="2">
+        <v>47848</v>
+      </c>
+      <c r="D466">
+        <v>2030</v>
+      </c>
+      <c r="E466" t="s">
+        <v>20</v>
+      </c>
+      <c r="F466" t="s">
+        <v>34</v>
+      </c>
+      <c r="G466">
+        <v>0.5019165000000001</v>
+      </c>
+      <c r="H466">
+        <v>0.52119009360000013</v>
+      </c>
+      <c r="I466">
+        <v>0.4471683210782611</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I461" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="711" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9874C7DE-2873-402B-A1C7-92BBBC2B0E3D}"/>
+  <xr:revisionPtr revIDLastSave="769" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{667BC7F2-5C26-4C08-9F6F-6D8E2B237192}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="74">
   <si>
     <t>Id</t>
   </si>
@@ -107,22 +107,7 @@
     <t>Nivel de Satisfacción Servicios Prestados - Comunicaciones Internas</t>
   </si>
   <si>
-    <t>2026</t>
-  </si>
-  <si>
     <t>Heurístico 2obs</t>
-  </si>
-  <si>
-    <t>2027</t>
-  </si>
-  <si>
-    <t>2028</t>
-  </si>
-  <si>
-    <t>2029</t>
-  </si>
-  <si>
-    <t>2030</t>
   </si>
   <si>
     <t>Estudiantes vinculados a investigación</t>
@@ -255,9 +240,6 @@
   </si>
   <si>
     <t>Estudiantes Posgrado</t>
-  </si>
-  <si>
-    <t>2025</t>
   </si>
   <si>
     <t>Ingresos totales de educación para la vida</t>
@@ -738,7 +720,7 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2">
         <v>87.327254990955836</v>
@@ -767,7 +749,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3">
         <v>89.678717759448261</v>
@@ -796,7 +778,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4">
         <v>91.472292114637227</v>
@@ -825,7 +807,7 @@
         <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5">
         <v>93.301737956929969</v>
@@ -854,7 +836,7 @@
         <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6">
         <v>95.167772716068569</v>
@@ -871,7 +853,7 @@
         <v>148</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2">
         <v>46203</v>
@@ -883,7 +865,7 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G7">
         <v>5.386000000000001</v>
@@ -900,7 +882,7 @@
         <v>148</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2">
         <v>46387</v>
@@ -912,7 +894,7 @@
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G8">
         <v>5.5362857142857154</v>
@@ -929,7 +911,7 @@
         <v>148</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2">
         <v>46568</v>
@@ -941,7 +923,7 @@
         <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G9">
         <v>5.6865714285714297</v>
@@ -958,7 +940,7 @@
         <v>148</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2">
         <v>46752</v>
@@ -970,7 +952,7 @@
         <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G10">
         <v>5.8368571428571441</v>
@@ -987,7 +969,7 @@
         <v>148</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C11" s="2">
         <v>46934</v>
@@ -999,7 +981,7 @@
         <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G11">
         <v>5.9871428571428584</v>
@@ -1016,7 +998,7 @@
         <v>148</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C12" s="2">
         <v>47118</v>
@@ -1028,7 +1010,7 @@
         <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G12">
         <v>6.1374285714285728</v>
@@ -1045,7 +1027,7 @@
         <v>148</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C13" s="2">
         <v>47299</v>
@@ -1057,7 +1039,7 @@
         <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G13">
         <v>6.2877142857142871</v>
@@ -1074,7 +1056,7 @@
         <v>148</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C14" s="2">
         <v>47483</v>
@@ -1086,7 +1068,7 @@
         <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G14">
         <v>6.4380000000000006</v>
@@ -1103,7 +1085,7 @@
         <v>148</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C15" s="2">
         <v>47664</v>
@@ -1115,7 +1097,7 @@
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G15">
         <v>6.5882857142857159</v>
@@ -1132,7 +1114,7 @@
         <v>148</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C16" s="2">
         <v>47848</v>
@@ -1144,7 +1126,7 @@
         <v>20</v>
       </c>
       <c r="F16" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G16">
         <v>6.7385714285714302</v>
@@ -1161,7 +1143,7 @@
         <v>148</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C17" s="2">
         <v>46203</v>
@@ -1173,7 +1155,7 @@
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G17">
         <v>5.1583252300892388</v>
@@ -1190,7 +1172,7 @@
         <v>148</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C18" s="2">
         <v>46387</v>
@@ -1202,7 +1184,7 @@
         <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G18">
         <v>5.2470829040598819</v>
@@ -1219,7 +1201,7 @@
         <v>148</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C19" s="2">
         <v>46568</v>
@@ -1231,7 +1213,7 @@
         <v>13</v>
       </c>
       <c r="F19" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G19">
         <v>5.3371612882599546</v>
@@ -1248,7 +1230,7 @@
         <v>148</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C20" s="2">
         <v>46752</v>
@@ -1260,7 +1242,7 @@
         <v>14</v>
       </c>
       <c r="F20" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G20">
         <v>5.4285603826894571</v>
@@ -1277,7 +1259,7 @@
         <v>148</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C21" s="2">
         <v>46934</v>
@@ -1289,7 +1271,7 @@
         <v>15</v>
       </c>
       <c r="F21" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G21">
         <v>5.5212801873483901</v>
@@ -1306,7 +1288,7 @@
         <v>148</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C22" s="2">
         <v>47118</v>
@@ -1318,7 +1300,7 @@
         <v>16</v>
       </c>
       <c r="F22" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G22">
         <v>5.6153207022367528</v>
@@ -1335,7 +1317,7 @@
         <v>148</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C23" s="2">
         <v>47299</v>
@@ -1347,7 +1329,7 @@
         <v>17</v>
       </c>
       <c r="F23" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G23">
         <v>5.7106819273545444</v>
@@ -1364,7 +1346,7 @@
         <v>148</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C24" s="2">
         <v>47483</v>
@@ -1376,7 +1358,7 @@
         <v>18</v>
       </c>
       <c r="F24" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G24">
         <v>5.8073638627017674</v>
@@ -1393,7 +1375,7 @@
         <v>148</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C25" s="2">
         <v>47664</v>
@@ -1405,7 +1387,7 @@
         <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G25">
         <v>5.9053665082784192</v>
@@ -1422,7 +1404,7 @@
         <v>148</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C26" s="2">
         <v>47848</v>
@@ -1434,7 +1416,7 @@
         <v>20</v>
       </c>
       <c r="F26" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G26">
         <v>6.0046898640845008</v>
@@ -1451,7 +1433,7 @@
         <v>148</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C27" s="2">
         <v>46203</v>
@@ -1463,7 +1445,7 @@
         <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G27">
         <v>5.3560000000000008</v>
@@ -1480,7 +1462,7 @@
         <v>148</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C28" s="2">
         <v>46387</v>
@@ -1492,7 +1474,7 @@
         <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G28">
         <v>5.51668</v>
@@ -1509,7 +1491,7 @@
         <v>148</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C29" s="2">
         <v>46568</v>
@@ -1521,7 +1503,7 @@
         <v>13</v>
       </c>
       <c r="F29" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G29">
         <v>5.6821804</v>
@@ -1538,7 +1520,7 @@
         <v>148</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C30" s="2">
         <v>46752</v>
@@ -1550,7 +1532,7 @@
         <v>14</v>
       </c>
       <c r="F30" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G30">
         <v>5.8526458120000013</v>
@@ -1567,7 +1549,7 @@
         <v>148</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C31" s="2">
         <v>46934</v>
@@ -1579,7 +1561,7 @@
         <v>15</v>
       </c>
       <c r="F31" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G31">
         <v>6.0282251863600003</v>
@@ -1596,7 +1578,7 @@
         <v>148</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C32" s="2">
         <v>47118</v>
@@ -1608,7 +1590,7 @@
         <v>16</v>
       </c>
       <c r="F32" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G32">
         <v>6.2090719419508007</v>
@@ -1625,7 +1607,7 @@
         <v>148</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C33" s="2">
         <v>47299</v>
@@ -1637,7 +1619,7 @@
         <v>17</v>
       </c>
       <c r="F33" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G33">
         <v>6.395344100209325</v>
@@ -1654,7 +1636,7 @@
         <v>148</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C34" s="2">
         <v>47483</v>
@@ -1666,7 +1648,7 @@
         <v>18</v>
       </c>
       <c r="F34" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G34">
         <v>6.5872044232156064</v>
@@ -1683,7 +1665,7 @@
         <v>148</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C35" s="2">
         <v>47664</v>
@@ -1695,7 +1677,7 @@
         <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G35">
         <v>6.7848205559120736</v>
@@ -1712,7 +1694,7 @@
         <v>148</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C36" s="2">
         <v>47848</v>
@@ -1724,7 +1706,7 @@
         <v>20</v>
       </c>
       <c r="F36" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G36">
         <v>6.988365172589436</v>
@@ -1741,7 +1723,7 @@
         <v>202</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C37" s="2">
         <v>46387</v>
@@ -1754,7 +1736,7 @@
         <v>12</v>
       </c>
       <c r="F37" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G37">
         <v>82.343356496442809</v>
@@ -1771,7 +1753,7 @@
         <v>202</v>
       </c>
       <c r="B38" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C38" s="2">
         <v>46752</v>
@@ -1784,7 +1766,7 @@
         <v>14</v>
       </c>
       <c r="F38" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G38">
         <v>83.708992087657649</v>
@@ -1801,7 +1783,7 @@
         <v>202</v>
       </c>
       <c r="B39" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C39" s="2">
         <v>47118</v>
@@ -1814,7 +1796,7 @@
         <v>16</v>
       </c>
       <c r="F39" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G39">
         <v>85.097276264591429</v>
@@ -1831,7 +1813,7 @@
         <v>202</v>
       </c>
       <c r="B40" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C40" s="2">
         <v>47483</v>
@@ -1844,7 +1826,7 @@
         <v>18</v>
       </c>
       <c r="F40" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G40">
         <v>86.5085846460683</v>
@@ -1861,7 +1843,7 @@
         <v>202</v>
       </c>
       <c r="B41" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C41" s="2">
         <v>47848</v>
@@ -1874,7 +1856,7 @@
         <v>20</v>
       </c>
       <c r="F41" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G41">
         <v>87.943299080418527</v>
@@ -1891,7 +1873,7 @@
         <v>193</v>
       </c>
       <c r="B42" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C42" s="2">
         <v>46203</v>
@@ -1903,7 +1885,7 @@
         <v>10</v>
       </c>
       <c r="F42" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G42">
         <v>94.862857142857138</v>
@@ -1920,7 +1902,7 @@
         <v>193</v>
       </c>
       <c r="B43" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C43" s="2">
         <v>46387</v>
@@ -1932,7 +1914,7 @@
         <v>12</v>
       </c>
       <c r="F43" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G43">
         <v>95.406785714285718</v>
@@ -1949,7 +1931,7 @@
         <v>193</v>
       </c>
       <c r="B44" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C44" s="2">
         <v>46568</v>
@@ -1961,7 +1943,7 @@
         <v>13</v>
       </c>
       <c r="F44" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G44">
         <v>95.950714285714284</v>
@@ -1978,7 +1960,7 @@
         <v>193</v>
       </c>
       <c r="B45" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C45" s="2">
         <v>46752</v>
@@ -1990,7 +1972,7 @@
         <v>14</v>
       </c>
       <c r="F45" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G45">
         <v>96.49464285714285</v>
@@ -2007,7 +1989,7 @@
         <v>193</v>
       </c>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C46" s="2">
         <v>46934</v>
@@ -2019,7 +2001,7 @@
         <v>15</v>
       </c>
       <c r="F46" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G46">
         <v>97.038571428571416</v>
@@ -2036,7 +2018,7 @@
         <v>193</v>
       </c>
       <c r="B47" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C47" s="2">
         <v>47118</v>
@@ -2048,7 +2030,7 @@
         <v>16</v>
       </c>
       <c r="F47" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G47">
         <v>97.582499999999996</v>
@@ -2065,7 +2047,7 @@
         <v>193</v>
       </c>
       <c r="B48" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C48" s="2">
         <v>47299</v>
@@ -2077,7 +2059,7 @@
         <v>17</v>
       </c>
       <c r="F48" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G48">
         <v>98.126428571428562</v>
@@ -2094,7 +2076,7 @@
         <v>193</v>
       </c>
       <c r="B49" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C49" s="2">
         <v>47483</v>
@@ -2106,7 +2088,7 @@
         <v>18</v>
       </c>
       <c r="F49" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G49">
         <v>98.670357142857128</v>
@@ -2123,7 +2105,7 @@
         <v>193</v>
       </c>
       <c r="B50" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C50" s="2">
         <v>47664</v>
@@ -2135,7 +2117,7 @@
         <v>19</v>
       </c>
       <c r="F50" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G50">
         <v>99.214285714285708</v>
@@ -2152,7 +2134,7 @@
         <v>193</v>
       </c>
       <c r="B51" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C51" s="2">
         <v>47848</v>
@@ -2164,7 +2146,7 @@
         <v>20</v>
       </c>
       <c r="F51" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G51">
         <v>99.758214285714274</v>
@@ -2181,7 +2163,7 @@
         <v>200</v>
       </c>
       <c r="B52" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C52" s="2">
         <v>46387</v>
@@ -2193,7 +2175,7 @@
         <v>12</v>
       </c>
       <c r="F52" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G52">
         <v>88.274000000000001</v>
@@ -2210,7 +2192,7 @@
         <v>200</v>
       </c>
       <c r="B53" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C53" s="2">
         <v>46752</v>
@@ -2222,7 +2204,7 @@
         <v>14</v>
       </c>
       <c r="F53" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G53">
         <v>89.156740000000013</v>
@@ -2239,7 +2221,7 @@
         <v>200</v>
       </c>
       <c r="B54" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C54" s="2">
         <v>47118</v>
@@ -2251,7 +2233,7 @@
         <v>16</v>
       </c>
       <c r="F54" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G54">
         <v>90.048307400000013</v>
@@ -2268,7 +2250,7 @@
         <v>200</v>
       </c>
       <c r="B55" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C55" s="2">
         <v>47483</v>
@@ -2280,7 +2262,7 @@
         <v>18</v>
       </c>
       <c r="F55" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G55">
         <v>90.948790474000006</v>
@@ -2297,7 +2279,7 @@
         <v>200</v>
       </c>
       <c r="B56" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C56" s="2">
         <v>47848</v>
@@ -2309,7 +2291,7 @@
         <v>20</v>
       </c>
       <c r="F56" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G56">
         <v>91.858278378740025</v>
@@ -2326,7 +2308,7 @@
         <v>203</v>
       </c>
       <c r="B57" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C57" s="2">
         <v>46387</v>
@@ -2338,7 +2320,7 @@
         <v>12</v>
       </c>
       <c r="F57" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G57">
         <v>337385.42515227583</v>
@@ -2355,7 +2337,7 @@
         <v>203</v>
       </c>
       <c r="B58" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C58" s="2">
         <v>46752</v>
@@ -2367,7 +2349,7 @@
         <v>14</v>
       </c>
       <c r="F58" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G58">
         <v>360065.15581525367</v>
@@ -2384,7 +2366,7 @@
         <v>203</v>
       </c>
       <c r="B59" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C59" s="2">
         <v>47118</v>
@@ -2396,7 +2378,7 @@
         <v>16</v>
       </c>
       <c r="F59" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G59">
         <v>382744.8864782317</v>
@@ -2413,7 +2395,7 @@
         <v>203</v>
       </c>
       <c r="B60" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C60" s="2">
         <v>47483</v>
@@ -2425,7 +2407,7 @@
         <v>18</v>
       </c>
       <c r="F60" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G60">
         <v>405424.61714120972</v>
@@ -2442,7 +2424,7 @@
         <v>203</v>
       </c>
       <c r="B61" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C61" s="2">
         <v>47848</v>
@@ -2454,7 +2436,7 @@
         <v>20</v>
       </c>
       <c r="F61" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G61">
         <v>428104.34780418762</v>
@@ -2471,7 +2453,7 @@
         <v>203</v>
       </c>
       <c r="B62" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C62" s="2">
         <v>46387</v>
@@ -2483,7 +2465,7 @@
         <v>12</v>
       </c>
       <c r="F62" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G62">
         <v>321304.73279046162</v>
@@ -2500,7 +2482,7 @@
         <v>203</v>
       </c>
       <c r="B63" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C63" s="2">
         <v>46752</v>
@@ -2512,7 +2494,7 @@
         <v>14</v>
       </c>
       <c r="F63" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G63">
         <v>339023.55597144237</v>
@@ -2529,7 +2511,7 @@
         <v>203</v>
       </c>
       <c r="B64" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C64" s="2">
         <v>47118</v>
@@ -2541,7 +2523,7 @@
         <v>16</v>
       </c>
       <c r="F64" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G64">
         <v>356742.37915242318</v>
@@ -2558,7 +2540,7 @@
         <v>203</v>
       </c>
       <c r="B65" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C65" s="2">
         <v>47483</v>
@@ -2570,7 +2552,7 @@
         <v>18</v>
       </c>
       <c r="F65" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G65">
         <v>374461.20233340398</v>
@@ -2587,7 +2569,7 @@
         <v>203</v>
       </c>
       <c r="B66" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C66" s="2">
         <v>47848</v>
@@ -2599,7 +2581,7 @@
         <v>20</v>
       </c>
       <c r="F66" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G66">
         <v>392180.02551438479</v>
@@ -2616,7 +2598,7 @@
         <v>204</v>
       </c>
       <c r="B67" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C67" s="2">
         <v>46387</v>
@@ -2628,7 +2610,7 @@
         <v>12</v>
       </c>
       <c r="F67" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G67">
         <v>132301.57511745999</v>
@@ -2645,7 +2627,7 @@
         <v>204</v>
       </c>
       <c r="B68" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C68" s="2">
         <v>46752</v>
@@ -2657,7 +2639,7 @@
         <v>14</v>
       </c>
       <c r="F68" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G68">
         <v>136270.62237098379</v>
@@ -2674,7 +2656,7 @@
         <v>204</v>
       </c>
       <c r="B69" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C69" s="2">
         <v>47118</v>
@@ -2686,7 +2668,7 @@
         <v>16</v>
       </c>
       <c r="F69" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G69">
         <v>140358.74104211331</v>
@@ -2703,7 +2685,7 @@
         <v>204</v>
       </c>
       <c r="B70" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C70" s="2">
         <v>47483</v>
@@ -2715,7 +2697,7 @@
         <v>18</v>
       </c>
       <c r="F70" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G70">
         <v>144569.5032733767</v>
@@ -2732,7 +2714,7 @@
         <v>204</v>
       </c>
       <c r="B71" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C71" s="2">
         <v>47848</v>
@@ -2744,7 +2726,7 @@
         <v>20</v>
       </c>
       <c r="F71" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G71">
         <v>148906.58837157799</v>
@@ -2761,7 +2743,7 @@
         <v>205</v>
       </c>
       <c r="B72" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C72" s="2">
         <v>46387</v>
@@ -2773,7 +2755,7 @@
         <v>12</v>
       </c>
       <c r="F72" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G72">
         <v>5855</v>
@@ -2790,7 +2772,7 @@
         <v>205</v>
       </c>
       <c r="B73" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C73" s="2">
         <v>46752</v>
@@ -2802,7 +2784,7 @@
         <v>14</v>
       </c>
       <c r="F73" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G73">
         <v>6219.0240919999987</v>
@@ -2819,7 +2801,7 @@
         <v>205</v>
       </c>
       <c r="B74" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C74" s="2">
         <v>47118</v>
@@ -2831,7 +2813,7 @@
         <v>16</v>
       </c>
       <c r="F74" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G74">
         <v>6485.9967514999989</v>
@@ -2848,7 +2830,7 @@
         <v>205</v>
       </c>
       <c r="B75" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C75" s="2">
         <v>47483</v>
@@ -2860,7 +2842,7 @@
         <v>18</v>
       </c>
       <c r="F75" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G75">
         <v>6752.9694109999982</v>
@@ -2877,7 +2859,7 @@
         <v>205</v>
       </c>
       <c r="B76" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C76" s="2">
         <v>47848</v>
@@ -2889,7 +2871,7 @@
         <v>20</v>
       </c>
       <c r="F76" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G76">
         <v>7019.9420704999966</v>
@@ -2906,7 +2888,7 @@
         <v>207</v>
       </c>
       <c r="B77" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C77" s="2">
         <v>46387</v>
@@ -2918,7 +2900,7 @@
         <v>12</v>
       </c>
       <c r="F77" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G77">
         <v>293409.4756239889</v>
@@ -2935,7 +2917,7 @@
         <v>207</v>
       </c>
       <c r="B78" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C78" s="2">
         <v>46752</v>
@@ -2947,7 +2929,7 @@
         <v>14</v>
       </c>
       <c r="F78" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G78">
         <v>310591.22318889661</v>
@@ -2964,7 +2946,7 @@
         <v>207</v>
       </c>
       <c r="B79" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C79" s="2">
         <v>47118</v>
@@ -2976,7 +2958,7 @@
         <v>16</v>
       </c>
       <c r="F79" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G79">
         <v>328779.11566018942</v>
@@ -2993,7 +2975,7 @@
         <v>207</v>
       </c>
       <c r="B80" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C80" s="2">
         <v>47483</v>
@@ -3005,7 +2987,7 @@
         <v>18</v>
       </c>
       <c r="F80" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G80">
         <v>348032.07181599637</v>
@@ -3022,7 +3004,7 @@
         <v>207</v>
       </c>
       <c r="B81" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C81" s="2">
         <v>47848</v>
@@ -3034,7 +3016,7 @@
         <v>20</v>
       </c>
       <c r="F81" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G81">
         <v>368412.46065557672</v>
@@ -3051,7 +3033,7 @@
         <v>228</v>
       </c>
       <c r="B82" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C82" s="2">
         <v>46387</v>
@@ -3063,7 +3045,7 @@
         <v>12</v>
       </c>
       <c r="F82" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G82">
         <v>743.69125717621739</v>
@@ -3080,7 +3062,7 @@
         <v>228</v>
       </c>
       <c r="B83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C83" s="2">
         <v>46752</v>
@@ -3092,7 +3074,7 @@
         <v>14</v>
       </c>
       <c r="F83" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G83">
         <v>845.42962114370084</v>
@@ -3109,7 +3091,7 @@
         <v>228</v>
       </c>
       <c r="B84" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C84" s="2">
         <v>47118</v>
@@ -3121,7 +3103,7 @@
         <v>16</v>
       </c>
       <c r="F84" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G84">
         <v>947.16798511118441</v>
@@ -3138,7 +3120,7 @@
         <v>228</v>
       </c>
       <c r="B85" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C85" s="2">
         <v>47483</v>
@@ -3150,7 +3132,7 @@
         <v>18</v>
       </c>
       <c r="F85" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G85">
         <v>1048.906349078668</v>
@@ -3167,7 +3149,7 @@
         <v>228</v>
       </c>
       <c r="B86" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C86" s="2">
         <v>47848</v>
@@ -3179,7 +3161,7 @@
         <v>20</v>
       </c>
       <c r="F86" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G86">
         <v>1150.644713046152</v>
@@ -3196,7 +3178,7 @@
         <v>228</v>
       </c>
       <c r="B87" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C87" s="2">
         <v>46387</v>
@@ -3208,7 +3190,7 @@
         <v>12</v>
       </c>
       <c r="F87" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G87">
         <v>663.92078647276094</v>
@@ -3225,7 +3207,7 @@
         <v>228</v>
       </c>
       <c r="B88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C88" s="2">
         <v>46752</v>
@@ -3237,7 +3219,7 @@
         <v>14</v>
       </c>
       <c r="F88" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G88">
         <v>760.60175637119119</v>
@@ -3254,7 +3236,7 @@
         <v>228</v>
       </c>
       <c r="B89" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C89" s="2">
         <v>47118</v>
@@ -3266,7 +3248,7 @@
         <v>16</v>
       </c>
       <c r="F89" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G89">
         <v>870.7081039242845</v>
@@ -3283,7 +3265,7 @@
         <v>228</v>
       </c>
       <c r="B90" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C90" s="2">
         <v>47483</v>
@@ -3295,7 +3277,7 @@
         <v>18</v>
       </c>
       <c r="F90" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G90">
         <v>994.23982913204077</v>
@@ -3312,7 +3294,7 @@
         <v>228</v>
       </c>
       <c r="B91" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C91" s="2">
         <v>47848</v>
@@ -3324,7 +3306,7 @@
         <v>20</v>
       </c>
       <c r="F91" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G91">
         <v>1131.1969319944601</v>
@@ -3341,7 +3323,7 @@
         <v>244</v>
       </c>
       <c r="B92" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C92" s="2">
         <v>46387</v>
@@ -3353,7 +3335,7 @@
         <v>12</v>
       </c>
       <c r="F92" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G92">
         <v>24</v>
@@ -3370,7 +3352,7 @@
         <v>244</v>
       </c>
       <c r="B93" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C93" s="2">
         <v>46752</v>
@@ -3382,7 +3364,7 @@
         <v>14</v>
       </c>
       <c r="F93" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G93">
         <v>23.5</v>
@@ -3399,7 +3381,7 @@
         <v>244</v>
       </c>
       <c r="B94" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C94" s="2">
         <v>47118</v>
@@ -3411,7 +3393,7 @@
         <v>16</v>
       </c>
       <c r="F94" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G94">
         <v>23</v>
@@ -3428,7 +3410,7 @@
         <v>244</v>
       </c>
       <c r="B95" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C95" s="2">
         <v>47483</v>
@@ -3440,7 +3422,7 @@
         <v>18</v>
       </c>
       <c r="F95" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G95">
         <v>22.5</v>
@@ -3457,7 +3439,7 @@
         <v>244</v>
       </c>
       <c r="B96" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C96" s="2">
         <v>47848</v>
@@ -3469,7 +3451,7 @@
         <v>20</v>
       </c>
       <c r="F96" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G96">
         <v>22</v>
@@ -3486,7 +3468,7 @@
         <v>245</v>
       </c>
       <c r="B97" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C97" s="2">
         <v>46203</v>
@@ -3498,7 +3480,7 @@
         <v>10</v>
       </c>
       <c r="F97" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G97">
         <v>86.600803392352617</v>
@@ -3515,7 +3497,7 @@
         <v>245</v>
       </c>
       <c r="B98" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C98" s="2">
         <v>46387</v>
@@ -3527,7 +3509,7 @@
         <v>12</v>
       </c>
       <c r="F98" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G98">
         <v>86.701724256657954</v>
@@ -3544,7 +3526,7 @@
         <v>245</v>
       </c>
       <c r="B99" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C99" s="2">
         <v>46568</v>
@@ -3556,7 +3538,7 @@
         <v>13</v>
       </c>
       <c r="F99" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G99">
         <v>86.802762729812784</v>
@@ -3573,7 +3555,7 @@
         <v>245</v>
       </c>
       <c r="B100" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C100" s="2">
         <v>46752</v>
@@ -3585,7 +3567,7 @@
         <v>14</v>
       </c>
       <c r="F100" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G100">
         <v>86.903918948873411</v>
@@ -3602,7 +3584,7 @@
         <v>245</v>
       </c>
       <c r="B101" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C101" s="2">
         <v>46934</v>
@@ -3614,7 +3596,7 @@
         <v>15</v>
       </c>
       <c r="F101" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G101">
         <v>87.005193051055869</v>
@@ -3631,7 +3613,7 @@
         <v>245</v>
       </c>
       <c r="B102" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C102" s="2">
         <v>47118</v>
@@ -3643,7 +3625,7 @@
         <v>16</v>
       </c>
       <c r="F102" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G102">
         <v>87.106585173736121</v>
@@ -3660,7 +3642,7 @@
         <v>245</v>
       </c>
       <c r="B103" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C103" s="2">
         <v>47299</v>
@@ -3672,7 +3654,7 @@
         <v>17</v>
       </c>
       <c r="F103" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G103">
         <v>87.208095454450159</v>
@@ -3689,7 +3671,7 @@
         <v>245</v>
       </c>
       <c r="B104" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C104" s="2">
         <v>47483</v>
@@ -3701,7 +3683,7 @@
         <v>18</v>
       </c>
       <c r="F104" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G104">
         <v>87.309724030894301</v>
@@ -3718,7 +3700,7 @@
         <v>245</v>
       </c>
       <c r="B105" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C105" s="2">
         <v>47664</v>
@@ -3730,7 +3712,7 @@
         <v>19</v>
       </c>
       <c r="F105" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G105">
         <v>87.411471040925349</v>
@@ -3747,7 +3729,7 @@
         <v>245</v>
       </c>
       <c r="B106" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C106" s="2">
         <v>47848</v>
@@ -3759,7 +3741,7 @@
         <v>20</v>
       </c>
       <c r="F106" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G106">
         <v>87.513336622560715</v>
@@ -3776,7 +3758,7 @@
         <v>245</v>
       </c>
       <c r="B107" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C107" s="2">
         <v>46203</v>
@@ -3788,7 +3770,7 @@
         <v>10</v>
       </c>
       <c r="F107" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G107">
         <v>86.53</v>
@@ -3805,7 +3787,7 @@
         <v>245</v>
       </c>
       <c r="B108" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C108" s="2">
         <v>46387</v>
@@ -3817,7 +3799,7 @@
         <v>12</v>
       </c>
       <c r="F108" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G108">
         <v>87.215000000000003</v>
@@ -3834,7 +3816,7 @@
         <v>245</v>
       </c>
       <c r="B109" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C109" s="2">
         <v>46568</v>
@@ -3846,7 +3828,7 @@
         <v>13</v>
       </c>
       <c r="F109" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G109">
         <v>87.9</v>
@@ -3863,7 +3845,7 @@
         <v>245</v>
       </c>
       <c r="B110" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C110" s="2">
         <v>46752</v>
@@ -3875,7 +3857,7 @@
         <v>14</v>
       </c>
       <c r="F110" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G110">
         <v>88.585000000000008</v>
@@ -3892,7 +3874,7 @@
         <v>245</v>
       </c>
       <c r="B111" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C111" s="2">
         <v>46934</v>
@@ -3904,7 +3886,7 @@
         <v>15</v>
       </c>
       <c r="F111" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G111">
         <v>89.27000000000001</v>
@@ -3921,7 +3903,7 @@
         <v>245</v>
       </c>
       <c r="B112" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C112" s="2">
         <v>47118</v>
@@ -3933,7 +3915,7 @@
         <v>16</v>
       </c>
       <c r="F112" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G112">
         <v>89.955000000000013</v>
@@ -3950,7 +3932,7 @@
         <v>245</v>
       </c>
       <c r="B113" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C113" s="2">
         <v>47299</v>
@@ -3962,7 +3944,7 @@
         <v>17</v>
       </c>
       <c r="F113" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G113">
         <v>90.640000000000015</v>
@@ -3979,7 +3961,7 @@
         <v>245</v>
       </c>
       <c r="B114" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C114" s="2">
         <v>47483</v>
@@ -3991,7 +3973,7 @@
         <v>18</v>
       </c>
       <c r="F114" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G114">
         <v>91.325000000000017</v>
@@ -4008,7 +3990,7 @@
         <v>245</v>
       </c>
       <c r="B115" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C115" s="2">
         <v>47664</v>
@@ -4020,7 +4002,7 @@
         <v>19</v>
       </c>
       <c r="F115" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G115">
         <v>92.010000000000019</v>
@@ -4037,7 +4019,7 @@
         <v>245</v>
       </c>
       <c r="B116" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C116" s="2">
         <v>47848</v>
@@ -4049,7 +4031,7 @@
         <v>20</v>
       </c>
       <c r="F116" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G116">
         <v>92.695000000000022</v>
@@ -4066,7 +4048,7 @@
         <v>276</v>
       </c>
       <c r="B117" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C117" s="2">
         <v>46203</v>
@@ -4078,7 +4060,7 @@
         <v>10</v>
       </c>
       <c r="F117" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G117">
         <v>76.651428571428568</v>
@@ -4095,7 +4077,7 @@
         <v>276</v>
       </c>
       <c r="B118" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C118" s="2">
         <v>46387</v>
@@ -4107,7 +4089,7 @@
         <v>12</v>
       </c>
       <c r="F118" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G118">
         <v>73.707142857142856</v>
@@ -4124,7 +4106,7 @@
         <v>276</v>
       </c>
       <c r="B119" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C119" s="2">
         <v>46568</v>
@@ -4136,7 +4118,7 @@
         <v>13</v>
       </c>
       <c r="F119" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G119">
         <v>70.762857142857143</v>
@@ -4153,7 +4135,7 @@
         <v>276</v>
       </c>
       <c r="B120" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C120" s="2">
         <v>46752</v>
@@ -4165,7 +4147,7 @@
         <v>14</v>
       </c>
       <c r="F120" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G120">
         <v>67.818571428571431</v>
@@ -4182,7 +4164,7 @@
         <v>276</v>
       </c>
       <c r="B121" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C121" s="2">
         <v>46934</v>
@@ -4194,7 +4176,7 @@
         <v>15</v>
       </c>
       <c r="F121" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G121">
         <v>64.874285714285719</v>
@@ -4211,7 +4193,7 @@
         <v>276</v>
       </c>
       <c r="B122" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C122" s="2">
         <v>47118</v>
@@ -4223,7 +4205,7 @@
         <v>16</v>
       </c>
       <c r="F122" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G122">
         <v>61.930000000000007</v>
@@ -4240,7 +4222,7 @@
         <v>276</v>
       </c>
       <c r="B123" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C123" s="2">
         <v>47299</v>
@@ -4252,7 +4234,7 @@
         <v>17</v>
       </c>
       <c r="F123" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G123">
         <v>58.985714285714288</v>
@@ -4269,7 +4251,7 @@
         <v>276</v>
       </c>
       <c r="B124" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C124" s="2">
         <v>47483</v>
@@ -4281,7 +4263,7 @@
         <v>18</v>
       </c>
       <c r="F124" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G124">
         <v>56.041428571428582</v>
@@ -4298,7 +4280,7 @@
         <v>276</v>
       </c>
       <c r="B125" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C125" s="2">
         <v>47664</v>
@@ -4310,7 +4292,7 @@
         <v>19</v>
       </c>
       <c r="F125" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G125">
         <v>53.09714285714287</v>
@@ -4327,7 +4309,7 @@
         <v>276</v>
       </c>
       <c r="B126" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C126" s="2">
         <v>47848</v>
@@ -4339,7 +4321,7 @@
         <v>20</v>
       </c>
       <c r="F126" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G126">
         <v>50.152857142857158</v>
@@ -4356,7 +4338,7 @@
         <v>276</v>
       </c>
       <c r="B127" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C127" s="2">
         <v>46203</v>
@@ -4368,7 +4350,7 @@
         <v>10</v>
       </c>
       <c r="F127" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G127">
         <v>82.234038282271925</v>
@@ -4385,7 +4367,7 @@
         <v>276</v>
       </c>
       <c r="B128" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C128" s="2">
         <v>46387</v>
@@ -4397,7 +4379,7 @@
         <v>12</v>
       </c>
       <c r="F128" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G128">
         <v>80.333060729510137</v>
@@ -4414,7 +4396,7 @@
         <v>276</v>
       </c>
       <c r="B129" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C129" s="2">
         <v>46568</v>
@@ -4426,7 +4408,7 @@
         <v>13</v>
       </c>
       <c r="F129" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G129">
         <v>78.476027457384305</v>
@@ -4443,7 +4425,7 @@
         <v>276</v>
       </c>
       <c r="B130" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C130" s="2">
         <v>46752</v>
@@ -4455,7 +4437,7 @@
         <v>14</v>
       </c>
       <c r="F130" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G130">
         <v>76.661922620232403</v>
@@ -4472,7 +4454,7 @@
         <v>276</v>
       </c>
       <c r="B131" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C131" s="2">
         <v>46934</v>
@@ -4484,7 +4466,7 @@
         <v>15</v>
       </c>
       <c r="F131" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G131">
         <v>74.889753855366578</v>
@@ -4501,7 +4483,7 @@
         <v>276</v>
       </c>
       <c r="B132" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C132" s="2">
         <v>47118</v>
@@ -4513,7 +4495,7 @@
         <v>16</v>
       </c>
       <c r="F132" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G132">
         <v>73.158551740224951</v>
@@ -4530,7 +4512,7 @@
         <v>276</v>
       </c>
       <c r="B133" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C133" s="2">
         <v>47299</v>
@@ -4542,7 +4524,7 @@
         <v>17</v>
       </c>
       <c r="F133" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G133">
         <v>71.467369262072097</v>
@@ -4559,7 +4541,7 @@
         <v>276</v>
       </c>
       <c r="B134" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C134" s="2">
         <v>47483</v>
@@ -4571,7 +4553,7 @@
         <v>18</v>
       </c>
       <c r="F134" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G134">
         <v>69.815281299958414</v>
@@ -4588,7 +4570,7 @@
         <v>276</v>
       </c>
       <c r="B135" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C135" s="2">
         <v>47664</v>
@@ -4600,7 +4582,7 @@
         <v>19</v>
       </c>
       <c r="F135" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G135">
         <v>68.201384118654829</v>
@@ -4617,7 +4599,7 @@
         <v>276</v>
       </c>
       <c r="B136" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C136" s="2">
         <v>47848</v>
@@ -4629,7 +4611,7 @@
         <v>20</v>
       </c>
       <c r="F136" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G136">
         <v>66.624794874285968</v>
@@ -4646,7 +4628,7 @@
         <v>277</v>
       </c>
       <c r="B137" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C137" s="2">
         <v>46203</v>
@@ -4658,7 +4640,7 @@
         <v>10</v>
       </c>
       <c r="F137" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G137">
         <v>67.447000000000003</v>
@@ -4675,7 +4657,7 @@
         <v>277</v>
       </c>
       <c r="B138" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C138" s="2">
         <v>46387</v>
@@ -4687,7 +4669,7 @@
         <v>12</v>
       </c>
       <c r="F138" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G138">
         <v>65.823999999999998</v>
@@ -4704,7 +4686,7 @@
         <v>277</v>
       </c>
       <c r="B139" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C139" s="2">
         <v>46568</v>
@@ -4716,7 +4698,7 @@
         <v>13</v>
       </c>
       <c r="F139" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G139">
         <v>64.200999999999993</v>
@@ -4733,7 +4715,7 @@
         <v>277</v>
       </c>
       <c r="B140" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C140" s="2">
         <v>46752</v>
@@ -4745,7 +4727,7 @@
         <v>14</v>
       </c>
       <c r="F140" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G140">
         <v>62.578000000000003</v>
@@ -4762,7 +4744,7 @@
         <v>277</v>
       </c>
       <c r="B141" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C141" s="2">
         <v>46934</v>
@@ -4774,7 +4756,7 @@
         <v>15</v>
       </c>
       <c r="F141" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G141">
         <v>60.954999999999998</v>
@@ -4791,7 +4773,7 @@
         <v>277</v>
       </c>
       <c r="B142" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C142" s="2">
         <v>47118</v>
@@ -4803,7 +4785,7 @@
         <v>16</v>
       </c>
       <c r="F142" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G142">
         <v>59.331999999999987</v>
@@ -4820,7 +4802,7 @@
         <v>277</v>
       </c>
       <c r="B143" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C143" s="2">
         <v>47299</v>
@@ -4832,7 +4814,7 @@
         <v>17</v>
       </c>
       <c r="F143" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G143">
         <v>57.709000000000003</v>
@@ -4849,7 +4831,7 @@
         <v>277</v>
       </c>
       <c r="B144" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C144" s="2">
         <v>47483</v>
@@ -4861,7 +4843,7 @@
         <v>18</v>
       </c>
       <c r="F144" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G144">
         <v>56.085999999999991</v>
@@ -4878,7 +4860,7 @@
         <v>277</v>
       </c>
       <c r="B145" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C145" s="2">
         <v>47664</v>
@@ -4890,7 +4872,7 @@
         <v>19</v>
       </c>
       <c r="F145" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G145">
         <v>54.462999999999987</v>
@@ -4907,7 +4889,7 @@
         <v>277</v>
       </c>
       <c r="B146" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C146" s="2">
         <v>47848</v>
@@ -4919,7 +4901,7 @@
         <v>20</v>
       </c>
       <c r="F146" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G146">
         <v>52.839999999999989</v>
@@ -4936,7 +4918,7 @@
         <v>277</v>
       </c>
       <c r="B147" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C147" s="2">
         <v>46203</v>
@@ -4948,7 +4930,7 @@
         <v>10</v>
       </c>
       <c r="F147" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G147">
         <v>67.888278699901591</v>
@@ -4965,7 +4947,7 @@
         <v>277</v>
       </c>
       <c r="B148" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C148" s="2">
         <v>46387</v>
@@ -4977,7 +4959,7 @@
         <v>12</v>
       </c>
       <c r="F148" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G148">
         <v>66.419057282540876</v>
@@ -4994,7 +4976,7 @@
         <v>277</v>
       </c>
       <c r="B149" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C149" s="2">
         <v>46568</v>
@@ -5006,7 +4988,7 @@
         <v>13</v>
       </c>
       <c r="F149" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G149">
         <v>64.9816323934553</v>
@@ -5023,7 +5005,7 @@
         <v>277</v>
       </c>
       <c r="B150" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C150" s="2">
         <v>46752</v>
@@ -5035,7 +5017,7 @@
         <v>14</v>
       </c>
       <c r="F150" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G150">
         <v>63.57531590000643</v>
@@ -5052,7 +5034,7 @@
         <v>277</v>
       </c>
       <c r="B151" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C151" s="2">
         <v>46934</v>
@@ -5064,7 +5046,7 @@
         <v>15</v>
       </c>
       <c r="F151" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G151">
         <v>62.199434561953034</v>
@@ -5081,7 +5063,7 @@
         <v>277</v>
       </c>
       <c r="B152" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C152" s="2">
         <v>47118</v>
@@ -5093,7 +5075,7 @@
         <v>16</v>
       </c>
       <c r="F152" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G152">
         <v>60.853329709153464</v>
@@ -5110,7 +5092,7 @@
         <v>277</v>
       </c>
       <c r="B153" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C153" s="2">
         <v>47299</v>
@@ -5122,7 +5104,7 @@
         <v>17</v>
       </c>
       <c r="F153" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G153">
         <v>59.536356926243137</v>
@@ -5139,7 +5121,7 @@
         <v>277</v>
       </c>
       <c r="B154" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C154" s="2">
         <v>47483</v>
@@ -5151,7 +5133,7 @@
         <v>18</v>
       </c>
       <c r="F154" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G154">
         <v>58.247885744136177</v>
@@ -5168,7 +5150,7 @@
         <v>277</v>
       </c>
       <c r="B155" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C155" s="2">
         <v>47664</v>
@@ -5180,7 +5162,7 @@
         <v>19</v>
       </c>
       <c r="F155" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G155">
         <v>56.987299338203513</v>
@@ -5197,7 +5179,7 @@
         <v>277</v>
       </c>
       <c r="B156" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C156" s="2">
         <v>47848</v>
@@ -5209,7 +5191,7 @@
         <v>20</v>
       </c>
       <c r="F156" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G156">
         <v>55.753994232982812</v>
@@ -5226,7 +5208,7 @@
         <v>325</v>
       </c>
       <c r="B157" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C157" s="2">
         <v>46387</v>
@@ -5238,7 +5220,7 @@
         <v>12</v>
       </c>
       <c r="F157" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G157">
         <v>6</v>
@@ -5255,7 +5237,7 @@
         <v>325</v>
       </c>
       <c r="B158" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C158" s="2">
         <v>46752</v>
@@ -5267,7 +5249,7 @@
         <v>14</v>
       </c>
       <c r="F158" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G158">
         <v>6</v>
@@ -5284,7 +5266,7 @@
         <v>325</v>
       </c>
       <c r="B159" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C159" s="2">
         <v>47118</v>
@@ -5296,7 +5278,7 @@
         <v>16</v>
       </c>
       <c r="F159" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G159">
         <v>7</v>
@@ -5313,7 +5295,7 @@
         <v>325</v>
       </c>
       <c r="B160" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C160" s="2">
         <v>47483</v>
@@ -5325,7 +5307,7 @@
         <v>18</v>
       </c>
       <c r="F160" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G160">
         <v>7</v>
@@ -5342,7 +5324,7 @@
         <v>325</v>
       </c>
       <c r="B161" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C161" s="2">
         <v>47848</v>
@@ -5354,7 +5336,7 @@
         <v>20</v>
       </c>
       <c r="F161" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G161">
         <v>7</v>
@@ -5371,7 +5353,7 @@
         <v>332</v>
       </c>
       <c r="B162" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C162" s="2">
         <v>46387</v>
@@ -5383,7 +5365,7 @@
         <v>12</v>
       </c>
       <c r="F162" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G162">
         <v>0.71510849492151418</v>
@@ -5400,7 +5382,7 @@
         <v>332</v>
       </c>
       <c r="B163" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C163" s="2">
         <v>46752</v>
@@ -5412,7 +5394,7 @@
         <v>14</v>
       </c>
       <c r="F163" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G163">
         <v>0.57208679593721135</v>
@@ -5429,7 +5411,7 @@
         <v>332</v>
       </c>
       <c r="B164" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C164" s="2">
         <v>47118</v>
@@ -5441,7 +5423,7 @@
         <v>16</v>
       </c>
       <c r="F164" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G164">
         <v>0.45766943674976912</v>
@@ -5458,7 +5440,7 @@
         <v>332</v>
       </c>
       <c r="B165" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C165" s="2">
         <v>47483</v>
@@ -5470,7 +5452,7 @@
         <v>18</v>
       </c>
       <c r="F165" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G165">
         <v>0.3661355493998153</v>
@@ -5487,7 +5469,7 @@
         <v>332</v>
       </c>
       <c r="B166" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C166" s="2">
         <v>47848</v>
@@ -5499,7 +5481,7 @@
         <v>20</v>
       </c>
       <c r="F166" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G166">
         <v>0.29290843951985218</v>
@@ -5516,7 +5498,7 @@
         <v>332</v>
       </c>
       <c r="B167" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C167" s="2">
         <v>46387</v>
@@ -5528,7 +5510,7 @@
         <v>12</v>
       </c>
       <c r="F167" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G167">
         <v>0.72500000000000009</v>
@@ -5545,7 +5527,7 @@
         <v>332</v>
       </c>
       <c r="B168" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C168" s="2">
         <v>46752</v>
@@ -5557,7 +5539,7 @@
         <v>14</v>
       </c>
       <c r="F168" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G168">
         <v>0.58000000000000007</v>
@@ -5574,7 +5556,7 @@
         <v>332</v>
       </c>
       <c r="B169" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C169" s="2">
         <v>47118</v>
@@ -5586,7 +5568,7 @@
         <v>16</v>
       </c>
       <c r="F169" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G169">
         <v>0.46400000000000008</v>
@@ -5603,7 +5585,7 @@
         <v>332</v>
       </c>
       <c r="B170" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C170" s="2">
         <v>47483</v>
@@ -5615,7 +5597,7 @@
         <v>18</v>
       </c>
       <c r="F170" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G170">
         <v>0.37120000000000009</v>
@@ -5632,7 +5614,7 @@
         <v>332</v>
       </c>
       <c r="B171" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C171" s="2">
         <v>47848</v>
@@ -5644,7 +5626,7 @@
         <v>20</v>
       </c>
       <c r="F171" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G171">
         <v>0.29696000000000011</v>
@@ -5661,7 +5643,7 @@
         <v>334</v>
       </c>
       <c r="B172" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C172" s="2">
         <v>46387</v>
@@ -5673,7 +5655,7 @@
         <v>12</v>
       </c>
       <c r="F172" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G172">
         <v>90.42</v>
@@ -5690,7 +5672,7 @@
         <v>334</v>
       </c>
       <c r="B173" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C173" s="2">
         <v>46752</v>
@@ -5702,7 +5684,7 @@
         <v>14</v>
       </c>
       <c r="F173" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G173">
         <v>91.365000000000009</v>
@@ -5719,7 +5701,7 @@
         <v>334</v>
       </c>
       <c r="B174" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C174" s="2">
         <v>47118</v>
@@ -5731,7 +5713,7 @@
         <v>16</v>
       </c>
       <c r="F174" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G174">
         <v>92.31</v>
@@ -5748,7 +5730,7 @@
         <v>334</v>
       </c>
       <c r="B175" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C175" s="2">
         <v>47483</v>
@@ -5760,7 +5742,7 @@
         <v>18</v>
       </c>
       <c r="F175" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G175">
         <v>93.25500000000001</v>
@@ -5777,7 +5759,7 @@
         <v>334</v>
       </c>
       <c r="B176" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C176" s="2">
         <v>47848</v>
@@ -5789,7 +5771,7 @@
         <v>20</v>
       </c>
       <c r="F176" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G176">
         <v>94.2</v>
@@ -5806,7 +5788,7 @@
         <v>334</v>
       </c>
       <c r="B177" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C177" s="2">
         <v>46387</v>
@@ -5818,7 +5800,7 @@
         <v>12</v>
       </c>
       <c r="F177" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G177">
         <v>89.680861034164366</v>
@@ -5835,7 +5817,7 @@
         <v>334</v>
       </c>
       <c r="B178" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C178" s="2">
         <v>46752</v>
@@ -5847,7 +5829,7 @@
         <v>14</v>
       </c>
       <c r="F178" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G178">
         <v>90.58039935364728</v>
@@ -5864,7 +5846,7 @@
         <v>334</v>
       </c>
       <c r="B179" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C179" s="2">
         <v>47118</v>
@@ -5876,7 +5858,7 @@
         <v>16</v>
       </c>
       <c r="F179" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G179">
         <v>91.605034626038787</v>
@@ -5893,7 +5875,7 @@
         <v>334</v>
       </c>
       <c r="B180" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C180" s="2">
         <v>47483</v>
@@ -5905,7 +5887,7 @@
         <v>18</v>
       </c>
       <c r="F180" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G180">
         <v>92.754766851338871</v>
@@ -5922,7 +5904,7 @@
         <v>334</v>
       </c>
       <c r="B181" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C181" s="2">
         <v>47848</v>
@@ -5934,7 +5916,7 @@
         <v>20</v>
       </c>
       <c r="F181" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G181">
         <v>94.029596029547562</v>
@@ -5951,7 +5933,7 @@
         <v>361</v>
       </c>
       <c r="B182" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C182" s="2">
         <v>46387</v>
@@ -5963,7 +5945,7 @@
         <v>12</v>
       </c>
       <c r="F182" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G182">
         <v>4.82</v>
@@ -5980,7 +5962,7 @@
         <v>361</v>
       </c>
       <c r="B183" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C183" s="2">
         <v>46752</v>
@@ -5992,7 +5974,7 @@
         <v>14</v>
       </c>
       <c r="F183" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G183">
         <v>4.8499999999999996</v>
@@ -6009,7 +5991,7 @@
         <v>361</v>
       </c>
       <c r="B184" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C184" s="2">
         <v>47118</v>
@@ -6021,7 +6003,7 @@
         <v>16</v>
       </c>
       <c r="F184" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G184">
         <v>4.87</v>
@@ -6038,7 +6020,7 @@
         <v>361</v>
       </c>
       <c r="B185" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C185" s="2">
         <v>47483</v>
@@ -6050,7 +6032,7 @@
         <v>18</v>
       </c>
       <c r="F185" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G185">
         <v>4.91</v>
@@ -6067,7 +6049,7 @@
         <v>361</v>
       </c>
       <c r="B186" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C186" s="2">
         <v>47848</v>
@@ -6079,7 +6061,7 @@
         <v>20</v>
       </c>
       <c r="F186" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G186">
         <v>4.96</v>
@@ -6096,7 +6078,7 @@
         <v>364</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C187" s="4">
         <v>46387</v>
@@ -6108,7 +6090,7 @@
         <v>12</v>
       </c>
       <c r="F187" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G187" s="3">
         <v>144368.4</v>
@@ -6125,7 +6107,7 @@
         <v>364</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C188" s="4">
         <v>46752</v>
@@ -6133,11 +6115,11 @@
       <c r="D188" s="3">
         <v>2027</v>
       </c>
-      <c r="E188" s="3" t="s">
+      <c r="E188" t="s">
         <v>14</v>
       </c>
       <c r="F188" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G188" s="3">
         <v>158805.24</v>
@@ -6154,7 +6136,7 @@
         <v>364</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C189" s="4">
         <v>47118</v>
@@ -6162,11 +6144,11 @@
       <c r="D189" s="3">
         <v>2028</v>
       </c>
-      <c r="E189" s="3" t="s">
+      <c r="E189" t="s">
         <v>16</v>
       </c>
       <c r="F189" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G189" s="3">
         <v>174685.76400000011</v>
@@ -6183,7 +6165,7 @@
         <v>364</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C190" s="4">
         <v>47483</v>
@@ -6191,11 +6173,11 @@
       <c r="D190" s="3">
         <v>2029</v>
       </c>
-      <c r="E190" s="3" t="s">
+      <c r="E190" t="s">
         <v>18</v>
       </c>
       <c r="F190" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G190" s="3">
         <v>192154.34039999999</v>
@@ -6212,7 +6194,7 @@
         <v>364</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C191" s="4">
         <v>47848</v>
@@ -6220,11 +6202,11 @@
       <c r="D191" s="3">
         <v>2030</v>
       </c>
-      <c r="E191" s="3" t="s">
+      <c r="E191" t="s">
         <v>20</v>
       </c>
       <c r="F191" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G191" s="3">
         <v>211369.7744400001</v>
@@ -6241,7 +6223,7 @@
         <v>367</v>
       </c>
       <c r="B192" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C192" s="4">
         <v>46387</v>
@@ -6253,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="F192" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G192" s="3">
         <v>5.0095999999999998</v>
@@ -6270,7 +6252,7 @@
         <v>367</v>
       </c>
       <c r="B193" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C193" s="4">
         <v>46752</v>
@@ -6278,11 +6260,11 @@
       <c r="D193" s="3">
         <v>2027</v>
       </c>
-      <c r="E193" s="3" t="s">
+      <c r="E193" t="s">
         <v>14</v>
       </c>
       <c r="F193" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G193" s="3">
         <v>5.0596959999999997</v>
@@ -6299,7 +6281,7 @@
         <v>367</v>
       </c>
       <c r="B194" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C194" s="4">
         <v>47118</v>
@@ -6307,11 +6289,11 @@
       <c r="D194" s="3">
         <v>2028</v>
       </c>
-      <c r="E194" s="3" t="s">
+      <c r="E194" t="s">
         <v>16</v>
       </c>
       <c r="F194" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G194" s="3">
         <v>5.1102929600000007</v>
@@ -6328,7 +6310,7 @@
         <v>367</v>
       </c>
       <c r="B195" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C195" s="4">
         <v>47483</v>
@@ -6336,11 +6318,11 @@
       <c r="D195" s="3">
         <v>2029</v>
       </c>
-      <c r="E195" s="3" t="s">
+      <c r="E195" t="s">
         <v>18</v>
       </c>
       <c r="F195" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G195" s="3">
         <v>5.1613958896000014</v>
@@ -6357,7 +6339,7 @@
         <v>367</v>
       </c>
       <c r="B196" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C196" s="4">
         <v>47848</v>
@@ -6365,11 +6347,11 @@
       <c r="D196" s="3">
         <v>2030</v>
       </c>
-      <c r="E196" s="3" t="s">
+      <c r="E196" t="s">
         <v>20</v>
       </c>
       <c r="F196" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G196" s="3">
         <v>5.213009848496001</v>
@@ -6386,7 +6368,7 @@
         <v>369</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C197" s="4">
         <v>46387</v>
@@ -6398,7 +6380,7 @@
         <v>12</v>
       </c>
       <c r="F197" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G197" s="3">
         <v>73.44</v>
@@ -6415,7 +6397,7 @@
         <v>369</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C198" s="4">
         <v>46752</v>
@@ -6423,11 +6405,11 @@
       <c r="D198" s="3">
         <v>2027</v>
       </c>
-      <c r="E198" s="3" t="s">
+      <c r="E198" t="s">
         <v>14</v>
       </c>
       <c r="F198" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G198" s="3">
         <v>74.908799999999999</v>
@@ -6444,7 +6426,7 @@
         <v>369</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C199" s="4">
         <v>47118</v>
@@ -6452,11 +6434,11 @@
       <c r="D199" s="3">
         <v>2028</v>
       </c>
-      <c r="E199" s="3" t="s">
+      <c r="E199" t="s">
         <v>16</v>
       </c>
       <c r="F199" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G199" s="3">
         <v>76.406976000000014</v>
@@ -6473,7 +6455,7 @@
         <v>369</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C200" s="4">
         <v>47483</v>
@@ -6481,11 +6463,11 @@
       <c r="D200" s="3">
         <v>2029</v>
       </c>
-      <c r="E200" s="3" t="s">
+      <c r="E200" t="s">
         <v>18</v>
       </c>
       <c r="F200" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G200" s="3">
         <v>77.935115519999997</v>
@@ -6502,7 +6484,7 @@
         <v>369</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C201" s="4">
         <v>47848</v>
@@ -6510,11 +6492,11 @@
       <c r="D201" s="3">
         <v>2030</v>
       </c>
-      <c r="E201" s="3" t="s">
+      <c r="E201" t="s">
         <v>20</v>
       </c>
       <c r="F201" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G201" s="3">
         <v>79.493817830400005</v>
@@ -6531,7 +6513,7 @@
         <v>377</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C202" s="4">
         <v>46387</v>
@@ -6543,7 +6525,7 @@
         <v>12</v>
       </c>
       <c r="F202" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G202">
         <v>11828.030016950001</v>
@@ -6560,7 +6542,7 @@
         <v>377</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C203" s="4">
         <v>46752</v>
@@ -6568,11 +6550,11 @@
       <c r="D203" s="3">
         <v>2027</v>
       </c>
-      <c r="E203" s="3" t="s">
+      <c r="E203" t="s">
         <v>14</v>
       </c>
       <c r="F203" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G203">
         <v>13602.2345194925</v>
@@ -6589,7 +6571,7 @@
         <v>377</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C204" s="4">
         <v>47118</v>
@@ -6597,11 +6579,11 @@
       <c r="D204" s="3">
         <v>2028</v>
       </c>
-      <c r="E204" s="3" t="s">
+      <c r="E204" t="s">
         <v>16</v>
       </c>
       <c r="F204" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G204">
         <v>15642.569697416369</v>
@@ -6618,7 +6600,7 @@
         <v>377</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C205" s="4">
         <v>47483</v>
@@ -6626,11 +6608,11 @@
       <c r="D205" s="3">
         <v>2029</v>
       </c>
-      <c r="E205" s="3" t="s">
+      <c r="E205" t="s">
         <v>18</v>
       </c>
       <c r="F205" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G205">
         <v>17988.95515202883</v>
@@ -6647,7 +6629,7 @@
         <v>377</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C206" s="4">
         <v>47848</v>
@@ -6655,11 +6637,11 @@
       <c r="D206" s="3">
         <v>2030</v>
       </c>
-      <c r="E206" s="3" t="s">
+      <c r="E206" t="s">
         <v>20</v>
       </c>
       <c r="F206" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G206">
         <v>20687.298424833149</v>
@@ -6676,7 +6658,7 @@
         <v>424</v>
       </c>
       <c r="B207" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C207" s="2">
         <v>46387</v>
@@ -6688,7 +6670,7 @@
         <v>12</v>
       </c>
       <c r="F207" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G207">
         <v>11.6</v>
@@ -6705,7 +6687,7 @@
         <v>424</v>
       </c>
       <c r="B208" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C208" s="2">
         <v>46752</v>
@@ -6717,7 +6699,7 @@
         <v>14</v>
       </c>
       <c r="F208" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G208">
         <v>12.2</v>
@@ -6734,7 +6716,7 @@
         <v>424</v>
       </c>
       <c r="B209" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C209" s="2">
         <v>47118</v>
@@ -6746,7 +6728,7 @@
         <v>16</v>
       </c>
       <c r="F209" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G209">
         <v>12.8</v>
@@ -6763,7 +6745,7 @@
         <v>424</v>
       </c>
       <c r="B210" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C210" s="2">
         <v>47483</v>
@@ -6775,7 +6757,7 @@
         <v>18</v>
       </c>
       <c r="F210" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G210">
         <v>13.4</v>
@@ -6792,7 +6774,7 @@
         <v>424</v>
       </c>
       <c r="B211" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C211" s="2">
         <v>47848</v>
@@ -6804,7 +6786,7 @@
         <v>20</v>
       </c>
       <c r="F211" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G211">
         <v>14</v>
@@ -6821,7 +6803,7 @@
         <v>460</v>
       </c>
       <c r="B212" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C212" s="2">
         <v>46387</v>
@@ -6833,7 +6815,7 @@
         <v>12</v>
       </c>
       <c r="F212" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G212">
         <v>92.354399999999998</v>
@@ -6850,7 +6832,7 @@
         <v>460</v>
       </c>
       <c r="B213" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C213" s="2">
         <v>46752</v>
@@ -6862,7 +6844,7 @@
         <v>14</v>
       </c>
       <c r="F213" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G213">
         <v>93.277944000000005</v>
@@ -6879,7 +6861,7 @@
         <v>460</v>
       </c>
       <c r="B214" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C214" s="2">
         <v>47118</v>
@@ -6891,7 +6873,7 @@
         <v>16</v>
       </c>
       <c r="F214" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G214">
         <v>94.21072344000001</v>
@@ -6908,7 +6890,7 @@
         <v>460</v>
       </c>
       <c r="B215" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C215" s="2">
         <v>47483</v>
@@ -6920,7 +6902,7 @@
         <v>18</v>
       </c>
       <c r="F215" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G215">
         <v>95.152830674399993</v>
@@ -6937,7 +6919,7 @@
         <v>460</v>
       </c>
       <c r="B216" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C216" s="2">
         <v>47848</v>
@@ -6949,7 +6931,7 @@
         <v>20</v>
       </c>
       <c r="F216" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G216">
         <v>96.104358981144017</v>
@@ -6966,7 +6948,7 @@
         <v>77</v>
       </c>
       <c r="B217" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C217" s="2">
         <v>46387</v>
@@ -6978,7 +6960,7 @@
         <v>12</v>
       </c>
       <c r="F217" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G217">
         <v>95.596500000000006</v>
@@ -6995,7 +6977,7 @@
         <v>77</v>
       </c>
       <c r="B218" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C218" s="2">
         <v>46752</v>
@@ -7007,7 +6989,7 @@
         <v>14</v>
       </c>
       <c r="F218" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G218">
         <v>96.552465000000012</v>
@@ -7024,7 +7006,7 @@
         <v>77</v>
       </c>
       <c r="B219" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C219" s="2">
         <v>47118</v>
@@ -7036,7 +7018,7 @@
         <v>16</v>
       </c>
       <c r="F219" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G219">
         <v>97.517989650000018</v>
@@ -7053,7 +7035,7 @@
         <v>77</v>
       </c>
       <c r="B220" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C220" s="2">
         <v>47483</v>
@@ -7065,7 +7047,7 @@
         <v>18</v>
       </c>
       <c r="F220" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G220">
         <v>98.493169546500013</v>
@@ -7082,7 +7064,7 @@
         <v>77</v>
       </c>
       <c r="B221" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C221" s="2">
         <v>47848</v>
@@ -7094,7 +7076,7 @@
         <v>20</v>
       </c>
       <c r="F221" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G221">
         <v>99.478101241965021</v>
@@ -7111,7 +7093,7 @@
         <v>98</v>
       </c>
       <c r="B222" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C222" s="2">
         <v>46387</v>
@@ -7123,7 +7105,7 @@
         <v>12</v>
       </c>
       <c r="F222" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G222">
         <v>8</v>
@@ -7140,7 +7122,7 @@
         <v>98</v>
       </c>
       <c r="B223" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C223" s="2">
         <v>46752</v>
@@ -7152,7 +7134,7 @@
         <v>14</v>
       </c>
       <c r="F223" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G223">
         <v>7</v>
@@ -7169,7 +7151,7 @@
         <v>98</v>
       </c>
       <c r="B224" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C224" s="2">
         <v>47118</v>
@@ -7181,7 +7163,7 @@
         <v>16</v>
       </c>
       <c r="F224" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G224">
         <v>7</v>
@@ -7198,7 +7180,7 @@
         <v>98</v>
       </c>
       <c r="B225" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C225" s="2">
         <v>47483</v>
@@ -7210,7 +7192,7 @@
         <v>18</v>
       </c>
       <c r="F225" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G225">
         <v>9</v>
@@ -7227,7 +7209,7 @@
         <v>98</v>
       </c>
       <c r="B226" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C226" s="2">
         <v>47848</v>
@@ -7239,7 +7221,7 @@
         <v>20</v>
       </c>
       <c r="F226" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G226">
         <v>9</v>
@@ -7256,7 +7238,7 @@
         <v>386.1</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C227" s="4">
         <v>46387</v>
@@ -7268,7 +7250,7 @@
         <v>12</v>
       </c>
       <c r="F227" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G227">
         <v>5021.3256906738234</v>
@@ -7285,7 +7267,7 @@
         <v>386.1</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C228" s="4">
         <v>46752</v>
@@ -7293,11 +7275,11 @@
       <c r="D228" s="3">
         <v>2027</v>
       </c>
-      <c r="E228" s="3" t="s">
+      <c r="E228" t="s">
         <v>14</v>
       </c>
       <c r="F228" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G228">
         <v>5914.5712658767779</v>
@@ -7314,7 +7296,7 @@
         <v>386.1</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C229" s="4">
         <v>47118</v>
@@ -7322,11 +7304,11 @@
       <c r="D229" s="3">
         <v>2028</v>
       </c>
-      <c r="E229" s="3" t="s">
+      <c r="E229" t="s">
         <v>16</v>
       </c>
       <c r="F229" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G229">
         <v>6920.7335283964458</v>
@@ -7343,7 +7325,7 @@
         <v>386.1</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C230" s="4">
         <v>47483</v>
@@ -7351,11 +7333,11 @@
       <c r="D230" s="3">
         <v>2029</v>
       </c>
-      <c r="E230" s="3" t="s">
+      <c r="E230" t="s">
         <v>18</v>
       </c>
       <c r="F230" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G230">
         <v>8039.8124782328259</v>
@@ -7372,7 +7354,7 @@
         <v>386.1</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C231" s="4">
         <v>47848</v>
@@ -7380,11 +7362,11 @@
       <c r="D231" s="3">
         <v>2030</v>
       </c>
-      <c r="E231" s="3" t="s">
+      <c r="E231" t="s">
         <v>20</v>
       </c>
       <c r="F231" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G231">
         <v>9271.8081153859184</v>
@@ -7401,7 +7383,7 @@
         <v>386.2</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C232" s="4">
         <v>46387</v>
@@ -7413,7 +7395,7 @@
         <v>12</v>
       </c>
       <c r="F232" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G232">
         <v>8322.3104068060129</v>
@@ -7430,7 +7412,7 @@
         <v>386.2</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C233" s="4">
         <v>46752</v>
@@ -7438,11 +7420,11 @@
       <c r="D233" s="3">
         <v>2027</v>
       </c>
-      <c r="E233" s="3" t="s">
+      <c r="E233" t="s">
         <v>14</v>
       </c>
       <c r="F233" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G233">
         <v>9300.7150739219178</v>
@@ -7459,7 +7441,7 @@
         <v>386.2</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C234" s="4">
         <v>47118</v>
@@ -7467,11 +7449,11 @@
       <c r="D234" s="3">
         <v>2028</v>
       </c>
-      <c r="E234" s="3" t="s">
+      <c r="E234" t="s">
         <v>16</v>
       </c>
       <c r="F234" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G234">
         <v>10394.14497391682</v>
@@ -7488,7 +7470,7 @@
         <v>386.2</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C235" s="4">
         <v>47483</v>
@@ -7496,11 +7478,11 @@
       <c r="D235" s="3">
         <v>2029</v>
       </c>
-      <c r="E235" s="3" t="s">
+      <c r="E235" t="s">
         <v>18</v>
       </c>
       <c r="F235" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G235">
         <v>11616.122941098</v>
@@ -7517,7 +7499,7 @@
         <v>386.2</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C236" s="4">
         <v>47848</v>
@@ -7525,11 +7507,11 @@
       <c r="D236" s="3">
         <v>2030</v>
       </c>
-      <c r="E236" s="3" t="s">
+      <c r="E236" t="s">
         <v>20</v>
       </c>
       <c r="F236" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G236">
         <v>12981.76160918564</v>
@@ -7546,7 +7528,7 @@
         <v>386.3</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C237" s="4">
         <v>46387</v>
@@ -7558,7 +7540,7 @@
         <v>12</v>
       </c>
       <c r="F237" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G237">
         <v>5646.493414116343</v>
@@ -7575,7 +7557,7 @@
         <v>386.3</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C238" s="4">
         <v>46752</v>
@@ -7583,11 +7565,11 @@
       <c r="D238" s="3">
         <v>2027</v>
       </c>
-      <c r="E238" s="3" t="s">
+      <c r="E238" t="s">
         <v>14</v>
       </c>
       <c r="F238" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G238">
         <v>6374.4716673772846</v>
@@ -7604,7 +7586,7 @@
         <v>386.3</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C239" s="4">
         <v>47118</v>
@@ -7612,11 +7594,11 @@
       <c r="D239" s="3">
         <v>2028</v>
       </c>
-      <c r="E239" s="3" t="s">
+      <c r="E239" t="s">
         <v>16</v>
       </c>
       <c r="F239" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G239">
         <v>7227.2111180454294</v>
@@ -7633,7 +7615,7 @@
         <v>386.3</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C240" s="4">
         <v>47483</v>
@@ -7641,11 +7623,11 @@
       <c r="D240" s="3">
         <v>2029</v>
       </c>
-      <c r="E240" s="3" t="s">
+      <c r="E240" t="s">
         <v>18</v>
       </c>
       <c r="F240" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G240">
         <v>8204.7117661207758</v>
@@ -7662,7 +7644,7 @@
         <v>386.3</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C241" s="4">
         <v>47848</v>
@@ -7670,11 +7652,11 @@
       <c r="D241" s="3">
         <v>2030</v>
       </c>
-      <c r="E241" s="3" t="s">
+      <c r="E241" t="s">
         <v>20</v>
       </c>
       <c r="F241" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G241">
         <v>9306.9736116033237</v>
@@ -7691,7 +7673,7 @@
         <v>379</v>
       </c>
       <c r="B242" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C242" s="2">
         <v>46203</v>
@@ -7720,7 +7702,7 @@
         <v>274</v>
       </c>
       <c r="B243" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C243" s="2">
         <v>46203</v>
@@ -7749,7 +7731,7 @@
         <v>379</v>
       </c>
       <c r="B244" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C244" s="2">
         <v>46387</v>
@@ -7778,7 +7760,7 @@
         <v>274</v>
       </c>
       <c r="B245" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C245" s="2">
         <v>46387</v>
@@ -7807,7 +7789,7 @@
         <v>379</v>
       </c>
       <c r="B246" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C246" s="2">
         <v>46568</v>
@@ -7836,7 +7818,7 @@
         <v>274</v>
       </c>
       <c r="B247" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C247" s="2">
         <v>46568</v>
@@ -7865,7 +7847,7 @@
         <v>379</v>
       </c>
       <c r="B248" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C248" s="2">
         <v>46752</v>
@@ -7894,7 +7876,7 @@
         <v>274</v>
       </c>
       <c r="B249" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C249" s="2">
         <v>46752</v>
@@ -7923,7 +7905,7 @@
         <v>379</v>
       </c>
       <c r="B250" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C250" s="2">
         <v>46934</v>
@@ -7952,7 +7934,7 @@
         <v>274</v>
       </c>
       <c r="B251" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C251" s="2">
         <v>46934</v>
@@ -7981,7 +7963,7 @@
         <v>379</v>
       </c>
       <c r="B252" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C252" s="2">
         <v>47118</v>
@@ -8010,7 +7992,7 @@
         <v>274</v>
       </c>
       <c r="B253" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C253" s="2">
         <v>47118</v>
@@ -8039,7 +8021,7 @@
         <v>379</v>
       </c>
       <c r="B254" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C254" s="2">
         <v>47299</v>
@@ -8068,7 +8050,7 @@
         <v>274</v>
       </c>
       <c r="B255" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C255" s="2">
         <v>47299</v>
@@ -8097,7 +8079,7 @@
         <v>379</v>
       </c>
       <c r="B256" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C256" s="2">
         <v>47483</v>
@@ -8126,7 +8108,7 @@
         <v>274</v>
       </c>
       <c r="B257" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C257" s="2">
         <v>47483</v>
@@ -8155,7 +8137,7 @@
         <v>379</v>
       </c>
       <c r="B258" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C258" s="2">
         <v>47664</v>
@@ -8184,7 +8166,7 @@
         <v>274</v>
       </c>
       <c r="B259" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C259" s="2">
         <v>47664</v>
@@ -8213,7 +8195,7 @@
         <v>379</v>
       </c>
       <c r="B260" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C260" s="2">
         <v>47848</v>
@@ -8242,7 +8224,7 @@
         <v>274</v>
       </c>
       <c r="B261" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C261" s="2">
         <v>47848</v>
@@ -8573,7 +8555,7 @@
         <v>10</v>
       </c>
       <c r="F272" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G272">
         <v>57181.535034514192</v>
@@ -8602,7 +8584,7 @@
         <v>12</v>
       </c>
       <c r="F273" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G273">
         <v>57651.823600328113</v>
@@ -8631,7 +8613,7 @@
         <v>13</v>
       </c>
       <c r="F274" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G274">
         <v>58122.112166142033</v>
@@ -8660,7 +8642,7 @@
         <v>14</v>
       </c>
       <c r="F275" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G275">
         <v>58592.400731955953</v>
@@ -8689,7 +8671,7 @@
         <v>15</v>
       </c>
       <c r="F276" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G276">
         <v>59062.689297769859</v>
@@ -8718,7 +8700,7 @@
         <v>16</v>
       </c>
       <c r="F277" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G277">
         <v>59532.977863583779</v>
@@ -8747,7 +8729,7 @@
         <v>17</v>
       </c>
       <c r="F278" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G278">
         <v>60003.2664293977</v>
@@ -8776,7 +8758,7 @@
         <v>18</v>
       </c>
       <c r="F279" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G279">
         <v>60473.55499521162</v>
@@ -8805,7 +8787,7 @@
         <v>19</v>
       </c>
       <c r="F280" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G280">
         <v>60943.84356102554</v>
@@ -8834,7 +8816,7 @@
         <v>20</v>
       </c>
       <c r="F281" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G281">
         <v>61414.13212683946</v>
@@ -8851,7 +8833,7 @@
         <v>379</v>
       </c>
       <c r="B282" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C282" s="2">
         <v>46203</v>
@@ -8863,7 +8845,7 @@
         <v>10</v>
       </c>
       <c r="F282" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G282">
         <v>12825.87818782696</v>
@@ -8880,7 +8862,7 @@
         <v>274</v>
       </c>
       <c r="B283" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C283" s="2">
         <v>46203</v>
@@ -8892,7 +8874,7 @@
         <v>10</v>
       </c>
       <c r="F283" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G283">
         <v>44355.842350450519</v>
@@ -8909,7 +8891,7 @@
         <v>379</v>
       </c>
       <c r="B284" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C284" s="2">
         <v>46387</v>
@@ -8921,7 +8903,7 @@
         <v>12</v>
       </c>
       <c r="F284" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G284">
         <v>12931.36440561766</v>
@@ -8938,7 +8920,7 @@
         <v>274</v>
       </c>
       <c r="B285" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C285" s="2">
         <v>46387</v>
@@ -8950,7 +8932,7 @@
         <v>12</v>
       </c>
       <c r="F285" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G285">
         <v>44720.646224146301</v>
@@ -8967,7 +8949,7 @@
         <v>379</v>
       </c>
       <c r="B286" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C286" s="2">
         <v>46568</v>
@@ -8979,7 +8961,7 @@
         <v>13</v>
       </c>
       <c r="F286" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G286">
         <v>13036.850623408351</v>
@@ -8996,7 +8978,7 @@
         <v>274</v>
       </c>
       <c r="B287" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C287" s="2">
         <v>46568</v>
@@ -9008,7 +8990,7 @@
         <v>13</v>
       </c>
       <c r="F287" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G287">
         <v>45085.450097842077</v>
@@ -9025,7 +9007,7 @@
         <v>379</v>
       </c>
       <c r="B288" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C288" s="2">
         <v>46752</v>
@@ -9037,7 +9019,7 @@
         <v>14</v>
       </c>
       <c r="F288" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G288">
         <v>13142.33684119905</v>
@@ -9054,7 +9036,7 @@
         <v>274</v>
       </c>
       <c r="B289" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C289" s="2">
         <v>46752</v>
@@ -9066,7 +9048,7 @@
         <v>14</v>
       </c>
       <c r="F289" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G289">
         <v>45450.253971537859</v>
@@ -9083,7 +9065,7 @@
         <v>379</v>
       </c>
       <c r="B290" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C290" s="2">
         <v>46934</v>
@@ -9095,7 +9077,7 @@
         <v>15</v>
       </c>
       <c r="F290" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G290">
         <v>13247.82305898975</v>
@@ -9112,7 +9094,7 @@
         <v>274</v>
       </c>
       <c r="B291" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C291" s="2">
         <v>46934</v>
@@ -9124,7 +9106,7 @@
         <v>15</v>
       </c>
       <c r="F291" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G291">
         <v>45815.057845233627</v>
@@ -9141,7 +9123,7 @@
         <v>379</v>
       </c>
       <c r="B292" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C292" s="2">
         <v>47118</v>
@@ -9153,7 +9135,7 @@
         <v>16</v>
       </c>
       <c r="F292" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G292">
         <v>13353.30927678045</v>
@@ -9170,7 +9152,7 @@
         <v>274</v>
       </c>
       <c r="B293" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C293" s="2">
         <v>47118</v>
@@ -9182,7 +9164,7 @@
         <v>16</v>
       </c>
       <c r="F293" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G293">
         <v>46179.861718929409</v>
@@ -9199,7 +9181,7 @@
         <v>379</v>
       </c>
       <c r="B294" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C294" s="2">
         <v>47299</v>
@@ -9211,7 +9193,7 @@
         <v>17</v>
       </c>
       <c r="F294" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G294">
         <v>13458.795494571141</v>
@@ -9228,7 +9210,7 @@
         <v>274</v>
       </c>
       <c r="B295" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C295" s="2">
         <v>47299</v>
@@ -9240,7 +9222,7 @@
         <v>17</v>
       </c>
       <c r="F295" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G295">
         <v>46544.665592625191</v>
@@ -9257,7 +9239,7 @@
         <v>379</v>
       </c>
       <c r="B296" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C296" s="2">
         <v>47483</v>
@@ -9269,7 +9251,7 @@
         <v>18</v>
       </c>
       <c r="F296" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G296">
         <v>13564.281712361841</v>
@@ -9286,7 +9268,7 @@
         <v>274</v>
       </c>
       <c r="B297" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C297" s="2">
         <v>47483</v>
@@ -9298,7 +9280,7 @@
         <v>18</v>
       </c>
       <c r="F297" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G297">
         <v>46909.469466320967</v>
@@ -9315,7 +9297,7 @@
         <v>379</v>
       </c>
       <c r="B298" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C298" s="2">
         <v>47664</v>
@@ -9327,7 +9309,7 @@
         <v>19</v>
       </c>
       <c r="F298" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G298">
         <v>13669.76793015254</v>
@@ -9344,7 +9326,7 @@
         <v>274</v>
       </c>
       <c r="B299" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C299" s="2">
         <v>47664</v>
@@ -9356,7 +9338,7 @@
         <v>19</v>
       </c>
       <c r="F299" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G299">
         <v>47274.273340016749</v>
@@ -9373,7 +9355,7 @@
         <v>379</v>
       </c>
       <c r="B300" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C300" s="2">
         <v>47848</v>
@@ -9385,7 +9367,7 @@
         <v>20</v>
       </c>
       <c r="F300" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G300">
         <v>13775.25414794324</v>
@@ -9402,7 +9384,7 @@
         <v>274</v>
       </c>
       <c r="B301" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C301" s="2">
         <v>47848</v>
@@ -9414,7 +9396,7 @@
         <v>20</v>
       </c>
       <c r="F301" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G301">
         <v>47639.077213712531</v>
@@ -9431,7 +9413,7 @@
         <v>14.1</v>
       </c>
       <c r="B302" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C302" s="2">
         <v>46203</v>
@@ -9443,7 +9425,7 @@
         <v>10</v>
       </c>
       <c r="F302" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G302">
         <v>8922.1224131696708</v>
@@ -9460,7 +9442,7 @@
         <v>14.2</v>
       </c>
       <c r="B303" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C303" s="2">
         <v>46203</v>
@@ -9472,7 +9454,7 @@
         <v>10</v>
       </c>
       <c r="F303" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G303">
         <v>48259.41262134452</v>
@@ -9489,7 +9471,7 @@
         <v>14.1</v>
       </c>
       <c r="B304" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C304" s="2">
         <v>46387</v>
@@ -9501,7 +9483,7 @@
         <v>12</v>
       </c>
       <c r="F304" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G304">
         <v>8995.5022577501495</v>
@@ -9518,7 +9500,7 @@
         <v>14.2</v>
       </c>
       <c r="B305" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C305" s="2">
         <v>46387</v>
@@ -9530,7 +9512,7 @@
         <v>12</v>
       </c>
       <c r="F305" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G305">
         <v>48656.321342577961</v>
@@ -9547,7 +9529,7 @@
         <v>14.1</v>
       </c>
       <c r="B306" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C306" s="2">
         <v>46568</v>
@@ -9559,7 +9541,7 @@
         <v>13</v>
       </c>
       <c r="F306" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G306">
         <v>9068.8821023306264</v>
@@ -9576,7 +9558,7 @@
         <v>14.2</v>
       </c>
       <c r="B307" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C307" s="2">
         <v>46568</v>
@@ -9588,7 +9570,7 @@
         <v>13</v>
       </c>
       <c r="F307" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G307">
         <v>49053.23006381141</v>
@@ -9605,7 +9587,7 @@
         <v>14.1</v>
       </c>
       <c r="B308" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C308" s="2">
         <v>46752</v>
@@ -9617,7 +9599,7 @@
         <v>14</v>
       </c>
       <c r="F308" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G308">
         <v>9142.261946911105</v>
@@ -9634,7 +9616,7 @@
         <v>14.2</v>
       </c>
       <c r="B309" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C309" s="2">
         <v>46752</v>
@@ -9646,7 +9628,7 @@
         <v>14</v>
       </c>
       <c r="F309" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G309">
         <v>49450.138785044852</v>
@@ -9663,7 +9645,7 @@
         <v>14.1</v>
       </c>
       <c r="B310" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C310" s="2">
         <v>46934</v>
@@ -9675,7 +9657,7 @@
         <v>15</v>
       </c>
       <c r="F310" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G310">
         <v>9215.6417914915819</v>
@@ -9692,7 +9674,7 @@
         <v>14.2</v>
       </c>
       <c r="B311" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C311" s="2">
         <v>46934</v>
@@ -9704,7 +9686,7 @@
         <v>15</v>
       </c>
       <c r="F311" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G311">
         <v>49847.047506278293</v>
@@ -9721,7 +9703,7 @@
         <v>14.1</v>
       </c>
       <c r="B312" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C312" s="2">
         <v>47118</v>
@@ -9733,7 +9715,7 @@
         <v>16</v>
       </c>
       <c r="F312" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G312">
         <v>9289.0216360720588</v>
@@ -9750,7 +9732,7 @@
         <v>14.2</v>
       </c>
       <c r="B313" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C313" s="2">
         <v>47118</v>
@@ -9762,7 +9744,7 @@
         <v>16</v>
       </c>
       <c r="F313" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G313">
         <v>50243.956227511728</v>
@@ -9779,7 +9761,7 @@
         <v>14.1</v>
       </c>
       <c r="B314" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C314" s="2">
         <v>47299</v>
@@ -9791,7 +9773,7 @@
         <v>17</v>
       </c>
       <c r="F314" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G314">
         <v>9362.4014806525374</v>
@@ -9808,7 +9790,7 @@
         <v>14.2</v>
       </c>
       <c r="B315" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C315" s="2">
         <v>47299</v>
@@ -9820,7 +9802,7 @@
         <v>17</v>
       </c>
       <c r="F315" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G315">
         <v>50640.864948745169</v>
@@ -9837,7 +9819,7 @@
         <v>14.1</v>
       </c>
       <c r="B316" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C316" s="2">
         <v>47483</v>
@@ -9849,7 +9831,7 @@
         <v>18</v>
       </c>
       <c r="F316" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G316">
         <v>9435.7813252330143</v>
@@ -9866,7 +9848,7 @@
         <v>14.2</v>
       </c>
       <c r="B317" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C317" s="2">
         <v>47483</v>
@@ -9878,7 +9860,7 @@
         <v>18</v>
       </c>
       <c r="F317" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G317">
         <v>51037.773669978611</v>
@@ -9895,7 +9877,7 @@
         <v>14.1</v>
       </c>
       <c r="B318" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C318" s="2">
         <v>47664</v>
@@ -9907,7 +9889,7 @@
         <v>19</v>
       </c>
       <c r="F318" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G318">
         <v>9509.161169813493</v>
@@ -9924,7 +9906,7 @@
         <v>14.2</v>
       </c>
       <c r="B319" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C319" s="2">
         <v>47664</v>
@@ -9936,7 +9918,7 @@
         <v>19</v>
       </c>
       <c r="F319" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G319">
         <v>51434.682391212053</v>
@@ -9953,7 +9935,7 @@
         <v>14.1</v>
       </c>
       <c r="B320" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C320" s="2">
         <v>47848</v>
@@ -9965,7 +9947,7 @@
         <v>20</v>
       </c>
       <c r="F320" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G320">
         <v>9582.5410143939698</v>
@@ -9982,7 +9964,7 @@
         <v>14.2</v>
       </c>
       <c r="B321" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C321" s="2">
         <v>47848</v>
@@ -9994,7 +9976,7 @@
         <v>20</v>
       </c>
       <c r="F321" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G321">
         <v>51831.591112445501</v>
@@ -10011,7 +9993,7 @@
         <v>14.1</v>
       </c>
       <c r="B322" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C322" s="2">
         <v>46203</v>
@@ -10040,7 +10022,7 @@
         <v>14.2</v>
       </c>
       <c r="B323" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C323" s="2">
         <v>46203</v>
@@ -10069,7 +10051,7 @@
         <v>14.1</v>
       </c>
       <c r="B324" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C324" s="2">
         <v>46387</v>
@@ -10098,7 +10080,7 @@
         <v>14.2</v>
       </c>
       <c r="B325" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C325" s="2">
         <v>46387</v>
@@ -10127,7 +10109,7 @@
         <v>14.1</v>
       </c>
       <c r="B326" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C326" s="2">
         <v>46568</v>
@@ -10156,7 +10138,7 @@
         <v>14.2</v>
       </c>
       <c r="B327" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C327" s="2">
         <v>46568</v>
@@ -10185,7 +10167,7 @@
         <v>14.1</v>
       </c>
       <c r="B328" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C328" s="2">
         <v>46752</v>
@@ -10214,7 +10196,7 @@
         <v>14.2</v>
       </c>
       <c r="B329" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C329" s="2">
         <v>46752</v>
@@ -10243,7 +10225,7 @@
         <v>14.1</v>
       </c>
       <c r="B330" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C330" s="2">
         <v>46934</v>
@@ -10272,7 +10254,7 @@
         <v>14.2</v>
       </c>
       <c r="B331" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C331" s="2">
         <v>46934</v>
@@ -10301,7 +10283,7 @@
         <v>14.1</v>
       </c>
       <c r="B332" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C332" s="2">
         <v>47118</v>
@@ -10330,7 +10312,7 @@
         <v>14.2</v>
       </c>
       <c r="B333" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C333" s="2">
         <v>47118</v>
@@ -10359,7 +10341,7 @@
         <v>14.1</v>
       </c>
       <c r="B334" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C334" s="2">
         <v>47299</v>
@@ -10388,7 +10370,7 @@
         <v>14.2</v>
       </c>
       <c r="B335" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C335" s="2">
         <v>47299</v>
@@ -10417,7 +10399,7 @@
         <v>14.1</v>
       </c>
       <c r="B336" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C336" s="2">
         <v>47483</v>
@@ -10446,7 +10428,7 @@
         <v>14.2</v>
       </c>
       <c r="B337" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C337" s="2">
         <v>47483</v>
@@ -10475,7 +10457,7 @@
         <v>14.1</v>
       </c>
       <c r="B338" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C338" s="2">
         <v>47664</v>
@@ -10504,7 +10486,7 @@
         <v>14.2</v>
       </c>
       <c r="B339" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C339" s="2">
         <v>47664</v>
@@ -10533,7 +10515,7 @@
         <v>14.1</v>
       </c>
       <c r="B340" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C340" s="2">
         <v>47848</v>
@@ -10562,7 +10544,7 @@
         <v>14.2</v>
       </c>
       <c r="B341" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C341" s="2">
         <v>47848</v>
@@ -10591,7 +10573,7 @@
         <v>14.3</v>
       </c>
       <c r="B342" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C342" s="2">
         <v>46203</v>
@@ -10603,7 +10585,7 @@
         <v>10</v>
       </c>
       <c r="F342" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G342">
         <v>53184.163304725829</v>
@@ -10620,7 +10602,7 @@
         <v>14.4</v>
       </c>
       <c r="B343" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C343" s="2">
         <v>46203</v>
@@ -10632,7 +10614,7 @@
         <v>10</v>
       </c>
       <c r="F343" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G343">
         <v>3997.37172978836</v>
@@ -10649,7 +10631,7 @@
         <v>14.3</v>
       </c>
       <c r="B344" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C344" s="2">
         <v>46387</v>
@@ -10661,7 +10643,7 @@
         <v>12</v>
       </c>
       <c r="F344" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G344">
         <v>53621.575554493087</v>
@@ -10678,7 +10660,7 @@
         <v>14.4</v>
       </c>
       <c r="B345" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C345" s="2">
         <v>46387</v>
@@ -10690,7 +10672,7 @@
         <v>12</v>
       </c>
       <c r="F345" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G345">
         <v>4030.2480458350101</v>
@@ -10707,7 +10689,7 @@
         <v>14.3</v>
       </c>
       <c r="B346" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C346" s="2">
         <v>46568</v>
@@ -10719,7 +10701,7 @@
         <v>13</v>
       </c>
       <c r="F346" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G346">
         <v>54058.987804260367</v>
@@ -10736,7 +10718,7 @@
         <v>14.4</v>
       </c>
       <c r="B347" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C347" s="2">
         <v>46568</v>
@@ -10748,7 +10730,7 @@
         <v>13</v>
       </c>
       <c r="F347" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G347">
         <v>4063.1243618816602</v>
@@ -10765,7 +10747,7 @@
         <v>14.3</v>
       </c>
       <c r="B348" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C348" s="2">
         <v>46752</v>
@@ -10777,7 +10759,7 @@
         <v>14</v>
       </c>
       <c r="F348" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G348">
         <v>54496.400054027639</v>
@@ -10794,7 +10776,7 @@
         <v>14.4</v>
       </c>
       <c r="B349" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C349" s="2">
         <v>46752</v>
@@ -10806,7 +10788,7 @@
         <v>14</v>
       </c>
       <c r="F349" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G349">
         <v>4096.0006779283094</v>
@@ -10823,7 +10805,7 @@
         <v>14.3</v>
       </c>
       <c r="B350" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C350" s="2">
         <v>46934</v>
@@ -10835,7 +10817,7 @@
         <v>15</v>
       </c>
       <c r="F350" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G350">
         <v>54933.812303794897</v>
@@ -10852,7 +10834,7 @@
         <v>14.4</v>
       </c>
       <c r="B351" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C351" s="2">
         <v>46934</v>
@@ -10864,7 +10846,7 @@
         <v>15</v>
       </c>
       <c r="F351" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G351">
         <v>4128.8769939749591</v>
@@ -10881,7 +10863,7 @@
         <v>14.3</v>
       </c>
       <c r="B352" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C352" s="2">
         <v>47118</v>
@@ -10893,7 +10875,7 @@
         <v>16</v>
       </c>
       <c r="F352" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G352">
         <v>55371.22455356217</v>
@@ -10910,7 +10892,7 @@
         <v>14.4</v>
       </c>
       <c r="B353" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C353" s="2">
         <v>47118</v>
@@ -10922,7 +10904,7 @@
         <v>16</v>
       </c>
       <c r="F353" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G353">
         <v>4161.7533100216096</v>
@@ -10939,7 +10921,7 @@
         <v>14.3</v>
       </c>
       <c r="B354" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C354" s="2">
         <v>47299</v>
@@ -10951,7 +10933,7 @@
         <v>17</v>
       </c>
       <c r="F354" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G354">
         <v>55808.636803329442</v>
@@ -10968,7 +10950,7 @@
         <v>14.4</v>
       </c>
       <c r="B355" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C355" s="2">
         <v>47299</v>
@@ -10980,7 +10962,7 @@
         <v>17</v>
       </c>
       <c r="F355" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G355">
         <v>4194.6296260682593</v>
@@ -10997,7 +10979,7 @@
         <v>14.3</v>
       </c>
       <c r="B356" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C356" s="2">
         <v>47483</v>
@@ -11009,7 +10991,7 @@
         <v>18</v>
       </c>
       <c r="F356" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G356">
         <v>56246.049053096707</v>
@@ -11026,7 +11008,7 @@
         <v>14.4</v>
       </c>
       <c r="B357" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C357" s="2">
         <v>47483</v>
@@ -11038,7 +11020,7 @@
         <v>18</v>
       </c>
       <c r="F357" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G357">
         <v>4227.505942114909</v>
@@ -11055,7 +11037,7 @@
         <v>14.3</v>
       </c>
       <c r="B358" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C358" s="2">
         <v>47664</v>
@@ -11067,7 +11049,7 @@
         <v>19</v>
       </c>
       <c r="F358" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G358">
         <v>56683.461302863987</v>
@@ -11084,7 +11066,7 @@
         <v>14.4</v>
       </c>
       <c r="B359" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C359" s="2">
         <v>47664</v>
@@ -11096,7 +11078,7 @@
         <v>19</v>
       </c>
       <c r="F359" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G359">
         <v>4260.3822581615595</v>
@@ -11113,7 +11095,7 @@
         <v>14.3</v>
       </c>
       <c r="B360" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C360" s="2">
         <v>47848</v>
@@ -11125,7 +11107,7 @@
         <v>20</v>
       </c>
       <c r="F360" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G360">
         <v>57120.873552631252</v>
@@ -11142,7 +11124,7 @@
         <v>14.4</v>
       </c>
       <c r="B361" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C361" s="2">
         <v>47848</v>
@@ -11154,7 +11136,7 @@
         <v>20</v>
       </c>
       <c r="F361" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G361">
         <v>4293.2585742082092</v>
@@ -11171,7 +11153,7 @@
         <v>14.3</v>
       </c>
       <c r="B362" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C362" s="2">
         <v>46203</v>
@@ -11200,7 +11182,7 @@
         <v>14.4</v>
       </c>
       <c r="B363" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C363" s="2">
         <v>46203</v>
@@ -11229,7 +11211,7 @@
         <v>14.3</v>
       </c>
       <c r="B364" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C364" s="2">
         <v>46387</v>
@@ -11258,7 +11240,7 @@
         <v>14.4</v>
       </c>
       <c r="B365" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C365" s="2">
         <v>46387</v>
@@ -11287,7 +11269,7 @@
         <v>14.3</v>
       </c>
       <c r="B366" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C366" s="2">
         <v>46568</v>
@@ -11316,7 +11298,7 @@
         <v>14.4</v>
       </c>
       <c r="B367" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C367" s="2">
         <v>46568</v>
@@ -11345,7 +11327,7 @@
         <v>14.3</v>
       </c>
       <c r="B368" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C368" s="2">
         <v>46752</v>
@@ -11374,7 +11356,7 @@
         <v>14.4</v>
       </c>
       <c r="B369" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C369" s="2">
         <v>46752</v>
@@ -11403,7 +11385,7 @@
         <v>14.3</v>
       </c>
       <c r="B370" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C370" s="2">
         <v>46934</v>
@@ -11432,7 +11414,7 @@
         <v>14.4</v>
       </c>
       <c r="B371" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C371" s="2">
         <v>46934</v>
@@ -11461,7 +11443,7 @@
         <v>14.3</v>
       </c>
       <c r="B372" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C372" s="2">
         <v>47118</v>
@@ -11490,7 +11472,7 @@
         <v>14.4</v>
       </c>
       <c r="B373" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C373" s="2">
         <v>47118</v>
@@ -11519,7 +11501,7 @@
         <v>14.3</v>
       </c>
       <c r="B374" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C374" s="2">
         <v>47299</v>
@@ -11548,7 +11530,7 @@
         <v>14.4</v>
       </c>
       <c r="B375" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C375" s="2">
         <v>47299</v>
@@ -11577,7 +11559,7 @@
         <v>14.3</v>
       </c>
       <c r="B376" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C376" s="2">
         <v>47483</v>
@@ -11606,7 +11588,7 @@
         <v>14.4</v>
       </c>
       <c r="B377" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C377" s="2">
         <v>47483</v>
@@ -11635,7 +11617,7 @@
         <v>14.3</v>
       </c>
       <c r="B378" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C378" s="2">
         <v>47664</v>
@@ -11664,7 +11646,7 @@
         <v>14.4</v>
       </c>
       <c r="B379" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C379" s="2">
         <v>47664</v>
@@ -11693,7 +11675,7 @@
         <v>14.3</v>
       </c>
       <c r="B380" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C380" s="2">
         <v>47848</v>
@@ -11722,7 +11704,7 @@
         <v>14.4</v>
       </c>
       <c r="B381" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C381" s="2">
         <v>47848</v>
@@ -11751,7 +11733,7 @@
         <v>194</v>
       </c>
       <c r="B382" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C382" s="2">
         <v>46387</v>
@@ -11763,7 +11745,7 @@
         <v>12</v>
       </c>
       <c r="F382" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G382">
         <v>90.299279905306122</v>
@@ -11780,7 +11762,7 @@
         <v>194</v>
       </c>
       <c r="B383" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C383" s="2">
         <v>46752</v>
@@ -11792,7 +11774,7 @@
         <v>14</v>
       </c>
       <c r="F383" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G383">
         <v>91.205371802411875</v>
@@ -11809,7 +11791,7 @@
         <v>194</v>
       </c>
       <c r="B384" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C384" s="2">
         <v>47118</v>
@@ -11821,7 +11803,7 @@
         <v>16</v>
       </c>
       <c r="F384" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G384">
         <v>92.111463699517614</v>
@@ -11838,7 +11820,7 @@
         <v>194</v>
       </c>
       <c r="B385" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C385" s="2">
         <v>47483</v>
@@ -11850,7 +11832,7 @@
         <v>18</v>
       </c>
       <c r="F385" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G385">
         <v>93.017555596623353</v>
@@ -11867,7 +11849,7 @@
         <v>194</v>
       </c>
       <c r="B386" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C386" s="2">
         <v>47848</v>
@@ -11879,7 +11861,7 @@
         <v>20</v>
       </c>
       <c r="F386" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G386">
         <v>93.923647493729106</v>
@@ -11896,7 +11878,7 @@
         <v>194</v>
       </c>
       <c r="B387" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C387" s="2">
         <v>46387</v>
@@ -11908,7 +11890,7 @@
         <v>12</v>
       </c>
       <c r="F387" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G387">
         <v>90.703306625415365</v>
@@ -11925,7 +11907,7 @@
         <v>194</v>
       </c>
       <c r="B388" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C388" s="2">
         <v>46752</v>
@@ -11937,7 +11919,7 @@
         <v>14</v>
       </c>
       <c r="F388" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G388">
         <v>91.412109253156885</v>
@@ -11954,7 +11936,7 @@
         <v>194</v>
       </c>
       <c r="B389" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C389" s="2">
         <v>47118</v>
@@ -11966,7 +11948,7 @@
         <v>16</v>
       </c>
       <c r="F389" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G389">
         <v>92.126450831833978</v>
@@ -11983,7 +11965,7 @@
         <v>194</v>
       </c>
       <c r="B390" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C390" s="2">
         <v>47483</v>
@@ -11995,7 +11977,7 @@
         <v>18</v>
       </c>
       <c r="F390" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G390">
         <v>92.846374645678779</v>
@@ -12012,7 +11994,7 @@
         <v>194</v>
       </c>
       <c r="B391" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C391" s="2">
         <v>47848</v>
@@ -12024,7 +12006,7 @@
         <v>20</v>
       </c>
       <c r="F391" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G391">
         <v>93.571924317168822</v>
@@ -12041,7 +12023,7 @@
         <v>323</v>
       </c>
       <c r="B392" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C392" s="2">
         <v>46387</v>
@@ -12053,7 +12035,7 @@
         <v>12</v>
       </c>
       <c r="F392" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G392">
         <v>1</v>
@@ -12070,7 +12052,7 @@
         <v>323</v>
       </c>
       <c r="B393" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C393" s="2">
         <v>46752</v>
@@ -12082,7 +12064,7 @@
         <v>14</v>
       </c>
       <c r="F393" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G393">
         <v>1</v>
@@ -12099,7 +12081,7 @@
         <v>323</v>
       </c>
       <c r="B394" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C394" s="2">
         <v>47118</v>
@@ -12111,7 +12093,7 @@
         <v>16</v>
       </c>
       <c r="F394" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G394">
         <v>2</v>
@@ -12128,7 +12110,7 @@
         <v>323</v>
       </c>
       <c r="B395" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C395" s="2">
         <v>47483</v>
@@ -12140,7 +12122,7 @@
         <v>18</v>
       </c>
       <c r="F395" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G395">
         <v>2</v>
@@ -12157,7 +12139,7 @@
         <v>323</v>
       </c>
       <c r="B396" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C396" s="2">
         <v>47848</v>
@@ -12169,7 +12151,7 @@
         <v>20</v>
       </c>
       <c r="F396" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G396">
         <v>2</v>
@@ -12186,7 +12168,7 @@
         <v>376</v>
       </c>
       <c r="B397" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C397" s="2">
         <v>46387</v>
@@ -12198,7 +12180,7 @@
         <v>12</v>
       </c>
       <c r="F397" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G397">
         <v>34790.444801582693</v>
@@ -12215,7 +12197,7 @@
         <v>376</v>
       </c>
       <c r="B398" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C398" s="2">
         <v>46752</v>
@@ -12227,7 +12209,7 @@
         <v>14</v>
       </c>
       <c r="F398" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G398">
         <v>37492.873343857507</v>
@@ -12244,7 +12226,7 @@
         <v>376</v>
       </c>
       <c r="B399" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C399" s="2">
         <v>47118</v>
@@ -12256,7 +12238,7 @@
         <v>16</v>
       </c>
       <c r="F399" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G399">
         <v>40195.301886132322</v>
@@ -12273,7 +12255,7 @@
         <v>376</v>
       </c>
       <c r="B400" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C400" s="2">
         <v>47483</v>
@@ -12285,7 +12267,7 @@
         <v>18</v>
       </c>
       <c r="F400" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G400">
         <v>42897.730428407129</v>
@@ -12302,7 +12284,7 @@
         <v>376</v>
       </c>
       <c r="B401" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C401" s="2">
         <v>47848</v>
@@ -12314,7 +12296,7 @@
         <v>20</v>
       </c>
       <c r="F401" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G401">
         <v>45600.15897068195</v>
@@ -12331,7 +12313,7 @@
         <v>376</v>
       </c>
       <c r="B402" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C402" s="2">
         <v>46387</v>
@@ -12343,7 +12325,7 @@
         <v>12</v>
       </c>
       <c r="F402" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G402">
         <v>33364.614089900009</v>
@@ -12360,7 +12342,7 @@
         <v>376</v>
       </c>
       <c r="B403" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C403" s="2">
         <v>46752</v>
@@ -12372,7 +12354,7 @@
         <v>14</v>
       </c>
       <c r="F403" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G403">
         <v>36512.365153479492</v>
@@ -12389,7 +12371,7 @@
         <v>376</v>
       </c>
       <c r="B404" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C404" s="2">
         <v>47118</v>
@@ -12401,7 +12383,7 @@
         <v>16</v>
       </c>
       <c r="F404" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G404">
         <v>40167.943620047838</v>
@@ -12418,7 +12400,7 @@
         <v>376</v>
       </c>
       <c r="B405" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C405" s="2">
         <v>47483</v>
@@ -12430,7 +12412,7 @@
         <v>18</v>
       </c>
       <c r="F405" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G405">
         <v>44331.349489605069</v>
@@ -12447,7 +12429,7 @@
         <v>376</v>
       </c>
       <c r="B406" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C406" s="2">
         <v>47848</v>
@@ -12459,7 +12441,7 @@
         <v>20</v>
       </c>
       <c r="F406" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G406">
         <v>49002.582762151171</v>
@@ -12476,7 +12458,7 @@
         <v>466</v>
       </c>
       <c r="B407" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C407" s="2">
         <v>46387</v>
@@ -12485,10 +12467,10 @@
         <v>2026</v>
       </c>
       <c r="E407" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F407" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G407">
         <v>58.919999999999987</v>
@@ -12505,7 +12487,7 @@
         <v>466</v>
       </c>
       <c r="B408" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C408" s="2">
         <v>46752</v>
@@ -12514,10 +12496,10 @@
         <v>2027</v>
       </c>
       <c r="E408" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F408" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G408">
         <v>60.687600000000003</v>
@@ -12534,7 +12516,7 @@
         <v>466</v>
       </c>
       <c r="B409" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C409" s="2">
         <v>47118</v>
@@ -12543,10 +12525,10 @@
         <v>2028</v>
       </c>
       <c r="E409" t="s">
+        <v>16</v>
+      </c>
+      <c r="F409" t="s">
         <v>25</v>
-      </c>
-      <c r="F409" t="s">
-        <v>30</v>
       </c>
       <c r="G409">
         <v>62.508228000000003</v>
@@ -12563,7 +12545,7 @@
         <v>466</v>
       </c>
       <c r="B410" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C410" s="2">
         <v>47483</v>
@@ -12572,10 +12554,10 @@
         <v>2029</v>
       </c>
       <c r="E410" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F410" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G410">
         <v>64.383474839999991</v>
@@ -12592,7 +12574,7 @@
         <v>466</v>
       </c>
       <c r="B411" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C411" s="2">
         <v>47848</v>
@@ -12601,10 +12583,10 @@
         <v>2030</v>
       </c>
       <c r="E411" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F411" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G411">
         <v>66.314979085199994</v>
@@ -12621,7 +12603,7 @@
         <v>466</v>
       </c>
       <c r="B412" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C412" s="2">
         <v>46387</v>
@@ -12630,10 +12612,10 @@
         <v>2026</v>
       </c>
       <c r="E412" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F412" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G412">
         <v>56.235212373037847</v>
@@ -12650,7 +12632,7 @@
         <v>466</v>
       </c>
       <c r="B413" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C413" s="2">
         <v>46752</v>
@@ -12659,10 +12641,10 @@
         <v>2027</v>
       </c>
       <c r="E413" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F413" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G413">
         <v>57.922268744228987</v>
@@ -12679,7 +12661,7 @@
         <v>466</v>
       </c>
       <c r="B414" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C414" s="2">
         <v>47118</v>
@@ -12688,10 +12670,10 @@
         <v>2028</v>
       </c>
       <c r="E414" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F414" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G414">
         <v>59.659936806555862</v>
@@ -12708,7 +12690,7 @@
         <v>466</v>
       </c>
       <c r="B415" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C415" s="2">
         <v>47483</v>
@@ -12717,10 +12699,10 @@
         <v>2029</v>
       </c>
       <c r="E415" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F415" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G415">
         <v>61.449734910752539</v>
@@ -12737,7 +12719,7 @@
         <v>466</v>
       </c>
       <c r="B416" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C416" s="2">
         <v>47848</v>
@@ -12746,10 +12728,10 @@
         <v>2030</v>
       </c>
       <c r="E416" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F416" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G416">
         <v>63.293226958075117</v>
@@ -12766,19 +12748,19 @@
         <v>96</v>
       </c>
       <c r="B417" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C417" s="2">
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="D417">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E417" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="F417" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G417">
         <v>846.88288415165562</v>
@@ -12795,19 +12777,19 @@
         <v>96</v>
       </c>
       <c r="B418" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C418" s="2">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="D418">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E418" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F418" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G418">
         <v>914.63351488378817</v>
@@ -12824,19 +12806,19 @@
         <v>96</v>
       </c>
       <c r="B419" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C419" s="2">
-        <v>46752</v>
+        <v>47118</v>
       </c>
       <c r="D419">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E419" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F419" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G419">
         <v>987.8041960744913</v>
@@ -12853,19 +12835,19 @@
         <v>96</v>
       </c>
       <c r="B420" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C420" s="2">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="D420">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E420" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F420" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G420">
         <v>1066.8285317604509</v>
@@ -12882,19 +12864,19 @@
         <v>96</v>
       </c>
       <c r="B421" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C421" s="2">
-        <v>47483</v>
+        <v>47848</v>
       </c>
       <c r="D421">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E421" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F421" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G421">
         <v>1152.1748143012869</v>
@@ -12911,7 +12893,7 @@
         <v>385</v>
       </c>
       <c r="B422" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C422" s="2">
         <v>46387</v>
@@ -12920,10 +12902,10 @@
         <v>2026</v>
       </c>
       <c r="E422" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F422" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G422">
         <v>18662.155890318401</v>
@@ -12940,7 +12922,7 @@
         <v>385</v>
       </c>
       <c r="B423" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C423" s="2">
         <v>46752</v>
@@ -12949,10 +12931,10 @@
         <v>2027</v>
       </c>
       <c r="E423" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F423" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G423">
         <v>20323.640878613929</v>
@@ -12969,7 +12951,7 @@
         <v>385</v>
       </c>
       <c r="B424" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C424" s="2">
         <v>47118</v>
@@ -12978,10 +12960,10 @@
         <v>2028</v>
       </c>
       <c r="E424" t="s">
+        <v>16</v>
+      </c>
+      <c r="F424" t="s">
         <v>25</v>
-      </c>
-      <c r="F424" t="s">
-        <v>30</v>
       </c>
       <c r="G424">
         <v>21985.12586690945</v>
@@ -12998,7 +12980,7 @@
         <v>385</v>
       </c>
       <c r="B425" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C425" s="2">
         <v>47483</v>
@@ -13007,10 +12989,10 @@
         <v>2029</v>
       </c>
       <c r="E425" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F425" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G425">
         <v>23646.61085520497</v>
@@ -13027,7 +13009,7 @@
         <v>385</v>
       </c>
       <c r="B426" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C426" s="2">
         <v>47848</v>
@@ -13036,10 +13018,10 @@
         <v>2030</v>
       </c>
       <c r="E426" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F426" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G426">
         <v>25308.09584350049</v>
@@ -13056,7 +13038,7 @@
         <v>385</v>
       </c>
       <c r="B427" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C427" s="2">
         <v>46387</v>
@@ -13065,10 +13047,10 @@
         <v>2026</v>
       </c>
       <c r="E427" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F427" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G427">
         <v>17370.137802849709</v>
@@ -13085,7 +13067,7 @@
         <v>385</v>
       </c>
       <c r="B428" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C428" s="2">
         <v>46752</v>
@@ -13094,10 +13076,10 @@
         <v>2027</v>
       </c>
       <c r="E428" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F428" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G428">
         <v>18957.986444229311</v>
@@ -13114,7 +13096,7 @@
         <v>385</v>
       </c>
       <c r="B429" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C429" s="2">
         <v>47118</v>
@@ -13123,10 +13105,10 @@
         <v>2028</v>
       </c>
       <c r="E429" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F429" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G429">
         <v>20767.420529644682</v>
@@ -13143,7 +13125,7 @@
         <v>385</v>
       </c>
       <c r="B430" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C430" s="2">
         <v>47483</v>
@@ -13152,10 +13134,10 @@
         <v>2029</v>
       </c>
       <c r="E430" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F430" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G430">
         <v>22798.440059095828</v>
@@ -13172,7 +13154,7 @@
         <v>385</v>
       </c>
       <c r="B431" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C431" s="2">
         <v>47848</v>
@@ -13181,10 +13163,10 @@
         <v>2030</v>
       </c>
       <c r="E431" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F431" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G431">
         <v>25051.045032582759</v>
@@ -13201,7 +13183,7 @@
         <v>386.1</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C432" s="4">
         <v>46387</v>
@@ -13213,7 +13195,7 @@
         <v>12</v>
       </c>
       <c r="F432" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G432">
         <v>5053.2904950000002</v>
@@ -13230,7 +13212,7 @@
         <v>386.1</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C433" s="4">
         <v>46752</v>
@@ -13238,11 +13220,11 @@
       <c r="D433" s="3">
         <v>2027</v>
       </c>
-      <c r="E433" s="3" t="s">
+      <c r="E433" t="s">
         <v>14</v>
       </c>
       <c r="F433" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G433">
         <v>6316.6131187499996</v>
@@ -13259,7 +13241,7 @@
         <v>386.1</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C434" s="4">
         <v>47118</v>
@@ -13267,11 +13249,11 @@
       <c r="D434" s="3">
         <v>2028</v>
       </c>
-      <c r="E434" s="3" t="s">
+      <c r="E434" t="s">
         <v>16</v>
       </c>
       <c r="F434" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G434">
         <v>7895.7663984375004</v>
@@ -13288,7 +13270,7 @@
         <v>386.1</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C435" s="4">
         <v>47483</v>
@@ -13296,11 +13278,11 @@
       <c r="D435" s="3">
         <v>2029</v>
       </c>
-      <c r="E435" s="3" t="s">
+      <c r="E435" t="s">
         <v>18</v>
       </c>
       <c r="F435" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G435">
         <v>9050.2238278000004</v>
@@ -13317,7 +13299,7 @@
         <v>386.1</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C436" s="4">
         <v>47848</v>
@@ -13325,11 +13307,11 @@
       <c r="D436" s="3">
         <v>2030</v>
       </c>
-      <c r="E436" s="3" t="s">
+      <c r="E436" t="s">
         <v>20</v>
       </c>
       <c r="F436" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G436">
         <v>10086.119943899999</v>
@@ -13346,7 +13328,7 @@
         <v>386.2</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C437" s="4">
         <v>46387</v>
@@ -13358,7 +13340,7 @@
         <v>12</v>
       </c>
       <c r="F437" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G437">
         <v>6864.5522870000004</v>
@@ -13375,7 +13357,7 @@
         <v>386.2</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C438" s="4">
         <v>46752</v>
@@ -13383,11 +13365,11 @@
       <c r="D438" s="3">
         <v>2027</v>
       </c>
-      <c r="E438" s="3" t="s">
+      <c r="E438" t="s">
         <v>14</v>
       </c>
       <c r="F438" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G438">
         <v>6928.2554168999995</v>
@@ -13404,7 +13386,7 @@
         <v>386.2</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C439" s="4">
         <v>47118</v>
@@ -13412,11 +13394,11 @@
       <c r="D439" s="3">
         <v>2028</v>
       </c>
-      <c r="E439" s="3" t="s">
+      <c r="E439" t="s">
         <v>16</v>
       </c>
       <c r="F439" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G439">
         <v>6991.9585467999996</v>
@@ -13433,7 +13415,7 @@
         <v>386.2</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C440" s="4">
         <v>47483</v>
@@ -13441,11 +13423,11 @@
       <c r="D440" s="3">
         <v>2029</v>
       </c>
-      <c r="E440" s="3" t="s">
+      <c r="E440" t="s">
         <v>18</v>
       </c>
       <c r="F440" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G440">
         <v>7055.6616766999996</v>
@@ -13462,7 +13444,7 @@
         <v>386.2</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C441" s="4">
         <v>47848</v>
@@ -13470,11 +13452,11 @@
       <c r="D441" s="3">
         <v>2030</v>
       </c>
-      <c r="E441" s="3" t="s">
+      <c r="E441" t="s">
         <v>20</v>
       </c>
       <c r="F441" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G441">
         <v>7119.3648065999996</v>
@@ -13491,7 +13473,7 @@
         <v>386.3</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C442" s="4">
         <v>46387</v>
@@ -13503,7 +13485,7 @@
         <v>12</v>
       </c>
       <c r="F442" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G442">
         <v>5855.0681234999993</v>
@@ -13520,7 +13502,7 @@
         <v>386.3</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C443" s="4">
         <v>46752</v>
@@ -13528,11 +13510,11 @@
       <c r="D443" s="3">
         <v>2027</v>
       </c>
-      <c r="E443" s="3" t="s">
+      <c r="E443" t="s">
         <v>14</v>
       </c>
       <c r="F443" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G443">
         <v>6416.9538656999994</v>
@@ -13549,7 +13531,7 @@
         <v>386.3</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C444" s="4">
         <v>47118</v>
@@ -13557,11 +13539,11 @@
       <c r="D444" s="3">
         <v>2028</v>
       </c>
-      <c r="E444" s="3" t="s">
+      <c r="E444" t="s">
         <v>16</v>
       </c>
       <c r="F444" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G444">
         <v>6978.8396078999986</v>
@@ -13578,7 +13560,7 @@
         <v>386.3</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C445" s="4">
         <v>47483</v>
@@ -13586,11 +13568,11 @@
       <c r="D445" s="3">
         <v>2029</v>
       </c>
-      <c r="E445" s="3" t="s">
+      <c r="E445" t="s">
         <v>18</v>
       </c>
       <c r="F445" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G445">
         <v>7540.7253500999996</v>
@@ -13607,7 +13589,7 @@
         <v>386.3</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C446" s="4">
         <v>47848</v>
@@ -13615,11 +13597,11 @@
       <c r="D446" s="3">
         <v>2030</v>
       </c>
-      <c r="E446" s="3" t="s">
+      <c r="E446" t="s">
         <v>20</v>
       </c>
       <c r="F446" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G446">
         <v>8102.6110922999997</v>
@@ -13633,10 +13615,10 @@
     </row>
     <row r="447" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B447" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C447" s="2">
         <v>46387</v>
@@ -13648,7 +13630,7 @@
         <v>12</v>
       </c>
       <c r="F447" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G447">
         <v>15.7</v>
@@ -13662,10 +13644,10 @@
     </row>
     <row r="448" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B448" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C448" s="2">
         <v>46752</v>
@@ -13677,7 +13659,7 @@
         <v>14</v>
       </c>
       <c r="F448" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G448">
         <v>16.3</v>
@@ -13691,10 +13673,10 @@
     </row>
     <row r="449" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B449" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C449" s="2">
         <v>47118</v>
@@ -13706,7 +13688,7 @@
         <v>16</v>
       </c>
       <c r="F449" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G449">
         <v>16.8</v>
@@ -13720,10 +13702,10 @@
     </row>
     <row r="450" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B450" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C450" s="2">
         <v>47483</v>
@@ -13735,7 +13717,7 @@
         <v>18</v>
       </c>
       <c r="F450" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G450">
         <v>17.399999999999999</v>
@@ -13749,10 +13731,10 @@
     </row>
     <row r="451" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B451" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C451" s="2">
         <v>47848</v>
@@ -13764,7 +13746,7 @@
         <v>20</v>
       </c>
       <c r="F451" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G451">
         <v>18</v>
@@ -13778,10 +13760,10 @@
     </row>
     <row r="452" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B452" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C452" s="2">
         <v>46387</v>
@@ -13793,7 +13775,7 @@
         <v>12</v>
       </c>
       <c r="F452" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G452">
         <v>15.7</v>
@@ -13807,10 +13789,10 @@
     </row>
     <row r="453" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B453" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C453" s="2">
         <v>46752</v>
@@ -13822,7 +13804,7 @@
         <v>14</v>
       </c>
       <c r="F453" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G453">
         <v>16.3</v>
@@ -13836,10 +13818,10 @@
     </row>
     <row r="454" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B454" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C454" s="2">
         <v>47118</v>
@@ -13851,7 +13833,7 @@
         <v>16</v>
       </c>
       <c r="F454" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G454">
         <v>16.8</v>
@@ -13865,10 +13847,10 @@
     </row>
     <row r="455" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B455" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C455" s="2">
         <v>47483</v>
@@ -13880,7 +13862,7 @@
         <v>18</v>
       </c>
       <c r="F455" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G455">
         <v>17.399999999999999</v>
@@ -13894,10 +13876,10 @@
     </row>
     <row r="456" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B456" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C456" s="2">
         <v>47848</v>
@@ -13909,7 +13891,7 @@
         <v>20</v>
       </c>
       <c r="F456" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G456">
         <v>18</v>
@@ -13923,10 +13905,10 @@
     </row>
     <row r="457" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B457" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C457" s="2">
         <v>46387</v>
@@ -13938,7 +13920,7 @@
         <v>12</v>
       </c>
       <c r="F457" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G457">
         <v>34.965000000000003</v>
@@ -13952,10 +13934,10 @@
     </row>
     <row r="458" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B458" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C458" s="2">
         <v>46752</v>
@@ -13967,7 +13949,7 @@
         <v>14</v>
       </c>
       <c r="F458" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G458">
         <v>36.713250000000002</v>
@@ -13981,10 +13963,10 @@
     </row>
     <row r="459" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B459" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C459" s="2">
         <v>47118</v>
@@ -13996,7 +13978,7 @@
         <v>16</v>
       </c>
       <c r="F459" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G459">
         <v>38.548912499999993</v>
@@ -14010,10 +13992,10 @@
     </row>
     <row r="460" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B460" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C460" s="2">
         <v>47483</v>
@@ -14025,7 +14007,7 @@
         <v>18</v>
       </c>
       <c r="F460" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G460">
         <v>40.476358124999997</v>
@@ -14039,10 +14021,10 @@
     </row>
     <row r="461" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B461" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C461" s="2">
         <v>47848</v>
@@ -14054,7 +14036,7 @@
         <v>20</v>
       </c>
       <c r="F461" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G461">
         <v>42.50017603125</v>
@@ -14071,7 +14053,7 @@
         <v>332</v>
       </c>
       <c r="B462" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C462" s="2">
         <v>46387</v>
@@ -14083,7 +14065,7 @@
         <v>12</v>
       </c>
       <c r="F462" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G462">
         <v>0.76500000000000001</v>
@@ -14100,7 +14082,7 @@
         <v>332</v>
       </c>
       <c r="B463" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C463" s="2">
         <v>46752</v>
@@ -14112,7 +14094,7 @@
         <v>14</v>
       </c>
       <c r="F463" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G463">
         <v>0.6885</v>
@@ -14129,7 +14111,7 @@
         <v>332</v>
       </c>
       <c r="B464" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C464" s="2">
         <v>47118</v>
@@ -14141,7 +14123,7 @@
         <v>16</v>
       </c>
       <c r="F464" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G464">
         <v>0.61965000000000003</v>
@@ -14158,7 +14140,7 @@
         <v>332</v>
       </c>
       <c r="B465" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C465" s="2">
         <v>47483</v>
@@ -14170,7 +14152,7 @@
         <v>18</v>
       </c>
       <c r="F465" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G465">
         <v>0.55768499999999999</v>
@@ -14187,7 +14169,7 @@
         <v>332</v>
       </c>
       <c r="B466" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C466" s="2">
         <v>47848</v>
@@ -14199,7 +14181,7 @@
         <v>20</v>
       </c>
       <c r="F466" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G466">
         <v>0.5019165000000001</v>

--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="769" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{667BC7F2-5C26-4C08-9F6F-6D8E2B237192}"/>
+  <xr:revisionPtr revIDLastSave="779" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90EDE26E-CD4B-4997-9504-0F4F4C9EC229}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Proyecciones" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$I$466</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$K$466</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -668,7 +668,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}">
-  <dimension ref="A1:I466"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:K466"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
@@ -703,7 +704,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>109</v>
       </c>
@@ -732,7 +733,7 @@
         <v>96.466210501716631</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>109</v>
       </c>
@@ -761,7 +762,7 @@
         <v>98.817673270209056</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>109</v>
       </c>
@@ -790,7 +791,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>109</v>
       </c>
@@ -819,7 +820,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>109</v>
       </c>
@@ -848,7 +849,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>148</v>
       </c>
@@ -877,7 +878,7 @@
         <v>6.4632000000000014</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>148</v>
       </c>
@@ -906,7 +907,7 @@
         <v>6.6767605714285727</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>148</v>
       </c>
@@ -935,7 +936,7 @@
         <v>6.8921245714285728</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>148</v>
       </c>
@@ -964,7 +965,7 @@
         <v>7.1092920000000008</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>148</v>
       </c>
@@ -993,7 +994,7 @@
         <v>7.3282628571428594</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>148</v>
       </c>
@@ -1022,7 +1023,7 @@
         <v>7.5490371428571432</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>148</v>
       </c>
@@ -1051,7 +1052,7 @@
         <v>7.7716148571428576</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>148</v>
       </c>
@@ -1080,7 +1081,7 @@
         <v>7.9959960000000017</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>148</v>
       </c>
@@ -1109,7 +1110,7 @@
         <v>8.2221805714285736</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>148</v>
       </c>
@@ -1138,7 +1139,7 @@
         <v>8.4501685714285717</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>148</v>
       </c>
@@ -1167,7 +1168,7 @@
         <v>6.1899902761070864</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>148</v>
       </c>
@@ -1196,7 +1197,7 @@
         <v>6.3279819822962171</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>148</v>
       </c>
@@ -1225,7 +1226,7 @@
         <v>6.4686394813710644</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>148</v>
       </c>
@@ -1254,7 +1255,7 @@
         <v>6.6119865461157588</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>148</v>
       </c>
@@ -1283,7 +1284,7 @@
         <v>6.7580469493144291</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>148</v>
       </c>
@@ -1312,7 +1313,7 @@
         <v>6.906844463751205</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>148</v>
       </c>
@@ -1341,7 +1342,7 @@
         <v>7.0584028622102162</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>148</v>
       </c>
@@ -1370,7 +1371,7 @@
         <v>7.2127459174755941</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>148</v>
       </c>
@@ -1399,7 +1400,7 @@
         <v>7.3698974023314676</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>148</v>
       </c>
@@ -1428,7 +1429,7 @@
         <v>7.5298810895619628</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>148</v>
       </c>
@@ -1457,7 +1458,7 @@
         <v>6.4272000000000009</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>148</v>
       </c>
@@ -1486,7 +1487,7 @@
         <v>6.6531160800000002</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>148</v>
       </c>
@@ -1515,7 +1516,7 @@
         <v>6.8868026448000004</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>148</v>
       </c>
@@ -1544,7 +1545,7 @@
         <v>7.1285225990160006</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>148</v>
       </c>
@@ -1573,7 +1574,7 @@
         <v>7.3785476281046396</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>148</v>
       </c>
@@ -1602,7 +1603,7 @@
         <v>7.6371584885994839</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>148</v>
       </c>
@@ -1631,7 +1632,7 @@
         <v>7.9046453078587247</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>148</v>
       </c>
@@ -1660,7 +1661,7 @@
         <v>8.1813078936337824</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>148</v>
       </c>
@@ -1689,7 +1690,7 @@
         <v>8.4674560537782675</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>148</v>
       </c>
@@ -1718,7 +1719,7 @@
         <v>8.7634099264271512</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>202</v>
       </c>
@@ -1748,7 +1749,7 @@
         <v>86.460524321264955</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>202</v>
       </c>
@@ -1778,7 +1779,7 @@
         <v>87.89444169204053</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>202</v>
       </c>
@@ -1808,7 +1809,7 @@
         <v>89.352140077821005</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>202</v>
       </c>
@@ -1838,7 +1839,7 @@
         <v>90.834013878371721</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>202</v>
       </c>
@@ -1868,7 +1869,7 @@
         <v>92.340464034439464</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>193</v>
       </c>
@@ -1897,7 +1898,7 @@
         <v>97.708742857142852</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>193</v>
       </c>
@@ -1926,7 +1927,7 @@
         <v>98.622035714285715</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>193</v>
       </c>
@@ -1955,7 +1956,7 @@
         <v>98.785214285714289</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>193</v>
       </c>
@@ -1984,7 +1985,7 @@
         <v>98.948392857142849</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>193</v>
       </c>
@@ -2013,7 +2014,7 @@
         <v>99.111571428571423</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>193</v>
       </c>
@@ -2042,7 +2043,7 @@
         <v>99.274749999999997</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>193</v>
       </c>
@@ -2071,7 +2072,7 @@
         <v>99.437928571428571</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>193</v>
       </c>
@@ -2100,7 +2101,7 @@
         <v>99.601107142857131</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>193</v>
       </c>
@@ -2129,7 +2130,7 @@
         <v>99.764285714285705</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>193</v>
       </c>
@@ -2158,7 +2159,7 @@
         <v>99.927464285714279</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>200</v>
       </c>
@@ -2187,7 +2188,7 @@
         <v>90.92222000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>200</v>
       </c>
@@ -2216,7 +2217,7 @@
         <v>91.911683266000011</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>200</v>
       </c>
@@ -2245,7 +2246,7 @@
         <v>92.91184357532002</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>200</v>
       </c>
@@ -2274,7 +2275,7 @@
         <v>93.922815922499808</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>200</v>
       </c>
@@ -2303,7 +2304,7 @@
         <v>94.944716532265687</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>203</v>
       </c>
@@ -2332,7 +2333,7 @@
         <v>361906.34571078792</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>203</v>
       </c>
@@ -2361,7 +2362,7 @@
         <v>387019.50024189468</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>203</v>
       </c>
@@ -2390,7 +2391,7 @@
         <v>412231.55552550871</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>203</v>
       </c>
@@ -2419,7 +2420,7 @@
         <v>437542.51156162989</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>203</v>
       </c>
@@ -2448,7 +2449,7 @@
         <v>462952.36835025827</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>203</v>
       </c>
@@ -2477,7 +2478,7 @@
         <v>344656.92064585851</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>203</v>
       </c>
@@ -2506,7 +2507,7 @@
         <v>364402.73401411739</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>203</v>
       </c>
@@ -2535,7 +2536,7 @@
         <v>384225.81483198522</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>203</v>
       </c>
@@ -2564,7 +2565,7 @@
         <v>404126.16309946158</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>203</v>
       </c>
@@ -2593,7 +2594,7 @@
         <v>424103.77881654678</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>204</v>
       </c>
@@ -2622,7 +2623,7 @@
         <v>158761.89014095199</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>204</v>
       </c>
@@ -2651,7 +2652,7 @@
         <v>164342.37057940639</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>204</v>
       </c>
@@ -2680,7 +2681,7 @@
         <v>170114.7941430413</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>204</v>
       </c>
@@ -2709,7 +2710,7 @@
         <v>176085.65498697289</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>204</v>
       </c>
@@ -2738,7 +2739,7 @@
         <v>182261.6641668115</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>205</v>
       </c>
@@ -2767,7 +2768,7 @@
         <v>7026</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>205</v>
       </c>
@@ -2796,7 +2797,7 @@
         <v>7500.1430549519973</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>205</v>
       </c>
@@ -2825,7 +2826,7 @@
         <v>7861.0280628179989</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>205</v>
       </c>
@@ -2854,7 +2855,7 @@
         <v>8225.1167425979966</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>205</v>
       </c>
@@ -2883,7 +2884,7 @@
         <v>8592.4090942919956</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>207</v>
       </c>
@@ -2912,7 +2913,7 @@
         <v>272575.96766625863</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>207</v>
       </c>
@@ -2941,7 +2942,7 @@
         <v>287876.12222860788</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>207</v>
       </c>
@@ -2970,7 +2971,7 @@
         <v>304033.49472771061</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>207</v>
       </c>
@@ -2999,7 +3000,7 @@
         <v>321096.01419443771</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>207</v>
       </c>
@@ -3028,7 +3029,7 @@
         <v>339114.28347773122</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>228</v>
       </c>
@@ -3057,7 +3058,7 @@
         <v>892.42950861146085</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>228</v>
       </c>
@@ -3086,7 +3087,7 @@
         <v>1019.5881230993029</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>228</v>
       </c>
@@ -3115,7 +3116,7 @@
         <v>1147.967597954756</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>228</v>
       </c>
@@ -3144,7 +3145,7 @@
         <v>1277.5679331778181</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>228</v>
       </c>
@@ -3173,7 +3174,7 @@
         <v>1408.3891287684901</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>228</v>
       </c>
@@ -3202,7 +3203,7 @@
         <v>796.70494376731313</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>228</v>
       </c>
@@ -3231,7 +3232,7 @@
         <v>917.28571818365663</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>228</v>
       </c>
@@ -3260,7 +3261,7 @@
         <v>1055.298221956233</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>228</v>
       </c>
@@ -3289,7 +3290,7 @@
         <v>1210.984111882826</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>228</v>
       </c>
@@ -3318,7 +3319,7 @@
         <v>1384.585044761219</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>244</v>
       </c>
@@ -3347,7 +3348,7 @@
         <v>19.733333333333331</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>244</v>
       </c>
@@ -3376,7 +3377,7 @@
         <v>19.196888888888889</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>244</v>
       </c>
@@ -3405,7 +3406,7 @@
         <v>18.66577777777778</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>244</v>
       </c>
@@ -3434,7 +3435,7 @@
         <v>18.14</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>244</v>
       </c>
@@ -3463,7 +3464,7 @@
         <v>17.61955555555555</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>245</v>
       </c>
@@ -3492,7 +3493,7 @@
         <v>89.198827494123194</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>245</v>
       </c>
@@ -3521,7 +3522,7 @@
         <v>89.380807536188684</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>245</v>
       </c>
@@ -3550,7 +3551,7 @@
         <v>89.563090584620838</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>245</v>
       </c>
@@ -3579,7 +3580,7 @@
         <v>89.745677098501574</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>245</v>
       </c>
@@ -3608,7 +3609,7 @@
         <v>89.928567537571354</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>245</v>
       </c>
@@ -3637,7 +3638,7 @@
         <v>90.11176236223001</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>245</v>
       </c>
@@ -3666,7 +3667,7 @@
         <v>90.295262033537696</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>245</v>
       </c>
@@ -3695,7 +3696,7 @@
         <v>90.479067013215754</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>245</v>
       </c>
@@ -3724,7 +3725,7 @@
         <v>90.663177763647781</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>245</v>
       </c>
@@ -3753,7 +3754,7 @@
         <v>90.847594747880279</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>245</v>
       </c>
@@ -3782,7 +3783,7 @@
         <v>89.125900000000001</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>245</v>
       </c>
@@ -3811,7 +3812,7 @@
         <v>89.909943499999997</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>245</v>
       </c>
@@ -3840,7 +3841,7 @@
         <v>90.695220000000006</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>245</v>
       </c>
@@ -3869,7 +3870,7 @@
         <v>91.481729500000014</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>245</v>
       </c>
@@ -3898,7 +3899,7 @@
         <v>92.269472000000007</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>245</v>
       </c>
@@ -3927,7 +3928,7 @@
         <v>93.058447500000014</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>245</v>
       </c>
@@ -3956,7 +3957,7 @@
         <v>93.84865600000002</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>245</v>
       </c>
@@ -3985,7 +3986,7 @@
         <v>94.640097500000024</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>245</v>
       </c>
@@ -4014,7 +4015,7 @@
         <v>95.432772000000014</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>245</v>
       </c>
@@ -4043,7 +4044,7 @@
         <v>96.226679500000017</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>276</v>
       </c>
@@ -4072,7 +4073,7 @@
         <v>64.626946951668998</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>276</v>
       </c>
@@ -4101,7 +4102,7 @@
         <v>61.797659797529029</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>276</v>
       </c>
@@ -4130,7 +4131,7 @@
         <v>58.996085245839843</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>276</v>
       </c>
@@ -4159,7 +4160,7 @@
         <v>56.222223296601427</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>276</v>
       </c>
@@ -4188,7 +4189,7 @@
         <v>53.476073949813816</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>276</v>
       </c>
@@ -4217,7 +4218,7 @@
         <v>50.757637205477003</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>276</v>
       </c>
@@ -4246,7 +4247,7 @@
         <v>48.06691306359096</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>276</v>
       </c>
@@ -4275,7 +4276,7 @@
         <v>45.403901524155707</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>276</v>
       </c>
@@ -4304,7 +4305,7 @@
         <v>42.768602587171237</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>276</v>
       </c>
@@ -4333,7 +4334,7 @@
         <v>40.16101625263758</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>276</v>
       </c>
@@ -4362,7 +4363,7 @@
         <v>69.3338001487799</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>276</v>
       </c>
@@ -4391,7 +4392,7 @@
         <v>67.352972385300021</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>276</v>
       </c>
@@ -4420,7 +4421,7 @@
         <v>65.426674283148913</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>276</v>
       </c>
@@ -4449,7 +4450,7 @@
         <v>63.553443269459287</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>276</v>
       </c>
@@ -4478,7 +4479,7 @@
         <v>61.731855251410558</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>276</v>
       </c>
@@ -4507,7 +4508,7 @@
         <v>59.960523618738179</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>276</v>
       </c>
@@ -4536,7 +4537,7 @@
         <v>58.238098271797057</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>276</v>
       </c>
@@ -4565,7 +4566,7 @@
         <v>56.563264674531062</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>276</v>
       </c>
@@ -4594,7 +4595,7 @@
         <v>54.934742931716322</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>276</v>
       </c>
@@ -4623,7 +4624,7 @@
         <v>53.351286889862124</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>277</v>
       </c>
@@ -4651,8 +4652,16 @@
       <c r="I137">
         <v>65.423590000000004</v>
       </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J137">
+        <f>+G137*0.95</f>
+        <v>64.074650000000005</v>
+      </c>
+      <c r="K137">
+        <f>+G137*1.05</f>
+        <v>70.81935</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>277</v>
       </c>
@@ -4680,8 +4689,16 @@
       <c r="I138">
         <v>63.790038399999993</v>
       </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J138">
+        <f t="shared" ref="J138:J146" si="1">+G138*0.95</f>
+        <v>62.532799999999995</v>
+      </c>
+      <c r="K138">
+        <f t="shared" ref="K138:K146" si="2">+G138*1.05</f>
+        <v>69.115200000000002</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>277</v>
       </c>
@@ -4709,8 +4726,16 @@
       <c r="I139">
         <v>62.159408199999987</v>
       </c>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J139">
+        <f t="shared" si="1"/>
+        <v>60.990949999999991</v>
+      </c>
+      <c r="K139">
+        <f t="shared" si="2"/>
+        <v>67.411050000000003</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>277</v>
       </c>
@@ -4738,8 +4763,16 @@
       <c r="I140">
         <v>60.531699400000001</v>
       </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J140">
+        <f t="shared" si="1"/>
+        <v>59.449100000000001</v>
+      </c>
+      <c r="K140">
+        <f t="shared" si="2"/>
+        <v>65.706900000000005</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>277</v>
       </c>
@@ -4767,8 +4800,16 @@
       <c r="I141">
         <v>58.906911999999991</v>
       </c>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J141">
+        <f t="shared" si="1"/>
+        <v>57.907249999999998</v>
+      </c>
+      <c r="K141">
+        <f t="shared" si="2"/>
+        <v>64.002750000000006</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>277</v>
       </c>
@@ -4796,8 +4837,16 @@
       <c r="I142">
         <v>57.285045999999987</v>
       </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J142">
+        <f t="shared" si="1"/>
+        <v>56.365399999999987</v>
+      </c>
+      <c r="K142">
+        <f t="shared" si="2"/>
+        <v>62.298599999999986</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>277</v>
       </c>
@@ -4825,8 +4874,16 @@
       <c r="I143">
         <v>55.666101400000002</v>
       </c>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J143">
+        <f t="shared" si="1"/>
+        <v>54.823549999999997</v>
+      </c>
+      <c r="K143">
+        <f t="shared" si="2"/>
+        <v>60.594450000000009</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>277</v>
       </c>
@@ -4854,8 +4911,16 @@
       <c r="I144">
         <v>54.050078199999987</v>
       </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J144">
+        <f t="shared" si="1"/>
+        <v>53.281699999999987</v>
+      </c>
+      <c r="K144">
+        <f t="shared" si="2"/>
+        <v>58.890299999999996</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>277</v>
       </c>
@@ -4883,8 +4948,16 @@
       <c r="I145">
         <v>52.436976399999992</v>
       </c>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J145">
+        <f t="shared" si="1"/>
+        <v>51.739849999999983</v>
+      </c>
+      <c r="K145">
+        <f t="shared" si="2"/>
+        <v>57.186149999999991</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>277</v>
       </c>
@@ -4912,8 +4985,16 @@
       <c r="I146">
         <v>50.826795999999987</v>
       </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J146">
+        <f t="shared" si="1"/>
+        <v>50.197999999999986</v>
+      </c>
+      <c r="K146">
+        <f t="shared" si="2"/>
+        <v>55.481999999999992</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>277</v>
       </c>
@@ -4941,8 +5022,16 @@
       <c r="I147">
         <v>65.851630338904542</v>
       </c>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J147">
+        <f>+G147*0.95</f>
+        <v>64.493864764906505</v>
+      </c>
+      <c r="K147">
+        <f>+G147*1.05</f>
+        <v>71.282692634896677</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>277</v>
       </c>
@@ -4970,8 +5059,16 @@
       <c r="I148">
         <v>64.366708412510363</v>
       </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J148">
+        <f t="shared" ref="J148:J156" si="3">+G148*0.95</f>
+        <v>63.098104418413833</v>
+      </c>
+      <c r="K148">
+        <f t="shared" ref="K148:K156" si="4">+G148*1.05</f>
+        <v>69.740010146667927</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>277</v>
       </c>
@@ -4999,8 +5096,16 @@
       <c r="I149">
         <v>62.915216483343421</v>
       </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J149">
+        <f t="shared" si="3"/>
+        <v>61.732550773782535</v>
+      </c>
+      <c r="K149">
+        <f t="shared" si="4"/>
+        <v>68.230714013128065</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>277</v>
       </c>
@@ -5028,8 +5133,16 @@
       <c r="I150">
         <v>61.496403070076219</v>
       </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J150">
+        <f t="shared" si="3"/>
+        <v>60.396550105006106</v>
+      </c>
+      <c r="K150">
+        <f t="shared" si="4"/>
+        <v>66.754081695006761</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>277</v>
       </c>
@@ -5057,8 +5170,16 @@
       <c r="I151">
         <v>60.109533560671402</v>
       </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J151">
+        <f t="shared" si="3"/>
+        <v>59.089462833855379</v>
+      </c>
+      <c r="K151">
+        <f t="shared" si="4"/>
+        <v>65.309406290050688</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>277</v>
       </c>
@@ -5086,8 +5207,16 @@
       <c r="I152">
         <v>58.75388983418766</v>
       </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J152">
+        <f t="shared" si="3"/>
+        <v>57.810663223695791</v>
+      </c>
+      <c r="K152">
+        <f t="shared" si="4"/>
+        <v>63.895996194611136</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>277</v>
       </c>
@@ -5115,8 +5244,16 @@
       <c r="I153">
         <v>57.428769891054131</v>
       </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J153">
+        <f t="shared" si="3"/>
+        <v>56.559539079930978</v>
+      </c>
+      <c r="K153">
+        <f t="shared" si="4"/>
+        <v>62.513174772555296</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>277</v>
       </c>
@@ -5144,8 +5281,16 @@
       <c r="I154">
         <v>56.133487491624052</v>
       </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J154">
+        <f t="shared" si="3"/>
+        <v>55.335491456929368</v>
+      </c>
+      <c r="K154">
+        <f t="shared" si="4"/>
+        <v>61.160280031342985</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>277</v>
       </c>
@@ -5173,8 +5318,16 @@
       <c r="I155">
         <v>54.867371802822348</v>
       </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J155">
+        <f t="shared" si="3"/>
+        <v>54.137934371293333</v>
+      </c>
+      <c r="K155">
+        <f t="shared" si="4"/>
+        <v>59.836664305113693</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>277</v>
       </c>
@@ -5202,8 +5355,16 @@
       <c r="I156">
         <v>53.629767052706171</v>
       </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J156">
+        <f t="shared" si="3"/>
+        <v>52.966294521333673</v>
+      </c>
+      <c r="K156">
+        <f t="shared" si="4"/>
+        <v>58.541693944631952</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>325</v>
       </c>
@@ -5232,7 +5393,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>325</v>
       </c>
@@ -5261,7 +5422,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>325</v>
       </c>
@@ -5290,7 +5451,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>325</v>
       </c>
@@ -5319,7 +5480,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>325</v>
       </c>
@@ -5348,7 +5509,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>332</v>
       </c>
@@ -5377,7 +5538,7 @@
         <v>0.64546314585089737</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>332</v>
       </c>
@@ -5406,7 +5567,7 @@
         <v>0.51469902830302305</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>332</v>
       </c>
@@ -5435,7 +5596,7 @@
         <v>0.41042203194026261</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>332</v>
       </c>
@@ -5464,7 +5625,7 @@
         <v>0.32726787299048538</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>332</v>
       </c>
@@ -5493,7 +5654,7 @@
         <v>0.26095849634300861</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>332</v>
       </c>
@@ -5522,7 +5683,7 @@
         <v>0.65439130434782633</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>332</v>
       </c>
@@ -5551,7 +5712,7 @@
         <v>0.52181843478260892</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>332</v>
       </c>
@@ -5580,7 +5741,7 @@
         <v>0.41609906086956538</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>332</v>
       </c>
@@ -5609,7 +5770,7 @@
         <v>0.33179469913043491</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>332</v>
       </c>
@@ -5638,7 +5799,7 @@
         <v>0.26456811965217403</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>334</v>
       </c>
@@ -5667,7 +5828,7 @@
         <v>93.70400000673547</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>334</v>
       </c>
@@ -5696,7 +5857,7 @@
         <v>94.782871493406859</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>334</v>
       </c>
@@ -5725,7 +5886,7 @@
         <v>95.863802289969655</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>334</v>
       </c>
@@ -5754,7 +5915,7 @@
         <v>96.946792396423888</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>334</v>
       </c>
@@ -5783,7 +5944,7 @@
         <v>98.0318418127695</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>334</v>
       </c>
@@ -5812,7 +5973,7 @@
         <v>92.93801595829882</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>334</v>
       </c>
@@ -5841,7 +6002,7 @@
         <v>93.968919736860101</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>334</v>
       </c>
@@ -5870,7 +6031,7 @@
         <v>95.131696762608669</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>334</v>
       </c>
@@ -5899,7 +6060,7 @@
         <v>96.426755945691355</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>334</v>
       </c>
@@ -5928,7 +6089,7 @@
         <v>97.854506196255059</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>361</v>
       </c>
@@ -5957,7 +6118,7 @@
         <v>4.83446</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>361</v>
       </c>
@@ -5986,7 +6147,7 @@
         <v>4.8645499999999995</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>361</v>
       </c>
@@ -6015,7 +6176,7 @@
         <v>4.8846099999999995</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>361</v>
       </c>
@@ -6044,7 +6205,7 @@
         <v>4.9247299999999994</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>361</v>
       </c>
@@ -6073,7 +6234,7 @@
         <v>4.9748799999999997</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
         <v>364</v>
       </c>
@@ -6102,7 +6263,7 @@
         <v>115494.72</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>364</v>
       </c>
@@ -6131,7 +6292,7 @@
         <v>126091.36056</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3">
         <v>364</v>
       </c>
@@ -6160,7 +6321,7 @@
         <v>137652.38203200011</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
         <v>364</v>
       </c>
@@ -6189,7 +6350,7 @@
         <v>150264.6941928</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
         <v>364</v>
       </c>
@@ -6218,7 +6379,7 @@
         <v>164022.94496544011</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>367</v>
       </c>
@@ -6247,7 +6408,7 @@
         <v>5.5479450746268659</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
         <v>367</v>
       </c>
@@ -6276,7 +6437,7 @@
         <v>5.6197363811343282</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>367</v>
       </c>
@@ -6305,7 +6466,7 @@
         <v>5.6924087192644777</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
         <v>367</v>
       </c>
@@ -6334,7 +6495,7 @@
         <v>5.7659725305191172</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>367</v>
       </c>
@@ -6363,7 +6524,7 @@
         <v>5.8404383771269233</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
         <v>369</v>
       </c>
@@ -6392,7 +6553,7 @@
         <v>88.128</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
         <v>369</v>
       </c>
@@ -6421,7 +6582,7 @@
         <v>90.340012799999997</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
         <v>369</v>
       </c>
@@ -6450,7 +6611,7 @@
         <v>92.605254912000021</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
         <v>369</v>
       </c>
@@ -6479,7 +6640,7 @@
         <v>94.924970703359989</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3">
         <v>369</v>
       </c>
@@ -6508,7 +6669,7 @@
         <v>97.3004330244096</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
         <v>377</v>
       </c>
@@ -6537,7 +6698,7 @@
         <v>14193.63602034</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="3">
         <v>377</v>
       </c>
@@ -6566,7 +6727,7 @@
         <v>16404.294830507952</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3">
         <v>377</v>
       </c>
@@ -6595,7 +6756,7 @@
         <v>18958.794473268641</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
         <v>377</v>
       </c>
@@ -6624,7 +6785,7 @@
         <v>21910.547375171111</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3">
         <v>377</v>
       </c>
@@ -6653,7 +6814,7 @@
         <v>25321.253271995771</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>424</v>
       </c>
@@ -6682,7 +6843,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>424</v>
       </c>
@@ -6711,7 +6872,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>424</v>
       </c>
@@ -6740,7 +6901,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>424</v>
       </c>
@@ -6769,7 +6930,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>424</v>
       </c>
@@ -6798,7 +6959,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>460</v>
       </c>
@@ -6827,7 +6988,7 @@
         <v>95.125032000000004</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>460</v>
       </c>
@@ -6856,7 +7017,7 @@
         <v>96.160232469600004</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>460</v>
       </c>
@@ -6885,7 +7046,7 @@
         <v>97.206624445392023</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>460</v>
       </c>
@@ -6914,7 +7075,7 @@
         <v>98.545849202319999</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>460</v>
       </c>
@@ -6943,7 +7104,7 @@
         <v>98.831307694343209</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>77</v>
       </c>
@@ -6972,7 +7133,7 @@
         <v>98.67895</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>77</v>
       </c>
@@ -7001,7 +7162,7 @@
         <v>98.965739499999998</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>77</v>
       </c>
@@ -7030,7 +7191,7 @@
         <v>99.255396895000004</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>77</v>
       </c>
@@ -7059,7 +7220,7 @@
         <v>99.547950863950007</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>77</v>
       </c>
@@ -7088,7 +7249,7 @@
         <v>99.843430372589509</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>98</v>
       </c>
@@ -7117,7 +7278,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>98</v>
       </c>
@@ -7146,7 +7307,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>98</v>
       </c>
@@ -7175,7 +7336,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>98</v>
       </c>
@@ -7204,7 +7365,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>98</v>
       </c>
@@ -7233,7 +7394,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="3">
         <v>386.1</v>
       </c>
@@ -7262,7 +7423,7 @@
         <v>6025.5908288085884</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="3">
         <v>386.1</v>
       </c>
@@ -7291,7 +7452,7 @@
         <v>7132.9729466473937</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3">
         <v>386.1</v>
       </c>
@@ -7320,7 +7481,7 @@
         <v>8387.9290364164917</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3">
         <v>386.1</v>
       </c>
@@ -7349,7 +7510,7 @@
         <v>9792.4915984875806</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="3">
         <v>386.1</v>
       </c>
@@ -7378,7 +7539,7 @@
         <v>11348.693133232369</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="3">
         <v>386.2</v>
       </c>
@@ -7407,7 +7568,7 @@
         <v>9176.5019107995558</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="3">
         <v>386.2</v>
       </c>
@@ -7436,7 +7597,7 @@
         <v>10283.967217993961</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="3">
         <v>386.2</v>
       </c>
@@ -7465,7 +7626,7 @@
         <v>11524.99750015523</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="3">
         <v>386.2</v>
       </c>
@@ -7494,7 +7655,7 @@
         <v>12915.691019463869</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3">
         <v>386.2</v>
       </c>
@@ -7523,7 +7684,7 @@
         <v>14474.085149544269</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="3">
         <v>386.3</v>
       </c>
@@ -7552,7 +7713,7 @@
         <v>6775.7920969396118</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="3">
         <v>386.3</v>
       </c>
@@ -7581,7 +7742,7 @@
         <v>7687.612830857006</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="3">
         <v>386.3</v>
       </c>
@@ -7610,7 +7771,7 @@
         <v>8759.3798750710612</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="3">
         <v>386.3</v>
       </c>
@@ -7639,7 +7800,7 @@
         <v>9993.3389311351038</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="3">
         <v>386.3</v>
       </c>
@@ -7668,7 +7829,7 @@
         <v>11391.73570060247</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>379</v>
       </c>
@@ -7697,7 +7858,7 @@
         <v>13317.175813442071</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>274</v>
       </c>
@@ -7726,7 +7887,7 @@
         <v>46054.901058930787</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>379</v>
       </c>
@@ -7755,7 +7916,7 @@
         <v>13418.021660158851</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>274</v>
       </c>
@@ -7784,7 +7945,7 @@
         <v>46403.657098334967</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>379</v>
       </c>
@@ -7813,7 +7974,7 @@
         <v>13536.316299144</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>274</v>
       </c>
@@ -7842,7 +8003,7 @@
         <v>46812.756442714293</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>379</v>
       </c>
@@ -7871,7 +8032,7 @@
         <v>13665.23975007113</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>274</v>
       </c>
@@ -7900,7 +8061,7 @@
         <v>47258.613496777638</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>379</v>
       </c>
@@ -7929,7 +8090,7 @@
         <v>13801.316029168571</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>274</v>
       </c>
@@ -7958,7 +8119,7 @@
         <v>47729.20723662855</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>379</v>
       </c>
@@ -7987,7 +8148,7 @@
         <v>13942.80055708834</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>274</v>
       </c>
@@ -8016,7 +8177,7 @@
         <v>48218.50436884314</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>379</v>
       </c>
@@ -8045,7 +8206,7 @@
         <v>14088.84540208515</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>274</v>
       </c>
@@ -8074,7 +8235,7 @@
         <v>48723.572483938951</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>379</v>
       </c>
@@ -8103,7 +8264,7 @@
         <v>14239.06717106818</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>274</v>
       </c>
@@ -8132,7 +8293,7 @@
         <v>49243.085690367268</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>379</v>
       </c>
@@ -8161,7 +8322,7 @@
         <v>14393.32333139659</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>274</v>
       </c>
@@ -8190,7 +8351,7 @@
         <v>49776.551066298169</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>379</v>
       </c>
@@ -8219,7 +8380,7 @@
         <v>14551.59642655029</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>274</v>
       </c>
@@ -8248,7 +8409,7 @@
         <v>50323.908241701443</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>14</v>
       </c>
@@ -8277,7 +8438,7 @@
         <v>59371.884262853768</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>14</v>
       </c>
@@ -8306,7 +8467,7 @@
         <v>59821.484690416968</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>14</v>
       </c>
@@ -8335,7 +8496,7 @@
         <v>60348.876962857597</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>14</v>
       </c>
@@ -8364,7 +8525,7 @@
         <v>60923.655603197178</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>14</v>
       </c>
@@ -8393,7 +8554,7 @@
         <v>61530.323654041553</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>14</v>
       </c>
@@ -8422,7 +8583,7 @@
         <v>62161.103267851133</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>14</v>
       </c>
@@ -8451,7 +8612,7 @@
         <v>62812.214115662013</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>14</v>
       </c>
@@ -8480,7 +8641,7 @@
         <v>63481.946918379748</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>14</v>
       </c>
@@ -8509,7 +8670,7 @@
         <v>64169.666223595093</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>14</v>
       </c>
@@ -8538,7 +8699,7 @@
         <v>64875.294205010192</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>14</v>
       </c>
@@ -8567,7 +8728,7 @@
         <v>60802.946712188583</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>14</v>
       </c>
@@ -8596,7 +8757,7 @@
         <v>61412.55539447139</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>14</v>
       </c>
@@ -8625,7 +8786,7 @@
         <v>62023.951131092377</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>14</v>
       </c>
@@ -8654,7 +8815,7 @@
         <v>62637.133922051551</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>14</v>
       </c>
@@ -8683,7 +8844,7 @@
         <v>63252.103767348883</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>14</v>
       </c>
@@ -8712,7 +8873,7 @@
         <v>63868.860666984387</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>14</v>
       </c>
@@ -8741,7 +8902,7 @@
         <v>64487.404620958077</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>14</v>
       </c>
@@ -8770,7 +8931,7 @@
         <v>65107.735629269962</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>14</v>
       </c>
@@ -8799,7 +8960,7 @@
         <v>65729.853691919998</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>14</v>
       </c>
@@ -8828,7 +8989,7 @@
         <v>66353.758808908198</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>379</v>
       </c>
@@ -8857,7 +9018,7 @@
         <v>13638.16461941349</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>274</v>
       </c>
@@ -8886,7 +9047,7 @@
         <v>47164.979344832544</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>379</v>
       </c>
@@ -8915,7 +9076,7 @@
         <v>13774.90048522195</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>274</v>
       </c>
@@ -8944,7 +9105,7 @@
         <v>47637.854138950643</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>379</v>
       </c>
@@ -8973,7 +9134,7 @@
         <v>13912.037189189839</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>274</v>
       </c>
@@ -9002,7 +9163,7 @@
         <v>48112.115155044899</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>379</v>
       </c>
@@ -9031,7 +9192,7 @@
         <v>14049.574731317151</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>274</v>
       </c>
@@ -9060,7 +9221,7 @@
         <v>48587.762393115328</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>379</v>
       </c>
@@ -9089,7 +9250,7 @@
         <v>14187.513111603899</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>274</v>
       </c>
@@ -9118,7 +9279,7 @@
         <v>49064.795853161922</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>379</v>
       </c>
@@ -9147,7 +9308,7 @@
         <v>14325.85233005006</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>274</v>
       </c>
@@ -9176,7 +9337,7 @@
         <v>49543.215535184667</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>379</v>
       </c>
@@ -9205,7 +9366,7 @@
         <v>14464.59238665566</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>274</v>
       </c>
@@ -9234,7 +9395,7 @@
         <v>50023.021439183598</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>379</v>
       </c>
@@ -9263,7 +9424,7 @@
         <v>14603.73328142068</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>274</v>
       </c>
@@ -9292,7 +9453,7 @@
         <v>50504.213565158687</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>379</v>
       </c>
@@ -9321,7 +9482,7 @@
         <v>14743.275014345139</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>274</v>
       </c>
@@ -9350,7 +9511,7 @@
         <v>50986.791913109962</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>379</v>
       </c>
@@ -9379,7 +9540,7 @@
         <v>14883.217585429011</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>274</v>
       </c>
@@ -9408,7 +9569,7 @@
         <v>51470.756483037367</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>14.1</v>
       </c>
@@ -9437,7 +9598,7 @@
         <v>9487.176818882821</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>14.2</v>
       </c>
@@ -9466,7 +9627,7 @@
         <v>51315.769893305762</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>14.1</v>
       </c>
@@ -9495,7 +9656,7 @@
         <v>9582.2949944297943</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>14.2</v>
       </c>
@@ -9524,7 +9685,7 @@
         <v>51830.260400041603</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>14.1</v>
       </c>
@@ -9553,7 +9714,7 @@
         <v>9677.6920067997835</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>14.2</v>
       </c>
@@ -9582,7 +9743,7 @@
         <v>52346.259124292606</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>14.1</v>
       </c>
@@ -9611,7 +9772,7 @@
         <v>9773.3678559927885</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>14.2</v>
       </c>
@@ -9640,7 +9801,7 @@
         <v>52863.766066058772</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>14.1</v>
       </c>
@@ -9669,7 +9830,7 @@
         <v>9869.3225420088074</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>14.2</v>
       </c>
@@ -9698,7 +9859,7 @@
         <v>53382.781225340077</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>14.1</v>
       </c>
@@ -9727,7 +9888,7 @@
         <v>9965.556064847844</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>14.2</v>
       </c>
@@ -9756,7 +9917,7 @@
         <v>53903.304602136559</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>14.1</v>
       </c>
@@ -9785,7 +9946,7 @@
         <v>10062.0684245099</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>14.2</v>
       </c>
@@ -9814,7 +9975,7 @@
         <v>54425.336196448203</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>14.1</v>
       </c>
@@ -9843,7 +10004,7 @@
         <v>10158.859620994959</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>14.2</v>
       </c>
@@ -9872,7 +10033,7 @@
         <v>54948.876008275001</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>14.1</v>
       </c>
@@ -9901,7 +10062,7 @@
         <v>10255.92965430305</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>14.2</v>
       </c>
@@ -9930,7 +10091,7 @@
         <v>55473.924037616962</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>14.1</v>
       </c>
@@ -9959,7 +10120,7 @@
         <v>10353.278524434139</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>14.2</v>
       </c>
@@ -9988,7 +10149,7 @@
         <v>56000.480284474063</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>14.1</v>
       </c>
@@ -10017,7 +10178,7 @@
         <v>9263.8859550375455</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>14.2</v>
       </c>
@@ -10046,7 +10207,7 @@
         <v>50107.998307816233</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>14.1</v>
       </c>
@@ -10075,7 +10236,7 @@
         <v>9334.0377977488515</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>14.2</v>
       </c>
@@ -10104,7 +10265,7 @@
         <v>50487.446892668122</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>14.1</v>
       </c>
@@ -10133,7 +10294,7 @@
         <v>9416.3276210569329</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>14.2</v>
       </c>
@@ -10162,7 +10323,7 @@
         <v>50932.549341800674</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>14.1</v>
       </c>
@@ -10191,7 +10352,7 @@
         <v>9506.0112118610195</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>14.2</v>
       </c>
@@ -10220,7 +10381,7 @@
         <v>51417.644391336173</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>14.1</v>
       </c>
@@ -10249,7 +10410,7 @@
         <v>9600.6705561847666</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>14.2</v>
       </c>
@@ -10278,7 +10439,7 @@
         <v>51929.65309785679</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>14.1</v>
       </c>
@@ -10307,7 +10468,7 @@
         <v>9699.0920645745646</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>14.2</v>
       </c>
@@ -10336,7 +10497,7 @@
         <v>52462.011203276568</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>14.1</v>
       </c>
@@ -10365,7 +10526,7 @@
         <v>9800.6858865173472</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>14.2</v>
       </c>
@@ -10394,7 +10555,7 @@
         <v>53011.528229144671</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>14.1</v>
       </c>
@@ -10423,7 +10584,7 @@
         <v>9905.1853205803909</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>14.2</v>
       </c>
@@ -10452,7 +10613,7 @@
         <v>53576.761597799363</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>14.1</v>
       </c>
@@ -10481,7 +10642,7 @@
         <v>10012.491216151881</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>14.2</v>
       </c>
@@ -10510,7 +10671,7 @@
         <v>54157.175007443213</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>14.1</v>
       </c>
@@ -10539,7 +10700,7 @@
         <v>10122.59142987548</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>14.2</v>
       </c>
@@ -10568,7 +10729,7 @@
         <v>54752.70277513472</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>14.3</v>
       </c>
@@ -10597,7 +10758,7 @@
         <v>56552.414086080753</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>14.4</v>
       </c>
@@ -10626,7 +10787,7 @@
         <v>4250.5326261078344</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>14.3</v>
       </c>
@@ -10655,7 +10816,7 @@
         <v>57119.407044400919</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>14.4</v>
       </c>
@@ -10684,7 +10845,7 @@
         <v>4293.1483500704726</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>14.3</v>
       </c>
@@ -10713,7 +10874,7 @@
         <v>57688.062130009188</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>14.4</v>
       </c>
@@ -10742,7 +10903,7 @@
         <v>4335.8890010831956</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>14.3</v>
       </c>
@@ -10771,7 +10932,7 @@
         <v>58258.379342905551</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>14.4</v>
       </c>
@@ -10800,7 +10961,7 @@
         <v>4378.7545791459988</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>14.3</v>
       </c>
@@ -10829,7 +10990,7 @@
         <v>58830.358683090002</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>14.4</v>
       </c>
@@ -10858,7 +11019,7 @@
         <v>4421.7450842588833</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>14.3</v>
       </c>
@@ -10887,7 +11048,7 @@
         <v>59404.000150562548</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>14.4</v>
       </c>
@@ -10916,7 +11077,7 @@
         <v>4464.8605164218507</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>14.3</v>
       </c>
@@ -10945,7 +11106,7 @@
         <v>59979.303745323188</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>14.4</v>
       </c>
@@ -10974,7 +11135,7 @@
         <v>4508.1008756348992</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>14.3</v>
       </c>
@@ -11003,7 +11164,7 @@
         <v>60556.269467371923</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>14.4</v>
       </c>
@@ -11032,7 +11193,7 @@
         <v>4551.4661618980308</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>14.3</v>
       </c>
@@ -11061,7 +11222,7 @@
         <v>61134.897316708753</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>14.4</v>
       </c>
@@ -11090,7 +11251,7 @@
         <v>4594.9563752112444</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>14.3</v>
       </c>
@@ -11119,7 +11280,7 @@
         <v>61715.187293333664</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>14.4</v>
       </c>
@@ -11148,7 +11309,7 @@
         <v>4638.5715155745374</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>14.3</v>
       </c>
@@ -11177,7 +11338,7 @@
         <v>55221.39247291936</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>14.4</v>
       </c>
@@ -11206,7 +11367,7 @@
         <v>4150.4917899344118</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>14.3</v>
       </c>
@@ -11235,7 +11396,7 @@
         <v>55639.562823662178</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>14.4</v>
       </c>
@@ -11264,7 +11425,7 @@
         <v>4181.9218667547893</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>14.3</v>
       </c>
@@ -11293,7 +11454,7 @@
         <v>56130.086849052597</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>14.4</v>
       </c>
@@ -11322,7 +11483,7 @@
         <v>4218.7901138050047</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>14.3</v>
       </c>
@@ -11351,7 +11512,7 @@
         <v>56664.68461830516</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>14.4</v>
       </c>
@@ -11380,7 +11541,7 @@
         <v>4258.9709848920229</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>14.3</v>
       </c>
@@ -11409,7 +11570,7 @@
         <v>57228.942514991417</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>14.4</v>
       </c>
@@ -11438,7 +11599,7 @@
         <v>4301.3811390501323</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>14.3</v>
       </c>
@@ -11467,7 +11628,7 @@
         <v>57815.626415133163</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>14.4</v>
       </c>
@@ -11496,7 +11657,7 @@
         <v>4345.4768527179676</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>14.3</v>
       </c>
@@ -11525,7 +11686,7 @@
         <v>58421.220260043949</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>14.4</v>
       </c>
@@ -11554,7 +11715,7 @@
         <v>4390.9938556180596</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>14.3</v>
       </c>
@@ -11583,7 +11744,7 @@
         <v>59044.134260669722</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>14.4</v>
       </c>
@@ -11612,7 +11773,7 @@
         <v>4437.8126577100284</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>14.3</v>
       </c>
@@ -11641,7 +11802,7 @@
         <v>59683.777386974543</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>14.4</v>
       </c>
@@ -11670,7 +11831,7 @@
         <v>4485.8888366205483</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>14.3</v>
       </c>
@@ -11699,7 +11860,7 @@
         <v>60340.077253239288</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>14.4</v>
       </c>
@@ -12018,7 +12179,7 @@
         <v>96.379082046683891</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>323</v>
       </c>
@@ -12047,7 +12208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>323</v>
       </c>
@@ -12076,7 +12237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>323</v>
       </c>
@@ -12105,7 +12266,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>323</v>
       </c>
@@ -12134,7 +12295,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>323</v>
       </c>
@@ -12163,7 +12324,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>376</v>
       </c>
@@ -12192,7 +12353,7 @@
         <v>36033.446856183858</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>376</v>
       </c>
@@ -12221,7 +12382,7 @@
         <v>38872.61512155136</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>376</v>
       </c>
@@ -12250,7 +12411,7 @@
         <v>41717.57657108127</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>376</v>
       </c>
@@ -12279,7 +12440,7 @@
         <v>44568.331204773582</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>376</v>
       </c>
@@ -12308,7 +12469,7 @@
         <v>47424.879022628324</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>376</v>
       </c>
@@ -12337,7 +12498,7 @@
         <v>34556.673694232348</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>376</v>
       </c>
@@ -12366,7 +12527,7 @@
         <v>37856.02412414951</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>376</v>
       </c>
@@ -12395,7 +12556,7 @@
         <v>41689.182193960667</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>376</v>
       </c>
@@ -12424,7 +12585,7 @@
         <v>46057.780844716202</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>376</v>
       </c>
@@ -12453,7 +12614,7 @@
         <v>50963.453017466447</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>466</v>
       </c>
@@ -12482,7 +12643,7 @@
         <v>60.742268041340189</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>466</v>
       </c>
@@ -12511,7 +12672,7 @@
         <v>62.622639562581618</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>466</v>
       </c>
@@ -12540,7 +12701,7 @@
         <v>64.561276595843793</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>466</v>
       </c>
@@ -12569,7 +12730,7 @@
         <v>66.559986395217919</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>466</v>
       </c>
@@ -12598,7 +12759,7 @@
         <v>68.620632331635861</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>466</v>
       </c>
@@ -12627,7 +12788,7 @@
         <v>57.97444574550294</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>466</v>
       </c>
@@ -12656,7 +12817,7 @@
         <v>59.769135016331823</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>466</v>
       </c>
@@ -12685,7 +12846,7 @@
         <v>61.619434834385345</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>466</v>
       </c>
@@ -12714,7 +12875,7 @@
         <v>63.527070103221561</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>466</v>
       </c>
@@ -12743,7 +12904,7 @@
         <v>65.493819286181989</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>96</v>
       </c>
@@ -12772,7 +12933,7 @@
         <v>990.23735660954856</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>96</v>
       </c>
@@ -12801,7 +12962,7 @@
         <v>1074.101030045967</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>96</v>
       </c>
@@ -12830,7 +12991,7 @@
         <v>1165.04537214991</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>96</v>
       </c>
@@ -12859,7 +13020,7 @@
         <v>1263.666562398188</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>96</v>
       </c>
@@ -12888,7 +13049,7 @@
         <v>1370.6108527044289</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>385</v>
       </c>
@@ -12917,7 +13078,7 @@
         <v>22394.58706838209</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>385</v>
       </c>
@@ -12946,7 +13107,7 @@
         <v>24510.31089960839</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>385</v>
       </c>
@@ -12975,7 +13136,7 @@
         <v>26645.972550694249</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>385</v>
       </c>
@@ -13004,7 +13165,7 @@
         <v>28801.572021639651</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>385</v>
       </c>
@@ -13033,7 +13194,7 @@
         <v>30977.109312444602</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>385</v>
       </c>
@@ -13062,7 +13223,7 @@
         <v>20844.165363419648</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>385</v>
       </c>
@@ -13091,7 +13252,7 @@
         <v>22863.33165174054</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>385</v>
       </c>
@@ -13120,7 +13281,7 @@
         <v>25170.11368192935</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>385</v>
       </c>
@@ -13149,7 +13310,7 @@
         <v>27768.499991978719</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>385</v>
       </c>
@@ -13178,7 +13339,7 @@
         <v>30662.479119881289</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="3">
         <v>386.1</v>
       </c>
@@ -13207,7 +13368,7 @@
         <v>6063.9485940000004</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="3">
         <v>386.1</v>
       </c>
@@ -13236,7 +13397,7 @@
         <v>7617.8354212124996</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="3">
         <v>386.1</v>
       </c>
@@ -13265,7 +13426,7 @@
         <v>9569.6688749062487</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="3">
         <v>386.1</v>
       </c>
@@ -13294,7 +13455,7 @@
         <v>11023.172622260399</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="3">
         <v>386.1</v>
       </c>
@@ -13323,7 +13484,7 @@
         <v>12345.410811333601</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="3">
         <v>386.2</v>
       </c>
@@ -13352,7 +13513,7 @@
         <v>7569.1213256024957</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="3">
         <v>386.2</v>
       </c>
@@ -13381,7 +13542,7 @@
         <v>7660.696088310985</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="3">
         <v>386.2</v>
       </c>
@@ -13410,7 +13571,7 @@
         <v>7752.6631555816357</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="3">
         <v>386.2</v>
       </c>
@@ -13439,7 +13600,7 @@
         <v>7845.0225274144459</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="3">
         <v>386.2</v>
       </c>
@@ -13468,7 +13629,7 @@
         <v>7937.7742038094157</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" s="3">
         <v>386.3</v>
       </c>
@@ -13497,7 +13658,7 @@
         <v>7026.0817481999993</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" s="3">
         <v>386.3</v>
       </c>
@@ -13526,7 +13687,7 @@
         <v>7738.846362034199</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="3">
         <v>386.3</v>
       </c>
@@ -13555,7 +13716,7 @@
         <v>8458.3536047747984</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" s="3">
         <v>386.3</v>
       </c>
@@ -13584,7 +13745,7 @@
         <v>9184.6034764218002</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="3">
         <v>386.3</v>
       </c>
@@ -13613,7 +13774,7 @@
         <v>9917.5959769751989</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>68</v>
       </c>
@@ -13642,7 +13803,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>68</v>
       </c>
@@ -13671,7 +13832,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>68</v>
       </c>
@@ -13700,7 +13861,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>68</v>
       </c>
@@ -13729,7 +13890,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>68</v>
       </c>
@@ -13758,7 +13919,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>68</v>
       </c>
@@ -13787,7 +13948,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>68</v>
       </c>
@@ -13816,7 +13977,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>68</v>
       </c>
@@ -13845,7 +14006,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>68</v>
       </c>
@@ -13874,7 +14035,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>68</v>
       </c>
@@ -13903,7 +14064,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>69</v>
       </c>
@@ -13932,7 +14093,7 @@
         <v>41.957999999999991</v>
       </c>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>69</v>
       </c>
@@ -13961,7 +14122,7 @@
         <v>44.276179499999998</v>
       </c>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>69</v>
       </c>
@@ -13990,7 +14151,7 @@
         <v>46.721281949999991</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>69</v>
       </c>
@@ -14019,7 +14180,7 @@
         <v>49.300204196249993</v>
       </c>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>69</v>
       </c>
@@ -14048,7 +14209,7 @@
         <v>52.020215462249993</v>
       </c>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>332</v>
       </c>
@@ -14077,7 +14238,7 @@
         <v>0.69049565217391329</v>
       </c>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>332</v>
       </c>
@@ -14106,7 +14267,7 @@
         <v>0.61943446956521764</v>
       </c>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>332</v>
       </c>
@@ -14135,7 +14296,7 @@
         <v>0.5556805669565219</v>
       </c>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>332</v>
       </c>
@@ -14164,7 +14325,7 @@
         <v>0.49848310017391317</v>
       </c>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466">
         <v>332</v>
       </c>
@@ -14194,6 +14355,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K466" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="194"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="806" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE06279F-7464-4E9C-B64C-E3089C350EEC}"/>
+  <xr:revisionPtr revIDLastSave="838" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD912394-2A60-4FB6-A895-E6383712DB52}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -7153,13 +7153,13 @@
         <v>30</v>
       </c>
       <c r="G218">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H218">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I218">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.3">
@@ -7182,13 +7182,13 @@
         <v>30</v>
       </c>
       <c r="G219">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H219">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I219">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.3">
@@ -7211,13 +7211,13 @@
         <v>30</v>
       </c>
       <c r="G220">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H220">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I220">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.3">
@@ -7240,13 +7240,13 @@
         <v>30</v>
       </c>
       <c r="G221">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H221">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I221">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.3">
@@ -7269,13 +7269,13 @@
         <v>30</v>
       </c>
       <c r="G222">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H222">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I222">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.3">

--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="838" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD912394-2A60-4FB6-A895-E6383712DB52}"/>
+  <xr:revisionPtr revIDLastSave="852" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41D3913D-FFF1-4C41-B037-E0442A58B53E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="74">
   <si>
     <t>Id</t>
   </si>
@@ -120,9 +120,6 @@
   </si>
   <si>
     <t>Índice de satisfacción del estudiante (SSI)</t>
-  </si>
-  <si>
-    <t>Suavizado_Exponencial_Holt</t>
   </si>
   <si>
     <t>Great Place to Work</t>
@@ -1158,7 +1155,7 @@
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G17">
         <v>5.1583252300892388</v>
@@ -1187,7 +1184,7 @@
         <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G18">
         <v>5.2470829040598819</v>
@@ -1216,7 +1213,7 @@
         <v>13</v>
       </c>
       <c r="F19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G19">
         <v>5.3371612882599546</v>
@@ -1245,7 +1242,7 @@
         <v>14</v>
       </c>
       <c r="F20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G20">
         <v>5.4285603826894571</v>
@@ -1274,7 +1271,7 @@
         <v>15</v>
       </c>
       <c r="F21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G21">
         <v>5.5212801873483901</v>
@@ -1303,7 +1300,7 @@
         <v>16</v>
       </c>
       <c r="F22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G22">
         <v>5.6153207022367528</v>
@@ -1332,7 +1329,7 @@
         <v>17</v>
       </c>
       <c r="F23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G23">
         <v>5.7106819273545444</v>
@@ -1361,7 +1358,7 @@
         <v>18</v>
       </c>
       <c r="F24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G24">
         <v>5.8073638627017674</v>
@@ -1390,7 +1387,7 @@
         <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G25">
         <v>5.9053665082784192</v>
@@ -1419,7 +1416,7 @@
         <v>20</v>
       </c>
       <c r="F26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G26">
         <v>6.0046898640845008</v>
@@ -1448,7 +1445,7 @@
         <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G27">
         <v>5.3560000000000008</v>
@@ -1477,7 +1474,7 @@
         <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G28">
         <v>5.51668</v>
@@ -1506,7 +1503,7 @@
         <v>13</v>
       </c>
       <c r="F29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G29">
         <v>5.6821804</v>
@@ -1535,7 +1532,7 @@
         <v>14</v>
       </c>
       <c r="F30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G30">
         <v>5.8526458120000013</v>
@@ -1564,7 +1561,7 @@
         <v>15</v>
       </c>
       <c r="F31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G31">
         <v>6.0282251863600003</v>
@@ -1593,7 +1590,7 @@
         <v>16</v>
       </c>
       <c r="F32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G32">
         <v>6.2090719419508007</v>
@@ -1622,7 +1619,7 @@
         <v>17</v>
       </c>
       <c r="F33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G33">
         <v>6.395344100209325</v>
@@ -1651,7 +1648,7 @@
         <v>18</v>
       </c>
       <c r="F34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G34">
         <v>6.5872044232156064</v>
@@ -1680,7 +1677,7 @@
         <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G35">
         <v>6.7848205559120736</v>
@@ -1709,7 +1706,7 @@
         <v>20</v>
       </c>
       <c r="F36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G36">
         <v>6.988365172589436</v>
@@ -1726,7 +1723,7 @@
         <v>202</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C37" s="2">
         <v>46752</v>
@@ -1739,7 +1736,7 @@
         <v>14</v>
       </c>
       <c r="F37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G37">
         <v>82.343356496442809</v>
@@ -1756,7 +1753,7 @@
         <v>202</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C38" s="2">
         <v>47483</v>
@@ -1769,7 +1766,7 @@
         <v>18</v>
       </c>
       <c r="F38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G38">
         <v>83.708992087657649</v>
@@ -1786,7 +1783,7 @@
         <v>202</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C39" s="2">
         <v>48213</v>
@@ -1796,10 +1793,10 @@
         <v>2031</v>
       </c>
       <c r="E39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G39">
         <v>85.097276264591429</v>
@@ -2106,7 +2103,7 @@
         <v>200</v>
       </c>
       <c r="B50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C50" s="2">
         <v>46387</v>
@@ -2118,7 +2115,7 @@
         <v>12</v>
       </c>
       <c r="F50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G50">
         <v>88.274000000000001</v>
@@ -2135,7 +2132,7 @@
         <v>200</v>
       </c>
       <c r="B51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C51" s="2">
         <v>46752</v>
@@ -2147,7 +2144,7 @@
         <v>14</v>
       </c>
       <c r="F51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G51">
         <v>89.156740000000013</v>
@@ -2164,7 +2161,7 @@
         <v>200</v>
       </c>
       <c r="B52" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C52" s="2">
         <v>47118</v>
@@ -2176,7 +2173,7 @@
         <v>16</v>
       </c>
       <c r="F52" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G52">
         <v>90.048307400000013</v>
@@ -2193,7 +2190,7 @@
         <v>200</v>
       </c>
       <c r="B53" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C53" s="2">
         <v>47483</v>
@@ -2205,7 +2202,7 @@
         <v>18</v>
       </c>
       <c r="F53" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G53">
         <v>90.948790474000006</v>
@@ -2222,7 +2219,7 @@
         <v>200</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C54" s="2">
         <v>47848</v>
@@ -2234,7 +2231,7 @@
         <v>20</v>
       </c>
       <c r="F54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G54">
         <v>91.858278378740025</v>
@@ -2251,7 +2248,7 @@
         <v>203</v>
       </c>
       <c r="B55" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C55" s="2">
         <v>46387</v>
@@ -2263,7 +2260,7 @@
         <v>12</v>
       </c>
       <c r="F55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G55">
         <v>337385.42515227583</v>
@@ -2280,7 +2277,7 @@
         <v>203</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C56" s="2">
         <v>46752</v>
@@ -2292,7 +2289,7 @@
         <v>14</v>
       </c>
       <c r="F56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G56">
         <v>360065.15581525367</v>
@@ -2309,7 +2306,7 @@
         <v>203</v>
       </c>
       <c r="B57" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C57" s="2">
         <v>47118</v>
@@ -2321,7 +2318,7 @@
         <v>16</v>
       </c>
       <c r="F57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G57">
         <v>382744.8864782317</v>
@@ -2338,7 +2335,7 @@
         <v>203</v>
       </c>
       <c r="B58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C58" s="2">
         <v>47483</v>
@@ -2350,7 +2347,7 @@
         <v>18</v>
       </c>
       <c r="F58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G58">
         <v>405424.61714120972</v>
@@ -2367,7 +2364,7 @@
         <v>203</v>
       </c>
       <c r="B59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C59" s="2">
         <v>47848</v>
@@ -2379,7 +2376,7 @@
         <v>20</v>
       </c>
       <c r="F59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G59">
         <v>428104.34780418762</v>
@@ -2396,7 +2393,7 @@
         <v>203</v>
       </c>
       <c r="B60" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C60" s="2">
         <v>46387</v>
@@ -2408,7 +2405,7 @@
         <v>12</v>
       </c>
       <c r="F60" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G60">
         <v>321304.73279046162</v>
@@ -2425,7 +2422,7 @@
         <v>203</v>
       </c>
       <c r="B61" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C61" s="2">
         <v>46752</v>
@@ -2437,7 +2434,7 @@
         <v>14</v>
       </c>
       <c r="F61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G61">
         <v>339023.55597144237</v>
@@ -2454,7 +2451,7 @@
         <v>203</v>
       </c>
       <c r="B62" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C62" s="2">
         <v>47118</v>
@@ -2466,7 +2463,7 @@
         <v>16</v>
       </c>
       <c r="F62" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G62">
         <v>356742.37915242318</v>
@@ -2483,7 +2480,7 @@
         <v>203</v>
       </c>
       <c r="B63" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C63" s="2">
         <v>47483</v>
@@ -2495,7 +2492,7 @@
         <v>18</v>
       </c>
       <c r="F63" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G63">
         <v>374461.20233340398</v>
@@ -2512,7 +2509,7 @@
         <v>203</v>
       </c>
       <c r="B64" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C64" s="2">
         <v>47848</v>
@@ -2524,7 +2521,7 @@
         <v>20</v>
       </c>
       <c r="F64" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G64">
         <v>392180.02551438479</v>
@@ -2541,7 +2538,7 @@
         <v>204</v>
       </c>
       <c r="B65" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C65" s="2">
         <v>46387</v>
@@ -2553,7 +2550,7 @@
         <v>12</v>
       </c>
       <c r="F65" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G65">
         <v>132301.57511745999</v>
@@ -2570,7 +2567,7 @@
         <v>204</v>
       </c>
       <c r="B66" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C66" s="2">
         <v>46752</v>
@@ -2582,7 +2579,7 @@
         <v>14</v>
       </c>
       <c r="F66" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G66">
         <v>136270.62237098379</v>
@@ -2599,7 +2596,7 @@
         <v>204</v>
       </c>
       <c r="B67" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C67" s="2">
         <v>47118</v>
@@ -2611,7 +2608,7 @@
         <v>16</v>
       </c>
       <c r="F67" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G67">
         <v>140358.74104211331</v>
@@ -2628,7 +2625,7 @@
         <v>204</v>
       </c>
       <c r="B68" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C68" s="2">
         <v>47483</v>
@@ -2640,7 +2637,7 @@
         <v>18</v>
       </c>
       <c r="F68" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G68">
         <v>144569.5032733767</v>
@@ -2657,7 +2654,7 @@
         <v>204</v>
       </c>
       <c r="B69" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C69" s="2">
         <v>47848</v>
@@ -2669,7 +2666,7 @@
         <v>20</v>
       </c>
       <c r="F69" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G69">
         <v>148906.58837157799</v>
@@ -2686,7 +2683,7 @@
         <v>205</v>
       </c>
       <c r="B70" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C70" s="2">
         <v>46387</v>
@@ -2715,7 +2712,7 @@
         <v>205</v>
       </c>
       <c r="B71" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C71" s="2">
         <v>46752</v>
@@ -2744,7 +2741,7 @@
         <v>205</v>
       </c>
       <c r="B72" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C72" s="2">
         <v>47118</v>
@@ -2773,7 +2770,7 @@
         <v>205</v>
       </c>
       <c r="B73" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C73" s="2">
         <v>47483</v>
@@ -2802,7 +2799,7 @@
         <v>205</v>
       </c>
       <c r="B74" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C74" s="2">
         <v>47848</v>
@@ -2831,7 +2828,7 @@
         <v>207</v>
       </c>
       <c r="B75" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C75" s="2">
         <v>46387</v>
@@ -2843,7 +2840,7 @@
         <v>12</v>
       </c>
       <c r="F75" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G75">
         <v>293409.4756239889</v>
@@ -2860,7 +2857,7 @@
         <v>207</v>
       </c>
       <c r="B76" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C76" s="2">
         <v>46752</v>
@@ -2872,7 +2869,7 @@
         <v>14</v>
       </c>
       <c r="F76" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G76">
         <v>310591.22318889661</v>
@@ -2889,7 +2886,7 @@
         <v>207</v>
       </c>
       <c r="B77" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C77" s="2">
         <v>47118</v>
@@ -2901,7 +2898,7 @@
         <v>16</v>
       </c>
       <c r="F77" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G77">
         <v>328779.11566018942</v>
@@ -2918,7 +2915,7 @@
         <v>207</v>
       </c>
       <c r="B78" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C78" s="2">
         <v>47483</v>
@@ -2930,7 +2927,7 @@
         <v>18</v>
       </c>
       <c r="F78" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G78">
         <v>348032.07181599637</v>
@@ -2947,7 +2944,7 @@
         <v>207</v>
       </c>
       <c r="B79" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C79" s="2">
         <v>47848</v>
@@ -2959,7 +2956,7 @@
         <v>20</v>
       </c>
       <c r="F79" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G79">
         <v>368412.46065557672</v>
@@ -2976,7 +2973,7 @@
         <v>228</v>
       </c>
       <c r="B80" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C80" s="2">
         <v>46387</v>
@@ -2988,7 +2985,7 @@
         <v>12</v>
       </c>
       <c r="F80" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G80">
         <v>743.69125717621739</v>
@@ -3005,7 +3002,7 @@
         <v>228</v>
       </c>
       <c r="B81" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C81" s="2">
         <v>46752</v>
@@ -3017,7 +3014,7 @@
         <v>14</v>
       </c>
       <c r="F81" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G81">
         <v>845.42962114370084</v>
@@ -3034,7 +3031,7 @@
         <v>228</v>
       </c>
       <c r="B82" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C82" s="2">
         <v>47118</v>
@@ -3046,7 +3043,7 @@
         <v>16</v>
       </c>
       <c r="F82" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G82">
         <v>947.16798511118441</v>
@@ -3063,7 +3060,7 @@
         <v>228</v>
       </c>
       <c r="B83" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C83" s="2">
         <v>47483</v>
@@ -3075,7 +3072,7 @@
         <v>18</v>
       </c>
       <c r="F83" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G83">
         <v>1048.906349078668</v>
@@ -3092,7 +3089,7 @@
         <v>228</v>
       </c>
       <c r="B84" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C84" s="2">
         <v>47848</v>
@@ -3104,7 +3101,7 @@
         <v>20</v>
       </c>
       <c r="F84" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G84">
         <v>1150.644713046152</v>
@@ -3121,7 +3118,7 @@
         <v>228</v>
       </c>
       <c r="B85" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C85" s="2">
         <v>46387</v>
@@ -3133,7 +3130,7 @@
         <v>12</v>
       </c>
       <c r="F85" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G85">
         <v>663.92078647276094</v>
@@ -3150,7 +3147,7 @@
         <v>228</v>
       </c>
       <c r="B86" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C86" s="2">
         <v>46752</v>
@@ -3162,7 +3159,7 @@
         <v>14</v>
       </c>
       <c r="F86" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G86">
         <v>760.60175637119119</v>
@@ -3179,7 +3176,7 @@
         <v>228</v>
       </c>
       <c r="B87" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C87" s="2">
         <v>47118</v>
@@ -3191,7 +3188,7 @@
         <v>16</v>
       </c>
       <c r="F87" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G87">
         <v>870.7081039242845</v>
@@ -3208,7 +3205,7 @@
         <v>228</v>
       </c>
       <c r="B88" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C88" s="2">
         <v>47483</v>
@@ -3220,7 +3217,7 @@
         <v>18</v>
       </c>
       <c r="F88" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G88">
         <v>994.23982913204077</v>
@@ -3237,7 +3234,7 @@
         <v>228</v>
       </c>
       <c r="B89" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C89" s="2">
         <v>47848</v>
@@ -3249,7 +3246,7 @@
         <v>20</v>
       </c>
       <c r="F89" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G89">
         <v>1131.1969319944601</v>
@@ -3266,7 +3263,7 @@
         <v>244</v>
       </c>
       <c r="B90" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C90" s="2">
         <v>46387</v>
@@ -3295,7 +3292,7 @@
         <v>244</v>
       </c>
       <c r="B91" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C91" s="2">
         <v>46752</v>
@@ -3324,7 +3321,7 @@
         <v>244</v>
       </c>
       <c r="B92" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C92" s="2">
         <v>47118</v>
@@ -3353,7 +3350,7 @@
         <v>244</v>
       </c>
       <c r="B93" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C93" s="2">
         <v>47483</v>
@@ -3382,7 +3379,7 @@
         <v>244</v>
       </c>
       <c r="B94" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C94" s="2">
         <v>47848</v>
@@ -3411,7 +3408,7 @@
         <v>245</v>
       </c>
       <c r="B95" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C95" s="2">
         <v>46203</v>
@@ -3423,7 +3420,7 @@
         <v>10</v>
       </c>
       <c r="F95" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G95">
         <v>86.600803392352617</v>
@@ -3440,7 +3437,7 @@
         <v>245</v>
       </c>
       <c r="B96" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C96" s="2">
         <v>46387</v>
@@ -3452,7 +3449,7 @@
         <v>12</v>
       </c>
       <c r="F96" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G96">
         <v>86.701724256657954</v>
@@ -3469,7 +3466,7 @@
         <v>245</v>
       </c>
       <c r="B97" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C97" s="2">
         <v>46568</v>
@@ -3481,7 +3478,7 @@
         <v>13</v>
       </c>
       <c r="F97" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G97">
         <v>86.802762729812784</v>
@@ -3498,7 +3495,7 @@
         <v>245</v>
       </c>
       <c r="B98" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C98" s="2">
         <v>46752</v>
@@ -3510,7 +3507,7 @@
         <v>14</v>
       </c>
       <c r="F98" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G98">
         <v>86.903918948873411</v>
@@ -3527,7 +3524,7 @@
         <v>245</v>
       </c>
       <c r="B99" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C99" s="2">
         <v>46934</v>
@@ -3539,7 +3536,7 @@
         <v>15</v>
       </c>
       <c r="F99" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G99">
         <v>87.005193051055869</v>
@@ -3556,7 +3553,7 @@
         <v>245</v>
       </c>
       <c r="B100" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C100" s="2">
         <v>47118</v>
@@ -3568,7 +3565,7 @@
         <v>16</v>
       </c>
       <c r="F100" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G100">
         <v>87.106585173736121</v>
@@ -3585,7 +3582,7 @@
         <v>245</v>
       </c>
       <c r="B101" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C101" s="2">
         <v>47299</v>
@@ -3597,7 +3594,7 @@
         <v>17</v>
       </c>
       <c r="F101" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G101">
         <v>87.208095454450159</v>
@@ -3614,7 +3611,7 @@
         <v>245</v>
       </c>
       <c r="B102" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C102" s="2">
         <v>47483</v>
@@ -3626,7 +3623,7 @@
         <v>18</v>
       </c>
       <c r="F102" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G102">
         <v>87.309724030894301</v>
@@ -3643,7 +3640,7 @@
         <v>245</v>
       </c>
       <c r="B103" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C103" s="2">
         <v>47664</v>
@@ -3655,7 +3652,7 @@
         <v>19</v>
       </c>
       <c r="F103" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G103">
         <v>87.411471040925349</v>
@@ -3672,7 +3669,7 @@
         <v>245</v>
       </c>
       <c r="B104" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C104" s="2">
         <v>47848</v>
@@ -3684,7 +3681,7 @@
         <v>20</v>
       </c>
       <c r="F104" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G104">
         <v>87.513336622560715</v>
@@ -3701,7 +3698,7 @@
         <v>245</v>
       </c>
       <c r="B105" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C105" s="2">
         <v>46203</v>
@@ -3713,7 +3710,7 @@
         <v>10</v>
       </c>
       <c r="F105" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G105">
         <v>86.53</v>
@@ -3730,7 +3727,7 @@
         <v>245</v>
       </c>
       <c r="B106" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C106" s="2">
         <v>46387</v>
@@ -3742,7 +3739,7 @@
         <v>12</v>
       </c>
       <c r="F106" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G106">
         <v>87.215000000000003</v>
@@ -3759,7 +3756,7 @@
         <v>245</v>
       </c>
       <c r="B107" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C107" s="2">
         <v>46568</v>
@@ -3771,7 +3768,7 @@
         <v>13</v>
       </c>
       <c r="F107" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G107">
         <v>87.9</v>
@@ -3788,7 +3785,7 @@
         <v>245</v>
       </c>
       <c r="B108" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C108" s="2">
         <v>46752</v>
@@ -3800,7 +3797,7 @@
         <v>14</v>
       </c>
       <c r="F108" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G108">
         <v>88.585000000000008</v>
@@ -3817,7 +3814,7 @@
         <v>245</v>
       </c>
       <c r="B109" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C109" s="2">
         <v>46934</v>
@@ -3829,7 +3826,7 @@
         <v>15</v>
       </c>
       <c r="F109" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G109">
         <v>89.27000000000001</v>
@@ -3846,7 +3843,7 @@
         <v>245</v>
       </c>
       <c r="B110" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C110" s="2">
         <v>47118</v>
@@ -3858,7 +3855,7 @@
         <v>16</v>
       </c>
       <c r="F110" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G110">
         <v>89.955000000000013</v>
@@ -3875,7 +3872,7 @@
         <v>245</v>
       </c>
       <c r="B111" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C111" s="2">
         <v>47299</v>
@@ -3887,7 +3884,7 @@
         <v>17</v>
       </c>
       <c r="F111" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G111">
         <v>90.640000000000015</v>
@@ -3904,7 +3901,7 @@
         <v>245</v>
       </c>
       <c r="B112" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C112" s="2">
         <v>47483</v>
@@ -3916,7 +3913,7 @@
         <v>18</v>
       </c>
       <c r="F112" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G112">
         <v>91.325000000000017</v>
@@ -3933,7 +3930,7 @@
         <v>245</v>
       </c>
       <c r="B113" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C113" s="2">
         <v>47664</v>
@@ -3945,7 +3942,7 @@
         <v>19</v>
       </c>
       <c r="F113" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G113">
         <v>92.010000000000019</v>
@@ -3962,7 +3959,7 @@
         <v>245</v>
       </c>
       <c r="B114" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C114" s="2">
         <v>47848</v>
@@ -3974,7 +3971,7 @@
         <v>20</v>
       </c>
       <c r="F114" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G114">
         <v>92.695000000000022</v>
@@ -3991,7 +3988,7 @@
         <v>276</v>
       </c>
       <c r="B115" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C115" s="2">
         <v>46203</v>
@@ -4020,7 +4017,7 @@
         <v>276</v>
       </c>
       <c r="B116" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C116" s="2">
         <v>46387</v>
@@ -4049,7 +4046,7 @@
         <v>276</v>
       </c>
       <c r="B117" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C117" s="2">
         <v>46568</v>
@@ -4078,7 +4075,7 @@
         <v>276</v>
       </c>
       <c r="B118" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C118" s="2">
         <v>46752</v>
@@ -4107,7 +4104,7 @@
         <v>276</v>
       </c>
       <c r="B119" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C119" s="2">
         <v>46934</v>
@@ -4136,7 +4133,7 @@
         <v>276</v>
       </c>
       <c r="B120" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C120" s="2">
         <v>47118</v>
@@ -4165,7 +4162,7 @@
         <v>276</v>
       </c>
       <c r="B121" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C121" s="2">
         <v>47299</v>
@@ -4194,7 +4191,7 @@
         <v>276</v>
       </c>
       <c r="B122" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C122" s="2">
         <v>47483</v>
@@ -4223,7 +4220,7 @@
         <v>276</v>
       </c>
       <c r="B123" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C123" s="2">
         <v>47664</v>
@@ -4252,7 +4249,7 @@
         <v>276</v>
       </c>
       <c r="B124" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C124" s="2">
         <v>47848</v>
@@ -4281,7 +4278,7 @@
         <v>276</v>
       </c>
       <c r="B125" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C125" s="2">
         <v>46203</v>
@@ -4293,7 +4290,7 @@
         <v>10</v>
       </c>
       <c r="F125" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G125">
         <v>82.234038282271925</v>
@@ -4310,7 +4307,7 @@
         <v>276</v>
       </c>
       <c r="B126" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C126" s="2">
         <v>46387</v>
@@ -4322,7 +4319,7 @@
         <v>12</v>
       </c>
       <c r="F126" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G126">
         <v>80.333060729510137</v>
@@ -4339,7 +4336,7 @@
         <v>276</v>
       </c>
       <c r="B127" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C127" s="2">
         <v>46568</v>
@@ -4351,7 +4348,7 @@
         <v>13</v>
       </c>
       <c r="F127" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G127">
         <v>78.476027457384305</v>
@@ -4368,7 +4365,7 @@
         <v>276</v>
       </c>
       <c r="B128" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C128" s="2">
         <v>46752</v>
@@ -4380,7 +4377,7 @@
         <v>14</v>
       </c>
       <c r="F128" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G128">
         <v>76.661922620232403</v>
@@ -4397,7 +4394,7 @@
         <v>276</v>
       </c>
       <c r="B129" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C129" s="2">
         <v>46934</v>
@@ -4409,7 +4406,7 @@
         <v>15</v>
       </c>
       <c r="F129" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G129">
         <v>74.889753855366578</v>
@@ -4426,7 +4423,7 @@
         <v>276</v>
       </c>
       <c r="B130" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C130" s="2">
         <v>47118</v>
@@ -4438,7 +4435,7 @@
         <v>16</v>
       </c>
       <c r="F130" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G130">
         <v>73.158551740224951</v>
@@ -4455,7 +4452,7 @@
         <v>276</v>
       </c>
       <c r="B131" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C131" s="2">
         <v>47299</v>
@@ -4467,7 +4464,7 @@
         <v>17</v>
       </c>
       <c r="F131" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G131">
         <v>71.467369262072097</v>
@@ -4484,7 +4481,7 @@
         <v>276</v>
       </c>
       <c r="B132" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C132" s="2">
         <v>47483</v>
@@ -4496,7 +4493,7 @@
         <v>18</v>
       </c>
       <c r="F132" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G132">
         <v>69.815281299958414</v>
@@ -4513,7 +4510,7 @@
         <v>276</v>
       </c>
       <c r="B133" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C133" s="2">
         <v>47664</v>
@@ -4525,7 +4522,7 @@
         <v>19</v>
       </c>
       <c r="F133" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G133">
         <v>68.201384118654829</v>
@@ -4542,7 +4539,7 @@
         <v>276</v>
       </c>
       <c r="B134" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C134" s="2">
         <v>47848</v>
@@ -4554,7 +4551,7 @@
         <v>20</v>
       </c>
       <c r="F134" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G134">
         <v>66.624794874285968</v>
@@ -4571,7 +4568,7 @@
         <v>277</v>
       </c>
       <c r="B135" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C135" s="2">
         <v>46203</v>
@@ -4608,7 +4605,7 @@
         <v>277</v>
       </c>
       <c r="B136" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C136" s="2">
         <v>46387</v>
@@ -4645,7 +4642,7 @@
         <v>277</v>
       </c>
       <c r="B137" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C137" s="2">
         <v>46568</v>
@@ -4682,7 +4679,7 @@
         <v>277</v>
       </c>
       <c r="B138" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C138" s="2">
         <v>46752</v>
@@ -4719,7 +4716,7 @@
         <v>277</v>
       </c>
       <c r="B139" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C139" s="2">
         <v>46934</v>
@@ -4756,7 +4753,7 @@
         <v>277</v>
       </c>
       <c r="B140" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C140" s="2">
         <v>47118</v>
@@ -4793,7 +4790,7 @@
         <v>277</v>
       </c>
       <c r="B141" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C141" s="2">
         <v>47299</v>
@@ -4830,7 +4827,7 @@
         <v>277</v>
       </c>
       <c r="B142" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C142" s="2">
         <v>47483</v>
@@ -4867,7 +4864,7 @@
         <v>277</v>
       </c>
       <c r="B143" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C143" s="2">
         <v>47664</v>
@@ -4904,7 +4901,7 @@
         <v>277</v>
       </c>
       <c r="B144" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C144" s="2">
         <v>47848</v>
@@ -4941,7 +4938,7 @@
         <v>277</v>
       </c>
       <c r="B145" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C145" s="2">
         <v>46203</v>
@@ -4953,7 +4950,7 @@
         <v>10</v>
       </c>
       <c r="F145" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G145">
         <v>67.888278699901591</v>
@@ -4978,7 +4975,7 @@
         <v>277</v>
       </c>
       <c r="B146" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C146" s="2">
         <v>46387</v>
@@ -4990,7 +4987,7 @@
         <v>12</v>
       </c>
       <c r="F146" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G146">
         <v>66.419057282540876</v>
@@ -5015,7 +5012,7 @@
         <v>277</v>
       </c>
       <c r="B147" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C147" s="2">
         <v>46568</v>
@@ -5027,7 +5024,7 @@
         <v>13</v>
       </c>
       <c r="F147" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G147">
         <v>64.9816323934553</v>
@@ -5052,7 +5049,7 @@
         <v>277</v>
       </c>
       <c r="B148" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C148" s="2">
         <v>46752</v>
@@ -5064,7 +5061,7 @@
         <v>14</v>
       </c>
       <c r="F148" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G148">
         <v>63.57531590000643</v>
@@ -5089,7 +5086,7 @@
         <v>277</v>
       </c>
       <c r="B149" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C149" s="2">
         <v>46934</v>
@@ -5101,7 +5098,7 @@
         <v>15</v>
       </c>
       <c r="F149" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G149">
         <v>62.199434561953034</v>
@@ -5126,7 +5123,7 @@
         <v>277</v>
       </c>
       <c r="B150" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C150" s="2">
         <v>47118</v>
@@ -5138,7 +5135,7 @@
         <v>16</v>
       </c>
       <c r="F150" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G150">
         <v>60.853329709153464</v>
@@ -5163,7 +5160,7 @@
         <v>277</v>
       </c>
       <c r="B151" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C151" s="2">
         <v>47299</v>
@@ -5175,7 +5172,7 @@
         <v>17</v>
       </c>
       <c r="F151" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G151">
         <v>59.536356926243137</v>
@@ -5200,7 +5197,7 @@
         <v>277</v>
       </c>
       <c r="B152" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C152" s="2">
         <v>47483</v>
@@ -5212,7 +5209,7 @@
         <v>18</v>
       </c>
       <c r="F152" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G152">
         <v>58.247885744136177</v>
@@ -5237,7 +5234,7 @@
         <v>277</v>
       </c>
       <c r="B153" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C153" s="2">
         <v>47664</v>
@@ -5249,7 +5246,7 @@
         <v>19</v>
       </c>
       <c r="F153" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G153">
         <v>56.987299338203513</v>
@@ -5274,7 +5271,7 @@
         <v>277</v>
       </c>
       <c r="B154" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C154" s="2">
         <v>47848</v>
@@ -5286,7 +5283,7 @@
         <v>20</v>
       </c>
       <c r="F154" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G154">
         <v>55.753994232982812</v>
@@ -5311,7 +5308,7 @@
         <v>325</v>
       </c>
       <c r="B155" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C155" s="2">
         <v>46387</v>
@@ -5340,7 +5337,7 @@
         <v>325</v>
       </c>
       <c r="B156" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C156" s="2">
         <v>46752</v>
@@ -5369,7 +5366,7 @@
         <v>325</v>
       </c>
       <c r="B157" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C157" s="2">
         <v>47118</v>
@@ -5398,7 +5395,7 @@
         <v>325</v>
       </c>
       <c r="B158" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C158" s="2">
         <v>47483</v>
@@ -5427,7 +5424,7 @@
         <v>325</v>
       </c>
       <c r="B159" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C159" s="2">
         <v>47848</v>
@@ -5456,7 +5453,7 @@
         <v>332</v>
       </c>
       <c r="B160" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C160" s="2">
         <v>46387</v>
@@ -5468,7 +5465,7 @@
         <v>12</v>
       </c>
       <c r="F160" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G160">
         <v>0.71510849492151418</v>
@@ -5485,7 +5482,7 @@
         <v>332</v>
       </c>
       <c r="B161" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C161" s="2">
         <v>46752</v>
@@ -5497,7 +5494,7 @@
         <v>14</v>
       </c>
       <c r="F161" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G161">
         <v>0.57208679593721135</v>
@@ -5514,7 +5511,7 @@
         <v>332</v>
       </c>
       <c r="B162" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C162" s="2">
         <v>47118</v>
@@ -5526,7 +5523,7 @@
         <v>16</v>
       </c>
       <c r="F162" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G162">
         <v>0.45766943674976912</v>
@@ -5543,7 +5540,7 @@
         <v>332</v>
       </c>
       <c r="B163" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C163" s="2">
         <v>47483</v>
@@ -5555,7 +5552,7 @@
         <v>18</v>
       </c>
       <c r="F163" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G163">
         <v>0.3661355493998153</v>
@@ -5572,7 +5569,7 @@
         <v>332</v>
       </c>
       <c r="B164" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C164" s="2">
         <v>47848</v>
@@ -5584,7 +5581,7 @@
         <v>20</v>
       </c>
       <c r="F164" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G164">
         <v>0.29290843951985218</v>
@@ -5601,7 +5598,7 @@
         <v>332</v>
       </c>
       <c r="B165" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C165" s="2">
         <v>46387</v>
@@ -5613,7 +5610,7 @@
         <v>12</v>
       </c>
       <c r="F165" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G165">
         <v>0.72500000000000009</v>
@@ -5630,7 +5627,7 @@
         <v>332</v>
       </c>
       <c r="B166" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C166" s="2">
         <v>46752</v>
@@ -5642,7 +5639,7 @@
         <v>14</v>
       </c>
       <c r="F166" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G166">
         <v>0.58000000000000007</v>
@@ -5659,7 +5656,7 @@
         <v>332</v>
       </c>
       <c r="B167" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C167" s="2">
         <v>47118</v>
@@ -5671,7 +5668,7 @@
         <v>16</v>
       </c>
       <c r="F167" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G167">
         <v>0.46400000000000008</v>
@@ -5688,7 +5685,7 @@
         <v>332</v>
       </c>
       <c r="B168" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C168" s="2">
         <v>47483</v>
@@ -5700,7 +5697,7 @@
         <v>18</v>
       </c>
       <c r="F168" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G168">
         <v>0.37120000000000009</v>
@@ -5717,7 +5714,7 @@
         <v>332</v>
       </c>
       <c r="B169" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C169" s="2">
         <v>47848</v>
@@ -5729,7 +5726,7 @@
         <v>20</v>
       </c>
       <c r="F169" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G169">
         <v>0.29696000000000011</v>
@@ -5746,7 +5743,7 @@
         <v>334</v>
       </c>
       <c r="B170" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C170" s="2">
         <v>46387</v>
@@ -5775,7 +5772,7 @@
         <v>334</v>
       </c>
       <c r="B171" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C171" s="2">
         <v>46752</v>
@@ -5804,7 +5801,7 @@
         <v>334</v>
       </c>
       <c r="B172" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C172" s="2">
         <v>47118</v>
@@ -5833,7 +5830,7 @@
         <v>334</v>
       </c>
       <c r="B173" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C173" s="2">
         <v>47483</v>
@@ -5862,7 +5859,7 @@
         <v>334</v>
       </c>
       <c r="B174" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C174" s="2">
         <v>47848</v>
@@ -5891,7 +5888,7 @@
         <v>334</v>
       </c>
       <c r="B175" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C175" s="2">
         <v>46387</v>
@@ -5903,7 +5900,7 @@
         <v>12</v>
       </c>
       <c r="F175" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G175">
         <v>89.680861034164366</v>
@@ -5920,7 +5917,7 @@
         <v>334</v>
       </c>
       <c r="B176" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C176" s="2">
         <v>46752</v>
@@ -5932,7 +5929,7 @@
         <v>14</v>
       </c>
       <c r="F176" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G176">
         <v>90.58039935364728</v>
@@ -5949,7 +5946,7 @@
         <v>334</v>
       </c>
       <c r="B177" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C177" s="2">
         <v>47118</v>
@@ -5961,7 +5958,7 @@
         <v>16</v>
       </c>
       <c r="F177" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G177">
         <v>91.605034626038787</v>
@@ -5978,7 +5975,7 @@
         <v>334</v>
       </c>
       <c r="B178" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C178" s="2">
         <v>47483</v>
@@ -5990,7 +5987,7 @@
         <v>18</v>
       </c>
       <c r="F178" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G178">
         <v>92.754766851338871</v>
@@ -6007,7 +6004,7 @@
         <v>334</v>
       </c>
       <c r="B179" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C179" s="2">
         <v>47848</v>
@@ -6019,7 +6016,7 @@
         <v>20</v>
       </c>
       <c r="F179" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G179">
         <v>94.029596029547562</v>
@@ -6036,7 +6033,7 @@
         <v>361</v>
       </c>
       <c r="B180" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C180" s="2">
         <v>46752</v>
@@ -6048,7 +6045,7 @@
         <v>14</v>
       </c>
       <c r="F180" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G180">
         <v>4.82</v>
@@ -6065,7 +6062,7 @@
         <v>361</v>
       </c>
       <c r="B181" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C181" s="2">
         <v>47483</v>
@@ -6077,7 +6074,7 @@
         <v>18</v>
       </c>
       <c r="F181" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G181">
         <v>4.8499999999999996</v>
@@ -6094,7 +6091,7 @@
         <v>361</v>
       </c>
       <c r="B182" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C182" s="2">
         <v>48213</v>
@@ -6103,10 +6100,10 @@
         <v>2031</v>
       </c>
       <c r="E182" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F182" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G182">
         <v>4.87</v>
@@ -6123,7 +6120,7 @@
         <v>364</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C183" s="4">
         <v>46387</v>
@@ -6135,7 +6132,7 @@
         <v>12</v>
       </c>
       <c r="F183" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G183" s="3">
         <v>144368.4</v>
@@ -6152,7 +6149,7 @@
         <v>364</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C184" s="4">
         <v>46752</v>
@@ -6164,7 +6161,7 @@
         <v>14</v>
       </c>
       <c r="F184" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G184" s="3">
         <v>158805.24</v>
@@ -6181,7 +6178,7 @@
         <v>364</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C185" s="4">
         <v>47118</v>
@@ -6193,7 +6190,7 @@
         <v>16</v>
       </c>
       <c r="F185" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G185" s="3">
         <v>174685.76400000011</v>
@@ -6210,7 +6207,7 @@
         <v>364</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C186" s="4">
         <v>47483</v>
@@ -6222,7 +6219,7 @@
         <v>18</v>
       </c>
       <c r="F186" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G186" s="3">
         <v>192154.34039999999</v>
@@ -6239,7 +6236,7 @@
         <v>364</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C187" s="4">
         <v>47848</v>
@@ -6251,7 +6248,7 @@
         <v>20</v>
       </c>
       <c r="F187" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G187" s="3">
         <v>211369.7744400001</v>
@@ -6268,7 +6265,7 @@
         <v>367</v>
       </c>
       <c r="B188" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C188" s="4">
         <v>46387</v>
@@ -6280,7 +6277,7 @@
         <v>12</v>
       </c>
       <c r="F188" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G188" s="3">
         <v>5.0095999999999998</v>
@@ -6297,7 +6294,7 @@
         <v>367</v>
       </c>
       <c r="B189" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C189" s="4">
         <v>46752</v>
@@ -6309,7 +6306,7 @@
         <v>14</v>
       </c>
       <c r="F189" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G189" s="3">
         <v>5.0596959999999997</v>
@@ -6326,7 +6323,7 @@
         <v>367</v>
       </c>
       <c r="B190" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C190" s="4">
         <v>47118</v>
@@ -6338,7 +6335,7 @@
         <v>16</v>
       </c>
       <c r="F190" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G190" s="3">
         <v>5.1102929600000007</v>
@@ -6355,7 +6352,7 @@
         <v>367</v>
       </c>
       <c r="B191" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C191" s="4">
         <v>47483</v>
@@ -6367,7 +6364,7 @@
         <v>18</v>
       </c>
       <c r="F191" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G191" s="3">
         <v>5.1613958896000014</v>
@@ -6384,7 +6381,7 @@
         <v>367</v>
       </c>
       <c r="B192" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C192" s="4">
         <v>47848</v>
@@ -6396,7 +6393,7 @@
         <v>20</v>
       </c>
       <c r="F192" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G192" s="3">
         <v>5.213009848496001</v>
@@ -6413,7 +6410,7 @@
         <v>369</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C193" s="4">
         <v>46387</v>
@@ -6425,7 +6422,7 @@
         <v>12</v>
       </c>
       <c r="F193" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G193" s="3">
         <v>73.44</v>
@@ -6442,7 +6439,7 @@
         <v>369</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C194" s="4">
         <v>46752</v>
@@ -6454,7 +6451,7 @@
         <v>14</v>
       </c>
       <c r="F194" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G194" s="3">
         <v>74.908799999999999</v>
@@ -6471,7 +6468,7 @@
         <v>369</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C195" s="4">
         <v>47118</v>
@@ -6483,7 +6480,7 @@
         <v>16</v>
       </c>
       <c r="F195" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G195" s="3">
         <v>76.406976000000014</v>
@@ -6500,7 +6497,7 @@
         <v>369</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C196" s="4">
         <v>47483</v>
@@ -6512,7 +6509,7 @@
         <v>18</v>
       </c>
       <c r="F196" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G196" s="3">
         <v>77.935115519999997</v>
@@ -6529,7 +6526,7 @@
         <v>369</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C197" s="4">
         <v>47848</v>
@@ -6541,7 +6538,7 @@
         <v>20</v>
       </c>
       <c r="F197" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G197" s="3">
         <v>79.493817830400005</v>
@@ -6558,7 +6555,7 @@
         <v>377</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C198" s="4">
         <v>46387</v>
@@ -6570,7 +6567,7 @@
         <v>12</v>
       </c>
       <c r="F198" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G198">
         <v>11828.030016950001</v>
@@ -6587,7 +6584,7 @@
         <v>377</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C199" s="4">
         <v>46752</v>
@@ -6599,7 +6596,7 @@
         <v>14</v>
       </c>
       <c r="F199" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G199">
         <v>13602.2345194925</v>
@@ -6616,7 +6613,7 @@
         <v>377</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C200" s="4">
         <v>47118</v>
@@ -6628,7 +6625,7 @@
         <v>16</v>
       </c>
       <c r="F200" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G200">
         <v>15642.569697416369</v>
@@ -6645,7 +6642,7 @@
         <v>377</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C201" s="4">
         <v>47483</v>
@@ -6657,7 +6654,7 @@
         <v>18</v>
       </c>
       <c r="F201" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G201">
         <v>17988.95515202883</v>
@@ -6674,7 +6671,7 @@
         <v>377</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C202" s="4">
         <v>47848</v>
@@ -6686,7 +6683,7 @@
         <v>20</v>
       </c>
       <c r="F202" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G202">
         <v>20687.298424833149</v>
@@ -6703,7 +6700,7 @@
         <v>424</v>
       </c>
       <c r="B203" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C203" s="2">
         <v>46387</v>
@@ -6732,7 +6729,7 @@
         <v>424</v>
       </c>
       <c r="B204" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C204" s="2">
         <v>46752</v>
@@ -6761,7 +6758,7 @@
         <v>424</v>
       </c>
       <c r="B205" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C205" s="2">
         <v>47118</v>
@@ -6790,7 +6787,7 @@
         <v>424</v>
       </c>
       <c r="B206" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C206" s="2">
         <v>47483</v>
@@ -6819,7 +6816,7 @@
         <v>424</v>
       </c>
       <c r="B207" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C207" s="2">
         <v>47848</v>
@@ -6848,7 +6845,7 @@
         <v>460</v>
       </c>
       <c r="B208" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C208" s="2">
         <v>46387</v>
@@ -6860,7 +6857,7 @@
         <v>12</v>
       </c>
       <c r="F208" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G208">
         <v>92.354399999999998</v>
@@ -6877,7 +6874,7 @@
         <v>460</v>
       </c>
       <c r="B209" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C209" s="2">
         <v>46752</v>
@@ -6889,7 +6886,7 @@
         <v>14</v>
       </c>
       <c r="F209" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G209">
         <v>93.277944000000005</v>
@@ -6906,7 +6903,7 @@
         <v>460</v>
       </c>
       <c r="B210" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C210" s="2">
         <v>47118</v>
@@ -6918,7 +6915,7 @@
         <v>16</v>
       </c>
       <c r="F210" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G210">
         <v>94.21072344000001</v>
@@ -6935,7 +6932,7 @@
         <v>460</v>
       </c>
       <c r="B211" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C211" s="2">
         <v>47483</v>
@@ -6947,7 +6944,7 @@
         <v>18</v>
       </c>
       <c r="F211" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G211">
         <v>95.152830674399993</v>
@@ -6964,7 +6961,7 @@
         <v>460</v>
       </c>
       <c r="B212" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C212" s="2">
         <v>47848</v>
@@ -6976,7 +6973,7 @@
         <v>20</v>
       </c>
       <c r="F212" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G212">
         <v>96.104358981144017</v>
@@ -6993,7 +6990,7 @@
         <v>77</v>
       </c>
       <c r="B213" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C213" s="2">
         <v>46387</v>
@@ -7005,7 +7002,7 @@
         <v>12</v>
       </c>
       <c r="F213" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G213">
         <v>95.596500000000006</v>
@@ -7022,7 +7019,7 @@
         <v>77</v>
       </c>
       <c r="B214" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C214" s="2">
         <v>46752</v>
@@ -7034,7 +7031,7 @@
         <v>14</v>
       </c>
       <c r="F214" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G214">
         <v>96.552465000000012</v>
@@ -7051,7 +7048,7 @@
         <v>77</v>
       </c>
       <c r="B215" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C215" s="2">
         <v>47118</v>
@@ -7063,7 +7060,7 @@
         <v>16</v>
       </c>
       <c r="F215" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G215">
         <v>97.517989650000018</v>
@@ -7080,7 +7077,7 @@
         <v>77</v>
       </c>
       <c r="B216" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C216" s="2">
         <v>47483</v>
@@ -7092,7 +7089,7 @@
         <v>18</v>
       </c>
       <c r="F216" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G216">
         <v>98.493169546500013</v>
@@ -7109,7 +7106,7 @@
         <v>77</v>
       </c>
       <c r="B217" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C217" s="2">
         <v>47848</v>
@@ -7121,7 +7118,7 @@
         <v>20</v>
       </c>
       <c r="F217" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G217">
         <v>99.478101241965021</v>
@@ -7138,7 +7135,7 @@
         <v>98</v>
       </c>
       <c r="B218" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C218" s="2">
         <v>46387</v>
@@ -7150,7 +7147,7 @@
         <v>12</v>
       </c>
       <c r="F218" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G218">
         <v>3</v>
@@ -7167,7 +7164,7 @@
         <v>98</v>
       </c>
       <c r="B219" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C219" s="2">
         <v>46752</v>
@@ -7179,7 +7176,7 @@
         <v>14</v>
       </c>
       <c r="F219" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G219">
         <v>3</v>
@@ -7196,7 +7193,7 @@
         <v>98</v>
       </c>
       <c r="B220" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C220" s="2">
         <v>47118</v>
@@ -7208,7 +7205,7 @@
         <v>16</v>
       </c>
       <c r="F220" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G220">
         <v>3</v>
@@ -7225,7 +7222,7 @@
         <v>98</v>
       </c>
       <c r="B221" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C221" s="2">
         <v>47483</v>
@@ -7237,7 +7234,7 @@
         <v>18</v>
       </c>
       <c r="F221" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G221">
         <v>4</v>
@@ -7254,7 +7251,7 @@
         <v>98</v>
       </c>
       <c r="B222" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C222" s="2">
         <v>47848</v>
@@ -7266,7 +7263,7 @@
         <v>20</v>
       </c>
       <c r="F222" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G222">
         <v>4</v>
@@ -7283,7 +7280,7 @@
         <v>386.1</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C223" s="4">
         <v>46387</v>
@@ -7295,7 +7292,7 @@
         <v>12</v>
       </c>
       <c r="F223" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G223">
         <v>5021.3256906738234</v>
@@ -7312,7 +7309,7 @@
         <v>386.1</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C224" s="4">
         <v>46752</v>
@@ -7324,7 +7321,7 @@
         <v>14</v>
       </c>
       <c r="F224" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G224">
         <v>5914.5712658767779</v>
@@ -7341,7 +7338,7 @@
         <v>386.1</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C225" s="4">
         <v>47118</v>
@@ -7353,7 +7350,7 @@
         <v>16</v>
       </c>
       <c r="F225" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G225">
         <v>6920.7335283964458</v>
@@ -7370,7 +7367,7 @@
         <v>386.1</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C226" s="4">
         <v>47483</v>
@@ -7382,7 +7379,7 @@
         <v>18</v>
       </c>
       <c r="F226" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G226">
         <v>8039.8124782328259</v>
@@ -7399,7 +7396,7 @@
         <v>386.1</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C227" s="4">
         <v>47848</v>
@@ -7411,7 +7408,7 @@
         <v>20</v>
       </c>
       <c r="F227" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G227">
         <v>9271.8081153859184</v>
@@ -7428,7 +7425,7 @@
         <v>386.2</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C228" s="4">
         <v>46387</v>
@@ -7440,7 +7437,7 @@
         <v>12</v>
       </c>
       <c r="F228" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G228">
         <v>8322.3104068060129</v>
@@ -7457,7 +7454,7 @@
         <v>386.2</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C229" s="4">
         <v>46752</v>
@@ -7469,7 +7466,7 @@
         <v>14</v>
       </c>
       <c r="F229" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G229">
         <v>9300.7150739219178</v>
@@ -7486,7 +7483,7 @@
         <v>386.2</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C230" s="4">
         <v>47118</v>
@@ -7498,7 +7495,7 @@
         <v>16</v>
       </c>
       <c r="F230" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G230">
         <v>10394.14497391682</v>
@@ -7515,7 +7512,7 @@
         <v>386.2</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C231" s="4">
         <v>47483</v>
@@ -7527,7 +7524,7 @@
         <v>18</v>
       </c>
       <c r="F231" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G231">
         <v>11616.122941098</v>
@@ -7544,7 +7541,7 @@
         <v>386.2</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C232" s="4">
         <v>47848</v>
@@ -7556,7 +7553,7 @@
         <v>20</v>
       </c>
       <c r="F232" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G232">
         <v>12981.76160918564</v>
@@ -7573,7 +7570,7 @@
         <v>386.3</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C233" s="4">
         <v>46387</v>
@@ -7585,7 +7582,7 @@
         <v>12</v>
       </c>
       <c r="F233" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G233">
         <v>5646.493414116343</v>
@@ -7602,7 +7599,7 @@
         <v>386.3</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C234" s="4">
         <v>46752</v>
@@ -7614,7 +7611,7 @@
         <v>14</v>
       </c>
       <c r="F234" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G234">
         <v>6374.4716673772846</v>
@@ -7631,7 +7628,7 @@
         <v>386.3</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C235" s="4">
         <v>47118</v>
@@ -7643,7 +7640,7 @@
         <v>16</v>
       </c>
       <c r="F235" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G235">
         <v>7227.2111180454294</v>
@@ -7660,7 +7657,7 @@
         <v>386.3</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C236" s="4">
         <v>47483</v>
@@ -7672,7 +7669,7 @@
         <v>18</v>
       </c>
       <c r="F236" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G236">
         <v>8204.7117661207758</v>
@@ -7689,7 +7686,7 @@
         <v>386.3</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C237" s="4">
         <v>47848</v>
@@ -7701,7 +7698,7 @@
         <v>20</v>
       </c>
       <c r="F237" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G237">
         <v>9306.9736116033237</v>
@@ -7718,7 +7715,7 @@
         <v>379</v>
       </c>
       <c r="B238" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C238" s="2">
         <v>46203</v>
@@ -7747,7 +7744,7 @@
         <v>274</v>
       </c>
       <c r="B239" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C239" s="2">
         <v>46203</v>
@@ -7776,7 +7773,7 @@
         <v>379</v>
       </c>
       <c r="B240" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C240" s="2">
         <v>46387</v>
@@ -7805,7 +7802,7 @@
         <v>274</v>
       </c>
       <c r="B241" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C241" s="2">
         <v>46387</v>
@@ -7834,7 +7831,7 @@
         <v>379</v>
       </c>
       <c r="B242" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C242" s="2">
         <v>46568</v>
@@ -7863,7 +7860,7 @@
         <v>274</v>
       </c>
       <c r="B243" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C243" s="2">
         <v>46568</v>
@@ -7892,7 +7889,7 @@
         <v>379</v>
       </c>
       <c r="B244" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C244" s="2">
         <v>46752</v>
@@ -7921,7 +7918,7 @@
         <v>274</v>
       </c>
       <c r="B245" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C245" s="2">
         <v>46752</v>
@@ -7950,7 +7947,7 @@
         <v>379</v>
       </c>
       <c r="B246" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C246" s="2">
         <v>46934</v>
@@ -7979,7 +7976,7 @@
         <v>274</v>
       </c>
       <c r="B247" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C247" s="2">
         <v>46934</v>
@@ -8008,7 +8005,7 @@
         <v>379</v>
       </c>
       <c r="B248" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C248" s="2">
         <v>47118</v>
@@ -8037,7 +8034,7 @@
         <v>274</v>
       </c>
       <c r="B249" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C249" s="2">
         <v>47118</v>
@@ -8066,7 +8063,7 @@
         <v>379</v>
       </c>
       <c r="B250" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C250" s="2">
         <v>47299</v>
@@ -8095,7 +8092,7 @@
         <v>274</v>
       </c>
       <c r="B251" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C251" s="2">
         <v>47299</v>
@@ -8124,7 +8121,7 @@
         <v>379</v>
       </c>
       <c r="B252" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C252" s="2">
         <v>47483</v>
@@ -8153,7 +8150,7 @@
         <v>274</v>
       </c>
       <c r="B253" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C253" s="2">
         <v>47483</v>
@@ -8182,7 +8179,7 @@
         <v>379</v>
       </c>
       <c r="B254" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C254" s="2">
         <v>47664</v>
@@ -8211,7 +8208,7 @@
         <v>274</v>
       </c>
       <c r="B255" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C255" s="2">
         <v>47664</v>
@@ -8240,7 +8237,7 @@
         <v>379</v>
       </c>
       <c r="B256" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C256" s="2">
         <v>47848</v>
@@ -8269,7 +8266,7 @@
         <v>274</v>
       </c>
       <c r="B257" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C257" s="2">
         <v>47848</v>
@@ -8600,7 +8597,7 @@
         <v>10</v>
       </c>
       <c r="F268" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G268">
         <v>57181.535034514192</v>
@@ -8629,7 +8626,7 @@
         <v>12</v>
       </c>
       <c r="F269" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G269">
         <v>57651.823600328113</v>
@@ -8658,7 +8655,7 @@
         <v>13</v>
       </c>
       <c r="F270" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G270">
         <v>58122.112166142033</v>
@@ -8687,7 +8684,7 @@
         <v>14</v>
       </c>
       <c r="F271" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G271">
         <v>58592.400731955953</v>
@@ -8716,7 +8713,7 @@
         <v>15</v>
       </c>
       <c r="F272" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G272">
         <v>59062.689297769859</v>
@@ -8745,7 +8742,7 @@
         <v>16</v>
       </c>
       <c r="F273" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G273">
         <v>59532.977863583779</v>
@@ -8774,7 +8771,7 @@
         <v>17</v>
       </c>
       <c r="F274" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G274">
         <v>60003.2664293977</v>
@@ -8803,7 +8800,7 @@
         <v>18</v>
       </c>
       <c r="F275" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G275">
         <v>60473.55499521162</v>
@@ -8832,7 +8829,7 @@
         <v>19</v>
       </c>
       <c r="F276" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G276">
         <v>60943.84356102554</v>
@@ -8861,7 +8858,7 @@
         <v>20</v>
       </c>
       <c r="F277" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G277">
         <v>61414.13212683946</v>
@@ -8878,7 +8875,7 @@
         <v>379</v>
       </c>
       <c r="B278" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C278" s="2">
         <v>46203</v>
@@ -8890,7 +8887,7 @@
         <v>10</v>
       </c>
       <c r="F278" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G278">
         <v>12825.87818782696</v>
@@ -8907,7 +8904,7 @@
         <v>274</v>
       </c>
       <c r="B279" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C279" s="2">
         <v>46203</v>
@@ -8919,7 +8916,7 @@
         <v>10</v>
       </c>
       <c r="F279" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G279">
         <v>44355.842350450519</v>
@@ -8936,7 +8933,7 @@
         <v>379</v>
       </c>
       <c r="B280" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C280" s="2">
         <v>46387</v>
@@ -8948,7 +8945,7 @@
         <v>12</v>
       </c>
       <c r="F280" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G280">
         <v>12931.36440561766</v>
@@ -8965,7 +8962,7 @@
         <v>274</v>
       </c>
       <c r="B281" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C281" s="2">
         <v>46387</v>
@@ -8977,7 +8974,7 @@
         <v>12</v>
       </c>
       <c r="F281" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G281">
         <v>44720.646224146301</v>
@@ -8994,7 +8991,7 @@
         <v>379</v>
       </c>
       <c r="B282" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C282" s="2">
         <v>46568</v>
@@ -9006,7 +9003,7 @@
         <v>13</v>
       </c>
       <c r="F282" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G282">
         <v>13036.850623408351</v>
@@ -9023,7 +9020,7 @@
         <v>274</v>
       </c>
       <c r="B283" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C283" s="2">
         <v>46568</v>
@@ -9035,7 +9032,7 @@
         <v>13</v>
       </c>
       <c r="F283" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G283">
         <v>45085.450097842077</v>
@@ -9052,7 +9049,7 @@
         <v>379</v>
       </c>
       <c r="B284" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C284" s="2">
         <v>46752</v>
@@ -9064,7 +9061,7 @@
         <v>14</v>
       </c>
       <c r="F284" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G284">
         <v>13142.33684119905</v>
@@ -9081,7 +9078,7 @@
         <v>274</v>
       </c>
       <c r="B285" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C285" s="2">
         <v>46752</v>
@@ -9093,7 +9090,7 @@
         <v>14</v>
       </c>
       <c r="F285" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G285">
         <v>45450.253971537859</v>
@@ -9110,7 +9107,7 @@
         <v>379</v>
       </c>
       <c r="B286" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C286" s="2">
         <v>46934</v>
@@ -9122,7 +9119,7 @@
         <v>15</v>
       </c>
       <c r="F286" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G286">
         <v>13247.82305898975</v>
@@ -9139,7 +9136,7 @@
         <v>274</v>
       </c>
       <c r="B287" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C287" s="2">
         <v>46934</v>
@@ -9151,7 +9148,7 @@
         <v>15</v>
       </c>
       <c r="F287" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G287">
         <v>45815.057845233627</v>
@@ -9168,7 +9165,7 @@
         <v>379</v>
       </c>
       <c r="B288" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C288" s="2">
         <v>47118</v>
@@ -9180,7 +9177,7 @@
         <v>16</v>
       </c>
       <c r="F288" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G288">
         <v>13353.30927678045</v>
@@ -9197,7 +9194,7 @@
         <v>274</v>
       </c>
       <c r="B289" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C289" s="2">
         <v>47118</v>
@@ -9209,7 +9206,7 @@
         <v>16</v>
       </c>
       <c r="F289" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G289">
         <v>46179.861718929409</v>
@@ -9226,7 +9223,7 @@
         <v>379</v>
       </c>
       <c r="B290" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C290" s="2">
         <v>47299</v>
@@ -9238,7 +9235,7 @@
         <v>17</v>
       </c>
       <c r="F290" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G290">
         <v>13458.795494571141</v>
@@ -9255,7 +9252,7 @@
         <v>274</v>
       </c>
       <c r="B291" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C291" s="2">
         <v>47299</v>
@@ -9267,7 +9264,7 @@
         <v>17</v>
       </c>
       <c r="F291" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G291">
         <v>46544.665592625191</v>
@@ -9284,7 +9281,7 @@
         <v>379</v>
       </c>
       <c r="B292" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C292" s="2">
         <v>47483</v>
@@ -9296,7 +9293,7 @@
         <v>18</v>
       </c>
       <c r="F292" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G292">
         <v>13564.281712361841</v>
@@ -9313,7 +9310,7 @@
         <v>274</v>
       </c>
       <c r="B293" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C293" s="2">
         <v>47483</v>
@@ -9325,7 +9322,7 @@
         <v>18</v>
       </c>
       <c r="F293" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G293">
         <v>46909.469466320967</v>
@@ -9342,7 +9339,7 @@
         <v>379</v>
       </c>
       <c r="B294" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C294" s="2">
         <v>47664</v>
@@ -9354,7 +9351,7 @@
         <v>19</v>
       </c>
       <c r="F294" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G294">
         <v>13669.76793015254</v>
@@ -9371,7 +9368,7 @@
         <v>274</v>
       </c>
       <c r="B295" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C295" s="2">
         <v>47664</v>
@@ -9383,7 +9380,7 @@
         <v>19</v>
       </c>
       <c r="F295" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G295">
         <v>47274.273340016749</v>
@@ -9400,7 +9397,7 @@
         <v>379</v>
       </c>
       <c r="B296" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C296" s="2">
         <v>47848</v>
@@ -9412,7 +9409,7 @@
         <v>20</v>
       </c>
       <c r="F296" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G296">
         <v>13775.25414794324</v>
@@ -9429,7 +9426,7 @@
         <v>274</v>
       </c>
       <c r="B297" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C297" s="2">
         <v>47848</v>
@@ -9441,7 +9438,7 @@
         <v>20</v>
       </c>
       <c r="F297" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G297">
         <v>47639.077213712531</v>
@@ -9458,7 +9455,7 @@
         <v>14.1</v>
       </c>
       <c r="B298" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C298" s="2">
         <v>46203</v>
@@ -9470,7 +9467,7 @@
         <v>10</v>
       </c>
       <c r="F298" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G298">
         <v>8922.1224131696708</v>
@@ -9487,7 +9484,7 @@
         <v>14.2</v>
       </c>
       <c r="B299" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C299" s="2">
         <v>46203</v>
@@ -9499,7 +9496,7 @@
         <v>10</v>
       </c>
       <c r="F299" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G299">
         <v>48259.41262134452</v>
@@ -9516,7 +9513,7 @@
         <v>14.1</v>
       </c>
       <c r="B300" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C300" s="2">
         <v>46387</v>
@@ -9528,7 +9525,7 @@
         <v>12</v>
       </c>
       <c r="F300" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G300">
         <v>8995.5022577501495</v>
@@ -9545,7 +9542,7 @@
         <v>14.2</v>
       </c>
       <c r="B301" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C301" s="2">
         <v>46387</v>
@@ -9557,7 +9554,7 @@
         <v>12</v>
       </c>
       <c r="F301" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G301">
         <v>48656.321342577961</v>
@@ -9574,7 +9571,7 @@
         <v>14.1</v>
       </c>
       <c r="B302" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C302" s="2">
         <v>46568</v>
@@ -9586,7 +9583,7 @@
         <v>13</v>
       </c>
       <c r="F302" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G302">
         <v>9068.8821023306264</v>
@@ -9603,7 +9600,7 @@
         <v>14.2</v>
       </c>
       <c r="B303" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C303" s="2">
         <v>46568</v>
@@ -9615,7 +9612,7 @@
         <v>13</v>
       </c>
       <c r="F303" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G303">
         <v>49053.23006381141</v>
@@ -9632,7 +9629,7 @@
         <v>14.1</v>
       </c>
       <c r="B304" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C304" s="2">
         <v>46752</v>
@@ -9644,7 +9641,7 @@
         <v>14</v>
       </c>
       <c r="F304" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G304">
         <v>9142.261946911105</v>
@@ -9661,7 +9658,7 @@
         <v>14.2</v>
       </c>
       <c r="B305" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C305" s="2">
         <v>46752</v>
@@ -9673,7 +9670,7 @@
         <v>14</v>
       </c>
       <c r="F305" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G305">
         <v>49450.138785044852</v>
@@ -9690,7 +9687,7 @@
         <v>14.1</v>
       </c>
       <c r="B306" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C306" s="2">
         <v>46934</v>
@@ -9702,7 +9699,7 @@
         <v>15</v>
       </c>
       <c r="F306" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G306">
         <v>9215.6417914915819</v>
@@ -9719,7 +9716,7 @@
         <v>14.2</v>
       </c>
       <c r="B307" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C307" s="2">
         <v>46934</v>
@@ -9731,7 +9728,7 @@
         <v>15</v>
       </c>
       <c r="F307" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G307">
         <v>49847.047506278293</v>
@@ -9748,7 +9745,7 @@
         <v>14.1</v>
       </c>
       <c r="B308" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C308" s="2">
         <v>47118</v>
@@ -9760,7 +9757,7 @@
         <v>16</v>
       </c>
       <c r="F308" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G308">
         <v>9289.0216360720588</v>
@@ -9777,7 +9774,7 @@
         <v>14.2</v>
       </c>
       <c r="B309" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C309" s="2">
         <v>47118</v>
@@ -9789,7 +9786,7 @@
         <v>16</v>
       </c>
       <c r="F309" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G309">
         <v>50243.956227511728</v>
@@ -9806,7 +9803,7 @@
         <v>14.1</v>
       </c>
       <c r="B310" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C310" s="2">
         <v>47299</v>
@@ -9818,7 +9815,7 @@
         <v>17</v>
       </c>
       <c r="F310" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G310">
         <v>9362.4014806525374</v>
@@ -9835,7 +9832,7 @@
         <v>14.2</v>
       </c>
       <c r="B311" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C311" s="2">
         <v>47299</v>
@@ -9847,7 +9844,7 @@
         <v>17</v>
       </c>
       <c r="F311" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G311">
         <v>50640.864948745169</v>
@@ -9864,7 +9861,7 @@
         <v>14.1</v>
       </c>
       <c r="B312" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C312" s="2">
         <v>47483</v>
@@ -9876,7 +9873,7 @@
         <v>18</v>
       </c>
       <c r="F312" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G312">
         <v>9435.7813252330143</v>
@@ -9893,7 +9890,7 @@
         <v>14.2</v>
       </c>
       <c r="B313" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C313" s="2">
         <v>47483</v>
@@ -9905,7 +9902,7 @@
         <v>18</v>
       </c>
       <c r="F313" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G313">
         <v>51037.773669978611</v>
@@ -9922,7 +9919,7 @@
         <v>14.1</v>
       </c>
       <c r="B314" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C314" s="2">
         <v>47664</v>
@@ -9934,7 +9931,7 @@
         <v>19</v>
       </c>
       <c r="F314" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G314">
         <v>9509.161169813493</v>
@@ -9951,7 +9948,7 @@
         <v>14.2</v>
       </c>
       <c r="B315" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C315" s="2">
         <v>47664</v>
@@ -9963,7 +9960,7 @@
         <v>19</v>
       </c>
       <c r="F315" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G315">
         <v>51434.682391212053</v>
@@ -9980,7 +9977,7 @@
         <v>14.1</v>
       </c>
       <c r="B316" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C316" s="2">
         <v>47848</v>
@@ -9992,7 +9989,7 @@
         <v>20</v>
       </c>
       <c r="F316" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G316">
         <v>9582.5410143939698</v>
@@ -10009,7 +10006,7 @@
         <v>14.2</v>
       </c>
       <c r="B317" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C317" s="2">
         <v>47848</v>
@@ -10021,7 +10018,7 @@
         <v>20</v>
       </c>
       <c r="F317" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G317">
         <v>51831.591112445501</v>
@@ -10038,7 +10035,7 @@
         <v>14.1</v>
       </c>
       <c r="B318" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C318" s="2">
         <v>46203</v>
@@ -10067,7 +10064,7 @@
         <v>14.2</v>
       </c>
       <c r="B319" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C319" s="2">
         <v>46203</v>
@@ -10096,7 +10093,7 @@
         <v>14.1</v>
       </c>
       <c r="B320" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C320" s="2">
         <v>46387</v>
@@ -10125,7 +10122,7 @@
         <v>14.2</v>
       </c>
       <c r="B321" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C321" s="2">
         <v>46387</v>
@@ -10154,7 +10151,7 @@
         <v>14.1</v>
       </c>
       <c r="B322" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C322" s="2">
         <v>46568</v>
@@ -10183,7 +10180,7 @@
         <v>14.2</v>
       </c>
       <c r="B323" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C323" s="2">
         <v>46568</v>
@@ -10212,7 +10209,7 @@
         <v>14.1</v>
       </c>
       <c r="B324" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C324" s="2">
         <v>46752</v>
@@ -10241,7 +10238,7 @@
         <v>14.2</v>
       </c>
       <c r="B325" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C325" s="2">
         <v>46752</v>
@@ -10270,7 +10267,7 @@
         <v>14.1</v>
       </c>
       <c r="B326" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C326" s="2">
         <v>46934</v>
@@ -10299,7 +10296,7 @@
         <v>14.2</v>
       </c>
       <c r="B327" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C327" s="2">
         <v>46934</v>
@@ -10328,7 +10325,7 @@
         <v>14.1</v>
       </c>
       <c r="B328" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C328" s="2">
         <v>47118</v>
@@ -10357,7 +10354,7 @@
         <v>14.2</v>
       </c>
       <c r="B329" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C329" s="2">
         <v>47118</v>
@@ -10386,7 +10383,7 @@
         <v>14.1</v>
       </c>
       <c r="B330" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C330" s="2">
         <v>47299</v>
@@ -10415,7 +10412,7 @@
         <v>14.2</v>
       </c>
       <c r="B331" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C331" s="2">
         <v>47299</v>
@@ -10444,7 +10441,7 @@
         <v>14.1</v>
       </c>
       <c r="B332" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C332" s="2">
         <v>47483</v>
@@ -10473,7 +10470,7 @@
         <v>14.2</v>
       </c>
       <c r="B333" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C333" s="2">
         <v>47483</v>
@@ -10502,7 +10499,7 @@
         <v>14.1</v>
       </c>
       <c r="B334" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C334" s="2">
         <v>47664</v>
@@ -10531,7 +10528,7 @@
         <v>14.2</v>
       </c>
       <c r="B335" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C335" s="2">
         <v>47664</v>
@@ -10560,7 +10557,7 @@
         <v>14.1</v>
       </c>
       <c r="B336" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C336" s="2">
         <v>47848</v>
@@ -10589,7 +10586,7 @@
         <v>14.2</v>
       </c>
       <c r="B337" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C337" s="2">
         <v>47848</v>
@@ -10618,7 +10615,7 @@
         <v>14.3</v>
       </c>
       <c r="B338" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C338" s="2">
         <v>46203</v>
@@ -10630,7 +10627,7 @@
         <v>10</v>
       </c>
       <c r="F338" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G338">
         <v>53184.163304725829</v>
@@ -10647,7 +10644,7 @@
         <v>14.4</v>
       </c>
       <c r="B339" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C339" s="2">
         <v>46203</v>
@@ -10659,7 +10656,7 @@
         <v>10</v>
       </c>
       <c r="F339" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G339">
         <v>3997.37172978836</v>
@@ -10676,7 +10673,7 @@
         <v>14.3</v>
       </c>
       <c r="B340" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C340" s="2">
         <v>46387</v>
@@ -10688,7 +10685,7 @@
         <v>12</v>
       </c>
       <c r="F340" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G340">
         <v>53621.575554493087</v>
@@ -10705,7 +10702,7 @@
         <v>14.4</v>
       </c>
       <c r="B341" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C341" s="2">
         <v>46387</v>
@@ -10717,7 +10714,7 @@
         <v>12</v>
       </c>
       <c r="F341" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G341">
         <v>4030.2480458350101</v>
@@ -10734,7 +10731,7 @@
         <v>14.3</v>
       </c>
       <c r="B342" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C342" s="2">
         <v>46568</v>
@@ -10746,7 +10743,7 @@
         <v>13</v>
       </c>
       <c r="F342" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G342">
         <v>54058.987804260367</v>
@@ -10763,7 +10760,7 @@
         <v>14.4</v>
       </c>
       <c r="B343" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C343" s="2">
         <v>46568</v>
@@ -10775,7 +10772,7 @@
         <v>13</v>
       </c>
       <c r="F343" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G343">
         <v>4063.1243618816602</v>
@@ -10792,7 +10789,7 @@
         <v>14.3</v>
       </c>
       <c r="B344" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C344" s="2">
         <v>46752</v>
@@ -10804,7 +10801,7 @@
         <v>14</v>
       </c>
       <c r="F344" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G344">
         <v>54496.400054027639</v>
@@ -10821,7 +10818,7 @@
         <v>14.4</v>
       </c>
       <c r="B345" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C345" s="2">
         <v>46752</v>
@@ -10833,7 +10830,7 @@
         <v>14</v>
       </c>
       <c r="F345" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G345">
         <v>4096.0006779283094</v>
@@ -10850,7 +10847,7 @@
         <v>14.3</v>
       </c>
       <c r="B346" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C346" s="2">
         <v>46934</v>
@@ -10862,7 +10859,7 @@
         <v>15</v>
       </c>
       <c r="F346" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G346">
         <v>54933.812303794897</v>
@@ -10879,7 +10876,7 @@
         <v>14.4</v>
       </c>
       <c r="B347" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C347" s="2">
         <v>46934</v>
@@ -10891,7 +10888,7 @@
         <v>15</v>
       </c>
       <c r="F347" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G347">
         <v>4128.8769939749591</v>
@@ -10908,7 +10905,7 @@
         <v>14.3</v>
       </c>
       <c r="B348" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C348" s="2">
         <v>47118</v>
@@ -10920,7 +10917,7 @@
         <v>16</v>
       </c>
       <c r="F348" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G348">
         <v>55371.22455356217</v>
@@ -10937,7 +10934,7 @@
         <v>14.4</v>
       </c>
       <c r="B349" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C349" s="2">
         <v>47118</v>
@@ -10949,7 +10946,7 @@
         <v>16</v>
       </c>
       <c r="F349" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G349">
         <v>4161.7533100216096</v>
@@ -10966,7 +10963,7 @@
         <v>14.3</v>
       </c>
       <c r="B350" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C350" s="2">
         <v>47299</v>
@@ -10978,7 +10975,7 @@
         <v>17</v>
       </c>
       <c r="F350" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G350">
         <v>55808.636803329442</v>
@@ -10995,7 +10992,7 @@
         <v>14.4</v>
       </c>
       <c r="B351" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C351" s="2">
         <v>47299</v>
@@ -11007,7 +11004,7 @@
         <v>17</v>
       </c>
       <c r="F351" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G351">
         <v>4194.6296260682593</v>
@@ -11024,7 +11021,7 @@
         <v>14.3</v>
       </c>
       <c r="B352" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C352" s="2">
         <v>47483</v>
@@ -11036,7 +11033,7 @@
         <v>18</v>
       </c>
       <c r="F352" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G352">
         <v>56246.049053096707</v>
@@ -11053,7 +11050,7 @@
         <v>14.4</v>
       </c>
       <c r="B353" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C353" s="2">
         <v>47483</v>
@@ -11065,7 +11062,7 @@
         <v>18</v>
       </c>
       <c r="F353" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G353">
         <v>4227.505942114909</v>
@@ -11082,7 +11079,7 @@
         <v>14.3</v>
       </c>
       <c r="B354" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C354" s="2">
         <v>47664</v>
@@ -11094,7 +11091,7 @@
         <v>19</v>
       </c>
       <c r="F354" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G354">
         <v>56683.461302863987</v>
@@ -11111,7 +11108,7 @@
         <v>14.4</v>
       </c>
       <c r="B355" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C355" s="2">
         <v>47664</v>
@@ -11123,7 +11120,7 @@
         <v>19</v>
       </c>
       <c r="F355" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G355">
         <v>4260.3822581615595</v>
@@ -11140,7 +11137,7 @@
         <v>14.3</v>
       </c>
       <c r="B356" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C356" s="2">
         <v>47848</v>
@@ -11152,7 +11149,7 @@
         <v>20</v>
       </c>
       <c r="F356" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G356">
         <v>57120.873552631252</v>
@@ -11169,7 +11166,7 @@
         <v>14.4</v>
       </c>
       <c r="B357" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C357" s="2">
         <v>47848</v>
@@ -11181,7 +11178,7 @@
         <v>20</v>
       </c>
       <c r="F357" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G357">
         <v>4293.2585742082092</v>
@@ -11198,7 +11195,7 @@
         <v>14.3</v>
       </c>
       <c r="B358" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C358" s="2">
         <v>46203</v>
@@ -11227,7 +11224,7 @@
         <v>14.4</v>
       </c>
       <c r="B359" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C359" s="2">
         <v>46203</v>
@@ -11256,7 +11253,7 @@
         <v>14.3</v>
       </c>
       <c r="B360" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C360" s="2">
         <v>46387</v>
@@ -11285,7 +11282,7 @@
         <v>14.4</v>
       </c>
       <c r="B361" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C361" s="2">
         <v>46387</v>
@@ -11314,7 +11311,7 @@
         <v>14.3</v>
       </c>
       <c r="B362" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C362" s="2">
         <v>46568</v>
@@ -11343,7 +11340,7 @@
         <v>14.4</v>
       </c>
       <c r="B363" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C363" s="2">
         <v>46568</v>
@@ -11372,7 +11369,7 @@
         <v>14.3</v>
       </c>
       <c r="B364" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C364" s="2">
         <v>46752</v>
@@ -11401,7 +11398,7 @@
         <v>14.4</v>
       </c>
       <c r="B365" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C365" s="2">
         <v>46752</v>
@@ -11430,7 +11427,7 @@
         <v>14.3</v>
       </c>
       <c r="B366" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C366" s="2">
         <v>46934</v>
@@ -11459,7 +11456,7 @@
         <v>14.4</v>
       </c>
       <c r="B367" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C367" s="2">
         <v>46934</v>
@@ -11488,7 +11485,7 @@
         <v>14.3</v>
       </c>
       <c r="B368" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C368" s="2">
         <v>47118</v>
@@ -11517,7 +11514,7 @@
         <v>14.4</v>
       </c>
       <c r="B369" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C369" s="2">
         <v>47118</v>
@@ -11546,7 +11543,7 @@
         <v>14.3</v>
       </c>
       <c r="B370" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C370" s="2">
         <v>47299</v>
@@ -11575,7 +11572,7 @@
         <v>14.4</v>
       </c>
       <c r="B371" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C371" s="2">
         <v>47299</v>
@@ -11604,7 +11601,7 @@
         <v>14.3</v>
       </c>
       <c r="B372" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C372" s="2">
         <v>47483</v>
@@ -11633,7 +11630,7 @@
         <v>14.4</v>
       </c>
       <c r="B373" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C373" s="2">
         <v>47483</v>
@@ -11662,7 +11659,7 @@
         <v>14.3</v>
       </c>
       <c r="B374" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C374" s="2">
         <v>47664</v>
@@ -11691,7 +11688,7 @@
         <v>14.4</v>
       </c>
       <c r="B375" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C375" s="2">
         <v>47664</v>
@@ -11720,7 +11717,7 @@
         <v>14.3</v>
       </c>
       <c r="B376" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C376" s="2">
         <v>47848</v>
@@ -11749,7 +11746,7 @@
         <v>14.4</v>
       </c>
       <c r="B377" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C377" s="2">
         <v>47848</v>
@@ -11790,7 +11787,7 @@
         <v>12</v>
       </c>
       <c r="F378" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G378">
         <v>90.299279905306122</v>
@@ -11819,7 +11816,7 @@
         <v>14</v>
       </c>
       <c r="F379" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G379">
         <v>91.205371802411875</v>
@@ -11848,7 +11845,7 @@
         <v>16</v>
       </c>
       <c r="F380" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G380">
         <v>92.111463699517614</v>
@@ -11877,7 +11874,7 @@
         <v>18</v>
       </c>
       <c r="F381" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G381">
         <v>93.017555596623353</v>
@@ -11906,7 +11903,7 @@
         <v>20</v>
       </c>
       <c r="F382" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G382">
         <v>93.923647493729106</v>
@@ -11935,7 +11932,7 @@
         <v>12</v>
       </c>
       <c r="F383" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G383">
         <v>90.703306625415365</v>
@@ -11964,7 +11961,7 @@
         <v>14</v>
       </c>
       <c r="F384" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G384">
         <v>91.412109253156885</v>
@@ -11993,7 +11990,7 @@
         <v>16</v>
       </c>
       <c r="F385" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G385">
         <v>92.126450831833978</v>
@@ -12022,7 +12019,7 @@
         <v>18</v>
       </c>
       <c r="F386" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G386">
         <v>92.846374645678779</v>
@@ -12051,7 +12048,7 @@
         <v>20</v>
       </c>
       <c r="F387" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G387">
         <v>93.571924317168822</v>
@@ -12068,7 +12065,7 @@
         <v>323</v>
       </c>
       <c r="B388" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C388" s="2">
         <v>46387</v>
@@ -12080,7 +12077,7 @@
         <v>12</v>
       </c>
       <c r="F388" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G388">
         <v>1</v>
@@ -12097,7 +12094,7 @@
         <v>323</v>
       </c>
       <c r="B389" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C389" s="2">
         <v>46752</v>
@@ -12109,7 +12106,7 @@
         <v>14</v>
       </c>
       <c r="F389" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G389">
         <v>1</v>
@@ -12126,7 +12123,7 @@
         <v>323</v>
       </c>
       <c r="B390" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C390" s="2">
         <v>47118</v>
@@ -12138,7 +12135,7 @@
         <v>16</v>
       </c>
       <c r="F390" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G390">
         <v>2</v>
@@ -12155,7 +12152,7 @@
         <v>323</v>
       </c>
       <c r="B391" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C391" s="2">
         <v>47483</v>
@@ -12167,7 +12164,7 @@
         <v>18</v>
       </c>
       <c r="F391" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G391">
         <v>2</v>
@@ -12184,7 +12181,7 @@
         <v>323</v>
       </c>
       <c r="B392" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C392" s="2">
         <v>47848</v>
@@ -12196,7 +12193,7 @@
         <v>20</v>
       </c>
       <c r="F392" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G392">
         <v>2</v>
@@ -12213,7 +12210,7 @@
         <v>376</v>
       </c>
       <c r="B393" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C393" s="2">
         <v>46387</v>
@@ -12242,7 +12239,7 @@
         <v>376</v>
       </c>
       <c r="B394" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C394" s="2">
         <v>46752</v>
@@ -12271,7 +12268,7 @@
         <v>376</v>
       </c>
       <c r="B395" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C395" s="2">
         <v>47118</v>
@@ -12300,7 +12297,7 @@
         <v>376</v>
       </c>
       <c r="B396" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C396" s="2">
         <v>47483</v>
@@ -12329,7 +12326,7 @@
         <v>376</v>
       </c>
       <c r="B397" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C397" s="2">
         <v>47848</v>
@@ -12358,7 +12355,7 @@
         <v>376</v>
       </c>
       <c r="B398" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C398" s="2">
         <v>46387</v>
@@ -12370,7 +12367,7 @@
         <v>12</v>
       </c>
       <c r="F398" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G398">
         <v>33364.614089900009</v>
@@ -12387,7 +12384,7 @@
         <v>376</v>
       </c>
       <c r="B399" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C399" s="2">
         <v>46752</v>
@@ -12399,7 +12396,7 @@
         <v>14</v>
       </c>
       <c r="F399" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G399">
         <v>36512.365153479492</v>
@@ -12416,7 +12413,7 @@
         <v>376</v>
       </c>
       <c r="B400" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C400" s="2">
         <v>47118</v>
@@ -12428,7 +12425,7 @@
         <v>16</v>
       </c>
       <c r="F400" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G400">
         <v>40167.943620047838</v>
@@ -12445,7 +12442,7 @@
         <v>376</v>
       </c>
       <c r="B401" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C401" s="2">
         <v>47483</v>
@@ -12457,7 +12454,7 @@
         <v>18</v>
       </c>
       <c r="F401" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G401">
         <v>44331.349489605069</v>
@@ -12474,7 +12471,7 @@
         <v>376</v>
       </c>
       <c r="B402" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C402" s="2">
         <v>47848</v>
@@ -12486,7 +12483,7 @@
         <v>20</v>
       </c>
       <c r="F402" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G402">
         <v>49002.582762151171</v>
@@ -12503,7 +12500,7 @@
         <v>466</v>
       </c>
       <c r="B403" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C403" s="2">
         <v>46387</v>
@@ -12532,7 +12529,7 @@
         <v>466</v>
       </c>
       <c r="B404" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C404" s="2">
         <v>46752</v>
@@ -12561,7 +12558,7 @@
         <v>466</v>
       </c>
       <c r="B405" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C405" s="2">
         <v>47118</v>
@@ -12590,7 +12587,7 @@
         <v>466</v>
       </c>
       <c r="B406" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C406" s="2">
         <v>47483</v>
@@ -12619,7 +12616,7 @@
         <v>466</v>
       </c>
       <c r="B407" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C407" s="2">
         <v>47848</v>
@@ -12648,7 +12645,7 @@
         <v>466</v>
       </c>
       <c r="B408" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C408" s="2">
         <v>46387</v>
@@ -12660,7 +12657,7 @@
         <v>12</v>
       </c>
       <c r="F408" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G408">
         <v>56.235212373037847</v>
@@ -12677,7 +12674,7 @@
         <v>466</v>
       </c>
       <c r="B409" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C409" s="2">
         <v>46752</v>
@@ -12689,7 +12686,7 @@
         <v>14</v>
       </c>
       <c r="F409" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G409">
         <v>57.922268744228987</v>
@@ -12706,7 +12703,7 @@
         <v>466</v>
       </c>
       <c r="B410" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C410" s="2">
         <v>47118</v>
@@ -12718,7 +12715,7 @@
         <v>16</v>
       </c>
       <c r="F410" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G410">
         <v>59.659936806555862</v>
@@ -12735,7 +12732,7 @@
         <v>466</v>
       </c>
       <c r="B411" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C411" s="2">
         <v>47483</v>
@@ -12747,7 +12744,7 @@
         <v>18</v>
       </c>
       <c r="F411" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G411">
         <v>61.449734910752539</v>
@@ -12764,7 +12761,7 @@
         <v>466</v>
       </c>
       <c r="B412" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C412" s="2">
         <v>47848</v>
@@ -12776,7 +12773,7 @@
         <v>20</v>
       </c>
       <c r="F412" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G412">
         <v>63.293226958075117</v>
@@ -12793,7 +12790,7 @@
         <v>96</v>
       </c>
       <c r="B413" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C413" s="2">
         <v>46387</v>
@@ -12805,7 +12802,7 @@
         <v>12</v>
       </c>
       <c r="F413" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G413">
         <v>846.88288415165562</v>
@@ -12822,7 +12819,7 @@
         <v>96</v>
       </c>
       <c r="B414" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C414" s="2">
         <v>46752</v>
@@ -12834,7 +12831,7 @@
         <v>14</v>
       </c>
       <c r="F414" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G414">
         <v>914.63351488378817</v>
@@ -12851,7 +12848,7 @@
         <v>96</v>
       </c>
       <c r="B415" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C415" s="2">
         <v>47118</v>
@@ -12863,7 +12860,7 @@
         <v>16</v>
       </c>
       <c r="F415" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G415">
         <v>987.8041960744913</v>
@@ -12880,7 +12877,7 @@
         <v>96</v>
       </c>
       <c r="B416" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C416" s="2">
         <v>47483</v>
@@ -12892,7 +12889,7 @@
         <v>18</v>
       </c>
       <c r="F416" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G416">
         <v>1066.8285317604509</v>
@@ -12909,7 +12906,7 @@
         <v>96</v>
       </c>
       <c r="B417" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C417" s="2">
         <v>47848</v>
@@ -12921,7 +12918,7 @@
         <v>20</v>
       </c>
       <c r="F417" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G417">
         <v>1152.1748143012869</v>
@@ -12938,7 +12935,7 @@
         <v>385</v>
       </c>
       <c r="B418" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C418" s="2">
         <v>46387</v>
@@ -12967,7 +12964,7 @@
         <v>385</v>
       </c>
       <c r="B419" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C419" s="2">
         <v>46752</v>
@@ -12996,7 +12993,7 @@
         <v>385</v>
       </c>
       <c r="B420" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C420" s="2">
         <v>47118</v>
@@ -13025,7 +13022,7 @@
         <v>385</v>
       </c>
       <c r="B421" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C421" s="2">
         <v>47483</v>
@@ -13054,7 +13051,7 @@
         <v>385</v>
       </c>
       <c r="B422" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C422" s="2">
         <v>47848</v>
@@ -13083,7 +13080,7 @@
         <v>385</v>
       </c>
       <c r="B423" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C423" s="2">
         <v>46387</v>
@@ -13095,7 +13092,7 @@
         <v>12</v>
       </c>
       <c r="F423" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G423">
         <v>17370.137802849709</v>
@@ -13112,7 +13109,7 @@
         <v>385</v>
       </c>
       <c r="B424" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C424" s="2">
         <v>46752</v>
@@ -13124,7 +13121,7 @@
         <v>14</v>
       </c>
       <c r="F424" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G424">
         <v>18957.986444229311</v>
@@ -13141,7 +13138,7 @@
         <v>385</v>
       </c>
       <c r="B425" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C425" s="2">
         <v>47118</v>
@@ -13153,7 +13150,7 @@
         <v>16</v>
       </c>
       <c r="F425" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G425">
         <v>20767.420529644682</v>
@@ -13170,7 +13167,7 @@
         <v>385</v>
       </c>
       <c r="B426" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C426" s="2">
         <v>47483</v>
@@ -13182,7 +13179,7 @@
         <v>18</v>
       </c>
       <c r="F426" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G426">
         <v>22798.440059095828</v>
@@ -13199,7 +13196,7 @@
         <v>385</v>
       </c>
       <c r="B427" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C427" s="2">
         <v>47848</v>
@@ -13211,7 +13208,7 @@
         <v>20</v>
       </c>
       <c r="F427" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G427">
         <v>25051.045032582759</v>
@@ -13228,7 +13225,7 @@
         <v>386.1</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C428" s="4">
         <v>46387</v>
@@ -13257,7 +13254,7 @@
         <v>386.1</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C429" s="4">
         <v>46752</v>
@@ -13286,7 +13283,7 @@
         <v>386.1</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C430" s="4">
         <v>47118</v>
@@ -13315,7 +13312,7 @@
         <v>386.1</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C431" s="4">
         <v>47483</v>
@@ -13344,7 +13341,7 @@
         <v>386.1</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C432" s="4">
         <v>47848</v>
@@ -13373,7 +13370,7 @@
         <v>386.2</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C433" s="4">
         <v>46387</v>
@@ -13402,7 +13399,7 @@
         <v>386.2</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C434" s="4">
         <v>46752</v>
@@ -13431,7 +13428,7 @@
         <v>386.2</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C435" s="4">
         <v>47118</v>
@@ -13460,7 +13457,7 @@
         <v>386.2</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C436" s="4">
         <v>47483</v>
@@ -13489,7 +13486,7 @@
         <v>386.2</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C437" s="4">
         <v>47848</v>
@@ -13518,7 +13515,7 @@
         <v>386.3</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C438" s="4">
         <v>46387</v>
@@ -13547,7 +13544,7 @@
         <v>386.3</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C439" s="4">
         <v>46752</v>
@@ -13576,7 +13573,7 @@
         <v>386.3</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C440" s="4">
         <v>47118</v>
@@ -13605,7 +13602,7 @@
         <v>386.3</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C441" s="4">
         <v>47483</v>
@@ -13634,7 +13631,7 @@
         <v>386.3</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C442" s="4">
         <v>47848</v>
@@ -13660,10 +13657,10 @@
     </row>
     <row r="443" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B443" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C443" s="2">
         <v>46387</v>
@@ -13675,7 +13672,7 @@
         <v>12</v>
       </c>
       <c r="F443" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G443">
         <v>15.7</v>
@@ -13689,10 +13686,10 @@
     </row>
     <row r="444" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B444" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C444" s="2">
         <v>46752</v>
@@ -13704,7 +13701,7 @@
         <v>14</v>
       </c>
       <c r="F444" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G444">
         <v>16.3</v>
@@ -13718,10 +13715,10 @@
     </row>
     <row r="445" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B445" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C445" s="2">
         <v>47118</v>
@@ -13733,7 +13730,7 @@
         <v>16</v>
       </c>
       <c r="F445" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G445">
         <v>16.8</v>
@@ -13747,10 +13744,10 @@
     </row>
     <row r="446" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B446" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C446" s="2">
         <v>47483</v>
@@ -13762,7 +13759,7 @@
         <v>18</v>
       </c>
       <c r="F446" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G446">
         <v>17.399999999999999</v>
@@ -13776,10 +13773,10 @@
     </row>
     <row r="447" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B447" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C447" s="2">
         <v>47848</v>
@@ -13791,7 +13788,7 @@
         <v>20</v>
       </c>
       <c r="F447" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G447">
         <v>18</v>
@@ -13805,10 +13802,10 @@
     </row>
     <row r="448" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B448" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C448" s="2">
         <v>46387</v>
@@ -13834,10 +13831,10 @@
     </row>
     <row r="449" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B449" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C449" s="2">
         <v>46752</v>
@@ -13863,10 +13860,10 @@
     </row>
     <row r="450" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B450" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C450" s="2">
         <v>47118</v>
@@ -13892,10 +13889,10 @@
     </row>
     <row r="451" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B451" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C451" s="2">
         <v>47483</v>
@@ -13921,10 +13918,10 @@
     </row>
     <row r="452" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B452" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C452" s="2">
         <v>47848</v>
@@ -13950,10 +13947,10 @@
     </row>
     <row r="453" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B453" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C453" s="2">
         <v>46387</v>
@@ -13979,10 +13976,10 @@
     </row>
     <row r="454" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B454" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C454" s="2">
         <v>46752</v>
@@ -14008,10 +14005,10 @@
     </row>
     <row r="455" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B455" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C455" s="2">
         <v>47118</v>
@@ -14037,10 +14034,10 @@
     </row>
     <row r="456" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B456" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C456" s="2">
         <v>47483</v>
@@ -14066,10 +14063,10 @@
     </row>
     <row r="457" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B457" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C457" s="2">
         <v>47848</v>
@@ -14098,7 +14095,7 @@
         <v>332</v>
       </c>
       <c r="B458" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C458" s="2">
         <v>46387</v>
@@ -14110,7 +14107,7 @@
         <v>12</v>
       </c>
       <c r="F458" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G458">
         <v>0.76500000000000001</v>
@@ -14127,7 +14124,7 @@
         <v>332</v>
       </c>
       <c r="B459" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C459" s="2">
         <v>46752</v>
@@ -14139,7 +14136,7 @@
         <v>14</v>
       </c>
       <c r="F459" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G459">
         <v>0.6885</v>
@@ -14156,7 +14153,7 @@
         <v>332</v>
       </c>
       <c r="B460" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C460" s="2">
         <v>47118</v>
@@ -14168,7 +14165,7 @@
         <v>16</v>
       </c>
       <c r="F460" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G460">
         <v>0.61965000000000003</v>
@@ -14185,7 +14182,7 @@
         <v>332</v>
       </c>
       <c r="B461" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C461" s="2">
         <v>47483</v>
@@ -14197,7 +14194,7 @@
         <v>18</v>
       </c>
       <c r="F461" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G461">
         <v>0.55768499999999999</v>
@@ -14214,7 +14211,7 @@
         <v>332</v>
       </c>
       <c r="B462" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C462" s="2">
         <v>47848</v>
@@ -14226,7 +14223,7 @@
         <v>20</v>
       </c>
       <c r="F462" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G462">
         <v>0.5019165000000001</v>

--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="852" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41D3913D-FFF1-4C41-B037-E0442A58B53E}"/>
+  <xr:revisionPtr revIDLastSave="855" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6FCFA14-45E3-4F79-9999-B1D040A3F42F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -668,6 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K462"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -703,7 +704,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>109</v>
       </c>
@@ -732,7 +733,7 @@
         <v>96.466210501716631</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>109</v>
       </c>
@@ -761,7 +762,7 @@
         <v>98.817673270209056</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>109</v>
       </c>
@@ -790,7 +791,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>109</v>
       </c>
@@ -819,7 +820,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>109</v>
       </c>
@@ -848,7 +849,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>148</v>
       </c>
@@ -877,7 +878,7 @@
         <v>6.4632000000000014</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>148</v>
       </c>
@@ -906,7 +907,7 @@
         <v>6.6767605714285727</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>148</v>
       </c>
@@ -935,7 +936,7 @@
         <v>6.8921245714285728</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>148</v>
       </c>
@@ -964,7 +965,7 @@
         <v>7.1092920000000008</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>148</v>
       </c>
@@ -993,7 +994,7 @@
         <v>7.3282628571428594</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>148</v>
       </c>
@@ -1022,7 +1023,7 @@
         <v>7.5490371428571432</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>148</v>
       </c>
@@ -1051,7 +1052,7 @@
         <v>7.7716148571428576</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>148</v>
       </c>
@@ -1080,7 +1081,7 @@
         <v>7.9959960000000017</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>148</v>
       </c>
@@ -1109,7 +1110,7 @@
         <v>8.2221805714285736</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>148</v>
       </c>
@@ -1138,7 +1139,7 @@
         <v>8.4501685714285717</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>148</v>
       </c>
@@ -1167,7 +1168,7 @@
         <v>6.1899902761070864</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>148</v>
       </c>
@@ -1196,7 +1197,7 @@
         <v>6.3279819822962171</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>148</v>
       </c>
@@ -1225,7 +1226,7 @@
         <v>6.4686394813710644</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>148</v>
       </c>
@@ -1254,7 +1255,7 @@
         <v>6.6119865461157588</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>148</v>
       </c>
@@ -1283,7 +1284,7 @@
         <v>6.7580469493144291</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>148</v>
       </c>
@@ -1312,7 +1313,7 @@
         <v>6.906844463751205</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>148</v>
       </c>
@@ -1341,7 +1342,7 @@
         <v>7.0584028622102162</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>148</v>
       </c>
@@ -1370,7 +1371,7 @@
         <v>7.2127459174755941</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>148</v>
       </c>
@@ -1399,7 +1400,7 @@
         <v>7.3698974023314676</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>148</v>
       </c>
@@ -1428,7 +1429,7 @@
         <v>7.5298810895619628</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>148</v>
       </c>
@@ -1457,7 +1458,7 @@
         <v>6.4272000000000009</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>148</v>
       </c>
@@ -1486,7 +1487,7 @@
         <v>6.6531160800000002</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>148</v>
       </c>
@@ -1515,7 +1516,7 @@
         <v>6.8868026448000004</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>148</v>
       </c>
@@ -1544,7 +1545,7 @@
         <v>7.1285225990160006</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>148</v>
       </c>
@@ -1573,7 +1574,7 @@
         <v>7.3785476281046396</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>148</v>
       </c>
@@ -1602,7 +1603,7 @@
         <v>7.6371584885994839</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>148</v>
       </c>
@@ -1631,7 +1632,7 @@
         <v>7.9046453078587247</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>148</v>
       </c>
@@ -1660,7 +1661,7 @@
         <v>8.1813078936337824</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>148</v>
       </c>
@@ -1689,7 +1690,7 @@
         <v>8.4674560537782675</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>148</v>
       </c>
@@ -1718,7 +1719,7 @@
         <v>8.7634099264271512</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>202</v>
       </c>
@@ -1748,7 +1749,7 @@
         <v>86.460524321264955</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>202</v>
       </c>
@@ -1778,7 +1779,7 @@
         <v>87.89444169204053</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>202</v>
       </c>
@@ -1808,7 +1809,7 @@
         <v>89.352140077821005</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>193</v>
       </c>
@@ -1837,7 +1838,7 @@
         <v>97.708742857142852</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>193</v>
       </c>
@@ -1866,7 +1867,7 @@
         <v>98.622035714285715</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>193</v>
       </c>
@@ -1895,7 +1896,7 @@
         <v>98.785214285714289</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>193</v>
       </c>
@@ -1924,7 +1925,7 @@
         <v>98.948392857142849</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>193</v>
       </c>
@@ -1953,7 +1954,7 @@
         <v>99.111571428571423</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>193</v>
       </c>
@@ -1982,7 +1983,7 @@
         <v>99.274749999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>193</v>
       </c>
@@ -2011,7 +2012,7 @@
         <v>99.437928571428571</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>193</v>
       </c>
@@ -2040,7 +2041,7 @@
         <v>99.601107142857131</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>193</v>
       </c>
@@ -2069,7 +2070,7 @@
         <v>99.764285714285705</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>193</v>
       </c>
@@ -2098,7 +2099,7 @@
         <v>99.927464285714279</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>200</v>
       </c>
@@ -2127,7 +2128,7 @@
         <v>90.92222000000001</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>200</v>
       </c>
@@ -2156,7 +2157,7 @@
         <v>91.911683266000011</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>200</v>
       </c>
@@ -2185,7 +2186,7 @@
         <v>92.91184357532002</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>200</v>
       </c>
@@ -2214,7 +2215,7 @@
         <v>93.922815922499808</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>200</v>
       </c>
@@ -2243,7 +2244,7 @@
         <v>94.944716532265687</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>203</v>
       </c>
@@ -2272,7 +2273,7 @@
         <v>361906.34571078792</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>203</v>
       </c>
@@ -2301,7 +2302,7 @@
         <v>387019.50024189468</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>203</v>
       </c>
@@ -2330,7 +2331,7 @@
         <v>412231.55552550871</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>203</v>
       </c>
@@ -2359,7 +2360,7 @@
         <v>437542.51156162989</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>203</v>
       </c>
@@ -2388,7 +2389,7 @@
         <v>462952.36835025827</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>203</v>
       </c>
@@ -2417,7 +2418,7 @@
         <v>344656.92064585851</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>203</v>
       </c>
@@ -2446,7 +2447,7 @@
         <v>364402.73401411739</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>203</v>
       </c>
@@ -2475,7 +2476,7 @@
         <v>384225.81483198522</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>203</v>
       </c>
@@ -2504,7 +2505,7 @@
         <v>404126.16309946158</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>203</v>
       </c>
@@ -2533,7 +2534,7 @@
         <v>424103.77881654678</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>204</v>
       </c>
@@ -2562,7 +2563,7 @@
         <v>158761.89014095199</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>204</v>
       </c>
@@ -2591,7 +2592,7 @@
         <v>164342.37057940639</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>204</v>
       </c>
@@ -2620,7 +2621,7 @@
         <v>170114.7941430413</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>204</v>
       </c>
@@ -2649,7 +2650,7 @@
         <v>176085.65498697289</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>204</v>
       </c>
@@ -2678,7 +2679,7 @@
         <v>182261.6641668115</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>205</v>
       </c>
@@ -2707,7 +2708,7 @@
         <v>7026</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>205</v>
       </c>
@@ -2736,7 +2737,7 @@
         <v>7500.1430549519973</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>205</v>
       </c>
@@ -2765,7 +2766,7 @@
         <v>7861.0280628179989</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>205</v>
       </c>
@@ -2794,7 +2795,7 @@
         <v>8225.1167425979966</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>205</v>
       </c>
@@ -2823,7 +2824,7 @@
         <v>8592.4090942919956</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>207</v>
       </c>
@@ -2852,7 +2853,7 @@
         <v>272575.96766625863</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>207</v>
       </c>
@@ -2881,7 +2882,7 @@
         <v>287876.12222860788</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>207</v>
       </c>
@@ -2910,7 +2911,7 @@
         <v>304033.49472771061</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>207</v>
       </c>
@@ -2939,7 +2940,7 @@
         <v>321096.01419443771</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>207</v>
       </c>
@@ -2968,7 +2969,7 @@
         <v>339114.28347773122</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>228</v>
       </c>
@@ -2997,7 +2998,7 @@
         <v>892.42950861146085</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>228</v>
       </c>
@@ -3026,7 +3027,7 @@
         <v>1019.5881230993029</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>228</v>
       </c>
@@ -3055,7 +3056,7 @@
         <v>1147.967597954756</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>228</v>
       </c>
@@ -3084,7 +3085,7 @@
         <v>1277.5679331778181</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>228</v>
       </c>
@@ -3113,7 +3114,7 @@
         <v>1408.3891287684901</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>228</v>
       </c>
@@ -3142,7 +3143,7 @@
         <v>796.70494376731313</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>228</v>
       </c>
@@ -3171,7 +3172,7 @@
         <v>917.28571818365663</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>228</v>
       </c>
@@ -3200,7 +3201,7 @@
         <v>1055.298221956233</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>228</v>
       </c>
@@ -3229,7 +3230,7 @@
         <v>1210.984111882826</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>228</v>
       </c>
@@ -3258,7 +3259,7 @@
         <v>1384.585044761219</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>244</v>
       </c>
@@ -3287,7 +3288,7 @@
         <v>19.733333333333331</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>244</v>
       </c>
@@ -3316,7 +3317,7 @@
         <v>19.196888888888889</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>244</v>
       </c>
@@ -3345,7 +3346,7 @@
         <v>18.66577777777778</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>244</v>
       </c>
@@ -3374,7 +3375,7 @@
         <v>18.14</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>244</v>
       </c>
@@ -3403,7 +3404,7 @@
         <v>17.61955555555555</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>245</v>
       </c>
@@ -3432,7 +3433,7 @@
         <v>89.198827494123194</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>245</v>
       </c>
@@ -3461,7 +3462,7 @@
         <v>89.380807536188684</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>245</v>
       </c>
@@ -3490,7 +3491,7 @@
         <v>89.563090584620838</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>245</v>
       </c>
@@ -3519,7 +3520,7 @@
         <v>89.745677098501574</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>245</v>
       </c>
@@ -3548,7 +3549,7 @@
         <v>89.928567537571354</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>245</v>
       </c>
@@ -3577,7 +3578,7 @@
         <v>90.11176236223001</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>245</v>
       </c>
@@ -3606,7 +3607,7 @@
         <v>90.295262033537696</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>245</v>
       </c>
@@ -3635,7 +3636,7 @@
         <v>90.479067013215754</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>245</v>
       </c>
@@ -3664,7 +3665,7 @@
         <v>90.663177763647781</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>245</v>
       </c>
@@ -3693,7 +3694,7 @@
         <v>90.847594747880279</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>245</v>
       </c>
@@ -3722,7 +3723,7 @@
         <v>89.125900000000001</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>245</v>
       </c>
@@ -3751,7 +3752,7 @@
         <v>89.909943499999997</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>245</v>
       </c>
@@ -3780,7 +3781,7 @@
         <v>90.695220000000006</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>245</v>
       </c>
@@ -3809,7 +3810,7 @@
         <v>91.481729500000014</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>245</v>
       </c>
@@ -3838,7 +3839,7 @@
         <v>92.269472000000007</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>245</v>
       </c>
@@ -3867,7 +3868,7 @@
         <v>93.058447500000014</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>245</v>
       </c>
@@ -3896,7 +3897,7 @@
         <v>93.84865600000002</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>245</v>
       </c>
@@ -3925,7 +3926,7 @@
         <v>94.640097500000024</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>245</v>
       </c>
@@ -3954,7 +3955,7 @@
         <v>95.432772000000014</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>245</v>
       </c>
@@ -3983,7 +3984,7 @@
         <v>96.226679500000017</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>276</v>
       </c>
@@ -4012,7 +4013,7 @@
         <v>64.626946951668998</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>276</v>
       </c>
@@ -4041,7 +4042,7 @@
         <v>61.797659797529029</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>276</v>
       </c>
@@ -4070,7 +4071,7 @@
         <v>58.996085245839843</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>276</v>
       </c>
@@ -4099,7 +4100,7 @@
         <v>56.222223296601427</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>276</v>
       </c>
@@ -4128,7 +4129,7 @@
         <v>53.476073949813816</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>276</v>
       </c>
@@ -4157,7 +4158,7 @@
         <v>50.757637205477003</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>276</v>
       </c>
@@ -4186,7 +4187,7 @@
         <v>48.06691306359096</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>276</v>
       </c>
@@ -4215,7 +4216,7 @@
         <v>45.403901524155707</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>276</v>
       </c>
@@ -4244,7 +4245,7 @@
         <v>42.768602587171237</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>276</v>
       </c>
@@ -4273,7 +4274,7 @@
         <v>40.16101625263758</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>276</v>
       </c>
@@ -4302,7 +4303,7 @@
         <v>69.3338001487799</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>276</v>
       </c>
@@ -4331,7 +4332,7 @@
         <v>67.352972385300021</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>276</v>
       </c>
@@ -4360,7 +4361,7 @@
         <v>65.426674283148913</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>276</v>
       </c>
@@ -4389,7 +4390,7 @@
         <v>63.553443269459287</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>276</v>
       </c>
@@ -4418,7 +4419,7 @@
         <v>61.731855251410558</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>276</v>
       </c>
@@ -4447,7 +4448,7 @@
         <v>59.960523618738179</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>276</v>
       </c>
@@ -4476,7 +4477,7 @@
         <v>58.238098271797057</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>276</v>
       </c>
@@ -4505,7 +4506,7 @@
         <v>56.563264674531062</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>276</v>
       </c>
@@ -4534,7 +4535,7 @@
         <v>54.934742931716322</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>276</v>
       </c>
@@ -4563,7 +4564,7 @@
         <v>53.351286889862124</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>277</v>
       </c>
@@ -4600,7 +4601,7 @@
         <v>70.81935</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>277</v>
       </c>
@@ -4637,7 +4638,7 @@
         <v>69.115200000000002</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>277</v>
       </c>
@@ -4674,7 +4675,7 @@
         <v>67.411050000000003</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>277</v>
       </c>
@@ -4711,7 +4712,7 @@
         <v>65.706900000000005</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>277</v>
       </c>
@@ -4748,7 +4749,7 @@
         <v>64.002750000000006</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>277</v>
       </c>
@@ -4785,7 +4786,7 @@
         <v>62.298599999999986</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>277</v>
       </c>
@@ -4822,7 +4823,7 @@
         <v>60.594450000000009</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>277</v>
       </c>
@@ -4859,7 +4860,7 @@
         <v>58.890299999999996</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>277</v>
       </c>
@@ -4896,7 +4897,7 @@
         <v>57.186149999999991</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>277</v>
       </c>
@@ -4933,7 +4934,7 @@
         <v>55.481999999999992</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>277</v>
       </c>
@@ -4970,7 +4971,7 @@
         <v>71.282692634896677</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>277</v>
       </c>
@@ -5007,7 +5008,7 @@
         <v>69.740010146667927</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>277</v>
       </c>
@@ -5044,7 +5045,7 @@
         <v>68.230714013128065</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>277</v>
       </c>
@@ -5081,7 +5082,7 @@
         <v>66.754081695006761</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>277</v>
       </c>
@@ -5118,7 +5119,7 @@
         <v>65.309406290050688</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>277</v>
       </c>
@@ -5155,7 +5156,7 @@
         <v>63.895996194611136</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>277</v>
       </c>
@@ -5192,7 +5193,7 @@
         <v>62.513174772555296</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>277</v>
       </c>
@@ -5229,7 +5230,7 @@
         <v>61.160280031342985</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>277</v>
       </c>
@@ -5266,7 +5267,7 @@
         <v>59.836664305113693</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>277</v>
       </c>
@@ -5303,7 +5304,7 @@
         <v>58.541693944631952</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>325</v>
       </c>
@@ -5332,7 +5333,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>325</v>
       </c>
@@ -5361,7 +5362,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>325</v>
       </c>
@@ -5390,7 +5391,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>325</v>
       </c>
@@ -5419,7 +5420,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>325</v>
       </c>
@@ -5448,7 +5449,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>332</v>
       </c>
@@ -5477,7 +5478,7 @@
         <v>0.64546314585089737</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>332</v>
       </c>
@@ -5506,7 +5507,7 @@
         <v>0.51469902830302305</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>332</v>
       </c>
@@ -5535,7 +5536,7 @@
         <v>0.41042203194026261</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>332</v>
       </c>
@@ -5564,7 +5565,7 @@
         <v>0.32726787299048538</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>332</v>
       </c>
@@ -5593,7 +5594,7 @@
         <v>0.26095849634300861</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>332</v>
       </c>
@@ -5622,7 +5623,7 @@
         <v>0.65439130434782633</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>332</v>
       </c>
@@ -5651,7 +5652,7 @@
         <v>0.52181843478260892</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>332</v>
       </c>
@@ -5680,7 +5681,7 @@
         <v>0.41609906086956538</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>332</v>
       </c>
@@ -5709,7 +5710,7 @@
         <v>0.33179469913043491</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>332</v>
       </c>
@@ -5738,7 +5739,7 @@
         <v>0.26456811965217403</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>334</v>
       </c>
@@ -5767,7 +5768,7 @@
         <v>93.70400000673547</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>334</v>
       </c>
@@ -5796,7 +5797,7 @@
         <v>94.782871493406859</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>334</v>
       </c>
@@ -5825,7 +5826,7 @@
         <v>95.863802289969655</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>334</v>
       </c>
@@ -5854,7 +5855,7 @@
         <v>96.946792396423888</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>334</v>
       </c>
@@ -5883,7 +5884,7 @@
         <v>98.0318418127695</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>334</v>
       </c>
@@ -5912,7 +5913,7 @@
         <v>92.93801595829882</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>334</v>
       </c>
@@ -5941,7 +5942,7 @@
         <v>93.968919736860101</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>334</v>
       </c>
@@ -5970,7 +5971,7 @@
         <v>95.131696762608669</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>334</v>
       </c>
@@ -5999,7 +6000,7 @@
         <v>96.426755945691355</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>334</v>
       </c>
@@ -6115,7 +6116,7 @@
         <v>4.8846099999999995</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3">
         <v>364</v>
       </c>
@@ -6144,7 +6145,7 @@
         <v>115494.72</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
         <v>364</v>
       </c>
@@ -6173,7 +6174,7 @@
         <v>126091.36056</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3">
         <v>364</v>
       </c>
@@ -6202,7 +6203,7 @@
         <v>137652.38203200011</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
         <v>364</v>
       </c>
@@ -6231,7 +6232,7 @@
         <v>150264.6941928</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
         <v>364</v>
       </c>
@@ -6260,7 +6261,7 @@
         <v>164022.94496544011</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>367</v>
       </c>
@@ -6289,7 +6290,7 @@
         <v>5.5479450746268659</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3">
         <v>367</v>
       </c>
@@ -6318,7 +6319,7 @@
         <v>5.6197363811343282</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
         <v>367</v>
       </c>
@@ -6347,7 +6348,7 @@
         <v>5.6924087192644777</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
         <v>367</v>
       </c>
@@ -6376,7 +6377,7 @@
         <v>5.7659725305191172</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>367</v>
       </c>
@@ -6405,7 +6406,7 @@
         <v>5.8404383771269233</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
         <v>369</v>
       </c>
@@ -6434,7 +6435,7 @@
         <v>88.128</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>369</v>
       </c>
@@ -6463,7 +6464,7 @@
         <v>90.340012799999997</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
         <v>369</v>
       </c>
@@ -6492,7 +6493,7 @@
         <v>92.605254912000021</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>369</v>
       </c>
@@ -6521,7 +6522,7 @@
         <v>94.924970703359989</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
         <v>369</v>
       </c>
@@ -6550,7 +6551,7 @@
         <v>97.3004330244096</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
         <v>377</v>
       </c>
@@ -6579,7 +6580,7 @@
         <v>14193.63602034</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
         <v>377</v>
       </c>
@@ -6608,7 +6609,7 @@
         <v>16404.294830507952</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
         <v>377</v>
       </c>
@@ -6637,7 +6638,7 @@
         <v>18958.794473268641</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3">
         <v>377</v>
       </c>
@@ -6666,7 +6667,7 @@
         <v>21910.547375171111</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
         <v>377</v>
       </c>
@@ -6695,7 +6696,7 @@
         <v>25321.253271995771</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>424</v>
       </c>
@@ -6724,7 +6725,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>424</v>
       </c>
@@ -6753,7 +6754,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>424</v>
       </c>
@@ -6782,7 +6783,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>424</v>
       </c>
@@ -6811,7 +6812,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>424</v>
       </c>
@@ -6840,7 +6841,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>460</v>
       </c>
@@ -6869,7 +6870,7 @@
         <v>95.125032000000004</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>460</v>
       </c>
@@ -6898,7 +6899,7 @@
         <v>96.160232469600004</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>460</v>
       </c>
@@ -6927,7 +6928,7 @@
         <v>97.206624445392023</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>460</v>
       </c>
@@ -6956,7 +6957,7 @@
         <v>98.545849202319999</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>460</v>
       </c>
@@ -6985,7 +6986,7 @@
         <v>98.831307694343209</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>77</v>
       </c>
@@ -7014,7 +7015,7 @@
         <v>98.67895</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>77</v>
       </c>
@@ -7043,7 +7044,7 @@
         <v>98.965739499999998</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>77</v>
       </c>
@@ -7072,7 +7073,7 @@
         <v>99.255396895000004</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>77</v>
       </c>
@@ -7101,7 +7102,7 @@
         <v>99.547950863950007</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>77</v>
       </c>
@@ -7130,7 +7131,7 @@
         <v>99.843430372589509</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>98</v>
       </c>
@@ -7159,7 +7160,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>98</v>
       </c>
@@ -7188,7 +7189,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>98</v>
       </c>
@@ -7217,7 +7218,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>98</v>
       </c>
@@ -7246,7 +7247,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>98</v>
       </c>
@@ -7275,7 +7276,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="3">
         <v>386.1</v>
       </c>
@@ -7304,7 +7305,7 @@
         <v>6025.5908288085884</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="3">
         <v>386.1</v>
       </c>
@@ -7333,7 +7334,7 @@
         <v>7132.9729466473937</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="3">
         <v>386.1</v>
       </c>
@@ -7362,7 +7363,7 @@
         <v>8387.9290364164917</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="3">
         <v>386.1</v>
       </c>
@@ -7391,7 +7392,7 @@
         <v>9792.4915984875806</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="3">
         <v>386.1</v>
       </c>
@@ -7420,7 +7421,7 @@
         <v>11348.693133232369</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="3">
         <v>386.2</v>
       </c>
@@ -7449,7 +7450,7 @@
         <v>9176.5019107995558</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3">
         <v>386.2</v>
       </c>
@@ -7478,7 +7479,7 @@
         <v>10283.967217993961</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3">
         <v>386.2</v>
       </c>
@@ -7507,7 +7508,7 @@
         <v>11524.99750015523</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="3">
         <v>386.2</v>
       </c>
@@ -7536,7 +7537,7 @@
         <v>12915.691019463869</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="3">
         <v>386.2</v>
       </c>
@@ -7565,7 +7566,7 @@
         <v>14474.085149544269</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="3">
         <v>386.3</v>
       </c>
@@ -7594,7 +7595,7 @@
         <v>6775.7920969396118</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="3">
         <v>386.3</v>
       </c>
@@ -7623,7 +7624,7 @@
         <v>7687.612830857006</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="3">
         <v>386.3</v>
       </c>
@@ -7652,7 +7653,7 @@
         <v>8759.3798750710612</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3">
         <v>386.3</v>
       </c>
@@ -7681,7 +7682,7 @@
         <v>9993.3389311351038</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="3">
         <v>386.3</v>
       </c>
@@ -7710,7 +7711,7 @@
         <v>11391.73570060247</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>379</v>
       </c>
@@ -7739,7 +7740,7 @@
         <v>13317.175813442071</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>274</v>
       </c>
@@ -7768,7 +7769,7 @@
         <v>46054.901058930787</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>379</v>
       </c>
@@ -7797,7 +7798,7 @@
         <v>13418.021660158851</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>274</v>
       </c>
@@ -7826,7 +7827,7 @@
         <v>46403.657098334967</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>379</v>
       </c>
@@ -7855,7 +7856,7 @@
         <v>13536.316299144</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>274</v>
       </c>
@@ -7884,7 +7885,7 @@
         <v>46812.756442714293</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>379</v>
       </c>
@@ -7913,7 +7914,7 @@
         <v>13665.23975007113</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>274</v>
       </c>
@@ -7942,7 +7943,7 @@
         <v>47258.613496777638</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>379</v>
       </c>
@@ -7971,7 +7972,7 @@
         <v>13801.316029168571</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>274</v>
       </c>
@@ -8000,7 +8001,7 @@
         <v>47729.20723662855</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>379</v>
       </c>
@@ -8029,7 +8030,7 @@
         <v>13942.80055708834</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>274</v>
       </c>
@@ -8058,7 +8059,7 @@
         <v>48218.50436884314</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>379</v>
       </c>
@@ -8087,7 +8088,7 @@
         <v>14088.84540208515</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>274</v>
       </c>
@@ -8116,7 +8117,7 @@
         <v>48723.572483938951</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>379</v>
       </c>
@@ -8145,7 +8146,7 @@
         <v>14239.06717106818</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>274</v>
       </c>
@@ -8174,7 +8175,7 @@
         <v>49243.085690367268</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>379</v>
       </c>
@@ -8203,7 +8204,7 @@
         <v>14393.32333139659</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>274</v>
       </c>
@@ -8232,7 +8233,7 @@
         <v>49776.551066298169</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>379</v>
       </c>
@@ -8261,7 +8262,7 @@
         <v>14551.59642655029</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>274</v>
       </c>
@@ -8290,7 +8291,7 @@
         <v>50323.908241701443</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>14</v>
       </c>
@@ -8319,7 +8320,7 @@
         <v>59371.884262853768</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>14</v>
       </c>
@@ -8348,7 +8349,7 @@
         <v>59821.484690416968</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>14</v>
       </c>
@@ -8377,7 +8378,7 @@
         <v>60348.876962857597</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>14</v>
       </c>
@@ -8406,7 +8407,7 @@
         <v>60923.655603197178</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>14</v>
       </c>
@@ -8435,7 +8436,7 @@
         <v>61530.323654041553</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>14</v>
       </c>
@@ -8464,7 +8465,7 @@
         <v>62161.103267851133</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>14</v>
       </c>
@@ -8493,7 +8494,7 @@
         <v>62812.214115662013</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>14</v>
       </c>
@@ -8522,7 +8523,7 @@
         <v>63481.946918379748</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>14</v>
       </c>
@@ -8551,7 +8552,7 @@
         <v>64169.666223595093</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>14</v>
       </c>
@@ -8580,7 +8581,7 @@
         <v>64875.294205010192</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>14</v>
       </c>
@@ -8609,7 +8610,7 @@
         <v>60802.946712188583</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>14</v>
       </c>
@@ -8638,7 +8639,7 @@
         <v>61412.55539447139</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>14</v>
       </c>
@@ -8667,7 +8668,7 @@
         <v>62023.951131092377</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>14</v>
       </c>
@@ -8696,7 +8697,7 @@
         <v>62637.133922051551</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>14</v>
       </c>
@@ -8725,7 +8726,7 @@
         <v>63252.103767348883</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>14</v>
       </c>
@@ -8754,7 +8755,7 @@
         <v>63868.860666984387</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>14</v>
       </c>
@@ -8783,7 +8784,7 @@
         <v>64487.404620958077</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>14</v>
       </c>
@@ -8812,7 +8813,7 @@
         <v>65107.735629269962</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>14</v>
       </c>
@@ -8841,7 +8842,7 @@
         <v>65729.853691919998</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>14</v>
       </c>
@@ -8870,7 +8871,7 @@
         <v>66353.758808908198</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>379</v>
       </c>
@@ -8899,7 +8900,7 @@
         <v>13638.16461941349</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>274</v>
       </c>
@@ -8928,7 +8929,7 @@
         <v>47164.979344832544</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>379</v>
       </c>
@@ -8957,7 +8958,7 @@
         <v>13774.90048522195</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>274</v>
       </c>
@@ -8986,7 +8987,7 @@
         <v>47637.854138950643</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>379</v>
       </c>
@@ -9015,7 +9016,7 @@
         <v>13912.037189189839</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>274</v>
       </c>
@@ -9044,7 +9045,7 @@
         <v>48112.115155044899</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>379</v>
       </c>
@@ -9073,7 +9074,7 @@
         <v>14049.574731317151</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>274</v>
       </c>
@@ -9102,7 +9103,7 @@
         <v>48587.762393115328</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>379</v>
       </c>
@@ -9131,7 +9132,7 @@
         <v>14187.513111603899</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>274</v>
       </c>
@@ -9160,7 +9161,7 @@
         <v>49064.795853161922</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>379</v>
       </c>
@@ -9189,7 +9190,7 @@
         <v>14325.85233005006</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>274</v>
       </c>
@@ -9218,7 +9219,7 @@
         <v>49543.215535184667</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>379</v>
       </c>
@@ -9247,7 +9248,7 @@
         <v>14464.59238665566</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>274</v>
       </c>
@@ -9276,7 +9277,7 @@
         <v>50023.021439183598</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>379</v>
       </c>
@@ -9305,7 +9306,7 @@
         <v>14603.73328142068</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>274</v>
       </c>
@@ -9334,7 +9335,7 @@
         <v>50504.213565158687</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>379</v>
       </c>
@@ -9363,7 +9364,7 @@
         <v>14743.275014345139</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>274</v>
       </c>
@@ -9392,7 +9393,7 @@
         <v>50986.791913109962</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>379</v>
       </c>
@@ -9421,7 +9422,7 @@
         <v>14883.217585429011</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>274</v>
       </c>
@@ -9450,7 +9451,7 @@
         <v>51470.756483037367</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>14.1</v>
       </c>
@@ -9479,7 +9480,7 @@
         <v>9487.176818882821</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>14.2</v>
       </c>
@@ -9508,7 +9509,7 @@
         <v>51315.769893305762</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>14.1</v>
       </c>
@@ -9537,7 +9538,7 @@
         <v>9582.2949944297943</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>14.2</v>
       </c>
@@ -9566,7 +9567,7 @@
         <v>51830.260400041603</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>14.1</v>
       </c>
@@ -9595,7 +9596,7 @@
         <v>9677.6920067997835</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>14.2</v>
       </c>
@@ -9624,7 +9625,7 @@
         <v>52346.259124292606</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>14.1</v>
       </c>
@@ -9653,7 +9654,7 @@
         <v>9773.3678559927885</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>14.2</v>
       </c>
@@ -9682,7 +9683,7 @@
         <v>52863.766066058772</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>14.1</v>
       </c>
@@ -9711,7 +9712,7 @@
         <v>9869.3225420088074</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>14.2</v>
       </c>
@@ -9740,7 +9741,7 @@
         <v>53382.781225340077</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>14.1</v>
       </c>
@@ -9769,7 +9770,7 @@
         <v>9965.556064847844</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>14.2</v>
       </c>
@@ -9798,7 +9799,7 @@
         <v>53903.304602136559</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>14.1</v>
       </c>
@@ -9827,7 +9828,7 @@
         <v>10062.0684245099</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>14.2</v>
       </c>
@@ -9856,7 +9857,7 @@
         <v>54425.336196448203</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>14.1</v>
       </c>
@@ -9885,7 +9886,7 @@
         <v>10158.859620994959</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>14.2</v>
       </c>
@@ -9914,7 +9915,7 @@
         <v>54948.876008275001</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>14.1</v>
       </c>
@@ -9943,7 +9944,7 @@
         <v>10255.92965430305</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>14.2</v>
       </c>
@@ -9972,7 +9973,7 @@
         <v>55473.924037616962</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>14.1</v>
       </c>
@@ -10001,7 +10002,7 @@
         <v>10353.278524434139</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>14.2</v>
       </c>
@@ -10030,7 +10031,7 @@
         <v>56000.480284474063</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>14.1</v>
       </c>
@@ -10059,7 +10060,7 @@
         <v>9263.8859550375455</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>14.2</v>
       </c>
@@ -10088,7 +10089,7 @@
         <v>50107.998307816233</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>14.1</v>
       </c>
@@ -10117,7 +10118,7 @@
         <v>9334.0377977488515</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>14.2</v>
       </c>
@@ -10146,7 +10147,7 @@
         <v>50487.446892668122</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>14.1</v>
       </c>
@@ -10175,7 +10176,7 @@
         <v>9416.3276210569329</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>14.2</v>
       </c>
@@ -10204,7 +10205,7 @@
         <v>50932.549341800674</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>14.1</v>
       </c>
@@ -10233,7 +10234,7 @@
         <v>9506.0112118610195</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>14.2</v>
       </c>
@@ -10262,7 +10263,7 @@
         <v>51417.644391336173</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>14.1</v>
       </c>
@@ -10291,7 +10292,7 @@
         <v>9600.6705561847666</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>14.2</v>
       </c>
@@ -10320,7 +10321,7 @@
         <v>51929.65309785679</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>14.1</v>
       </c>
@@ -10349,7 +10350,7 @@
         <v>9699.0920645745646</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>14.2</v>
       </c>
@@ -10378,7 +10379,7 @@
         <v>52462.011203276568</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>14.1</v>
       </c>
@@ -10407,7 +10408,7 @@
         <v>9800.6858865173472</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>14.2</v>
       </c>
@@ -10436,7 +10437,7 @@
         <v>53011.528229144671</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>14.1</v>
       </c>
@@ -10465,7 +10466,7 @@
         <v>9905.1853205803909</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>14.2</v>
       </c>
@@ -10494,7 +10495,7 @@
         <v>53576.761597799363</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>14.1</v>
       </c>
@@ -10523,7 +10524,7 @@
         <v>10012.491216151881</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>14.2</v>
       </c>
@@ -10552,7 +10553,7 @@
         <v>54157.175007443213</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>14.1</v>
       </c>
@@ -10581,7 +10582,7 @@
         <v>10122.59142987548</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>14.2</v>
       </c>
@@ -10610,7 +10611,7 @@
         <v>54752.70277513472</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>14.3</v>
       </c>
@@ -10639,7 +10640,7 @@
         <v>56552.414086080753</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>14.4</v>
       </c>
@@ -10668,7 +10669,7 @@
         <v>4250.5326261078344</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>14.3</v>
       </c>
@@ -10697,7 +10698,7 @@
         <v>57119.407044400919</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>14.4</v>
       </c>
@@ -10726,7 +10727,7 @@
         <v>4293.1483500704726</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>14.3</v>
       </c>
@@ -10755,7 +10756,7 @@
         <v>57688.062130009188</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>14.4</v>
       </c>
@@ -10784,7 +10785,7 @@
         <v>4335.8890010831956</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>14.3</v>
       </c>
@@ -10813,7 +10814,7 @@
         <v>58258.379342905551</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>14.4</v>
       </c>
@@ -10842,7 +10843,7 @@
         <v>4378.7545791459988</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>14.3</v>
       </c>
@@ -10871,7 +10872,7 @@
         <v>58830.358683090002</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>14.4</v>
       </c>
@@ -10900,7 +10901,7 @@
         <v>4421.7450842588833</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>14.3</v>
       </c>
@@ -10929,7 +10930,7 @@
         <v>59404.000150562548</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>14.4</v>
       </c>
@@ -10958,7 +10959,7 @@
         <v>4464.8605164218507</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>14.3</v>
       </c>
@@ -10987,7 +10988,7 @@
         <v>59979.303745323188</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>14.4</v>
       </c>
@@ -11016,7 +11017,7 @@
         <v>4508.1008756348992</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>14.3</v>
       </c>
@@ -11045,7 +11046,7 @@
         <v>60556.269467371923</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>14.4</v>
       </c>
@@ -11074,7 +11075,7 @@
         <v>4551.4661618980308</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>14.3</v>
       </c>
@@ -11103,7 +11104,7 @@
         <v>61134.897316708753</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>14.4</v>
       </c>
@@ -11132,7 +11133,7 @@
         <v>4594.9563752112444</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>14.3</v>
       </c>
@@ -11161,7 +11162,7 @@
         <v>61715.187293333664</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>14.4</v>
       </c>
@@ -11190,7 +11191,7 @@
         <v>4638.5715155745374</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>14.3</v>
       </c>
@@ -11219,7 +11220,7 @@
         <v>55221.39247291936</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>14.4</v>
       </c>
@@ -11248,7 +11249,7 @@
         <v>4150.4917899344118</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>14.3</v>
       </c>
@@ -11277,7 +11278,7 @@
         <v>55639.562823662178</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>14.4</v>
       </c>
@@ -11306,7 +11307,7 @@
         <v>4181.9218667547893</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>14.3</v>
       </c>
@@ -11335,7 +11336,7 @@
         <v>56130.086849052597</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>14.4</v>
       </c>
@@ -11364,7 +11365,7 @@
         <v>4218.7901138050047</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>14.3</v>
       </c>
@@ -11393,7 +11394,7 @@
         <v>56664.68461830516</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>14.4</v>
       </c>
@@ -11422,7 +11423,7 @@
         <v>4258.9709848920229</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>14.3</v>
       </c>
@@ -11451,7 +11452,7 @@
         <v>57228.942514991417</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>14.4</v>
       </c>
@@ -11480,7 +11481,7 @@
         <v>4301.3811390501323</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>14.3</v>
       </c>
@@ -11509,7 +11510,7 @@
         <v>57815.626415133163</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>14.4</v>
       </c>
@@ -11538,7 +11539,7 @@
         <v>4345.4768527179676</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>14.3</v>
       </c>
@@ -11567,7 +11568,7 @@
         <v>58421.220260043949</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>14.4</v>
       </c>
@@ -11596,7 +11597,7 @@
         <v>4390.9938556180596</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>14.3</v>
       </c>
@@ -11625,7 +11626,7 @@
         <v>59044.134260669722</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>14.4</v>
       </c>
@@ -11654,7 +11655,7 @@
         <v>4437.8126577100284</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>14.3</v>
       </c>
@@ -11683,7 +11684,7 @@
         <v>59683.777386974543</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>14.4</v>
       </c>
@@ -11712,7 +11713,7 @@
         <v>4485.8888366205483</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>14.3</v>
       </c>
@@ -11741,7 +11742,7 @@
         <v>60340.077253239288</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>14.4</v>
       </c>
@@ -11770,7 +11771,7 @@
         <v>4535.2169517708999</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>194</v>
       </c>
@@ -11799,7 +11800,7 @@
         <v>93.008258302465308</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>194</v>
       </c>
@@ -11828,7 +11829,7 @@
         <v>93.941532956484238</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>194</v>
       </c>
@@ -11857,7 +11858,7 @@
         <v>94.87480761050314</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>194</v>
       </c>
@@ -11886,7 +11887,7 @@
         <v>95.808082264522056</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>194</v>
       </c>
@@ -11915,7 +11916,7 @@
         <v>96.741356918540987</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>194</v>
       </c>
@@ -11944,7 +11945,7 @@
         <v>93.424405824177825</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>194</v>
       </c>
@@ -11973,7 +11974,7 @@
         <v>94.15447253075159</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>194</v>
       </c>
@@ -12002,7 +12003,7 @@
         <v>94.890244356788997</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>194</v>
       </c>
@@ -12031,7 +12032,7 @@
         <v>95.631765885049148</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>194</v>
       </c>
@@ -12060,7 +12061,7 @@
         <v>96.379082046683891</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>323</v>
       </c>
@@ -12089,7 +12090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>323</v>
       </c>
@@ -12118,7 +12119,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>323</v>
       </c>
@@ -12147,7 +12148,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>323</v>
       </c>
@@ -12176,7 +12177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>323</v>
       </c>
@@ -12205,7 +12206,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>376</v>
       </c>
@@ -12234,7 +12235,7 @@
         <v>36033.446856183858</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>376</v>
       </c>
@@ -12263,7 +12264,7 @@
         <v>38872.61512155136</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>376</v>
       </c>
@@ -12292,7 +12293,7 @@
         <v>41717.57657108127</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>376</v>
       </c>
@@ -12321,7 +12322,7 @@
         <v>44568.331204773582</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>376</v>
       </c>
@@ -12350,7 +12351,7 @@
         <v>47424.879022628324</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>376</v>
       </c>
@@ -12379,7 +12380,7 @@
         <v>34556.673694232348</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>376</v>
       </c>
@@ -12408,7 +12409,7 @@
         <v>37856.02412414951</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>376</v>
       </c>
@@ -12437,7 +12438,7 @@
         <v>41689.182193960667</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>376</v>
       </c>
@@ -12466,7 +12467,7 @@
         <v>46057.780844716202</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>376</v>
       </c>
@@ -12495,7 +12496,7 @@
         <v>50963.453017466447</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>466</v>
       </c>
@@ -12524,7 +12525,7 @@
         <v>60.742268041340189</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>466</v>
       </c>
@@ -12553,7 +12554,7 @@
         <v>62.622639562581618</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>466</v>
       </c>
@@ -12582,7 +12583,7 @@
         <v>64.561276595843793</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>466</v>
       </c>
@@ -12611,7 +12612,7 @@
         <v>66.559986395217919</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>466</v>
       </c>
@@ -12640,7 +12641,7 @@
         <v>68.620632331635861</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>466</v>
       </c>
@@ -12669,7 +12670,7 @@
         <v>57.97444574550294</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>466</v>
       </c>
@@ -12698,7 +12699,7 @@
         <v>59.769135016331823</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>466</v>
       </c>
@@ -12727,7 +12728,7 @@
         <v>61.619434834385345</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>466</v>
       </c>
@@ -12756,7 +12757,7 @@
         <v>63.527070103221561</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>466</v>
       </c>
@@ -12785,7 +12786,7 @@
         <v>65.493819286181989</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>96</v>
       </c>
@@ -12814,7 +12815,7 @@
         <v>990.23735660954856</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>96</v>
       </c>
@@ -12843,7 +12844,7 @@
         <v>1074.101030045967</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>96</v>
       </c>
@@ -12872,7 +12873,7 @@
         <v>1165.04537214991</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>96</v>
       </c>
@@ -12901,7 +12902,7 @@
         <v>1263.666562398188</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>96</v>
       </c>
@@ -12930,7 +12931,7 @@
         <v>1370.6108527044289</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>385</v>
       </c>
@@ -12959,7 +12960,7 @@
         <v>22394.58706838209</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>385</v>
       </c>
@@ -12988,7 +12989,7 @@
         <v>24510.31089960839</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>385</v>
       </c>
@@ -13017,7 +13018,7 @@
         <v>26645.972550694249</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>385</v>
       </c>
@@ -13046,7 +13047,7 @@
         <v>28801.572021639651</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>385</v>
       </c>
@@ -13075,7 +13076,7 @@
         <v>30977.109312444602</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>385</v>
       </c>
@@ -13104,7 +13105,7 @@
         <v>20844.165363419648</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>385</v>
       </c>
@@ -13133,7 +13134,7 @@
         <v>22863.33165174054</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>385</v>
       </c>
@@ -13162,7 +13163,7 @@
         <v>25170.11368192935</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>385</v>
       </c>
@@ -13191,7 +13192,7 @@
         <v>27768.499991978719</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>385</v>
       </c>
@@ -13220,7 +13221,7 @@
         <v>30662.479119881289</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="3">
         <v>386.1</v>
       </c>
@@ -13249,7 +13250,7 @@
         <v>6063.9485940000004</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="3">
         <v>386.1</v>
       </c>
@@ -13278,7 +13279,7 @@
         <v>7617.8354212124996</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="3">
         <v>386.1</v>
       </c>
@@ -13307,7 +13308,7 @@
         <v>9569.6688749062487</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="3">
         <v>386.1</v>
       </c>
@@ -13336,7 +13337,7 @@
         <v>11023.172622260399</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="3">
         <v>386.1</v>
       </c>
@@ -13365,7 +13366,7 @@
         <v>12345.410811333601</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="3">
         <v>386.2</v>
       </c>
@@ -13394,7 +13395,7 @@
         <v>7569.1213256024957</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="3">
         <v>386.2</v>
       </c>
@@ -13423,7 +13424,7 @@
         <v>7660.696088310985</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="3">
         <v>386.2</v>
       </c>
@@ -13452,7 +13453,7 @@
         <v>7752.6631555816357</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="3">
         <v>386.2</v>
       </c>
@@ -13481,7 +13482,7 @@
         <v>7845.0225274144459</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="3">
         <v>386.2</v>
       </c>
@@ -13510,7 +13511,7 @@
         <v>7937.7742038094157</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="3">
         <v>386.3</v>
       </c>
@@ -13539,7 +13540,7 @@
         <v>7026.0817481999993</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="3">
         <v>386.3</v>
       </c>
@@ -13568,7 +13569,7 @@
         <v>7738.846362034199</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="3">
         <v>386.3</v>
       </c>
@@ -13597,7 +13598,7 @@
         <v>8458.3536047747984</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="3">
         <v>386.3</v>
       </c>
@@ -13626,7 +13627,7 @@
         <v>9184.6034764218002</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" s="3">
         <v>386.3</v>
       </c>
@@ -13655,7 +13656,7 @@
         <v>9917.5959769751989</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>67</v>
       </c>
@@ -13684,7 +13685,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>67</v>
       </c>
@@ -13713,7 +13714,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>67</v>
       </c>
@@ -13742,7 +13743,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>67</v>
       </c>
@@ -13771,7 +13772,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>67</v>
       </c>
@@ -13800,7 +13801,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>67</v>
       </c>
@@ -13829,7 +13830,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>67</v>
       </c>
@@ -13858,7 +13859,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>67</v>
       </c>
@@ -13887,7 +13888,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>67</v>
       </c>
@@ -13916,7 +13917,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>67</v>
       </c>
@@ -13945,7 +13946,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>68</v>
       </c>
@@ -13974,7 +13975,7 @@
         <v>41.957999999999991</v>
       </c>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>68</v>
       </c>
@@ -14003,7 +14004,7 @@
         <v>44.276179499999998</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>68</v>
       </c>
@@ -14032,7 +14033,7 @@
         <v>46.721281949999991</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>68</v>
       </c>
@@ -14061,7 +14062,7 @@
         <v>49.300204196249993</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>68</v>
       </c>
@@ -14090,7 +14091,7 @@
         <v>52.020215462249993</v>
       </c>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>332</v>
       </c>
@@ -14119,7 +14120,7 @@
         <v>0.69049565217391329</v>
       </c>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>332</v>
       </c>
@@ -14148,7 +14149,7 @@
         <v>0.61943446956521764</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>332</v>
       </c>
@@ -14177,7 +14178,7 @@
         <v>0.5556805669565219</v>
       </c>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>332</v>
       </c>
@@ -14206,7 +14207,7 @@
         <v>0.49848310017391317</v>
       </c>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>332</v>
       </c>
@@ -14236,6 +14237,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K462" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Índice de Inclusión"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="963" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69871D06-0733-48E2-9F52-117163E6197B}"/>
+  <xr:revisionPtr revIDLastSave="1007" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{480F34D1-A8D8-4709-B7D6-10F0B47B0C87}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -8600,184 +8600,184 @@
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273">
-        <v>14.3</v>
+        <v>194</v>
       </c>
       <c r="B273" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="C273" s="2">
-        <v>46203</v>
+        <v>46387</v>
       </c>
       <c r="D273">
         <v>2026</v>
       </c>
       <c r="E273" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F273" t="s">
         <v>30</v>
       </c>
       <c r="G273">
-        <v>53184.163304725829</v>
+        <v>90.299279905306122</v>
       </c>
       <c r="H273">
-        <v>50081.414848975357</v>
+        <v>87.590301508146936</v>
       </c>
       <c r="I273">
-        <v>56552.414086080753</v>
+        <v>93.008258302465308</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274">
-        <v>14.4</v>
+        <v>194</v>
       </c>
       <c r="B274" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="C274" s="2">
-        <v>46203</v>
+        <v>46752</v>
       </c>
       <c r="D274">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E274" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F274" t="s">
         <v>30</v>
       </c>
       <c r="G274">
-        <v>3997.37172978836</v>
+        <v>91.205371802411875</v>
       </c>
       <c r="H274">
-        <v>3764.1662379467821</v>
+        <v>88.469210648339512</v>
       </c>
       <c r="I274">
-        <v>4250.5326261078344</v>
+        <v>93.941532956484238</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275">
-        <v>14.3</v>
+        <v>194</v>
       </c>
       <c r="B275" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="C275" s="2">
-        <v>46387</v>
+        <v>47118</v>
       </c>
       <c r="D275">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="E275" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F275" t="s">
         <v>30</v>
       </c>
       <c r="G275">
-        <v>53621.575554493087</v>
+        <v>92.111463699517614</v>
       </c>
       <c r="H275">
-        <v>50399.460587916547</v>
+        <v>89.348119788532088</v>
       </c>
       <c r="I275">
-        <v>57119.407044400919</v>
+        <v>94.87480761050314</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276">
-        <v>14.4</v>
+        <v>194</v>
       </c>
       <c r="B276" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="C276" s="2">
-        <v>46387</v>
+        <v>47483</v>
       </c>
       <c r="D276">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="E276" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F276" t="s">
         <v>30</v>
       </c>
       <c r="G276">
-        <v>4030.2480458350101</v>
+        <v>93.017555596623353</v>
       </c>
       <c r="H276">
-        <v>3788.0708547842928</v>
+        <v>90.22702892872465</v>
       </c>
       <c r="I276">
-        <v>4293.1483500704726</v>
+        <v>95.808082264522056</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277">
-        <v>14.3</v>
+        <v>194</v>
       </c>
       <c r="B277" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="C277" s="2">
-        <v>46568</v>
+        <v>47848</v>
       </c>
       <c r="D277">
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="E277" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F277" t="s">
         <v>30</v>
       </c>
       <c r="G277">
-        <v>54058.987804260367</v>
+        <v>93.923647493729106</v>
       </c>
       <c r="H277">
-        <v>50715.975216732273</v>
+        <v>91.105938068917226</v>
       </c>
       <c r="I277">
-        <v>57688.062130009188</v>
+        <v>96.741356918540987</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278">
-        <v>14.4</v>
+        <v>194</v>
       </c>
       <c r="B278" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="C278" s="2">
-        <v>46568</v>
+        <v>46387</v>
       </c>
       <c r="D278">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E278" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F278" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G278">
-        <v>4063.1243618816602</v>
+        <v>90.703306625415365</v>
       </c>
       <c r="H278">
-        <v>3811.8603919448801</v>
+        <v>87.982207426652906</v>
       </c>
       <c r="I278">
-        <v>4335.8890010831956</v>
+        <v>93.424405824177825</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279">
-        <v>14.3</v>
+        <v>194</v>
       </c>
       <c r="B279" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="C279" s="2">
         <v>46752</v>
@@ -8789,372 +8789,372 @@
         <v>14</v>
       </c>
       <c r="F279" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G279">
-        <v>54496.400054027639</v>
+        <v>91.412109253156885</v>
       </c>
       <c r="H279">
-        <v>51030.958735422559</v>
+        <v>88.669745975562179</v>
       </c>
       <c r="I279">
-        <v>58258.379342905551</v>
+        <v>94.15447253075159</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280">
-        <v>14.4</v>
+        <v>194</v>
       </c>
       <c r="B280" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="C280" s="2">
-        <v>46752</v>
+        <v>47118</v>
       </c>
       <c r="D280">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E280" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F280" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G280">
-        <v>4096.0006779283094</v>
+        <v>92.126450831833978</v>
       </c>
       <c r="H280">
-        <v>3835.5348494285399</v>
+        <v>89.362657306878958</v>
       </c>
       <c r="I280">
-        <v>4378.7545791459988</v>
+        <v>94.890244356788997</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281">
-        <v>14.3</v>
+        <v>194</v>
       </c>
       <c r="B281" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="C281" s="2">
-        <v>46934</v>
+        <v>47483</v>
       </c>
       <c r="D281">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E281" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F281" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G281">
-        <v>54933.812303794897</v>
+        <v>92.846374645678779</v>
       </c>
       <c r="H281">
-        <v>51344.411143987381</v>
+        <v>90.060983406308409</v>
       </c>
       <c r="I281">
-        <v>58830.358683090002</v>
+        <v>95.631765885049148</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282">
-        <v>14.4</v>
+        <v>194</v>
       </c>
       <c r="B282" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="C282" s="2">
-        <v>46934</v>
+        <v>47848</v>
       </c>
       <c r="D282">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="E282" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F282" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G282">
-        <v>4128.8769939749591</v>
+        <v>93.571924317168822</v>
       </c>
       <c r="H282">
-        <v>3859.094227235275</v>
+        <v>90.764766587653753</v>
       </c>
       <c r="I282">
-        <v>4421.7450842588833</v>
+        <v>96.379082046683891</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283">
-        <v>14.3</v>
+        <v>323</v>
       </c>
       <c r="B283" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="C283" s="2">
-        <v>47118</v>
+        <v>46387</v>
       </c>
       <c r="D283">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="E283" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F283" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G283">
-        <v>55371.22455356217</v>
+        <v>2</v>
       </c>
       <c r="H283">
-        <v>51656.332442426763</v>
+        <v>1</v>
       </c>
       <c r="I283">
-        <v>59404.000150562548</v>
+        <v>3</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284">
-        <v>14.4</v>
+        <v>323</v>
       </c>
       <c r="B284" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="C284" s="2">
-        <v>47118</v>
+        <v>46752</v>
       </c>
       <c r="D284">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E284" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F284" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G284">
-        <v>4161.7533100216096</v>
+        <v>2</v>
       </c>
       <c r="H284">
-        <v>3882.5385253650838</v>
+        <v>1</v>
       </c>
       <c r="I284">
-        <v>4464.8605164218507</v>
+        <v>3</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285">
-        <v>14.3</v>
+        <v>323</v>
       </c>
       <c r="B285" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="C285" s="2">
-        <v>47299</v>
+        <v>47118</v>
       </c>
       <c r="D285">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="E285" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F285" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G285">
-        <v>55808.636803329442</v>
+        <v>2</v>
       </c>
       <c r="H285">
-        <v>51966.722630740682</v>
+        <v>1</v>
       </c>
       <c r="I285">
-        <v>59979.303745323188</v>
+        <v>3</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286">
-        <v>14.4</v>
+        <v>323</v>
       </c>
       <c r="B286" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="C286" s="2">
-        <v>47299</v>
+        <v>47483</v>
       </c>
       <c r="D286">
         <v>2029</v>
       </c>
       <c r="E286" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F286" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G286">
-        <v>4194.6296260682593</v>
+        <v>3</v>
       </c>
       <c r="H286">
-        <v>3905.867743817967</v>
+        <v>2</v>
       </c>
       <c r="I286">
-        <v>4508.1008756348992</v>
+        <v>4</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287">
-        <v>14.3</v>
+        <v>323</v>
       </c>
       <c r="B287" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="C287" s="2">
-        <v>47483</v>
+        <v>47848</v>
       </c>
       <c r="D287">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E287" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F287" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G287">
-        <v>56246.049053096707</v>
+        <v>3</v>
       </c>
       <c r="H287">
-        <v>52275.581708929167</v>
+        <v>2</v>
       </c>
       <c r="I287">
-        <v>60556.269467371923</v>
+        <v>4</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288">
-        <v>14.4</v>
+        <v>376</v>
       </c>
       <c r="B288" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C288" s="2">
-        <v>47483</v>
+        <v>46387</v>
       </c>
       <c r="D288">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="E288" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F288" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G288">
-        <v>4227.505942114909</v>
+        <v>34790.444801582693</v>
       </c>
       <c r="H288">
-        <v>3929.081882593925</v>
+        <v>33746.731457535207</v>
       </c>
       <c r="I288">
-        <v>4551.4661618980308</v>
+        <v>36033.446856183858</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289">
-        <v>14.3</v>
+        <v>376</v>
       </c>
       <c r="B289" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C289" s="2">
-        <v>47664</v>
+        <v>46752</v>
       </c>
       <c r="D289">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="E289" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F289" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G289">
-        <v>56683.461302863987</v>
+        <v>37492.873343857507</v>
       </c>
       <c r="H289">
-        <v>52582.909676992182</v>
+        <v>36334.343557532309</v>
       </c>
       <c r="I289">
-        <v>61134.897316708753</v>
+        <v>38872.61512155136</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290">
-        <v>14.4</v>
+        <v>376</v>
       </c>
       <c r="B290" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C290" s="2">
-        <v>47664</v>
+        <v>47118</v>
       </c>
       <c r="D290">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="E290" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F290" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G290">
-        <v>4260.3822581615595</v>
+        <v>40195.301886132322</v>
       </c>
       <c r="H290">
-        <v>3952.1809416929568</v>
+        <v>38917.091286153307</v>
       </c>
       <c r="I290">
-        <v>4594.9563752112444</v>
+        <v>41717.57657108127</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291">
-        <v>14.3</v>
+        <v>376</v>
       </c>
       <c r="B291" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C291" s="2">
-        <v>47848</v>
+        <v>47483</v>
       </c>
       <c r="D291">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="E291" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F291" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G291">
-        <v>57120.873552631252</v>
+        <v>42897.730428407129</v>
       </c>
       <c r="H291">
-        <v>52888.706534929763</v>
+        <v>41494.974643398207</v>
       </c>
       <c r="I291">
-        <v>61715.187293333664</v>
+        <v>44568.331204773582</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292">
-        <v>14.4</v>
+        <v>376</v>
       </c>
       <c r="B292" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C292" s="2">
         <v>47848</v>
@@ -9166,24 +9166,24 @@
         <v>20</v>
       </c>
       <c r="F292" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G292">
-        <v>4293.2585742082092</v>
+        <v>45600.15897068195</v>
       </c>
       <c r="H292">
-        <v>3975.164921115063</v>
+        <v>44067.993629267032</v>
       </c>
       <c r="I292">
-        <v>4638.5715155745374</v>
+        <v>47424.879022628324</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293">
-        <v>194</v>
+        <v>376</v>
       </c>
       <c r="B293" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="C293" s="2">
         <v>46387</v>
@@ -9195,24 +9195,24 @@
         <v>12</v>
       </c>
       <c r="F293" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G293">
-        <v>90.299279905306122</v>
+        <v>33364.614089900009</v>
       </c>
       <c r="H293">
-        <v>87.590301508146936</v>
+        <v>32363.67566720301</v>
       </c>
       <c r="I293">
-        <v>93.008258302465308</v>
+        <v>34556.673694232348</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294">
-        <v>194</v>
+        <v>376</v>
       </c>
       <c r="B294" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="C294" s="2">
         <v>46752</v>
@@ -9224,24 +9224,24 @@
         <v>14</v>
       </c>
       <c r="F294" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G294">
-        <v>91.205371802411875</v>
+        <v>36512.365153479492</v>
       </c>
       <c r="H294">
-        <v>88.469210648339512</v>
+        <v>35384.133070236967</v>
       </c>
       <c r="I294">
-        <v>93.941532956484238</v>
+        <v>37856.02412414951</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295">
-        <v>194</v>
+        <v>376</v>
       </c>
       <c r="B295" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="C295" s="2">
         <v>47118</v>
@@ -9253,24 +9253,24 @@
         <v>16</v>
       </c>
       <c r="F295" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G295">
-        <v>92.111463699517614</v>
+        <v>40167.943620047838</v>
       </c>
       <c r="H295">
-        <v>89.348119788532088</v>
+        <v>38890.603012930333</v>
       </c>
       <c r="I295">
-        <v>94.87480761050314</v>
+        <v>41689.182193960667</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296">
-        <v>194</v>
+        <v>376</v>
       </c>
       <c r="B296" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="C296" s="2">
         <v>47483</v>
@@ -9282,24 +9282,24 @@
         <v>18</v>
       </c>
       <c r="F296" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G296">
-        <v>93.017555596623353</v>
+        <v>44331.349489605069</v>
       </c>
       <c r="H296">
-        <v>90.22702892872465</v>
+        <v>42881.71436129498</v>
       </c>
       <c r="I296">
-        <v>95.808082264522056</v>
+        <v>46057.780844716202</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297">
-        <v>194</v>
+        <v>376</v>
       </c>
       <c r="B297" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="C297" s="2">
         <v>47848</v>
@@ -9311,24 +9311,24 @@
         <v>20</v>
       </c>
       <c r="F297" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G297">
-        <v>93.923647493729106</v>
+        <v>49002.582762151171</v>
       </c>
       <c r="H297">
-        <v>91.105938068917226</v>
+        <v>47356.095981342893</v>
       </c>
       <c r="I297">
-        <v>96.741356918540987</v>
+        <v>50963.453017466447</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298">
-        <v>194</v>
+        <v>466</v>
       </c>
       <c r="B298" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C298" s="2">
         <v>46387</v>
@@ -9340,24 +9340,24 @@
         <v>12</v>
       </c>
       <c r="F298" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G298">
-        <v>90.703306625415365</v>
+        <v>58.919999999999987</v>
       </c>
       <c r="H298">
-        <v>87.982207426652906</v>
+        <v>57.152399999902997</v>
       </c>
       <c r="I298">
-        <v>93.424405824177825</v>
+        <v>60.742268041340189</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299">
-        <v>194</v>
+        <v>466</v>
       </c>
       <c r="B299" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C299" s="2">
         <v>46752</v>
@@ -9369,24 +9369,24 @@
         <v>14</v>
       </c>
       <c r="F299" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G299">
-        <v>91.412109253156885</v>
+        <v>60.687600000000003</v>
       </c>
       <c r="H299">
-        <v>88.669745975562179</v>
+        <v>58.812353159905193</v>
       </c>
       <c r="I299">
-        <v>94.15447253075159</v>
+        <v>62.622639562581618</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300">
-        <v>194</v>
+        <v>466</v>
       </c>
       <c r="B300" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C300" s="2">
         <v>47118</v>
@@ -9398,24 +9398,24 @@
         <v>16</v>
       </c>
       <c r="F300" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G300">
-        <v>92.126450831833978</v>
+        <v>62.508228000000003</v>
       </c>
       <c r="H300">
-        <v>89.362657306878958</v>
+        <v>60.520466349507103</v>
       </c>
       <c r="I300">
-        <v>94.890244356788997</v>
+        <v>64.561276595843793</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301">
-        <v>194</v>
+        <v>466</v>
       </c>
       <c r="B301" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C301" s="2">
         <v>47483</v>
@@ -9427,24 +9427,24 @@
         <v>18</v>
       </c>
       <c r="F301" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G301">
-        <v>92.846374645678779</v>
+        <v>64.383474839999991</v>
       </c>
       <c r="H301">
-        <v>90.060983406308409</v>
+        <v>62.27813521264077</v>
       </c>
       <c r="I301">
-        <v>95.631765885049148</v>
+        <v>66.559986395217919</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302">
-        <v>194</v>
+        <v>466</v>
       </c>
       <c r="B302" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C302" s="2">
         <v>47848</v>
@@ -9456,24 +9456,24 @@
         <v>20</v>
       </c>
       <c r="F302" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G302">
-        <v>93.571924317168822</v>
+        <v>66.314979085199994</v>
       </c>
       <c r="H302">
-        <v>90.764766587653753</v>
+        <v>64.086795787847493</v>
       </c>
       <c r="I302">
-        <v>96.379082046683891</v>
+        <v>68.620632331635861</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303">
-        <v>323</v>
+        <v>466</v>
       </c>
       <c r="B303" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C303" s="2">
         <v>46387</v>
@@ -9485,24 +9485,24 @@
         <v>12</v>
       </c>
       <c r="F303" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G303">
-        <v>2</v>
+        <v>56.235212373037847</v>
       </c>
       <c r="H303">
-        <v>1</v>
+        <v>54.54815600174971</v>
       </c>
       <c r="I303">
-        <v>3</v>
+        <v>57.97444574550294</v>
       </c>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304">
-        <v>323</v>
+        <v>466</v>
       </c>
       <c r="B304" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C304" s="2">
         <v>46752</v>
@@ -9514,24 +9514,24 @@
         <v>14</v>
       </c>
       <c r="F304" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G304">
-        <v>2</v>
+        <v>57.922268744228987</v>
       </c>
       <c r="H304">
-        <v>1</v>
+        <v>56.132470639937168</v>
       </c>
       <c r="I304">
-        <v>3</v>
+        <v>59.769135016331823</v>
       </c>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305">
-        <v>323</v>
+        <v>466</v>
       </c>
       <c r="B305" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C305" s="2">
         <v>47118</v>
@@ -9543,24 +9543,24 @@
         <v>16</v>
       </c>
       <c r="F305" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G305">
-        <v>2</v>
+        <v>59.659936806555862</v>
       </c>
       <c r="H305">
-        <v>1</v>
+        <v>57.762750816014403</v>
       </c>
       <c r="I305">
-        <v>3</v>
+        <v>61.619434834385345</v>
       </c>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306">
-        <v>323</v>
+        <v>466</v>
       </c>
       <c r="B306" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C306" s="2">
         <v>47483</v>
@@ -9572,24 +9572,24 @@
         <v>18</v>
       </c>
       <c r="F306" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G306">
-        <v>3</v>
+        <v>61.449734910752539</v>
       </c>
       <c r="H306">
-        <v>2</v>
+        <v>59.440328579080322</v>
       </c>
       <c r="I306">
-        <v>4</v>
+        <v>63.527070103221561</v>
       </c>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307">
-        <v>323</v>
+        <v>466</v>
       </c>
       <c r="B307" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C307" s="2">
         <v>47848</v>
@@ -9601,24 +9601,24 @@
         <v>20</v>
       </c>
       <c r="F307" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G307">
-        <v>3</v>
+        <v>63.293226958075117</v>
       </c>
       <c r="H307">
-        <v>2</v>
+        <v>61.166574532195703</v>
       </c>
       <c r="I307">
-        <v>4</v>
+        <v>65.493819286181989</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A308">
-        <v>376</v>
+        <v>96</v>
       </c>
       <c r="B308" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C308" s="2">
         <v>46387</v>
@@ -9630,24 +9630,24 @@
         <v>12</v>
       </c>
       <c r="F308" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="G308">
-        <v>34790.444801582693</v>
+        <v>846.88288415165562</v>
       </c>
       <c r="H308">
-        <v>33746.731457535207</v>
+        <v>703.52841169356259</v>
       </c>
       <c r="I308">
-        <v>36033.446856183858</v>
+        <v>990.23735660954856</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309">
-        <v>376</v>
+        <v>96</v>
       </c>
       <c r="B309" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C309" s="2">
         <v>46752</v>
@@ -9659,24 +9659,24 @@
         <v>14</v>
       </c>
       <c r="F309" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="G309">
-        <v>37492.873343857507</v>
+        <v>914.63351488378817</v>
       </c>
       <c r="H309">
-        <v>36334.343557532309</v>
+        <v>755.16599972142001</v>
       </c>
       <c r="I309">
-        <v>38872.61512155136</v>
+        <v>1074.101030045967</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310">
-        <v>376</v>
+        <v>96</v>
       </c>
       <c r="B310" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C310" s="2">
         <v>47118</v>
@@ -9688,24 +9688,24 @@
         <v>16</v>
       </c>
       <c r="F310" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="G310">
-        <v>40195.301886132322</v>
+        <v>987.8041960744913</v>
       </c>
       <c r="H310">
-        <v>38917.091286153307</v>
+        <v>810.56301999889411</v>
       </c>
       <c r="I310">
-        <v>41717.57657108127</v>
+        <v>1165.04537214991</v>
       </c>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311">
-        <v>376</v>
+        <v>96</v>
       </c>
       <c r="B311" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C311" s="2">
         <v>47483</v>
@@ -9717,24 +9717,24 @@
         <v>18</v>
       </c>
       <c r="F311" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="G311">
-        <v>42897.730428407129</v>
+        <v>1066.8285317604509</v>
       </c>
       <c r="H311">
-        <v>41494.974643398207</v>
+        <v>869.9905011225452</v>
       </c>
       <c r="I311">
-        <v>44568.331204773582</v>
+        <v>1263.666562398188</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312">
-        <v>376</v>
+        <v>96</v>
       </c>
       <c r="B312" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C312" s="2">
         <v>47848</v>
@@ -9746,24 +9746,24 @@
         <v>20</v>
       </c>
       <c r="F312" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="G312">
-        <v>45600.15897068195</v>
+        <v>1152.1748143012869</v>
       </c>
       <c r="H312">
-        <v>44067.993629267032</v>
+        <v>933.73877589798656</v>
       </c>
       <c r="I312">
-        <v>47424.879022628324</v>
+        <v>1370.6108527044289</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A313">
-        <v>376</v>
+      <c r="A313" t="s">
+        <v>67</v>
       </c>
       <c r="B313" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="C313" s="2">
         <v>46387</v>
@@ -9775,24 +9775,24 @@
         <v>12</v>
       </c>
       <c r="F313" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G313">
-        <v>33364.614089900009</v>
+        <v>15.7</v>
       </c>
       <c r="H313">
-        <v>32363.67566720301</v>
+        <v>15.2</v>
       </c>
       <c r="I313">
-        <v>34556.673694232348</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A314">
-        <v>376</v>
+      <c r="A314" t="s">
+        <v>67</v>
       </c>
       <c r="B314" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="C314" s="2">
         <v>46752</v>
@@ -9804,24 +9804,24 @@
         <v>14</v>
       </c>
       <c r="F314" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G314">
-        <v>36512.365153479492</v>
+        <v>16.3</v>
       </c>
       <c r="H314">
-        <v>35384.133070236967</v>
+        <v>15.8</v>
       </c>
       <c r="I314">
-        <v>37856.02412414951</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A315">
-        <v>376</v>
+      <c r="A315" t="s">
+        <v>67</v>
       </c>
       <c r="B315" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="C315" s="2">
         <v>47118</v>
@@ -9833,24 +9833,24 @@
         <v>16</v>
       </c>
       <c r="F315" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G315">
-        <v>40167.943620047838</v>
+        <v>16.8</v>
       </c>
       <c r="H315">
-        <v>38890.603012930333</v>
+        <v>16.3</v>
       </c>
       <c r="I315">
-        <v>41689.182193960667</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A316">
-        <v>376</v>
+      <c r="A316" t="s">
+        <v>67</v>
       </c>
       <c r="B316" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="C316" s="2">
         <v>47483</v>
@@ -9862,24 +9862,24 @@
         <v>18</v>
       </c>
       <c r="F316" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G316">
-        <v>44331.349489605069</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="H316">
-        <v>42881.71436129498</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="I316">
-        <v>46057.780844716202</v>
+        <v>17.899999999999999</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A317">
-        <v>376</v>
+      <c r="A317" t="s">
+        <v>67</v>
       </c>
       <c r="B317" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="C317" s="2">
         <v>47848</v>
@@ -9891,24 +9891,24 @@
         <v>20</v>
       </c>
       <c r="F317" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G317">
-        <v>49002.582762151171</v>
+        <v>18</v>
       </c>
       <c r="H317">
-        <v>47356.095981342893</v>
+        <v>17.5</v>
       </c>
       <c r="I317">
-        <v>50963.453017466447</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A318">
-        <v>466</v>
+      <c r="A318" t="s">
+        <v>67</v>
       </c>
       <c r="B318" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C318" s="2">
         <v>46387</v>
@@ -9923,21 +9923,21 @@
         <v>25</v>
       </c>
       <c r="G318">
-        <v>58.919999999999987</v>
+        <v>15.7</v>
       </c>
       <c r="H318">
-        <v>57.152399999902997</v>
+        <v>15.2</v>
       </c>
       <c r="I318">
-        <v>60.742268041340189</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A319">
-        <v>466</v>
+      <c r="A319" t="s">
+        <v>67</v>
       </c>
       <c r="B319" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C319" s="2">
         <v>46752</v>
@@ -9952,21 +9952,21 @@
         <v>25</v>
       </c>
       <c r="G319">
-        <v>60.687600000000003</v>
+        <v>16.3</v>
       </c>
       <c r="H319">
-        <v>58.812353159905193</v>
+        <v>15.8</v>
       </c>
       <c r="I319">
-        <v>62.622639562581618</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A320">
-        <v>466</v>
+      <c r="A320" t="s">
+        <v>67</v>
       </c>
       <c r="B320" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C320" s="2">
         <v>47118</v>
@@ -9981,21 +9981,21 @@
         <v>25</v>
       </c>
       <c r="G320">
-        <v>62.508228000000003</v>
+        <v>16.8</v>
       </c>
       <c r="H320">
-        <v>60.520466349507103</v>
+        <v>16.3</v>
       </c>
       <c r="I320">
-        <v>64.561276595843793</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A321">
-        <v>466</v>
+      <c r="A321" t="s">
+        <v>67</v>
       </c>
       <c r="B321" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C321" s="2">
         <v>47483</v>
@@ -10010,21 +10010,21 @@
         <v>25</v>
       </c>
       <c r="G321">
-        <v>64.383474839999991</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="H321">
-        <v>62.27813521264077</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="I321">
-        <v>66.559986395217919</v>
+        <v>17.899999999999999</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A322">
-        <v>466</v>
+      <c r="A322" t="s">
+        <v>67</v>
       </c>
       <c r="B322" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C322" s="2">
         <v>47848</v>
@@ -10039,21 +10039,21 @@
         <v>25</v>
       </c>
       <c r="G322">
-        <v>66.314979085199994</v>
+        <v>18</v>
       </c>
       <c r="H322">
-        <v>64.086795787847493</v>
+        <v>17.5</v>
       </c>
       <c r="I322">
-        <v>68.620632331635861</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A323">
-        <v>466</v>
+      <c r="A323" t="s">
+        <v>68</v>
       </c>
       <c r="B323" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C323" s="2">
         <v>46387</v>
@@ -10065,24 +10065,24 @@
         <v>12</v>
       </c>
       <c r="F323" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G323">
-        <v>56.235212373037847</v>
+        <v>34.965000000000003</v>
       </c>
       <c r="H323">
-        <v>54.54815600174971</v>
+        <v>32.813568677938846</v>
       </c>
       <c r="I323">
-        <v>57.97444574550294</v>
+        <v>41.957999999999991</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A324">
-        <v>466</v>
+      <c r="A324" t="s">
+        <v>68</v>
       </c>
       <c r="B324" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C324" s="2">
         <v>46752</v>
@@ -10094,24 +10094,24 @@
         <v>14</v>
       </c>
       <c r="F324" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G324">
-        <v>57.922268744228987</v>
+        <v>36.713250000000002</v>
       </c>
       <c r="H324">
-        <v>56.132470639937168</v>
+        <v>34.386477025190871</v>
       </c>
       <c r="I324">
-        <v>59.769135016331823</v>
+        <v>44.276179499999998</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A325">
-        <v>466</v>
+      <c r="A325" t="s">
+        <v>68</v>
       </c>
       <c r="B325" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C325" s="2">
         <v>47118</v>
@@ -10123,24 +10123,24 @@
         <v>16</v>
       </c>
       <c r="F325" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G325">
-        <v>59.659936806555862</v>
+        <v>38.548912499999993</v>
       </c>
       <c r="H325">
-        <v>57.762750816014403</v>
+        <v>36.03464228547324</v>
       </c>
       <c r="I325">
-        <v>61.619434834385345</v>
+        <v>46.721281949999991</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A326">
-        <v>466</v>
+      <c r="A326" t="s">
+        <v>68</v>
       </c>
       <c r="B326" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C326" s="2">
         <v>47483</v>
@@ -10152,24 +10152,24 @@
         <v>18</v>
       </c>
       <c r="F326" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G326">
-        <v>61.449734910752539</v>
+        <v>40.476358124999997</v>
       </c>
       <c r="H326">
-        <v>59.440328579080322</v>
+        <v>37.76165787922087</v>
       </c>
       <c r="I326">
-        <v>63.527070103221561</v>
+        <v>49.300204196249993</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A327">
-        <v>466</v>
+      <c r="A327" t="s">
+        <v>68</v>
       </c>
       <c r="B327" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C327" s="2">
         <v>47848</v>
@@ -10181,24 +10181,24 @@
         <v>20</v>
       </c>
       <c r="F327" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G327">
-        <v>63.293226958075117</v>
+        <v>42.50017603125</v>
       </c>
       <c r="H327">
-        <v>61.166574532195703</v>
+        <v>39.571288426629593</v>
       </c>
       <c r="I327">
-        <v>65.493819286181989</v>
+        <v>52.020215462249993</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A328">
-        <v>96</v>
+        <v>332</v>
       </c>
       <c r="B328" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C328" s="2">
         <v>46387</v>
@@ -10210,24 +10210,24 @@
         <v>12</v>
       </c>
       <c r="F328" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="G328">
-        <v>846.88288415165562</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="H328">
-        <v>703.52841169356259</v>
+        <v>0.79122857142857139</v>
       </c>
       <c r="I328">
-        <v>990.23735660954856</v>
+        <v>0.69049565217391329</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A329">
-        <v>96</v>
+        <v>332</v>
       </c>
       <c r="B329" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C329" s="2">
         <v>46752</v>
@@ -10239,24 +10239,24 @@
         <v>14</v>
       </c>
       <c r="F329" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="G329">
-        <v>914.63351488378817</v>
+        <v>0.6885</v>
       </c>
       <c r="H329">
-        <v>755.16599972142001</v>
+        <v>0.71281388571428561</v>
       </c>
       <c r="I329">
-        <v>1074.101030045967</v>
+        <v>0.61943446956521764</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A330">
-        <v>96</v>
+        <v>332</v>
       </c>
       <c r="B330" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C330" s="2">
         <v>47118</v>
@@ -10268,24 +10268,24 @@
         <v>16</v>
       </c>
       <c r="F330" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="G330">
-        <v>987.8041960744913</v>
+        <v>0.61965000000000003</v>
       </c>
       <c r="H330">
-        <v>810.56301999889411</v>
+        <v>0.64216985142857141</v>
       </c>
       <c r="I330">
-        <v>1165.04537214991</v>
+        <v>0.5556805669565219</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A331">
-        <v>96</v>
+        <v>332</v>
       </c>
       <c r="B331" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C331" s="2">
         <v>47483</v>
@@ -10297,24 +10297,24 @@
         <v>18</v>
       </c>
       <c r="F331" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="G331">
-        <v>1066.8285317604509</v>
+        <v>0.55768499999999999</v>
       </c>
       <c r="H331">
-        <v>869.9905011225452</v>
+        <v>0.57852648514285721</v>
       </c>
       <c r="I331">
-        <v>1263.666562398188</v>
+        <v>0.49848310017391317</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A332">
-        <v>96</v>
+        <v>332</v>
       </c>
       <c r="B332" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C332" s="2">
         <v>47848</v>
@@ -10326,285 +10326,285 @@
         <v>20</v>
       </c>
       <c r="F332" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="G332">
-        <v>1152.1748143012869</v>
+        <v>0.5019165000000001</v>
       </c>
       <c r="H332">
-        <v>933.73877589798656</v>
+        <v>0.52119009360000013</v>
       </c>
       <c r="I332">
-        <v>1370.6108527044289</v>
+        <v>0.4471683210782611</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B333" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="C333" s="2">
-        <v>46387</v>
+        <v>46203</v>
       </c>
       <c r="D333">
         <v>2026</v>
       </c>
       <c r="E333" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F333" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="G333">
-        <v>15.7</v>
+        <v>55894.216286956827</v>
       </c>
       <c r="H333">
-        <v>15.2</v>
+        <v>52633.364136739263</v>
       </c>
       <c r="I333">
-        <v>16.2</v>
+        <v>59434.099703060769</v>
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B334" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="C334" s="2">
-        <v>46752</v>
+        <v>46387</v>
       </c>
       <c r="D334">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E334" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F334" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="G334">
-        <v>16.3</v>
+        <v>56228.497834688897</v>
       </c>
       <c r="H334">
-        <v>15.8</v>
+        <v>52849.733176102003</v>
       </c>
       <c r="I334">
-        <v>16.8</v>
+        <v>59896.38353783304</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B335" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="C335" s="2">
-        <v>47118</v>
+        <v>46568</v>
       </c>
       <c r="D335">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E335" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F335" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="G335">
-        <v>16.8</v>
+        <v>56937.735204384422</v>
       </c>
       <c r="H335">
-        <v>16.3</v>
+        <v>53416.700622997058</v>
       </c>
       <c r="I335">
-        <v>17.3</v>
+        <v>60760.064874053744</v>
       </c>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B336" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="C336" s="2">
-        <v>47483</v>
+        <v>46752</v>
       </c>
       <c r="D336">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="E336" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F336" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="G336">
-        <v>17.399999999999999</v>
+        <v>57359.757865754007</v>
       </c>
       <c r="H336">
-        <v>16.899999999999999</v>
+        <v>53712.234823202583</v>
       </c>
       <c r="I336">
-        <v>17.899999999999999</v>
+        <v>61319.39961992656</v>
       </c>
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B337" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="C337" s="2">
-        <v>47848</v>
+        <v>46934</v>
       </c>
       <c r="D337">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="E337" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F337" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="G337">
-        <v>18</v>
+        <v>58148.528487435011</v>
       </c>
       <c r="H337">
-        <v>17.5</v>
+        <v>54349.076258639267</v>
       </c>
       <c r="I337">
-        <v>18.3</v>
+        <v>62273.100015186057</v>
       </c>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B338" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="C338" s="2">
-        <v>46387</v>
+        <v>47118</v>
       </c>
       <c r="D338">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="E338" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F338" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G338">
-        <v>15.7</v>
+        <v>58676.177343389703</v>
       </c>
       <c r="H338">
-        <v>15.2</v>
+        <v>54739.553761700852</v>
       </c>
       <c r="I338">
-        <v>16.2</v>
+        <v>62949.657982901139</v>
       </c>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B339" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="C339" s="2">
-        <v>46752</v>
+        <v>47299</v>
       </c>
       <c r="D339">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="E339" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F339" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G339">
-        <v>16.3</v>
+        <v>59565.317653089878</v>
       </c>
       <c r="H339">
-        <v>15.8</v>
+        <v>55464.79036566284</v>
       </c>
       <c r="I339">
-        <v>16.8</v>
+        <v>64016.727245848073</v>
       </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B340" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="C340" s="2">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="D340">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E340" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F340" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G340">
-        <v>16.8</v>
+        <v>60218.948763961882</v>
       </c>
       <c r="H340">
-        <v>16.3</v>
+        <v>55968.030280039573</v>
       </c>
       <c r="I340">
-        <v>17.3</v>
+        <v>64833.618534697212</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B341" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="C341" s="2">
-        <v>47483</v>
+        <v>47664</v>
       </c>
       <c r="D341">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E341" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F341" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G341">
-        <v>17.399999999999999</v>
+        <v>61232.239830473409</v>
       </c>
       <c r="H341">
-        <v>16.899999999999999</v>
+        <v>56802.623945673287</v>
       </c>
       <c r="I341">
-        <v>17.899999999999999</v>
+        <v>66040.898146756881</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B342" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="C342" s="2">
         <v>47848</v>
@@ -10616,285 +10616,285 @@
         <v>20</v>
       </c>
       <c r="F342" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G342">
-        <v>18</v>
+        <v>62035.469907580176</v>
       </c>
       <c r="H342">
-        <v>17.5</v>
+        <v>57439.173434127872</v>
       </c>
       <c r="I342">
-        <v>18.2</v>
+        <v>67025.07167802086</v>
       </c>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B343" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C343" s="2">
-        <v>46387</v>
+        <v>46203</v>
       </c>
       <c r="D343">
         <v>2026</v>
       </c>
       <c r="E343" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F343" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G343">
-        <v>34.965000000000003</v>
+        <v>8721.2600990757528</v>
       </c>
       <c r="H343">
-        <v>32.813568677938846</v>
+        <v>8212.4643481759558</v>
       </c>
       <c r="I343">
-        <v>41.957999999999991</v>
+        <v>9273.5935253778844</v>
       </c>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B344" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C344" s="2">
-        <v>46752</v>
+        <v>46387</v>
       </c>
       <c r="D344">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E344" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F344" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G344">
-        <v>36.713250000000002</v>
+        <v>8773.4185605009152</v>
       </c>
       <c r="H344">
-        <v>34.386477025190871</v>
+        <v>8246.2247404852751</v>
       </c>
       <c r="I344">
-        <v>44.276179499999998</v>
+        <v>9345.7243795247377</v>
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B345" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C345" s="2">
-        <v>47118</v>
+        <v>46568</v>
       </c>
       <c r="D345">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E345" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F345" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G345">
-        <v>38.548912499999993</v>
+        <v>8884.0819526011546</v>
       </c>
       <c r="H345">
-        <v>36.03464228547324</v>
+        <v>8334.6895388231787</v>
       </c>
       <c r="I345">
-        <v>46.721281949999991</v>
+        <v>9480.4859000589404</v>
       </c>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B346" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C346" s="2">
-        <v>47483</v>
+        <v>46752</v>
       </c>
       <c r="D346">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="E346" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F346" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G346">
-        <v>40.476358124999997</v>
+        <v>8949.9307942525447</v>
       </c>
       <c r="H346">
-        <v>37.76165787922087</v>
+        <v>8380.8021923208544</v>
       </c>
       <c r="I346">
-        <v>49.300204196249993</v>
+        <v>9567.7597563764448</v>
       </c>
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B347" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C347" s="2">
-        <v>47848</v>
+        <v>46934</v>
       </c>
       <c r="D347">
+        <v>2028</v>
+      </c>
+      <c r="E347" t="s">
+        <v>15</v>
+      </c>
+      <c r="F347" t="s">
+        <v>11</v>
+      </c>
+      <c r="G347">
+        <v>9073.0038813654046</v>
+      </c>
+      <c r="H347">
+        <v>8480.1695360152007</v>
+      </c>
+      <c r="I347">
+        <v>9716.5670884436513</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A348" t="s">
+        <v>75</v>
+      </c>
+      <c r="B348" t="s">
+        <v>62</v>
+      </c>
+      <c r="C348" s="2">
+        <v>47118</v>
+      </c>
+      <c r="D348">
+        <v>2028</v>
+      </c>
+      <c r="E348" t="s">
+        <v>16</v>
+      </c>
+      <c r="F348" t="s">
+        <v>11</v>
+      </c>
+      <c r="G348">
+        <v>9155.3337397918185</v>
+      </c>
+      <c r="H348">
+        <v>8541.0963383439848</v>
+      </c>
+      <c r="I348">
+        <v>9822.1314634454029</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A349" t="s">
+        <v>75</v>
+      </c>
+      <c r="B349" t="s">
+        <v>62</v>
+      </c>
+      <c r="C349" s="2">
+        <v>47299</v>
+      </c>
+      <c r="D349">
+        <v>2029</v>
+      </c>
+      <c r="E349" t="s">
+        <v>17</v>
+      </c>
+      <c r="F349" t="s">
+        <v>11</v>
+      </c>
+      <c r="G349">
+        <v>9294.0676629164827</v>
+      </c>
+      <c r="H349">
+        <v>8654.2561154495597</v>
+      </c>
+      <c r="I349">
+        <v>9988.6279134199758</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A350" t="s">
+        <v>75</v>
+      </c>
+      <c r="B350" t="s">
+        <v>62</v>
+      </c>
+      <c r="C350" s="2">
+        <v>47483</v>
+      </c>
+      <c r="D350">
+        <v>2029</v>
+      </c>
+      <c r="E350" t="s">
+        <v>18</v>
+      </c>
+      <c r="F350" t="s">
+        <v>11</v>
+      </c>
+      <c r="G350">
+        <v>9396.0547253613113</v>
+      </c>
+      <c r="H350">
+        <v>8732.7774093699172</v>
+      </c>
+      <c r="I350">
+        <v>10116.088711262581</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A351" t="s">
+        <v>75</v>
+      </c>
+      <c r="B351" t="s">
+        <v>62</v>
+      </c>
+      <c r="C351" s="2">
+        <v>47664</v>
+      </c>
+      <c r="D351">
         <v>2030</v>
       </c>
-      <c r="E347" t="s">
-        <v>20</v>
-      </c>
-      <c r="F347" t="s">
-        <v>25</v>
-      </c>
-      <c r="G347">
-        <v>42.50017603125</v>
-      </c>
-      <c r="H347">
-        <v>39.571288426629593</v>
-      </c>
-      <c r="I347">
-        <v>52.020215462249993</v>
-      </c>
-    </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A348">
-        <v>332</v>
-      </c>
-      <c r="B348" t="s">
-        <v>44</v>
-      </c>
-      <c r="C348" s="2">
-        <v>46387</v>
-      </c>
-      <c r="D348">
-        <v>2026</v>
-      </c>
-      <c r="E348" t="s">
-        <v>12</v>
-      </c>
-      <c r="F348" t="s">
-        <v>28</v>
-      </c>
-      <c r="G348">
-        <v>0.76500000000000001</v>
-      </c>
-      <c r="H348">
-        <v>0.79122857142857139</v>
-      </c>
-      <c r="I348">
-        <v>0.69049565217391329</v>
-      </c>
-    </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A349">
-        <v>332</v>
-      </c>
-      <c r="B349" t="s">
-        <v>44</v>
-      </c>
-      <c r="C349" s="2">
-        <v>46752</v>
-      </c>
-      <c r="D349">
-        <v>2027</v>
-      </c>
-      <c r="E349" t="s">
-        <v>14</v>
-      </c>
-      <c r="F349" t="s">
-        <v>28</v>
-      </c>
-      <c r="G349">
-        <v>0.6885</v>
-      </c>
-      <c r="H349">
-        <v>0.71281388571428561</v>
-      </c>
-      <c r="I349">
-        <v>0.61943446956521764</v>
-      </c>
-    </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A350">
-        <v>332</v>
-      </c>
-      <c r="B350" t="s">
-        <v>44</v>
-      </c>
-      <c r="C350" s="2">
-        <v>47118</v>
-      </c>
-      <c r="D350">
-        <v>2028</v>
-      </c>
-      <c r="E350" t="s">
-        <v>16</v>
-      </c>
-      <c r="F350" t="s">
-        <v>28</v>
-      </c>
-      <c r="G350">
-        <v>0.61965000000000003</v>
-      </c>
-      <c r="H350">
-        <v>0.64216985142857141</v>
-      </c>
-      <c r="I350">
-        <v>0.5556805669565219</v>
-      </c>
-    </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A351">
-        <v>332</v>
-      </c>
-      <c r="B351" t="s">
-        <v>44</v>
-      </c>
-      <c r="C351" s="2">
-        <v>47483</v>
-      </c>
-      <c r="D351">
-        <v>2029</v>
-      </c>
       <c r="E351" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F351" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G351">
-        <v>0.55768499999999999</v>
+        <v>9554.1600810522741</v>
       </c>
       <c r="H351">
-        <v>0.57852648514285721</v>
+        <v>8863.0003361511826</v>
       </c>
       <c r="I351">
-        <v>0.49848310017391317</v>
+        <v>10304.462396565341</v>
       </c>
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A352">
-        <v>332</v>
+      <c r="A352" t="s">
+        <v>75</v>
       </c>
       <c r="B352" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="C352" s="2">
         <v>47848</v>
@@ -10906,24 +10906,24 @@
         <v>20</v>
       </c>
       <c r="F352" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G352">
-        <v>0.5019165000000001</v>
+        <v>9679.4892991217203</v>
       </c>
       <c r="H352">
-        <v>0.52119009360000013</v>
+        <v>8962.32212691116</v>
       </c>
       <c r="I352">
-        <v>0.4471683210782611</v>
+        <v>10458.02449867468</v>
       </c>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B353" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="C353" s="2">
         <v>46203</v>
@@ -10938,21 +10938,21 @@
         <v>11</v>
       </c>
       <c r="G353">
-        <v>55894.216286956827</v>
+        <v>47172.956187881093</v>
       </c>
       <c r="H353">
-        <v>52633.364136739263</v>
+        <v>44420.899788563307</v>
       </c>
       <c r="I353">
-        <v>59434.099703060769</v>
+        <v>50160.506177682902</v>
       </c>
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B354" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="C354" s="2">
         <v>46387</v>
@@ -10967,21 +10967,21 @@
         <v>11</v>
       </c>
       <c r="G354">
-        <v>56228.497834688897</v>
+        <v>47455.079274187992</v>
       </c>
       <c r="H354">
-        <v>52849.733176102003</v>
+        <v>44603.508435616743</v>
       </c>
       <c r="I354">
-        <v>59896.38353783304</v>
+        <v>50550.659158308314</v>
       </c>
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B355" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="C355" s="2">
         <v>46568</v>
@@ -10996,21 +10996,21 @@
         <v>11</v>
       </c>
       <c r="G355">
-        <v>56937.735204384422</v>
+        <v>48053.653251783267</v>
       </c>
       <c r="H355">
-        <v>53416.700622997058</v>
+        <v>45082.011084173893</v>
       </c>
       <c r="I355">
-        <v>60760.064874053744</v>
+        <v>51279.578973994801</v>
       </c>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B356" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="C356" s="2">
         <v>46752</v>
@@ -11025,21 +11025,21 @@
         <v>11</v>
       </c>
       <c r="G356">
-        <v>57359.757865754007</v>
+        <v>48409.827071501481</v>
       </c>
       <c r="H356">
-        <v>53712.234823202583</v>
+        <v>45331.432630881733</v>
       </c>
       <c r="I356">
-        <v>61319.39961992656</v>
+        <v>51751.639863550117</v>
       </c>
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B357" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="C357" s="2">
         <v>46934</v>
@@ -11054,21 +11054,21 @@
         <v>11</v>
       </c>
       <c r="G357">
-        <v>58148.528487435011</v>
+        <v>49075.524606069623</v>
       </c>
       <c r="H357">
-        <v>54349.076258639267</v>
+        <v>45868.90672262408</v>
       </c>
       <c r="I357">
-        <v>62273.100015186057</v>
+        <v>52556.532926742417</v>
       </c>
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B358" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="C358" s="2">
         <v>47118</v>
@@ -11083,21 +11083,21 @@
         <v>11</v>
       </c>
       <c r="G358">
-        <v>58676.177343389703</v>
+        <v>49520.843603597888</v>
       </c>
       <c r="H358">
-        <v>54739.553761700852</v>
+        <v>46198.457423356878</v>
       </c>
       <c r="I358">
-        <v>62949.657982901139</v>
+        <v>53127.526519455743</v>
       </c>
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B359" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="C359" s="2">
         <v>47299</v>
@@ -11112,21 +11112,21 @@
         <v>11</v>
       </c>
       <c r="G359">
-        <v>59565.317653089878</v>
+        <v>50271.249990173397</v>
       </c>
       <c r="H359">
-        <v>55464.79036566284</v>
+        <v>46810.534250213277</v>
       </c>
       <c r="I359">
-        <v>64016.727245848073</v>
+        <v>54028.099332428108</v>
       </c>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B360" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="C360" s="2">
         <v>47483</v>
@@ -11141,21 +11141,21 @@
         <v>11</v>
       </c>
       <c r="G360">
-        <v>60218.948763961882</v>
+        <v>50822.894038600578</v>
       </c>
       <c r="H360">
-        <v>55968.030280039573</v>
+        <v>47235.252870669661</v>
       </c>
       <c r="I360">
-        <v>64833.618534697212</v>
+        <v>54717.529823434626</v>
       </c>
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B361" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="C361" s="2">
         <v>47664</v>
@@ -11170,21 +11170,21 @@
         <v>11</v>
       </c>
       <c r="G361">
-        <v>61232.239830473409</v>
+        <v>51678.079749421137</v>
       </c>
       <c r="H361">
-        <v>56802.623945673287</v>
+        <v>47939.62360952211</v>
       </c>
       <c r="I361">
-        <v>66040.898146756881</v>
+        <v>55736.435750191551</v>
       </c>
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B362" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="C362" s="2">
         <v>47848</v>
@@ -11199,21 +11199,21 @@
         <v>11</v>
       </c>
       <c r="G362">
-        <v>62035.469907580176</v>
+        <v>52355.980608458471</v>
       </c>
       <c r="H362">
-        <v>57439.173434127872</v>
+        <v>48476.851307216719</v>
       </c>
       <c r="I362">
-        <v>67025.07167802086</v>
+        <v>56567.047179346191</v>
       </c>
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B363" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C363" s="2">
         <v>46203</v>
@@ -11228,543 +11228,543 @@
         <v>11</v>
       </c>
       <c r="G363">
-        <v>8721.2600990757528</v>
+        <v>12537.131244690319</v>
       </c>
       <c r="H363">
-        <v>8212.4643481759558</v>
+        <v>11805.718692684501</v>
       </c>
       <c r="I363">
-        <v>9273.5935253778844</v>
+        <v>13331.13080183151</v>
       </c>
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B364" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C364" s="2">
-        <v>46387</v>
+        <v>46203</v>
       </c>
       <c r="D364">
         <v>2026</v>
       </c>
       <c r="E364" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F364" t="s">
         <v>11</v>
       </c>
       <c r="G364">
-        <v>8773.4185605009152</v>
+        <v>43357.26636981326</v>
       </c>
       <c r="H364">
-        <v>8246.2247404852751</v>
+        <v>40827.816193005718</v>
       </c>
       <c r="I364">
-        <v>9345.7243795247377</v>
+        <v>46103.161712582711</v>
       </c>
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B365" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C365" s="2">
-        <v>46568</v>
+        <v>46387</v>
       </c>
       <c r="D365">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E365" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F365" t="s">
         <v>11</v>
       </c>
       <c r="G365">
-        <v>8884.0819526011546</v>
+        <v>12612.110945900889</v>
       </c>
       <c r="H365">
-        <v>8334.6895388231787</v>
+        <v>11854.25049479175</v>
       </c>
       <c r="I365">
-        <v>9480.4859000589404</v>
+        <v>13434.821550067139</v>
       </c>
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B366" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C366" s="2">
-        <v>46752</v>
+        <v>46387</v>
       </c>
       <c r="D366">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E366" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F366" t="s">
         <v>11</v>
       </c>
       <c r="G366">
-        <v>8949.9307942525447</v>
+        <v>43616.569300784227</v>
       </c>
       <c r="H366">
-        <v>8380.8021923208544</v>
+        <v>40995.654132188363</v>
       </c>
       <c r="I366">
-        <v>9567.7597563764448</v>
+        <v>46461.756298823602</v>
       </c>
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B367" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C367" s="2">
-        <v>46934</v>
+        <v>46568</v>
       </c>
       <c r="D367">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E367" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F367" t="s">
         <v>11</v>
       </c>
       <c r="G367">
-        <v>9073.0038813654046</v>
+        <v>12771.193630625579</v>
       </c>
       <c r="H367">
-        <v>8480.1695360152007</v>
+        <v>11981.421886849521</v>
       </c>
       <c r="I367">
-        <v>9716.5670884436513</v>
+        <v>13628.54617821467</v>
       </c>
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B368" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C368" s="2">
-        <v>47118</v>
+        <v>46568</v>
       </c>
       <c r="D368">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E368" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F368" t="s">
         <v>11</v>
       </c>
       <c r="G368">
-        <v>9155.3337397918185</v>
+        <v>44166.726286606223</v>
       </c>
       <c r="H368">
-        <v>8541.0963383439848</v>
+        <v>41435.452026336097</v>
       </c>
       <c r="I368">
-        <v>9822.1314634454029</v>
+        <v>47131.71580878269</v>
       </c>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B369" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C369" s="2">
-        <v>47299</v>
+        <v>46752</v>
       </c>
       <c r="D369">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="E369" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F369" t="s">
         <v>11</v>
       </c>
       <c r="G369">
-        <v>9294.0676629164827</v>
+        <v>12865.853755506139</v>
       </c>
       <c r="H369">
-        <v>8654.2561154495597</v>
+        <v>12047.710517434291</v>
       </c>
       <c r="I369">
-        <v>9988.6279134199758</v>
+        <v>13754.005547440311</v>
       </c>
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B370" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C370" s="2">
-        <v>47483</v>
+        <v>46752</v>
       </c>
       <c r="D370">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="E370" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F370" t="s">
         <v>11</v>
       </c>
       <c r="G370">
-        <v>9396.0547253613113</v>
+        <v>44494.090192187417</v>
       </c>
       <c r="H370">
-        <v>8732.7774093699172</v>
+        <v>41664.698554705283</v>
       </c>
       <c r="I370">
-        <v>10116.088711262581</v>
+        <v>47565.59299997893</v>
       </c>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B371" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C371" s="2">
-        <v>47664</v>
+        <v>46934</v>
       </c>
       <c r="D371">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="E371" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F371" t="s">
         <v>11</v>
       </c>
       <c r="G371">
-        <v>9554.1600810522741</v>
+        <v>13042.775831937121</v>
       </c>
       <c r="H371">
-        <v>8863.0003361511826</v>
+        <v>12190.55471829286</v>
       </c>
       <c r="I371">
-        <v>10304.462396565341</v>
+        <v>13967.92154479676</v>
       </c>
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B372" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C372" s="2">
-        <v>47848</v>
+        <v>46934</v>
       </c>
       <c r="D372">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="E372" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F372" t="s">
         <v>11</v>
       </c>
       <c r="G372">
-        <v>9679.4892991217203</v>
+        <v>45105.941296304023</v>
       </c>
       <c r="H372">
-        <v>8962.32212691116</v>
+        <v>42158.697855273451</v>
       </c>
       <c r="I372">
-        <v>10458.02449867468</v>
+        <v>48305.380491800541</v>
       </c>
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B373" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C373" s="2">
-        <v>46203</v>
+        <v>47118</v>
       </c>
       <c r="D373">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="E373" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F373" t="s">
         <v>11</v>
       </c>
       <c r="G373">
-        <v>47172.956187881093</v>
+        <v>13161.128022873159</v>
       </c>
       <c r="H373">
-        <v>44420.899788563307</v>
+        <v>12278.13923113135</v>
       </c>
       <c r="I373">
-        <v>50160.506177682902</v>
+        <v>14119.6742054359</v>
       </c>
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B374" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C374" s="2">
-        <v>46387</v>
+        <v>47118</v>
       </c>
       <c r="D374">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="E374" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F374" t="s">
         <v>11</v>
       </c>
       <c r="G374">
-        <v>47455.079274187992</v>
+        <v>45515.239673078882</v>
       </c>
       <c r="H374">
-        <v>44603.508435616743</v>
+        <v>42461.592112252431</v>
       </c>
       <c r="I374">
-        <v>50550.659158308314</v>
+        <v>48830.187993711741</v>
       </c>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B375" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C375" s="2">
-        <v>46568</v>
+        <v>47299</v>
       </c>
       <c r="D375">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="E375" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F375" t="s">
         <v>11</v>
       </c>
       <c r="G375">
-        <v>48053.653251783267</v>
+        <v>13360.563125432371</v>
       </c>
       <c r="H375">
-        <v>45082.011084173893</v>
+        <v>12440.810560856149</v>
       </c>
       <c r="I375">
-        <v>51279.578973994801</v>
+        <v>14359.01895853269</v>
       </c>
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B376" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C376" s="2">
-        <v>46752</v>
+        <v>47299</v>
       </c>
       <c r="D376">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="E376" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F376" t="s">
         <v>11</v>
       </c>
       <c r="G376">
-        <v>48409.827071501481</v>
+        <v>46204.947764697747</v>
       </c>
       <c r="H376">
-        <v>45331.432630881733</v>
+        <v>43024.159739244213</v>
       </c>
       <c r="I376">
-        <v>51751.639863550117</v>
+        <v>49657.915965262648</v>
       </c>
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B377" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C377" s="2">
-        <v>46934</v>
+        <v>47483</v>
       </c>
       <c r="D377">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E377" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F377" t="s">
         <v>11</v>
       </c>
       <c r="G377">
-        <v>49075.524606069623</v>
+        <v>13507.173268072969</v>
       </c>
       <c r="H377">
-        <v>45868.90672262408</v>
+        <v>12553.687800635609</v>
       </c>
       <c r="I377">
-        <v>52556.532926742417</v>
+        <v>14542.248530057001</v>
       </c>
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B378" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C378" s="2">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="D378">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E378" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F378" t="s">
         <v>11</v>
       </c>
       <c r="G378">
-        <v>49520.843603597888</v>
+        <v>46711.970853386927</v>
       </c>
       <c r="H378">
-        <v>46198.457423356878</v>
+        <v>43414.524046412167</v>
       </c>
       <c r="I378">
-        <v>53127.526519455743</v>
+        <v>50291.580332680867</v>
       </c>
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B379" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C379" s="2">
-        <v>47299</v>
+        <v>47664</v>
       </c>
       <c r="D379">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E379" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F379" t="s">
         <v>11</v>
       </c>
       <c r="G379">
-        <v>50271.249990173397</v>
+        <v>13734.45551539364</v>
       </c>
       <c r="H379">
-        <v>46810.534250213277</v>
+        <v>12740.888033810341</v>
       </c>
       <c r="I379">
-        <v>54028.099332428108</v>
+        <v>14813.042611285809</v>
       </c>
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B380" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C380" s="2">
-        <v>47483</v>
+        <v>47664</v>
       </c>
       <c r="D380">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E380" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F380" t="s">
         <v>11</v>
       </c>
       <c r="G380">
-        <v>50822.894038600578</v>
+        <v>47497.982959815643</v>
       </c>
       <c r="H380">
-        <v>47235.252870669661</v>
+        <v>44061.920186393188</v>
       </c>
       <c r="I380">
-        <v>54717.529823434626</v>
+        <v>51228.06978007171</v>
       </c>
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B381" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C381" s="2">
-        <v>47664</v>
+        <v>47848</v>
       </c>
       <c r="D381">
         <v>2030</v>
       </c>
       <c r="E381" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F381" t="s">
         <v>11</v>
       </c>
       <c r="G381">
-        <v>51678.079749421137</v>
+        <v>13914.62086281833</v>
       </c>
       <c r="H381">
-        <v>47939.62360952211</v>
+        <v>12883.666750655109</v>
       </c>
       <c r="I381">
-        <v>55736.435750191551</v>
+        <v>15033.79376495904</v>
       </c>
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B382" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C382" s="2">
         <v>47848</v>
@@ -11779,166 +11779,166 @@
         <v>11</v>
       </c>
       <c r="G382">
-        <v>52355.980608458471</v>
+        <v>48121.0502952725</v>
       </c>
       <c r="H382">
-        <v>48476.851307216719</v>
+        <v>44555.693023045947</v>
       </c>
       <c r="I382">
-        <v>56567.047179346191</v>
+        <v>51991.495350439531</v>
       </c>
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B383" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C383" s="2">
-        <v>46203</v>
+        <v>46387</v>
       </c>
       <c r="D383">
         <v>2026</v>
       </c>
       <c r="E383" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F383" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G383">
-        <v>12537.131244690319</v>
+        <v>17370.13780255078</v>
       </c>
       <c r="H383">
-        <v>11805.718692684501</v>
+        <v>13896.11024204063</v>
       </c>
       <c r="I383">
-        <v>13331.13080183151</v>
+        <v>20844.16536306094</v>
       </c>
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B384" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C384" s="2">
-        <v>46203</v>
+        <v>46752</v>
       </c>
       <c r="D384">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E384" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F384" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G384">
-        <v>43357.26636981326</v>
+        <v>18957.986443793259</v>
       </c>
       <c r="H384">
-        <v>40827.816193005718</v>
+        <v>15052.64123637185</v>
       </c>
       <c r="I384">
-        <v>46103.161712582711</v>
+        <v>22863.33165121467</v>
       </c>
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B385" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C385" s="2">
-        <v>46203</v>
+        <v>47118</v>
       </c>
       <c r="D385">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="E385" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F385" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G385">
-        <v>51986.836747227833</v>
+        <v>20767.420529046809</v>
       </c>
       <c r="H385">
-        <v>48953.939970933527</v>
+        <v>16364.72737688889</v>
       </c>
       <c r="I385">
-        <v>55279.25863775819</v>
+        <v>25170.113681204741</v>
       </c>
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B386" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C386" s="2">
-        <v>46203</v>
+        <v>47483</v>
       </c>
       <c r="D386">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="E386" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F386" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G386">
-        <v>3907.3795397289932</v>
+        <v>22798.440058311451</v>
       </c>
       <c r="H386">
-        <v>3679.4241658057222</v>
+        <v>17828.38012559955</v>
       </c>
       <c r="I386">
-        <v>4154.841065302583</v>
+        <v>27768.499991023338</v>
       </c>
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B387" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C387" s="2">
-        <v>46387</v>
+        <v>47848</v>
       </c>
       <c r="D387">
-        <v>2026</v>
+        <v>2030</v>
       </c>
       <c r="E387" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F387" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G387">
-        <v>12612.110945900889</v>
+        <v>25051.04503158716</v>
       </c>
       <c r="H387">
-        <v>11854.25049479175</v>
+        <v>19439.610944511642</v>
       </c>
       <c r="I387">
-        <v>13434.821550067139</v>
+        <v>30662.47911866269</v>
       </c>
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B388" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C388" s="2">
         <v>46387</v>
@@ -11950,24 +11950,24 @@
         <v>12</v>
       </c>
       <c r="F388" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G388">
-        <v>43616.569300784227</v>
+        <v>3882.965030497624</v>
       </c>
       <c r="H388">
-        <v>40995.654132188363</v>
+        <v>3106.3720243981002</v>
       </c>
       <c r="I388">
-        <v>46461.756298823602</v>
+        <v>4659.5580365971491</v>
       </c>
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B389" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C389" s="2">
         <v>46387</v>
@@ -11979,24 +11979,24 @@
         <v>12</v>
       </c>
       <c r="F389" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G389">
-        <v>52297.749779093952</v>
+        <v>7993.5712202772638</v>
       </c>
       <c r="H389">
-        <v>49155.183367365782</v>
+        <v>6394.8569762218112</v>
       </c>
       <c r="I389">
-        <v>55709.225740719368</v>
+        <v>9592.2854643327155</v>
       </c>
     </row>
     <row r="390" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B390" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C390" s="2">
         <v>46387</v>
@@ -12008,430 +12008,430 @@
         <v>12</v>
       </c>
       <c r="F390" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G390">
-        <v>3930.7480555949551</v>
+        <v>5493.601551775897</v>
       </c>
       <c r="H390">
-        <v>3694.5498087362248</v>
+        <v>4394.8812414207177</v>
       </c>
       <c r="I390">
-        <v>4187.1577971136721</v>
+        <v>6592.3218621310752</v>
       </c>
     </row>
     <row r="391" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B391" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C391" s="2">
-        <v>46568</v>
+        <v>46752</v>
       </c>
       <c r="D391">
         <v>2027</v>
       </c>
       <c r="E391" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F391" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G391">
-        <v>12771.193630625579</v>
+        <v>4237.9167768655952</v>
       </c>
       <c r="H391">
-        <v>11981.421886849521</v>
+        <v>3364.9059208312819</v>
       </c>
       <c r="I391">
-        <v>13628.54617821467</v>
+        <v>5110.9276328999076</v>
       </c>
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B392" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C392" s="2">
-        <v>46568</v>
+        <v>46752</v>
       </c>
       <c r="D392">
         <v>2027</v>
       </c>
       <c r="E392" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F392" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G392">
-        <v>44166.726286606223</v>
+        <v>8724.2839725346639</v>
       </c>
       <c r="H392">
-        <v>41435.452026336097</v>
+        <v>6927.0814741925242</v>
       </c>
       <c r="I392">
-        <v>47131.71580878269</v>
+        <v>10521.486470876809</v>
       </c>
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B393" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C393" s="2">
-        <v>46568</v>
+        <v>46752</v>
       </c>
       <c r="D393">
         <v>2027</v>
       </c>
       <c r="E393" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F393" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G393">
-        <v>52957.406713258679</v>
+        <v>5995.7856943930001</v>
       </c>
       <c r="H393">
-        <v>49682.515997836963</v>
+        <v>4760.6538413480421</v>
       </c>
       <c r="I393">
-        <v>56512.529975225843</v>
+        <v>7230.9175474379581</v>
       </c>
     </row>
     <row r="394" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B394" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C394" s="2">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="D394">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E394" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F394" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G394">
-        <v>3980.3284911257451</v>
+        <v>4642.4023001179348</v>
       </c>
       <c r="H394">
-        <v>3734.184625160105</v>
+        <v>3658.2130124929331</v>
       </c>
       <c r="I394">
-        <v>4247.5348988278984</v>
+        <v>5626.591587742937</v>
       </c>
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B395" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C395" s="2">
-        <v>46752</v>
+        <v>47118</v>
       </c>
       <c r="D395">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E395" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F395" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G395">
-        <v>12865.853755506139</v>
+        <v>9556.9682260094723</v>
       </c>
       <c r="H395">
-        <v>12047.710517434291</v>
+        <v>7530.8909620954637</v>
       </c>
       <c r="I395">
-        <v>13754.005547440311</v>
+        <v>11583.045489923479</v>
       </c>
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B396" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C396" s="2">
-        <v>46752</v>
+        <v>47118</v>
       </c>
       <c r="D396">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E396" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F396" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G396">
-        <v>44494.090192187417</v>
+        <v>6568.0500029194072</v>
       </c>
       <c r="H396">
-        <v>41664.698554705283</v>
+        <v>5175.6234023004927</v>
       </c>
       <c r="I396">
-        <v>47565.59299997893</v>
+        <v>7960.4766035383218</v>
       </c>
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B397" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C397" s="2">
-        <v>46752</v>
+        <v>47483</v>
       </c>
       <c r="D397">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="E397" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F397" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G397">
-        <v>53349.9271681053</v>
+        <v>5096.4216002546455</v>
       </c>
       <c r="H397">
-        <v>49957.390380911413</v>
+        <v>3985.4016913991331</v>
       </c>
       <c r="I397">
-        <v>57032.763481523849</v>
+        <v>6207.4415091101582</v>
       </c>
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B398" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C398" s="2">
-        <v>46752</v>
+        <v>47483</v>
       </c>
       <c r="D398">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="E398" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F398" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G398">
-        <v>4009.830697648717</v>
+        <v>10491.62398070169</v>
       </c>
       <c r="H398">
-        <v>3754.844442291178</v>
+        <v>8204.4499529087188</v>
       </c>
       <c r="I398">
-        <v>4286.6361384027168</v>
+        <v>12778.79800849465</v>
       </c>
     </row>
     <row r="399" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B399" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C399" s="2">
-        <v>46934</v>
+        <v>47483</v>
       </c>
       <c r="D399">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E399" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F399" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G399">
-        <v>13042.775831937121</v>
+        <v>7210.3944773551166</v>
       </c>
       <c r="H399">
-        <v>12190.55471829286</v>
+        <v>5638.5284812917034</v>
       </c>
       <c r="I399">
-        <v>13967.92154479676</v>
+        <v>8782.2604734185334</v>
       </c>
     </row>
     <row r="400" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B400" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C400" s="2">
-        <v>46934</v>
+        <v>47848</v>
       </c>
       <c r="D400">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="E400" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F400" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G400">
-        <v>45105.941296304023</v>
+        <v>5599.9746772757262</v>
       </c>
       <c r="H400">
-        <v>42158.697855273451</v>
+        <v>4345.5803495659638</v>
       </c>
       <c r="I400">
-        <v>48305.380491800541</v>
+        <v>6854.3690049854886</v>
       </c>
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B401" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C401" s="2">
-        <v>46934</v>
+        <v>47848</v>
       </c>
       <c r="D401">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="E401" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F401" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G401">
-        <v>54083.557448022257</v>
+        <v>11528.25123661131</v>
       </c>
       <c r="H401">
-        <v>50549.712340806982</v>
+        <v>8945.9229596103742</v>
       </c>
       <c r="I401">
-        <v>57919.793840793631</v>
+        <v>14110.57951361224</v>
       </c>
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B402" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C402" s="2">
-        <v>46934</v>
+        <v>47848</v>
       </c>
       <c r="D402">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="E402" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F402" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G402">
-        <v>4064.9710394127519</v>
+        <v>7922.8191177001318</v>
       </c>
       <c r="H402">
-        <v>3799.3639178322928</v>
+        <v>6148.1076353353019</v>
       </c>
       <c r="I402">
-        <v>4353.3061743924336</v>
+        <v>9697.5306000649616</v>
       </c>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B403" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C403" s="2">
-        <v>47118</v>
+        <v>46387</v>
       </c>
       <c r="D403">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="E403" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F403" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G403">
-        <v>13161.128022873159</v>
+        <v>18662.155890000002</v>
       </c>
       <c r="H403">
-        <v>12278.13923113135</v>
+        <v>14929.724711999999</v>
       </c>
       <c r="I403">
-        <v>14119.6742054359</v>
+        <v>22394.587068000001</v>
       </c>
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B404" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C404" s="2">
-        <v>47118</v>
+        <v>46752</v>
       </c>
       <c r="D404">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E404" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F404" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G404">
-        <v>45515.239673078882</v>
+        <v>20323.6408782</v>
       </c>
       <c r="H404">
-        <v>42461.592112252431</v>
+        <v>16136.9708572908</v>
       </c>
       <c r="I404">
-        <v>48830.187993711741</v>
+        <v>24510.310899109201</v>
       </c>
     </row>
     <row r="405" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B405" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C405" s="2">
         <v>47118</v>
@@ -12443,430 +12443,430 @@
         <v>16</v>
       </c>
       <c r="F405" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G405">
-        <v>54574.320120023061</v>
+        <v>21985.125866400002</v>
       </c>
       <c r="H405">
-        <v>50912.892854885758</v>
+        <v>17324.279182723199</v>
       </c>
       <c r="I405">
-        <v>58549.055881736633</v>
+        <v>26645.9725500768</v>
       </c>
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B406" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C406" s="2">
-        <v>47118</v>
+        <v>47483</v>
       </c>
       <c r="D406">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E406" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F406" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G406">
-        <v>4101.8572233666337</v>
+        <v>23646.6108546</v>
       </c>
       <c r="H406">
-        <v>3826.6609068150929</v>
+        <v>18491.649688297199</v>
       </c>
       <c r="I406">
-        <v>4400.6021011645098</v>
+        <v>28801.5720209028</v>
       </c>
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B407" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C407" s="2">
-        <v>47299</v>
+        <v>47848</v>
       </c>
       <c r="D407">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E407" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F407" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G407">
-        <v>13360.563125432371</v>
+        <v>25308.095842800001</v>
       </c>
       <c r="H407">
-        <v>12440.810560856149</v>
+        <v>19639.0823740128</v>
       </c>
       <c r="I407">
-        <v>14359.01895853269</v>
+        <v>30977.109311587199</v>
       </c>
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B408" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C408" s="2">
-        <v>47299</v>
+        <v>46387</v>
       </c>
       <c r="D408">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="E408" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F408" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G408">
-        <v>46204.947764697747</v>
+        <v>4171.7860582501517</v>
       </c>
       <c r="H408">
-        <v>43024.159739244213</v>
+        <v>3337.4288466001221</v>
       </c>
       <c r="I408">
-        <v>49657.915965262648</v>
+        <v>5006.1432699001816</v>
       </c>
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B409" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C409" s="2">
-        <v>47299</v>
+        <v>46387</v>
       </c>
       <c r="D409">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="E409" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F409" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G409">
-        <v>55401.30357549285</v>
+        <v>8588.145582168343</v>
       </c>
       <c r="H409">
-        <v>51587.430569838638</v>
+        <v>6870.516465734675</v>
       </c>
       <c r="I409">
-        <v>59541.529866629993</v>
+        <v>10305.77469860201</v>
       </c>
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B410" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C410" s="2">
-        <v>47299</v>
+        <v>46387</v>
       </c>
       <c r="D410">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="E410" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F410" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G410">
-        <v>4164.0140775970331</v>
+        <v>5902.224249581509</v>
       </c>
       <c r="H410">
-        <v>3877.359795824203</v>
+        <v>4721.7793996652072</v>
       </c>
       <c r="I410">
-        <v>4475.1973792180906</v>
+        <v>7082.6690994978098</v>
       </c>
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B411" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C411" s="2">
-        <v>47483</v>
+        <v>46752</v>
       </c>
       <c r="D411">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="E411" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F411" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G411">
-        <v>13507.173268072969</v>
+        <v>4543.1986619503914</v>
       </c>
       <c r="H411">
-        <v>12553.687800635609</v>
+        <v>3607.2997375886112</v>
       </c>
       <c r="I411">
-        <v>14542.248530057001</v>
+        <v>5479.0975863121721</v>
       </c>
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B412" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C412" s="2">
-        <v>47483</v>
+        <v>46752</v>
       </c>
       <c r="D412">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="E412" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F412" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G412">
-        <v>46711.970853386927</v>
+        <v>9352.7450767473601</v>
       </c>
       <c r="H412">
-        <v>43414.524046412167</v>
+        <v>7426.0795909374046</v>
       </c>
       <c r="I412">
-        <v>50291.580332680867</v>
+        <v>11279.410562557319</v>
       </c>
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B413" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C413" s="2">
-        <v>47483</v>
+        <v>46752</v>
       </c>
       <c r="D413">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="E413" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F413" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G413">
-        <v>56009.241500221229</v>
+        <v>6427.6971395022492</v>
       </c>
       <c r="H413">
-        <v>52055.490648525119</v>
+        <v>5103.5915287647867</v>
       </c>
       <c r="I413">
-        <v>60301.314991008629</v>
+        <v>7751.8027502397144</v>
       </c>
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B414" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C414" s="2">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="D414">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="E414" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F414" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G414">
-        <v>4209.7072637406518</v>
+        <v>4914.611265650632</v>
       </c>
       <c r="H414">
-        <v>3912.5396315144558</v>
+        <v>3872.7136773326979</v>
       </c>
       <c r="I414">
-        <v>4532.3035436885784</v>
+        <v>5956.5088539685657</v>
       </c>
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B415" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C415" s="2">
-        <v>47664</v>
+        <v>47118</v>
       </c>
       <c r="D415">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="E415" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F415" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G415">
-        <v>13734.45551539364</v>
+        <v>10117.344571326381</v>
       </c>
       <c r="H415">
-        <v>12740.888033810341</v>
+        <v>7972.4675222051874</v>
       </c>
       <c r="I415">
-        <v>14813.042611285809</v>
+        <v>12262.22162044757</v>
       </c>
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B416" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C416" s="2">
-        <v>47664</v>
+        <v>47118</v>
       </c>
       <c r="D416">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="E416" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F416" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G416">
-        <v>47497.982959815643</v>
+        <v>6953.1700294229913</v>
       </c>
       <c r="H416">
-        <v>44061.920186393188</v>
+        <v>5479.0979831853183</v>
       </c>
       <c r="I416">
-        <v>51228.06978007171</v>
+        <v>8427.2420756606643</v>
       </c>
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B417" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C417" s="2">
-        <v>47664</v>
+        <v>47483</v>
       </c>
       <c r="D417">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="E417" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F417" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G417">
-        <v>56951.696744279317</v>
+        <v>5286.0238693508727</v>
       </c>
       <c r="H417">
-        <v>52831.740635157374</v>
+        <v>4133.6706658323828</v>
       </c>
       <c r="I417">
-        <v>61424.197683883052</v>
+        <v>6438.3770728693626</v>
       </c>
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B418" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C418" s="2">
-        <v>47664</v>
+        <v>47483</v>
       </c>
       <c r="D418">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="E418" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F418" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G418">
-        <v>4280.5430861940968</v>
+        <v>10881.9440659054</v>
       </c>
       <c r="H418">
-        <v>3970.8833105159201</v>
+        <v>8509.6802595380213</v>
       </c>
       <c r="I418">
-        <v>4616.7004628738414</v>
+        <v>13254.207872272769</v>
       </c>
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B419" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C419" s="2">
-        <v>47848</v>
+        <v>47483</v>
       </c>
       <c r="D419">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="E419" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F419" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G419">
-        <v>13914.62086281833</v>
+        <v>7478.6429193437334</v>
       </c>
       <c r="H419">
-        <v>12883.666750655109</v>
+        <v>5848.2987629267991</v>
       </c>
       <c r="I419">
-        <v>15033.79376495904</v>
+        <v>9108.9870757606677</v>
       </c>
     </row>
     <row r="420" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B420" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C420" s="2">
         <v>47848</v>
@@ -12878,24 +12878,24 @@
         <v>20</v>
       </c>
       <c r="F420" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G420">
-        <v>48121.0502952725</v>
+        <v>5657.4364730511124</v>
       </c>
       <c r="H420">
-        <v>44555.693023045947</v>
+        <v>4390.1707030876642</v>
       </c>
       <c r="I420">
-        <v>51991.495350439531</v>
+        <v>6924.7022430145616</v>
       </c>
     </row>
     <row r="421" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B421" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C421" s="2">
         <v>47848</v>
@@ -12907,24 +12907,24 @@
         <v>20</v>
       </c>
       <c r="F421" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G421">
-        <v>57698.775666982758</v>
+        <v>11646.543560484421</v>
       </c>
       <c r="H421">
-        <v>53423.791057117443</v>
+        <v>9037.7178029359075</v>
       </c>
       <c r="I421">
-        <v>62339.570903145846</v>
+        <v>14255.369318032919</v>
       </c>
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B422" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C422" s="2">
         <v>47848</v>
@@ -12936,575 +12936,575 @@
         <v>20</v>
       </c>
       <c r="F422" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G422">
-        <v>4336.6942405974251</v>
+        <v>8004.1158092644746</v>
       </c>
       <c r="H422">
-        <v>4015.38237701044</v>
+        <v>6211.1938679892328</v>
       </c>
       <c r="I422">
-        <v>4685.5007748750149</v>
+        <v>9797.0377505397155</v>
       </c>
     </row>
     <row r="423" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B423" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C423" s="2">
-        <v>46387</v>
+        <v>46203</v>
       </c>
       <c r="D423">
         <v>2026</v>
       </c>
       <c r="E423" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F423" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G423">
-        <v>17370.13780255078</v>
+        <v>51260.595121212886</v>
       </c>
       <c r="H423">
-        <v>13896.11024204063</v>
+        <v>48370.08567434227</v>
       </c>
       <c r="I423">
-        <v>20844.16536306094</v>
+        <v>54291.004041569555</v>
       </c>
     </row>
     <row r="424" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B424" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C424" s="2">
-        <v>46752</v>
+        <v>46387</v>
       </c>
       <c r="D424">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E424" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F424" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G424">
-        <v>18957.986443793259</v>
+        <v>51455.868033972649</v>
       </c>
       <c r="H424">
-        <v>15052.64123637185</v>
+        <v>48458.556359833121</v>
       </c>
       <c r="I424">
-        <v>22863.33165121467</v>
+        <v>54598.995006497091</v>
       </c>
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B425" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C425" s="2">
-        <v>47118</v>
+        <v>46568</v>
       </c>
       <c r="D425">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E425" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F425" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G425">
-        <v>20767.420529046809</v>
+        <v>52021.926509646677</v>
       </c>
       <c r="H425">
-        <v>16364.72737688889</v>
+        <v>48893.788502240117</v>
       </c>
       <c r="I425">
-        <v>25170.113681204741</v>
+        <v>55303.754686777713</v>
       </c>
     </row>
     <row r="426" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B426" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C426" s="2">
-        <v>47483</v>
+        <v>46752</v>
       </c>
       <c r="D426">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="E426" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F426" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G426">
-        <v>22798.440058311451</v>
+        <v>52296.474910174133</v>
       </c>
       <c r="H426">
-        <v>17828.38012559955</v>
+        <v>49053.635338822925</v>
       </c>
       <c r="I426">
-        <v>27768.499991023338</v>
+        <v>55699.400127032255</v>
       </c>
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B427" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C427" s="2">
-        <v>47848</v>
+        <v>46934</v>
       </c>
       <c r="D427">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="E427" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F427" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G427">
-        <v>25051.04503158716</v>
+        <v>52933.347043187729</v>
       </c>
       <c r="H427">
-        <v>19439.610944511642</v>
+        <v>49550.71878972822</v>
       </c>
       <c r="I427">
-        <v>30662.47911866269</v>
+        <v>56484.500537504922</v>
       </c>
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B428" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C428" s="2">
-        <v>46387</v>
+        <v>47118</v>
       </c>
       <c r="D428">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="E428" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F428" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G428">
-        <v>3882.965030497624</v>
+        <v>53304.540455814997</v>
       </c>
       <c r="H428">
-        <v>3106.3720243981002</v>
+        <v>49797.245568722465</v>
       </c>
       <c r="I428">
-        <v>4659.5580365971491</v>
+        <v>56987.400520889569</v>
       </c>
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B429" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C429" s="2">
-        <v>46387</v>
+        <v>47299</v>
       </c>
       <c r="D429">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="E429" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F429" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G429">
-        <v>7993.5712202772638</v>
+        <v>54032.531658887943</v>
       </c>
       <c r="H429">
-        <v>6394.8569762218112</v>
+        <v>50374.212926895103</v>
       </c>
       <c r="I429">
-        <v>9592.2854643327155</v>
+        <v>57875.602059976161</v>
       </c>
     </row>
     <row r="430" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B430" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C430" s="2">
-        <v>46387</v>
+        <v>47483</v>
       </c>
       <c r="D430">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="E430" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F430" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G430">
-        <v>5493.601551775897</v>
+        <v>54520.179189933886</v>
       </c>
       <c r="H430">
-        <v>4394.8812414207177</v>
+        <v>50724.735518108806</v>
       </c>
       <c r="I430">
-        <v>6592.3218621310752</v>
+        <v>58508.259593249124</v>
       </c>
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B431" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C431" s="2">
-        <v>46752</v>
+        <v>47664</v>
       </c>
       <c r="D431">
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="E431" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F431" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G431">
-        <v>4237.9167768655952</v>
+        <v>55362.507169224577</v>
       </c>
       <c r="H431">
-        <v>3364.9059208312819</v>
+        <v>51402.030340884601</v>
       </c>
       <c r="I431">
-        <v>5110.9276328999076</v>
+        <v>59525.778437065368</v>
       </c>
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B432" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C432" s="2">
-        <v>46752</v>
+        <v>47848</v>
       </c>
       <c r="D432">
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="E432" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F432" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G432">
-        <v>8724.2839725346639</v>
+        <v>55989.645266493884</v>
       </c>
       <c r="H432">
-        <v>6927.0814741925242</v>
+        <v>51876.562021195532</v>
       </c>
       <c r="I432">
-        <v>10521.486470876809</v>
+        <v>60314.498377038588</v>
       </c>
     </row>
     <row r="433" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B433" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C433" s="2">
-        <v>46752</v>
+        <v>46203</v>
       </c>
       <c r="D433">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E433" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F433" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G433">
-        <v>5995.7856943930001</v>
+        <v>4633.6211657439417</v>
       </c>
       <c r="H433">
-        <v>4760.6538413480421</v>
+        <v>4263.2784623969783</v>
       </c>
       <c r="I433">
-        <v>7230.9175474379581</v>
+        <v>5143.0956614912157</v>
       </c>
     </row>
     <row r="434" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B434" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C434" s="2">
-        <v>47118</v>
+        <v>46387</v>
       </c>
       <c r="D434">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="E434" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F434" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G434">
-        <v>4642.4023001179348</v>
+        <v>4772.6298007162604</v>
       </c>
       <c r="H434">
-        <v>3658.2130124929331</v>
+        <v>4391.1768162688877</v>
       </c>
       <c r="I434">
-        <v>5626.591587742937</v>
+        <v>5297.3885313359524</v>
       </c>
     </row>
     <row r="435" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B435" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C435" s="2">
-        <v>47118</v>
+        <v>46568</v>
       </c>
       <c r="D435">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E435" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F435" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G435">
-        <v>9556.9682260094723</v>
+        <v>4915.8086947377487</v>
       </c>
       <c r="H435">
-        <v>7530.8909620954637</v>
+        <v>4522.9121207569542</v>
       </c>
       <c r="I435">
-        <v>11583.045489923479</v>
+        <v>5456.3101872760308</v>
       </c>
     </row>
     <row r="436" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B436" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C436" s="2">
-        <v>47118</v>
+        <v>46752</v>
       </c>
       <c r="D436">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E436" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F436" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G436">
-        <v>6568.0500029194072</v>
+        <v>5063.2829555798817</v>
       </c>
       <c r="H436">
-        <v>5175.6234023004927</v>
+        <v>4658.5994843796634</v>
       </c>
       <c r="I436">
-        <v>7960.4766035383218</v>
+        <v>5619.9994928943115</v>
       </c>
     </row>
     <row r="437" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B437" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C437" s="2">
-        <v>47483</v>
+        <v>46934</v>
       </c>
       <c r="D437">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="E437" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F437" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G437">
-        <v>5096.4216002546455</v>
+        <v>5215.1814442472787</v>
       </c>
       <c r="H437">
-        <v>3985.4016913991331</v>
+        <v>4798.3574689110537</v>
       </c>
       <c r="I437">
-        <v>6207.4415091101582</v>
+        <v>5788.5994776811413</v>
       </c>
     </row>
     <row r="438" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B438" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C438" s="2">
-        <v>47483</v>
+        <v>47118</v>
       </c>
       <c r="D438">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="E438" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F438" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G438">
-        <v>10491.62398070169</v>
+        <v>5371.6368875746975</v>
       </c>
       <c r="H438">
-        <v>8204.4499529087188</v>
+        <v>4942.3081929783857</v>
       </c>
       <c r="I438">
-        <v>12778.79800849465</v>
+        <v>5962.2574620115756</v>
       </c>
     </row>
     <row r="439" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B439" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C439" s="2">
-        <v>47483</v>
+        <v>47299</v>
       </c>
       <c r="D439">
         <v>2029</v>
       </c>
       <c r="E439" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F439" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G439">
-        <v>7210.3944773551166</v>
+        <v>5532.7859942019386</v>
       </c>
       <c r="H439">
-        <v>5638.5284812917034</v>
+        <v>5090.5774387677375</v>
       </c>
       <c r="I439">
-        <v>8782.2604734185334</v>
+        <v>6141.1251858719233</v>
       </c>
     </row>
     <row r="440" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B440" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C440" s="2">
-        <v>47848</v>
+        <v>47483</v>
       </c>
       <c r="D440">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="E440" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F440" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G440">
-        <v>5599.9746772757262</v>
+        <v>5698.7695740279969</v>
       </c>
       <c r="H440">
-        <v>4345.5803495659638</v>
+        <v>5243.2947619307697</v>
       </c>
       <c r="I440">
-        <v>6854.3690049854886</v>
+        <v>6325.3589414480812</v>
       </c>
     </row>
     <row r="441" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B441" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C441" s="2">
-        <v>47848</v>
+        <v>47664</v>
       </c>
       <c r="D441">
         <v>2030</v>
       </c>
       <c r="E441" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F441" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G441">
-        <v>11528.25123661131</v>
+        <v>5869.7326612488368</v>
       </c>
       <c r="H441">
-        <v>8945.9229596103742</v>
+        <v>5400.5936047886926</v>
       </c>
       <c r="I441">
-        <v>14110.57951361224</v>
+        <v>6515.1197096915239</v>
       </c>
     </row>
     <row r="442" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B442" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C442" s="2">
         <v>47848</v>
@@ -13516,575 +13516,575 @@
         <v>20</v>
       </c>
       <c r="F442" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G442">
-        <v>7922.8191177001318</v>
+        <v>6045.8246410863021</v>
       </c>
       <c r="H442">
-        <v>6148.1076353353019</v>
+        <v>5562.6114129323532</v>
       </c>
       <c r="I442">
-        <v>9697.5306000649616</v>
+        <v>6710.5733009822698</v>
       </c>
     </row>
     <row r="443" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A443" t="s">
-        <v>81</v>
+      <c r="A443">
+        <v>14.3</v>
       </c>
       <c r="B443" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C443" s="2">
-        <v>46387</v>
+        <v>46203</v>
       </c>
       <c r="D443">
         <v>2026</v>
       </c>
       <c r="E443" t="s">
+        <v>10</v>
+      </c>
+      <c r="F443" t="s">
+        <v>30</v>
+      </c>
+      <c r="G443">
+        <v>53184.163304725829</v>
+      </c>
+      <c r="H443">
+        <v>50081.414848975357</v>
+      </c>
+      <c r="I443">
+        <v>56552.414086080753</v>
+      </c>
+    </row>
+    <row r="444" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A444">
+        <v>14.3</v>
+      </c>
+      <c r="B444" t="s">
+        <v>64</v>
+      </c>
+      <c r="C444" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D444">
+        <v>2026</v>
+      </c>
+      <c r="E444" t="s">
         <v>12</v>
       </c>
-      <c r="F443" t="s">
-        <v>25</v>
-      </c>
-      <c r="G443">
-        <v>18662.155890000002</v>
-      </c>
-      <c r="H443">
-        <v>14929.724711999999</v>
-      </c>
-      <c r="I443">
-        <v>22394.587068000001</v>
-      </c>
-    </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A444" t="s">
-        <v>81</v>
-      </c>
-      <c r="B444" t="s">
-        <v>66</v>
-      </c>
-      <c r="C444" s="2">
+      <c r="F444" t="s">
+        <v>30</v>
+      </c>
+      <c r="G444">
+        <v>53526.535975186511</v>
+      </c>
+      <c r="H444">
+        <v>50310.440217615651</v>
+      </c>
+      <c r="I444">
+        <v>57034.506789580322</v>
+      </c>
+    </row>
+    <row r="445" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A445">
+        <v>14.3</v>
+      </c>
+      <c r="B445" t="s">
+        <v>64</v>
+      </c>
+      <c r="C445" s="2">
+        <v>46568</v>
+      </c>
+      <c r="D445">
+        <v>2027</v>
+      </c>
+      <c r="E445" t="s">
+        <v>13</v>
+      </c>
+      <c r="F445" t="s">
+        <v>30</v>
+      </c>
+      <c r="G445">
+        <v>53873.065912246195</v>
+      </c>
+      <c r="H445">
+        <v>50534.43164683941</v>
+      </c>
+      <c r="I445">
+        <v>57514.56106805458</v>
+      </c>
+    </row>
+    <row r="446" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A446">
+        <v>14.3</v>
+      </c>
+      <c r="B446" t="s">
+        <v>64</v>
+      </c>
+      <c r="C446" s="2">
         <v>46752</v>
       </c>
-      <c r="D444">
+      <c r="D446">
         <v>2027</v>
       </c>
-      <c r="E444" t="s">
+      <c r="E446" t="s">
         <v>14</v>
       </c>
-      <c r="F444" t="s">
-        <v>25</v>
-      </c>
-      <c r="G444">
-        <v>20323.6408782</v>
-      </c>
-      <c r="H444">
-        <v>16136.9708572908</v>
-      </c>
-      <c r="I444">
-        <v>24510.310899109201</v>
-      </c>
-    </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A445" t="s">
-        <v>81</v>
-      </c>
-      <c r="B445" t="s">
-        <v>66</v>
-      </c>
-      <c r="C445" s="2">
+      <c r="F446" t="s">
+        <v>30</v>
+      </c>
+      <c r="G446">
+        <v>54215.88309044324</v>
+      </c>
+      <c r="H446">
+        <v>50753.287504158223</v>
+      </c>
+      <c r="I446">
+        <v>57992.462157122616</v>
+      </c>
+    </row>
+    <row r="447" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A447">
+        <v>14.3</v>
+      </c>
+      <c r="B447" t="s">
+        <v>64</v>
+      </c>
+      <c r="C447" s="2">
+        <v>46934</v>
+      </c>
+      <c r="D447">
+        <v>2028</v>
+      </c>
+      <c r="E447" t="s">
+        <v>15</v>
+      </c>
+      <c r="F447" t="s">
+        <v>30</v>
+      </c>
+      <c r="G447">
+        <v>54554.876127011761</v>
+      </c>
+      <c r="H447">
+        <v>50966.903108108992</v>
+      </c>
+      <c r="I447">
+        <v>58468.091849472083</v>
+      </c>
+    </row>
+    <row r="448" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A448">
+        <v>14.3</v>
+      </c>
+      <c r="B448" t="s">
+        <v>64</v>
+      </c>
+      <c r="C448" s="2">
         <v>47118</v>
       </c>
-      <c r="D445">
+      <c r="D448">
         <v>2028</v>
       </c>
-      <c r="E445" t="s">
+      <c r="E448" t="s">
         <v>16</v>
       </c>
-      <c r="F445" t="s">
-        <v>25</v>
-      </c>
-      <c r="G445">
-        <v>21985.125866400002</v>
-      </c>
-      <c r="H445">
-        <v>17324.279182723199</v>
-      </c>
-      <c r="I445">
-        <v>26645.9725500768</v>
-      </c>
-    </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A446" t="s">
-        <v>81</v>
-      </c>
-      <c r="B446" t="s">
-        <v>66</v>
-      </c>
-      <c r="C446" s="2">
+      <c r="F448" t="s">
+        <v>30</v>
+      </c>
+      <c r="G448">
+        <v>54889.930297702944</v>
+      </c>
+      <c r="H448">
+        <v>51175.17063678478</v>
+      </c>
+      <c r="I448">
+        <v>58941.328391571289</v>
+      </c>
+    </row>
+    <row r="449" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A449">
+        <v>14.3</v>
+      </c>
+      <c r="B449" t="s">
+        <v>64</v>
+      </c>
+      <c r="C449" s="2">
+        <v>47299</v>
+      </c>
+      <c r="D449">
+        <v>2029</v>
+      </c>
+      <c r="E449" t="s">
+        <v>17</v>
+      </c>
+      <c r="F449" t="s">
+        <v>30</v>
+      </c>
+      <c r="G449">
+        <v>55220.927436540442</v>
+      </c>
+      <c r="H449">
+        <v>51377.979033621363</v>
+      </c>
+      <c r="I449">
+        <v>59412.04637728259</v>
+      </c>
+    </row>
+    <row r="450" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A450">
+        <v>14.3</v>
+      </c>
+      <c r="B450" t="s">
+        <v>64</v>
+      </c>
+      <c r="C450" s="2">
         <v>47483</v>
       </c>
-      <c r="D446">
+      <c r="D450">
         <v>2029</v>
       </c>
-      <c r="E446" t="s">
+      <c r="E450" t="s">
         <v>18</v>
       </c>
-      <c r="F446" t="s">
-        <v>25</v>
-      </c>
-      <c r="G446">
-        <v>23646.6108546</v>
-      </c>
-      <c r="H446">
-        <v>18491.649688297199</v>
-      </c>
-      <c r="I446">
-        <v>28801.5720209028</v>
-      </c>
-    </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A447" t="s">
-        <v>81</v>
-      </c>
-      <c r="B447" t="s">
-        <v>66</v>
-      </c>
-      <c r="C447" s="2">
+      <c r="F450" t="s">
+        <v>30</v>
+      </c>
+      <c r="G450">
+        <v>55547.745832568638</v>
+      </c>
+      <c r="H450">
+        <v>51575.213910357692</v>
+      </c>
+      <c r="I450">
+        <v>59880.116638284191</v>
+      </c>
+    </row>
+    <row r="451" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A451">
+        <v>14.3</v>
+      </c>
+      <c r="B451" t="s">
+        <v>64</v>
+      </c>
+      <c r="C451" s="2">
+        <v>47664</v>
+      </c>
+      <c r="D451">
+        <v>2030</v>
+      </c>
+      <c r="E451" t="s">
+        <v>19</v>
+      </c>
+      <c r="F451" t="s">
+        <v>30</v>
+      </c>
+      <c r="G451">
+        <v>55870.260123503278</v>
+      </c>
+      <c r="H451">
+        <v>51766.757447084776</v>
+      </c>
+      <c r="I451">
+        <v>60345.406131204654</v>
+      </c>
+    </row>
+    <row r="452" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A452">
+        <v>14.3</v>
+      </c>
+      <c r="B452" t="s">
+        <v>64</v>
+      </c>
+      <c r="C452" s="2">
         <v>47848</v>
       </c>
-      <c r="D447">
+      <c r="D452">
         <v>2030</v>
       </c>
-      <c r="E447" t="s">
+      <c r="E452" t="s">
         <v>20</v>
       </c>
-      <c r="F447" t="s">
-        <v>25</v>
-      </c>
-      <c r="G447">
-        <v>25308.095842800001</v>
-      </c>
-      <c r="H447">
-        <v>19639.0823740128</v>
-      </c>
-      <c r="I447">
-        <v>30977.109311587199</v>
-      </c>
-    </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A448" t="s">
-        <v>82</v>
-      </c>
-      <c r="B448" t="s">
-        <v>57</v>
-      </c>
-      <c r="C448" s="2">
+      <c r="F452" t="s">
+        <v>30</v>
+      </c>
+      <c r="G452">
+        <v>56188.341186191523</v>
+      </c>
+      <c r="H452">
+        <v>51952.488289296452</v>
+      </c>
+      <c r="I452">
+        <v>60807.777821371405</v>
+      </c>
+    </row>
+    <row r="453" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A453">
+        <v>14.4</v>
+      </c>
+      <c r="B453" t="s">
+        <v>65</v>
+      </c>
+      <c r="C453" s="2">
+        <v>46203</v>
+      </c>
+      <c r="D453">
+        <v>2026</v>
+      </c>
+      <c r="E453" t="s">
+        <v>10</v>
+      </c>
+      <c r="F453" t="s">
+        <v>30</v>
+      </c>
+      <c r="G453">
+        <v>3997.37172978836</v>
+      </c>
+      <c r="H453">
+        <v>3764.1662379467821</v>
+      </c>
+      <c r="I453">
+        <v>4250.5326261078344</v>
+      </c>
+    </row>
+    <row r="454" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A454">
+        <v>14.4</v>
+      </c>
+      <c r="B454" t="s">
+        <v>65</v>
+      </c>
+      <c r="C454" s="2">
         <v>46387</v>
       </c>
-      <c r="D448">
+      <c r="D454">
         <v>2026</v>
       </c>
-      <c r="E448" t="s">
+      <c r="E454" t="s">
         <v>12</v>
       </c>
-      <c r="F448" t="s">
-        <v>25</v>
-      </c>
-      <c r="G448">
-        <v>4171.7860582501517</v>
-      </c>
-      <c r="H448">
-        <v>3337.4288466001221</v>
-      </c>
-      <c r="I448">
-        <v>5006.1432699001816</v>
-      </c>
-    </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A449" t="s">
-        <v>83</v>
-      </c>
-      <c r="B449" t="s">
-        <v>58</v>
-      </c>
-      <c r="C449" s="2">
-        <v>46387</v>
-      </c>
-      <c r="D449">
-        <v>2026</v>
-      </c>
-      <c r="E449" t="s">
-        <v>12</v>
-      </c>
-      <c r="F449" t="s">
-        <v>25</v>
-      </c>
-      <c r="G449">
-        <v>8588.145582168343</v>
-      </c>
-      <c r="H449">
-        <v>6870.516465734675</v>
-      </c>
-      <c r="I449">
-        <v>10305.77469860201</v>
-      </c>
-    </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A450" t="s">
-        <v>84</v>
-      </c>
-      <c r="B450" t="s">
-        <v>59</v>
-      </c>
-      <c r="C450" s="2">
-        <v>46387</v>
-      </c>
-      <c r="D450">
-        <v>2026</v>
-      </c>
-      <c r="E450" t="s">
-        <v>12</v>
-      </c>
-      <c r="F450" t="s">
-        <v>25</v>
-      </c>
-      <c r="G450">
-        <v>5902.224249581509</v>
-      </c>
-      <c r="H450">
-        <v>4721.7793996652072</v>
-      </c>
-      <c r="I450">
-        <v>7082.6690994978098</v>
-      </c>
-    </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A451" t="s">
-        <v>82</v>
-      </c>
-      <c r="B451" t="s">
-        <v>57</v>
-      </c>
-      <c r="C451" s="2">
+      <c r="F454" t="s">
+        <v>30</v>
+      </c>
+      <c r="G454">
+        <v>4125.2876251415873</v>
+      </c>
+      <c r="H454">
+        <v>3877.0912250851857</v>
+      </c>
+      <c r="I454">
+        <v>4378.0486048910698</v>
+      </c>
+    </row>
+    <row r="455" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A455">
+        <v>14.4</v>
+      </c>
+      <c r="B455" t="s">
+        <v>65</v>
+      </c>
+      <c r="C455" s="2">
+        <v>46568</v>
+      </c>
+      <c r="D455">
+        <v>2027</v>
+      </c>
+      <c r="E455" t="s">
+        <v>13</v>
+      </c>
+      <c r="F455" t="s">
+        <v>30</v>
+      </c>
+      <c r="G455">
+        <v>4249.0462538958354</v>
+      </c>
+      <c r="H455">
+        <v>3993.4039618377415</v>
+      </c>
+      <c r="I455">
+        <v>4509.3900630378021</v>
+      </c>
+    </row>
+    <row r="456" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A456">
+        <v>14.4</v>
+      </c>
+      <c r="B456" t="s">
+        <v>65</v>
+      </c>
+      <c r="C456" s="2">
         <v>46752</v>
       </c>
-      <c r="D451">
+      <c r="D456">
         <v>2027</v>
       </c>
-      <c r="E451" t="s">
+      <c r="E456" t="s">
         <v>14</v>
       </c>
-      <c r="F451" t="s">
-        <v>25</v>
-      </c>
-      <c r="G451">
-        <v>4543.1986619503914</v>
-      </c>
-      <c r="H451">
-        <v>3607.2997375886112</v>
-      </c>
-      <c r="I451">
-        <v>5479.0975863121721</v>
-      </c>
-    </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A452" t="s">
-        <v>83</v>
-      </c>
-      <c r="B452" t="s">
-        <v>58</v>
-      </c>
-      <c r="C452" s="2">
-        <v>46752</v>
-      </c>
-      <c r="D452">
-        <v>2027</v>
-      </c>
-      <c r="E452" t="s">
-        <v>14</v>
-      </c>
-      <c r="F452" t="s">
-        <v>25</v>
-      </c>
-      <c r="G452">
-        <v>9352.7450767473601</v>
-      </c>
-      <c r="H452">
-        <v>7426.0795909374046</v>
-      </c>
-      <c r="I452">
-        <v>11279.410562557319</v>
-      </c>
-    </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A453" t="s">
-        <v>84</v>
-      </c>
-      <c r="B453" t="s">
-        <v>59</v>
-      </c>
-      <c r="C453" s="2">
-        <v>46752</v>
-      </c>
-      <c r="D453">
-        <v>2027</v>
-      </c>
-      <c r="E453" t="s">
-        <v>14</v>
-      </c>
-      <c r="F453" t="s">
-        <v>25</v>
-      </c>
-      <c r="G453">
-        <v>6427.6971395022492</v>
-      </c>
-      <c r="H453">
-        <v>5103.5915287647867</v>
-      </c>
-      <c r="I453">
-        <v>7751.8027502397144</v>
-      </c>
-    </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A454" t="s">
-        <v>82</v>
-      </c>
-      <c r="B454" t="s">
-        <v>57</v>
-      </c>
-      <c r="C454" s="2">
+      <c r="F456" t="s">
+        <v>30</v>
+      </c>
+      <c r="G456">
+        <v>4376.5176415127107</v>
+      </c>
+      <c r="H456">
+        <v>4113.2060806928739</v>
+      </c>
+      <c r="I456">
+        <v>4644.6717649289367</v>
+      </c>
+    </row>
+    <row r="457" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A457">
+        <v>14.4</v>
+      </c>
+      <c r="B457" t="s">
+        <v>65</v>
+      </c>
+      <c r="C457" s="2">
+        <v>46934</v>
+      </c>
+      <c r="D457">
+        <v>2028</v>
+      </c>
+      <c r="E457" t="s">
+        <v>15</v>
+      </c>
+      <c r="F457" t="s">
+        <v>30</v>
+      </c>
+      <c r="G457">
+        <v>4507.8131707580924</v>
+      </c>
+      <c r="H457">
+        <v>4236.6022631136602</v>
+      </c>
+      <c r="I457">
+        <v>4784.0119178768045</v>
+      </c>
+    </row>
+    <row r="458" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A458">
+        <v>14.4</v>
+      </c>
+      <c r="B458" t="s">
+        <v>65</v>
+      </c>
+      <c r="C458" s="2">
         <v>47118</v>
       </c>
-      <c r="D454">
+      <c r="D458">
         <v>2028</v>
       </c>
-      <c r="E454" t="s">
+      <c r="E458" t="s">
         <v>16</v>
       </c>
-      <c r="F454" t="s">
-        <v>25</v>
-      </c>
-      <c r="G454">
-        <v>4914.611265650632</v>
-      </c>
-      <c r="H454">
-        <v>3872.7136773326979</v>
-      </c>
-      <c r="I454">
-        <v>5956.5088539685657</v>
-      </c>
-    </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A455" t="s">
-        <v>83</v>
-      </c>
-      <c r="B455" t="s">
-        <v>58</v>
-      </c>
-      <c r="C455" s="2">
-        <v>47118</v>
-      </c>
-      <c r="D455">
-        <v>2028</v>
-      </c>
-      <c r="E455" t="s">
-        <v>16</v>
-      </c>
-      <c r="F455" t="s">
-        <v>25</v>
-      </c>
-      <c r="G455">
-        <v>10117.344571326381</v>
-      </c>
-      <c r="H455">
-        <v>7972.4675222051874</v>
-      </c>
-      <c r="I455">
-        <v>12262.22162044757</v>
-      </c>
-    </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A456" t="s">
-        <v>84</v>
-      </c>
-      <c r="B456" t="s">
-        <v>59</v>
-      </c>
-      <c r="C456" s="2">
-        <v>47118</v>
-      </c>
-      <c r="D456">
-        <v>2028</v>
-      </c>
-      <c r="E456" t="s">
-        <v>16</v>
-      </c>
-      <c r="F456" t="s">
-        <v>25</v>
-      </c>
-      <c r="G456">
-        <v>6953.1700294229913</v>
-      </c>
-      <c r="H456">
-        <v>5479.0979831853183</v>
-      </c>
-      <c r="I456">
-        <v>8427.2420756606643</v>
-      </c>
-    </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A457" t="s">
-        <v>82</v>
-      </c>
-      <c r="B457" t="s">
-        <v>57</v>
-      </c>
-      <c r="C457" s="2">
-        <v>47483</v>
-      </c>
-      <c r="D457">
-        <v>2029</v>
-      </c>
-      <c r="E457" t="s">
-        <v>18</v>
-      </c>
-      <c r="F457" t="s">
-        <v>25</v>
-      </c>
-      <c r="G457">
-        <v>5286.0238693508727</v>
-      </c>
-      <c r="H457">
-        <v>4133.6706658323828</v>
-      </c>
-      <c r="I457">
-        <v>6438.3770728693626</v>
-      </c>
-    </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A458" t="s">
-        <v>83</v>
-      </c>
-      <c r="B458" t="s">
-        <v>58</v>
-      </c>
-      <c r="C458" s="2">
-        <v>47483</v>
-      </c>
-      <c r="D458">
-        <v>2029</v>
-      </c>
-      <c r="E458" t="s">
-        <v>18</v>
-      </c>
       <c r="F458" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G458">
-        <v>10881.9440659054</v>
+        <v>4643.0475658808355</v>
       </c>
       <c r="H458">
-        <v>8509.6802595380213</v>
+        <v>4363.7003310070704</v>
       </c>
       <c r="I458">
-        <v>13254.207872272769</v>
+        <v>4927.5322754131084</v>
       </c>
     </row>
     <row r="459" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A459" t="s">
-        <v>84</v>
+      <c r="A459">
+        <v>14.4</v>
       </c>
       <c r="B459" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C459" s="2">
-        <v>47483</v>
+        <v>47299</v>
       </c>
       <c r="D459">
         <v>2029</v>
       </c>
       <c r="E459" t="s">
+        <v>17</v>
+      </c>
+      <c r="F459" t="s">
+        <v>30</v>
+      </c>
+      <c r="G459">
+        <v>4782.3389928572606</v>
+      </c>
+      <c r="H459">
+        <v>4494.6113409372829</v>
+      </c>
+      <c r="I459">
+        <v>5075.3582436755014</v>
+      </c>
+    </row>
+    <row r="460" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A460">
+        <v>14.4</v>
+      </c>
+      <c r="B460" t="s">
+        <v>65</v>
+      </c>
+      <c r="C460" s="2">
+        <v>47483</v>
+      </c>
+      <c r="D460">
+        <v>2029</v>
+      </c>
+      <c r="E460" t="s">
         <v>18</v>
       </c>
-      <c r="F459" t="s">
-        <v>25</v>
-      </c>
-      <c r="G459">
-        <v>7478.6429193437334</v>
-      </c>
-      <c r="H459">
-        <v>5848.2987629267991</v>
-      </c>
-      <c r="I459">
-        <v>9108.9870757606677</v>
-      </c>
-    </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A460" t="s">
-        <v>82</v>
-      </c>
-      <c r="B460" t="s">
-        <v>57</v>
-      </c>
-      <c r="C460" s="2">
-        <v>47848</v>
-      </c>
-      <c r="D460">
-        <v>2030</v>
-      </c>
-      <c r="E460" t="s">
-        <v>20</v>
-      </c>
       <c r="F460" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G460">
-        <v>5657.4364730511124</v>
+        <v>4925.8091626429787</v>
       </c>
       <c r="H460">
-        <v>4390.1707030876642</v>
+        <v>4629.4496811654017</v>
       </c>
       <c r="I460">
-        <v>6924.7022430145616</v>
+        <v>5227.6189909857667</v>
       </c>
     </row>
     <row r="461" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A461" t="s">
-        <v>83</v>
+      <c r="A461">
+        <v>14.4</v>
       </c>
       <c r="B461" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C461" s="2">
-        <v>47848</v>
+        <v>47664</v>
       </c>
       <c r="D461">
         <v>2030</v>
       </c>
       <c r="E461" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F461" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G461">
-        <v>11646.543560484421</v>
+        <v>5073.5834375222685</v>
       </c>
       <c r="H461">
-        <v>9037.7178029359075</v>
+        <v>4768.333171600364</v>
       </c>
       <c r="I461">
-        <v>14255.369318032919</v>
+        <v>5384.4475607153399</v>
       </c>
     </row>
     <row r="462" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A462" t="s">
-        <v>84</v>
+      <c r="A462">
+        <v>14.4</v>
       </c>
       <c r="B462" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C462" s="2">
         <v>47848</v>
@@ -14096,19 +14096,20 @@
         <v>20</v>
       </c>
       <c r="F462" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G462">
-        <v>8004.1158092644746</v>
+        <v>5225.7909406479366</v>
       </c>
       <c r="H462">
-        <v>6211.1938679892328</v>
+        <v>4911.3831667483755</v>
       </c>
       <c r="I462">
-        <v>9797.0377505397155</v>
+        <v>5545.9809875368001</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I462" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1007" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{480F34D1-A8D8-4709-B7D6-10F0B47B0C87}"/>
+  <xr:revisionPtr revIDLastSave="1049" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14429248-3C0E-4702-80BE-1944FB7657F2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -4042,7 +4042,7 @@
         <v>80.239346568574291</v>
       </c>
       <c r="I115">
-        <v>64.626946951668998</v>
+        <v>72.818857142857141</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
@@ -4071,7 +4071,7 @@
         <v>77.260747075396466</v>
       </c>
       <c r="I116">
-        <v>61.797659797529029</v>
+        <v>70.021785714285713</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
@@ -4100,7 +4100,7 @@
         <v>74.273878573356129</v>
       </c>
       <c r="I117">
-        <v>58.996085245839843</v>
+        <v>67.224714285714285</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
@@ -4129,7 +4129,7 @@
         <v>71.278741062453278</v>
       </c>
       <c r="I118">
-        <v>56.222223296601427</v>
+        <v>64.427642857142857</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
@@ -4158,7 +4158,7 @@
         <v>68.275334542687915</v>
       </c>
       <c r="I119">
-        <v>53.476073949813816</v>
+        <v>61.630571428571429</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
@@ -4187,7 +4187,7 @@
         <v>65.263659014060011</v>
       </c>
       <c r="I120">
-        <v>50.757637205477003</v>
+        <v>58.833500000000001</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
@@ -4216,7 +4216,7 @@
         <v>62.243714476569622</v>
       </c>
       <c r="I121">
-        <v>48.06691306359096</v>
+        <v>56.036428571428573</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
@@ -4245,7 +4245,7 @@
         <v>59.215500930216713</v>
       </c>
       <c r="I122">
-        <v>45.403901524155707</v>
+        <v>53.239357142857152</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
@@ -4274,7 +4274,7 @@
         <v>56.179018375001291</v>
       </c>
       <c r="I123">
-        <v>42.768602587171237</v>
+        <v>50.442285714285724</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
@@ -4303,7 +4303,7 @@
         <v>53.13426681092335</v>
       </c>
       <c r="I124">
-        <v>40.16101625263758</v>
+        <v>47.645214285714296</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
@@ -4332,7 +4332,7 @@
         <v>86.083268380521034</v>
       </c>
       <c r="I125">
-        <v>69.3338001487799</v>
+        <v>78.122336368158329</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
@@ -4361,7 +4361,7 @@
         <v>84.206116886725511</v>
       </c>
       <c r="I126">
-        <v>67.352972385300021</v>
+        <v>76.31640769303462</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
@@ -4390,7 +4390,7 @@
         <v>82.369751160866997</v>
       </c>
       <c r="I127">
-        <v>65.426674283148913</v>
+        <v>74.552226084515084</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
@@ -4419,7 +4419,7 @@
         <v>80.573288653722372</v>
       </c>
       <c r="I128">
-        <v>63.553443269459287</v>
+        <v>72.828826489220774</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
@@ -4448,7 +4448,7 @@
         <v>78.815865824149853</v>
       </c>
       <c r="I129">
-        <v>61.731855251410558</v>
+        <v>71.145266162598247</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
@@ -4477,7 +4477,7 @@
         <v>77.096637731899037</v>
       </c>
       <c r="I130">
-        <v>59.960523618738179</v>
+        <v>69.500624153213707</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
@@ -4506,7 +4506,7 @@
         <v>75.414777639089081</v>
       </c>
       <c r="I131">
-        <v>58.238098271797057</v>
+        <v>67.894000798968491</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
@@ -4535,7 +4535,7 @@
         <v>73.769476620171801</v>
       </c>
       <c r="I132">
-        <v>56.563264674531062</v>
+        <v>66.324517234960496</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
@@ -4564,7 +4564,7 @@
         <v>72.159943180200727</v>
       </c>
       <c r="I133">
-        <v>54.934742931716322</v>
+        <v>64.791314912722086</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
@@ -4593,7 +4593,7 @@
         <v>70.585402881230067</v>
       </c>
       <c r="I134">
-        <v>53.351286889862124</v>
+        <v>63.293555130571669</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
@@ -14109,7 +14109,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I462" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Prospectiva/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1049" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14429248-3C0E-4702-80BE-1944FB7657F2}"/>
+  <xr:revisionPtr revIDLastSave="1072" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{803FD8CF-5996-4F09-B1C4-9B9539E03452}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Proyecciones" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$I$462</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$I$522</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="86">
   <si>
     <t>Id</t>
   </si>
@@ -294,6 +294,9 @@
   </si>
   <si>
     <t>386,3</t>
+  </si>
+  <si>
+    <t>Polinomial_Grado_4</t>
   </si>
 </sst>
 </file>
@@ -701,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}">
-  <dimension ref="A1:I462"/>
+  <dimension ref="A1:I532"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
@@ -14108,6 +14111,2036 @@
         <v>5545.9809875368001</v>
       </c>
     </row>
+    <row r="463" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A463" t="s">
+        <v>74</v>
+      </c>
+      <c r="B463" t="s">
+        <v>9</v>
+      </c>
+      <c r="C463" s="2">
+        <v>46203</v>
+      </c>
+      <c r="D463">
+        <v>2026</v>
+      </c>
+      <c r="E463" t="s">
+        <v>10</v>
+      </c>
+      <c r="F463" t="s">
+        <v>85</v>
+      </c>
+      <c r="G463">
+        <v>55171.105118790183</v>
+      </c>
+      <c r="H463">
+        <v>51952.439061592617</v>
+      </c>
+      <c r="I463">
+        <v>58665.192575987538</v>
+      </c>
+    </row>
+    <row r="464" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A464" t="s">
+        <v>77</v>
+      </c>
+      <c r="B464" t="s">
+        <v>60</v>
+      </c>
+      <c r="C464" s="2">
+        <v>46203</v>
+      </c>
+      <c r="D464">
+        <v>2026</v>
+      </c>
+      <c r="E464" t="s">
+        <v>10</v>
+      </c>
+      <c r="F464" t="s">
+        <v>85</v>
+      </c>
+      <c r="G464">
+        <v>12374.93665244013</v>
+      </c>
+      <c r="H464">
+        <v>11652.986485275311</v>
+      </c>
+      <c r="I464">
+        <v>13158.66412804179</v>
+      </c>
+    </row>
+    <row r="465" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A465" t="s">
+        <v>78</v>
+      </c>
+      <c r="B465" t="s">
+        <v>61</v>
+      </c>
+      <c r="C465" s="2">
+        <v>46203</v>
+      </c>
+      <c r="D465">
+        <v>2026</v>
+      </c>
+      <c r="E465" t="s">
+        <v>10</v>
+      </c>
+      <c r="F465" t="s">
+        <v>85</v>
+      </c>
+      <c r="G465">
+        <v>42796.34744803737</v>
+      </c>
+      <c r="H465">
+        <v>40299.621116265618</v>
+      </c>
+      <c r="I465">
+        <v>45506.718764872203</v>
+      </c>
+    </row>
+    <row r="466" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A466" t="s">
+        <v>75</v>
+      </c>
+      <c r="B466" t="s">
+        <v>62</v>
+      </c>
+      <c r="C466" s="2">
+        <v>46203</v>
+      </c>
+      <c r="D466">
+        <v>2026</v>
+      </c>
+      <c r="E466" t="s">
+        <v>10</v>
+      </c>
+      <c r="F466" t="s">
+        <v>85</v>
+      </c>
+      <c r="G466">
+        <v>8608.43195696976</v>
+      </c>
+      <c r="H466">
+        <v>8106.218566718916</v>
+      </c>
+      <c r="I466">
+        <v>9153.6197697246807</v>
+      </c>
+    </row>
+    <row r="467" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A467" t="s">
+        <v>76</v>
+      </c>
+      <c r="B467" t="s">
+        <v>63</v>
+      </c>
+      <c r="C467" s="2">
+        <v>46203</v>
+      </c>
+      <c r="D467">
+        <v>2026</v>
+      </c>
+      <c r="E467" t="s">
+        <v>10</v>
+      </c>
+      <c r="F467" t="s">
+        <v>85</v>
+      </c>
+      <c r="G467">
+        <v>46562.673161820421</v>
+      </c>
+      <c r="H467">
+        <v>43846.220494873713</v>
+      </c>
+      <c r="I467">
+        <v>49511.57280626287</v>
+      </c>
+    </row>
+    <row r="468" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A468" t="s">
+        <v>74</v>
+      </c>
+      <c r="B468" t="s">
+        <v>9</v>
+      </c>
+      <c r="C468" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D468">
+        <v>2026</v>
+      </c>
+      <c r="E468" t="s">
+        <v>12</v>
+      </c>
+      <c r="F468" t="s">
+        <v>85</v>
+      </c>
+      <c r="G468">
+        <v>55967.26459514397</v>
+      </c>
+      <c r="H468">
+        <v>52604.197415085087</v>
+      </c>
+      <c r="I468">
+        <v>59618.109585812912</v>
+      </c>
+    </row>
+    <row r="469" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A469" t="s">
+        <v>77</v>
+      </c>
+      <c r="B469" t="s">
+        <v>60</v>
+      </c>
+      <c r="C469" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D469">
+        <v>2026</v>
+      </c>
+      <c r="E469" t="s">
+        <v>12</v>
+      </c>
+      <c r="F469" t="s">
+        <v>85</v>
+      </c>
+      <c r="G469">
+        <v>12553.516056711709</v>
+      </c>
+      <c r="H469">
+        <v>11799.176566474551</v>
+      </c>
+      <c r="I469">
+        <v>13372.40441122501</v>
+      </c>
+    </row>
+    <row r="470" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A470" t="s">
+        <v>78</v>
+      </c>
+      <c r="B470" t="s">
+        <v>61</v>
+      </c>
+      <c r="C470" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D470">
+        <v>2026</v>
+      </c>
+      <c r="E470" t="s">
+        <v>12</v>
+      </c>
+      <c r="F470" t="s">
+        <v>85</v>
+      </c>
+      <c r="G470">
+        <v>43413.930102956503</v>
+      </c>
+      <c r="H470">
+        <v>40805.191502941168</v>
+      </c>
+      <c r="I470">
+        <v>46245.898582891503</v>
+      </c>
+    </row>
+    <row r="471" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A471" t="s">
+        <v>75</v>
+      </c>
+      <c r="B471" t="s">
+        <v>62</v>
+      </c>
+      <c r="C471" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D471">
+        <v>2026</v>
+      </c>
+      <c r="E471" t="s">
+        <v>12</v>
+      </c>
+      <c r="F471" t="s">
+        <v>85</v>
+      </c>
+      <c r="G471">
+        <v>8732.6579383839708</v>
+      </c>
+      <c r="H471">
+        <v>8207.9134199640375</v>
+      </c>
+      <c r="I471">
+        <v>9302.3048689638272</v>
+      </c>
+    </row>
+    <row r="472" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A472" t="s">
+        <v>76</v>
+      </c>
+      <c r="B472" t="s">
+        <v>63</v>
+      </c>
+      <c r="C472" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D472">
+        <v>2026</v>
+      </c>
+      <c r="E472" t="s">
+        <v>12</v>
+      </c>
+      <c r="F472" t="s">
+        <v>85</v>
+      </c>
+      <c r="G472">
+        <v>47234.606656760006</v>
+      </c>
+      <c r="H472">
+        <v>44396.283995121063</v>
+      </c>
+      <c r="I472">
+        <v>50315.804716849103</v>
+      </c>
+    </row>
+    <row r="473" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A473" t="s">
+        <v>74</v>
+      </c>
+      <c r="B473" t="s">
+        <v>9</v>
+      </c>
+      <c r="C473" s="2">
+        <v>46568</v>
+      </c>
+      <c r="D473">
+        <v>2027</v>
+      </c>
+      <c r="E473" t="s">
+        <v>13</v>
+      </c>
+      <c r="F473" t="s">
+        <v>85</v>
+      </c>
+      <c r="G473">
+        <v>56889.849334480503</v>
+      </c>
+      <c r="H473">
+        <v>53371.776019523677</v>
+      </c>
+      <c r="I473">
+        <v>60708.964342016967</v>
+      </c>
+    </row>
+    <row r="474" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A474" t="s">
+        <v>77</v>
+      </c>
+      <c r="B474" t="s">
+        <v>60</v>
+      </c>
+      <c r="C474" s="2">
+        <v>46568</v>
+      </c>
+      <c r="D474">
+        <v>2027</v>
+      </c>
+      <c r="E474" t="s">
+        <v>13</v>
+      </c>
+      <c r="F474" t="s">
+        <v>85</v>
+      </c>
+      <c r="G474">
+        <v>12760.45277986082</v>
+      </c>
+      <c r="H474">
+        <v>11971.34525124611</v>
+      </c>
+      <c r="I474">
+        <v>13617.08427536717</v>
+      </c>
+    </row>
+    <row r="475" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A475" t="s">
+        <v>78</v>
+      </c>
+      <c r="B475" t="s">
+        <v>61</v>
+      </c>
+      <c r="C475" s="2">
+        <v>46568</v>
+      </c>
+      <c r="D475">
+        <v>2027</v>
+      </c>
+      <c r="E475" t="s">
+        <v>13</v>
+      </c>
+      <c r="F475" t="s">
+        <v>85</v>
+      </c>
+      <c r="G475">
+        <v>44129.581112119551</v>
+      </c>
+      <c r="H475">
+        <v>41400.603912725317</v>
+      </c>
+      <c r="I475">
+        <v>47092.077013817172</v>
+      </c>
+    </row>
+    <row r="476" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A476" t="s">
+        <v>75</v>
+      </c>
+      <c r="B476" t="s">
+        <v>62</v>
+      </c>
+      <c r="C476" s="2">
+        <v>46568</v>
+      </c>
+      <c r="D476">
+        <v>2027</v>
+      </c>
+      <c r="E476" t="s">
+        <v>13</v>
+      </c>
+      <c r="F476" t="s">
+        <v>85</v>
+      </c>
+      <c r="G476">
+        <v>8876.6102470429523</v>
+      </c>
+      <c r="H476">
+        <v>8327.6798841975942</v>
+      </c>
+      <c r="I476">
+        <v>9472.5126058489332</v>
+      </c>
+    </row>
+    <row r="477" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A477" t="s">
+        <v>76</v>
+      </c>
+      <c r="B477" t="s">
+        <v>63</v>
+      </c>
+      <c r="C477" s="2">
+        <v>46568</v>
+      </c>
+      <c r="D477">
+        <v>2027</v>
+      </c>
+      <c r="E477" t="s">
+        <v>13</v>
+      </c>
+      <c r="F477" t="s">
+        <v>85</v>
+      </c>
+      <c r="G477">
+        <v>48013.239087437563</v>
+      </c>
+      <c r="H477">
+        <v>45044.096135326086</v>
+      </c>
+      <c r="I477">
+        <v>51236.451736168048</v>
+      </c>
+    </row>
+    <row r="478" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A478" t="s">
+        <v>74</v>
+      </c>
+      <c r="B478" t="s">
+        <v>9</v>
+      </c>
+      <c r="C478" s="2">
+        <v>46752</v>
+      </c>
+      <c r="D478">
+        <v>2027</v>
+      </c>
+      <c r="E478" t="s">
+        <v>14</v>
+      </c>
+      <c r="F478" t="s">
+        <v>85</v>
+      </c>
+      <c r="G478">
+        <v>57951.82222692357</v>
+      </c>
+      <c r="H478">
+        <v>54266.649646082697</v>
+      </c>
+      <c r="I478">
+        <v>61952.335192078754</v>
+      </c>
+    </row>
+    <row r="479" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A479" t="s">
+        <v>77</v>
+      </c>
+      <c r="B479" t="s">
+        <v>60</v>
+      </c>
+      <c r="C479" s="2">
+        <v>46752</v>
+      </c>
+      <c r="D479">
+        <v>2027</v>
+      </c>
+      <c r="E479" t="s">
+        <v>14</v>
+      </c>
+      <c r="F479" t="s">
+        <v>85</v>
+      </c>
+      <c r="G479">
+        <v>12998.65441171677</v>
+      </c>
+      <c r="H479">
+        <v>12172.066342780599</v>
+      </c>
+      <c r="I479">
+        <v>13895.973659074019</v>
+      </c>
+    </row>
+    <row r="480" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A480" t="s">
+        <v>78</v>
+      </c>
+      <c r="B480" t="s">
+        <v>61</v>
+      </c>
+      <c r="C480" s="2">
+        <v>46752</v>
+      </c>
+      <c r="D480">
+        <v>2027</v>
+      </c>
+      <c r="E480" t="s">
+        <v>14</v>
+      </c>
+      <c r="F480" t="s">
+        <v>85</v>
+      </c>
+      <c r="G480">
+        <v>44953.35581787421</v>
+      </c>
+      <c r="H480">
+        <v>42094.75935082732</v>
+      </c>
+      <c r="I480">
+        <v>48056.562513816389</v>
+      </c>
+    </row>
+    <row r="481" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A481" t="s">
+        <v>75</v>
+      </c>
+      <c r="B481" t="s">
+        <v>62</v>
+      </c>
+      <c r="C481" s="2">
+        <v>46752</v>
+      </c>
+      <c r="D481">
+        <v>2027</v>
+      </c>
+      <c r="E481" t="s">
+        <v>14</v>
+      </c>
+      <c r="F481" t="s">
+        <v>85</v>
+      </c>
+      <c r="G481">
+        <v>9042.3115025291136</v>
+      </c>
+      <c r="H481">
+        <v>8467.3083855251225</v>
+      </c>
+      <c r="I481">
+        <v>9666.5176622455838</v>
+      </c>
+    </row>
+    <row r="482" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A482" t="s">
+        <v>76</v>
+      </c>
+      <c r="B482" t="s">
+        <v>63</v>
+      </c>
+      <c r="C482" s="2">
+        <v>46752</v>
+      </c>
+      <c r="D482">
+        <v>2027</v>
+      </c>
+      <c r="E482" t="s">
+        <v>14</v>
+      </c>
+      <c r="F482" t="s">
+        <v>85</v>
+      </c>
+      <c r="G482">
+        <v>48909.510724394473</v>
+      </c>
+      <c r="H482">
+        <v>45799.341260557587</v>
+      </c>
+      <c r="I482">
+        <v>52285.817529833177</v>
+      </c>
+    </row>
+    <row r="483" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A483" t="s">
+        <v>74</v>
+      </c>
+      <c r="B483" t="s">
+        <v>9</v>
+      </c>
+      <c r="C483" s="2">
+        <v>46934</v>
+      </c>
+      <c r="D483">
+        <v>2028</v>
+      </c>
+      <c r="E483" t="s">
+        <v>15</v>
+      </c>
+      <c r="F483" t="s">
+        <v>85</v>
+      </c>
+      <c r="G483">
+        <v>59166.789232411807</v>
+      </c>
+      <c r="H483">
+        <v>55300.803367122877</v>
+      </c>
+      <c r="I483">
+        <v>63363.587682938152</v>
+      </c>
+    </row>
+    <row r="484" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A484" t="s">
+        <v>77</v>
+      </c>
+      <c r="B484" t="s">
+        <v>60</v>
+      </c>
+      <c r="C484" s="2">
+        <v>46934</v>
+      </c>
+      <c r="D484">
+        <v>2028</v>
+      </c>
+      <c r="E484" t="s">
+        <v>15</v>
+      </c>
+      <c r="F484" t="s">
+        <v>85</v>
+      </c>
+      <c r="G484">
+        <v>13271.172783341721</v>
+      </c>
+      <c r="H484">
+        <v>12404.028105359081</v>
+      </c>
+      <c r="I484">
+        <v>14212.51907061473</v>
+      </c>
+    </row>
+    <row r="485" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A485" t="s">
+        <v>78</v>
+      </c>
+      <c r="B485" t="s">
+        <v>61</v>
+      </c>
+      <c r="C485" s="2">
+        <v>46934</v>
+      </c>
+      <c r="D485">
+        <v>2028</v>
+      </c>
+      <c r="E485" t="s">
+        <v>15</v>
+      </c>
+      <c r="F485" t="s">
+        <v>85</v>
+      </c>
+      <c r="G485">
+        <v>45895.808393236301</v>
+      </c>
+      <c r="H485">
+        <v>42896.954664207813</v>
+      </c>
+      <c r="I485">
+        <v>49151.274171407553</v>
+      </c>
+    </row>
+    <row r="486" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A486" t="s">
+        <v>75</v>
+      </c>
+      <c r="B486" t="s">
+        <v>62</v>
+      </c>
+      <c r="C486" s="2">
+        <v>46934</v>
+      </c>
+      <c r="D486">
+        <v>2028</v>
+      </c>
+      <c r="E486" t="s">
+        <v>15</v>
+      </c>
+      <c r="F486" t="s">
+        <v>85</v>
+      </c>
+      <c r="G486">
+        <v>9231.8846635921273</v>
+      </c>
+      <c r="H486">
+        <v>8628.6689731271545</v>
+      </c>
+      <c r="I486">
+        <v>9886.7175479558591</v>
+      </c>
+    </row>
+    <row r="487" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A487" t="s">
+        <v>76</v>
+      </c>
+      <c r="B487" t="s">
+        <v>63</v>
+      </c>
+      <c r="C487" s="2">
+        <v>46934</v>
+      </c>
+      <c r="D487">
+        <v>2028</v>
+      </c>
+      <c r="E487" t="s">
+        <v>15</v>
+      </c>
+      <c r="F487" t="s">
+        <v>85</v>
+      </c>
+      <c r="G487">
+        <v>49934.904568819693</v>
+      </c>
+      <c r="H487">
+        <v>46672.134393995737</v>
+      </c>
+      <c r="I487">
+        <v>53476.870134982288</v>
+      </c>
+    </row>
+    <row r="488" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A488" t="s">
+        <v>74</v>
+      </c>
+      <c r="B488" t="s">
+        <v>9</v>
+      </c>
+      <c r="C488" s="2">
+        <v>47118</v>
+      </c>
+      <c r="D488">
+        <v>2028</v>
+      </c>
+      <c r="E488" t="s">
+        <v>16</v>
+      </c>
+      <c r="F488" t="s">
+        <v>85</v>
+      </c>
+      <c r="G488">
+        <v>60548.99938069874</v>
+      </c>
+      <c r="H488">
+        <v>56486.726928715732</v>
+      </c>
+      <c r="I488">
+        <v>64958.880670014812</v>
+      </c>
+    </row>
+    <row r="489" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A489" t="s">
+        <v>77</v>
+      </c>
+      <c r="B489" t="s">
+        <v>60</v>
+      </c>
+      <c r="C489" s="2">
+        <v>47118</v>
+      </c>
+      <c r="D489">
+        <v>2028</v>
+      </c>
+      <c r="E489" t="s">
+        <v>16</v>
+      </c>
+      <c r="F489" t="s">
+        <v>85</v>
+      </c>
+      <c r="G489">
+        <v>13581.203967030749</v>
+      </c>
+      <c r="H489">
+        <v>12670.03200210447</v>
+      </c>
+      <c r="I489">
+        <v>14570.344958181229</v>
+      </c>
+    </row>
+    <row r="490" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A490" t="s">
+        <v>78</v>
+      </c>
+      <c r="B490" t="s">
+        <v>61</v>
+      </c>
+      <c r="C490" s="2">
+        <v>47118</v>
+      </c>
+      <c r="D490">
+        <v>2028</v>
+      </c>
+      <c r="E490" t="s">
+        <v>16</v>
+      </c>
+      <c r="F490" t="s">
+        <v>85</v>
+      </c>
+      <c r="G490">
+        <v>46967.991841889823</v>
+      </c>
+      <c r="H490">
+        <v>43816.878176333659</v>
+      </c>
+      <c r="I490">
+        <v>50388.746446239653</v>
+      </c>
+    </row>
+    <row r="491" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A491" t="s">
+        <v>75</v>
+      </c>
+      <c r="B491" t="s">
+        <v>62</v>
+      </c>
+      <c r="C491" s="2">
+        <v>47118</v>
+      </c>
+      <c r="D491">
+        <v>2028</v>
+      </c>
+      <c r="E491" t="s">
+        <v>16</v>
+      </c>
+      <c r="F491" t="s">
+        <v>85</v>
+      </c>
+      <c r="G491">
+        <v>9447.5530281489318</v>
+      </c>
+      <c r="H491">
+        <v>8813.7104411955952</v>
+      </c>
+      <c r="I491">
+        <v>10135.633553917891</v>
+      </c>
+    </row>
+    <row r="492" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A492" t="s">
+        <v>76</v>
+      </c>
+      <c r="B492" t="s">
+        <v>63</v>
+      </c>
+      <c r="C492" s="2">
+        <v>47118</v>
+      </c>
+      <c r="D492">
+        <v>2028</v>
+      </c>
+      <c r="E492" t="s">
+        <v>16</v>
+      </c>
+      <c r="F492" t="s">
+        <v>85</v>
+      </c>
+      <c r="G492">
+        <v>51101.446352549807</v>
+      </c>
+      <c r="H492">
+        <v>47673.016487520137</v>
+      </c>
+      <c r="I492">
+        <v>54823.247116096944</v>
+      </c>
+    </row>
+    <row r="493" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A493" t="s">
+        <v>74</v>
+      </c>
+      <c r="B493" t="s">
+        <v>9</v>
+      </c>
+      <c r="C493" s="2">
+        <v>47299</v>
+      </c>
+      <c r="D493">
+        <v>2029</v>
+      </c>
+      <c r="E493" t="s">
+        <v>17</v>
+      </c>
+      <c r="F493" t="s">
+        <v>85</v>
+      </c>
+      <c r="G493">
+        <v>62113.344771352698</v>
+      </c>
+      <c r="H493">
+        <v>57837.409123167949</v>
+      </c>
+      <c r="I493">
+        <v>66755.172426227189</v>
+      </c>
+    </row>
+    <row r="494" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A494" t="s">
+        <v>77</v>
+      </c>
+      <c r="B494" t="s">
+        <v>60</v>
+      </c>
+      <c r="C494" s="2">
+        <v>47299</v>
+      </c>
+      <c r="D494">
+        <v>2029</v>
+      </c>
+      <c r="E494" t="s">
+        <v>17</v>
+      </c>
+      <c r="F494" t="s">
+        <v>85</v>
+      </c>
+      <c r="G494">
+        <v>13932.08827631181</v>
+      </c>
+      <c r="H494">
+        <v>12972.99143273281</v>
+      </c>
+      <c r="I494">
+        <v>14973.255080147561</v>
+      </c>
+    </row>
+    <row r="495" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A495" t="s">
+        <v>78</v>
+      </c>
+      <c r="B495" t="s">
+        <v>61</v>
+      </c>
+      <c r="C495" s="2">
+        <v>47299</v>
+      </c>
+      <c r="D495">
+        <v>2029</v>
+      </c>
+      <c r="E495" t="s">
+        <v>17</v>
+      </c>
+      <c r="F495" t="s">
+        <v>85</v>
+      </c>
+      <c r="G495">
+        <v>48181.457998186939</v>
+      </c>
+      <c r="H495">
+        <v>44864.6053219327</v>
+      </c>
+      <c r="I495">
+        <v>51782.133907871772</v>
+      </c>
+    </row>
+    <row r="496" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A496" t="s">
+        <v>75</v>
+      </c>
+      <c r="B496" t="s">
+        <v>62</v>
+      </c>
+      <c r="C496" s="2">
+        <v>47299</v>
+      </c>
+      <c r="D496">
+        <v>2029</v>
+      </c>
+      <c r="E496" t="s">
+        <v>17</v>
+      </c>
+      <c r="F496" t="s">
+        <v>85</v>
+      </c>
+      <c r="G496">
+        <v>9691.6402332837351</v>
+      </c>
+      <c r="H496">
+        <v>9024.459450870092</v>
+      </c>
+      <c r="I496">
+        <v>10415.91170540544</v>
+      </c>
+    </row>
+    <row r="497" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A497" t="s">
+        <v>76</v>
+      </c>
+      <c r="B497" t="s">
+        <v>63</v>
+      </c>
+      <c r="C497" s="2">
+        <v>47299</v>
+      </c>
+      <c r="D497">
+        <v>2029</v>
+      </c>
+      <c r="E497" t="s">
+        <v>17</v>
+      </c>
+      <c r="F497" t="s">
+        <v>85</v>
+      </c>
+      <c r="G497">
+        <v>52421.704538068967</v>
+      </c>
+      <c r="H497">
+        <v>48812.949672297873</v>
+      </c>
+      <c r="I497">
+        <v>56339.26072082176</v>
+      </c>
+    </row>
+    <row r="498" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A498" t="s">
+        <v>74</v>
+      </c>
+      <c r="B498" t="s">
+        <v>9</v>
+      </c>
+      <c r="C498" s="2">
+        <v>47483</v>
+      </c>
+      <c r="D498">
+        <v>2029</v>
+      </c>
+      <c r="E498" t="s">
+        <v>18</v>
+      </c>
+      <c r="F498" t="s">
+        <v>85</v>
+      </c>
+      <c r="G498">
+        <v>63875.360573756872</v>
+      </c>
+      <c r="H498">
+        <v>59366.332161545834</v>
+      </c>
+      <c r="I498">
+        <v>68770.226751011302</v>
+      </c>
+    </row>
+    <row r="499" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A499" t="s">
+        <v>77</v>
+      </c>
+      <c r="B499" t="s">
+        <v>60</v>
+      </c>
+      <c r="C499" s="2">
+        <v>47483</v>
+      </c>
+      <c r="D499">
+        <v>2029</v>
+      </c>
+      <c r="E499" t="s">
+        <v>18</v>
+      </c>
+      <c r="F499" t="s">
+        <v>85</v>
+      </c>
+      <c r="G499">
+        <v>14327.310265945731</v>
+      </c>
+      <c r="H499">
+        <v>13315.930471304629</v>
+      </c>
+      <c r="I499">
+        <v>15425.23387532917</v>
+      </c>
+    </row>
+    <row r="500" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A500" t="s">
+        <v>78</v>
+      </c>
+      <c r="B500" t="s">
+        <v>61</v>
+      </c>
+      <c r="C500" s="2">
+        <v>47483</v>
+      </c>
+      <c r="D500">
+        <v>2029</v>
+      </c>
+      <c r="E500" t="s">
+        <v>18</v>
+      </c>
+      <c r="F500" t="s">
+        <v>85</v>
+      </c>
+      <c r="G500">
+        <v>49548.257527147973</v>
+      </c>
+      <c r="H500">
+        <v>46050.594281748607</v>
+      </c>
+      <c r="I500">
+        <v>53345.215974552368</v>
+      </c>
+    </row>
+    <row r="501" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A501" t="s">
+        <v>75</v>
+      </c>
+      <c r="B501" t="s">
+        <v>62</v>
+      </c>
+      <c r="C501" s="2">
+        <v>47483</v>
+      </c>
+      <c r="D501">
+        <v>2029</v>
+      </c>
+      <c r="E501" t="s">
+        <v>18</v>
+      </c>
+      <c r="F501" t="s">
+        <v>85</v>
+      </c>
+      <c r="G501">
+        <v>9966.5702552479997</v>
+      </c>
+      <c r="H501">
+        <v>9263.0196521743947</v>
+      </c>
+      <c r="I501">
+        <v>10730.32371522748</v>
+      </c>
+    </row>
+    <row r="502" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A502" t="s">
+        <v>76</v>
+      </c>
+      <c r="B502" t="s">
+        <v>63</v>
+      </c>
+      <c r="C502" s="2">
+        <v>47483</v>
+      </c>
+      <c r="D502">
+        <v>2029</v>
+      </c>
+      <c r="E502" t="s">
+        <v>18</v>
+      </c>
+      <c r="F502" t="s">
+        <v>85</v>
+      </c>
+      <c r="G502">
+        <v>53908.79031850888</v>
+      </c>
+      <c r="H502">
+        <v>50103.312509371441</v>
+      </c>
+      <c r="I502">
+        <v>58039.903035783827</v>
+      </c>
+    </row>
+    <row r="503" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A503" t="s">
+        <v>74</v>
+      </c>
+      <c r="B503" t="s">
+        <v>9</v>
+      </c>
+      <c r="C503" s="2">
+        <v>47664</v>
+      </c>
+      <c r="D503">
+        <v>2030</v>
+      </c>
+      <c r="E503" t="s">
+        <v>19</v>
+      </c>
+      <c r="F503" t="s">
+        <v>85</v>
+      </c>
+      <c r="G503">
+        <v>65851.225027109307</v>
+      </c>
+      <c r="H503">
+        <v>61087.466046199661</v>
+      </c>
+      <c r="I503">
+        <v>71022.619079339842</v>
+      </c>
+    </row>
+    <row r="504" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A504" t="s">
+        <v>77</v>
+      </c>
+      <c r="B504" t="s">
+        <v>60</v>
+      </c>
+      <c r="C504" s="2">
+        <v>47664</v>
+      </c>
+      <c r="D504">
+        <v>2030</v>
+      </c>
+      <c r="E504" t="s">
+        <v>19</v>
+      </c>
+      <c r="F504" t="s">
+        <v>85</v>
+      </c>
+      <c r="G504">
+        <v>14770.498731926211</v>
+      </c>
+      <c r="H504">
+        <v>13701.982603976259</v>
+      </c>
+      <c r="I504">
+        <v>15930.44783324234</v>
+      </c>
+    </row>
+    <row r="505" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A505" t="s">
+        <v>78</v>
+      </c>
+      <c r="B505" t="s">
+        <v>61</v>
+      </c>
+      <c r="C505" s="2">
+        <v>47664</v>
+      </c>
+      <c r="D505">
+        <v>2030</v>
+      </c>
+      <c r="E505" t="s">
+        <v>19</v>
+      </c>
+      <c r="F505" t="s">
+        <v>85</v>
+      </c>
+      <c r="G505">
+        <v>51080.939924461367</v>
+      </c>
+      <c r="H505">
+        <v>47385.681617295741</v>
+      </c>
+      <c r="I505">
+        <v>55092.401651998807</v>
+      </c>
+    </row>
+    <row r="506" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A506" t="s">
+        <v>75</v>
+      </c>
+      <c r="B506" t="s">
+        <v>62</v>
+      </c>
+      <c r="C506" s="2">
+        <v>47664</v>
+      </c>
+      <c r="D506">
+        <v>2030</v>
+      </c>
+      <c r="E506" t="s">
+        <v>19</v>
+      </c>
+      <c r="F506" t="s">
+        <v>85</v>
+      </c>
+      <c r="G506">
+        <v>10274.867409460459</v>
+      </c>
+      <c r="H506">
+        <v>9531.5708059527406</v>
+      </c>
+      <c r="I506">
+        <v>11081.76793692775</v>
+      </c>
+    </row>
+    <row r="507" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A507" t="s">
+        <v>76</v>
+      </c>
+      <c r="B507" t="s">
+        <v>63</v>
+      </c>
+      <c r="C507" s="2">
+        <v>47664</v>
+      </c>
+      <c r="D507">
+        <v>2030</v>
+      </c>
+      <c r="E507" t="s">
+        <v>19</v>
+      </c>
+      <c r="F507" t="s">
+        <v>85</v>
+      </c>
+      <c r="G507">
+        <v>55576.35761764885</v>
+      </c>
+      <c r="H507">
+        <v>51555.895240246929</v>
+      </c>
+      <c r="I507">
+        <v>59940.851142412102</v>
+      </c>
+    </row>
+    <row r="508" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A508" t="s">
+        <v>74</v>
+      </c>
+      <c r="B508" t="s">
+        <v>9</v>
+      </c>
+      <c r="C508" s="2">
+        <v>47848</v>
+      </c>
+      <c r="D508">
+        <v>2030</v>
+      </c>
+      <c r="E508" t="s">
+        <v>20</v>
+      </c>
+      <c r="F508" t="s">
+        <v>85</v>
+      </c>
+      <c r="G508">
+        <v>68057.759440422902</v>
+      </c>
+      <c r="H508">
+        <v>63015.262943288137</v>
+      </c>
+      <c r="I508">
+        <v>73531.742590741007</v>
+      </c>
+    </row>
+    <row r="509" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A509" t="s">
+        <v>77</v>
+      </c>
+      <c r="B509" t="s">
+        <v>60</v>
+      </c>
+      <c r="C509" s="2">
+        <v>47848</v>
+      </c>
+      <c r="D509">
+        <v>2030</v>
+      </c>
+      <c r="E509" t="s">
+        <v>20</v>
+      </c>
+      <c r="F509" t="s">
+        <v>85</v>
+      </c>
+      <c r="G509">
+        <v>15265.42671147986</v>
+      </c>
+      <c r="H509">
+        <v>14134.389466751159</v>
+      </c>
+      <c r="I509">
+        <v>16493.246864363478</v>
+      </c>
+    </row>
+    <row r="510" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A510" t="s">
+        <v>78</v>
+      </c>
+      <c r="B510" t="s">
+        <v>61</v>
+      </c>
+      <c r="C510" s="2">
+        <v>47848</v>
+      </c>
+      <c r="D510">
+        <v>2030</v>
+      </c>
+      <c r="E510" t="s">
+        <v>20</v>
+      </c>
+      <c r="F510" t="s">
+        <v>85</v>
+      </c>
+      <c r="G510">
+        <v>52792.553516483807</v>
+      </c>
+      <c r="H510">
+        <v>48881.077905613849</v>
+      </c>
+      <c r="I510">
+        <v>57038.734272176684</v>
+      </c>
+    </row>
+    <row r="511" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A511" t="s">
+        <v>75</v>
+      </c>
+      <c r="B511" t="s">
+        <v>62</v>
+      </c>
+      <c r="C511" s="2">
+        <v>47848</v>
+      </c>
+      <c r="D511">
+        <v>2030</v>
+      </c>
+      <c r="E511" t="s">
+        <v>20</v>
+      </c>
+      <c r="F511" t="s">
+        <v>85</v>
+      </c>
+      <c r="G511">
+        <v>10619.156350507121</v>
+      </c>
+      <c r="H511">
+        <v>9832.3679058062226</v>
+      </c>
+      <c r="I511">
+        <v>11473.270317984339</v>
+      </c>
+    </row>
+    <row r="512" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A512" t="s">
+        <v>76</v>
+      </c>
+      <c r="B512" t="s">
+        <v>63</v>
+      </c>
+      <c r="C512" s="2">
+        <v>47848</v>
+      </c>
+      <c r="D512">
+        <v>2030</v>
+      </c>
+      <c r="E512" t="s">
+        <v>20</v>
+      </c>
+      <c r="F512" t="s">
+        <v>85</v>
+      </c>
+      <c r="G512">
+        <v>57438.603089915778</v>
+      </c>
+      <c r="H512">
+        <v>53182.895037481932</v>
+      </c>
+      <c r="I512">
+        <v>62058.472272756677</v>
+      </c>
+    </row>
+    <row r="513" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A513" t="s">
+        <v>79</v>
+      </c>
+      <c r="B513" t="s">
+        <v>64</v>
+      </c>
+      <c r="C513" s="2">
+        <v>46203</v>
+      </c>
+      <c r="D513">
+        <v>2026</v>
+      </c>
+      <c r="E513" t="s">
+        <v>10</v>
+      </c>
+      <c r="F513" t="s">
+        <v>85</v>
+      </c>
+      <c r="G513">
+        <v>51314.275885893258</v>
+      </c>
+      <c r="H513">
+        <v>48320.616112575721</v>
+      </c>
+      <c r="I513">
+        <v>54564.103261328593</v>
+      </c>
+    </row>
+    <row r="514" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A514" t="s">
+        <v>79</v>
+      </c>
+      <c r="B514" t="s">
+        <v>64</v>
+      </c>
+      <c r="C514" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D514">
+        <v>2026</v>
+      </c>
+      <c r="E514" t="s">
+        <v>12</v>
+      </c>
+      <c r="F514" t="s">
+        <v>85</v>
+      </c>
+      <c r="G514">
+        <v>51917.593900602202</v>
+      </c>
+      <c r="H514">
+        <v>48790.783318617337</v>
+      </c>
+      <c r="I514">
+        <v>55311.965805421023</v>
+      </c>
+    </row>
+    <row r="515" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A515" t="s">
+        <v>79</v>
+      </c>
+      <c r="B515" t="s">
+        <v>64</v>
+      </c>
+      <c r="C515" s="2">
+        <v>46568</v>
+      </c>
+      <c r="D515">
+        <v>2027</v>
+      </c>
+      <c r="E515" t="s">
+        <v>13</v>
+      </c>
+      <c r="F515" t="s">
+        <v>85</v>
+      </c>
+      <c r="G515">
+        <v>52637.695105211649</v>
+      </c>
+      <c r="H515">
+        <v>49367.69121823254</v>
+      </c>
+      <c r="I515">
+        <v>56187.513372605485</v>
+      </c>
+    </row>
+    <row r="516" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A516" t="s">
+        <v>79</v>
+      </c>
+      <c r="B516" t="s">
+        <v>64</v>
+      </c>
+      <c r="C516" s="2">
+        <v>46752</v>
+      </c>
+      <c r="D516">
+        <v>2027</v>
+      </c>
+      <c r="E516" t="s">
+        <v>14</v>
+      </c>
+      <c r="F516" t="s">
+        <v>85</v>
+      </c>
+      <c r="G516">
+        <v>53487.060286191278</v>
+      </c>
+      <c r="H516">
+        <v>50062.360604727015</v>
+      </c>
+      <c r="I516">
+        <v>57204.811674196695</v>
+      </c>
+    </row>
+    <row r="517" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A517" t="s">
+        <v>79</v>
+      </c>
+      <c r="B517" t="s">
+        <v>64</v>
+      </c>
+      <c r="C517" s="2">
+        <v>46934</v>
+      </c>
+      <c r="D517">
+        <v>2028</v>
+      </c>
+      <c r="E517" t="s">
+        <v>15</v>
+      </c>
+      <c r="F517" t="s">
+        <v>85</v>
+      </c>
+      <c r="G517">
+        <v>54478.789194642908</v>
+      </c>
+      <c r="H517">
+        <v>50886.299873699405</v>
+      </c>
+      <c r="I517">
+        <v>58378.687989161976</v>
+      </c>
+    </row>
+    <row r="518" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A518" t="s">
+        <v>79</v>
+      </c>
+      <c r="B518" t="s">
+        <v>64</v>
+      </c>
+      <c r="C518" s="2">
+        <v>47118</v>
+      </c>
+      <c r="D518">
+        <v>2028</v>
+      </c>
+      <c r="E518" t="s">
+        <v>16</v>
+      </c>
+      <c r="F518" t="s">
+        <v>85</v>
+      </c>
+      <c r="G518">
+        <v>55626.599341041379</v>
+      </c>
+      <c r="H518">
+        <v>51851.498260621083</v>
+      </c>
+      <c r="I518">
+        <v>59724.735991549838</v>
+      </c>
+    </row>
+    <row r="519" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A519" t="s">
+        <v>79</v>
+      </c>
+      <c r="B519" t="s">
+        <v>64</v>
+      </c>
+      <c r="C519" s="2">
+        <v>47299</v>
+      </c>
+      <c r="D519">
+        <v>2029</v>
+      </c>
+      <c r="E519" t="s">
+        <v>17</v>
+      </c>
+      <c r="F519" t="s">
+        <v>85</v>
+      </c>
+      <c r="G519">
+        <v>56944.824729712469</v>
+      </c>
+      <c r="H519">
+        <v>52970.41902166856</v>
+      </c>
+      <c r="I519">
+        <v>61259.32051383896</v>
+      </c>
+    </row>
+    <row r="520" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A520" t="s">
+        <v>79</v>
+      </c>
+      <c r="B520" t="s">
+        <v>64</v>
+      </c>
+      <c r="C520" s="2">
+        <v>47483</v>
+      </c>
+      <c r="D520">
+        <v>2029</v>
+      </c>
+      <c r="E520" t="s">
+        <v>18</v>
+      </c>
+      <c r="F520" t="s">
+        <v>85</v>
+      </c>
+      <c r="G520">
+        <v>58448.414530034635</v>
+      </c>
+      <c r="H520">
+        <v>54255.992554971475</v>
+      </c>
+      <c r="I520">
+        <v>62999.582243003664</v>
+      </c>
+    </row>
+    <row r="521" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A521" t="s">
+        <v>79</v>
+      </c>
+      <c r="B521" t="s">
+        <v>64</v>
+      </c>
+      <c r="C521" s="2">
+        <v>47664</v>
+      </c>
+      <c r="D521">
+        <v>2030</v>
+      </c>
+      <c r="E521" t="s">
+        <v>19</v>
+      </c>
+      <c r="F521" t="s">
+        <v>85</v>
+      </c>
+      <c r="G521">
+        <v>60152.931681200957</v>
+      </c>
+      <c r="H521">
+        <v>55721.609459296589</v>
+      </c>
+      <c r="I521">
+        <v>64963.44234593182</v>
+      </c>
+    </row>
+    <row r="522" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A522" t="s">
+        <v>79</v>
+      </c>
+      <c r="B522" t="s">
+        <v>64</v>
+      </c>
+      <c r="C522" s="2">
+        <v>47848</v>
+      </c>
+      <c r="D522">
+        <v>2030</v>
+      </c>
+      <c r="E522" t="s">
+        <v>20</v>
+      </c>
+      <c r="F522" t="s">
+        <v>85</v>
+      </c>
+      <c r="G522">
+        <v>62074.551427219129</v>
+      </c>
+      <c r="H522">
+        <v>57381.113527039917</v>
+      </c>
+      <c r="I522">
+        <v>67169.607020662588</v>
+      </c>
+    </row>
+    <row r="523" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A523" t="s">
+        <v>80</v>
+      </c>
+      <c r="B523" t="s">
+        <v>65</v>
+      </c>
+      <c r="C523" s="2">
+        <v>46203</v>
+      </c>
+      <c r="D523">
+        <v>2026</v>
+      </c>
+      <c r="E523" t="s">
+        <v>10</v>
+      </c>
+      <c r="F523" t="s">
+        <v>85</v>
+      </c>
+      <c r="G523">
+        <v>3856.8292328969201</v>
+      </c>
+      <c r="H523">
+        <v>3631.822949016906</v>
+      </c>
+      <c r="I523">
+        <v>4101.0893146589506</v>
+      </c>
+    </row>
+    <row r="524" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A524" t="s">
+        <v>80</v>
+      </c>
+      <c r="B524" t="s">
+        <v>65</v>
+      </c>
+      <c r="C524" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D524">
+        <v>2026</v>
+      </c>
+      <c r="E524" t="s">
+        <v>12</v>
+      </c>
+      <c r="F524" t="s">
+        <v>85</v>
+      </c>
+      <c r="G524">
+        <v>4049.6706945417664</v>
+      </c>
+      <c r="H524">
+        <v>3813.4140964677513</v>
+      </c>
+      <c r="I524">
+        <v>4306.143780391898</v>
+      </c>
+    </row>
+    <row r="525" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A525" t="s">
+        <v>80</v>
+      </c>
+      <c r="B525" t="s">
+        <v>65</v>
+      </c>
+      <c r="C525" s="2">
+        <v>46568</v>
+      </c>
+      <c r="D525">
+        <v>2027</v>
+      </c>
+      <c r="E525" t="s">
+        <v>13</v>
+      </c>
+      <c r="F525" t="s">
+        <v>85</v>
+      </c>
+      <c r="G525">
+        <v>4252.1542292688546</v>
+      </c>
+      <c r="H525">
+        <v>4004.0848012911392</v>
+      </c>
+      <c r="I525">
+        <v>4521.4509694114931</v>
+      </c>
+    </row>
+    <row r="526" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A526" t="s">
+        <v>80</v>
+      </c>
+      <c r="B526" t="s">
+        <v>65</v>
+      </c>
+      <c r="C526" s="2">
+        <v>46752</v>
+      </c>
+      <c r="D526">
+        <v>2027</v>
+      </c>
+      <c r="E526" t="s">
+        <v>14</v>
+      </c>
+      <c r="F526" t="s">
+        <v>85</v>
+      </c>
+      <c r="G526">
+        <v>4464.7619407322973</v>
+      </c>
+      <c r="H526">
+        <v>4204.2890413556961</v>
+      </c>
+      <c r="I526">
+        <v>4747.5235178820676</v>
+      </c>
+    </row>
+    <row r="527" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A527" t="s">
+        <v>80</v>
+      </c>
+      <c r="B527" t="s">
+        <v>65</v>
+      </c>
+      <c r="C527" s="2">
+        <v>46934</v>
+      </c>
+      <c r="D527">
+        <v>2028</v>
+      </c>
+      <c r="E527" t="s">
+        <v>15</v>
+      </c>
+      <c r="F527" t="s">
+        <v>85</v>
+      </c>
+      <c r="G527">
+        <v>4688.0000377689121</v>
+      </c>
+      <c r="H527">
+        <v>4414.5034934234809</v>
+      </c>
+      <c r="I527">
+        <v>4984.8996937761713</v>
+      </c>
+    </row>
+    <row r="528" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A528" t="s">
+        <v>80</v>
+      </c>
+      <c r="B528" t="s">
+        <v>65</v>
+      </c>
+      <c r="C528" s="2">
+        <v>47118</v>
+      </c>
+      <c r="D528">
+        <v>2028</v>
+      </c>
+      <c r="E528" t="s">
+        <v>16</v>
+      </c>
+      <c r="F528" t="s">
+        <v>85</v>
+      </c>
+      <c r="G528">
+        <v>4922.4000396573583</v>
+      </c>
+      <c r="H528">
+        <v>4635.2286680946554</v>
+      </c>
+      <c r="I528">
+        <v>5234.1446784649797</v>
+      </c>
+    </row>
+    <row r="529" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A529" t="s">
+        <v>80</v>
+      </c>
+      <c r="B529" t="s">
+        <v>65</v>
+      </c>
+      <c r="C529" s="2">
+        <v>47299</v>
+      </c>
+      <c r="D529">
+        <v>2029</v>
+      </c>
+      <c r="E529" t="s">
+        <v>17</v>
+      </c>
+      <c r="F529" t="s">
+        <v>85</v>
+      </c>
+      <c r="G529">
+        <v>5168.5200416402267</v>
+      </c>
+      <c r="H529">
+        <v>4866.9901014993884</v>
+      </c>
+      <c r="I529">
+        <v>5495.8519123882288</v>
+      </c>
+    </row>
+    <row r="530" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A530" t="s">
+        <v>80</v>
+      </c>
+      <c r="B530" t="s">
+        <v>65</v>
+      </c>
+      <c r="C530" s="2">
+        <v>47483</v>
+      </c>
+      <c r="D530">
+        <v>2029</v>
+      </c>
+      <c r="E530" t="s">
+        <v>18</v>
+      </c>
+      <c r="F530" t="s">
+        <v>85</v>
+      </c>
+      <c r="G530">
+        <v>5426.9460437222388</v>
+      </c>
+      <c r="H530">
+        <v>5110.3396065743582</v>
+      </c>
+      <c r="I530">
+        <v>5770.6445080076401</v>
+      </c>
+    </row>
+    <row r="531" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A531" t="s">
+        <v>80</v>
+      </c>
+      <c r="B531" t="s">
+        <v>65</v>
+      </c>
+      <c r="C531" s="2">
+        <v>47664</v>
+      </c>
+      <c r="D531">
+        <v>2030</v>
+      </c>
+      <c r="E531" t="s">
+        <v>19</v>
+      </c>
+      <c r="F531" t="s">
+        <v>85</v>
+      </c>
+      <c r="G531">
+        <v>5698.2933459083506</v>
+      </c>
+      <c r="H531">
+        <v>5365.8565869030763</v>
+      </c>
+      <c r="I531">
+        <v>6059.1767334080223</v>
+      </c>
+    </row>
+    <row r="532" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A532" t="s">
+        <v>80</v>
+      </c>
+      <c r="B532" t="s">
+        <v>65</v>
+      </c>
+      <c r="C532" s="2">
+        <v>47848</v>
+      </c>
+      <c r="D532">
+        <v>2030</v>
+      </c>
+      <c r="E532" t="s">
+        <v>20</v>
+      </c>
+      <c r="F532" t="s">
+        <v>85</v>
+      </c>
+      <c r="G532">
+        <v>5983.2080132037681</v>
+      </c>
+      <c r="H532">
+        <v>5634.1494162482304</v>
+      </c>
+      <c r="I532">
+        <v>6362.1355700784234</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Prospectiva/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1072" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{803FD8CF-5996-4F09-B1C4-9B9539E03452}"/>
+  <xr:revisionPtr revIDLastSave="1107" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1356E6AB-8114-4148-A74E-6140AD6E1CB9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Proyecciones" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$I$522</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$I$532</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1867,10 +1867,12 @@
         <v>94.862857142857138</v>
       </c>
       <c r="H40">
+        <f>+G40*0.97</f>
         <v>92.016971428571424</v>
       </c>
       <c r="I40">
-        <v>97.708742857142852</v>
+        <f>+G40*1.005</f>
+        <v>95.337171428571409</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
@@ -1893,13 +1895,16 @@
         <v>25</v>
       </c>
       <c r="G41">
-        <v>95.406785714285718</v>
+        <f>+G40*1.0035</f>
+        <v>95.194877142857138</v>
       </c>
       <c r="H41">
-        <v>88.516964285714295</v>
+        <f t="shared" ref="H41:H49" si="1">+G41*0.97</f>
+        <v>92.339030828571424</v>
       </c>
       <c r="I41">
-        <v>98.622035714285715</v>
+        <f t="shared" ref="I41:I49" si="2">+G41*1.005</f>
+        <v>95.670851528571418</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
@@ -1922,13 +1927,16 @@
         <v>25</v>
       </c>
       <c r="G42">
-        <v>95.950714285714284</v>
+        <f t="shared" ref="G42:G49" si="3">+G41*1.0035</f>
+        <v>95.528059212857144</v>
       </c>
       <c r="H42">
-        <v>89.876785714285717</v>
+        <f t="shared" si="1"/>
+        <v>92.662217436471423</v>
       </c>
       <c r="I42">
-        <v>98.785214285714289</v>
+        <f t="shared" si="2"/>
+        <v>96.005699508921424</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
@@ -1951,13 +1959,16 @@
         <v>25</v>
       </c>
       <c r="G43">
-        <v>96.49464285714285</v>
+        <f t="shared" si="3"/>
+        <v>95.862407420102144</v>
       </c>
       <c r="H43">
-        <v>91.236607142857125</v>
+        <f t="shared" si="1"/>
+        <v>92.98653519749908</v>
       </c>
       <c r="I43">
-        <v>98.948392857142849</v>
+        <f t="shared" si="2"/>
+        <v>96.341719457202643</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
@@ -1980,13 +1991,16 @@
         <v>25</v>
       </c>
       <c r="G44">
-        <v>97.038571428571416</v>
+        <f t="shared" si="3"/>
+        <v>96.197925846072508</v>
       </c>
       <c r="H44">
-        <v>92.596428571428532</v>
+        <f t="shared" si="1"/>
+        <v>93.311988070690333</v>
       </c>
       <c r="I44">
-        <v>99.111571428571423</v>
+        <f t="shared" si="2"/>
+        <v>96.678915475302858</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
@@ -2009,13 +2023,16 @@
         <v>25</v>
       </c>
       <c r="G45">
-        <v>97.582499999999996</v>
+        <f t="shared" si="3"/>
+        <v>96.534618586533767</v>
       </c>
       <c r="H45">
-        <v>93.956249999999983</v>
+        <f t="shared" si="1"/>
+        <v>93.638580028937753</v>
       </c>
       <c r="I45">
-        <v>99.274749999999997</v>
+        <f t="shared" si="2"/>
+        <v>97.017291679466425</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
@@ -2038,13 +2055,16 @@
         <v>25</v>
       </c>
       <c r="G46">
-        <v>98.126428571428562</v>
+        <f t="shared" si="3"/>
+        <v>96.872489751586642</v>
       </c>
       <c r="H46">
-        <v>95.316071428571405</v>
+        <f t="shared" si="1"/>
+        <v>93.966315059039033</v>
       </c>
       <c r="I46">
-        <v>99.437928571428571</v>
+        <f t="shared" si="2"/>
+        <v>97.356852200344562</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
@@ -2067,13 +2087,16 @@
         <v>25</v>
       </c>
       <c r="G47">
-        <v>98.670357142857128</v>
+        <f t="shared" si="3"/>
+        <v>97.211543465717199</v>
       </c>
       <c r="H47">
-        <v>96.675892857142827</v>
+        <f t="shared" si="1"/>
+        <v>94.295197161745676</v>
       </c>
       <c r="I47">
-        <v>99.601107142857131</v>
+        <f t="shared" si="2"/>
+        <v>97.697601183045776</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
@@ -2096,13 +2119,16 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>99.214285714285708</v>
+        <f t="shared" si="3"/>
+        <v>97.55178386784722</v>
       </c>
       <c r="H48">
-        <v>98.035714285714278</v>
+        <f t="shared" si="1"/>
+        <v>94.625230351811794</v>
       </c>
       <c r="I48">
-        <v>99.764285714285705</v>
+        <f t="shared" si="2"/>
+        <v>98.039542787186448</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
@@ -2125,13 +2151,16 @@
         <v>25</v>
       </c>
       <c r="G49">
-        <v>99.758214285714274</v>
+        <f t="shared" si="3"/>
+        <v>97.893215111384691</v>
       </c>
       <c r="H49">
-        <v>99.395535714285685</v>
+        <f t="shared" si="1"/>
+        <v>94.956418658043148</v>
       </c>
       <c r="I49">
-        <v>99.927464285714279</v>
+        <f t="shared" si="2"/>
+        <v>98.38268118694161</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">

--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1107" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1356E6AB-8114-4148-A74E-6140AD6E1CB9}"/>
+  <xr:revisionPtr revIDLastSave="1161" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC2E5972-F9F3-4B6D-A118-01154D7D014C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Proyecciones" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$I$532</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$I$542</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1827" uniqueCount="87">
   <si>
     <t>Id</t>
   </si>
@@ -297,6 +297,9 @@
   </si>
   <si>
     <t>Polinomial_Grado_4</t>
+  </si>
+  <si>
+    <t>Tendencia_Historica</t>
   </si>
 </sst>
 </file>
@@ -704,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}">
-  <dimension ref="A1:I532"/>
+  <dimension ref="A1:I542"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
@@ -765,7 +768,7 @@
         <v>78.188299480195042</v>
       </c>
       <c r="I2">
-        <v>96.466210501716631</v>
+        <v>90.466210501716631</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -794,7 +797,7 @@
         <v>80.539762248687467</v>
       </c>
       <c r="I3">
-        <v>98.817673270209056</v>
+        <v>92.466210501716631</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -823,7 +826,7 @@
         <v>82.333336603876432</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>94.466210501716631</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -852,7 +855,7 @@
         <v>84.162782446169174</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>96.466210501716631</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -881,7 +884,7 @@
         <v>86.028817205307774</v>
       </c>
       <c r="I6">
-        <v>100</v>
+        <v>98.817673270209056</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -16168,6 +16171,296 @@
       </c>
       <c r="I532">
         <v>6362.1355700784234</v>
+      </c>
+    </row>
+    <row r="533" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A533">
+        <v>200</v>
+      </c>
+      <c r="B533" t="s">
+        <v>31</v>
+      </c>
+      <c r="C533" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D533">
+        <v>2026</v>
+      </c>
+      <c r="E533" t="s">
+        <v>12</v>
+      </c>
+      <c r="F533" t="s">
+        <v>86</v>
+      </c>
+      <c r="G533">
+        <v>91.3</v>
+      </c>
+      <c r="H533">
+        <v>86.74</v>
+      </c>
+      <c r="I533">
+        <v>95.87</v>
+      </c>
+    </row>
+    <row r="534" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A534">
+        <v>200</v>
+      </c>
+      <c r="B534" t="s">
+        <v>31</v>
+      </c>
+      <c r="C534" s="2">
+        <v>46752</v>
+      </c>
+      <c r="D534">
+        <v>2027</v>
+      </c>
+      <c r="E534" t="s">
+        <v>14</v>
+      </c>
+      <c r="F534" t="s">
+        <v>86</v>
+      </c>
+      <c r="G534">
+        <v>91.76</v>
+      </c>
+      <c r="H534">
+        <v>87.17</v>
+      </c>
+      <c r="I534">
+        <v>96.35</v>
+      </c>
+    </row>
+    <row r="535" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A535">
+        <v>200</v>
+      </c>
+      <c r="B535" t="s">
+        <v>31</v>
+      </c>
+      <c r="C535" s="2">
+        <v>47118</v>
+      </c>
+      <c r="D535">
+        <v>2028</v>
+      </c>
+      <c r="E535" t="s">
+        <v>16</v>
+      </c>
+      <c r="F535" t="s">
+        <v>86</v>
+      </c>
+      <c r="G535">
+        <v>92.22</v>
+      </c>
+      <c r="H535">
+        <v>87.61</v>
+      </c>
+      <c r="I535">
+        <v>96.83</v>
+      </c>
+    </row>
+    <row r="536" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A536">
+        <v>200</v>
+      </c>
+      <c r="B536" t="s">
+        <v>31</v>
+      </c>
+      <c r="C536" s="2">
+        <v>47483</v>
+      </c>
+      <c r="D536">
+        <v>2029</v>
+      </c>
+      <c r="E536" t="s">
+        <v>18</v>
+      </c>
+      <c r="F536" t="s">
+        <v>86</v>
+      </c>
+      <c r="G536">
+        <v>92.68</v>
+      </c>
+      <c r="H536">
+        <v>88.04</v>
+      </c>
+      <c r="I536">
+        <v>97.31</v>
+      </c>
+    </row>
+    <row r="537" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A537">
+        <v>200</v>
+      </c>
+      <c r="B537" t="s">
+        <v>31</v>
+      </c>
+      <c r="C537" s="2">
+        <v>47848</v>
+      </c>
+      <c r="D537">
+        <v>2030</v>
+      </c>
+      <c r="E537" t="s">
+        <v>20</v>
+      </c>
+      <c r="F537" t="s">
+        <v>86</v>
+      </c>
+      <c r="G537">
+        <v>93.14</v>
+      </c>
+      <c r="H537">
+        <v>88.48</v>
+      </c>
+      <c r="I537">
+        <v>97.8</v>
+      </c>
+    </row>
+    <row r="538" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A538">
+        <v>203</v>
+      </c>
+      <c r="B538" t="s">
+        <v>32</v>
+      </c>
+      <c r="C538" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D538">
+        <v>2026</v>
+      </c>
+      <c r="E538" t="s">
+        <v>12</v>
+      </c>
+      <c r="F538" t="s">
+        <v>86</v>
+      </c>
+      <c r="G538">
+        <v>346582.22</v>
+      </c>
+      <c r="H538">
+        <v>318855.64</v>
+      </c>
+      <c r="I538">
+        <v>374308.8</v>
+      </c>
+    </row>
+    <row r="539" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A539">
+        <v>203</v>
+      </c>
+      <c r="B539" t="s">
+        <v>32</v>
+      </c>
+      <c r="C539" s="2">
+        <v>46752</v>
+      </c>
+      <c r="D539">
+        <v>2027</v>
+      </c>
+      <c r="E539" t="s">
+        <v>14</v>
+      </c>
+      <c r="F539" t="s">
+        <v>86</v>
+      </c>
+      <c r="G539">
+        <v>382599.16</v>
+      </c>
+      <c r="H539">
+        <v>351991.22</v>
+      </c>
+      <c r="I539">
+        <v>413207.09</v>
+      </c>
+    </row>
+    <row r="540" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A540">
+        <v>203</v>
+      </c>
+      <c r="B540" t="s">
+        <v>32</v>
+      </c>
+      <c r="C540" s="2">
+        <v>47118</v>
+      </c>
+      <c r="D540">
+        <v>2028</v>
+      </c>
+      <c r="E540" t="s">
+        <v>16</v>
+      </c>
+      <c r="F540" t="s">
+        <v>86</v>
+      </c>
+      <c r="G540">
+        <v>418916.4</v>
+      </c>
+      <c r="H540">
+        <v>385403.08</v>
+      </c>
+      <c r="I540">
+        <v>452429.71</v>
+      </c>
+    </row>
+    <row r="541" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A541">
+        <v>203</v>
+      </c>
+      <c r="B541" t="s">
+        <v>32</v>
+      </c>
+      <c r="C541" s="2">
+        <v>47483</v>
+      </c>
+      <c r="D541">
+        <v>2029</v>
+      </c>
+      <c r="E541" t="s">
+        <v>18</v>
+      </c>
+      <c r="F541" t="s">
+        <v>86</v>
+      </c>
+      <c r="G541">
+        <v>455386.82</v>
+      </c>
+      <c r="H541">
+        <v>418955.87</v>
+      </c>
+      <c r="I541">
+        <v>491817.77</v>
+      </c>
+    </row>
+    <row r="542" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A542">
+        <v>203</v>
+      </c>
+      <c r="B542" t="s">
+        <v>32</v>
+      </c>
+      <c r="C542" s="2">
+        <v>47848</v>
+      </c>
+      <c r="D542">
+        <v>2030</v>
+      </c>
+      <c r="E542" t="s">
+        <v>20</v>
+      </c>
+      <c r="F542" t="s">
+        <v>86</v>
+      </c>
+      <c r="G542">
+        <v>491883.76</v>
+      </c>
+      <c r="H542">
+        <v>452533.06</v>
+      </c>
+      <c r="I542">
+        <v>531234.46</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1161" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC2E5972-F9F3-4B6D-A118-01154D7D014C}"/>
+  <xr:revisionPtr revIDLastSave="1196" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4482FEAB-A724-49EB-B14D-38517D833471}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Proyecciones" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$I$542</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$I$552</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1827" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="89">
   <si>
     <t>Id</t>
   </si>
@@ -300,6 +300,12 @@
   </si>
   <si>
     <t>Tendencia_Historica</t>
+  </si>
+  <si>
+    <t>Ensemble_Ponderado</t>
+  </si>
+  <si>
+    <t>ARIMA</t>
   </si>
 </sst>
 </file>
@@ -707,7 +713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}">
-  <dimension ref="A1:I542"/>
+  <dimension ref="A1:I557"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
@@ -2618,16 +2624,16 @@
         <v>12</v>
       </c>
       <c r="F65" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="G65">
-        <v>132301.57511745999</v>
+        <v>208028</v>
       </c>
       <c r="H65">
-        <v>105841.260093968</v>
+        <v>196794.48</v>
       </c>
       <c r="I65">
-        <v>158761.89014095199</v>
+        <v>219261.51</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
@@ -2647,16 +2653,16 @@
         <v>14</v>
       </c>
       <c r="F66" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="G66">
-        <v>136270.62237098379</v>
+        <v>221304.03</v>
       </c>
       <c r="H66">
-        <v>108198.8741625611</v>
+        <v>208468.4</v>
       </c>
       <c r="I66">
-        <v>164342.37057940639</v>
+        <v>234139.67</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
@@ -2676,16 +2682,16 @@
         <v>16</v>
       </c>
       <c r="F67" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="G67">
-        <v>140358.74104211331</v>
+        <v>235427.33</v>
       </c>
       <c r="H67">
-        <v>110602.6879411853</v>
+        <v>220830.83</v>
       </c>
       <c r="I67">
-        <v>170114.7941430413</v>
+        <v>250023.82</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
@@ -2705,16 +2711,16 @@
         <v>18</v>
       </c>
       <c r="F68" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="G68">
-        <v>144569.5032733767</v>
+        <v>250451.95</v>
       </c>
       <c r="H68">
-        <v>113053.3515597806</v>
+        <v>233922.12</v>
       </c>
       <c r="I68">
-        <v>176085.65498697289</v>
+        <v>266981.78000000003</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
@@ -2734,16 +2740,16 @@
         <v>20</v>
       </c>
       <c r="F69" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="G69">
-        <v>148906.58837157799</v>
+        <v>266435.42</v>
       </c>
       <c r="H69">
-        <v>115551.5125763446</v>
+        <v>247784.94</v>
       </c>
       <c r="I69">
-        <v>182261.6641668115</v>
+        <v>285085.90000000002</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
@@ -6475,16 +6481,16 @@
         <v>12</v>
       </c>
       <c r="F198" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="G198">
-        <v>11828.030016950001</v>
+        <v>11770.07</v>
       </c>
       <c r="H198">
-        <v>9462.4240135599994</v>
+        <v>11134.49</v>
       </c>
       <c r="I198">
-        <v>14193.63602034</v>
+        <v>12405.66</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.3">
@@ -6504,16 +6510,16 @@
         <v>14</v>
       </c>
       <c r="F199" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="G199">
-        <v>13602.2345194925</v>
+        <v>12574.74</v>
       </c>
       <c r="H199">
-        <v>10800.174208477039</v>
+        <v>11845.4</v>
       </c>
       <c r="I199">
-        <v>16404.294830507952</v>
+        <v>13304.07</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.3">
@@ -6533,16 +6539,16 @@
         <v>16</v>
       </c>
       <c r="F200" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="G200">
-        <v>15642.569697416369</v>
+        <v>13434.41</v>
       </c>
       <c r="H200">
-        <v>12326.344921564099</v>
+        <v>12601.48</v>
       </c>
       <c r="I200">
-        <v>18958.794473268641</v>
+        <v>14267.35</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.3">
@@ -6562,16 +6568,16 @@
         <v>18</v>
       </c>
       <c r="F201" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="G201">
-        <v>17988.95515202883</v>
+        <v>14352.86</v>
       </c>
       <c r="H201">
-        <v>14067.36292888654</v>
+        <v>13405.57</v>
       </c>
       <c r="I201">
-        <v>21910.547375171111</v>
+        <v>15300.15</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.3">
@@ -6591,16 +6597,16 @@
         <v>20</v>
       </c>
       <c r="F202" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="G202">
-        <v>20687.298424833149</v>
+        <v>15334.1</v>
       </c>
       <c r="H202">
-        <v>16053.343577670519</v>
+        <v>14260.71</v>
       </c>
       <c r="I202">
-        <v>25321.253271995771</v>
+        <v>16407.490000000002</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.3">
@@ -16461,6 +16467,441 @@
       </c>
       <c r="I542">
         <v>531234.46</v>
+      </c>
+    </row>
+    <row r="543" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A543">
+        <v>204</v>
+      </c>
+      <c r="B543" t="s">
+        <v>34</v>
+      </c>
+      <c r="C543" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D543">
+        <v>2026</v>
+      </c>
+      <c r="E543" t="s">
+        <v>12</v>
+      </c>
+      <c r="F543" t="s">
+        <v>87</v>
+      </c>
+      <c r="G543">
+        <v>208714.84</v>
+      </c>
+      <c r="H543">
+        <v>197444.24</v>
+      </c>
+      <c r="I543">
+        <v>219985.44</v>
+      </c>
+    </row>
+    <row r="544" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A544">
+        <v>204</v>
+      </c>
+      <c r="B544" t="s">
+        <v>34</v>
+      </c>
+      <c r="C544" s="2">
+        <v>46752</v>
+      </c>
+      <c r="D544">
+        <v>2027</v>
+      </c>
+      <c r="E544" t="s">
+        <v>14</v>
+      </c>
+      <c r="F544" t="s">
+        <v>87</v>
+      </c>
+      <c r="G544">
+        <v>220680.92</v>
+      </c>
+      <c r="H544">
+        <v>207881.43</v>
+      </c>
+      <c r="I544">
+        <v>233480.42</v>
+      </c>
+    </row>
+    <row r="545" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A545">
+        <v>204</v>
+      </c>
+      <c r="B545" t="s">
+        <v>34</v>
+      </c>
+      <c r="C545" s="2">
+        <v>47118</v>
+      </c>
+      <c r="D545">
+        <v>2028</v>
+      </c>
+      <c r="E545" t="s">
+        <v>16</v>
+      </c>
+      <c r="F545" t="s">
+        <v>87</v>
+      </c>
+      <c r="G545">
+        <v>231997.19</v>
+      </c>
+      <c r="H545">
+        <v>217613.36</v>
+      </c>
+      <c r="I545">
+        <v>246381.01</v>
+      </c>
+    </row>
+    <row r="546" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A546">
+        <v>204</v>
+      </c>
+      <c r="B546" t="s">
+        <v>34</v>
+      </c>
+      <c r="C546" s="2">
+        <v>47483</v>
+      </c>
+      <c r="D546">
+        <v>2029</v>
+      </c>
+      <c r="E546" t="s">
+        <v>18</v>
+      </c>
+      <c r="F546" t="s">
+        <v>87</v>
+      </c>
+      <c r="G546">
+        <v>242749</v>
+      </c>
+      <c r="H546">
+        <v>226727.56</v>
+      </c>
+      <c r="I546">
+        <v>258770.43</v>
+      </c>
+    </row>
+    <row r="547" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A547">
+        <v>204</v>
+      </c>
+      <c r="B547" t="s">
+        <v>34</v>
+      </c>
+      <c r="C547" s="2">
+        <v>47848</v>
+      </c>
+      <c r="D547">
+        <v>2030</v>
+      </c>
+      <c r="E547" t="s">
+        <v>20</v>
+      </c>
+      <c r="F547" t="s">
+        <v>87</v>
+      </c>
+      <c r="G547">
+        <v>252982.45</v>
+      </c>
+      <c r="H547">
+        <v>235273.68</v>
+      </c>
+      <c r="I547">
+        <v>270691.21999999997</v>
+      </c>
+    </row>
+    <row r="548" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A548">
+        <v>205</v>
+      </c>
+      <c r="B548" t="s">
+        <v>35</v>
+      </c>
+      <c r="C548" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D548">
+        <v>2026</v>
+      </c>
+      <c r="E548" t="s">
+        <v>12</v>
+      </c>
+      <c r="F548" t="s">
+        <v>86</v>
+      </c>
+      <c r="G548">
+        <v>6438.01</v>
+      </c>
+      <c r="H548">
+        <v>6090.36</v>
+      </c>
+      <c r="I548">
+        <v>6785.66</v>
+      </c>
+    </row>
+    <row r="549" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A549">
+        <v>205</v>
+      </c>
+      <c r="B549" t="s">
+        <v>35</v>
+      </c>
+      <c r="C549" s="2">
+        <v>46752</v>
+      </c>
+      <c r="D549">
+        <v>2027</v>
+      </c>
+      <c r="E549" t="s">
+        <v>14</v>
+      </c>
+      <c r="F549" t="s">
+        <v>86</v>
+      </c>
+      <c r="G549">
+        <v>7190.91</v>
+      </c>
+      <c r="H549">
+        <v>6773.84</v>
+      </c>
+      <c r="I549">
+        <v>7607.99</v>
+      </c>
+    </row>
+    <row r="550" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A550">
+        <v>205</v>
+      </c>
+      <c r="B550" t="s">
+        <v>35</v>
+      </c>
+      <c r="C550" s="2">
+        <v>47118</v>
+      </c>
+      <c r="D550">
+        <v>2028</v>
+      </c>
+      <c r="E550" t="s">
+        <v>16</v>
+      </c>
+      <c r="F550" t="s">
+        <v>86</v>
+      </c>
+      <c r="G550">
+        <v>8031.87</v>
+      </c>
+      <c r="H550">
+        <v>7533.89</v>
+      </c>
+      <c r="I550">
+        <v>8529.84</v>
+      </c>
+    </row>
+    <row r="551" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A551">
+        <v>205</v>
+      </c>
+      <c r="B551" t="s">
+        <v>35</v>
+      </c>
+      <c r="C551" s="2">
+        <v>47483</v>
+      </c>
+      <c r="D551">
+        <v>2029</v>
+      </c>
+      <c r="E551" t="s">
+        <v>18</v>
+      </c>
+      <c r="F551" t="s">
+        <v>86</v>
+      </c>
+      <c r="G551">
+        <v>8971.17</v>
+      </c>
+      <c r="H551">
+        <v>8379.07</v>
+      </c>
+      <c r="I551">
+        <v>9563.27</v>
+      </c>
+    </row>
+    <row r="552" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A552">
+        <v>205</v>
+      </c>
+      <c r="B552" t="s">
+        <v>35</v>
+      </c>
+      <c r="C552" s="2">
+        <v>47848</v>
+      </c>
+      <c r="D552">
+        <v>2030</v>
+      </c>
+      <c r="E552" t="s">
+        <v>20</v>
+      </c>
+      <c r="F552" t="s">
+        <v>86</v>
+      </c>
+      <c r="G552">
+        <v>10020.32</v>
+      </c>
+      <c r="H552">
+        <v>9318.9</v>
+      </c>
+      <c r="I552">
+        <v>10721.74</v>
+      </c>
+    </row>
+    <row r="553" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A553" s="3">
+        <v>377</v>
+      </c>
+      <c r="B553" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C553" s="4">
+        <v>46387</v>
+      </c>
+      <c r="D553" s="3">
+        <v>2026</v>
+      </c>
+      <c r="E553" t="s">
+        <v>12</v>
+      </c>
+      <c r="F553" t="s">
+        <v>88</v>
+      </c>
+      <c r="G553">
+        <v>11678.75</v>
+      </c>
+      <c r="H553">
+        <v>11048.1</v>
+      </c>
+      <c r="I553">
+        <v>12309.4</v>
+      </c>
+    </row>
+    <row r="554" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A554" s="3">
+        <v>377</v>
+      </c>
+      <c r="B554" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C554" s="4">
+        <v>46752</v>
+      </c>
+      <c r="D554" s="3">
+        <v>2027</v>
+      </c>
+      <c r="E554" t="s">
+        <v>14</v>
+      </c>
+      <c r="F554" t="s">
+        <v>88</v>
+      </c>
+      <c r="G554">
+        <v>12380.37</v>
+      </c>
+      <c r="H554">
+        <v>11662.31</v>
+      </c>
+      <c r="I554">
+        <v>13098.43</v>
+      </c>
+    </row>
+    <row r="555" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A555" s="3">
+        <v>377</v>
+      </c>
+      <c r="B555" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C555" s="4">
+        <v>47118</v>
+      </c>
+      <c r="D555" s="3">
+        <v>2028</v>
+      </c>
+      <c r="E555" t="s">
+        <v>16</v>
+      </c>
+      <c r="F555" t="s">
+        <v>88</v>
+      </c>
+      <c r="G555">
+        <v>13124.13</v>
+      </c>
+      <c r="H555">
+        <v>12310.44</v>
+      </c>
+      <c r="I555">
+        <v>13937.83</v>
+      </c>
+    </row>
+    <row r="556" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A556" s="3">
+        <v>377</v>
+      </c>
+      <c r="B556" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C556" s="4">
+        <v>47483</v>
+      </c>
+      <c r="D556" s="3">
+        <v>2029</v>
+      </c>
+      <c r="E556" t="s">
+        <v>18</v>
+      </c>
+      <c r="F556" t="s">
+        <v>88</v>
+      </c>
+      <c r="G556">
+        <v>13912.58</v>
+      </c>
+      <c r="H556">
+        <v>12994.35</v>
+      </c>
+      <c r="I556">
+        <v>14830.81</v>
+      </c>
+    </row>
+    <row r="557" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A557" s="3">
+        <v>377</v>
+      </c>
+      <c r="B557" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C557" s="4">
+        <v>47848</v>
+      </c>
+      <c r="D557" s="3">
+        <v>2030</v>
+      </c>
+      <c r="E557" t="s">
+        <v>20</v>
+      </c>
+      <c r="F557" t="s">
+        <v>88</v>
+      </c>
+      <c r="G557">
+        <v>14748.39</v>
+      </c>
+      <c r="H557">
+        <v>13716.01</v>
+      </c>
+      <c r="I557">
+        <v>15780.78</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1196" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4482FEAB-A724-49EB-B14D-38517D833471}"/>
+  <xr:revisionPtr revIDLastSave="1200" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0B411D9-B4E1-4C33-9343-8ACBBF706F58}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Proyecciones" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$I$552</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$I$557</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -16901,7 +16901,7 @@
         <v>13716.01</v>
       </c>
       <c r="I557">
-        <v>15780.78</v>
+        <v>15780.8</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Modelo_Prospectivo/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Prospectiva/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1200" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0B411D9-B4E1-4C33-9343-8ACBBF706F58}"/>
+  <xr:revisionPtr revIDLastSave="1206" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDD15E09-4F75-4AA4-9CCF-B027C0093CB2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1887" uniqueCount="90">
   <si>
     <t>Id</t>
   </si>
@@ -306,6 +306,9 @@
   </si>
   <si>
     <t>ARIMA</t>
+  </si>
+  <si>
+    <t>Prophet</t>
   </si>
 </sst>
 </file>
@@ -713,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}">
-  <dimension ref="A1:I557"/>
+  <dimension ref="A1:I562"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
@@ -16904,6 +16907,151 @@
         <v>15780.8</v>
       </c>
     </row>
+    <row r="558" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A558">
+        <v>376</v>
+      </c>
+      <c r="B558" t="s">
+        <v>72</v>
+      </c>
+      <c r="C558" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D558">
+        <v>2026</v>
+      </c>
+      <c r="E558" t="s">
+        <v>12</v>
+      </c>
+      <c r="F558" t="s">
+        <v>89</v>
+      </c>
+      <c r="G558">
+        <v>45618.99</v>
+      </c>
+      <c r="H558">
+        <v>43246.8</v>
+      </c>
+      <c r="I558">
+        <v>47991.18</v>
+      </c>
+    </row>
+    <row r="559" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A559">
+        <v>376</v>
+      </c>
+      <c r="B559" t="s">
+        <v>72</v>
+      </c>
+      <c r="C559" s="2">
+        <v>46752</v>
+      </c>
+      <c r="D559">
+        <v>2027</v>
+      </c>
+      <c r="E559" t="s">
+        <v>14</v>
+      </c>
+      <c r="F559" t="s">
+        <v>89</v>
+      </c>
+      <c r="G559">
+        <v>47010.37</v>
+      </c>
+      <c r="H559">
+        <v>44471.81</v>
+      </c>
+      <c r="I559">
+        <v>49548.93</v>
+      </c>
+    </row>
+    <row r="560" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A560">
+        <v>376</v>
+      </c>
+      <c r="B560" t="s">
+        <v>72</v>
+      </c>
+      <c r="C560" s="2">
+        <v>47118</v>
+      </c>
+      <c r="D560">
+        <v>2028</v>
+      </c>
+      <c r="E560" t="s">
+        <v>16</v>
+      </c>
+      <c r="F560" t="s">
+        <v>89</v>
+      </c>
+      <c r="G560">
+        <v>50052.08</v>
+      </c>
+      <c r="H560">
+        <v>47249.17</v>
+      </c>
+      <c r="I560">
+        <v>52855</v>
+      </c>
+    </row>
+    <row r="561" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A561">
+        <v>376</v>
+      </c>
+      <c r="B561" t="s">
+        <v>72</v>
+      </c>
+      <c r="C561" s="2">
+        <v>47483</v>
+      </c>
+      <c r="D561">
+        <v>2029</v>
+      </c>
+      <c r="E561" t="s">
+        <v>18</v>
+      </c>
+      <c r="F561" t="s">
+        <v>89</v>
+      </c>
+      <c r="G561">
+        <v>53243.94</v>
+      </c>
+      <c r="H561">
+        <v>50155.79</v>
+      </c>
+      <c r="I561">
+        <v>56332.08</v>
+      </c>
+    </row>
+    <row r="562" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A562">
+        <v>376</v>
+      </c>
+      <c r="B562" t="s">
+        <v>72</v>
+      </c>
+      <c r="C562" s="2">
+        <v>47848</v>
+      </c>
+      <c r="D562">
+        <v>2030</v>
+      </c>
+      <c r="E562" t="s">
+        <v>20</v>
+      </c>
+      <c r="F562" t="s">
+        <v>89</v>
+      </c>
+      <c r="G562">
+        <v>56401.09</v>
+      </c>
+      <c r="H562">
+        <v>53017.03</v>
+      </c>
+      <c r="I562">
+        <v>59785.16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Prospectiva/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1206" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDD15E09-4F75-4AA4-9CCF-B027C0093CB2}"/>
+  <xr:revisionPtr revIDLastSave="1219" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA794EB9-7572-453E-944A-9BAB9D934927}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Proyecciones" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$I$557</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyecciones!$A$1:$I$562</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1887" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1902" uniqueCount="90">
   <si>
     <t>Id</t>
   </si>
@@ -716,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}">
-  <dimension ref="A1:I562"/>
+  <dimension ref="A1:I567"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
@@ -17052,6 +17052,151 @@
         <v>59785.16</v>
       </c>
     </row>
+    <row r="563" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A563">
+        <v>207</v>
+      </c>
+      <c r="B563" t="s">
+        <v>36</v>
+      </c>
+      <c r="C563" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D563">
+        <v>2026</v>
+      </c>
+      <c r="E563" t="s">
+        <v>12</v>
+      </c>
+      <c r="F563" t="s">
+        <v>89</v>
+      </c>
+      <c r="G563">
+        <v>186914.73</v>
+      </c>
+      <c r="H563">
+        <v>177195.16</v>
+      </c>
+      <c r="I563">
+        <v>196634.29</v>
+      </c>
+    </row>
+    <row r="564" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A564">
+        <v>207</v>
+      </c>
+      <c r="B564" t="s">
+        <v>36</v>
+      </c>
+      <c r="C564" s="2">
+        <v>46752</v>
+      </c>
+      <c r="D564">
+        <v>2027</v>
+      </c>
+      <c r="E564" t="s">
+        <v>14</v>
+      </c>
+      <c r="F564" t="s">
+        <v>89</v>
+      </c>
+      <c r="G564">
+        <v>196895.97</v>
+      </c>
+      <c r="H564">
+        <v>186263.59</v>
+      </c>
+      <c r="I564">
+        <v>207528.36</v>
+      </c>
+    </row>
+    <row r="565" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A565">
+        <v>207</v>
+      </c>
+      <c r="B565" t="s">
+        <v>36</v>
+      </c>
+      <c r="C565" s="2">
+        <v>47118</v>
+      </c>
+      <c r="D565">
+        <v>2028</v>
+      </c>
+      <c r="E565" t="s">
+        <v>16</v>
+      </c>
+      <c r="F565" t="s">
+        <v>89</v>
+      </c>
+      <c r="G565">
+        <v>207410.22</v>
+      </c>
+      <c r="H565">
+        <v>195795.25</v>
+      </c>
+      <c r="I565">
+        <v>219025.19</v>
+      </c>
+    </row>
+    <row r="566" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A566">
+        <v>207</v>
+      </c>
+      <c r="B566" t="s">
+        <v>36</v>
+      </c>
+      <c r="C566" s="2">
+        <v>47483</v>
+      </c>
+      <c r="D566">
+        <v>2029</v>
+      </c>
+      <c r="E566" t="s">
+        <v>18</v>
+      </c>
+      <c r="F566" t="s">
+        <v>89</v>
+      </c>
+      <c r="G566">
+        <v>218485.92</v>
+      </c>
+      <c r="H566">
+        <v>205813.74</v>
+      </c>
+      <c r="I566">
+        <v>231158.11</v>
+      </c>
+    </row>
+    <row r="567" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A567">
+        <v>207</v>
+      </c>
+      <c r="B567" t="s">
+        <v>36</v>
+      </c>
+      <c r="C567" s="2">
+        <v>47848</v>
+      </c>
+      <c r="D567">
+        <v>2030</v>
+      </c>
+      <c r="E567" t="s">
+        <v>20</v>
+      </c>
+      <c r="F567" t="s">
+        <v>89</v>
+      </c>
+      <c r="G567">
+        <v>230153.07</v>
+      </c>
+      <c r="H567">
+        <v>216343.89</v>
+      </c>
+      <c r="I567">
+        <v>243962.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/Proyecciones_Multimodelo.xlsx
+++ b/Data/Proyecciones_Multimodelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Prospectiva/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1219" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA794EB9-7572-453E-944A-9BAB9D934927}"/>
+  <xr:revisionPtr revIDLastSave="1241" documentId="8_{44BC8EE8-0004-4F82-B9F9-910542D6C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21E91BAB-6DF8-475A-9F43-650D1B0AE027}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E56FC6A2-DA73-40EE-B621-BA207259297A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1902" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1922" uniqueCount="92">
   <si>
     <t>Id</t>
   </si>
@@ -309,6 +309,12 @@
   </si>
   <si>
     <t>Prophet</t>
+  </si>
+  <si>
+    <t>Prov-1</t>
+  </si>
+  <si>
+    <t>Total Programas</t>
   </si>
 </sst>
 </file>
@@ -716,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F5ABF9-7414-4626-A0F7-29EA0F0D3250}">
-  <dimension ref="A1:I567"/>
+  <dimension ref="A1:I572"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
@@ -17197,6 +17203,151 @@
         <v>243962.26</v>
       </c>
     </row>
+    <row r="568" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A568" t="s">
+        <v>90</v>
+      </c>
+      <c r="B568" t="s">
+        <v>91</v>
+      </c>
+      <c r="C568" s="2">
+        <v>46387</v>
+      </c>
+      <c r="D568">
+        <v>2026</v>
+      </c>
+      <c r="E568" t="s">
+        <v>12</v>
+      </c>
+      <c r="F568" t="s">
+        <v>86</v>
+      </c>
+      <c r="G568">
+        <v>113</v>
+      </c>
+      <c r="H568">
+        <v>108</v>
+      </c>
+      <c r="I568">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="569" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A569" t="s">
+        <v>90</v>
+      </c>
+      <c r="B569" t="s">
+        <v>91</v>
+      </c>
+      <c r="C569" s="2">
+        <v>46752</v>
+      </c>
+      <c r="D569">
+        <v>2027</v>
+      </c>
+      <c r="E569" t="s">
+        <v>14</v>
+      </c>
+      <c r="F569" t="s">
+        <v>86</v>
+      </c>
+      <c r="G569">
+        <v>116</v>
+      </c>
+      <c r="H569">
+        <v>111</v>
+      </c>
+      <c r="I569">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="570" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A570" t="s">
+        <v>90</v>
+      </c>
+      <c r="B570" t="s">
+        <v>91</v>
+      </c>
+      <c r="C570" s="2">
+        <v>47118</v>
+      </c>
+      <c r="D570">
+        <v>2028</v>
+      </c>
+      <c r="E570" t="s">
+        <v>16</v>
+      </c>
+      <c r="F570" t="s">
+        <v>86</v>
+      </c>
+      <c r="G570">
+        <v>119</v>
+      </c>
+      <c r="H570">
+        <v>114</v>
+      </c>
+      <c r="I570">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="571" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A571" t="s">
+        <v>90</v>
+      </c>
+      <c r="B571" t="s">
+        <v>91</v>
+      </c>
+      <c r="C571" s="2">
+        <v>47483</v>
+      </c>
+      <c r="D571">
+        <v>2029</v>
+      </c>
+      <c r="E571" t="s">
+        <v>18</v>
+      </c>
+      <c r="F571" t="s">
+        <v>86</v>
+      </c>
+      <c r="G571">
+        <v>122</v>
+      </c>
+      <c r="H571">
+        <v>117</v>
+      </c>
+      <c r="I571">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="572" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A572" t="s">
+        <v>90</v>
+      </c>
+      <c r="B572" t="s">
+        <v>91</v>
+      </c>
+      <c r="C572" s="2">
+        <v>47848</v>
+      </c>
+      <c r="D572">
+        <v>2030</v>
+      </c>
+      <c r="E572" t="s">
+        <v>20</v>
+      </c>
+      <c r="F572" t="s">
+        <v>86</v>
+      </c>
+      <c r="G572">
+        <v>125</v>
+      </c>
+      <c r="H572">
+        <v>120</v>
+      </c>
+      <c r="I572">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
